--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J381"/>
+  <dimension ref="A1:J386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E12" t="n">
-        <v>10.756</v>
+        <v>105.22</v>
       </c>
       <c r="F12" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G12" t="n">
-        <v>32.27</v>
+        <v>105.22</v>
       </c>
       <c r="H12" t="n">
-        <v>1.11</v>
+        <v>5.13</v>
       </c>
       <c r="I12" t="n">
-        <v>3.56</v>
+        <v>5.13</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E13" t="n">
-        <v>6.788</v>
+        <v>41.121</v>
       </c>
       <c r="F13" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G13" t="n">
-        <v>61.09</v>
+        <v>164.48</v>
       </c>
       <c r="H13" t="n">
-        <v>4.94</v>
+        <v>25.46</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>18.31</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E14" t="n">
-        <v>21.907</v>
+        <v>10.756</v>
       </c>
       <c r="F14" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G14" t="n">
-        <v>65.72</v>
+        <v>32.27</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>3.56</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E15" t="n">
-        <v>41.121</v>
+        <v>6.788</v>
       </c>
       <c r="F15" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G15" t="n">
-        <v>164.48</v>
+        <v>61.09</v>
       </c>
       <c r="H15" t="n">
-        <v>25.46</v>
+        <v>4.94</v>
       </c>
       <c r="I15" t="n">
-        <v>18.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E16" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F16" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G16" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H16" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1158,29 +1158,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E22" t="n">
-        <v>21.669</v>
+        <v>105.78</v>
       </c>
       <c r="F22" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G22" t="n">
-        <v>65.01000000000001</v>
+        <v>105.78</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.66</v>
+        <v>5.69</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.01</v>
+        <v>5.68</v>
       </c>
       <c r="J22" t="n">
         <v>7.91</v>
@@ -1192,29 +1192,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E23" t="n">
-        <v>10.536</v>
+        <v>6.799</v>
       </c>
       <c r="F23" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G23" t="n">
-        <v>31.61</v>
+        <v>61.19</v>
       </c>
       <c r="H23" t="n">
-        <v>0.45</v>
+        <v>5.04</v>
       </c>
       <c r="I23" t="n">
-        <v>1.44</v>
+        <v>8.98</v>
       </c>
       <c r="J23" t="n">
         <v>7.91</v>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E24" t="n">
-        <v>6.799</v>
+        <v>41.336</v>
       </c>
       <c r="F24" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G24" t="n">
-        <v>61.19</v>
+        <v>165.34</v>
       </c>
       <c r="H24" t="n">
-        <v>5.04</v>
+        <v>26.32</v>
       </c>
       <c r="I24" t="n">
-        <v>8.98</v>
+        <v>18.93</v>
       </c>
       <c r="J24" t="n">
         <v>7.91</v>
@@ -1260,29 +1260,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E25" t="n">
-        <v>41.336</v>
+        <v>21.669</v>
       </c>
       <c r="F25" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G25" t="n">
-        <v>165.34</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>26.32</v>
+        <v>-0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>18.93</v>
+        <v>-1.01</v>
       </c>
       <c r="J25" t="n">
         <v>7.91</v>
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E26" t="n">
-        <v>105.78</v>
+        <v>10.536</v>
       </c>
       <c r="F26" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G26" t="n">
-        <v>105.78</v>
+        <v>31.61</v>
       </c>
       <c r="H26" t="n">
-        <v>5.69</v>
+        <v>0.45</v>
       </c>
       <c r="I26" t="n">
-        <v>5.68</v>
+        <v>1.44</v>
       </c>
       <c r="J26" t="n">
         <v>7.91</v>
@@ -1498,29 +1498,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E32" t="n">
-        <v>22.053</v>
+        <v>103.08</v>
       </c>
       <c r="F32" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G32" t="n">
-        <v>66.16</v>
+        <v>103.08</v>
       </c>
       <c r="H32" t="n">
-        <v>0.49</v>
+        <v>2.99</v>
       </c>
       <c r="I32" t="n">
-        <v>0.75</v>
+        <v>2.99</v>
       </c>
       <c r="J32" t="n">
         <v>7.91</v>
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E33" t="n">
-        <v>10.714</v>
+        <v>38.849</v>
       </c>
       <c r="F33" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G33" t="n">
-        <v>32.14</v>
+        <v>155.4</v>
       </c>
       <c r="H33" t="n">
-        <v>0.98</v>
+        <v>16.38</v>
       </c>
       <c r="I33" t="n">
-        <v>3.15</v>
+        <v>11.78</v>
       </c>
       <c r="J33" t="n">
         <v>7.91</v>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E34" t="n">
-        <v>38.849</v>
+        <v>6.762</v>
       </c>
       <c r="F34" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G34" t="n">
-        <v>155.4</v>
+        <v>60.86</v>
       </c>
       <c r="H34" t="n">
-        <v>16.38</v>
+        <v>4.71</v>
       </c>
       <c r="I34" t="n">
-        <v>11.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>7.91</v>
@@ -1600,29 +1600,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E35" t="n">
-        <v>6.762</v>
+        <v>22.053</v>
       </c>
       <c r="F35" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G35" t="n">
-        <v>60.86</v>
+        <v>66.16</v>
       </c>
       <c r="H35" t="n">
-        <v>4.71</v>
+        <v>0.49</v>
       </c>
       <c r="I35" t="n">
-        <v>8.390000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J35" t="n">
         <v>7.91</v>
@@ -1634,29 +1634,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E36" t="n">
-        <v>103.08</v>
+        <v>10.714</v>
       </c>
       <c r="F36" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G36" t="n">
-        <v>103.08</v>
+        <v>32.14</v>
       </c>
       <c r="H36" t="n">
-        <v>2.99</v>
+        <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E42" t="n">
-        <v>10.61</v>
+        <v>6.629</v>
       </c>
       <c r="F42" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G42" t="n">
-        <v>31.83</v>
+        <v>59.66</v>
       </c>
       <c r="H42" t="n">
-        <v>0.67</v>
+        <v>3.51</v>
       </c>
       <c r="I42" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E43" t="n">
-        <v>100.06</v>
+        <v>10.61</v>
       </c>
       <c r="F43" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G43" t="n">
-        <v>100.06</v>
+        <v>31.83</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.03</v>
+        <v>0.67</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.03</v>
+        <v>2.15</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E44" t="n">
-        <v>22</v>
+        <v>100.06</v>
       </c>
       <c r="F44" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G44" t="n">
-        <v>66</v>
+        <v>100.06</v>
       </c>
       <c r="H44" t="n">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E45" t="n">
-        <v>6.629</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G45" t="n">
-        <v>59.66</v>
+        <v>66</v>
       </c>
       <c r="H45" t="n">
-        <v>3.51</v>
+        <v>0.33</v>
       </c>
       <c r="I45" t="n">
-        <v>6.25</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -2008,29 +2008,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E47" t="n">
-        <v>99.83</v>
+        <v>10.562</v>
       </c>
       <c r="F47" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G47" t="n">
-        <v>99.83</v>
+        <v>31.69</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.26</v>
+        <v>0.53</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.26</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>7.91</v>
@@ -2042,29 +2042,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E48" t="n">
-        <v>21.778</v>
+        <v>6.622</v>
       </c>
       <c r="F48" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G48" t="n">
-        <v>65.33</v>
+        <v>59.6</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.34</v>
+        <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.52</v>
+        <v>6.14</v>
       </c>
       <c r="J48" t="n">
         <v>7.91</v>
@@ -2076,29 +2076,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E49" t="n">
-        <v>6.622</v>
+        <v>38.312</v>
       </c>
       <c r="F49" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G49" t="n">
-        <v>59.6</v>
+        <v>153.25</v>
       </c>
       <c r="H49" t="n">
-        <v>3.45</v>
+        <v>14.23</v>
       </c>
       <c r="I49" t="n">
-        <v>6.14</v>
+        <v>10.24</v>
       </c>
       <c r="J49" t="n">
         <v>7.91</v>
@@ -2110,29 +2110,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E50" t="n">
-        <v>38.312</v>
+        <v>21.778</v>
       </c>
       <c r="F50" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G50" t="n">
-        <v>153.25</v>
+        <v>65.33</v>
       </c>
       <c r="H50" t="n">
-        <v>14.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I50" t="n">
-        <v>10.24</v>
+        <v>-0.52</v>
       </c>
       <c r="J50" t="n">
         <v>7.91</v>
@@ -2144,29 +2144,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E51" t="n">
-        <v>10.562</v>
+        <v>99.83</v>
       </c>
       <c r="F51" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G51" t="n">
-        <v>31.69</v>
+        <v>99.83</v>
       </c>
       <c r="H51" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>-0.26</v>
       </c>
       <c r="J51" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E62" t="n">
-        <v>105.5</v>
+        <v>10.712</v>
       </c>
       <c r="F62" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G62" t="n">
-        <v>105.5</v>
+        <v>32.14</v>
       </c>
       <c r="H62" t="n">
-        <v>5.41</v>
+        <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>5.41</v>
+        <v>3.15</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E63" t="n">
-        <v>41.064</v>
+        <v>22.7</v>
       </c>
       <c r="F63" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G63" t="n">
-        <v>164.26</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>25.24</v>
+        <v>2.43</v>
       </c>
       <c r="I63" t="n">
-        <v>18.16</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E64" t="n">
-        <v>6.817</v>
+        <v>105.5</v>
       </c>
       <c r="F64" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G64" t="n">
-        <v>61.35</v>
+        <v>105.5</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>5.41</v>
       </c>
       <c r="I64" t="n">
-        <v>9.26</v>
+        <v>5.41</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E65" t="n">
-        <v>22.7</v>
+        <v>41.064</v>
       </c>
       <c r="F65" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G65" t="n">
-        <v>68.09999999999999</v>
+        <v>164.26</v>
       </c>
       <c r="H65" t="n">
-        <v>2.43</v>
+        <v>25.24</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>18.16</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E66" t="n">
-        <v>10.712</v>
+        <v>6.817</v>
       </c>
       <c r="F66" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G66" t="n">
-        <v>32.14</v>
+        <v>61.35</v>
       </c>
       <c r="H66" t="n">
-        <v>0.98</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>3.15</v>
+        <v>9.26</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E72" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F72" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G72" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H72" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I72" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E73" t="n">
-        <v>104.22</v>
+        <v>10.892</v>
       </c>
       <c r="F73" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G73" t="n">
-        <v>104.22</v>
+        <v>32.68</v>
       </c>
       <c r="H73" t="n">
-        <v>4.13</v>
+        <v>1.52</v>
       </c>
       <c r="I73" t="n">
-        <v>4.13</v>
+        <v>4.88</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E75" t="n">
-        <v>41.15</v>
+        <v>104.22</v>
       </c>
       <c r="F75" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G75" t="n">
-        <v>164.6</v>
+        <v>104.22</v>
       </c>
       <c r="H75" t="n">
-        <v>25.58</v>
+        <v>4.13</v>
       </c>
       <c r="I75" t="n">
-        <v>18.4</v>
+        <v>4.13</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -2994,29 +2994,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E76" t="n">
-        <v>10.892</v>
+        <v>6.811</v>
       </c>
       <c r="F76" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G76" t="n">
-        <v>32.68</v>
+        <v>61.3</v>
       </c>
       <c r="H76" t="n">
-        <v>1.52</v>
+        <v>5.15</v>
       </c>
       <c r="I76" t="n">
-        <v>4.88</v>
+        <v>9.17</v>
       </c>
       <c r="J76" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E82" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F82" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G82" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I82" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E83" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F83" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G83" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H83" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E84" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F84" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G84" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H84" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I84" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E85" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F85" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G85" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I85" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E86" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F86" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G86" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H86" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I86" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E92" t="n">
-        <v>6.797</v>
+        <v>103.88</v>
       </c>
       <c r="F92" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G92" t="n">
-        <v>61.17</v>
+        <v>103.88</v>
       </c>
       <c r="H92" t="n">
-        <v>5.02</v>
+        <v>3.79</v>
       </c>
       <c r="I92" t="n">
-        <v>8.94</v>
+        <v>3.79</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E93" t="n">
-        <v>10.876</v>
+        <v>6.797</v>
       </c>
       <c r="F93" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G93" t="n">
-        <v>32.63</v>
+        <v>61.17</v>
       </c>
       <c r="H93" t="n">
-        <v>1.47</v>
+        <v>5.02</v>
       </c>
       <c r="I93" t="n">
-        <v>4.72</v>
+        <v>8.94</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E94" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F94" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G94" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H94" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I94" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E95" t="n">
-        <v>103.88</v>
+        <v>40.575</v>
       </c>
       <c r="F95" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G95" t="n">
-        <v>103.88</v>
+        <v>162.3</v>
       </c>
       <c r="H95" t="n">
-        <v>3.79</v>
+        <v>23.28</v>
       </c>
       <c r="I95" t="n">
-        <v>3.79</v>
+        <v>16.75</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E97" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F97" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G97" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H97" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I97" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E98" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F98" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G98" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H98" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I98" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E99" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F99" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G99" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H99" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E100" t="n">
-        <v>6.839</v>
+        <v>40.65</v>
       </c>
       <c r="F100" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G100" t="n">
-        <v>61.55</v>
+        <v>162.6</v>
       </c>
       <c r="H100" t="n">
-        <v>5.4</v>
+        <v>23.58</v>
       </c>
       <c r="I100" t="n">
-        <v>9.619999999999999</v>
+        <v>16.96</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E101" t="n">
-        <v>23.35</v>
+        <v>104.22</v>
       </c>
       <c r="F101" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G101" t="n">
-        <v>70.05</v>
+        <v>104.22</v>
       </c>
       <c r="H101" t="n">
-        <v>4.38</v>
+        <v>4.13</v>
       </c>
       <c r="I101" t="n">
-        <v>6.67</v>
+        <v>4.13</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E107" t="n">
-        <v>40.5</v>
+        <v>6.785</v>
       </c>
       <c r="F107" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G107" t="n">
-        <v>162</v>
+        <v>61.06</v>
       </c>
       <c r="H107" t="n">
-        <v>22.98</v>
+        <v>4.91</v>
       </c>
       <c r="I107" t="n">
-        <v>16.53</v>
+        <v>8.74</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E108" t="n">
-        <v>23.33</v>
+        <v>103.14</v>
       </c>
       <c r="F108" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G108" t="n">
-        <v>69.98999999999999</v>
+        <v>103.14</v>
       </c>
       <c r="H108" t="n">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="I108" t="n">
-        <v>6.58</v>
+        <v>3.05</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E110" t="n">
-        <v>103.14</v>
+        <v>23.33</v>
       </c>
       <c r="F110" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G110" t="n">
-        <v>103.14</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>3.05</v>
+        <v>4.32</v>
       </c>
       <c r="I110" t="n">
-        <v>3.05</v>
+        <v>6.58</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E111" t="n">
-        <v>6.785</v>
+        <v>40.5</v>
       </c>
       <c r="F111" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G111" t="n">
-        <v>61.06</v>
+        <v>162</v>
       </c>
       <c r="H111" t="n">
-        <v>4.91</v>
+        <v>22.98</v>
       </c>
       <c r="I111" t="n">
-        <v>8.74</v>
+        <v>16.53</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E117" t="n">
-        <v>105.96</v>
+        <v>10.756</v>
       </c>
       <c r="F117" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G117" t="n">
-        <v>105.96</v>
+        <v>32.27</v>
       </c>
       <c r="H117" t="n">
-        <v>5.87</v>
+        <v>1.11</v>
       </c>
       <c r="I117" t="n">
-        <v>5.86</v>
+        <v>3.56</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D118" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E118" t="n">
-        <v>41</v>
+        <v>6.861</v>
       </c>
       <c r="F118" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G118" t="n">
-        <v>164</v>
+        <v>61.75</v>
       </c>
       <c r="H118" t="n">
-        <v>24.98</v>
+        <v>5.6</v>
       </c>
       <c r="I118" t="n">
-        <v>17.97</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E119" t="n">
-        <v>6.861</v>
+        <v>23.145</v>
       </c>
       <c r="F119" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G119" t="n">
-        <v>61.75</v>
+        <v>69.44</v>
       </c>
       <c r="H119" t="n">
-        <v>5.6</v>
+        <v>3.77</v>
       </c>
       <c r="I119" t="n">
-        <v>9.970000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E120" t="n">
-        <v>10.756</v>
+        <v>105.96</v>
       </c>
       <c r="F120" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G120" t="n">
-        <v>32.27</v>
+        <v>105.96</v>
       </c>
       <c r="H120" t="n">
-        <v>1.11</v>
+        <v>5.87</v>
       </c>
       <c r="I120" t="n">
-        <v>3.56</v>
+        <v>5.86</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E121" t="n">
-        <v>23.145</v>
+        <v>41</v>
       </c>
       <c r="F121" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G121" t="n">
-        <v>69.44</v>
+        <v>164</v>
       </c>
       <c r="H121" t="n">
-        <v>3.77</v>
+        <v>24.98</v>
       </c>
       <c r="I121" t="n">
-        <v>5.74</v>
+        <v>17.97</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D127" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E127" t="n">
-        <v>39.36</v>
+        <v>6.868</v>
       </c>
       <c r="F127" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G127" t="n">
-        <v>157.44</v>
+        <v>61.81</v>
       </c>
       <c r="H127" t="n">
-        <v>18.42</v>
+        <v>5.66</v>
       </c>
       <c r="I127" t="n">
-        <v>13.25</v>
+        <v>10.08</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E128" t="n">
-        <v>103.46</v>
+        <v>23.17</v>
       </c>
       <c r="F128" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G128" t="n">
-        <v>103.46</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.37</v>
+        <v>3.84</v>
       </c>
       <c r="I128" t="n">
-        <v>3.37</v>
+        <v>5.85</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4796,29 +4796,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E129" t="n">
-        <v>23.17</v>
+        <v>11.458</v>
       </c>
       <c r="F129" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G129" t="n">
-        <v>69.51000000000001</v>
+        <v>34.37</v>
       </c>
       <c r="H129" t="n">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="I129" t="n">
-        <v>5.85</v>
+        <v>10.3</v>
       </c>
       <c r="J129" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E130" t="n">
-        <v>6.868</v>
+        <v>39.36</v>
       </c>
       <c r="F130" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G130" t="n">
-        <v>61.81</v>
+        <v>157.44</v>
       </c>
       <c r="H130" t="n">
-        <v>5.66</v>
+        <v>18.42</v>
       </c>
       <c r="I130" t="n">
-        <v>10.08</v>
+        <v>13.25</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E131" t="n">
-        <v>11.458</v>
+        <v>103.46</v>
       </c>
       <c r="F131" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G131" t="n">
-        <v>34.37</v>
+        <v>103.46</v>
       </c>
       <c r="H131" t="n">
-        <v>3.21</v>
+        <v>3.37</v>
       </c>
       <c r="I131" t="n">
-        <v>10.3</v>
+        <v>3.37</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E142" t="n">
-        <v>38.89</v>
+        <v>11.498</v>
       </c>
       <c r="F142" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G142" t="n">
-        <v>155.56</v>
+        <v>34.49</v>
       </c>
       <c r="H142" t="n">
-        <v>16.54</v>
+        <v>3.33</v>
       </c>
       <c r="I142" t="n">
-        <v>11.9</v>
+        <v>10.69</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E143" t="n">
-        <v>102.06</v>
+        <v>23.135</v>
       </c>
       <c r="F143" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G143" t="n">
-        <v>102.06</v>
+        <v>69.41</v>
       </c>
       <c r="H143" t="n">
-        <v>1.97</v>
+        <v>3.74</v>
       </c>
       <c r="I143" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E144" t="n">
-        <v>23.135</v>
+        <v>6.878</v>
       </c>
       <c r="F144" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G144" t="n">
-        <v>69.41</v>
+        <v>61.9</v>
       </c>
       <c r="H144" t="n">
-        <v>3.74</v>
+        <v>5.75</v>
       </c>
       <c r="I144" t="n">
-        <v>5.7</v>
+        <v>10.24</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E145" t="n">
-        <v>11.498</v>
+        <v>38.89</v>
       </c>
       <c r="F145" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G145" t="n">
-        <v>34.49</v>
+        <v>155.56</v>
       </c>
       <c r="H145" t="n">
-        <v>3.33</v>
+        <v>16.54</v>
       </c>
       <c r="I145" t="n">
-        <v>10.69</v>
+        <v>11.9</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E146" t="n">
-        <v>6.878</v>
+        <v>102.06</v>
       </c>
       <c r="F146" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G146" t="n">
-        <v>61.9</v>
+        <v>102.06</v>
       </c>
       <c r="H146" t="n">
-        <v>5.75</v>
+        <v>1.97</v>
       </c>
       <c r="I146" t="n">
-        <v>10.24</v>
+        <v>1.97</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E152" t="n">
-        <v>6.893</v>
+        <v>23.045</v>
       </c>
       <c r="F152" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G152" t="n">
-        <v>62.04</v>
+        <v>69.14</v>
       </c>
       <c r="H152" t="n">
-        <v>5.89</v>
+        <v>3.47</v>
       </c>
       <c r="I152" t="n">
-        <v>10.49</v>
+        <v>5.28</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E153" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F153" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G153" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H153" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I153" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E154" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F154" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G154" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H154" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I154" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D155" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E155" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F155" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G155" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H155" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I155" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E156" t="n">
-        <v>104.12</v>
+        <v>11.034</v>
       </c>
       <c r="F156" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G156" t="n">
-        <v>104.12</v>
+        <v>33.1</v>
       </c>
       <c r="H156" t="n">
-        <v>4.03</v>
+        <v>1.94</v>
       </c>
       <c r="I156" t="n">
-        <v>4.03</v>
+        <v>6.23</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5748,29 +5748,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E157" t="n">
-        <v>104.5</v>
+        <v>10.92</v>
       </c>
       <c r="F157" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G157" t="n">
-        <v>104.5</v>
+        <v>32.76</v>
       </c>
       <c r="H157" t="n">
-        <v>4.41</v>
+        <v>1.6</v>
       </c>
       <c r="I157" t="n">
-        <v>4.41</v>
+        <v>5.13</v>
       </c>
       <c r="J157" t="n">
         <v>7.91</v>
@@ -5782,29 +5782,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E158" t="n">
-        <v>10.92</v>
+        <v>40.015</v>
       </c>
       <c r="F158" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G158" t="n">
-        <v>32.76</v>
+        <v>160.06</v>
       </c>
       <c r="H158" t="n">
-        <v>1.6</v>
+        <v>21.04</v>
       </c>
       <c r="I158" t="n">
-        <v>5.13</v>
+        <v>15.13</v>
       </c>
       <c r="J158" t="n">
         <v>7.91</v>
@@ -5816,29 +5816,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E159" t="n">
-        <v>40.015</v>
+        <v>23.08</v>
       </c>
       <c r="F159" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G159" t="n">
-        <v>160.06</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H159" t="n">
-        <v>21.04</v>
+        <v>3.57</v>
       </c>
       <c r="I159" t="n">
-        <v>15.13</v>
+        <v>5.44</v>
       </c>
       <c r="J159" t="n">
         <v>7.91</v>
@@ -5850,29 +5850,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D160" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E160" t="n">
-        <v>23.08</v>
+        <v>6.913</v>
       </c>
       <c r="F160" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G160" t="n">
-        <v>69.23999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="H160" t="n">
-        <v>3.57</v>
+        <v>6.07</v>
       </c>
       <c r="I160" t="n">
-        <v>5.44</v>
+        <v>10.81</v>
       </c>
       <c r="J160" t="n">
         <v>7.91</v>
@@ -5884,29 +5884,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E161" t="n">
-        <v>6.913</v>
+        <v>104.5</v>
       </c>
       <c r="F161" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G161" t="n">
-        <v>62.22</v>
+        <v>104.5</v>
       </c>
       <c r="H161" t="n">
-        <v>6.07</v>
+        <v>4.41</v>
       </c>
       <c r="I161" t="n">
-        <v>10.81</v>
+        <v>4.41</v>
       </c>
       <c r="J161" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D167" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E167" t="n">
-        <v>10.726</v>
+        <v>6.911</v>
       </c>
       <c r="F167" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G167" t="n">
-        <v>32.18</v>
+        <v>62.2</v>
       </c>
       <c r="H167" t="n">
-        <v>1.02</v>
+        <v>6.05</v>
       </c>
       <c r="I167" t="n">
-        <v>3.27</v>
+        <v>10.77</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E168" t="n">
-        <v>22.92</v>
+        <v>103.98</v>
       </c>
       <c r="F168" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G168" t="n">
-        <v>68.76000000000001</v>
+        <v>103.98</v>
       </c>
       <c r="H168" t="n">
-        <v>3.09</v>
+        <v>3.89</v>
       </c>
       <c r="I168" t="n">
-        <v>4.71</v>
+        <v>3.89</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E170" t="n">
-        <v>6.911</v>
+        <v>10.726</v>
       </c>
       <c r="F170" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G170" t="n">
-        <v>62.2</v>
+        <v>32.18</v>
       </c>
       <c r="H170" t="n">
-        <v>6.05</v>
+        <v>1.02</v>
       </c>
       <c r="I170" t="n">
-        <v>10.77</v>
+        <v>3.27</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E171" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F171" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G171" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H171" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I171" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E177" t="n">
-        <v>38.245</v>
+        <v>6.922</v>
       </c>
       <c r="F177" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G177" t="n">
-        <v>152.98</v>
+        <v>62.3</v>
       </c>
       <c r="H177" t="n">
-        <v>13.96</v>
+        <v>6.15</v>
       </c>
       <c r="I177" t="n">
-        <v>10.04</v>
+        <v>10.95</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E178" t="n">
-        <v>10.642</v>
+        <v>102.54</v>
       </c>
       <c r="F178" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G178" t="n">
-        <v>31.93</v>
+        <v>102.54</v>
       </c>
       <c r="H178" t="n">
-        <v>0.77</v>
+        <v>2.45</v>
       </c>
       <c r="I178" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E179" t="n">
-        <v>102.54</v>
+        <v>22.95</v>
       </c>
       <c r="F179" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G179" t="n">
-        <v>102.54</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="I179" t="n">
-        <v>2.45</v>
+        <v>4.84</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E180" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F180" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G180" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H180" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I180" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E181" t="n">
-        <v>22.95</v>
+        <v>10.642</v>
       </c>
       <c r="F181" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G181" t="n">
-        <v>68.84999999999999</v>
+        <v>31.93</v>
       </c>
       <c r="H181" t="n">
-        <v>3.18</v>
+        <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>4.84</v>
+        <v>2.47</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E192" t="n">
-        <v>102.46</v>
+        <v>10.792</v>
       </c>
       <c r="F192" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G192" t="n">
-        <v>102.46</v>
+        <v>32.38</v>
       </c>
       <c r="H192" t="n">
-        <v>2.37</v>
+        <v>1.22</v>
       </c>
       <c r="I192" t="n">
-        <v>2.37</v>
+        <v>3.92</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D193" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E193" t="n">
-        <v>22.82</v>
+        <v>6.894</v>
       </c>
       <c r="F193" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G193" t="n">
-        <v>68.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="H193" t="n">
-        <v>2.79</v>
+        <v>5.9</v>
       </c>
       <c r="I193" t="n">
-        <v>4.25</v>
+        <v>10.51</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E195" t="n">
-        <v>6.894</v>
+        <v>22.82</v>
       </c>
       <c r="F195" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G195" t="n">
-        <v>62.05</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>5.9</v>
+        <v>2.79</v>
       </c>
       <c r="I195" t="n">
-        <v>10.51</v>
+        <v>4.25</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7074,29 +7074,29 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E196" t="n">
-        <v>10.792</v>
+        <v>102.46</v>
       </c>
       <c r="F196" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G196" t="n">
-        <v>32.38</v>
+        <v>102.46</v>
       </c>
       <c r="H196" t="n">
-        <v>1.22</v>
+        <v>2.37</v>
       </c>
       <c r="I196" t="n">
-        <v>3.92</v>
+        <v>2.37</v>
       </c>
       <c r="J196" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D202" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E202" t="n">
-        <v>38.04</v>
+        <v>6.822</v>
       </c>
       <c r="F202" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G202" t="n">
-        <v>152.16</v>
+        <v>61.4</v>
       </c>
       <c r="H202" t="n">
-        <v>13.14</v>
+        <v>5.25</v>
       </c>
       <c r="I202" t="n">
-        <v>9.449999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E203" t="n">
-        <v>11.044</v>
+        <v>100.08</v>
       </c>
       <c r="F203" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G203" t="n">
-        <v>33.13</v>
+        <v>100.08</v>
       </c>
       <c r="H203" t="n">
-        <v>1.97</v>
+        <v>-0.01</v>
       </c>
       <c r="I203" t="n">
-        <v>6.32</v>
+        <v>-0.01</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D205" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E205" t="n">
-        <v>100.08</v>
+        <v>11.044</v>
       </c>
       <c r="F205" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G205" t="n">
-        <v>100.08</v>
+        <v>33.13</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.01</v>
+        <v>1.97</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.01</v>
+        <v>6.32</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D206" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E206" t="n">
-        <v>6.822</v>
+        <v>38.04</v>
       </c>
       <c r="F206" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G206" t="n">
-        <v>61.4</v>
+        <v>152.16</v>
       </c>
       <c r="H206" t="n">
-        <v>5.25</v>
+        <v>13.14</v>
       </c>
       <c r="I206" t="n">
-        <v>9.35</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J206" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D212" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E212" t="n">
-        <v>37.25</v>
+        <v>11.338</v>
       </c>
       <c r="F212" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G212" t="n">
-        <v>149</v>
+        <v>34.01</v>
       </c>
       <c r="H212" t="n">
-        <v>9.98</v>
+        <v>2.85</v>
       </c>
       <c r="I212" t="n">
-        <v>7.18</v>
+        <v>9.15</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E213" t="n">
-        <v>6.84</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G213" t="n">
-        <v>61.56</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>5.41</v>
+        <v>-1.8</v>
       </c>
       <c r="I213" t="n">
-        <v>9.630000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E214" t="n">
-        <v>98.29000000000001</v>
+        <v>22.885</v>
       </c>
       <c r="F214" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G214" t="n">
-        <v>98.29000000000001</v>
+        <v>68.66</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.8</v>
+        <v>2.99</v>
       </c>
       <c r="I214" t="n">
-        <v>-1.8</v>
+        <v>4.55</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D215" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E215" t="n">
-        <v>11.338</v>
+        <v>37.25</v>
       </c>
       <c r="F215" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G215" t="n">
-        <v>34.01</v>
+        <v>149</v>
       </c>
       <c r="H215" t="n">
-        <v>2.85</v>
+        <v>9.98</v>
       </c>
       <c r="I215" t="n">
-        <v>9.15</v>
+        <v>7.18</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7754,29 +7754,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E216" t="n">
-        <v>22.885</v>
+        <v>6.84</v>
       </c>
       <c r="F216" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G216" t="n">
-        <v>68.66</v>
+        <v>61.56</v>
       </c>
       <c r="H216" t="n">
-        <v>2.99</v>
+        <v>5.41</v>
       </c>
       <c r="I216" t="n">
-        <v>4.55</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J216" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D222" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E222" t="n">
-        <v>6.818</v>
+        <v>35.89</v>
       </c>
       <c r="F222" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G222" t="n">
-        <v>61.36</v>
+        <v>143.56</v>
       </c>
       <c r="H222" t="n">
-        <v>5.21</v>
+        <v>4.54</v>
       </c>
       <c r="I222" t="n">
-        <v>9.279999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C223" t="n">
         <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E223" t="n">
-        <v>23.12</v>
+        <v>11.5</v>
       </c>
       <c r="F223" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G223" t="n">
-        <v>69.36</v>
+        <v>34.5</v>
       </c>
       <c r="H223" t="n">
-        <v>3.69</v>
+        <v>3.34</v>
       </c>
       <c r="I223" t="n">
-        <v>5.62</v>
+        <v>10.72</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8026,29 +8026,29 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E224" t="n">
-        <v>11.5</v>
+        <v>96.67</v>
       </c>
       <c r="F224" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G224" t="n">
-        <v>34.5</v>
+        <v>96.67</v>
       </c>
       <c r="H224" t="n">
-        <v>3.34</v>
+        <v>-3.42</v>
       </c>
       <c r="I224" t="n">
-        <v>10.72</v>
+        <v>-3.42</v>
       </c>
       <c r="J224" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D225" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E225" t="n">
-        <v>35.89</v>
+        <v>6.818</v>
       </c>
       <c r="F225" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G225" t="n">
-        <v>143.56</v>
+        <v>61.36</v>
       </c>
       <c r="H225" t="n">
-        <v>4.54</v>
+        <v>5.21</v>
       </c>
       <c r="I225" t="n">
-        <v>3.27</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E226" t="n">
-        <v>96.67</v>
+        <v>23.12</v>
       </c>
       <c r="F226" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G226" t="n">
-        <v>96.67</v>
+        <v>69.36</v>
       </c>
       <c r="H226" t="n">
-        <v>-3.42</v>
+        <v>3.69</v>
       </c>
       <c r="I226" t="n">
-        <v>-3.42</v>
+        <v>5.62</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E237" t="n">
-        <v>99.84999999999999</v>
+        <v>23.245</v>
       </c>
       <c r="F237" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G237" t="n">
-        <v>99.84999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="H237" t="n">
-        <v>-0.24</v>
+        <v>4.06</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.24</v>
+        <v>6.18</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E238" t="n">
-        <v>37.315</v>
+        <v>6.914</v>
       </c>
       <c r="F238" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G238" t="n">
-        <v>149.26</v>
+        <v>62.23</v>
       </c>
       <c r="H238" t="n">
-        <v>10.24</v>
+        <v>6.08</v>
       </c>
       <c r="I238" t="n">
-        <v>7.37</v>
+        <v>10.83</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8536,29 +8536,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D239" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E239" t="n">
-        <v>6.914</v>
+        <v>11.842</v>
       </c>
       <c r="F239" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G239" t="n">
-        <v>62.23</v>
+        <v>35.53</v>
       </c>
       <c r="H239" t="n">
-        <v>6.08</v>
+        <v>4.37</v>
       </c>
       <c r="I239" t="n">
-        <v>10.83</v>
+        <v>14.02</v>
       </c>
       <c r="J239" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E240" t="n">
-        <v>23.245</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F240" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G240" t="n">
-        <v>69.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>4.06</v>
+        <v>-0.24</v>
       </c>
       <c r="I240" t="n">
-        <v>6.18</v>
+        <v>-0.24</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D241" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E241" t="n">
-        <v>11.842</v>
+        <v>37.315</v>
       </c>
       <c r="F241" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G241" t="n">
-        <v>35.53</v>
+        <v>149.26</v>
       </c>
       <c r="H241" t="n">
-        <v>4.37</v>
+        <v>10.24</v>
       </c>
       <c r="I241" t="n">
-        <v>14.02</v>
+        <v>7.37</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D247" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E247" t="n">
-        <v>23.28</v>
+        <v>7.032</v>
       </c>
       <c r="F247" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G247" t="n">
-        <v>69.84</v>
+        <v>63.29</v>
       </c>
       <c r="H247" t="n">
-        <v>4.17</v>
+        <v>7.14</v>
       </c>
       <c r="I247" t="n">
-        <v>6.35</v>
+        <v>12.72</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E248" t="n">
-        <v>12.18</v>
+        <v>103.2</v>
       </c>
       <c r="F248" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G248" t="n">
-        <v>36.54</v>
+        <v>103.2</v>
       </c>
       <c r="H248" t="n">
-        <v>5.38</v>
+        <v>3.11</v>
       </c>
       <c r="I248" t="n">
-        <v>17.27</v>
+        <v>3.11</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8876,29 +8876,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D249" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E249" t="n">
-        <v>103.2</v>
+        <v>38.435</v>
       </c>
       <c r="F249" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G249" t="n">
-        <v>103.2</v>
+        <v>153.74</v>
       </c>
       <c r="H249" t="n">
-        <v>3.11</v>
+        <v>14.72</v>
       </c>
       <c r="I249" t="n">
-        <v>3.11</v>
+        <v>10.59</v>
       </c>
       <c r="J249" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D250" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E250" t="n">
-        <v>7.032</v>
+        <v>23.28</v>
       </c>
       <c r="F250" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G250" t="n">
-        <v>63.29</v>
+        <v>69.84</v>
       </c>
       <c r="H250" t="n">
-        <v>7.14</v>
+        <v>4.17</v>
       </c>
       <c r="I250" t="n">
-        <v>12.72</v>
+        <v>6.35</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E251" t="n">
-        <v>38.435</v>
+        <v>12.18</v>
       </c>
       <c r="F251" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G251" t="n">
-        <v>153.74</v>
+        <v>36.54</v>
       </c>
       <c r="H251" t="n">
-        <v>14.72</v>
+        <v>5.38</v>
       </c>
       <c r="I251" t="n">
-        <v>10.59</v>
+        <v>17.27</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D252" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E252" t="n">
-        <v>12.128</v>
+        <v>38.095</v>
       </c>
       <c r="F252" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G252" t="n">
-        <v>36.38</v>
+        <v>152.38</v>
       </c>
       <c r="H252" t="n">
-        <v>5.22</v>
+        <v>13.36</v>
       </c>
       <c r="I252" t="n">
-        <v>16.75</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D253" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E253" t="n">
-        <v>38.095</v>
+        <v>7.05</v>
       </c>
       <c r="F253" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G253" t="n">
-        <v>152.38</v>
+        <v>63.45</v>
       </c>
       <c r="H253" t="n">
-        <v>13.36</v>
+        <v>7.3</v>
       </c>
       <c r="I253" t="n">
-        <v>9.609999999999999</v>
+        <v>13</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D254" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E254" t="n">
-        <v>7.05</v>
+        <v>23.315</v>
       </c>
       <c r="F254" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G254" t="n">
-        <v>63.45</v>
+        <v>69.95</v>
       </c>
       <c r="H254" t="n">
-        <v>7.3</v>
+        <v>4.28</v>
       </c>
       <c r="I254" t="n">
-        <v>13</v>
+        <v>6.52</v>
       </c>
       <c r="J254" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E255" t="n">
-        <v>23.315</v>
+        <v>103.18</v>
       </c>
       <c r="F255" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G255" t="n">
-        <v>69.95</v>
+        <v>103.18</v>
       </c>
       <c r="H255" t="n">
-        <v>4.28</v>
+        <v>3.09</v>
       </c>
       <c r="I255" t="n">
-        <v>6.52</v>
+        <v>3.09</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D256" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E256" t="n">
-        <v>103.18</v>
+        <v>12.128</v>
       </c>
       <c r="F256" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G256" t="n">
-        <v>103.18</v>
+        <v>36.38</v>
       </c>
       <c r="H256" t="n">
-        <v>3.09</v>
+        <v>5.22</v>
       </c>
       <c r="I256" t="n">
-        <v>3.09</v>
+        <v>16.75</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E262" t="n">
-        <v>38.23</v>
+        <v>102.84</v>
       </c>
       <c r="F262" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G262" t="n">
-        <v>152.92</v>
+        <v>102.84</v>
       </c>
       <c r="H262" t="n">
-        <v>13.9</v>
+        <v>2.75</v>
       </c>
       <c r="I262" t="n">
-        <v>10</v>
+        <v>2.75</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E263" t="n">
-        <v>7.055</v>
+        <v>12.23</v>
       </c>
       <c r="F263" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G263" t="n">
-        <v>63.49</v>
+        <v>36.69</v>
       </c>
       <c r="H263" t="n">
-        <v>7.34</v>
+        <v>5.53</v>
       </c>
       <c r="I263" t="n">
-        <v>13.07</v>
+        <v>17.75</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D265" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E265" t="n">
-        <v>102.84</v>
+        <v>38.23</v>
       </c>
       <c r="F265" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G265" t="n">
-        <v>102.84</v>
+        <v>152.92</v>
       </c>
       <c r="H265" t="n">
-        <v>2.75</v>
+        <v>13.9</v>
       </c>
       <c r="I265" t="n">
-        <v>2.75</v>
+        <v>10</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D266" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E266" t="n">
-        <v>12.23</v>
+        <v>7.055</v>
       </c>
       <c r="F266" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G266" t="n">
-        <v>36.69</v>
+        <v>63.49</v>
       </c>
       <c r="H266" t="n">
-        <v>5.53</v>
+        <v>7.34</v>
       </c>
       <c r="I266" t="n">
-        <v>17.75</v>
+        <v>13.07</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D272" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E272" t="n">
-        <v>39.325</v>
+        <v>12.308</v>
       </c>
       <c r="F272" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G272" t="n">
-        <v>157.3</v>
+        <v>36.92</v>
       </c>
       <c r="H272" t="n">
-        <v>18.28</v>
+        <v>5.76</v>
       </c>
       <c r="I272" t="n">
-        <v>13.15</v>
+        <v>18.49</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E273" t="n">
-        <v>23.135</v>
+        <v>104.54</v>
       </c>
       <c r="F273" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G273" t="n">
-        <v>69.41</v>
+        <v>104.54</v>
       </c>
       <c r="H273" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="I273" t="n">
-        <v>5.7</v>
+        <v>4.45</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9726,29 +9726,29 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D274" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E274" t="n">
-        <v>104.54</v>
+        <v>7.091</v>
       </c>
       <c r="F274" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G274" t="n">
-        <v>104.54</v>
+        <v>63.82</v>
       </c>
       <c r="H274" t="n">
-        <v>4.45</v>
+        <v>7.67</v>
       </c>
       <c r="I274" t="n">
-        <v>4.45</v>
+        <v>13.66</v>
       </c>
       <c r="J274" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D275" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E275" t="n">
-        <v>12.308</v>
+        <v>39.325</v>
       </c>
       <c r="F275" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G275" t="n">
-        <v>36.92</v>
+        <v>157.3</v>
       </c>
       <c r="H275" t="n">
-        <v>5.76</v>
+        <v>18.28</v>
       </c>
       <c r="I275" t="n">
-        <v>18.49</v>
+        <v>13.15</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D276" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E276" t="n">
-        <v>7.091</v>
+        <v>23.135</v>
       </c>
       <c r="F276" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G276" t="n">
-        <v>63.82</v>
+        <v>69.41</v>
       </c>
       <c r="H276" t="n">
-        <v>7.67</v>
+        <v>3.74</v>
       </c>
       <c r="I276" t="n">
-        <v>13.66</v>
+        <v>5.7</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -10168,29 +10168,29 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D287" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E287" t="n">
-        <v>12.292</v>
+        <v>6.983</v>
       </c>
       <c r="F287" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G287" t="n">
-        <v>36.88</v>
+        <v>62.85</v>
       </c>
       <c r="H287" t="n">
-        <v>5.72</v>
+        <v>6.7</v>
       </c>
       <c r="I287" t="n">
-        <v>18.36</v>
+        <v>11.93</v>
       </c>
       <c r="J287" t="n">
         <v>7.91</v>
@@ -10202,29 +10202,29 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D288" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E288" t="n">
-        <v>38.18</v>
+        <v>22.83</v>
       </c>
       <c r="F288" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G288" t="n">
-        <v>152.72</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H288" t="n">
-        <v>13.7</v>
+        <v>2.82</v>
       </c>
       <c r="I288" t="n">
-        <v>9.85</v>
+        <v>4.29</v>
       </c>
       <c r="J288" t="n">
         <v>7.91</v>
@@ -10236,29 +10236,29 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E289" t="n">
-        <v>22.83</v>
+        <v>102.22</v>
       </c>
       <c r="F289" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G289" t="n">
-        <v>68.48999999999999</v>
+        <v>102.22</v>
       </c>
       <c r="H289" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="I289" t="n">
-        <v>4.29</v>
+        <v>2.13</v>
       </c>
       <c r="J289" t="n">
         <v>7.91</v>
@@ -10270,29 +10270,29 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D290" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E290" t="n">
-        <v>102.22</v>
+        <v>38.18</v>
       </c>
       <c r="F290" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G290" t="n">
-        <v>102.22</v>
+        <v>152.72</v>
       </c>
       <c r="H290" t="n">
-        <v>2.13</v>
+        <v>13.7</v>
       </c>
       <c r="I290" t="n">
-        <v>2.13</v>
+        <v>9.85</v>
       </c>
       <c r="J290" t="n">
         <v>7.91</v>
@@ -10304,29 +10304,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D291" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E291" t="n">
-        <v>6.983</v>
+        <v>12.292</v>
       </c>
       <c r="F291" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G291" t="n">
-        <v>62.85</v>
+        <v>36.88</v>
       </c>
       <c r="H291" t="n">
-        <v>6.7</v>
+        <v>5.72</v>
       </c>
       <c r="I291" t="n">
-        <v>11.93</v>
+        <v>18.36</v>
       </c>
       <c r="J291" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D297" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E297" t="n">
-        <v>6.915</v>
+        <v>38.49</v>
       </c>
       <c r="F297" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G297" t="n">
-        <v>62.23</v>
+        <v>153.96</v>
       </c>
       <c r="H297" t="n">
-        <v>6.08</v>
+        <v>14.94</v>
       </c>
       <c r="I297" t="n">
-        <v>10.83</v>
+        <v>10.75</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D298" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E298" t="n">
-        <v>100.42</v>
+        <v>22.78</v>
       </c>
       <c r="F298" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G298" t="n">
-        <v>100.42</v>
+        <v>68.34</v>
       </c>
       <c r="H298" t="n">
-        <v>0.33</v>
+        <v>2.67</v>
       </c>
       <c r="I298" t="n">
-        <v>0.33</v>
+        <v>4.07</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10576,29 +10576,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C299" t="n">
         <v>3</v>
       </c>
       <c r="D299" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E299" t="n">
-        <v>22.78</v>
+        <v>11.92</v>
       </c>
       <c r="F299" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G299" t="n">
-        <v>68.34</v>
+        <v>35.76</v>
       </c>
       <c r="H299" t="n">
-        <v>2.67</v>
+        <v>4.6</v>
       </c>
       <c r="I299" t="n">
-        <v>4.07</v>
+        <v>14.76</v>
       </c>
       <c r="J299" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D300" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E300" t="n">
-        <v>38.49</v>
+        <v>6.915</v>
       </c>
       <c r="F300" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G300" t="n">
-        <v>153.96</v>
+        <v>62.23</v>
       </c>
       <c r="H300" t="n">
-        <v>14.94</v>
+        <v>6.08</v>
       </c>
       <c r="I300" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E301" t="n">
-        <v>11.92</v>
+        <v>100.42</v>
       </c>
       <c r="F301" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G301" t="n">
-        <v>35.76</v>
+        <v>100.42</v>
       </c>
       <c r="H301" t="n">
-        <v>4.6</v>
+        <v>0.33</v>
       </c>
       <c r="I301" t="n">
-        <v>14.76</v>
+        <v>0.33</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E312" t="n">
-        <v>22.9</v>
+        <v>100.38</v>
       </c>
       <c r="F312" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G312" t="n">
-        <v>68.7</v>
+        <v>100.38</v>
       </c>
       <c r="H312" t="n">
-        <v>3.03</v>
+        <v>0.29</v>
       </c>
       <c r="I312" t="n">
-        <v>4.61</v>
+        <v>0.29</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D313" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E313" t="n">
-        <v>38.66</v>
+        <v>6.936</v>
       </c>
       <c r="F313" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G313" t="n">
-        <v>154.64</v>
+        <v>62.42</v>
       </c>
       <c r="H313" t="n">
-        <v>15.62</v>
+        <v>6.27</v>
       </c>
       <c r="I313" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D315" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E315" t="n">
-        <v>6.936</v>
+        <v>38.66</v>
       </c>
       <c r="F315" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G315" t="n">
-        <v>62.42</v>
+        <v>154.64</v>
       </c>
       <c r="H315" t="n">
-        <v>6.27</v>
+        <v>15.62</v>
       </c>
       <c r="I315" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D316" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E316" t="n">
-        <v>100.38</v>
+        <v>22.9</v>
       </c>
       <c r="F316" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G316" t="n">
-        <v>100.38</v>
+        <v>68.7</v>
       </c>
       <c r="H316" t="n">
-        <v>0.29</v>
+        <v>3.03</v>
       </c>
       <c r="I316" t="n">
-        <v>0.29</v>
+        <v>4.61</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D322" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E322" t="n">
-        <v>101.7</v>
+        <v>6.967</v>
       </c>
       <c r="F322" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G322" t="n">
-        <v>101.7</v>
+        <v>62.7</v>
       </c>
       <c r="H322" t="n">
-        <v>1.61</v>
+        <v>6.55</v>
       </c>
       <c r="I322" t="n">
-        <v>1.61</v>
+        <v>11.67</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D323" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E323" t="n">
-        <v>11.81</v>
+        <v>39.07</v>
       </c>
       <c r="F323" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G323" t="n">
-        <v>35.43</v>
+        <v>156.28</v>
       </c>
       <c r="H323" t="n">
-        <v>4.27</v>
+        <v>17.26</v>
       </c>
       <c r="I323" t="n">
-        <v>13.7</v>
+        <v>12.42</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11426,29 +11426,29 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D324" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E324" t="n">
-        <v>39.07</v>
+        <v>22.745</v>
       </c>
       <c r="F324" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G324" t="n">
-        <v>156.28</v>
+        <v>68.23</v>
       </c>
       <c r="H324" t="n">
-        <v>17.26</v>
+        <v>2.56</v>
       </c>
       <c r="I324" t="n">
-        <v>12.42</v>
+        <v>3.9</v>
       </c>
       <c r="J324" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E325" t="n">
-        <v>6.967</v>
+        <v>101.7</v>
       </c>
       <c r="F325" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G325" t="n">
-        <v>62.7</v>
+        <v>101.7</v>
       </c>
       <c r="H325" t="n">
-        <v>6.55</v>
+        <v>1.61</v>
       </c>
       <c r="I325" t="n">
-        <v>11.67</v>
+        <v>1.61</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C326" t="n">
         <v>3</v>
       </c>
       <c r="D326" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E326" t="n">
-        <v>22.745</v>
+        <v>11.81</v>
       </c>
       <c r="F326" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G326" t="n">
-        <v>68.23</v>
+        <v>35.43</v>
       </c>
       <c r="H326" t="n">
-        <v>2.56</v>
+        <v>4.27</v>
       </c>
       <c r="I326" t="n">
-        <v>3.9</v>
+        <v>13.7</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D337" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E337" t="n">
-        <v>11.284</v>
+        <v>39.15</v>
       </c>
       <c r="F337" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G337" t="n">
-        <v>33.85</v>
+        <v>156.6</v>
       </c>
       <c r="H337" t="n">
-        <v>2.69</v>
+        <v>17.58</v>
       </c>
       <c r="I337" t="n">
-        <v>8.630000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E338" t="n">
-        <v>22.845</v>
+        <v>101.04</v>
       </c>
       <c r="F338" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G338" t="n">
-        <v>68.53</v>
+        <v>101.04</v>
       </c>
       <c r="H338" t="n">
-        <v>2.86</v>
+        <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>4.36</v>
+        <v>0.95</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E339" t="n">
-        <v>6.938</v>
+        <v>22.845</v>
       </c>
       <c r="F339" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G339" t="n">
-        <v>62.44</v>
+        <v>68.53</v>
       </c>
       <c r="H339" t="n">
-        <v>6.29</v>
+        <v>2.86</v>
       </c>
       <c r="I339" t="n">
-        <v>11.2</v>
+        <v>4.36</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D340" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E340" t="n">
-        <v>39.15</v>
+        <v>11.284</v>
       </c>
       <c r="F340" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G340" t="n">
-        <v>156.6</v>
+        <v>33.85</v>
       </c>
       <c r="H340" t="n">
-        <v>17.58</v>
+        <v>2.69</v>
       </c>
       <c r="I340" t="n">
-        <v>12.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D341" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E341" t="n">
-        <v>101.04</v>
+        <v>6.938</v>
       </c>
       <c r="F341" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G341" t="n">
-        <v>101.04</v>
+        <v>62.44</v>
       </c>
       <c r="H341" t="n">
-        <v>0.95</v>
+        <v>6.29</v>
       </c>
       <c r="I341" t="n">
-        <v>0.95</v>
+        <v>11.2</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C347" t="n">
         <v>3</v>
       </c>
       <c r="D347" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E347" t="n">
-        <v>11.206</v>
+        <v>22.82</v>
       </c>
       <c r="F347" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G347" t="n">
-        <v>33.62</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H347" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="I347" t="n">
-        <v>7.89</v>
+        <v>4.25</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D348" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E348" t="n">
-        <v>7.005</v>
+        <v>39</v>
       </c>
       <c r="F348" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G348" t="n">
-        <v>63.05</v>
+        <v>156</v>
       </c>
       <c r="H348" t="n">
-        <v>6.9</v>
+        <v>16.98</v>
       </c>
       <c r="I348" t="n">
-        <v>12.29</v>
+        <v>12.21</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D350" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E350" t="n">
-        <v>39</v>
+        <v>7.005</v>
       </c>
       <c r="F350" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G350" t="n">
-        <v>156</v>
+        <v>63.05</v>
       </c>
       <c r="H350" t="n">
-        <v>16.98</v>
+        <v>6.9</v>
       </c>
       <c r="I350" t="n">
-        <v>12.21</v>
+        <v>12.29</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C351" t="n">
         <v>3</v>
       </c>
       <c r="D351" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E351" t="n">
-        <v>22.82</v>
+        <v>11.206</v>
       </c>
       <c r="F351" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G351" t="n">
-        <v>68.45999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="H351" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="I351" t="n">
-        <v>4.25</v>
+        <v>7.89</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D357" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E357" t="n">
-        <v>6.978</v>
+        <v>22.5</v>
       </c>
       <c r="F357" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G357" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="H357" t="n">
-        <v>6.65</v>
+        <v>1.83</v>
       </c>
       <c r="I357" t="n">
-        <v>11.84</v>
+        <v>2.79</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E358" t="n">
-        <v>40.07</v>
+        <v>101.98</v>
       </c>
       <c r="F358" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G358" t="n">
-        <v>160.28</v>
+        <v>101.98</v>
       </c>
       <c r="H358" t="n">
-        <v>21.26</v>
+        <v>1.89</v>
       </c>
       <c r="I358" t="n">
-        <v>15.29</v>
+        <v>1.89</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D359" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E359" t="n">
-        <v>101.98</v>
+        <v>11.13</v>
       </c>
       <c r="F359" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G359" t="n">
-        <v>101.98</v>
+        <v>33.39</v>
       </c>
       <c r="H359" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="I359" t="n">
-        <v>1.89</v>
+        <v>7.16</v>
       </c>
       <c r="J359" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D360" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E360" t="n">
-        <v>22.5</v>
+        <v>6.978</v>
       </c>
       <c r="F360" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G360" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="H360" t="n">
-        <v>1.83</v>
+        <v>6.65</v>
       </c>
       <c r="I360" t="n">
-        <v>2.79</v>
+        <v>11.84</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D361" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E361" t="n">
-        <v>11.13</v>
+        <v>40.07</v>
       </c>
       <c r="F361" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G361" t="n">
-        <v>33.39</v>
+        <v>160.28</v>
       </c>
       <c r="H361" t="n">
-        <v>2.23</v>
+        <v>21.26</v>
       </c>
       <c r="I361" t="n">
-        <v>7.16</v>
+        <v>15.29</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D367" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E367" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F367" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G367" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H367" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I367" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D368" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E368" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
       <c r="F368" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G368" t="n">
-        <v>62.19</v>
+        <v>32.73</v>
       </c>
       <c r="H368" t="n">
-        <v>6.04</v>
+        <v>1.57</v>
       </c>
       <c r="I368" t="n">
-        <v>10.76</v>
+        <v>5.04</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12956,29 +12956,29 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C369" t="n">
         <v>3</v>
       </c>
       <c r="D369" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E369" t="n">
-        <v>10.91</v>
+        <v>22.275</v>
       </c>
       <c r="F369" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G369" t="n">
-        <v>32.73</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H369" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="I369" t="n">
-        <v>5.04</v>
+        <v>1.75</v>
       </c>
       <c r="J369" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D370" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E370" t="n">
-        <v>101.5</v>
+        <v>39.935</v>
       </c>
       <c r="F370" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G370" t="n">
-        <v>101.5</v>
+        <v>159.74</v>
       </c>
       <c r="H370" t="n">
-        <v>1.41</v>
+        <v>20.72</v>
       </c>
       <c r="I370" t="n">
-        <v>1.41</v>
+        <v>14.9</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E371" t="n">
-        <v>22.275</v>
+        <v>6.91</v>
       </c>
       <c r="F371" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G371" t="n">
-        <v>66.81999999999999</v>
+        <v>62.19</v>
       </c>
       <c r="H371" t="n">
-        <v>1.15</v>
+        <v>6.04</v>
       </c>
       <c r="I371" t="n">
-        <v>1.75</v>
+        <v>10.76</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D377" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E377" t="n">
-        <v>10.962</v>
+        <v>6.941</v>
       </c>
       <c r="F377" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G377" t="n">
-        <v>32.89</v>
+        <v>62.47</v>
       </c>
       <c r="H377" t="n">
-        <v>1.73</v>
+        <v>6.32</v>
       </c>
       <c r="I377" t="n">
-        <v>5.55</v>
+        <v>11.26</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D378" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E378" t="n">
-        <v>39.57</v>
+        <v>10.962</v>
       </c>
       <c r="F378" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G378" t="n">
-        <v>158.28</v>
+        <v>32.89</v>
       </c>
       <c r="H378" t="n">
-        <v>19.26</v>
+        <v>1.73</v>
       </c>
       <c r="I378" t="n">
-        <v>13.85</v>
+        <v>5.55</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D379" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E379" t="n">
-        <v>22.13</v>
+        <v>39.57</v>
       </c>
       <c r="F379" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G379" t="n">
-        <v>66.39</v>
+        <v>158.28</v>
       </c>
       <c r="H379" t="n">
-        <v>0.72</v>
+        <v>19.26</v>
       </c>
       <c r="I379" t="n">
-        <v>1.1</v>
+        <v>13.85</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D380" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E380" t="n">
-        <v>101.88</v>
+        <v>22.13</v>
       </c>
       <c r="F380" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G380" t="n">
-        <v>101.88</v>
+        <v>66.39</v>
       </c>
       <c r="H380" t="n">
-        <v>1.79</v>
+        <v>0.72</v>
       </c>
       <c r="I380" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,31 +13364,201 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
+      <c r="D381" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E381" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="F381" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G381" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="H381" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I381" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J381" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E382" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="F382" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G382" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H382" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I382" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J382" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>3</v>
+      </c>
+      <c r="D383" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E383" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="F383" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G383" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="H383" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I383" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J383" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>4</v>
+      </c>
+      <c r="D384" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E384" t="n">
+        <v>38.585</v>
+      </c>
+      <c r="F384" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G384" t="n">
+        <v>154.34</v>
+      </c>
+      <c r="H384" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="I384" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="J384" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>3</v>
+      </c>
+      <c r="D385" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E385" t="n">
+        <v>22.145</v>
+      </c>
+      <c r="F385" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G385" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="H385" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I385" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J385" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C381" t="n">
+      <c r="C386" t="n">
         <v>9</v>
       </c>
-      <c r="D381" t="n">
+      <c r="D386" t="n">
         <v>6.239</v>
       </c>
-      <c r="E381" t="n">
-        <v>6.941</v>
-      </c>
-      <c r="F381" t="n">
+      <c r="E386" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="F386" t="n">
         <v>56.15</v>
       </c>
-      <c r="G381" t="n">
-        <v>62.47</v>
-      </c>
-      <c r="H381" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="I381" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="J381" t="n">
+      <c r="G386" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="H386" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="I386" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J386" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J386"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E12" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F12" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G12" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E13" t="n">
-        <v>41.121</v>
+        <v>6.788</v>
       </c>
       <c r="F13" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G13" t="n">
-        <v>164.48</v>
+        <v>61.09</v>
       </c>
       <c r="H13" t="n">
-        <v>25.46</v>
+        <v>4.94</v>
       </c>
       <c r="I13" t="n">
-        <v>18.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E14" t="n">
-        <v>10.756</v>
+        <v>105.22</v>
       </c>
       <c r="F14" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G14" t="n">
-        <v>32.27</v>
+        <v>105.22</v>
       </c>
       <c r="H14" t="n">
-        <v>1.11</v>
+        <v>5.13</v>
       </c>
       <c r="I14" t="n">
-        <v>3.56</v>
+        <v>5.13</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E15" t="n">
-        <v>6.788</v>
+        <v>41.121</v>
       </c>
       <c r="F15" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G15" t="n">
-        <v>61.09</v>
+        <v>164.48</v>
       </c>
       <c r="H15" t="n">
-        <v>4.94</v>
+        <v>25.46</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>18.31</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E16" t="n">
-        <v>21.907</v>
+        <v>10.756</v>
       </c>
       <c r="F16" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G16" t="n">
-        <v>65.72</v>
+        <v>32.27</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>3.56</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1158,29 +1158,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E22" t="n">
-        <v>105.78</v>
+        <v>10.536</v>
       </c>
       <c r="F22" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G22" t="n">
-        <v>105.78</v>
+        <v>31.61</v>
       </c>
       <c r="H22" t="n">
-        <v>5.69</v>
+        <v>0.45</v>
       </c>
       <c r="I22" t="n">
-        <v>5.68</v>
+        <v>1.44</v>
       </c>
       <c r="J22" t="n">
         <v>7.91</v>
@@ -1192,29 +1192,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E23" t="n">
-        <v>6.799</v>
+        <v>41.336</v>
       </c>
       <c r="F23" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G23" t="n">
-        <v>61.19</v>
+        <v>165.34</v>
       </c>
       <c r="H23" t="n">
-        <v>5.04</v>
+        <v>26.32</v>
       </c>
       <c r="I23" t="n">
-        <v>8.98</v>
+        <v>18.93</v>
       </c>
       <c r="J23" t="n">
         <v>7.91</v>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E24" t="n">
-        <v>41.336</v>
+        <v>21.669</v>
       </c>
       <c r="F24" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G24" t="n">
-        <v>165.34</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>26.32</v>
+        <v>-0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>18.93</v>
+        <v>-1.01</v>
       </c>
       <c r="J24" t="n">
         <v>7.91</v>
@@ -1260,29 +1260,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E25" t="n">
-        <v>21.669</v>
+        <v>105.78</v>
       </c>
       <c r="F25" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G25" t="n">
-        <v>65.01000000000001</v>
+        <v>105.78</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.66</v>
+        <v>5.69</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.01</v>
+        <v>5.68</v>
       </c>
       <c r="J25" t="n">
         <v>7.91</v>
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E26" t="n">
-        <v>10.536</v>
+        <v>6.799</v>
       </c>
       <c r="F26" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G26" t="n">
-        <v>31.61</v>
+        <v>61.19</v>
       </c>
       <c r="H26" t="n">
-        <v>0.45</v>
+        <v>5.04</v>
       </c>
       <c r="I26" t="n">
-        <v>1.44</v>
+        <v>8.98</v>
       </c>
       <c r="J26" t="n">
         <v>7.91</v>
@@ -1498,29 +1498,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E32" t="n">
-        <v>103.08</v>
+        <v>10.714</v>
       </c>
       <c r="F32" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G32" t="n">
-        <v>103.08</v>
+        <v>32.14</v>
       </c>
       <c r="H32" t="n">
-        <v>2.99</v>
+        <v>0.98</v>
       </c>
       <c r="I32" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
         <v>7.91</v>
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E33" t="n">
-        <v>38.849</v>
+        <v>6.762</v>
       </c>
       <c r="F33" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G33" t="n">
-        <v>155.4</v>
+        <v>60.86</v>
       </c>
       <c r="H33" t="n">
-        <v>16.38</v>
+        <v>4.71</v>
       </c>
       <c r="I33" t="n">
-        <v>11.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>7.91</v>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E34" t="n">
-        <v>6.762</v>
+        <v>22.053</v>
       </c>
       <c r="F34" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G34" t="n">
-        <v>60.86</v>
+        <v>66.16</v>
       </c>
       <c r="H34" t="n">
-        <v>4.71</v>
+        <v>0.49</v>
       </c>
       <c r="I34" t="n">
-        <v>8.390000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J34" t="n">
         <v>7.91</v>
@@ -1600,29 +1600,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E35" t="n">
-        <v>22.053</v>
+        <v>103.08</v>
       </c>
       <c r="F35" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G35" t="n">
-        <v>66.16</v>
+        <v>103.08</v>
       </c>
       <c r="H35" t="n">
-        <v>0.49</v>
+        <v>2.99</v>
       </c>
       <c r="I35" t="n">
-        <v>0.75</v>
+        <v>2.99</v>
       </c>
       <c r="J35" t="n">
         <v>7.91</v>
@@ -1634,29 +1634,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E36" t="n">
-        <v>10.714</v>
+        <v>38.849</v>
       </c>
       <c r="F36" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G36" t="n">
-        <v>32.14</v>
+        <v>155.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.98</v>
+        <v>16.38</v>
       </c>
       <c r="I36" t="n">
-        <v>3.15</v>
+        <v>11.78</v>
       </c>
       <c r="J36" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E42" t="n">
-        <v>6.629</v>
+        <v>22</v>
       </c>
       <c r="F42" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G42" t="n">
-        <v>59.66</v>
+        <v>66</v>
       </c>
       <c r="H42" t="n">
-        <v>3.51</v>
+        <v>0.33</v>
       </c>
       <c r="I42" t="n">
-        <v>6.25</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E43" t="n">
-        <v>10.61</v>
+        <v>6.629</v>
       </c>
       <c r="F43" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G43" t="n">
-        <v>31.83</v>
+        <v>59.66</v>
       </c>
       <c r="H43" t="n">
-        <v>0.67</v>
+        <v>3.51</v>
       </c>
       <c r="I43" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E44" t="n">
-        <v>100.06</v>
+        <v>10.61</v>
       </c>
       <c r="F44" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G44" t="n">
-        <v>100.06</v>
+        <v>31.83</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.03</v>
+        <v>0.67</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.03</v>
+        <v>2.15</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>100.06</v>
       </c>
       <c r="F45" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G45" t="n">
-        <v>66</v>
+        <v>100.06</v>
       </c>
       <c r="H45" t="n">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -2008,29 +2008,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E47" t="n">
-        <v>10.562</v>
+        <v>99.83</v>
       </c>
       <c r="F47" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G47" t="n">
-        <v>31.69</v>
+        <v>99.83</v>
       </c>
       <c r="H47" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>-0.26</v>
       </c>
       <c r="J47" t="n">
         <v>7.91</v>
@@ -2042,29 +2042,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E48" t="n">
-        <v>6.622</v>
+        <v>38.312</v>
       </c>
       <c r="F48" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G48" t="n">
-        <v>59.6</v>
+        <v>153.25</v>
       </c>
       <c r="H48" t="n">
-        <v>3.45</v>
+        <v>14.23</v>
       </c>
       <c r="I48" t="n">
-        <v>6.14</v>
+        <v>10.24</v>
       </c>
       <c r="J48" t="n">
         <v>7.91</v>
@@ -2076,29 +2076,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E49" t="n">
-        <v>38.312</v>
+        <v>21.778</v>
       </c>
       <c r="F49" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G49" t="n">
-        <v>153.25</v>
+        <v>65.33</v>
       </c>
       <c r="H49" t="n">
-        <v>14.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I49" t="n">
-        <v>10.24</v>
+        <v>-0.52</v>
       </c>
       <c r="J49" t="n">
         <v>7.91</v>
@@ -2110,29 +2110,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E50" t="n">
-        <v>21.778</v>
+        <v>6.622</v>
       </c>
       <c r="F50" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G50" t="n">
-        <v>65.33</v>
+        <v>59.6</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.34</v>
+        <v>3.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.52</v>
+        <v>6.14</v>
       </c>
       <c r="J50" t="n">
         <v>7.91</v>
@@ -2144,29 +2144,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E51" t="n">
-        <v>99.83</v>
+        <v>10.562</v>
       </c>
       <c r="F51" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G51" t="n">
-        <v>99.83</v>
+        <v>31.69</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.26</v>
+        <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.26</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E62" t="n">
-        <v>10.712</v>
+        <v>6.817</v>
       </c>
       <c r="F62" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G62" t="n">
-        <v>32.14</v>
+        <v>61.35</v>
       </c>
       <c r="H62" t="n">
-        <v>0.98</v>
+        <v>5.2</v>
       </c>
       <c r="I62" t="n">
-        <v>3.15</v>
+        <v>9.26</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E63" t="n">
-        <v>22.7</v>
+        <v>41.064</v>
       </c>
       <c r="F63" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G63" t="n">
-        <v>68.09999999999999</v>
+        <v>164.26</v>
       </c>
       <c r="H63" t="n">
-        <v>2.43</v>
+        <v>25.24</v>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>18.16</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E64" t="n">
-        <v>105.5</v>
+        <v>10.712</v>
       </c>
       <c r="F64" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G64" t="n">
-        <v>105.5</v>
+        <v>32.14</v>
       </c>
       <c r="H64" t="n">
-        <v>5.41</v>
+        <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>5.41</v>
+        <v>3.15</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E65" t="n">
-        <v>41.064</v>
+        <v>22.7</v>
       </c>
       <c r="F65" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G65" t="n">
-        <v>164.26</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>25.24</v>
+        <v>2.43</v>
       </c>
       <c r="I65" t="n">
-        <v>18.16</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E66" t="n">
-        <v>6.817</v>
+        <v>105.5</v>
       </c>
       <c r="F66" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G66" t="n">
-        <v>61.35</v>
+        <v>105.5</v>
       </c>
       <c r="H66" t="n">
-        <v>5.2</v>
+        <v>5.41</v>
       </c>
       <c r="I66" t="n">
-        <v>9.26</v>
+        <v>5.41</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E72" t="n">
-        <v>41.15</v>
+        <v>104.22</v>
       </c>
       <c r="F72" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G72" t="n">
-        <v>164.6</v>
+        <v>104.22</v>
       </c>
       <c r="H72" t="n">
-        <v>25.58</v>
+        <v>4.13</v>
       </c>
       <c r="I72" t="n">
-        <v>18.4</v>
+        <v>4.13</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E73" t="n">
-        <v>10.892</v>
+        <v>6.811</v>
       </c>
       <c r="F73" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G73" t="n">
-        <v>32.68</v>
+        <v>61.3</v>
       </c>
       <c r="H73" t="n">
-        <v>1.52</v>
+        <v>5.15</v>
       </c>
       <c r="I73" t="n">
-        <v>4.88</v>
+        <v>9.17</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E75" t="n">
-        <v>104.22</v>
+        <v>10.892</v>
       </c>
       <c r="F75" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G75" t="n">
-        <v>104.22</v>
+        <v>32.68</v>
       </c>
       <c r="H75" t="n">
-        <v>4.13</v>
+        <v>1.52</v>
       </c>
       <c r="I75" t="n">
-        <v>4.13</v>
+        <v>4.88</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -2994,29 +2994,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E76" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F76" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G76" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H76" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I76" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J76" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E82" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F82" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G82" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H82" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I82" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E83" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F83" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G83" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H83" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I83" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E84" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F84" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G84" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H84" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I84" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E85" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F85" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G85" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I85" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E86" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F86" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G86" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H86" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I86" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E92" t="n">
-        <v>103.88</v>
+        <v>40.575</v>
       </c>
       <c r="F92" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G92" t="n">
-        <v>103.88</v>
+        <v>162.3</v>
       </c>
       <c r="H92" t="n">
-        <v>3.79</v>
+        <v>23.28</v>
       </c>
       <c r="I92" t="n">
-        <v>3.79</v>
+        <v>16.75</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E93" t="n">
-        <v>6.797</v>
+        <v>103.88</v>
       </c>
       <c r="F93" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G93" t="n">
-        <v>61.17</v>
+        <v>103.88</v>
       </c>
       <c r="H93" t="n">
-        <v>5.02</v>
+        <v>3.79</v>
       </c>
       <c r="I93" t="n">
-        <v>8.94</v>
+        <v>3.79</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D94" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E94" t="n">
-        <v>10.876</v>
+        <v>6.797</v>
       </c>
       <c r="F94" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G94" t="n">
-        <v>32.63</v>
+        <v>61.17</v>
       </c>
       <c r="H94" t="n">
-        <v>1.47</v>
+        <v>5.02</v>
       </c>
       <c r="I94" t="n">
-        <v>4.72</v>
+        <v>8.94</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E95" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F95" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G95" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H95" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I95" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E97" t="n">
-        <v>23.35</v>
+        <v>104.22</v>
       </c>
       <c r="F97" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G97" t="n">
-        <v>70.05</v>
+        <v>104.22</v>
       </c>
       <c r="H97" t="n">
-        <v>4.38</v>
+        <v>4.13</v>
       </c>
       <c r="I97" t="n">
-        <v>6.67</v>
+        <v>4.13</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E98" t="n">
-        <v>6.839</v>
+        <v>40.65</v>
       </c>
       <c r="F98" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G98" t="n">
-        <v>61.55</v>
+        <v>162.6</v>
       </c>
       <c r="H98" t="n">
-        <v>5.4</v>
+        <v>23.58</v>
       </c>
       <c r="I98" t="n">
-        <v>9.619999999999999</v>
+        <v>16.96</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E99" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F99" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G99" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H99" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I99" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E100" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F100" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G100" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H100" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I100" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E101" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F101" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G101" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H101" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I101" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E107" t="n">
-        <v>6.785</v>
+        <v>40.5</v>
       </c>
       <c r="F107" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G107" t="n">
-        <v>61.06</v>
+        <v>162</v>
       </c>
       <c r="H107" t="n">
-        <v>4.91</v>
+        <v>22.98</v>
       </c>
       <c r="I107" t="n">
-        <v>8.74</v>
+        <v>16.53</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E108" t="n">
-        <v>103.14</v>
+        <v>23.33</v>
       </c>
       <c r="F108" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G108" t="n">
-        <v>103.14</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>3.05</v>
+        <v>4.32</v>
       </c>
       <c r="I108" t="n">
-        <v>3.05</v>
+        <v>6.58</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E110" t="n">
-        <v>23.33</v>
+        <v>103.14</v>
       </c>
       <c r="F110" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G110" t="n">
-        <v>69.98999999999999</v>
+        <v>103.14</v>
       </c>
       <c r="H110" t="n">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="I110" t="n">
-        <v>6.58</v>
+        <v>3.05</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E111" t="n">
-        <v>40.5</v>
+        <v>6.785</v>
       </c>
       <c r="F111" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G111" t="n">
-        <v>162</v>
+        <v>61.06</v>
       </c>
       <c r="H111" t="n">
-        <v>22.98</v>
+        <v>4.91</v>
       </c>
       <c r="I111" t="n">
-        <v>16.53</v>
+        <v>8.74</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E117" t="n">
-        <v>10.756</v>
+        <v>105.96</v>
       </c>
       <c r="F117" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G117" t="n">
-        <v>32.27</v>
+        <v>105.96</v>
       </c>
       <c r="H117" t="n">
-        <v>1.11</v>
+        <v>5.87</v>
       </c>
       <c r="I117" t="n">
-        <v>3.56</v>
+        <v>5.86</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E118" t="n">
-        <v>6.861</v>
+        <v>23.145</v>
       </c>
       <c r="F118" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G118" t="n">
-        <v>61.75</v>
+        <v>69.44</v>
       </c>
       <c r="H118" t="n">
-        <v>5.6</v>
+        <v>3.77</v>
       </c>
       <c r="I118" t="n">
-        <v>9.970000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E119" t="n">
-        <v>23.145</v>
+        <v>41</v>
       </c>
       <c r="F119" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G119" t="n">
-        <v>69.44</v>
+        <v>164</v>
       </c>
       <c r="H119" t="n">
-        <v>3.77</v>
+        <v>24.98</v>
       </c>
       <c r="I119" t="n">
-        <v>5.74</v>
+        <v>17.97</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E120" t="n">
-        <v>105.96</v>
+        <v>10.756</v>
       </c>
       <c r="F120" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G120" t="n">
-        <v>105.96</v>
+        <v>32.27</v>
       </c>
       <c r="H120" t="n">
-        <v>5.87</v>
+        <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>5.86</v>
+        <v>3.56</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
+        <v>6.861</v>
       </c>
       <c r="F121" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G121" t="n">
-        <v>164</v>
+        <v>61.75</v>
       </c>
       <c r="H121" t="n">
-        <v>24.98</v>
+        <v>5.6</v>
       </c>
       <c r="I121" t="n">
-        <v>17.97</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E127" t="n">
-        <v>6.868</v>
+        <v>39.36</v>
       </c>
       <c r="F127" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G127" t="n">
-        <v>61.81</v>
+        <v>157.44</v>
       </c>
       <c r="H127" t="n">
-        <v>5.66</v>
+        <v>18.42</v>
       </c>
       <c r="I127" t="n">
-        <v>10.08</v>
+        <v>13.25</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E128" t="n">
-        <v>23.17</v>
+        <v>11.458</v>
       </c>
       <c r="F128" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G128" t="n">
-        <v>69.51000000000001</v>
+        <v>34.37</v>
       </c>
       <c r="H128" t="n">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="I128" t="n">
-        <v>5.85</v>
+        <v>10.3</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4796,29 +4796,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E129" t="n">
-        <v>11.458</v>
+        <v>103.46</v>
       </c>
       <c r="F129" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G129" t="n">
-        <v>34.37</v>
+        <v>103.46</v>
       </c>
       <c r="H129" t="n">
-        <v>3.21</v>
+        <v>3.37</v>
       </c>
       <c r="I129" t="n">
-        <v>10.3</v>
+        <v>3.37</v>
       </c>
       <c r="J129" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D130" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E130" t="n">
-        <v>39.36</v>
+        <v>6.868</v>
       </c>
       <c r="F130" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G130" t="n">
-        <v>157.44</v>
+        <v>61.81</v>
       </c>
       <c r="H130" t="n">
-        <v>18.42</v>
+        <v>5.66</v>
       </c>
       <c r="I130" t="n">
-        <v>13.25</v>
+        <v>10.08</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E131" t="n">
-        <v>103.46</v>
+        <v>23.17</v>
       </c>
       <c r="F131" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G131" t="n">
-        <v>103.46</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>3.37</v>
+        <v>3.84</v>
       </c>
       <c r="I131" t="n">
-        <v>3.37</v>
+        <v>5.85</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E142" t="n">
-        <v>11.498</v>
+        <v>38.89</v>
       </c>
       <c r="F142" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G142" t="n">
-        <v>34.49</v>
+        <v>155.56</v>
       </c>
       <c r="H142" t="n">
-        <v>3.33</v>
+        <v>16.54</v>
       </c>
       <c r="I142" t="n">
-        <v>10.69</v>
+        <v>11.9</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D143" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E143" t="n">
-        <v>23.135</v>
+        <v>6.878</v>
       </c>
       <c r="F143" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G143" t="n">
-        <v>69.41</v>
+        <v>61.9</v>
       </c>
       <c r="H143" t="n">
-        <v>3.74</v>
+        <v>5.75</v>
       </c>
       <c r="I143" t="n">
-        <v>5.7</v>
+        <v>10.24</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E144" t="n">
-        <v>6.878</v>
+        <v>102.06</v>
       </c>
       <c r="F144" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G144" t="n">
-        <v>61.9</v>
+        <v>102.06</v>
       </c>
       <c r="H144" t="n">
-        <v>5.75</v>
+        <v>1.97</v>
       </c>
       <c r="I144" t="n">
-        <v>10.24</v>
+        <v>1.97</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E145" t="n">
-        <v>38.89</v>
+        <v>11.498</v>
       </c>
       <c r="F145" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G145" t="n">
-        <v>155.56</v>
+        <v>34.49</v>
       </c>
       <c r="H145" t="n">
-        <v>16.54</v>
+        <v>3.33</v>
       </c>
       <c r="I145" t="n">
-        <v>11.9</v>
+        <v>10.69</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E146" t="n">
-        <v>102.06</v>
+        <v>23.135</v>
       </c>
       <c r="F146" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G146" t="n">
-        <v>102.06</v>
+        <v>69.41</v>
       </c>
       <c r="H146" t="n">
-        <v>1.97</v>
+        <v>3.74</v>
       </c>
       <c r="I146" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D152" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E152" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F152" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G152" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H152" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I152" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E153" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F153" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G153" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H153" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I153" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E154" t="n">
-        <v>104.12</v>
+        <v>11.034</v>
       </c>
       <c r="F154" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G154" t="n">
-        <v>104.12</v>
+        <v>33.1</v>
       </c>
       <c r="H154" t="n">
-        <v>4.03</v>
+        <v>1.94</v>
       </c>
       <c r="I154" t="n">
-        <v>4.03</v>
+        <v>6.23</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E155" t="n">
-        <v>6.893</v>
+        <v>23.045</v>
       </c>
       <c r="F155" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G155" t="n">
-        <v>62.04</v>
+        <v>69.14</v>
       </c>
       <c r="H155" t="n">
-        <v>5.89</v>
+        <v>3.47</v>
       </c>
       <c r="I155" t="n">
-        <v>10.49</v>
+        <v>5.28</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E156" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F156" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G156" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H156" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I156" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5748,29 +5748,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E157" t="n">
-        <v>10.92</v>
+        <v>40.015</v>
       </c>
       <c r="F157" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G157" t="n">
-        <v>32.76</v>
+        <v>160.06</v>
       </c>
       <c r="H157" t="n">
-        <v>1.6</v>
+        <v>21.04</v>
       </c>
       <c r="I157" t="n">
-        <v>5.13</v>
+        <v>15.13</v>
       </c>
       <c r="J157" t="n">
         <v>7.91</v>
@@ -5782,29 +5782,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E158" t="n">
-        <v>40.015</v>
+        <v>23.08</v>
       </c>
       <c r="F158" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G158" t="n">
-        <v>160.06</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H158" t="n">
-        <v>21.04</v>
+        <v>3.57</v>
       </c>
       <c r="I158" t="n">
-        <v>15.13</v>
+        <v>5.44</v>
       </c>
       <c r="J158" t="n">
         <v>7.91</v>
@@ -5816,29 +5816,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D159" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E159" t="n">
-        <v>23.08</v>
+        <v>6.913</v>
       </c>
       <c r="F159" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G159" t="n">
-        <v>69.23999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="H159" t="n">
-        <v>3.57</v>
+        <v>6.07</v>
       </c>
       <c r="I159" t="n">
-        <v>5.44</v>
+        <v>10.81</v>
       </c>
       <c r="J159" t="n">
         <v>7.91</v>
@@ -5850,29 +5850,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E160" t="n">
-        <v>6.913</v>
+        <v>104.5</v>
       </c>
       <c r="F160" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G160" t="n">
-        <v>62.22</v>
+        <v>104.5</v>
       </c>
       <c r="H160" t="n">
-        <v>6.07</v>
+        <v>4.41</v>
       </c>
       <c r="I160" t="n">
-        <v>10.81</v>
+        <v>4.41</v>
       </c>
       <c r="J160" t="n">
         <v>7.91</v>
@@ -5884,29 +5884,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E161" t="n">
-        <v>104.5</v>
+        <v>10.92</v>
       </c>
       <c r="F161" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G161" t="n">
-        <v>104.5</v>
+        <v>32.76</v>
       </c>
       <c r="H161" t="n">
-        <v>4.41</v>
+        <v>1.6</v>
       </c>
       <c r="I161" t="n">
-        <v>4.41</v>
+        <v>5.13</v>
       </c>
       <c r="J161" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E167" t="n">
-        <v>6.911</v>
+        <v>10.726</v>
       </c>
       <c r="F167" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G167" t="n">
-        <v>62.2</v>
+        <v>32.18</v>
       </c>
       <c r="H167" t="n">
-        <v>6.05</v>
+        <v>1.02</v>
       </c>
       <c r="I167" t="n">
-        <v>10.77</v>
+        <v>3.27</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E168" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F168" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G168" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I168" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D170" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E170" t="n">
-        <v>10.726</v>
+        <v>6.911</v>
       </c>
       <c r="F170" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G170" t="n">
-        <v>32.18</v>
+        <v>62.2</v>
       </c>
       <c r="H170" t="n">
-        <v>1.02</v>
+        <v>6.05</v>
       </c>
       <c r="I170" t="n">
-        <v>3.27</v>
+        <v>10.77</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E171" t="n">
-        <v>22.92</v>
+        <v>103.98</v>
       </c>
       <c r="F171" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G171" t="n">
-        <v>68.76000000000001</v>
+        <v>103.98</v>
       </c>
       <c r="H171" t="n">
-        <v>3.09</v>
+        <v>3.89</v>
       </c>
       <c r="I171" t="n">
-        <v>4.71</v>
+        <v>3.89</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E177" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F177" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G177" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H177" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I177" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E178" t="n">
-        <v>102.54</v>
+        <v>22.95</v>
       </c>
       <c r="F178" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G178" t="n">
-        <v>102.54</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="I178" t="n">
-        <v>2.45</v>
+        <v>4.84</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E179" t="n">
-        <v>22.95</v>
+        <v>10.642</v>
       </c>
       <c r="F179" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G179" t="n">
-        <v>68.84999999999999</v>
+        <v>31.93</v>
       </c>
       <c r="H179" t="n">
-        <v>3.18</v>
+        <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>4.84</v>
+        <v>2.47</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E180" t="n">
-        <v>38.245</v>
+        <v>6.922</v>
       </c>
       <c r="F180" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G180" t="n">
-        <v>152.98</v>
+        <v>62.3</v>
       </c>
       <c r="H180" t="n">
-        <v>13.96</v>
+        <v>6.15</v>
       </c>
       <c r="I180" t="n">
-        <v>10.04</v>
+        <v>10.95</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E181" t="n">
-        <v>10.642</v>
+        <v>102.54</v>
       </c>
       <c r="F181" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G181" t="n">
-        <v>31.93</v>
+        <v>102.54</v>
       </c>
       <c r="H181" t="n">
-        <v>0.77</v>
+        <v>2.45</v>
       </c>
       <c r="I181" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C192" t="n">
         <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E192" t="n">
-        <v>10.792</v>
+        <v>22.82</v>
       </c>
       <c r="F192" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G192" t="n">
-        <v>32.38</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H192" t="n">
-        <v>1.22</v>
+        <v>2.79</v>
       </c>
       <c r="I192" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E193" t="n">
-        <v>6.894</v>
+        <v>38.755</v>
       </c>
       <c r="F193" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G193" t="n">
-        <v>62.05</v>
+        <v>155.02</v>
       </c>
       <c r="H193" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="I193" t="n">
-        <v>10.51</v>
+        <v>11.51</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E194" t="n">
-        <v>38.755</v>
+        <v>102.46</v>
       </c>
       <c r="F194" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G194" t="n">
-        <v>155.02</v>
+        <v>102.46</v>
       </c>
       <c r="H194" t="n">
-        <v>16</v>
+        <v>2.37</v>
       </c>
       <c r="I194" t="n">
-        <v>11.51</v>
+        <v>2.37</v>
       </c>
       <c r="J194" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E195" t="n">
-        <v>22.82</v>
+        <v>10.792</v>
       </c>
       <c r="F195" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G195" t="n">
-        <v>68.45999999999999</v>
+        <v>32.38</v>
       </c>
       <c r="H195" t="n">
-        <v>2.79</v>
+        <v>1.22</v>
       </c>
       <c r="I195" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7074,29 +7074,29 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D196" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E196" t="n">
-        <v>102.46</v>
+        <v>6.894</v>
       </c>
       <c r="F196" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G196" t="n">
-        <v>102.46</v>
+        <v>62.05</v>
       </c>
       <c r="H196" t="n">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="I196" t="n">
-        <v>2.37</v>
+        <v>10.51</v>
       </c>
       <c r="J196" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C207" t="n">
         <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E207" t="n">
-        <v>11.172</v>
+        <v>22.725</v>
       </c>
       <c r="F207" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G207" t="n">
-        <v>33.52</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H207" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="I207" t="n">
-        <v>7.57</v>
+        <v>3.82</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D208" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E208" t="n">
-        <v>6.865</v>
+        <v>37.82</v>
       </c>
       <c r="F208" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G208" t="n">
-        <v>61.79</v>
+        <v>151.28</v>
       </c>
       <c r="H208" t="n">
-        <v>5.64</v>
+        <v>12.26</v>
       </c>
       <c r="I208" t="n">
-        <v>10.04</v>
+        <v>8.82</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7516,29 +7516,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E209" t="n">
-        <v>99.90000000000001</v>
+        <v>11.172</v>
       </c>
       <c r="F209" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G209" t="n">
-        <v>99.90000000000001</v>
+        <v>33.52</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.19</v>
+        <v>2.36</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.19</v>
+        <v>7.57</v>
       </c>
       <c r="J209" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E210" t="n">
-        <v>37.82</v>
+        <v>6.865</v>
       </c>
       <c r="F210" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G210" t="n">
-        <v>151.28</v>
+        <v>61.79</v>
       </c>
       <c r="H210" t="n">
-        <v>12.26</v>
+        <v>5.64</v>
       </c>
       <c r="I210" t="n">
-        <v>8.82</v>
+        <v>10.04</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E211" t="n">
-        <v>22.725</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F211" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G211" t="n">
-        <v>68.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H211" t="n">
-        <v>2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="I211" t="n">
-        <v>3.82</v>
+        <v>-0.19</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E217" t="n">
-        <v>11.546</v>
+        <v>6.864</v>
       </c>
       <c r="F217" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G217" t="n">
-        <v>34.64</v>
+        <v>61.78</v>
       </c>
       <c r="H217" t="n">
-        <v>3.48</v>
+        <v>5.63</v>
       </c>
       <c r="I217" t="n">
-        <v>11.17</v>
+        <v>10.03</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E218" t="n">
-        <v>23.175</v>
+        <v>36.75</v>
       </c>
       <c r="F218" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G218" t="n">
-        <v>69.53</v>
+        <v>147</v>
       </c>
       <c r="H218" t="n">
-        <v>3.86</v>
+        <v>7.98</v>
       </c>
       <c r="I218" t="n">
-        <v>5.88</v>
+        <v>5.74</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E220" t="n">
-        <v>36.75</v>
+        <v>23.175</v>
       </c>
       <c r="F220" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G220" t="n">
-        <v>147</v>
+        <v>69.53</v>
       </c>
       <c r="H220" t="n">
-        <v>7.98</v>
+        <v>3.86</v>
       </c>
       <c r="I220" t="n">
-        <v>5.74</v>
+        <v>5.88</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E221" t="n">
-        <v>6.864</v>
+        <v>11.546</v>
       </c>
       <c r="F221" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G221" t="n">
-        <v>61.78</v>
+        <v>34.64</v>
       </c>
       <c r="H221" t="n">
-        <v>5.63</v>
+        <v>3.48</v>
       </c>
       <c r="I221" t="n">
-        <v>10.03</v>
+        <v>11.17</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C227" t="n">
         <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E227" t="n">
-        <v>23.07</v>
+        <v>11.512</v>
       </c>
       <c r="F227" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G227" t="n">
-        <v>69.20999999999999</v>
+        <v>34.54</v>
       </c>
       <c r="H227" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="I227" t="n">
-        <v>5.39</v>
+        <v>10.85</v>
       </c>
       <c r="J227" t="n">
         <v>7.91</v>
@@ -8162,29 +8162,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D228" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E228" t="n">
-        <v>6.779</v>
+        <v>36.64</v>
       </c>
       <c r="F228" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G228" t="n">
-        <v>61.01</v>
+        <v>146.56</v>
       </c>
       <c r="H228" t="n">
-        <v>4.86</v>
+        <v>7.54</v>
       </c>
       <c r="I228" t="n">
-        <v>8.66</v>
+        <v>5.42</v>
       </c>
       <c r="J228" t="n">
         <v>7.91</v>
@@ -8196,29 +8196,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E229" t="n">
-        <v>36.64</v>
+        <v>97.34</v>
       </c>
       <c r="F229" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G229" t="n">
-        <v>146.56</v>
+        <v>97.34</v>
       </c>
       <c r="H229" t="n">
-        <v>7.54</v>
+        <v>-2.75</v>
       </c>
       <c r="I229" t="n">
-        <v>5.42</v>
+        <v>-2.75</v>
       </c>
       <c r="J229" t="n">
         <v>7.91</v>
@@ -8230,29 +8230,29 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E230" t="n">
-        <v>11.512</v>
+        <v>23.07</v>
       </c>
       <c r="F230" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G230" t="n">
-        <v>34.54</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H230" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="I230" t="n">
-        <v>10.85</v>
+        <v>5.39</v>
       </c>
       <c r="J230" t="n">
         <v>7.91</v>
@@ -8264,29 +8264,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D231" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E231" t="n">
-        <v>97.34</v>
+        <v>6.779</v>
       </c>
       <c r="F231" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G231" t="n">
-        <v>97.34</v>
+        <v>61.01</v>
       </c>
       <c r="H231" t="n">
-        <v>-2.75</v>
+        <v>4.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-2.75</v>
+        <v>8.66</v>
       </c>
       <c r="J231" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D237" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E237" t="n">
-        <v>23.245</v>
+        <v>37.315</v>
       </c>
       <c r="F237" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G237" t="n">
-        <v>69.73</v>
+        <v>149.26</v>
       </c>
       <c r="H237" t="n">
-        <v>4.06</v>
+        <v>10.24</v>
       </c>
       <c r="I237" t="n">
-        <v>6.18</v>
+        <v>7.37</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E238" t="n">
-        <v>6.914</v>
+        <v>23.245</v>
       </c>
       <c r="F238" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G238" t="n">
-        <v>62.23</v>
+        <v>69.73</v>
       </c>
       <c r="H238" t="n">
-        <v>6.08</v>
+        <v>4.06</v>
       </c>
       <c r="I238" t="n">
-        <v>10.83</v>
+        <v>6.18</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8536,29 +8536,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D239" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E239" t="n">
-        <v>11.842</v>
+        <v>6.914</v>
       </c>
       <c r="F239" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G239" t="n">
-        <v>35.53</v>
+        <v>62.23</v>
       </c>
       <c r="H239" t="n">
-        <v>4.37</v>
+        <v>6.08</v>
       </c>
       <c r="I239" t="n">
-        <v>14.02</v>
+        <v>10.83</v>
       </c>
       <c r="J239" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D240" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E240" t="n">
-        <v>99.84999999999999</v>
+        <v>11.842</v>
       </c>
       <c r="F240" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G240" t="n">
-        <v>99.84999999999999</v>
+        <v>35.53</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.24</v>
+        <v>4.37</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.24</v>
+        <v>14.02</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D241" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E241" t="n">
-        <v>37.315</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F241" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G241" t="n">
-        <v>149.26</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H241" t="n">
-        <v>10.24</v>
+        <v>-0.24</v>
       </c>
       <c r="I241" t="n">
-        <v>7.37</v>
+        <v>-0.24</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D242" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E242" t="n">
-        <v>12.08</v>
+        <v>38.52</v>
       </c>
       <c r="F242" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G242" t="n">
-        <v>36.24</v>
+        <v>154.08</v>
       </c>
       <c r="H242" t="n">
-        <v>5.08</v>
+        <v>15.06</v>
       </c>
       <c r="I242" t="n">
-        <v>16.3</v>
+        <v>10.83</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E243" t="n">
-        <v>23.465</v>
+        <v>102.86</v>
       </c>
       <c r="F243" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G243" t="n">
-        <v>70.39</v>
+        <v>102.86</v>
       </c>
       <c r="H243" t="n">
-        <v>4.72</v>
+        <v>2.77</v>
       </c>
       <c r="I243" t="n">
-        <v>7.19</v>
+        <v>2.77</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E245" t="n">
-        <v>102.86</v>
+        <v>12.08</v>
       </c>
       <c r="F245" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G245" t="n">
-        <v>102.86</v>
+        <v>36.24</v>
       </c>
       <c r="H245" t="n">
-        <v>2.77</v>
+        <v>5.08</v>
       </c>
       <c r="I245" t="n">
-        <v>2.77</v>
+        <v>16.3</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E246" t="n">
-        <v>38.52</v>
+        <v>23.465</v>
       </c>
       <c r="F246" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G246" t="n">
-        <v>154.08</v>
+        <v>70.39</v>
       </c>
       <c r="H246" t="n">
-        <v>15.06</v>
+        <v>4.72</v>
       </c>
       <c r="I246" t="n">
-        <v>10.83</v>
+        <v>7.19</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E252" t="n">
-        <v>38.095</v>
+        <v>103.18</v>
       </c>
       <c r="F252" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G252" t="n">
-        <v>152.38</v>
+        <v>103.18</v>
       </c>
       <c r="H252" t="n">
-        <v>13.36</v>
+        <v>3.09</v>
       </c>
       <c r="I252" t="n">
-        <v>9.609999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D253" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E253" t="n">
-        <v>7.05</v>
+        <v>23.315</v>
       </c>
       <c r="F253" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G253" t="n">
-        <v>63.45</v>
+        <v>69.95</v>
       </c>
       <c r="H253" t="n">
-        <v>7.3</v>
+        <v>4.28</v>
       </c>
       <c r="I253" t="n">
-        <v>13</v>
+        <v>6.52</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C254" t="n">
         <v>3</v>
       </c>
       <c r="D254" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E254" t="n">
-        <v>23.315</v>
+        <v>12.128</v>
       </c>
       <c r="F254" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G254" t="n">
-        <v>69.95</v>
+        <v>36.38</v>
       </c>
       <c r="H254" t="n">
-        <v>4.28</v>
+        <v>5.22</v>
       </c>
       <c r="I254" t="n">
-        <v>6.52</v>
+        <v>16.75</v>
       </c>
       <c r="J254" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D255" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E255" t="n">
-        <v>103.18</v>
+        <v>38.095</v>
       </c>
       <c r="F255" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G255" t="n">
-        <v>103.18</v>
+        <v>152.38</v>
       </c>
       <c r="H255" t="n">
-        <v>3.09</v>
+        <v>13.36</v>
       </c>
       <c r="I255" t="n">
-        <v>3.09</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D256" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E256" t="n">
-        <v>12.128</v>
+        <v>7.05</v>
       </c>
       <c r="F256" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G256" t="n">
-        <v>36.38</v>
+        <v>63.45</v>
       </c>
       <c r="H256" t="n">
-        <v>5.22</v>
+        <v>7.3</v>
       </c>
       <c r="I256" t="n">
-        <v>16.75</v>
+        <v>13</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E257" t="n">
-        <v>37.84</v>
+        <v>12.232</v>
       </c>
       <c r="F257" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G257" t="n">
-        <v>151.36</v>
+        <v>36.7</v>
       </c>
       <c r="H257" t="n">
-        <v>12.34</v>
+        <v>5.54</v>
       </c>
       <c r="I257" t="n">
-        <v>8.880000000000001</v>
+        <v>17.78</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D258" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E258" t="n">
-        <v>12.232</v>
+        <v>7.056</v>
       </c>
       <c r="F258" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G258" t="n">
-        <v>36.7</v>
+        <v>63.5</v>
       </c>
       <c r="H258" t="n">
-        <v>5.54</v>
+        <v>7.35</v>
       </c>
       <c r="I258" t="n">
-        <v>17.78</v>
+        <v>13.09</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D259" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E259" t="n">
-        <v>7.056</v>
+        <v>23.2</v>
       </c>
       <c r="F259" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G259" t="n">
-        <v>63.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H259" t="n">
-        <v>7.35</v>
+        <v>3.93</v>
       </c>
       <c r="I259" t="n">
-        <v>13.09</v>
+        <v>5.98</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E260" t="n">
-        <v>23.2</v>
+        <v>103.02</v>
       </c>
       <c r="F260" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G260" t="n">
-        <v>69.59999999999999</v>
+        <v>103.02</v>
       </c>
       <c r="H260" t="n">
-        <v>3.93</v>
+        <v>2.93</v>
       </c>
       <c r="I260" t="n">
-        <v>5.98</v>
+        <v>2.93</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D261" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E261" t="n">
-        <v>103.02</v>
+        <v>37.84</v>
       </c>
       <c r="F261" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G261" t="n">
-        <v>103.02</v>
+        <v>151.36</v>
       </c>
       <c r="H261" t="n">
-        <v>2.93</v>
+        <v>12.34</v>
       </c>
       <c r="I261" t="n">
-        <v>2.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9488,29 +9488,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D267" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E267" t="n">
-        <v>23.12</v>
+        <v>38.865</v>
       </c>
       <c r="F267" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G267" t="n">
-        <v>69.36</v>
+        <v>155.46</v>
       </c>
       <c r="H267" t="n">
-        <v>3.69</v>
+        <v>16.44</v>
       </c>
       <c r="I267" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="J267" t="n">
         <v>7.91</v>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E268" t="n">
-        <v>7.06</v>
+        <v>12.388</v>
       </c>
       <c r="F268" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G268" t="n">
-        <v>63.54</v>
+        <v>37.16</v>
       </c>
       <c r="H268" t="n">
-        <v>7.39</v>
+        <v>6</v>
       </c>
       <c r="I268" t="n">
-        <v>13.16</v>
+        <v>19.26</v>
       </c>
       <c r="J268" t="n">
         <v>7.91</v>
@@ -9556,29 +9556,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D269" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E269" t="n">
-        <v>103.36</v>
+        <v>7.06</v>
       </c>
       <c r="F269" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G269" t="n">
-        <v>103.36</v>
+        <v>63.54</v>
       </c>
       <c r="H269" t="n">
-        <v>3.27</v>
+        <v>7.39</v>
       </c>
       <c r="I269" t="n">
-        <v>3.27</v>
+        <v>13.16</v>
       </c>
       <c r="J269" t="n">
         <v>7.91</v>
@@ -9590,29 +9590,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D270" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E270" t="n">
-        <v>38.865</v>
+        <v>23.12</v>
       </c>
       <c r="F270" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G270" t="n">
-        <v>155.46</v>
+        <v>69.36</v>
       </c>
       <c r="H270" t="n">
-        <v>16.44</v>
+        <v>3.69</v>
       </c>
       <c r="I270" t="n">
-        <v>11.83</v>
+        <v>5.62</v>
       </c>
       <c r="J270" t="n">
         <v>7.91</v>
@@ -9624,29 +9624,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E271" t="n">
-        <v>12.388</v>
+        <v>103.36</v>
       </c>
       <c r="F271" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G271" t="n">
-        <v>37.16</v>
+        <v>103.36</v>
       </c>
       <c r="H271" t="n">
-        <v>6</v>
+        <v>3.27</v>
       </c>
       <c r="I271" t="n">
-        <v>19.26</v>
+        <v>3.27</v>
       </c>
       <c r="J271" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D277" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E277" t="n">
-        <v>7.063</v>
+        <v>38.985</v>
       </c>
       <c r="F277" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G277" t="n">
-        <v>63.57</v>
+        <v>155.94</v>
       </c>
       <c r="H277" t="n">
-        <v>7.42</v>
+        <v>16.92</v>
       </c>
       <c r="I277" t="n">
-        <v>13.21</v>
+        <v>12.17</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C278" t="n">
         <v>3</v>
       </c>
       <c r="D278" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E278" t="n">
-        <v>22.96</v>
+        <v>12.492</v>
       </c>
       <c r="F278" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G278" t="n">
-        <v>68.88</v>
+        <v>37.48</v>
       </c>
       <c r="H278" t="n">
-        <v>3.21</v>
+        <v>6.32</v>
       </c>
       <c r="I278" t="n">
-        <v>4.89</v>
+        <v>20.28</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9896,29 +9896,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E279" t="n">
-        <v>12.492</v>
+        <v>103.76</v>
       </c>
       <c r="F279" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G279" t="n">
-        <v>37.48</v>
+        <v>103.76</v>
       </c>
       <c r="H279" t="n">
-        <v>6.32</v>
+        <v>3.67</v>
       </c>
       <c r="I279" t="n">
-        <v>20.28</v>
+        <v>3.67</v>
       </c>
       <c r="J279" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D280" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E280" t="n">
-        <v>38.985</v>
+        <v>7.063</v>
       </c>
       <c r="F280" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G280" t="n">
-        <v>155.94</v>
+        <v>63.57</v>
       </c>
       <c r="H280" t="n">
-        <v>16.92</v>
+        <v>7.42</v>
       </c>
       <c r="I280" t="n">
-        <v>12.17</v>
+        <v>13.21</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E281" t="n">
-        <v>103.76</v>
+        <v>22.96</v>
       </c>
       <c r="F281" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G281" t="n">
-        <v>103.76</v>
+        <v>68.88</v>
       </c>
       <c r="H281" t="n">
-        <v>3.67</v>
+        <v>3.21</v>
       </c>
       <c r="I281" t="n">
-        <v>3.67</v>
+        <v>4.89</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -10338,29 +10338,29 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D292" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E292" t="n">
-        <v>6.96</v>
+        <v>38.26</v>
       </c>
       <c r="F292" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G292" t="n">
-        <v>62.64</v>
+        <v>153.04</v>
       </c>
       <c r="H292" t="n">
-        <v>6.49</v>
+        <v>14.02</v>
       </c>
       <c r="I292" t="n">
-        <v>11.56</v>
+        <v>10.08</v>
       </c>
       <c r="J292" t="n">
         <v>7.91</v>
@@ -10372,29 +10372,29 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C293" t="n">
         <v>3</v>
       </c>
       <c r="D293" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E293" t="n">
-        <v>22.685</v>
+        <v>12.096</v>
       </c>
       <c r="F293" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G293" t="n">
-        <v>68.05</v>
+        <v>36.29</v>
       </c>
       <c r="H293" t="n">
-        <v>2.38</v>
+        <v>5.13</v>
       </c>
       <c r="I293" t="n">
-        <v>3.62</v>
+        <v>16.46</v>
       </c>
       <c r="J293" t="n">
         <v>7.91</v>
@@ -10406,29 +10406,29 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D294" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E294" t="n">
-        <v>101.5</v>
+        <v>22.685</v>
       </c>
       <c r="F294" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G294" t="n">
-        <v>101.5</v>
+        <v>68.05</v>
       </c>
       <c r="H294" t="n">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="I294" t="n">
-        <v>1.41</v>
+        <v>3.62</v>
       </c>
       <c r="J294" t="n">
         <v>7.91</v>
@@ -10440,29 +10440,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D295" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E295" t="n">
-        <v>12.096</v>
+        <v>6.96</v>
       </c>
       <c r="F295" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G295" t="n">
-        <v>36.29</v>
+        <v>62.64</v>
       </c>
       <c r="H295" t="n">
-        <v>5.13</v>
+        <v>6.49</v>
       </c>
       <c r="I295" t="n">
-        <v>16.46</v>
+        <v>11.56</v>
       </c>
       <c r="J295" t="n">
         <v>7.91</v>
@@ -10474,29 +10474,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E296" t="n">
-        <v>38.26</v>
+        <v>101.5</v>
       </c>
       <c r="F296" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G296" t="n">
-        <v>153.04</v>
+        <v>101.5</v>
       </c>
       <c r="H296" t="n">
-        <v>14.02</v>
+        <v>1.41</v>
       </c>
       <c r="I296" t="n">
-        <v>10.08</v>
+        <v>1.41</v>
       </c>
       <c r="J296" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D307" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E307" t="n">
-        <v>22.555</v>
+        <v>38.055</v>
       </c>
       <c r="F307" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G307" t="n">
-        <v>67.66</v>
+        <v>152.22</v>
       </c>
       <c r="H307" t="n">
-        <v>1.99</v>
+        <v>13.2</v>
       </c>
       <c r="I307" t="n">
-        <v>3.03</v>
+        <v>9.5</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D308" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E308" t="n">
-        <v>11.686</v>
+        <v>99.95</v>
       </c>
       <c r="F308" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G308" t="n">
-        <v>35.06</v>
+        <v>99.95</v>
       </c>
       <c r="H308" t="n">
-        <v>3.9</v>
+        <v>-0.14</v>
       </c>
       <c r="I308" t="n">
-        <v>12.52</v>
+        <v>-0.14</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10916,29 +10916,29 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D309" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E309" t="n">
-        <v>6.916</v>
+        <v>22.555</v>
       </c>
       <c r="F309" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G309" t="n">
-        <v>62.24</v>
+        <v>67.66</v>
       </c>
       <c r="H309" t="n">
-        <v>6.09</v>
+        <v>1.99</v>
       </c>
       <c r="I309" t="n">
-        <v>10.85</v>
+        <v>3.03</v>
       </c>
       <c r="J309" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D310" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E310" t="n">
-        <v>99.95</v>
+        <v>11.686</v>
       </c>
       <c r="F310" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G310" t="n">
-        <v>99.95</v>
+        <v>35.06</v>
       </c>
       <c r="H310" t="n">
-        <v>-0.14</v>
+        <v>3.9</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.14</v>
+        <v>12.52</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D311" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E311" t="n">
-        <v>38.055</v>
+        <v>6.916</v>
       </c>
       <c r="F311" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G311" t="n">
-        <v>152.22</v>
+        <v>62.24</v>
       </c>
       <c r="H311" t="n">
-        <v>13.2</v>
+        <v>6.09</v>
       </c>
       <c r="I311" t="n">
-        <v>9.5</v>
+        <v>10.85</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D312" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E312" t="n">
-        <v>100.38</v>
+        <v>22.9</v>
       </c>
       <c r="F312" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G312" t="n">
-        <v>100.38</v>
+        <v>68.7</v>
       </c>
       <c r="H312" t="n">
-        <v>0.29</v>
+        <v>3.03</v>
       </c>
       <c r="I312" t="n">
-        <v>0.29</v>
+        <v>4.61</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E313" t="n">
-        <v>6.936</v>
+        <v>100.38</v>
       </c>
       <c r="F313" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G313" t="n">
-        <v>62.42</v>
+        <v>100.38</v>
       </c>
       <c r="H313" t="n">
-        <v>6.27</v>
+        <v>0.29</v>
       </c>
       <c r="I313" t="n">
-        <v>11.17</v>
+        <v>0.29</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11086,29 +11086,29 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D314" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E314" t="n">
-        <v>11.742</v>
+        <v>6.936</v>
       </c>
       <c r="F314" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G314" t="n">
-        <v>35.23</v>
+        <v>62.42</v>
       </c>
       <c r="H314" t="n">
-        <v>4.07</v>
+        <v>6.27</v>
       </c>
       <c r="I314" t="n">
-        <v>13.06</v>
+        <v>11.17</v>
       </c>
       <c r="J314" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D315" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E315" t="n">
-        <v>38.66</v>
+        <v>11.742</v>
       </c>
       <c r="F315" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G315" t="n">
-        <v>154.64</v>
+        <v>35.23</v>
       </c>
       <c r="H315" t="n">
-        <v>15.62</v>
+        <v>4.07</v>
       </c>
       <c r="I315" t="n">
-        <v>11.24</v>
+        <v>13.06</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D316" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E316" t="n">
-        <v>22.9</v>
+        <v>38.66</v>
       </c>
       <c r="F316" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G316" t="n">
-        <v>68.7</v>
+        <v>154.64</v>
       </c>
       <c r="H316" t="n">
-        <v>3.03</v>
+        <v>15.62</v>
       </c>
       <c r="I316" t="n">
-        <v>4.61</v>
+        <v>11.24</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11188,29 +11188,29 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D317" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E317" t="n">
-        <v>6.943</v>
+        <v>22.77</v>
       </c>
       <c r="F317" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G317" t="n">
-        <v>62.49</v>
+        <v>68.31</v>
       </c>
       <c r="H317" t="n">
-        <v>6.34</v>
+        <v>2.64</v>
       </c>
       <c r="I317" t="n">
-        <v>11.29</v>
+        <v>4.02</v>
       </c>
       <c r="J317" t="n">
         <v>7.91</v>
@@ -11222,29 +11222,29 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D318" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E318" t="n">
-        <v>38.91</v>
+        <v>11.822</v>
       </c>
       <c r="F318" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G318" t="n">
-        <v>155.64</v>
+        <v>35.47</v>
       </c>
       <c r="H318" t="n">
-        <v>16.62</v>
+        <v>4.31</v>
       </c>
       <c r="I318" t="n">
-        <v>11.96</v>
+        <v>13.83</v>
       </c>
       <c r="J318" t="n">
         <v>7.91</v>
@@ -11290,29 +11290,29 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D320" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E320" t="n">
-        <v>11.822</v>
+        <v>38.91</v>
       </c>
       <c r="F320" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G320" t="n">
-        <v>35.47</v>
+        <v>155.64</v>
       </c>
       <c r="H320" t="n">
-        <v>4.31</v>
+        <v>16.62</v>
       </c>
       <c r="I320" t="n">
-        <v>13.83</v>
+        <v>11.96</v>
       </c>
       <c r="J320" t="n">
         <v>7.91</v>
@@ -11324,29 +11324,29 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D321" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E321" t="n">
-        <v>22.77</v>
+        <v>6.943</v>
       </c>
       <c r="F321" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G321" t="n">
-        <v>68.31</v>
+        <v>62.49</v>
       </c>
       <c r="H321" t="n">
-        <v>2.64</v>
+        <v>6.34</v>
       </c>
       <c r="I321" t="n">
-        <v>4.02</v>
+        <v>11.29</v>
       </c>
       <c r="J321" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D327" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E327" t="n">
-        <v>11.708</v>
+        <v>39.38</v>
       </c>
       <c r="F327" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G327" t="n">
-        <v>35.12</v>
+        <v>157.52</v>
       </c>
       <c r="H327" t="n">
-        <v>3.96</v>
+        <v>18.5</v>
       </c>
       <c r="I327" t="n">
-        <v>12.71</v>
+        <v>13.31</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D328" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E328" t="n">
-        <v>102.72</v>
+        <v>22.83</v>
       </c>
       <c r="F328" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G328" t="n">
-        <v>102.72</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H328" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="I328" t="n">
-        <v>2.63</v>
+        <v>4.29</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11596,29 +11596,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D329" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E329" t="n">
-        <v>22.83</v>
+        <v>7.027</v>
       </c>
       <c r="F329" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G329" t="n">
-        <v>68.48999999999999</v>
+        <v>63.24</v>
       </c>
       <c r="H329" t="n">
-        <v>2.82</v>
+        <v>7.09</v>
       </c>
       <c r="I329" t="n">
-        <v>4.29</v>
+        <v>12.63</v>
       </c>
       <c r="J329" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D330" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E330" t="n">
-        <v>39.38</v>
+        <v>11.708</v>
       </c>
       <c r="F330" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G330" t="n">
-        <v>157.52</v>
+        <v>35.12</v>
       </c>
       <c r="H330" t="n">
-        <v>18.5</v>
+        <v>3.96</v>
       </c>
       <c r="I330" t="n">
-        <v>13.31</v>
+        <v>12.71</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D331" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E331" t="n">
-        <v>7.027</v>
+        <v>102.72</v>
       </c>
       <c r="F331" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G331" t="n">
-        <v>63.24</v>
+        <v>102.72</v>
       </c>
       <c r="H331" t="n">
-        <v>7.09</v>
+        <v>2.63</v>
       </c>
       <c r="I331" t="n">
-        <v>12.63</v>
+        <v>2.63</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -12038,29 +12038,29 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D342" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E342" t="n">
-        <v>100.84</v>
+        <v>22.89</v>
       </c>
       <c r="F342" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G342" t="n">
-        <v>100.84</v>
+        <v>68.67</v>
       </c>
       <c r="H342" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="I342" t="n">
-        <v>0.75</v>
+        <v>4.57</v>
       </c>
       <c r="J342" t="n">
         <v>7.91</v>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D343" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E343" t="n">
-        <v>11.264</v>
+        <v>6.95</v>
       </c>
       <c r="F343" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G343" t="n">
-        <v>33.79</v>
+        <v>62.55</v>
       </c>
       <c r="H343" t="n">
-        <v>2.63</v>
+        <v>6.4</v>
       </c>
       <c r="I343" t="n">
-        <v>8.44</v>
+        <v>11.4</v>
       </c>
       <c r="J343" t="n">
         <v>7.91</v>
@@ -12106,29 +12106,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D344" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E344" t="n">
-        <v>38.99</v>
+        <v>11.264</v>
       </c>
       <c r="F344" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G344" t="n">
-        <v>155.96</v>
+        <v>33.79</v>
       </c>
       <c r="H344" t="n">
-        <v>16.94</v>
+        <v>2.63</v>
       </c>
       <c r="I344" t="n">
-        <v>12.19</v>
+        <v>8.44</v>
       </c>
       <c r="J344" t="n">
         <v>7.91</v>
@@ -12140,29 +12140,29 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E345" t="n">
-        <v>6.95</v>
+        <v>100.84</v>
       </c>
       <c r="F345" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G345" t="n">
-        <v>62.55</v>
+        <v>100.84</v>
       </c>
       <c r="H345" t="n">
-        <v>6.4</v>
+        <v>0.75</v>
       </c>
       <c r="I345" t="n">
-        <v>11.4</v>
+        <v>0.75</v>
       </c>
       <c r="J345" t="n">
         <v>7.91</v>
@@ -12174,29 +12174,29 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D346" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E346" t="n">
-        <v>22.89</v>
+        <v>38.99</v>
       </c>
       <c r="F346" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G346" t="n">
-        <v>68.67</v>
+        <v>155.96</v>
       </c>
       <c r="H346" t="n">
-        <v>3</v>
+        <v>16.94</v>
       </c>
       <c r="I346" t="n">
-        <v>4.57</v>
+        <v>12.19</v>
       </c>
       <c r="J346" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D352" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E352" t="n">
-        <v>101.76</v>
+        <v>22.75</v>
       </c>
       <c r="F352" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G352" t="n">
-        <v>101.76</v>
+        <v>68.25</v>
       </c>
       <c r="H352" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="I352" t="n">
-        <v>1.67</v>
+        <v>3.93</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D353" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E353" t="n">
-        <v>11.186</v>
+        <v>39.745</v>
       </c>
       <c r="F353" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G353" t="n">
-        <v>33.56</v>
+        <v>158.98</v>
       </c>
       <c r="H353" t="n">
-        <v>2.4</v>
+        <v>19.96</v>
       </c>
       <c r="I353" t="n">
-        <v>7.7</v>
+        <v>14.36</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D354" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E354" t="n">
-        <v>39.745</v>
+        <v>6.983</v>
       </c>
       <c r="F354" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G354" t="n">
-        <v>158.98</v>
+        <v>62.85</v>
       </c>
       <c r="H354" t="n">
-        <v>19.96</v>
+        <v>6.7</v>
       </c>
       <c r="I354" t="n">
-        <v>14.36</v>
+        <v>11.93</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E355" t="n">
-        <v>22.75</v>
+        <v>101.76</v>
       </c>
       <c r="F355" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G355" t="n">
-        <v>68.25</v>
+        <v>101.76</v>
       </c>
       <c r="H355" t="n">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="I355" t="n">
-        <v>3.93</v>
+        <v>1.67</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D356" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E356" t="n">
-        <v>6.983</v>
+        <v>11.186</v>
       </c>
       <c r="F356" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G356" t="n">
-        <v>62.85</v>
+        <v>33.56</v>
       </c>
       <c r="H356" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="I356" t="n">
-        <v>11.93</v>
+        <v>7.7</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E357" t="n">
-        <v>22.5</v>
+        <v>101.98</v>
       </c>
       <c r="F357" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G357" t="n">
-        <v>67.5</v>
+        <v>101.98</v>
       </c>
       <c r="H357" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="I357" t="n">
-        <v>2.79</v>
+        <v>1.89</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E358" t="n">
-        <v>101.98</v>
+        <v>11.13</v>
       </c>
       <c r="F358" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G358" t="n">
-        <v>101.98</v>
+        <v>33.39</v>
       </c>
       <c r="H358" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="I358" t="n">
-        <v>1.89</v>
+        <v>7.16</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D359" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E359" t="n">
-        <v>11.13</v>
+        <v>6.978</v>
       </c>
       <c r="F359" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G359" t="n">
-        <v>33.39</v>
+        <v>62.8</v>
       </c>
       <c r="H359" t="n">
-        <v>2.23</v>
+        <v>6.65</v>
       </c>
       <c r="I359" t="n">
-        <v>7.16</v>
+        <v>11.84</v>
       </c>
       <c r="J359" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D360" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E360" t="n">
-        <v>6.978</v>
+        <v>40.07</v>
       </c>
       <c r="F360" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G360" t="n">
-        <v>62.8</v>
+        <v>160.28</v>
       </c>
       <c r="H360" t="n">
-        <v>6.65</v>
+        <v>21.26</v>
       </c>
       <c r="I360" t="n">
-        <v>11.84</v>
+        <v>15.29</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D361" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E361" t="n">
-        <v>40.07</v>
+        <v>22.5</v>
       </c>
       <c r="F361" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G361" t="n">
-        <v>160.28</v>
+        <v>67.5</v>
       </c>
       <c r="H361" t="n">
-        <v>21.26</v>
+        <v>1.83</v>
       </c>
       <c r="I361" t="n">
-        <v>15.29</v>
+        <v>2.79</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D367" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E367" t="n">
-        <v>101.5</v>
+        <v>39.935</v>
       </c>
       <c r="F367" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G367" t="n">
-        <v>101.5</v>
+        <v>159.74</v>
       </c>
       <c r="H367" t="n">
-        <v>1.41</v>
+        <v>20.72</v>
       </c>
       <c r="I367" t="n">
-        <v>1.41</v>
+        <v>14.9</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D368" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E368" t="n">
-        <v>10.91</v>
+        <v>6.91</v>
       </c>
       <c r="F368" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G368" t="n">
-        <v>32.73</v>
+        <v>62.19</v>
       </c>
       <c r="H368" t="n">
-        <v>1.57</v>
+        <v>6.04</v>
       </c>
       <c r="I368" t="n">
-        <v>5.04</v>
+        <v>10.76</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12956,29 +12956,29 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C369" t="n">
         <v>3</v>
       </c>
       <c r="D369" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E369" t="n">
-        <v>22.275</v>
+        <v>10.91</v>
       </c>
       <c r="F369" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G369" t="n">
-        <v>66.81999999999999</v>
+        <v>32.73</v>
       </c>
       <c r="H369" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="I369" t="n">
-        <v>1.75</v>
+        <v>5.04</v>
       </c>
       <c r="J369" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E370" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F370" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G370" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H370" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D371" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E371" t="n">
-        <v>6.91</v>
+        <v>22.275</v>
       </c>
       <c r="F371" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G371" t="n">
-        <v>62.19</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H371" t="n">
-        <v>6.04</v>
+        <v>1.15</v>
       </c>
       <c r="I371" t="n">
-        <v>10.76</v>
+        <v>1.75</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E377" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F377" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G377" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H377" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D378" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E378" t="n">
-        <v>10.962</v>
+        <v>39.57</v>
       </c>
       <c r="F378" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G378" t="n">
-        <v>32.89</v>
+        <v>158.28</v>
       </c>
       <c r="H378" t="n">
-        <v>1.73</v>
+        <v>19.26</v>
       </c>
       <c r="I378" t="n">
-        <v>5.55</v>
+        <v>13.85</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D379" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E379" t="n">
-        <v>39.57</v>
+        <v>22.13</v>
       </c>
       <c r="F379" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G379" t="n">
-        <v>158.28</v>
+        <v>66.39</v>
       </c>
       <c r="H379" t="n">
-        <v>19.26</v>
+        <v>0.72</v>
       </c>
       <c r="I379" t="n">
-        <v>13.85</v>
+        <v>1.1</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E380" t="n">
-        <v>22.13</v>
+        <v>6.941</v>
       </c>
       <c r="F380" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G380" t="n">
-        <v>66.39</v>
+        <v>62.47</v>
       </c>
       <c r="H380" t="n">
-        <v>0.72</v>
+        <v>6.32</v>
       </c>
       <c r="I380" t="n">
-        <v>1.1</v>
+        <v>11.26</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D381" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E381" t="n">
-        <v>101.88</v>
+        <v>10.962</v>
       </c>
       <c r="F381" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G381" t="n">
-        <v>101.88</v>
+        <v>32.89</v>
       </c>
       <c r="H381" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="I381" t="n">
-        <v>1.79</v>
+        <v>5.55</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13559,6 +13559,176 @@
         <v>11.1</v>
       </c>
       <c r="J386" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>3</v>
+      </c>
+      <c r="D387" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E387" t="n">
+        <v>11.006</v>
+      </c>
+      <c r="F387" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G387" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="H387" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I387" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="J387" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>4</v>
+      </c>
+      <c r="D388" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E388" t="n">
+        <v>38.375</v>
+      </c>
+      <c r="F388" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G388" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="H388" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="I388" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="J388" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>3</v>
+      </c>
+      <c r="D389" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E389" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="F389" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G389" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I389" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J389" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+      <c r="D390" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E390" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="F390" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G390" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J390" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>9</v>
+      </c>
+      <c r="D391" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E391" t="n">
+        <v>6.893</v>
+      </c>
+      <c r="F391" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G391" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="H391" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="I391" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="J391" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J391"/>
+  <dimension ref="A1:J396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E12" t="n">
-        <v>21.907</v>
+        <v>10.756</v>
       </c>
       <c r="F12" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G12" t="n">
-        <v>65.72</v>
+        <v>32.27</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>3.56</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E13" t="n">
-        <v>6.788</v>
+        <v>41.121</v>
       </c>
       <c r="F13" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G13" t="n">
-        <v>61.09</v>
+        <v>164.48</v>
       </c>
       <c r="H13" t="n">
-        <v>4.94</v>
+        <v>25.46</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>18.31</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E14" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F14" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G14" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H14" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E15" t="n">
-        <v>41.121</v>
+        <v>6.788</v>
       </c>
       <c r="F15" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G15" t="n">
-        <v>164.48</v>
+        <v>61.09</v>
       </c>
       <c r="H15" t="n">
-        <v>25.46</v>
+        <v>4.94</v>
       </c>
       <c r="I15" t="n">
-        <v>18.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E16" t="n">
-        <v>10.756</v>
+        <v>105.22</v>
       </c>
       <c r="F16" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G16" t="n">
-        <v>32.27</v>
+        <v>105.22</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11</v>
+        <v>5.13</v>
       </c>
       <c r="I16" t="n">
-        <v>3.56</v>
+        <v>5.13</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1158,29 +1158,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E22" t="n">
-        <v>10.536</v>
+        <v>6.799</v>
       </c>
       <c r="F22" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G22" t="n">
-        <v>31.61</v>
+        <v>61.19</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>5.04</v>
       </c>
       <c r="I22" t="n">
-        <v>1.44</v>
+        <v>8.98</v>
       </c>
       <c r="J22" t="n">
         <v>7.91</v>
@@ -1192,29 +1192,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E23" t="n">
-        <v>41.336</v>
+        <v>21.669</v>
       </c>
       <c r="F23" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G23" t="n">
-        <v>165.34</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>26.32</v>
+        <v>-0.66</v>
       </c>
       <c r="I23" t="n">
-        <v>18.93</v>
+        <v>-1.01</v>
       </c>
       <c r="J23" t="n">
         <v>7.91</v>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E24" t="n">
-        <v>21.669</v>
+        <v>105.78</v>
       </c>
       <c r="F24" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G24" t="n">
-        <v>65.01000000000001</v>
+        <v>105.78</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.66</v>
+        <v>5.69</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.01</v>
+        <v>5.68</v>
       </c>
       <c r="J24" t="n">
         <v>7.91</v>
@@ -1260,29 +1260,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E25" t="n">
-        <v>105.78</v>
+        <v>10.536</v>
       </c>
       <c r="F25" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G25" t="n">
-        <v>105.78</v>
+        <v>31.61</v>
       </c>
       <c r="H25" t="n">
-        <v>5.69</v>
+        <v>0.45</v>
       </c>
       <c r="I25" t="n">
-        <v>5.68</v>
+        <v>1.44</v>
       </c>
       <c r="J25" t="n">
         <v>7.91</v>
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E26" t="n">
-        <v>6.799</v>
+        <v>41.336</v>
       </c>
       <c r="F26" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G26" t="n">
-        <v>61.19</v>
+        <v>165.34</v>
       </c>
       <c r="H26" t="n">
-        <v>5.04</v>
+        <v>26.32</v>
       </c>
       <c r="I26" t="n">
-        <v>8.98</v>
+        <v>18.93</v>
       </c>
       <c r="J26" t="n">
         <v>7.91</v>
@@ -1498,29 +1498,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E32" t="n">
-        <v>10.714</v>
+        <v>38.849</v>
       </c>
       <c r="F32" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G32" t="n">
-        <v>32.14</v>
+        <v>155.4</v>
       </c>
       <c r="H32" t="n">
-        <v>0.98</v>
+        <v>16.38</v>
       </c>
       <c r="I32" t="n">
-        <v>3.15</v>
+        <v>11.78</v>
       </c>
       <c r="J32" t="n">
         <v>7.91</v>
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E33" t="n">
-        <v>6.762</v>
+        <v>22.053</v>
       </c>
       <c r="F33" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G33" t="n">
-        <v>60.86</v>
+        <v>66.16</v>
       </c>
       <c r="H33" t="n">
-        <v>4.71</v>
+        <v>0.49</v>
       </c>
       <c r="I33" t="n">
-        <v>8.390000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J33" t="n">
         <v>7.91</v>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E34" t="n">
-        <v>22.053</v>
+        <v>103.08</v>
       </c>
       <c r="F34" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G34" t="n">
-        <v>66.16</v>
+        <v>103.08</v>
       </c>
       <c r="H34" t="n">
-        <v>0.49</v>
+        <v>2.99</v>
       </c>
       <c r="I34" t="n">
-        <v>0.75</v>
+        <v>2.99</v>
       </c>
       <c r="J34" t="n">
         <v>7.91</v>
@@ -1600,29 +1600,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E35" t="n">
-        <v>103.08</v>
+        <v>10.714</v>
       </c>
       <c r="F35" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G35" t="n">
-        <v>103.08</v>
+        <v>32.14</v>
       </c>
       <c r="H35" t="n">
-        <v>2.99</v>
+        <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="J35" t="n">
         <v>7.91</v>
@@ -1634,29 +1634,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E36" t="n">
-        <v>38.849</v>
+        <v>6.762</v>
       </c>
       <c r="F36" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G36" t="n">
-        <v>155.4</v>
+        <v>60.86</v>
       </c>
       <c r="H36" t="n">
-        <v>16.38</v>
+        <v>4.71</v>
       </c>
       <c r="I36" t="n">
-        <v>11.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E42" t="n">
-        <v>22</v>
+        <v>100.06</v>
       </c>
       <c r="F42" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G42" t="n">
-        <v>66</v>
+        <v>100.06</v>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E43" t="n">
-        <v>6.629</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G43" t="n">
-        <v>59.66</v>
+        <v>66</v>
       </c>
       <c r="H43" t="n">
-        <v>3.51</v>
+        <v>0.33</v>
       </c>
       <c r="I43" t="n">
-        <v>6.25</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E44" t="n">
-        <v>10.61</v>
+        <v>6.629</v>
       </c>
       <c r="F44" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G44" t="n">
-        <v>31.83</v>
+        <v>59.66</v>
       </c>
       <c r="H44" t="n">
-        <v>0.67</v>
+        <v>3.51</v>
       </c>
       <c r="I44" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E45" t="n">
-        <v>100.06</v>
+        <v>10.61</v>
       </c>
       <c r="F45" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G45" t="n">
-        <v>100.06</v>
+        <v>31.83</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03</v>
+        <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.03</v>
+        <v>2.15</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -2008,29 +2008,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E47" t="n">
-        <v>99.83</v>
+        <v>10.562</v>
       </c>
       <c r="F47" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G47" t="n">
-        <v>99.83</v>
+        <v>31.69</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.26</v>
+        <v>0.53</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.26</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>7.91</v>
@@ -2042,29 +2042,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E48" t="n">
-        <v>38.312</v>
+        <v>21.778</v>
       </c>
       <c r="F48" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G48" t="n">
-        <v>153.25</v>
+        <v>65.33</v>
       </c>
       <c r="H48" t="n">
-        <v>14.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I48" t="n">
-        <v>10.24</v>
+        <v>-0.52</v>
       </c>
       <c r="J48" t="n">
         <v>7.91</v>
@@ -2076,29 +2076,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E49" t="n">
-        <v>21.778</v>
+        <v>6.622</v>
       </c>
       <c r="F49" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G49" t="n">
-        <v>65.33</v>
+        <v>59.6</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.34</v>
+        <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.52</v>
+        <v>6.14</v>
       </c>
       <c r="J49" t="n">
         <v>7.91</v>
@@ -2110,29 +2110,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E50" t="n">
-        <v>6.622</v>
+        <v>38.312</v>
       </c>
       <c r="F50" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G50" t="n">
-        <v>59.6</v>
+        <v>153.25</v>
       </c>
       <c r="H50" t="n">
-        <v>3.45</v>
+        <v>14.23</v>
       </c>
       <c r="I50" t="n">
-        <v>6.14</v>
+        <v>10.24</v>
       </c>
       <c r="J50" t="n">
         <v>7.91</v>
@@ -2144,29 +2144,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E51" t="n">
-        <v>10.562</v>
+        <v>99.83</v>
       </c>
       <c r="F51" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G51" t="n">
-        <v>31.69</v>
+        <v>99.83</v>
       </c>
       <c r="H51" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>-0.26</v>
       </c>
       <c r="J51" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E62" t="n">
-        <v>6.817</v>
+        <v>105.5</v>
       </c>
       <c r="F62" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G62" t="n">
-        <v>61.35</v>
+        <v>105.5</v>
       </c>
       <c r="H62" t="n">
-        <v>5.2</v>
+        <v>5.41</v>
       </c>
       <c r="I62" t="n">
-        <v>9.26</v>
+        <v>5.41</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E63" t="n">
-        <v>41.064</v>
+        <v>22.7</v>
       </c>
       <c r="F63" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G63" t="n">
-        <v>164.26</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>25.24</v>
+        <v>2.43</v>
       </c>
       <c r="I63" t="n">
-        <v>18.16</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E64" t="n">
-        <v>10.712</v>
+        <v>6.817</v>
       </c>
       <c r="F64" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G64" t="n">
-        <v>32.14</v>
+        <v>61.35</v>
       </c>
       <c r="H64" t="n">
-        <v>0.98</v>
+        <v>5.2</v>
       </c>
       <c r="I64" t="n">
-        <v>3.15</v>
+        <v>9.26</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E65" t="n">
-        <v>22.7</v>
+        <v>41.064</v>
       </c>
       <c r="F65" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G65" t="n">
-        <v>68.09999999999999</v>
+        <v>164.26</v>
       </c>
       <c r="H65" t="n">
-        <v>2.43</v>
+        <v>25.24</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>18.16</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E66" t="n">
-        <v>105.5</v>
+        <v>10.712</v>
       </c>
       <c r="F66" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G66" t="n">
-        <v>105.5</v>
+        <v>32.14</v>
       </c>
       <c r="H66" t="n">
-        <v>5.41</v>
+        <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>5.41</v>
+        <v>3.15</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E72" t="n">
-        <v>104.22</v>
+        <v>10.892</v>
       </c>
       <c r="F72" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G72" t="n">
-        <v>104.22</v>
+        <v>32.68</v>
       </c>
       <c r="H72" t="n">
-        <v>4.13</v>
+        <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>4.13</v>
+        <v>4.88</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E73" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F73" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H73" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I73" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E75" t="n">
-        <v>10.892</v>
+        <v>6.811</v>
       </c>
       <c r="F75" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G75" t="n">
-        <v>32.68</v>
+        <v>61.3</v>
       </c>
       <c r="H75" t="n">
-        <v>1.52</v>
+        <v>5.15</v>
       </c>
       <c r="I75" t="n">
-        <v>4.88</v>
+        <v>9.17</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -2994,29 +2994,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E76" t="n">
-        <v>41.15</v>
+        <v>104.22</v>
       </c>
       <c r="F76" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G76" t="n">
-        <v>164.6</v>
+        <v>104.22</v>
       </c>
       <c r="H76" t="n">
-        <v>25.58</v>
+        <v>4.13</v>
       </c>
       <c r="I76" t="n">
-        <v>18.4</v>
+        <v>4.13</v>
       </c>
       <c r="J76" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E82" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F82" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G82" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I82" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E83" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F83" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G83" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H83" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I83" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E84" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F84" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G84" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H84" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I84" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E85" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F85" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G85" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I85" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E86" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F86" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G86" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H86" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I86" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E92" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F92" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G92" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H92" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I92" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E93" t="n">
-        <v>103.88</v>
+        <v>40.575</v>
       </c>
       <c r="F93" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G93" t="n">
-        <v>103.88</v>
+        <v>162.3</v>
       </c>
       <c r="H93" t="n">
-        <v>3.79</v>
+        <v>23.28</v>
       </c>
       <c r="I93" t="n">
-        <v>3.79</v>
+        <v>16.75</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E94" t="n">
-        <v>6.797</v>
+        <v>103.88</v>
       </c>
       <c r="F94" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G94" t="n">
-        <v>61.17</v>
+        <v>103.88</v>
       </c>
       <c r="H94" t="n">
-        <v>5.02</v>
+        <v>3.79</v>
       </c>
       <c r="I94" t="n">
-        <v>8.94</v>
+        <v>3.79</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E95" t="n">
-        <v>10.876</v>
+        <v>6.797</v>
       </c>
       <c r="F95" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G95" t="n">
-        <v>32.63</v>
+        <v>61.17</v>
       </c>
       <c r="H95" t="n">
-        <v>1.47</v>
+        <v>5.02</v>
       </c>
       <c r="I95" t="n">
-        <v>4.72</v>
+        <v>8.94</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E97" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F97" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G97" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H97" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E98" t="n">
-        <v>40.65</v>
+        <v>23.35</v>
       </c>
       <c r="F98" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G98" t="n">
-        <v>162.6</v>
+        <v>70.05</v>
       </c>
       <c r="H98" t="n">
-        <v>23.58</v>
+        <v>4.38</v>
       </c>
       <c r="I98" t="n">
-        <v>16.96</v>
+        <v>6.67</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E99" t="n">
-        <v>23.35</v>
+        <v>6.839</v>
       </c>
       <c r="F99" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G99" t="n">
-        <v>70.05</v>
+        <v>61.55</v>
       </c>
       <c r="H99" t="n">
-        <v>4.38</v>
+        <v>5.4</v>
       </c>
       <c r="I99" t="n">
-        <v>6.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E100" t="n">
-        <v>6.839</v>
+        <v>40.65</v>
       </c>
       <c r="F100" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G100" t="n">
-        <v>61.55</v>
+        <v>162.6</v>
       </c>
       <c r="H100" t="n">
-        <v>5.4</v>
+        <v>23.58</v>
       </c>
       <c r="I100" t="n">
-        <v>9.619999999999999</v>
+        <v>16.96</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E101" t="n">
-        <v>10.642</v>
+        <v>104.22</v>
       </c>
       <c r="F101" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G101" t="n">
-        <v>31.93</v>
+        <v>104.22</v>
       </c>
       <c r="H101" t="n">
-        <v>0.77</v>
+        <v>4.13</v>
       </c>
       <c r="I101" t="n">
-        <v>2.47</v>
+        <v>4.13</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E107" t="n">
-        <v>40.5</v>
+        <v>103.14</v>
       </c>
       <c r="F107" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G107" t="n">
-        <v>162</v>
+        <v>103.14</v>
       </c>
       <c r="H107" t="n">
-        <v>22.98</v>
+        <v>3.05</v>
       </c>
       <c r="I107" t="n">
-        <v>16.53</v>
+        <v>3.05</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E108" t="n">
-        <v>23.33</v>
+        <v>10.456</v>
       </c>
       <c r="F108" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G108" t="n">
-        <v>69.98999999999999</v>
+        <v>31.37</v>
       </c>
       <c r="H108" t="n">
-        <v>4.32</v>
+        <v>0.21</v>
       </c>
       <c r="I108" t="n">
-        <v>6.58</v>
+        <v>0.67</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E109" t="n">
-        <v>10.456</v>
+        <v>6.785</v>
       </c>
       <c r="F109" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G109" t="n">
-        <v>31.37</v>
+        <v>61.06</v>
       </c>
       <c r="H109" t="n">
-        <v>0.21</v>
+        <v>4.91</v>
       </c>
       <c r="I109" t="n">
-        <v>0.67</v>
+        <v>8.74</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E110" t="n">
-        <v>103.14</v>
+        <v>40.5</v>
       </c>
       <c r="F110" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G110" t="n">
-        <v>103.14</v>
+        <v>162</v>
       </c>
       <c r="H110" t="n">
-        <v>3.05</v>
+        <v>22.98</v>
       </c>
       <c r="I110" t="n">
-        <v>3.05</v>
+        <v>16.53</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E111" t="n">
-        <v>6.785</v>
+        <v>23.33</v>
       </c>
       <c r="F111" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G111" t="n">
-        <v>61.06</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="I111" t="n">
-        <v>8.74</v>
+        <v>6.58</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E122" t="n">
-        <v>23.165</v>
+        <v>106</v>
       </c>
       <c r="F122" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G122" t="n">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="H122" t="n">
-        <v>3.83</v>
+        <v>5.91</v>
       </c>
       <c r="I122" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E123" t="n">
-        <v>6.901</v>
+        <v>40.395</v>
       </c>
       <c r="F123" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G123" t="n">
-        <v>62.11</v>
+        <v>161.58</v>
       </c>
       <c r="H123" t="n">
-        <v>5.96</v>
+        <v>22.56</v>
       </c>
       <c r="I123" t="n">
-        <v>10.61</v>
+        <v>16.23</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E125" t="n">
-        <v>40.395</v>
+        <v>6.901</v>
       </c>
       <c r="F125" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G125" t="n">
-        <v>161.58</v>
+        <v>62.11</v>
       </c>
       <c r="H125" t="n">
-        <v>22.56</v>
+        <v>5.96</v>
       </c>
       <c r="I125" t="n">
-        <v>16.23</v>
+        <v>10.61</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E126" t="n">
-        <v>106</v>
+        <v>23.165</v>
       </c>
       <c r="F126" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G126" t="n">
-        <v>106</v>
+        <v>69.5</v>
       </c>
       <c r="H126" t="n">
-        <v>5.91</v>
+        <v>3.83</v>
       </c>
       <c r="I126" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E137" t="n">
-        <v>6.927</v>
+        <v>40.61</v>
       </c>
       <c r="F137" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G137" t="n">
-        <v>62.34</v>
+        <v>162.44</v>
       </c>
       <c r="H137" t="n">
-        <v>6.19</v>
+        <v>23.42</v>
       </c>
       <c r="I137" t="n">
-        <v>11.02</v>
+        <v>16.85</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E138" t="n">
-        <v>11.728</v>
+        <v>23.3</v>
       </c>
       <c r="F138" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G138" t="n">
-        <v>35.18</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
       <c r="I138" t="n">
-        <v>12.9</v>
+        <v>6.44</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D139" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E139" t="n">
-        <v>104.76</v>
+        <v>6.927</v>
       </c>
       <c r="F139" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G139" t="n">
-        <v>104.76</v>
+        <v>62.34</v>
       </c>
       <c r="H139" t="n">
-        <v>4.67</v>
+        <v>6.19</v>
       </c>
       <c r="I139" t="n">
-        <v>4.67</v>
+        <v>11.02</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>11.728</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>35.18</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>4.02</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>12.9</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E141" t="n">
-        <v>40.61</v>
+        <v>104.76</v>
       </c>
       <c r="F141" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G141" t="n">
-        <v>162.44</v>
+        <v>104.76</v>
       </c>
       <c r="H141" t="n">
-        <v>23.42</v>
+        <v>4.67</v>
       </c>
       <c r="I141" t="n">
-        <v>16.85</v>
+        <v>4.67</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5408,29 +5408,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E147" t="n">
-        <v>6.826</v>
+        <v>38.955</v>
       </c>
       <c r="F147" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G147" t="n">
-        <v>61.43</v>
+        <v>155.82</v>
       </c>
       <c r="H147" t="n">
-        <v>5.28</v>
+        <v>16.8</v>
       </c>
       <c r="I147" t="n">
-        <v>9.4</v>
+        <v>12.08</v>
       </c>
       <c r="J147" t="n">
         <v>7.91</v>
@@ -5442,29 +5442,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E148" t="n">
-        <v>22.755</v>
+        <v>11.162</v>
       </c>
       <c r="F148" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G148" t="n">
-        <v>68.27</v>
+        <v>33.49</v>
       </c>
       <c r="H148" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="I148" t="n">
-        <v>3.96</v>
+        <v>7.48</v>
       </c>
       <c r="J148" t="n">
         <v>7.91</v>
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E150" t="n">
-        <v>38.955</v>
+        <v>22.755</v>
       </c>
       <c r="F150" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G150" t="n">
-        <v>155.82</v>
+        <v>68.27</v>
       </c>
       <c r="H150" t="n">
-        <v>16.8</v>
+        <v>2.6</v>
       </c>
       <c r="I150" t="n">
-        <v>12.08</v>
+        <v>3.96</v>
       </c>
       <c r="J150" t="n">
         <v>7.91</v>
@@ -5544,29 +5544,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E151" t="n">
-        <v>11.162</v>
+        <v>6.826</v>
       </c>
       <c r="F151" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G151" t="n">
-        <v>33.49</v>
+        <v>61.43</v>
       </c>
       <c r="H151" t="n">
-        <v>2.33</v>
+        <v>5.28</v>
       </c>
       <c r="I151" t="n">
-        <v>7.48</v>
+        <v>9.4</v>
       </c>
       <c r="J151" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E162" t="n">
-        <v>6.927</v>
+        <v>103.84</v>
       </c>
       <c r="F162" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G162" t="n">
-        <v>62.34</v>
+        <v>103.84</v>
       </c>
       <c r="H162" t="n">
-        <v>6.19</v>
+        <v>3.75</v>
       </c>
       <c r="I162" t="n">
-        <v>11.02</v>
+        <v>3.75</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E163" t="n">
-        <v>23.01</v>
+        <v>38.845</v>
       </c>
       <c r="F163" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G163" t="n">
-        <v>69.03</v>
+        <v>155.38</v>
       </c>
       <c r="H163" t="n">
-        <v>3.36</v>
+        <v>16.36</v>
       </c>
       <c r="I163" t="n">
-        <v>5.12</v>
+        <v>11.77</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D164" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E164" t="n">
-        <v>10.748</v>
+        <v>6.927</v>
       </c>
       <c r="F164" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G164" t="n">
-        <v>32.24</v>
+        <v>62.34</v>
       </c>
       <c r="H164" t="n">
-        <v>1.08</v>
+        <v>6.19</v>
       </c>
       <c r="I164" t="n">
-        <v>3.47</v>
+        <v>11.02</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E165" t="n">
-        <v>38.845</v>
+        <v>23.01</v>
       </c>
       <c r="F165" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G165" t="n">
-        <v>155.38</v>
+        <v>69.03</v>
       </c>
       <c r="H165" t="n">
-        <v>16.36</v>
+        <v>3.36</v>
       </c>
       <c r="I165" t="n">
-        <v>11.77</v>
+        <v>5.12</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E166" t="n">
-        <v>103.84</v>
+        <v>10.748</v>
       </c>
       <c r="F166" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G166" t="n">
-        <v>103.84</v>
+        <v>32.24</v>
       </c>
       <c r="H166" t="n">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="I166" t="n">
-        <v>3.75</v>
+        <v>3.47</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6258,29 +6258,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E172" t="n">
-        <v>103.22</v>
+        <v>38.74</v>
       </c>
       <c r="F172" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G172" t="n">
-        <v>103.22</v>
+        <v>154.96</v>
       </c>
       <c r="H172" t="n">
-        <v>3.13</v>
+        <v>15.94</v>
       </c>
       <c r="I172" t="n">
-        <v>3.13</v>
+        <v>11.47</v>
       </c>
       <c r="J172" t="n">
         <v>7.91</v>
@@ -6292,29 +6292,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E173" t="n">
-        <v>6.926</v>
+        <v>22.95</v>
       </c>
       <c r="F173" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G173" t="n">
-        <v>62.33</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H173" t="n">
-        <v>6.18</v>
+        <v>3.18</v>
       </c>
       <c r="I173" t="n">
-        <v>11.01</v>
+        <v>4.84</v>
       </c>
       <c r="J173" t="n">
         <v>7.91</v>
@@ -6326,29 +6326,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D174" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E174" t="n">
-        <v>10.712</v>
+        <v>6.926</v>
       </c>
       <c r="F174" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G174" t="n">
-        <v>32.14</v>
+        <v>62.33</v>
       </c>
       <c r="H174" t="n">
-        <v>0.98</v>
+        <v>6.18</v>
       </c>
       <c r="I174" t="n">
-        <v>3.15</v>
+        <v>11.01</v>
       </c>
       <c r="J174" t="n">
         <v>7.91</v>
@@ -6360,29 +6360,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E175" t="n">
-        <v>22.95</v>
+        <v>103.22</v>
       </c>
       <c r="F175" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G175" t="n">
-        <v>68.84999999999999</v>
+        <v>103.22</v>
       </c>
       <c r="H175" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="I175" t="n">
-        <v>4.84</v>
+        <v>3.13</v>
       </c>
       <c r="J175" t="n">
         <v>7.91</v>
@@ -6394,29 +6394,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E176" t="n">
-        <v>38.74</v>
+        <v>10.712</v>
       </c>
       <c r="F176" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G176" t="n">
-        <v>154.96</v>
+        <v>32.14</v>
       </c>
       <c r="H176" t="n">
-        <v>15.94</v>
+        <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>11.47</v>
+        <v>3.15</v>
       </c>
       <c r="J176" t="n">
         <v>7.91</v>
@@ -6598,29 +6598,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E182" t="n">
-        <v>100.14</v>
+        <v>22.835</v>
       </c>
       <c r="F182" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G182" t="n">
-        <v>100.14</v>
+        <v>68.5</v>
       </c>
       <c r="H182" t="n">
-        <v>0.05</v>
+        <v>2.83</v>
       </c>
       <c r="I182" t="n">
-        <v>0.05</v>
+        <v>4.31</v>
       </c>
       <c r="J182" t="n">
         <v>7.91</v>
@@ -6632,29 +6632,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D183" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E183" t="n">
-        <v>10.776</v>
+        <v>6.848</v>
       </c>
       <c r="F183" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G183" t="n">
-        <v>32.33</v>
+        <v>61.63</v>
       </c>
       <c r="H183" t="n">
-        <v>1.17</v>
+        <v>5.48</v>
       </c>
       <c r="I183" t="n">
-        <v>3.75</v>
+        <v>9.76</v>
       </c>
       <c r="J183" t="n">
         <v>7.91</v>
@@ -6666,29 +6666,29 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E184" t="n">
-        <v>37.235</v>
+        <v>10.776</v>
       </c>
       <c r="F184" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G184" t="n">
-        <v>148.94</v>
+        <v>32.33</v>
       </c>
       <c r="H184" t="n">
-        <v>9.92</v>
+        <v>1.17</v>
       </c>
       <c r="I184" t="n">
-        <v>7.14</v>
+        <v>3.75</v>
       </c>
       <c r="J184" t="n">
         <v>7.91</v>
@@ -6700,29 +6700,29 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E185" t="n">
-        <v>22.835</v>
+        <v>100.14</v>
       </c>
       <c r="F185" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G185" t="n">
-        <v>68.5</v>
+        <v>100.14</v>
       </c>
       <c r="H185" t="n">
-        <v>2.83</v>
+        <v>0.05</v>
       </c>
       <c r="I185" t="n">
-        <v>4.31</v>
+        <v>0.05</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -6734,29 +6734,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E186" t="n">
-        <v>6.848</v>
+        <v>37.235</v>
       </c>
       <c r="F186" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G186" t="n">
-        <v>61.63</v>
+        <v>148.94</v>
       </c>
       <c r="H186" t="n">
-        <v>5.48</v>
+        <v>9.92</v>
       </c>
       <c r="I186" t="n">
-        <v>9.76</v>
+        <v>7.14</v>
       </c>
       <c r="J186" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E187" t="n">
-        <v>6.862</v>
+        <v>37.85</v>
       </c>
       <c r="F187" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G187" t="n">
-        <v>61.76</v>
+        <v>151.4</v>
       </c>
       <c r="H187" t="n">
-        <v>5.61</v>
+        <v>12.38</v>
       </c>
       <c r="I187" t="n">
-        <v>9.99</v>
+        <v>8.91</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E188" t="n">
-        <v>101.44</v>
+        <v>6.862</v>
       </c>
       <c r="F188" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G188" t="n">
-        <v>101.44</v>
+        <v>61.76</v>
       </c>
       <c r="H188" t="n">
-        <v>1.35</v>
+        <v>5.61</v>
       </c>
       <c r="I188" t="n">
-        <v>1.35</v>
+        <v>9.99</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E189" t="n">
-        <v>10.708</v>
+        <v>101.44</v>
       </c>
       <c r="F189" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G189" t="n">
-        <v>32.12</v>
+        <v>101.44</v>
       </c>
       <c r="H189" t="n">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I189" t="n">
-        <v>3.08</v>
+        <v>1.35</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E190" t="n">
-        <v>22.845</v>
+        <v>10.708</v>
       </c>
       <c r="F190" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G190" t="n">
-        <v>68.53</v>
+        <v>32.12</v>
       </c>
       <c r="H190" t="n">
-        <v>2.86</v>
+        <v>0.96</v>
       </c>
       <c r="I190" t="n">
-        <v>4.36</v>
+        <v>3.08</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E191" t="n">
-        <v>37.85</v>
+        <v>22.845</v>
       </c>
       <c r="F191" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G191" t="n">
-        <v>151.4</v>
+        <v>68.53</v>
       </c>
       <c r="H191" t="n">
-        <v>12.38</v>
+        <v>2.86</v>
       </c>
       <c r="I191" t="n">
-        <v>8.91</v>
+        <v>4.36</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E192" t="n">
-        <v>22.82</v>
+        <v>102.46</v>
       </c>
       <c r="F192" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G192" t="n">
-        <v>68.45999999999999</v>
+        <v>102.46</v>
       </c>
       <c r="H192" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="I192" t="n">
-        <v>4.25</v>
+        <v>2.37</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E193" t="n">
-        <v>38.755</v>
+        <v>10.792</v>
       </c>
       <c r="F193" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G193" t="n">
-        <v>155.02</v>
+        <v>32.38</v>
       </c>
       <c r="H193" t="n">
-        <v>16</v>
+        <v>1.22</v>
       </c>
       <c r="I193" t="n">
-        <v>11.51</v>
+        <v>3.92</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E194" t="n">
-        <v>102.46</v>
+        <v>22.82</v>
       </c>
       <c r="F194" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G194" t="n">
-        <v>102.46</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H194" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="I194" t="n">
-        <v>2.37</v>
+        <v>4.25</v>
       </c>
       <c r="J194" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E195" t="n">
-        <v>10.792</v>
+        <v>38.755</v>
       </c>
       <c r="F195" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G195" t="n">
-        <v>32.38</v>
+        <v>155.02</v>
       </c>
       <c r="H195" t="n">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="I195" t="n">
-        <v>3.92</v>
+        <v>11.51</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E197" t="n">
-        <v>38.565</v>
+        <v>11.022</v>
       </c>
       <c r="F197" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G197" t="n">
-        <v>154.26</v>
+        <v>33.07</v>
       </c>
       <c r="H197" t="n">
-        <v>15.24</v>
+        <v>1.91</v>
       </c>
       <c r="I197" t="n">
-        <v>10.96</v>
+        <v>6.13</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E198" t="n">
-        <v>102.48</v>
+        <v>22.6</v>
       </c>
       <c r="F198" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G198" t="n">
-        <v>102.48</v>
+        <v>67.8</v>
       </c>
       <c r="H198" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="I198" t="n">
-        <v>2.39</v>
+        <v>3.24</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E200" t="n">
-        <v>22.6</v>
+        <v>102.48</v>
       </c>
       <c r="F200" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G200" t="n">
-        <v>67.8</v>
+        <v>102.48</v>
       </c>
       <c r="H200" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="I200" t="n">
-        <v>3.24</v>
+        <v>2.39</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D201" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E201" t="n">
-        <v>11.022</v>
+        <v>38.565</v>
       </c>
       <c r="F201" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G201" t="n">
-        <v>33.07</v>
+        <v>154.26</v>
       </c>
       <c r="H201" t="n">
-        <v>1.91</v>
+        <v>15.24</v>
       </c>
       <c r="I201" t="n">
-        <v>6.13</v>
+        <v>10.96</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D207" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E207" t="n">
-        <v>22.725</v>
+        <v>6.865</v>
       </c>
       <c r="F207" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G207" t="n">
-        <v>68.18000000000001</v>
+        <v>61.79</v>
       </c>
       <c r="H207" t="n">
-        <v>2.51</v>
+        <v>5.64</v>
       </c>
       <c r="I207" t="n">
-        <v>3.82</v>
+        <v>10.04</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E208" t="n">
-        <v>37.82</v>
+        <v>11.172</v>
       </c>
       <c r="F208" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G208" t="n">
-        <v>151.28</v>
+        <v>33.52</v>
       </c>
       <c r="H208" t="n">
-        <v>12.26</v>
+        <v>2.36</v>
       </c>
       <c r="I208" t="n">
-        <v>8.82</v>
+        <v>7.57</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7516,29 +7516,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E209" t="n">
-        <v>11.172</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F209" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G209" t="n">
-        <v>33.52</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H209" t="n">
-        <v>2.36</v>
+        <v>-0.19</v>
       </c>
       <c r="I209" t="n">
-        <v>7.57</v>
+        <v>-0.19</v>
       </c>
       <c r="J209" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E210" t="n">
-        <v>6.865</v>
+        <v>22.725</v>
       </c>
       <c r="F210" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G210" t="n">
-        <v>61.79</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H210" t="n">
-        <v>5.64</v>
+        <v>2.51</v>
       </c>
       <c r="I210" t="n">
-        <v>10.04</v>
+        <v>3.82</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D211" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E211" t="n">
-        <v>99.90000000000001</v>
+        <v>37.82</v>
       </c>
       <c r="F211" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G211" t="n">
-        <v>99.90000000000001</v>
+        <v>151.28</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.19</v>
+        <v>12.26</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.19</v>
+        <v>8.82</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E222" t="n">
-        <v>35.89</v>
+        <v>23.12</v>
       </c>
       <c r="F222" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G222" t="n">
-        <v>143.56</v>
+        <v>69.36</v>
       </c>
       <c r="H222" t="n">
-        <v>4.54</v>
+        <v>3.69</v>
       </c>
       <c r="I222" t="n">
-        <v>3.27</v>
+        <v>5.62</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D223" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E223" t="n">
-        <v>11.5</v>
+        <v>6.818</v>
       </c>
       <c r="F223" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G223" t="n">
-        <v>34.5</v>
+        <v>61.36</v>
       </c>
       <c r="H223" t="n">
-        <v>3.34</v>
+        <v>5.21</v>
       </c>
       <c r="I223" t="n">
-        <v>10.72</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E225" t="n">
-        <v>6.818</v>
+        <v>11.5</v>
       </c>
       <c r="F225" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G225" t="n">
-        <v>61.36</v>
+        <v>34.5</v>
       </c>
       <c r="H225" t="n">
-        <v>5.21</v>
+        <v>3.34</v>
       </c>
       <c r="I225" t="n">
-        <v>9.279999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D226" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E226" t="n">
-        <v>23.12</v>
+        <v>35.89</v>
       </c>
       <c r="F226" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G226" t="n">
-        <v>69.36</v>
+        <v>143.56</v>
       </c>
       <c r="H226" t="n">
-        <v>3.69</v>
+        <v>4.54</v>
       </c>
       <c r="I226" t="n">
-        <v>5.62</v>
+        <v>3.27</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E232" t="n">
-        <v>37.44</v>
+        <v>97.86</v>
       </c>
       <c r="F232" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G232" t="n">
-        <v>149.76</v>
+        <v>97.86</v>
       </c>
       <c r="H232" t="n">
-        <v>10.74</v>
+        <v>-2.23</v>
       </c>
       <c r="I232" t="n">
-        <v>7.73</v>
+        <v>-2.23</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D233" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E233" t="n">
-        <v>11.544</v>
+        <v>6.812</v>
       </c>
       <c r="F233" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G233" t="n">
-        <v>34.63</v>
+        <v>61.31</v>
       </c>
       <c r="H233" t="n">
-        <v>3.47</v>
+        <v>5.16</v>
       </c>
       <c r="I233" t="n">
-        <v>11.14</v>
+        <v>9.19</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8366,29 +8366,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E234" t="n">
-        <v>6.812</v>
+        <v>23.17</v>
       </c>
       <c r="F234" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G234" t="n">
-        <v>61.31</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H234" t="n">
-        <v>5.16</v>
+        <v>3.84</v>
       </c>
       <c r="I234" t="n">
-        <v>9.19</v>
+        <v>5.85</v>
       </c>
       <c r="J234" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D235" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E235" t="n">
-        <v>97.86</v>
+        <v>37.44</v>
       </c>
       <c r="F235" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G235" t="n">
-        <v>97.86</v>
+        <v>149.76</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.23</v>
+        <v>10.74</v>
       </c>
       <c r="I235" t="n">
-        <v>-2.23</v>
+        <v>7.73</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C236" t="n">
         <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E236" t="n">
-        <v>23.17</v>
+        <v>11.544</v>
       </c>
       <c r="F236" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G236" t="n">
-        <v>69.51000000000001</v>
+        <v>34.63</v>
       </c>
       <c r="H236" t="n">
-        <v>3.84</v>
+        <v>3.47</v>
       </c>
       <c r="I236" t="n">
-        <v>5.85</v>
+        <v>11.14</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D247" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E247" t="n">
-        <v>7.032</v>
+        <v>12.18</v>
       </c>
       <c r="F247" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G247" t="n">
-        <v>63.29</v>
+        <v>36.54</v>
       </c>
       <c r="H247" t="n">
-        <v>7.14</v>
+        <v>5.38</v>
       </c>
       <c r="I247" t="n">
-        <v>12.72</v>
+        <v>17.27</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E248" t="n">
-        <v>103.2</v>
+        <v>23.28</v>
       </c>
       <c r="F248" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G248" t="n">
-        <v>103.2</v>
+        <v>69.84</v>
       </c>
       <c r="H248" t="n">
-        <v>3.11</v>
+        <v>4.17</v>
       </c>
       <c r="I248" t="n">
-        <v>3.11</v>
+        <v>6.35</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E250" t="n">
-        <v>23.28</v>
+        <v>103.2</v>
       </c>
       <c r="F250" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G250" t="n">
-        <v>69.84</v>
+        <v>103.2</v>
       </c>
       <c r="H250" t="n">
-        <v>4.17</v>
+        <v>3.11</v>
       </c>
       <c r="I250" t="n">
-        <v>6.35</v>
+        <v>3.11</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D251" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E251" t="n">
-        <v>12.18</v>
+        <v>7.032</v>
       </c>
       <c r="F251" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G251" t="n">
-        <v>36.54</v>
+        <v>63.29</v>
       </c>
       <c r="H251" t="n">
-        <v>5.38</v>
+        <v>7.14</v>
       </c>
       <c r="I251" t="n">
-        <v>17.27</v>
+        <v>12.72</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E257" t="n">
-        <v>12.232</v>
+        <v>103.02</v>
       </c>
       <c r="F257" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G257" t="n">
-        <v>36.7</v>
+        <v>103.02</v>
       </c>
       <c r="H257" t="n">
-        <v>5.54</v>
+        <v>2.93</v>
       </c>
       <c r="I257" t="n">
-        <v>17.78</v>
+        <v>2.93</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D258" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E258" t="n">
-        <v>7.056</v>
+        <v>23.2</v>
       </c>
       <c r="F258" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G258" t="n">
-        <v>63.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H258" t="n">
-        <v>7.35</v>
+        <v>3.93</v>
       </c>
       <c r="I258" t="n">
-        <v>13.09</v>
+        <v>5.98</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D259" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E259" t="n">
-        <v>23.2</v>
+        <v>37.84</v>
       </c>
       <c r="F259" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G259" t="n">
-        <v>69.59999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="H259" t="n">
-        <v>3.93</v>
+        <v>12.34</v>
       </c>
       <c r="I259" t="n">
-        <v>5.98</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E260" t="n">
-        <v>103.02</v>
+        <v>12.232</v>
       </c>
       <c r="F260" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G260" t="n">
-        <v>103.02</v>
+        <v>36.7</v>
       </c>
       <c r="H260" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="I260" t="n">
-        <v>2.93</v>
+        <v>17.78</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E261" t="n">
-        <v>37.84</v>
+        <v>7.056</v>
       </c>
       <c r="F261" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G261" t="n">
-        <v>151.36</v>
+        <v>63.5</v>
       </c>
       <c r="H261" t="n">
-        <v>12.34</v>
+        <v>7.35</v>
       </c>
       <c r="I261" t="n">
-        <v>8.880000000000001</v>
+        <v>13.09</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C272" t="n">
         <v>3</v>
       </c>
       <c r="D272" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E272" t="n">
-        <v>12.308</v>
+        <v>23.135</v>
       </c>
       <c r="F272" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G272" t="n">
-        <v>36.92</v>
+        <v>69.41</v>
       </c>
       <c r="H272" t="n">
-        <v>5.76</v>
+        <v>3.74</v>
       </c>
       <c r="I272" t="n">
-        <v>18.49</v>
+        <v>5.7</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E273" t="n">
-        <v>104.54</v>
+        <v>39.325</v>
       </c>
       <c r="F273" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G273" t="n">
-        <v>104.54</v>
+        <v>157.3</v>
       </c>
       <c r="H273" t="n">
-        <v>4.45</v>
+        <v>18.28</v>
       </c>
       <c r="I273" t="n">
-        <v>4.45</v>
+        <v>13.15</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E275" t="n">
-        <v>39.325</v>
+        <v>104.54</v>
       </c>
       <c r="F275" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G275" t="n">
-        <v>157.3</v>
+        <v>104.54</v>
       </c>
       <c r="H275" t="n">
-        <v>18.28</v>
+        <v>4.45</v>
       </c>
       <c r="I275" t="n">
-        <v>13.15</v>
+        <v>4.45</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C276" t="n">
         <v>3</v>
       </c>
       <c r="D276" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E276" t="n">
-        <v>23.135</v>
+        <v>12.308</v>
       </c>
       <c r="F276" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G276" t="n">
-        <v>69.41</v>
+        <v>36.92</v>
       </c>
       <c r="H276" t="n">
-        <v>3.74</v>
+        <v>5.76</v>
       </c>
       <c r="I276" t="n">
-        <v>5.7</v>
+        <v>18.49</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D282" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E282" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F282" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G282" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H282" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I282" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D283" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E283" t="n">
-        <v>22.97</v>
+        <v>7.054</v>
       </c>
       <c r="F283" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G283" t="n">
-        <v>68.91</v>
+        <v>63.49</v>
       </c>
       <c r="H283" t="n">
-        <v>3.24</v>
+        <v>7.34</v>
       </c>
       <c r="I283" t="n">
-        <v>4.93</v>
+        <v>13.07</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D284" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E284" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F284" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G284" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H284" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I284" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D285" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E285" t="n">
-        <v>39.745</v>
+        <v>104.46</v>
       </c>
       <c r="F285" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G285" t="n">
-        <v>158.98</v>
+        <v>104.46</v>
       </c>
       <c r="H285" t="n">
-        <v>19.96</v>
+        <v>4.37</v>
       </c>
       <c r="I285" t="n">
-        <v>14.36</v>
+        <v>4.37</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C286" t="n">
         <v>3</v>
       </c>
       <c r="D286" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E286" t="n">
-        <v>12.468</v>
+        <v>22.97</v>
       </c>
       <c r="F286" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G286" t="n">
-        <v>37.4</v>
+        <v>68.91</v>
       </c>
       <c r="H286" t="n">
-        <v>6.24</v>
+        <v>3.24</v>
       </c>
       <c r="I286" t="n">
-        <v>20.03</v>
+        <v>4.93</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D297" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E297" t="n">
-        <v>38.49</v>
+        <v>100.42</v>
       </c>
       <c r="F297" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G297" t="n">
-        <v>153.96</v>
+        <v>100.42</v>
       </c>
       <c r="H297" t="n">
-        <v>14.94</v>
+        <v>0.33</v>
       </c>
       <c r="I297" t="n">
-        <v>10.75</v>
+        <v>0.33</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D298" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E298" t="n">
-        <v>22.78</v>
+        <v>6.915</v>
       </c>
       <c r="F298" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G298" t="n">
-        <v>68.34</v>
+        <v>62.23</v>
       </c>
       <c r="H298" t="n">
-        <v>2.67</v>
+        <v>6.08</v>
       </c>
       <c r="I298" t="n">
-        <v>4.07</v>
+        <v>10.83</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10576,29 +10576,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C299" t="n">
         <v>3</v>
       </c>
       <c r="D299" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E299" t="n">
-        <v>11.92</v>
+        <v>22.78</v>
       </c>
       <c r="F299" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G299" t="n">
-        <v>35.76</v>
+        <v>68.34</v>
       </c>
       <c r="H299" t="n">
-        <v>4.6</v>
+        <v>2.67</v>
       </c>
       <c r="I299" t="n">
-        <v>14.76</v>
+        <v>4.07</v>
       </c>
       <c r="J299" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D300" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E300" t="n">
-        <v>6.915</v>
+        <v>11.92</v>
       </c>
       <c r="F300" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G300" t="n">
-        <v>62.23</v>
+        <v>35.76</v>
       </c>
       <c r="H300" t="n">
-        <v>6.08</v>
+        <v>4.6</v>
       </c>
       <c r="I300" t="n">
-        <v>10.83</v>
+        <v>14.76</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D301" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E301" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F301" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G301" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H301" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I301" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D307" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E307" t="n">
-        <v>38.055</v>
+        <v>11.686</v>
       </c>
       <c r="F307" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G307" t="n">
-        <v>152.22</v>
+        <v>35.06</v>
       </c>
       <c r="H307" t="n">
-        <v>13.2</v>
+        <v>3.9</v>
       </c>
       <c r="I307" t="n">
-        <v>9.5</v>
+        <v>12.52</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D308" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E308" t="n">
-        <v>99.95</v>
+        <v>22.555</v>
       </c>
       <c r="F308" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G308" t="n">
-        <v>99.95</v>
+        <v>67.66</v>
       </c>
       <c r="H308" t="n">
-        <v>-0.14</v>
+        <v>1.99</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.14</v>
+        <v>3.03</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10916,29 +10916,29 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D309" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E309" t="n">
-        <v>22.555</v>
+        <v>6.916</v>
       </c>
       <c r="F309" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G309" t="n">
-        <v>67.66</v>
+        <v>62.24</v>
       </c>
       <c r="H309" t="n">
-        <v>1.99</v>
+        <v>6.09</v>
       </c>
       <c r="I309" t="n">
-        <v>3.03</v>
+        <v>10.85</v>
       </c>
       <c r="J309" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D310" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E310" t="n">
-        <v>11.686</v>
+        <v>38.055</v>
       </c>
       <c r="F310" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G310" t="n">
-        <v>35.06</v>
+        <v>152.22</v>
       </c>
       <c r="H310" t="n">
-        <v>3.9</v>
+        <v>13.2</v>
       </c>
       <c r="I310" t="n">
-        <v>12.52</v>
+        <v>9.5</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E311" t="n">
-        <v>6.916</v>
+        <v>99.95</v>
       </c>
       <c r="F311" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G311" t="n">
-        <v>62.24</v>
+        <v>99.95</v>
       </c>
       <c r="H311" t="n">
-        <v>6.09</v>
+        <v>-0.14</v>
       </c>
       <c r="I311" t="n">
-        <v>10.85</v>
+        <v>-0.14</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D322" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E322" t="n">
-        <v>6.967</v>
+        <v>11.81</v>
       </c>
       <c r="F322" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G322" t="n">
-        <v>62.7</v>
+        <v>35.43</v>
       </c>
       <c r="H322" t="n">
-        <v>6.55</v>
+        <v>4.27</v>
       </c>
       <c r="I322" t="n">
-        <v>11.67</v>
+        <v>13.7</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D323" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E323" t="n">
-        <v>39.07</v>
+        <v>101.7</v>
       </c>
       <c r="F323" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G323" t="n">
-        <v>156.28</v>
+        <v>101.7</v>
       </c>
       <c r="H323" t="n">
-        <v>17.26</v>
+        <v>1.61</v>
       </c>
       <c r="I323" t="n">
-        <v>12.42</v>
+        <v>1.61</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D325" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E325" t="n">
-        <v>101.7</v>
+        <v>39.07</v>
       </c>
       <c r="F325" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G325" t="n">
-        <v>101.7</v>
+        <v>156.28</v>
       </c>
       <c r="H325" t="n">
-        <v>1.61</v>
+        <v>17.26</v>
       </c>
       <c r="I325" t="n">
-        <v>1.61</v>
+        <v>12.42</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D326" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E326" t="n">
-        <v>11.81</v>
+        <v>6.967</v>
       </c>
       <c r="F326" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G326" t="n">
-        <v>35.43</v>
+        <v>62.7</v>
       </c>
       <c r="H326" t="n">
-        <v>4.27</v>
+        <v>6.55</v>
       </c>
       <c r="I326" t="n">
-        <v>13.7</v>
+        <v>11.67</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11698,29 +11698,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D332" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E332" t="n">
-        <v>38.98</v>
+        <v>6.948</v>
       </c>
       <c r="F332" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G332" t="n">
-        <v>155.92</v>
+        <v>62.53</v>
       </c>
       <c r="H332" t="n">
-        <v>16.9</v>
+        <v>6.38</v>
       </c>
       <c r="I332" t="n">
-        <v>12.16</v>
+        <v>11.36</v>
       </c>
       <c r="J332" t="n">
         <v>7.91</v>
@@ -11732,29 +11732,29 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D333" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E333" t="n">
-        <v>101.38</v>
+        <v>22.745</v>
       </c>
       <c r="F333" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G333" t="n">
-        <v>101.38</v>
+        <v>68.23</v>
       </c>
       <c r="H333" t="n">
-        <v>1.29</v>
+        <v>2.56</v>
       </c>
       <c r="I333" t="n">
-        <v>1.29</v>
+        <v>3.9</v>
       </c>
       <c r="J333" t="n">
         <v>7.91</v>
@@ -11766,29 +11766,29 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C334" t="n">
         <v>3</v>
       </c>
       <c r="D334" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E334" t="n">
-        <v>22.745</v>
+        <v>11.5</v>
       </c>
       <c r="F334" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G334" t="n">
-        <v>68.23</v>
+        <v>34.5</v>
       </c>
       <c r="H334" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="I334" t="n">
-        <v>3.9</v>
+        <v>10.72</v>
       </c>
       <c r="J334" t="n">
         <v>7.91</v>
@@ -11800,29 +11800,29 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D335" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E335" t="n">
-        <v>6.948</v>
+        <v>38.98</v>
       </c>
       <c r="F335" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G335" t="n">
-        <v>62.53</v>
+        <v>155.92</v>
       </c>
       <c r="H335" t="n">
-        <v>6.38</v>
+        <v>16.9</v>
       </c>
       <c r="I335" t="n">
-        <v>11.36</v>
+        <v>12.16</v>
       </c>
       <c r="J335" t="n">
         <v>7.91</v>
@@ -11834,29 +11834,29 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D336" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E336" t="n">
-        <v>11.5</v>
+        <v>101.38</v>
       </c>
       <c r="F336" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G336" t="n">
-        <v>34.5</v>
+        <v>101.38</v>
       </c>
       <c r="H336" t="n">
-        <v>3.34</v>
+        <v>1.29</v>
       </c>
       <c r="I336" t="n">
-        <v>10.72</v>
+        <v>1.29</v>
       </c>
       <c r="J336" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D347" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E347" t="n">
-        <v>22.82</v>
+        <v>7.005</v>
       </c>
       <c r="F347" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G347" t="n">
-        <v>68.45999999999999</v>
+        <v>63.05</v>
       </c>
       <c r="H347" t="n">
-        <v>2.79</v>
+        <v>6.9</v>
       </c>
       <c r="I347" t="n">
-        <v>4.25</v>
+        <v>12.29</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D348" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E348" t="n">
-        <v>39</v>
+        <v>11.206</v>
       </c>
       <c r="F348" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G348" t="n">
-        <v>156</v>
+        <v>33.62</v>
       </c>
       <c r="H348" t="n">
-        <v>16.98</v>
+        <v>2.46</v>
       </c>
       <c r="I348" t="n">
-        <v>12.21</v>
+        <v>7.89</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12276,29 +12276,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D349" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E349" t="n">
-        <v>101.78</v>
+        <v>39</v>
       </c>
       <c r="F349" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G349" t="n">
-        <v>101.78</v>
+        <v>156</v>
       </c>
       <c r="H349" t="n">
-        <v>1.69</v>
+        <v>16.98</v>
       </c>
       <c r="I349" t="n">
-        <v>1.69</v>
+        <v>12.21</v>
       </c>
       <c r="J349" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D350" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E350" t="n">
-        <v>7.005</v>
+        <v>22.82</v>
       </c>
       <c r="F350" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G350" t="n">
-        <v>63.05</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H350" t="n">
-        <v>6.9</v>
+        <v>2.79</v>
       </c>
       <c r="I350" t="n">
-        <v>12.29</v>
+        <v>4.25</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E351" t="n">
-        <v>11.206</v>
+        <v>101.78</v>
       </c>
       <c r="F351" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G351" t="n">
-        <v>33.62</v>
+        <v>101.78</v>
       </c>
       <c r="H351" t="n">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="I351" t="n">
-        <v>7.89</v>
+        <v>1.69</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D357" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E357" t="n">
-        <v>101.98</v>
+        <v>22.5</v>
       </c>
       <c r="F357" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G357" t="n">
-        <v>101.98</v>
+        <v>67.5</v>
       </c>
       <c r="H357" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I357" t="n">
-        <v>1.89</v>
+        <v>2.79</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D358" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E358" t="n">
-        <v>11.13</v>
+        <v>40.07</v>
       </c>
       <c r="F358" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G358" t="n">
-        <v>33.39</v>
+        <v>160.28</v>
       </c>
       <c r="H358" t="n">
-        <v>2.23</v>
+        <v>21.26</v>
       </c>
       <c r="I358" t="n">
-        <v>7.16</v>
+        <v>15.29</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D360" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E360" t="n">
-        <v>40.07</v>
+        <v>11.13</v>
       </c>
       <c r="F360" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G360" t="n">
-        <v>160.28</v>
+        <v>33.39</v>
       </c>
       <c r="H360" t="n">
-        <v>21.26</v>
+        <v>2.23</v>
       </c>
       <c r="I360" t="n">
-        <v>15.29</v>
+        <v>7.16</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E361" t="n">
-        <v>22.5</v>
+        <v>101.98</v>
       </c>
       <c r="F361" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G361" t="n">
-        <v>67.5</v>
+        <v>101.98</v>
       </c>
       <c r="H361" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="I361" t="n">
-        <v>2.79</v>
+        <v>1.89</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D367" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E367" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F367" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G367" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H367" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I367" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D368" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E368" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
       <c r="F368" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G368" t="n">
-        <v>62.19</v>
+        <v>32.73</v>
       </c>
       <c r="H368" t="n">
-        <v>6.04</v>
+        <v>1.57</v>
       </c>
       <c r="I368" t="n">
-        <v>10.76</v>
+        <v>5.04</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12956,29 +12956,29 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C369" t="n">
         <v>3</v>
       </c>
       <c r="D369" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E369" t="n">
-        <v>10.91</v>
+        <v>22.275</v>
       </c>
       <c r="F369" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G369" t="n">
-        <v>32.73</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H369" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="I369" t="n">
-        <v>5.04</v>
+        <v>1.75</v>
       </c>
       <c r="J369" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D370" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E370" t="n">
-        <v>101.5</v>
+        <v>39.935</v>
       </c>
       <c r="F370" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G370" t="n">
-        <v>101.5</v>
+        <v>159.74</v>
       </c>
       <c r="H370" t="n">
-        <v>1.41</v>
+        <v>20.72</v>
       </c>
       <c r="I370" t="n">
-        <v>1.41</v>
+        <v>14.9</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E371" t="n">
-        <v>22.275</v>
+        <v>6.91</v>
       </c>
       <c r="F371" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G371" t="n">
-        <v>66.81999999999999</v>
+        <v>62.19</v>
       </c>
       <c r="H371" t="n">
-        <v>1.15</v>
+        <v>6.04</v>
       </c>
       <c r="I371" t="n">
-        <v>1.75</v>
+        <v>10.76</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D377" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E377" t="n">
-        <v>101.88</v>
+        <v>6.941</v>
       </c>
       <c r="F377" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G377" t="n">
-        <v>101.88</v>
+        <v>62.47</v>
       </c>
       <c r="H377" t="n">
-        <v>1.79</v>
+        <v>6.32</v>
       </c>
       <c r="I377" t="n">
-        <v>1.79</v>
+        <v>11.26</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D378" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E378" t="n">
-        <v>39.57</v>
+        <v>22.13</v>
       </c>
       <c r="F378" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G378" t="n">
-        <v>158.28</v>
+        <v>66.39</v>
       </c>
       <c r="H378" t="n">
-        <v>19.26</v>
+        <v>0.72</v>
       </c>
       <c r="I378" t="n">
-        <v>13.85</v>
+        <v>1.1</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C379" t="n">
         <v>3</v>
       </c>
       <c r="D379" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E379" t="n">
-        <v>22.13</v>
+        <v>10.962</v>
       </c>
       <c r="F379" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G379" t="n">
-        <v>66.39</v>
+        <v>32.89</v>
       </c>
       <c r="H379" t="n">
-        <v>0.72</v>
+        <v>1.73</v>
       </c>
       <c r="I379" t="n">
-        <v>1.1</v>
+        <v>5.55</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D380" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E380" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F380" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G380" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H380" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I380" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D381" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E381" t="n">
-        <v>10.962</v>
+        <v>39.57</v>
       </c>
       <c r="F381" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G381" t="n">
-        <v>32.89</v>
+        <v>158.28</v>
       </c>
       <c r="H381" t="n">
-        <v>1.73</v>
+        <v>19.26</v>
       </c>
       <c r="I381" t="n">
-        <v>5.55</v>
+        <v>13.85</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D387" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E387" t="n">
-        <v>11.006</v>
+        <v>6.893</v>
       </c>
       <c r="F387" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G387" t="n">
-        <v>33.02</v>
+        <v>62.04</v>
       </c>
       <c r="H387" t="n">
-        <v>1.86</v>
+        <v>5.89</v>
       </c>
       <c r="I387" t="n">
-        <v>5.97</v>
+        <v>10.49</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D388" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E388" t="n">
-        <v>38.375</v>
+        <v>11.006</v>
       </c>
       <c r="F388" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G388" t="n">
-        <v>153.5</v>
+        <v>33.02</v>
       </c>
       <c r="H388" t="n">
-        <v>14.48</v>
+        <v>1.86</v>
       </c>
       <c r="I388" t="n">
-        <v>10.42</v>
+        <v>5.97</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D389" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E389" t="n">
-        <v>21.83</v>
+        <v>38.375</v>
       </c>
       <c r="F389" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G389" t="n">
-        <v>65.48999999999999</v>
+        <v>153.5</v>
       </c>
       <c r="H389" t="n">
-        <v>-0.18</v>
+        <v>14.48</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.27</v>
+        <v>10.42</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D390" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E390" t="n">
-        <v>100.76</v>
+        <v>21.83</v>
       </c>
       <c r="F390" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G390" t="n">
-        <v>100.76</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H390" t="n">
-        <v>0.67</v>
+        <v>-0.18</v>
       </c>
       <c r="I390" t="n">
-        <v>0.67</v>
+        <v>-0.27</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,31 +13704,201 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E391" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="F391" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G391" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="H391" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J391" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E392" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="F392" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G392" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="H392" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I392" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J392" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>3</v>
+      </c>
+      <c r="D393" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E393" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F393" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G393" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H393" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I393" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="J393" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>4</v>
+      </c>
+      <c r="D394" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E394" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="F394" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G394" t="n">
+        <v>155.68</v>
+      </c>
+      <c r="H394" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="I394" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="J394" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>3</v>
+      </c>
+      <c r="D395" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E395" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="F395" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G395" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I395" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="J395" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C391" t="n">
+      <c r="C396" t="n">
         <v>9</v>
       </c>
-      <c r="D391" t="n">
+      <c r="D396" t="n">
         <v>6.239</v>
       </c>
-      <c r="E391" t="n">
-        <v>6.893</v>
-      </c>
-      <c r="F391" t="n">
+      <c r="E396" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="F396" t="n">
         <v>56.15</v>
       </c>
-      <c r="G391" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="H391" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="I391" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="J391" t="n">
+      <c r="G396" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="H396" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="I396" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J396" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J396"/>
+  <dimension ref="A1:J401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E12" t="n">
-        <v>10.756</v>
+        <v>105.22</v>
       </c>
       <c r="F12" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G12" t="n">
-        <v>32.27</v>
+        <v>105.22</v>
       </c>
       <c r="H12" t="n">
-        <v>1.11</v>
+        <v>5.13</v>
       </c>
       <c r="I12" t="n">
-        <v>3.56</v>
+        <v>5.13</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E13" t="n">
-        <v>41.121</v>
+        <v>6.788</v>
       </c>
       <c r="F13" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G13" t="n">
-        <v>164.48</v>
+        <v>61.09</v>
       </c>
       <c r="H13" t="n">
-        <v>25.46</v>
+        <v>4.94</v>
       </c>
       <c r="I13" t="n">
-        <v>18.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E14" t="n">
-        <v>21.907</v>
+        <v>10.756</v>
       </c>
       <c r="F14" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G14" t="n">
-        <v>65.72</v>
+        <v>32.27</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>3.56</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E15" t="n">
-        <v>6.788</v>
+        <v>41.121</v>
       </c>
       <c r="F15" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G15" t="n">
-        <v>61.09</v>
+        <v>164.48</v>
       </c>
       <c r="H15" t="n">
-        <v>4.94</v>
+        <v>25.46</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>18.31</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E16" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F16" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G16" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H16" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1158,29 +1158,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E22" t="n">
-        <v>6.799</v>
+        <v>41.336</v>
       </c>
       <c r="F22" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G22" t="n">
-        <v>61.19</v>
+        <v>165.34</v>
       </c>
       <c r="H22" t="n">
-        <v>5.04</v>
+        <v>26.32</v>
       </c>
       <c r="I22" t="n">
-        <v>8.98</v>
+        <v>18.93</v>
       </c>
       <c r="J22" t="n">
         <v>7.91</v>
@@ -1192,29 +1192,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E23" t="n">
-        <v>21.669</v>
+        <v>105.78</v>
       </c>
       <c r="F23" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G23" t="n">
-        <v>65.01000000000001</v>
+        <v>105.78</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.66</v>
+        <v>5.69</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.01</v>
+        <v>5.68</v>
       </c>
       <c r="J23" t="n">
         <v>7.91</v>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E24" t="n">
-        <v>105.78</v>
+        <v>10.536</v>
       </c>
       <c r="F24" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G24" t="n">
-        <v>105.78</v>
+        <v>31.61</v>
       </c>
       <c r="H24" t="n">
-        <v>5.69</v>
+        <v>0.45</v>
       </c>
       <c r="I24" t="n">
-        <v>5.68</v>
+        <v>1.44</v>
       </c>
       <c r="J24" t="n">
         <v>7.91</v>
@@ -1260,29 +1260,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E25" t="n">
-        <v>10.536</v>
+        <v>6.799</v>
       </c>
       <c r="F25" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G25" t="n">
-        <v>31.61</v>
+        <v>61.19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.45</v>
+        <v>5.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1.44</v>
+        <v>8.98</v>
       </c>
       <c r="J25" t="n">
         <v>7.91</v>
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E26" t="n">
-        <v>41.336</v>
+        <v>21.669</v>
       </c>
       <c r="F26" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G26" t="n">
-        <v>165.34</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>26.32</v>
+        <v>-0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>18.93</v>
+        <v>-1.01</v>
       </c>
       <c r="J26" t="n">
         <v>7.91</v>
@@ -1498,29 +1498,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E32" t="n">
-        <v>38.849</v>
+        <v>6.762</v>
       </c>
       <c r="F32" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G32" t="n">
-        <v>155.4</v>
+        <v>60.86</v>
       </c>
       <c r="H32" t="n">
-        <v>16.38</v>
+        <v>4.71</v>
       </c>
       <c r="I32" t="n">
-        <v>11.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>7.91</v>
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E33" t="n">
-        <v>22.053</v>
+        <v>103.08</v>
       </c>
       <c r="F33" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G33" t="n">
-        <v>66.16</v>
+        <v>103.08</v>
       </c>
       <c r="H33" t="n">
-        <v>0.49</v>
+        <v>2.99</v>
       </c>
       <c r="I33" t="n">
-        <v>0.75</v>
+        <v>2.99</v>
       </c>
       <c r="J33" t="n">
         <v>7.91</v>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E34" t="n">
-        <v>103.08</v>
+        <v>10.714</v>
       </c>
       <c r="F34" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G34" t="n">
-        <v>103.08</v>
+        <v>32.14</v>
       </c>
       <c r="H34" t="n">
-        <v>2.99</v>
+        <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="J34" t="n">
         <v>7.91</v>
@@ -1600,29 +1600,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E35" t="n">
-        <v>10.714</v>
+        <v>38.849</v>
       </c>
       <c r="F35" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G35" t="n">
-        <v>32.14</v>
+        <v>155.4</v>
       </c>
       <c r="H35" t="n">
-        <v>0.98</v>
+        <v>16.38</v>
       </c>
       <c r="I35" t="n">
-        <v>3.15</v>
+        <v>11.78</v>
       </c>
       <c r="J35" t="n">
         <v>7.91</v>
@@ -1634,29 +1634,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E36" t="n">
-        <v>6.762</v>
+        <v>22.053</v>
       </c>
       <c r="F36" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G36" t="n">
-        <v>60.86</v>
+        <v>66.16</v>
       </c>
       <c r="H36" t="n">
-        <v>4.71</v>
+        <v>0.49</v>
       </c>
       <c r="I36" t="n">
-        <v>8.390000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J36" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E42" t="n">
-        <v>100.06</v>
+        <v>10.61</v>
       </c>
       <c r="F42" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G42" t="n">
-        <v>100.06</v>
+        <v>31.83</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.03</v>
+        <v>0.67</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.03</v>
+        <v>2.15</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>100.06</v>
       </c>
       <c r="F43" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G43" t="n">
-        <v>66</v>
+        <v>100.06</v>
       </c>
       <c r="H43" t="n">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E44" t="n">
-        <v>6.629</v>
+        <v>22</v>
       </c>
       <c r="F44" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G44" t="n">
-        <v>59.66</v>
+        <v>66</v>
       </c>
       <c r="H44" t="n">
-        <v>3.51</v>
+        <v>0.33</v>
       </c>
       <c r="I44" t="n">
-        <v>6.25</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E45" t="n">
-        <v>10.61</v>
+        <v>6.629</v>
       </c>
       <c r="F45" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G45" t="n">
-        <v>31.83</v>
+        <v>59.66</v>
       </c>
       <c r="H45" t="n">
-        <v>0.67</v>
+        <v>3.51</v>
       </c>
       <c r="I45" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -2008,29 +2008,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E47" t="n">
-        <v>10.562</v>
+        <v>99.83</v>
       </c>
       <c r="F47" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G47" t="n">
-        <v>31.69</v>
+        <v>99.83</v>
       </c>
       <c r="H47" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>-0.26</v>
       </c>
       <c r="J47" t="n">
         <v>7.91</v>
@@ -2042,29 +2042,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E48" t="n">
-        <v>21.778</v>
+        <v>6.622</v>
       </c>
       <c r="F48" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G48" t="n">
-        <v>65.33</v>
+        <v>59.6</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.34</v>
+        <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.52</v>
+        <v>6.14</v>
       </c>
       <c r="J48" t="n">
         <v>7.91</v>
@@ -2076,29 +2076,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E49" t="n">
-        <v>6.622</v>
+        <v>38.312</v>
       </c>
       <c r="F49" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G49" t="n">
-        <v>59.6</v>
+        <v>153.25</v>
       </c>
       <c r="H49" t="n">
-        <v>3.45</v>
+        <v>14.23</v>
       </c>
       <c r="I49" t="n">
-        <v>6.14</v>
+        <v>10.24</v>
       </c>
       <c r="J49" t="n">
         <v>7.91</v>
@@ -2110,29 +2110,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E50" t="n">
-        <v>38.312</v>
+        <v>21.778</v>
       </c>
       <c r="F50" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G50" t="n">
-        <v>153.25</v>
+        <v>65.33</v>
       </c>
       <c r="H50" t="n">
-        <v>14.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I50" t="n">
-        <v>10.24</v>
+        <v>-0.52</v>
       </c>
       <c r="J50" t="n">
         <v>7.91</v>
@@ -2144,29 +2144,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E51" t="n">
-        <v>99.83</v>
+        <v>10.562</v>
       </c>
       <c r="F51" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G51" t="n">
-        <v>99.83</v>
+        <v>31.69</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.26</v>
+        <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.26</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E62" t="n">
-        <v>105.5</v>
+        <v>10.712</v>
       </c>
       <c r="F62" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G62" t="n">
-        <v>105.5</v>
+        <v>32.14</v>
       </c>
       <c r="H62" t="n">
-        <v>5.41</v>
+        <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>5.41</v>
+        <v>3.15</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E63" t="n">
-        <v>22.7</v>
+        <v>41.064</v>
       </c>
       <c r="F63" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G63" t="n">
-        <v>68.09999999999999</v>
+        <v>164.26</v>
       </c>
       <c r="H63" t="n">
-        <v>2.43</v>
+        <v>25.24</v>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>18.16</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E64" t="n">
-        <v>6.817</v>
+        <v>105.5</v>
       </c>
       <c r="F64" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G64" t="n">
-        <v>61.35</v>
+        <v>105.5</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>5.41</v>
       </c>
       <c r="I64" t="n">
-        <v>9.26</v>
+        <v>5.41</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E65" t="n">
-        <v>41.064</v>
+        <v>22.7</v>
       </c>
       <c r="F65" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G65" t="n">
-        <v>164.26</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>25.24</v>
+        <v>2.43</v>
       </c>
       <c r="I65" t="n">
-        <v>18.16</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E66" t="n">
-        <v>10.712</v>
+        <v>6.817</v>
       </c>
       <c r="F66" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G66" t="n">
-        <v>32.14</v>
+        <v>61.35</v>
       </c>
       <c r="H66" t="n">
-        <v>0.98</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>3.15</v>
+        <v>9.26</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E72" t="n">
-        <v>10.892</v>
+        <v>6.811</v>
       </c>
       <c r="F72" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G72" t="n">
-        <v>32.68</v>
+        <v>61.3</v>
       </c>
       <c r="H72" t="n">
-        <v>1.52</v>
+        <v>5.15</v>
       </c>
       <c r="I72" t="n">
-        <v>4.88</v>
+        <v>9.17</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E73" t="n">
-        <v>41.15</v>
+        <v>104.22</v>
       </c>
       <c r="F73" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G73" t="n">
-        <v>164.6</v>
+        <v>104.22</v>
       </c>
       <c r="H73" t="n">
-        <v>25.58</v>
+        <v>4.13</v>
       </c>
       <c r="I73" t="n">
-        <v>18.4</v>
+        <v>4.13</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E75" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F75" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G75" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H75" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I75" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -2994,29 +2994,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E76" t="n">
-        <v>104.22</v>
+        <v>10.892</v>
       </c>
       <c r="F76" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G76" t="n">
-        <v>104.22</v>
+        <v>32.68</v>
       </c>
       <c r="H76" t="n">
-        <v>4.13</v>
+        <v>1.52</v>
       </c>
       <c r="I76" t="n">
-        <v>4.13</v>
+        <v>4.88</v>
       </c>
       <c r="J76" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E82" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F82" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G82" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H82" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I82" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E83" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F83" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G83" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H83" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E84" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F84" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G84" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H84" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I84" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E85" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F85" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G85" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I85" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E86" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F86" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G86" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H86" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I86" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E92" t="n">
-        <v>10.876</v>
+        <v>6.797</v>
       </c>
       <c r="F92" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G92" t="n">
-        <v>32.63</v>
+        <v>61.17</v>
       </c>
       <c r="H92" t="n">
-        <v>1.47</v>
+        <v>5.02</v>
       </c>
       <c r="I92" t="n">
-        <v>4.72</v>
+        <v>8.94</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E93" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F93" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G93" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H93" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I93" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E94" t="n">
-        <v>103.88</v>
+        <v>40.575</v>
       </c>
       <c r="F94" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G94" t="n">
-        <v>103.88</v>
+        <v>162.3</v>
       </c>
       <c r="H94" t="n">
-        <v>3.79</v>
+        <v>23.28</v>
       </c>
       <c r="I94" t="n">
-        <v>3.79</v>
+        <v>16.75</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E95" t="n">
-        <v>6.797</v>
+        <v>103.88</v>
       </c>
       <c r="F95" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G95" t="n">
-        <v>61.17</v>
+        <v>103.88</v>
       </c>
       <c r="H95" t="n">
-        <v>5.02</v>
+        <v>3.79</v>
       </c>
       <c r="I95" t="n">
-        <v>8.94</v>
+        <v>3.79</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E97" t="n">
-        <v>10.642</v>
+        <v>104.22</v>
       </c>
       <c r="F97" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G97" t="n">
-        <v>31.93</v>
+        <v>104.22</v>
       </c>
       <c r="H97" t="n">
-        <v>0.77</v>
+        <v>4.13</v>
       </c>
       <c r="I97" t="n">
-        <v>2.47</v>
+        <v>4.13</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E98" t="n">
-        <v>23.35</v>
+        <v>6.839</v>
       </c>
       <c r="F98" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G98" t="n">
-        <v>70.05</v>
+        <v>61.55</v>
       </c>
       <c r="H98" t="n">
-        <v>4.38</v>
+        <v>5.4</v>
       </c>
       <c r="I98" t="n">
-        <v>6.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E99" t="n">
-        <v>6.839</v>
+        <v>40.65</v>
       </c>
       <c r="F99" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G99" t="n">
-        <v>61.55</v>
+        <v>162.6</v>
       </c>
       <c r="H99" t="n">
-        <v>5.4</v>
+        <v>23.58</v>
       </c>
       <c r="I99" t="n">
-        <v>9.619999999999999</v>
+        <v>16.96</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E100" t="n">
-        <v>40.65</v>
+        <v>23.35</v>
       </c>
       <c r="F100" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G100" t="n">
-        <v>162.6</v>
+        <v>70.05</v>
       </c>
       <c r="H100" t="n">
-        <v>23.58</v>
+        <v>4.38</v>
       </c>
       <c r="I100" t="n">
-        <v>16.96</v>
+        <v>6.67</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E101" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F101" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G101" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H101" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I101" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E107" t="n">
-        <v>103.14</v>
+        <v>40.5</v>
       </c>
       <c r="F107" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G107" t="n">
-        <v>103.14</v>
+        <v>162</v>
       </c>
       <c r="H107" t="n">
-        <v>3.05</v>
+        <v>22.98</v>
       </c>
       <c r="I107" t="n">
-        <v>3.05</v>
+        <v>16.53</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E108" t="n">
-        <v>10.456</v>
+        <v>6.785</v>
       </c>
       <c r="F108" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G108" t="n">
-        <v>31.37</v>
+        <v>61.06</v>
       </c>
       <c r="H108" t="n">
-        <v>0.21</v>
+        <v>4.91</v>
       </c>
       <c r="I108" t="n">
-        <v>0.67</v>
+        <v>8.74</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E109" t="n">
-        <v>6.785</v>
+        <v>23.33</v>
       </c>
       <c r="F109" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G109" t="n">
-        <v>61.06</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H109" t="n">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="I109" t="n">
-        <v>8.74</v>
+        <v>6.58</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E110" t="n">
-        <v>40.5</v>
+        <v>103.14</v>
       </c>
       <c r="F110" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G110" t="n">
-        <v>162</v>
+        <v>103.14</v>
       </c>
       <c r="H110" t="n">
-        <v>22.98</v>
+        <v>3.05</v>
       </c>
       <c r="I110" t="n">
-        <v>16.53</v>
+        <v>3.05</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E111" t="n">
-        <v>23.33</v>
+        <v>10.456</v>
       </c>
       <c r="F111" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G111" t="n">
-        <v>69.98999999999999</v>
+        <v>31.37</v>
       </c>
       <c r="H111" t="n">
-        <v>4.32</v>
+        <v>0.21</v>
       </c>
       <c r="I111" t="n">
-        <v>6.58</v>
+        <v>0.67</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E122" t="n">
-        <v>106</v>
+        <v>23.165</v>
       </c>
       <c r="F122" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G122" t="n">
-        <v>106</v>
+        <v>69.5</v>
       </c>
       <c r="H122" t="n">
-        <v>5.91</v>
+        <v>3.83</v>
       </c>
       <c r="I122" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E123" t="n">
-        <v>40.395</v>
+        <v>6.901</v>
       </c>
       <c r="F123" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G123" t="n">
-        <v>161.58</v>
+        <v>62.11</v>
       </c>
       <c r="H123" t="n">
-        <v>22.56</v>
+        <v>5.96</v>
       </c>
       <c r="I123" t="n">
-        <v>16.23</v>
+        <v>10.61</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E125" t="n">
-        <v>6.901</v>
+        <v>40.395</v>
       </c>
       <c r="F125" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G125" t="n">
-        <v>62.11</v>
+        <v>161.58</v>
       </c>
       <c r="H125" t="n">
-        <v>5.96</v>
+        <v>22.56</v>
       </c>
       <c r="I125" t="n">
-        <v>10.61</v>
+        <v>16.23</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E126" t="n">
-        <v>23.165</v>
+        <v>106</v>
       </c>
       <c r="F126" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G126" t="n">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="H126" t="n">
-        <v>3.83</v>
+        <v>5.91</v>
       </c>
       <c r="I126" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E137" t="n">
-        <v>40.61</v>
+        <v>104.76</v>
       </c>
       <c r="F137" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G137" t="n">
-        <v>162.44</v>
+        <v>104.76</v>
       </c>
       <c r="H137" t="n">
-        <v>23.42</v>
+        <v>4.67</v>
       </c>
       <c r="I137" t="n">
-        <v>16.85</v>
+        <v>4.67</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E138" t="n">
-        <v>23.3</v>
+        <v>11.728</v>
       </c>
       <c r="F138" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G138" t="n">
-        <v>69.90000000000001</v>
+        <v>35.18</v>
       </c>
       <c r="H138" t="n">
-        <v>4.23</v>
+        <v>4.02</v>
       </c>
       <c r="I138" t="n">
-        <v>6.44</v>
+        <v>12.9</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E139" t="n">
-        <v>6.927</v>
+        <v>40.61</v>
       </c>
       <c r="F139" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G139" t="n">
-        <v>62.34</v>
+        <v>162.44</v>
       </c>
       <c r="H139" t="n">
-        <v>6.19</v>
+        <v>23.42</v>
       </c>
       <c r="I139" t="n">
-        <v>11.02</v>
+        <v>16.85</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E140" t="n">
-        <v>11.728</v>
+        <v>23.3</v>
       </c>
       <c r="F140" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G140" t="n">
-        <v>35.18</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
       <c r="I140" t="n">
-        <v>12.9</v>
+        <v>6.44</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E141" t="n">
-        <v>104.76</v>
+        <v>6.927</v>
       </c>
       <c r="F141" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G141" t="n">
-        <v>104.76</v>
+        <v>62.34</v>
       </c>
       <c r="H141" t="n">
-        <v>4.67</v>
+        <v>6.19</v>
       </c>
       <c r="I141" t="n">
-        <v>4.67</v>
+        <v>11.02</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5408,29 +5408,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E147" t="n">
-        <v>38.955</v>
+        <v>22.755</v>
       </c>
       <c r="F147" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G147" t="n">
-        <v>155.82</v>
+        <v>68.27</v>
       </c>
       <c r="H147" t="n">
-        <v>16.8</v>
+        <v>2.6</v>
       </c>
       <c r="I147" t="n">
-        <v>12.08</v>
+        <v>3.96</v>
       </c>
       <c r="J147" t="n">
         <v>7.91</v>
@@ -5442,29 +5442,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D148" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E148" t="n">
-        <v>11.162</v>
+        <v>6.826</v>
       </c>
       <c r="F148" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G148" t="n">
-        <v>33.49</v>
+        <v>61.43</v>
       </c>
       <c r="H148" t="n">
-        <v>2.33</v>
+        <v>5.28</v>
       </c>
       <c r="I148" t="n">
-        <v>7.48</v>
+        <v>9.4</v>
       </c>
       <c r="J148" t="n">
         <v>7.91</v>
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E150" t="n">
-        <v>22.755</v>
+        <v>11.162</v>
       </c>
       <c r="F150" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G150" t="n">
-        <v>68.27</v>
+        <v>33.49</v>
       </c>
       <c r="H150" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="I150" t="n">
-        <v>3.96</v>
+        <v>7.48</v>
       </c>
       <c r="J150" t="n">
         <v>7.91</v>
@@ -5544,29 +5544,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D151" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E151" t="n">
-        <v>6.826</v>
+        <v>38.955</v>
       </c>
       <c r="F151" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G151" t="n">
-        <v>61.43</v>
+        <v>155.82</v>
       </c>
       <c r="H151" t="n">
-        <v>5.28</v>
+        <v>16.8</v>
       </c>
       <c r="I151" t="n">
-        <v>9.4</v>
+        <v>12.08</v>
       </c>
       <c r="J151" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E162" t="n">
-        <v>103.84</v>
+        <v>10.748</v>
       </c>
       <c r="F162" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G162" t="n">
-        <v>103.84</v>
+        <v>32.24</v>
       </c>
       <c r="H162" t="n">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>3.75</v>
+        <v>3.47</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E163" t="n">
-        <v>38.845</v>
+        <v>23.01</v>
       </c>
       <c r="F163" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G163" t="n">
-        <v>155.38</v>
+        <v>69.03</v>
       </c>
       <c r="H163" t="n">
-        <v>16.36</v>
+        <v>3.36</v>
       </c>
       <c r="I163" t="n">
-        <v>11.77</v>
+        <v>5.12</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E164" t="n">
-        <v>6.927</v>
+        <v>103.84</v>
       </c>
       <c r="F164" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G164" t="n">
-        <v>62.34</v>
+        <v>103.84</v>
       </c>
       <c r="H164" t="n">
-        <v>6.19</v>
+        <v>3.75</v>
       </c>
       <c r="I164" t="n">
-        <v>11.02</v>
+        <v>3.75</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E165" t="n">
-        <v>23.01</v>
+        <v>38.845</v>
       </c>
       <c r="F165" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G165" t="n">
-        <v>69.03</v>
+        <v>155.38</v>
       </c>
       <c r="H165" t="n">
-        <v>3.36</v>
+        <v>16.36</v>
       </c>
       <c r="I165" t="n">
-        <v>5.12</v>
+        <v>11.77</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D166" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E166" t="n">
-        <v>10.748</v>
+        <v>6.927</v>
       </c>
       <c r="F166" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G166" t="n">
-        <v>32.24</v>
+        <v>62.34</v>
       </c>
       <c r="H166" t="n">
-        <v>1.08</v>
+        <v>6.19</v>
       </c>
       <c r="I166" t="n">
-        <v>3.47</v>
+        <v>11.02</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6258,29 +6258,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E172" t="n">
-        <v>38.74</v>
+        <v>10.712</v>
       </c>
       <c r="F172" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G172" t="n">
-        <v>154.96</v>
+        <v>32.14</v>
       </c>
       <c r="H172" t="n">
-        <v>15.94</v>
+        <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>11.47</v>
+        <v>3.15</v>
       </c>
       <c r="J172" t="n">
         <v>7.91</v>
@@ -6292,29 +6292,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E173" t="n">
-        <v>22.95</v>
+        <v>103.22</v>
       </c>
       <c r="F173" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G173" t="n">
-        <v>68.84999999999999</v>
+        <v>103.22</v>
       </c>
       <c r="H173" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="I173" t="n">
-        <v>4.84</v>
+        <v>3.13</v>
       </c>
       <c r="J173" t="n">
         <v>7.91</v>
@@ -6326,29 +6326,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E174" t="n">
-        <v>6.926</v>
+        <v>22.95</v>
       </c>
       <c r="F174" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G174" t="n">
-        <v>62.33</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H174" t="n">
-        <v>6.18</v>
+        <v>3.18</v>
       </c>
       <c r="I174" t="n">
-        <v>11.01</v>
+        <v>4.84</v>
       </c>
       <c r="J174" t="n">
         <v>7.91</v>
@@ -6360,29 +6360,29 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E175" t="n">
-        <v>103.22</v>
+        <v>38.74</v>
       </c>
       <c r="F175" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G175" t="n">
-        <v>103.22</v>
+        <v>154.96</v>
       </c>
       <c r="H175" t="n">
-        <v>3.13</v>
+        <v>15.94</v>
       </c>
       <c r="I175" t="n">
-        <v>3.13</v>
+        <v>11.47</v>
       </c>
       <c r="J175" t="n">
         <v>7.91</v>
@@ -6394,29 +6394,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D176" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E176" t="n">
-        <v>10.712</v>
+        <v>6.926</v>
       </c>
       <c r="F176" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G176" t="n">
-        <v>32.14</v>
+        <v>62.33</v>
       </c>
       <c r="H176" t="n">
-        <v>0.98</v>
+        <v>6.18</v>
       </c>
       <c r="I176" t="n">
-        <v>3.15</v>
+        <v>11.01</v>
       </c>
       <c r="J176" t="n">
         <v>7.91</v>
@@ -6598,29 +6598,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E182" t="n">
-        <v>22.835</v>
+        <v>100.14</v>
       </c>
       <c r="F182" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G182" t="n">
-        <v>68.5</v>
+        <v>100.14</v>
       </c>
       <c r="H182" t="n">
-        <v>2.83</v>
+        <v>0.05</v>
       </c>
       <c r="I182" t="n">
-        <v>4.31</v>
+        <v>0.05</v>
       </c>
       <c r="J182" t="n">
         <v>7.91</v>
@@ -6632,29 +6632,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D183" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E183" t="n">
-        <v>6.848</v>
+        <v>37.235</v>
       </c>
       <c r="F183" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G183" t="n">
-        <v>61.63</v>
+        <v>148.94</v>
       </c>
       <c r="H183" t="n">
-        <v>5.48</v>
+        <v>9.92</v>
       </c>
       <c r="I183" t="n">
-        <v>9.76</v>
+        <v>7.14</v>
       </c>
       <c r="J183" t="n">
         <v>7.91</v>
@@ -6666,29 +6666,29 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E184" t="n">
-        <v>10.776</v>
+        <v>6.848</v>
       </c>
       <c r="F184" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G184" t="n">
-        <v>32.33</v>
+        <v>61.63</v>
       </c>
       <c r="H184" t="n">
-        <v>1.17</v>
+        <v>5.48</v>
       </c>
       <c r="I184" t="n">
-        <v>3.75</v>
+        <v>9.76</v>
       </c>
       <c r="J184" t="n">
         <v>7.91</v>
@@ -6700,29 +6700,29 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E185" t="n">
-        <v>100.14</v>
+        <v>22.835</v>
       </c>
       <c r="F185" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G185" t="n">
-        <v>100.14</v>
+        <v>68.5</v>
       </c>
       <c r="H185" t="n">
-        <v>0.05</v>
+        <v>2.83</v>
       </c>
       <c r="I185" t="n">
-        <v>0.05</v>
+        <v>4.31</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -6734,29 +6734,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E186" t="n">
-        <v>37.235</v>
+        <v>10.776</v>
       </c>
       <c r="F186" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G186" t="n">
-        <v>148.94</v>
+        <v>32.33</v>
       </c>
       <c r="H186" t="n">
-        <v>9.92</v>
+        <v>1.17</v>
       </c>
       <c r="I186" t="n">
-        <v>7.14</v>
+        <v>3.75</v>
       </c>
       <c r="J186" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E187" t="n">
-        <v>37.85</v>
+        <v>22.845</v>
       </c>
       <c r="F187" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G187" t="n">
-        <v>151.4</v>
+        <v>68.53</v>
       </c>
       <c r="H187" t="n">
-        <v>12.38</v>
+        <v>2.86</v>
       </c>
       <c r="I187" t="n">
-        <v>8.91</v>
+        <v>4.36</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D188" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E188" t="n">
-        <v>6.862</v>
+        <v>37.85</v>
       </c>
       <c r="F188" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G188" t="n">
-        <v>61.76</v>
+        <v>151.4</v>
       </c>
       <c r="H188" t="n">
-        <v>5.61</v>
+        <v>12.38</v>
       </c>
       <c r="I188" t="n">
-        <v>9.99</v>
+        <v>8.91</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D189" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E189" t="n">
-        <v>101.44</v>
+        <v>6.862</v>
       </c>
       <c r="F189" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G189" t="n">
-        <v>101.44</v>
+        <v>61.76</v>
       </c>
       <c r="H189" t="n">
-        <v>1.35</v>
+        <v>5.61</v>
       </c>
       <c r="I189" t="n">
-        <v>1.35</v>
+        <v>9.99</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E190" t="n">
-        <v>10.708</v>
+        <v>101.44</v>
       </c>
       <c r="F190" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G190" t="n">
-        <v>32.12</v>
+        <v>101.44</v>
       </c>
       <c r="H190" t="n">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>3.08</v>
+        <v>1.35</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E191" t="n">
-        <v>22.845</v>
+        <v>10.708</v>
       </c>
       <c r="F191" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G191" t="n">
-        <v>68.53</v>
+        <v>32.12</v>
       </c>
       <c r="H191" t="n">
-        <v>2.86</v>
+        <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>4.36</v>
+        <v>3.08</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E192" t="n">
-        <v>102.46</v>
+        <v>22.82</v>
       </c>
       <c r="F192" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G192" t="n">
-        <v>102.46</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H192" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="I192" t="n">
-        <v>2.37</v>
+        <v>4.25</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E193" t="n">
-        <v>10.792</v>
+        <v>38.755</v>
       </c>
       <c r="F193" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G193" t="n">
-        <v>32.38</v>
+        <v>155.02</v>
       </c>
       <c r="H193" t="n">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="I193" t="n">
-        <v>3.92</v>
+        <v>11.51</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E194" t="n">
-        <v>22.82</v>
+        <v>102.46</v>
       </c>
       <c r="F194" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G194" t="n">
-        <v>68.45999999999999</v>
+        <v>102.46</v>
       </c>
       <c r="H194" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="I194" t="n">
-        <v>4.25</v>
+        <v>2.37</v>
       </c>
       <c r="J194" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E195" t="n">
-        <v>38.755</v>
+        <v>10.792</v>
       </c>
       <c r="F195" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G195" t="n">
-        <v>155.02</v>
+        <v>32.38</v>
       </c>
       <c r="H195" t="n">
-        <v>16</v>
+        <v>1.22</v>
       </c>
       <c r="I195" t="n">
-        <v>11.51</v>
+        <v>3.92</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E197" t="n">
-        <v>11.022</v>
+        <v>102.48</v>
       </c>
       <c r="F197" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G197" t="n">
-        <v>33.07</v>
+        <v>102.48</v>
       </c>
       <c r="H197" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="I197" t="n">
-        <v>6.13</v>
+        <v>2.39</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D198" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E198" t="n">
-        <v>22.6</v>
+        <v>6.909</v>
       </c>
       <c r="F198" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G198" t="n">
-        <v>67.8</v>
+        <v>62.18</v>
       </c>
       <c r="H198" t="n">
-        <v>2.13</v>
+        <v>6.03</v>
       </c>
       <c r="I198" t="n">
-        <v>3.24</v>
+        <v>10.74</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7176,29 +7176,29 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D199" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E199" t="n">
-        <v>6.909</v>
+        <v>38.565</v>
       </c>
       <c r="F199" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G199" t="n">
-        <v>62.18</v>
+        <v>154.26</v>
       </c>
       <c r="H199" t="n">
-        <v>6.03</v>
+        <v>15.24</v>
       </c>
       <c r="I199" t="n">
-        <v>10.74</v>
+        <v>10.96</v>
       </c>
       <c r="J199" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E200" t="n">
-        <v>102.48</v>
+        <v>11.022</v>
       </c>
       <c r="F200" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G200" t="n">
-        <v>102.48</v>
+        <v>33.07</v>
       </c>
       <c r="H200" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>2.39</v>
+        <v>6.13</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E201" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F201" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G201" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H201" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I201" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D212" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E212" t="n">
-        <v>11.338</v>
+        <v>6.84</v>
       </c>
       <c r="F212" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G212" t="n">
-        <v>34.01</v>
+        <v>61.56</v>
       </c>
       <c r="H212" t="n">
-        <v>2.85</v>
+        <v>5.41</v>
       </c>
       <c r="I212" t="n">
-        <v>9.15</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E213" t="n">
-        <v>98.29000000000001</v>
+        <v>37.25</v>
       </c>
       <c r="F213" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G213" t="n">
-        <v>98.29000000000001</v>
+        <v>149</v>
       </c>
       <c r="H213" t="n">
-        <v>-1.8</v>
+        <v>9.98</v>
       </c>
       <c r="I213" t="n">
-        <v>-1.8</v>
+        <v>7.18</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E214" t="n">
-        <v>22.885</v>
+        <v>11.338</v>
       </c>
       <c r="F214" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G214" t="n">
-        <v>68.66</v>
+        <v>34.01</v>
       </c>
       <c r="H214" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="I214" t="n">
-        <v>4.55</v>
+        <v>9.15</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E215" t="n">
-        <v>37.25</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F215" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G215" t="n">
-        <v>149</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H215" t="n">
-        <v>9.98</v>
+        <v>-1.8</v>
       </c>
       <c r="I215" t="n">
-        <v>7.18</v>
+        <v>-1.8</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7754,29 +7754,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E216" t="n">
-        <v>6.84</v>
+        <v>22.885</v>
       </c>
       <c r="F216" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G216" t="n">
-        <v>61.56</v>
+        <v>68.66</v>
       </c>
       <c r="H216" t="n">
-        <v>5.41</v>
+        <v>2.99</v>
       </c>
       <c r="I216" t="n">
-        <v>9.630000000000001</v>
+        <v>4.55</v>
       </c>
       <c r="J216" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E217" t="n">
-        <v>6.864</v>
+        <v>11.546</v>
       </c>
       <c r="F217" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G217" t="n">
-        <v>61.78</v>
+        <v>34.64</v>
       </c>
       <c r="H217" t="n">
-        <v>5.63</v>
+        <v>3.48</v>
       </c>
       <c r="I217" t="n">
-        <v>10.03</v>
+        <v>11.17</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E218" t="n">
-        <v>36.75</v>
+        <v>6.864</v>
       </c>
       <c r="F218" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G218" t="n">
-        <v>147</v>
+        <v>61.78</v>
       </c>
       <c r="H218" t="n">
-        <v>7.98</v>
+        <v>5.63</v>
       </c>
       <c r="I218" t="n">
-        <v>5.74</v>
+        <v>10.03</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E219" t="n">
-        <v>98.02</v>
+        <v>36.75</v>
       </c>
       <c r="F219" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G219" t="n">
-        <v>98.02</v>
+        <v>147</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.07</v>
+        <v>7.98</v>
       </c>
       <c r="I219" t="n">
-        <v>-2.07</v>
+        <v>5.74</v>
       </c>
       <c r="J219" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E220" t="n">
-        <v>23.175</v>
+        <v>98.02</v>
       </c>
       <c r="F220" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G220" t="n">
-        <v>69.53</v>
+        <v>98.02</v>
       </c>
       <c r="H220" t="n">
-        <v>3.86</v>
+        <v>-2.07</v>
       </c>
       <c r="I220" t="n">
-        <v>5.88</v>
+        <v>-2.07</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C221" t="n">
         <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E221" t="n">
-        <v>11.546</v>
+        <v>23.175</v>
       </c>
       <c r="F221" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G221" t="n">
-        <v>34.64</v>
+        <v>69.53</v>
       </c>
       <c r="H221" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="I221" t="n">
-        <v>11.17</v>
+        <v>5.88</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D222" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E222" t="n">
-        <v>23.12</v>
+        <v>35.89</v>
       </c>
       <c r="F222" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G222" t="n">
-        <v>69.36</v>
+        <v>143.56</v>
       </c>
       <c r="H222" t="n">
-        <v>3.69</v>
+        <v>4.54</v>
       </c>
       <c r="I222" t="n">
-        <v>5.62</v>
+        <v>3.27</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E223" t="n">
-        <v>6.818</v>
+        <v>11.5</v>
       </c>
       <c r="F223" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G223" t="n">
-        <v>61.36</v>
+        <v>34.5</v>
       </c>
       <c r="H223" t="n">
-        <v>5.21</v>
+        <v>3.34</v>
       </c>
       <c r="I223" t="n">
-        <v>9.279999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D225" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E225" t="n">
-        <v>11.5</v>
+        <v>6.818</v>
       </c>
       <c r="F225" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G225" t="n">
-        <v>34.5</v>
+        <v>61.36</v>
       </c>
       <c r="H225" t="n">
-        <v>3.34</v>
+        <v>5.21</v>
       </c>
       <c r="I225" t="n">
-        <v>10.72</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E226" t="n">
-        <v>35.89</v>
+        <v>23.12</v>
       </c>
       <c r="F226" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G226" t="n">
-        <v>143.56</v>
+        <v>69.36</v>
       </c>
       <c r="H226" t="n">
-        <v>4.54</v>
+        <v>3.69</v>
       </c>
       <c r="I226" t="n">
-        <v>3.27</v>
+        <v>5.62</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D232" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E232" t="n">
-        <v>97.86</v>
+        <v>37.44</v>
       </c>
       <c r="F232" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G232" t="n">
-        <v>97.86</v>
+        <v>149.76</v>
       </c>
       <c r="H232" t="n">
-        <v>-2.23</v>
+        <v>10.74</v>
       </c>
       <c r="I232" t="n">
-        <v>-2.23</v>
+        <v>7.73</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E233" t="n">
-        <v>6.812</v>
+        <v>23.17</v>
       </c>
       <c r="F233" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G233" t="n">
-        <v>61.31</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H233" t="n">
-        <v>5.16</v>
+        <v>3.84</v>
       </c>
       <c r="I233" t="n">
-        <v>9.19</v>
+        <v>5.85</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8366,29 +8366,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C234" t="n">
         <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E234" t="n">
-        <v>23.17</v>
+        <v>11.544</v>
       </c>
       <c r="F234" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G234" t="n">
-        <v>69.51000000000001</v>
+        <v>34.63</v>
       </c>
       <c r="H234" t="n">
-        <v>3.84</v>
+        <v>3.47</v>
       </c>
       <c r="I234" t="n">
-        <v>5.85</v>
+        <v>11.14</v>
       </c>
       <c r="J234" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E235" t="n">
-        <v>37.44</v>
+        <v>97.86</v>
       </c>
       <c r="F235" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G235" t="n">
-        <v>149.76</v>
+        <v>97.86</v>
       </c>
       <c r="H235" t="n">
-        <v>10.74</v>
+        <v>-2.23</v>
       </c>
       <c r="I235" t="n">
-        <v>7.73</v>
+        <v>-2.23</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D236" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E236" t="n">
-        <v>11.544</v>
+        <v>6.812</v>
       </c>
       <c r="F236" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G236" t="n">
-        <v>34.63</v>
+        <v>61.31</v>
       </c>
       <c r="H236" t="n">
-        <v>3.47</v>
+        <v>5.16</v>
       </c>
       <c r="I236" t="n">
-        <v>11.14</v>
+        <v>9.19</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D247" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E247" t="n">
-        <v>12.18</v>
+        <v>7.032</v>
       </c>
       <c r="F247" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G247" t="n">
-        <v>36.54</v>
+        <v>63.29</v>
       </c>
       <c r="H247" t="n">
-        <v>5.38</v>
+        <v>7.14</v>
       </c>
       <c r="I247" t="n">
-        <v>17.27</v>
+        <v>12.72</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E248" t="n">
-        <v>23.28</v>
+        <v>103.2</v>
       </c>
       <c r="F248" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G248" t="n">
-        <v>69.84</v>
+        <v>103.2</v>
       </c>
       <c r="H248" t="n">
-        <v>4.17</v>
+        <v>3.11</v>
       </c>
       <c r="I248" t="n">
-        <v>6.35</v>
+        <v>3.11</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D250" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E250" t="n">
-        <v>103.2</v>
+        <v>12.18</v>
       </c>
       <c r="F250" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G250" t="n">
-        <v>103.2</v>
+        <v>36.54</v>
       </c>
       <c r="H250" t="n">
-        <v>3.11</v>
+        <v>5.38</v>
       </c>
       <c r="I250" t="n">
-        <v>3.11</v>
+        <v>17.27</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E251" t="n">
-        <v>7.032</v>
+        <v>23.28</v>
       </c>
       <c r="F251" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G251" t="n">
-        <v>63.29</v>
+        <v>69.84</v>
       </c>
       <c r="H251" t="n">
-        <v>7.14</v>
+        <v>4.17</v>
       </c>
       <c r="I251" t="n">
-        <v>12.72</v>
+        <v>6.35</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E257" t="n">
-        <v>103.02</v>
+        <v>12.232</v>
       </c>
       <c r="F257" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G257" t="n">
-        <v>103.02</v>
+        <v>36.7</v>
       </c>
       <c r="H257" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="I257" t="n">
-        <v>2.93</v>
+        <v>17.78</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D258" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E258" t="n">
-        <v>23.2</v>
+        <v>37.84</v>
       </c>
       <c r="F258" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G258" t="n">
-        <v>69.59999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="H258" t="n">
-        <v>3.93</v>
+        <v>12.34</v>
       </c>
       <c r="I258" t="n">
-        <v>5.98</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D259" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E259" t="n">
-        <v>37.84</v>
+        <v>7.056</v>
       </c>
       <c r="F259" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G259" t="n">
-        <v>151.36</v>
+        <v>63.5</v>
       </c>
       <c r="H259" t="n">
-        <v>12.34</v>
+        <v>7.35</v>
       </c>
       <c r="I259" t="n">
-        <v>8.880000000000001</v>
+        <v>13.09</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E260" t="n">
-        <v>12.232</v>
+        <v>103.02</v>
       </c>
       <c r="F260" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G260" t="n">
-        <v>36.7</v>
+        <v>103.02</v>
       </c>
       <c r="H260" t="n">
-        <v>5.54</v>
+        <v>2.93</v>
       </c>
       <c r="I260" t="n">
-        <v>17.78</v>
+        <v>2.93</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D261" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E261" t="n">
-        <v>7.056</v>
+        <v>23.2</v>
       </c>
       <c r="F261" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G261" t="n">
-        <v>63.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H261" t="n">
-        <v>7.35</v>
+        <v>3.93</v>
       </c>
       <c r="I261" t="n">
-        <v>13.09</v>
+        <v>5.98</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D262" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E262" t="n">
-        <v>102.84</v>
+        <v>12.23</v>
       </c>
       <c r="F262" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G262" t="n">
-        <v>102.84</v>
+        <v>36.69</v>
       </c>
       <c r="H262" t="n">
-        <v>2.75</v>
+        <v>5.53</v>
       </c>
       <c r="I262" t="n">
-        <v>2.75</v>
+        <v>17.75</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C263" t="n">
         <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E263" t="n">
-        <v>12.23</v>
+        <v>23.3</v>
       </c>
       <c r="F263" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G263" t="n">
-        <v>36.69</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H263" t="n">
-        <v>5.53</v>
+        <v>4.23</v>
       </c>
       <c r="I263" t="n">
-        <v>17.75</v>
+        <v>6.44</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9386,29 +9386,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D264" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E264" t="n">
-        <v>23.3</v>
+        <v>38.23</v>
       </c>
       <c r="F264" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G264" t="n">
-        <v>69.90000000000001</v>
+        <v>152.92</v>
       </c>
       <c r="H264" t="n">
-        <v>4.23</v>
+        <v>13.9</v>
       </c>
       <c r="I264" t="n">
-        <v>6.44</v>
+        <v>10</v>
       </c>
       <c r="J264" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E265" t="n">
-        <v>38.23</v>
+        <v>7.055</v>
       </c>
       <c r="F265" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G265" t="n">
-        <v>152.92</v>
+        <v>63.49</v>
       </c>
       <c r="H265" t="n">
-        <v>13.9</v>
+        <v>7.34</v>
       </c>
       <c r="I265" t="n">
-        <v>10</v>
+        <v>13.07</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E266" t="n">
-        <v>7.055</v>
+        <v>102.84</v>
       </c>
       <c r="F266" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G266" t="n">
-        <v>63.49</v>
+        <v>102.84</v>
       </c>
       <c r="H266" t="n">
-        <v>7.34</v>
+        <v>2.75</v>
       </c>
       <c r="I266" t="n">
-        <v>13.07</v>
+        <v>2.75</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E272" t="n">
-        <v>23.135</v>
+        <v>104.54</v>
       </c>
       <c r="F272" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G272" t="n">
-        <v>69.41</v>
+        <v>104.54</v>
       </c>
       <c r="H272" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="I272" t="n">
-        <v>5.7</v>
+        <v>4.45</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E273" t="n">
-        <v>39.325</v>
+        <v>12.308</v>
       </c>
       <c r="F273" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G273" t="n">
-        <v>157.3</v>
+        <v>36.92</v>
       </c>
       <c r="H273" t="n">
-        <v>18.28</v>
+        <v>5.76</v>
       </c>
       <c r="I273" t="n">
-        <v>13.15</v>
+        <v>18.49</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D275" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E275" t="n">
-        <v>104.54</v>
+        <v>23.135</v>
       </c>
       <c r="F275" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G275" t="n">
-        <v>104.54</v>
+        <v>69.41</v>
       </c>
       <c r="H275" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="I275" t="n">
-        <v>4.45</v>
+        <v>5.7</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D276" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E276" t="n">
-        <v>12.308</v>
+        <v>39.325</v>
       </c>
       <c r="F276" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G276" t="n">
-        <v>36.92</v>
+        <v>157.3</v>
       </c>
       <c r="H276" t="n">
-        <v>5.76</v>
+        <v>18.28</v>
       </c>
       <c r="I276" t="n">
-        <v>18.49</v>
+        <v>13.15</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E282" t="n">
-        <v>39.745</v>
+        <v>104.46</v>
       </c>
       <c r="F282" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G282" t="n">
-        <v>158.98</v>
+        <v>104.46</v>
       </c>
       <c r="H282" t="n">
-        <v>19.96</v>
+        <v>4.37</v>
       </c>
       <c r="I282" t="n">
-        <v>14.36</v>
+        <v>4.37</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D283" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E283" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F283" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G283" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H283" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I283" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C284" t="n">
         <v>3</v>
       </c>
       <c r="D284" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E284" t="n">
-        <v>12.468</v>
+        <v>22.97</v>
       </c>
       <c r="F284" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G284" t="n">
-        <v>37.4</v>
+        <v>68.91</v>
       </c>
       <c r="H284" t="n">
-        <v>6.24</v>
+        <v>3.24</v>
       </c>
       <c r="I284" t="n">
-        <v>20.03</v>
+        <v>4.93</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D285" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E285" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F285" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G285" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H285" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I285" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D286" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E286" t="n">
-        <v>22.97</v>
+        <v>7.054</v>
       </c>
       <c r="F286" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G286" t="n">
-        <v>68.91</v>
+        <v>63.49</v>
       </c>
       <c r="H286" t="n">
-        <v>3.24</v>
+        <v>7.34</v>
       </c>
       <c r="I286" t="n">
-        <v>4.93</v>
+        <v>13.07</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D297" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E297" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F297" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G297" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H297" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I297" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D298" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E298" t="n">
-        <v>6.915</v>
+        <v>22.78</v>
       </c>
       <c r="F298" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G298" t="n">
-        <v>62.23</v>
+        <v>68.34</v>
       </c>
       <c r="H298" t="n">
-        <v>6.08</v>
+        <v>2.67</v>
       </c>
       <c r="I298" t="n">
-        <v>10.83</v>
+        <v>4.07</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10576,29 +10576,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C299" t="n">
         <v>3</v>
       </c>
       <c r="D299" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E299" t="n">
-        <v>22.78</v>
+        <v>11.92</v>
       </c>
       <c r="F299" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G299" t="n">
-        <v>68.34</v>
+        <v>35.76</v>
       </c>
       <c r="H299" t="n">
-        <v>2.67</v>
+        <v>4.6</v>
       </c>
       <c r="I299" t="n">
-        <v>4.07</v>
+        <v>14.76</v>
       </c>
       <c r="J299" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E300" t="n">
-        <v>11.92</v>
+        <v>100.42</v>
       </c>
       <c r="F300" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G300" t="n">
-        <v>35.76</v>
+        <v>100.42</v>
       </c>
       <c r="H300" t="n">
-        <v>4.6</v>
+        <v>0.33</v>
       </c>
       <c r="I300" t="n">
-        <v>14.76</v>
+        <v>0.33</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D301" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E301" t="n">
-        <v>38.49</v>
+        <v>6.915</v>
       </c>
       <c r="F301" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G301" t="n">
-        <v>153.96</v>
+        <v>62.23</v>
       </c>
       <c r="H301" t="n">
-        <v>14.94</v>
+        <v>6.08</v>
       </c>
       <c r="I301" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D307" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E307" t="n">
-        <v>11.686</v>
+        <v>38.055</v>
       </c>
       <c r="F307" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G307" t="n">
-        <v>35.06</v>
+        <v>152.22</v>
       </c>
       <c r="H307" t="n">
-        <v>3.9</v>
+        <v>13.2</v>
       </c>
       <c r="I307" t="n">
-        <v>12.52</v>
+        <v>9.5</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D308" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E308" t="n">
-        <v>22.555</v>
+        <v>6.916</v>
       </c>
       <c r="F308" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G308" t="n">
-        <v>67.66</v>
+        <v>62.24</v>
       </c>
       <c r="H308" t="n">
-        <v>1.99</v>
+        <v>6.09</v>
       </c>
       <c r="I308" t="n">
-        <v>3.03</v>
+        <v>10.85</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10916,29 +10916,29 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D309" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E309" t="n">
-        <v>6.916</v>
+        <v>99.95</v>
       </c>
       <c r="F309" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G309" t="n">
-        <v>62.24</v>
+        <v>99.95</v>
       </c>
       <c r="H309" t="n">
-        <v>6.09</v>
+        <v>-0.14</v>
       </c>
       <c r="I309" t="n">
-        <v>10.85</v>
+        <v>-0.14</v>
       </c>
       <c r="J309" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D310" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E310" t="n">
-        <v>38.055</v>
+        <v>11.686</v>
       </c>
       <c r="F310" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G310" t="n">
-        <v>152.22</v>
+        <v>35.06</v>
       </c>
       <c r="H310" t="n">
-        <v>13.2</v>
+        <v>3.9</v>
       </c>
       <c r="I310" t="n">
-        <v>9.5</v>
+        <v>12.52</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D311" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E311" t="n">
-        <v>99.95</v>
+        <v>22.555</v>
       </c>
       <c r="F311" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G311" t="n">
-        <v>99.95</v>
+        <v>67.66</v>
       </c>
       <c r="H311" t="n">
-        <v>-0.14</v>
+        <v>1.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.14</v>
+        <v>3.03</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E312" t="n">
-        <v>22.9</v>
+        <v>100.38</v>
       </c>
       <c r="F312" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G312" t="n">
-        <v>68.7</v>
+        <v>100.38</v>
       </c>
       <c r="H312" t="n">
-        <v>3.03</v>
+        <v>0.29</v>
       </c>
       <c r="I312" t="n">
-        <v>4.61</v>
+        <v>0.29</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D313" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E313" t="n">
-        <v>100.38</v>
+        <v>6.936</v>
       </c>
       <c r="F313" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G313" t="n">
-        <v>100.38</v>
+        <v>62.42</v>
       </c>
       <c r="H313" t="n">
-        <v>0.29</v>
+        <v>6.27</v>
       </c>
       <c r="I313" t="n">
-        <v>0.29</v>
+        <v>11.17</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11086,29 +11086,29 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D314" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E314" t="n">
-        <v>6.936</v>
+        <v>11.742</v>
       </c>
       <c r="F314" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G314" t="n">
-        <v>62.42</v>
+        <v>35.23</v>
       </c>
       <c r="H314" t="n">
-        <v>6.27</v>
+        <v>4.07</v>
       </c>
       <c r="I314" t="n">
-        <v>11.17</v>
+        <v>13.06</v>
       </c>
       <c r="J314" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D315" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E315" t="n">
-        <v>11.742</v>
+        <v>38.66</v>
       </c>
       <c r="F315" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G315" t="n">
-        <v>35.23</v>
+        <v>154.64</v>
       </c>
       <c r="H315" t="n">
-        <v>4.07</v>
+        <v>15.62</v>
       </c>
       <c r="I315" t="n">
-        <v>13.06</v>
+        <v>11.24</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D316" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E316" t="n">
-        <v>38.66</v>
+        <v>22.9</v>
       </c>
       <c r="F316" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G316" t="n">
-        <v>154.64</v>
+        <v>68.7</v>
       </c>
       <c r="H316" t="n">
-        <v>15.62</v>
+        <v>3.03</v>
       </c>
       <c r="I316" t="n">
-        <v>11.24</v>
+        <v>4.61</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D322" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E322" t="n">
-        <v>11.81</v>
+        <v>39.07</v>
       </c>
       <c r="F322" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G322" t="n">
-        <v>35.43</v>
+        <v>156.28</v>
       </c>
       <c r="H322" t="n">
-        <v>4.27</v>
+        <v>17.26</v>
       </c>
       <c r="I322" t="n">
-        <v>13.7</v>
+        <v>12.42</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D323" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E323" t="n">
-        <v>101.7</v>
+        <v>6.967</v>
       </c>
       <c r="F323" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G323" t="n">
-        <v>101.7</v>
+        <v>62.7</v>
       </c>
       <c r="H323" t="n">
-        <v>1.61</v>
+        <v>6.55</v>
       </c>
       <c r="I323" t="n">
-        <v>1.61</v>
+        <v>11.67</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D325" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E325" t="n">
-        <v>39.07</v>
+        <v>11.81</v>
       </c>
       <c r="F325" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G325" t="n">
-        <v>156.28</v>
+        <v>35.43</v>
       </c>
       <c r="H325" t="n">
-        <v>17.26</v>
+        <v>4.27</v>
       </c>
       <c r="I325" t="n">
-        <v>12.42</v>
+        <v>13.7</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D326" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E326" t="n">
-        <v>6.967</v>
+        <v>101.7</v>
       </c>
       <c r="F326" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G326" t="n">
-        <v>62.7</v>
+        <v>101.7</v>
       </c>
       <c r="H326" t="n">
-        <v>6.55</v>
+        <v>1.61</v>
       </c>
       <c r="I326" t="n">
-        <v>11.67</v>
+        <v>1.61</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11698,29 +11698,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D332" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E332" t="n">
-        <v>6.948</v>
+        <v>38.98</v>
       </c>
       <c r="F332" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G332" t="n">
-        <v>62.53</v>
+        <v>155.92</v>
       </c>
       <c r="H332" t="n">
-        <v>6.38</v>
+        <v>16.9</v>
       </c>
       <c r="I332" t="n">
-        <v>11.36</v>
+        <v>12.16</v>
       </c>
       <c r="J332" t="n">
         <v>7.91</v>
@@ -11732,29 +11732,29 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C333" t="n">
         <v>3</v>
       </c>
       <c r="D333" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E333" t="n">
-        <v>22.745</v>
+        <v>11.5</v>
       </c>
       <c r="F333" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G333" t="n">
-        <v>68.23</v>
+        <v>34.5</v>
       </c>
       <c r="H333" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="I333" t="n">
-        <v>3.9</v>
+        <v>10.72</v>
       </c>
       <c r="J333" t="n">
         <v>7.91</v>
@@ -11766,29 +11766,29 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E334" t="n">
-        <v>11.5</v>
+        <v>101.38</v>
       </c>
       <c r="F334" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G334" t="n">
-        <v>34.5</v>
+        <v>101.38</v>
       </c>
       <c r="H334" t="n">
-        <v>3.34</v>
+        <v>1.29</v>
       </c>
       <c r="I334" t="n">
-        <v>10.72</v>
+        <v>1.29</v>
       </c>
       <c r="J334" t="n">
         <v>7.91</v>
@@ -11800,29 +11800,29 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D335" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E335" t="n">
-        <v>38.98</v>
+        <v>6.948</v>
       </c>
       <c r="F335" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G335" t="n">
-        <v>155.92</v>
+        <v>62.53</v>
       </c>
       <c r="H335" t="n">
-        <v>16.9</v>
+        <v>6.38</v>
       </c>
       <c r="I335" t="n">
-        <v>12.16</v>
+        <v>11.36</v>
       </c>
       <c r="J335" t="n">
         <v>7.91</v>
@@ -11834,29 +11834,29 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D336" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E336" t="n">
-        <v>101.38</v>
+        <v>22.745</v>
       </c>
       <c r="F336" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G336" t="n">
-        <v>101.38</v>
+        <v>68.23</v>
       </c>
       <c r="H336" t="n">
-        <v>1.29</v>
+        <v>2.56</v>
       </c>
       <c r="I336" t="n">
-        <v>1.29</v>
+        <v>3.9</v>
       </c>
       <c r="J336" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E347" t="n">
-        <v>7.005</v>
+        <v>101.78</v>
       </c>
       <c r="F347" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G347" t="n">
-        <v>63.05</v>
+        <v>101.78</v>
       </c>
       <c r="H347" t="n">
-        <v>6.9</v>
+        <v>1.69</v>
       </c>
       <c r="I347" t="n">
-        <v>12.29</v>
+        <v>1.69</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D348" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E348" t="n">
-        <v>11.206</v>
+        <v>39</v>
       </c>
       <c r="F348" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G348" t="n">
-        <v>33.62</v>
+        <v>156</v>
       </c>
       <c r="H348" t="n">
-        <v>2.46</v>
+        <v>16.98</v>
       </c>
       <c r="I348" t="n">
-        <v>7.89</v>
+        <v>12.21</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12276,29 +12276,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D349" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E349" t="n">
-        <v>39</v>
+        <v>22.82</v>
       </c>
       <c r="F349" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G349" t="n">
-        <v>156</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H349" t="n">
-        <v>16.98</v>
+        <v>2.79</v>
       </c>
       <c r="I349" t="n">
-        <v>12.21</v>
+        <v>4.25</v>
       </c>
       <c r="J349" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D350" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E350" t="n">
-        <v>22.82</v>
+        <v>7.005</v>
       </c>
       <c r="F350" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G350" t="n">
-        <v>68.45999999999999</v>
+        <v>63.05</v>
       </c>
       <c r="H350" t="n">
-        <v>2.79</v>
+        <v>6.9</v>
       </c>
       <c r="I350" t="n">
-        <v>4.25</v>
+        <v>12.29</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D351" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E351" t="n">
-        <v>101.78</v>
+        <v>11.206</v>
       </c>
       <c r="F351" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G351" t="n">
-        <v>101.78</v>
+        <v>33.62</v>
       </c>
       <c r="H351" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="I351" t="n">
-        <v>1.69</v>
+        <v>7.89</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C357" t="n">
         <v>3</v>
       </c>
       <c r="D357" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E357" t="n">
-        <v>22.5</v>
+        <v>11.13</v>
       </c>
       <c r="F357" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G357" t="n">
-        <v>67.5</v>
+        <v>33.39</v>
       </c>
       <c r="H357" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="I357" t="n">
-        <v>2.79</v>
+        <v>7.16</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D358" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E358" t="n">
-        <v>40.07</v>
+        <v>6.978</v>
       </c>
       <c r="F358" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G358" t="n">
-        <v>160.28</v>
+        <v>62.8</v>
       </c>
       <c r="H358" t="n">
-        <v>21.26</v>
+        <v>6.65</v>
       </c>
       <c r="I358" t="n">
-        <v>15.29</v>
+        <v>11.84</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E359" t="n">
-        <v>6.978</v>
+        <v>101.98</v>
       </c>
       <c r="F359" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G359" t="n">
-        <v>62.8</v>
+        <v>101.98</v>
       </c>
       <c r="H359" t="n">
-        <v>6.65</v>
+        <v>1.89</v>
       </c>
       <c r="I359" t="n">
-        <v>11.84</v>
+        <v>1.89</v>
       </c>
       <c r="J359" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C360" t="n">
         <v>3</v>
       </c>
       <c r="D360" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E360" t="n">
-        <v>11.13</v>
+        <v>22.5</v>
       </c>
       <c r="F360" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G360" t="n">
-        <v>33.39</v>
+        <v>67.5</v>
       </c>
       <c r="H360" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="I360" t="n">
-        <v>7.16</v>
+        <v>2.79</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D361" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E361" t="n">
-        <v>101.98</v>
+        <v>40.07</v>
       </c>
       <c r="F361" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G361" t="n">
-        <v>101.98</v>
+        <v>160.28</v>
       </c>
       <c r="H361" t="n">
-        <v>1.89</v>
+        <v>21.26</v>
       </c>
       <c r="I361" t="n">
-        <v>1.89</v>
+        <v>15.29</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -13058,29 +13058,29 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D372" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E372" t="n">
-        <v>100.88</v>
+        <v>6.878</v>
       </c>
       <c r="F372" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G372" t="n">
-        <v>100.88</v>
+        <v>61.9</v>
       </c>
       <c r="H372" t="n">
-        <v>0.79</v>
+        <v>5.75</v>
       </c>
       <c r="I372" t="n">
-        <v>0.79</v>
+        <v>10.24</v>
       </c>
       <c r="J372" t="n">
         <v>7.91</v>
@@ -13092,29 +13092,29 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D373" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E373" t="n">
-        <v>10.912</v>
+        <v>39.05</v>
       </c>
       <c r="F373" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G373" t="n">
-        <v>32.74</v>
+        <v>156.2</v>
       </c>
       <c r="H373" t="n">
-        <v>1.58</v>
+        <v>17.18</v>
       </c>
       <c r="I373" t="n">
-        <v>5.07</v>
+        <v>12.36</v>
       </c>
       <c r="J373" t="n">
         <v>7.91</v>
@@ -13126,29 +13126,29 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D374" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E374" t="n">
-        <v>39.05</v>
+        <v>21.94</v>
       </c>
       <c r="F374" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G374" t="n">
-        <v>156.2</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H374" t="n">
-        <v>17.18</v>
+        <v>0.15</v>
       </c>
       <c r="I374" t="n">
-        <v>12.36</v>
+        <v>0.23</v>
       </c>
       <c r="J374" t="n">
         <v>7.91</v>
@@ -13160,29 +13160,29 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E375" t="n">
-        <v>21.94</v>
+        <v>100.88</v>
       </c>
       <c r="F375" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G375" t="n">
-        <v>65.81999999999999</v>
+        <v>100.88</v>
       </c>
       <c r="H375" t="n">
-        <v>0.15</v>
+        <v>0.79</v>
       </c>
       <c r="I375" t="n">
-        <v>0.23</v>
+        <v>0.79</v>
       </c>
       <c r="J375" t="n">
         <v>7.91</v>
@@ -13194,29 +13194,29 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D376" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E376" t="n">
-        <v>6.878</v>
+        <v>10.912</v>
       </c>
       <c r="F376" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G376" t="n">
-        <v>61.9</v>
+        <v>32.74</v>
       </c>
       <c r="H376" t="n">
-        <v>5.75</v>
+        <v>1.58</v>
       </c>
       <c r="I376" t="n">
-        <v>10.24</v>
+        <v>5.07</v>
       </c>
       <c r="J376" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D387" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E387" t="n">
-        <v>6.893</v>
+        <v>100.76</v>
       </c>
       <c r="F387" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G387" t="n">
-        <v>62.04</v>
+        <v>100.76</v>
       </c>
       <c r="H387" t="n">
-        <v>5.89</v>
+        <v>0.67</v>
       </c>
       <c r="I387" t="n">
-        <v>10.49</v>
+        <v>0.67</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C388" t="n">
         <v>3</v>
       </c>
       <c r="D388" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E388" t="n">
-        <v>11.006</v>
+        <v>21.83</v>
       </c>
       <c r="F388" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G388" t="n">
-        <v>33.02</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H388" t="n">
-        <v>1.86</v>
+        <v>-0.18</v>
       </c>
       <c r="I388" t="n">
-        <v>5.97</v>
+        <v>-0.27</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D389" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E389" t="n">
-        <v>38.375</v>
+        <v>11.006</v>
       </c>
       <c r="F389" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G389" t="n">
-        <v>153.5</v>
+        <v>33.02</v>
       </c>
       <c r="H389" t="n">
-        <v>14.48</v>
+        <v>1.86</v>
       </c>
       <c r="I389" t="n">
-        <v>10.42</v>
+        <v>5.97</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D390" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E390" t="n">
-        <v>21.83</v>
+        <v>6.893</v>
       </c>
       <c r="F390" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G390" t="n">
-        <v>65.48999999999999</v>
+        <v>62.04</v>
       </c>
       <c r="H390" t="n">
-        <v>-0.18</v>
+        <v>5.89</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.27</v>
+        <v>10.49</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D391" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E391" t="n">
-        <v>100.76</v>
+        <v>38.375</v>
       </c>
       <c r="F391" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G391" t="n">
-        <v>100.76</v>
+        <v>153.5</v>
       </c>
       <c r="H391" t="n">
-        <v>0.67</v>
+        <v>14.48</v>
       </c>
       <c r="I391" t="n">
-        <v>0.67</v>
+        <v>10.42</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -13899,6 +13899,176 @@
         <v>11.1</v>
       </c>
       <c r="J396" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>3</v>
+      </c>
+      <c r="D397" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E397" t="n">
+        <v>11.202</v>
+      </c>
+      <c r="F397" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G397" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="H397" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I397" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="J397" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>4</v>
+      </c>
+      <c r="D398" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E398" t="n">
+        <v>39.435</v>
+      </c>
+      <c r="F398" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G398" t="n">
+        <v>157.74</v>
+      </c>
+      <c r="H398" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="I398" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="J398" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>3</v>
+      </c>
+      <c r="D399" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E399" t="n">
+        <v>22.145</v>
+      </c>
+      <c r="F399" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G399" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I399" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J399" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+      <c r="D400" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E400" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="F400" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G400" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="H400" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I400" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J400" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>9</v>
+      </c>
+      <c r="D401" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E401" t="n">
+        <v>6.982</v>
+      </c>
+      <c r="F401" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G401" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="H401" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I401" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="J401" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J401"/>
+  <dimension ref="A1:J406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E12" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F12" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G12" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E13" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F13" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G13" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H13" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E14" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F14" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G14" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H14" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I14" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E15" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F15" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G15" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H15" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I15" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E16" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F16" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G16" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E27" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F27" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G27" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H27" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E28" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F28" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G28" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H28" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E29" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F29" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G29" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H29" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I29" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E30" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F30" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G30" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E31" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F31" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G31" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I31" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E37" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F37" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G37" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E38" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F38" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G38" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H38" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E39" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F39" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G39" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H39" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I39" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E40" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F40" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G40" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H40" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I40" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E41" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F41" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G41" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H41" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I41" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E52" t="n">
-        <v>21.703</v>
+        <v>38.544</v>
       </c>
       <c r="F52" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G52" t="n">
-        <v>65.11</v>
+        <v>154.18</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5600000000000001</v>
+        <v>15.16</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.85</v>
+        <v>10.9</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E53" t="n">
-        <v>6.629</v>
+        <v>10.702</v>
       </c>
       <c r="F53" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G53" t="n">
-        <v>59.66</v>
+        <v>32.11</v>
       </c>
       <c r="H53" t="n">
-        <v>3.51</v>
+        <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E54" t="n">
-        <v>100.34</v>
+        <v>21.703</v>
       </c>
       <c r="F54" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G54" t="n">
-        <v>100.34</v>
+        <v>65.11</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E55" t="n">
-        <v>10.702</v>
+        <v>6.629</v>
       </c>
       <c r="F55" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G55" t="n">
-        <v>32.11</v>
+        <v>59.66</v>
       </c>
       <c r="H55" t="n">
-        <v>0.95</v>
+        <v>3.51</v>
       </c>
       <c r="I55" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E56" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F56" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G56" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H56" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E62" t="n">
-        <v>10.712</v>
+        <v>22.7</v>
       </c>
       <c r="F62" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G62" t="n">
-        <v>32.14</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>0.98</v>
+        <v>2.43</v>
       </c>
       <c r="I62" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E63" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F63" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G63" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H63" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I63" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E64" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F64" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G64" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H64" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I64" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E65" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F65" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G65" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H65" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E66" t="n">
-        <v>6.817</v>
+        <v>41.064</v>
       </c>
       <c r="F66" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G66" t="n">
-        <v>61.35</v>
+        <v>164.26</v>
       </c>
       <c r="H66" t="n">
-        <v>5.2</v>
+        <v>25.24</v>
       </c>
       <c r="I66" t="n">
-        <v>9.26</v>
+        <v>18.16</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E67" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F67" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G67" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H67" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I67" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E68" t="n">
-        <v>10.796</v>
+        <v>40.567</v>
       </c>
       <c r="F68" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G68" t="n">
-        <v>32.39</v>
+        <v>162.27</v>
       </c>
       <c r="H68" t="n">
-        <v>1.23</v>
+        <v>23.25</v>
       </c>
       <c r="I68" t="n">
-        <v>3.95</v>
+        <v>16.72</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E69" t="n">
-        <v>40.567</v>
+        <v>104.58</v>
       </c>
       <c r="F69" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G69" t="n">
-        <v>162.27</v>
+        <v>104.58</v>
       </c>
       <c r="H69" t="n">
-        <v>23.25</v>
+        <v>4.49</v>
       </c>
       <c r="I69" t="n">
-        <v>16.72</v>
+        <v>4.49</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E70" t="n">
-        <v>104.58</v>
+        <v>6.807</v>
       </c>
       <c r="F70" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G70" t="n">
-        <v>104.58</v>
+        <v>61.26</v>
       </c>
       <c r="H70" t="n">
-        <v>4.49</v>
+        <v>5.11</v>
       </c>
       <c r="I70" t="n">
-        <v>4.49</v>
+        <v>9.1</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E71" t="n">
-        <v>6.807</v>
+        <v>22.797</v>
       </c>
       <c r="F71" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G71" t="n">
-        <v>61.26</v>
+        <v>68.39</v>
       </c>
       <c r="H71" t="n">
-        <v>5.11</v>
+        <v>2.72</v>
       </c>
       <c r="I71" t="n">
-        <v>9.1</v>
+        <v>4.14</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E77" t="n">
-        <v>23.4</v>
+        <v>6.836</v>
       </c>
       <c r="F77" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G77" t="n">
-        <v>70.2</v>
+        <v>61.52</v>
       </c>
       <c r="H77" t="n">
-        <v>4.53</v>
+        <v>5.37</v>
       </c>
       <c r="I77" t="n">
-        <v>6.9</v>
+        <v>9.56</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E78" t="n">
-        <v>42.25</v>
+        <v>105.8</v>
       </c>
       <c r="F78" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G78" t="n">
-        <v>169</v>
+        <v>105.8</v>
       </c>
       <c r="H78" t="n">
-        <v>29.98</v>
+        <v>5.71</v>
       </c>
       <c r="I78" t="n">
-        <v>21.57</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E80" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F80" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G80" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H80" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I80" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E81" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F81" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G81" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H81" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E87" t="n">
-        <v>6.856</v>
+        <v>10.852</v>
       </c>
       <c r="F87" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G87" t="n">
-        <v>61.7</v>
+        <v>32.56</v>
       </c>
       <c r="H87" t="n">
-        <v>5.55</v>
+        <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>9.880000000000001</v>
+        <v>4.49</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E88" t="n">
-        <v>106.28</v>
+        <v>23.32</v>
       </c>
       <c r="F88" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G88" t="n">
-        <v>106.28</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>6.19</v>
+        <v>4.29</v>
       </c>
       <c r="I88" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E89" t="n">
-        <v>23.32</v>
+        <v>43.005</v>
       </c>
       <c r="F89" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G89" t="n">
-        <v>69.95999999999999</v>
+        <v>172.02</v>
       </c>
       <c r="H89" t="n">
-        <v>4.29</v>
+        <v>33</v>
       </c>
       <c r="I89" t="n">
-        <v>6.53</v>
+        <v>23.74</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E90" t="n">
-        <v>10.852</v>
+        <v>6.856</v>
       </c>
       <c r="F90" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G90" t="n">
-        <v>32.56</v>
+        <v>61.7</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4</v>
+        <v>5.55</v>
       </c>
       <c r="I90" t="n">
-        <v>4.49</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E91" t="n">
-        <v>43.005</v>
+        <v>106.28</v>
       </c>
       <c r="F91" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G91" t="n">
-        <v>172.02</v>
+        <v>106.28</v>
       </c>
       <c r="H91" t="n">
-        <v>33</v>
+        <v>6.19</v>
       </c>
       <c r="I91" t="n">
-        <v>23.74</v>
+        <v>6.18</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E102" t="n">
-        <v>10.556</v>
+        <v>40.97</v>
       </c>
       <c r="F102" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G102" t="n">
-        <v>31.67</v>
+        <v>163.88</v>
       </c>
       <c r="H102" t="n">
-        <v>0.51</v>
+        <v>24.86</v>
       </c>
       <c r="I102" t="n">
-        <v>1.64</v>
+        <v>17.88</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E103" t="n">
-        <v>103.46</v>
+        <v>23.29</v>
       </c>
       <c r="F103" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G103" t="n">
-        <v>103.46</v>
+        <v>69.87</v>
       </c>
       <c r="H103" t="n">
-        <v>3.37</v>
+        <v>4.2</v>
       </c>
       <c r="I103" t="n">
-        <v>3.37</v>
+        <v>6.4</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E104" t="n">
-        <v>6.804</v>
+        <v>10.556</v>
       </c>
       <c r="F104" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G104" t="n">
-        <v>61.24</v>
+        <v>31.67</v>
       </c>
       <c r="H104" t="n">
-        <v>5.09</v>
+        <v>0.51</v>
       </c>
       <c r="I104" t="n">
-        <v>9.07</v>
+        <v>1.64</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E105" t="n">
-        <v>23.29</v>
+        <v>103.46</v>
       </c>
       <c r="F105" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G105" t="n">
-        <v>69.87</v>
+        <v>103.46</v>
       </c>
       <c r="H105" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>3.37</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4014,29 +4014,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E106" t="n">
-        <v>40.97</v>
+        <v>6.804</v>
       </c>
       <c r="F106" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G106" t="n">
-        <v>163.88</v>
+        <v>61.24</v>
       </c>
       <c r="H106" t="n">
-        <v>24.86</v>
+        <v>5.09</v>
       </c>
       <c r="I106" t="n">
-        <v>17.88</v>
+        <v>9.07</v>
       </c>
       <c r="J106" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E117" t="n">
-        <v>105.96</v>
+        <v>6.861</v>
       </c>
       <c r="F117" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G117" t="n">
-        <v>105.96</v>
+        <v>61.75</v>
       </c>
       <c r="H117" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="I117" t="n">
-        <v>5.86</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E118" t="n">
-        <v>23.145</v>
+        <v>10.756</v>
       </c>
       <c r="F118" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G118" t="n">
-        <v>69.44</v>
+        <v>32.27</v>
       </c>
       <c r="H118" t="n">
-        <v>3.77</v>
+        <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>5.74</v>
+        <v>3.56</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E119" t="n">
-        <v>41</v>
+        <v>105.96</v>
       </c>
       <c r="F119" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G119" t="n">
-        <v>164</v>
+        <v>105.96</v>
       </c>
       <c r="H119" t="n">
-        <v>24.98</v>
+        <v>5.87</v>
       </c>
       <c r="I119" t="n">
-        <v>17.97</v>
+        <v>5.86</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E120" t="n">
-        <v>10.756</v>
+        <v>23.145</v>
       </c>
       <c r="F120" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G120" t="n">
-        <v>32.27</v>
+        <v>69.44</v>
       </c>
       <c r="H120" t="n">
-        <v>1.11</v>
+        <v>3.77</v>
       </c>
       <c r="I120" t="n">
-        <v>3.56</v>
+        <v>5.74</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E121" t="n">
-        <v>6.861</v>
+        <v>41</v>
       </c>
       <c r="F121" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G121" t="n">
-        <v>61.75</v>
+        <v>164</v>
       </c>
       <c r="H121" t="n">
-        <v>5.6</v>
+        <v>24.98</v>
       </c>
       <c r="I121" t="n">
-        <v>9.970000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E122" t="n">
-        <v>23.165</v>
+        <v>106</v>
       </c>
       <c r="F122" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G122" t="n">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="H122" t="n">
-        <v>3.83</v>
+        <v>5.91</v>
       </c>
       <c r="I122" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E123" t="n">
-        <v>6.901</v>
+        <v>23.165</v>
       </c>
       <c r="F123" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G123" t="n">
-        <v>62.11</v>
+        <v>69.5</v>
       </c>
       <c r="H123" t="n">
-        <v>5.96</v>
+        <v>3.83</v>
       </c>
       <c r="I123" t="n">
-        <v>10.61</v>
+        <v>5.83</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4626,29 +4626,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E124" t="n">
-        <v>11.038</v>
+        <v>6.901</v>
       </c>
       <c r="F124" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G124" t="n">
-        <v>33.11</v>
+        <v>62.11</v>
       </c>
       <c r="H124" t="n">
-        <v>1.95</v>
+        <v>5.96</v>
       </c>
       <c r="I124" t="n">
-        <v>6.26</v>
+        <v>10.61</v>
       </c>
       <c r="J124" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E125" t="n">
-        <v>40.395</v>
+        <v>11.038</v>
       </c>
       <c r="F125" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G125" t="n">
-        <v>161.58</v>
+        <v>33.11</v>
       </c>
       <c r="H125" t="n">
-        <v>22.56</v>
+        <v>1.95</v>
       </c>
       <c r="I125" t="n">
-        <v>16.23</v>
+        <v>6.26</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E126" t="n">
-        <v>106</v>
+        <v>40.395</v>
       </c>
       <c r="F126" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G126" t="n">
-        <v>106</v>
+        <v>161.58</v>
       </c>
       <c r="H126" t="n">
-        <v>5.91</v>
+        <v>22.56</v>
       </c>
       <c r="I126" t="n">
-        <v>5.9</v>
+        <v>16.23</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E127" t="n">
-        <v>39.36</v>
+        <v>23.17</v>
       </c>
       <c r="F127" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G127" t="n">
-        <v>157.44</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>18.42</v>
+        <v>3.84</v>
       </c>
       <c r="I127" t="n">
-        <v>13.25</v>
+        <v>5.85</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D128" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E128" t="n">
-        <v>11.458</v>
+        <v>6.868</v>
       </c>
       <c r="F128" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G128" t="n">
-        <v>34.37</v>
+        <v>61.81</v>
       </c>
       <c r="H128" t="n">
-        <v>3.21</v>
+        <v>5.66</v>
       </c>
       <c r="I128" t="n">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E130" t="n">
-        <v>6.868</v>
+        <v>11.458</v>
       </c>
       <c r="F130" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G130" t="n">
-        <v>61.81</v>
+        <v>34.37</v>
       </c>
       <c r="H130" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="I130" t="n">
-        <v>10.08</v>
+        <v>10.3</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E131" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F131" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G131" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H131" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I131" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E137" t="n">
-        <v>104.76</v>
+        <v>23.3</v>
       </c>
       <c r="F137" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G137" t="n">
-        <v>104.76</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>4.67</v>
+        <v>4.23</v>
       </c>
       <c r="I137" t="n">
-        <v>4.67</v>
+        <v>6.44</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E138" t="n">
-        <v>11.728</v>
+        <v>40.61</v>
       </c>
       <c r="F138" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G138" t="n">
-        <v>35.18</v>
+        <v>162.44</v>
       </c>
       <c r="H138" t="n">
-        <v>4.02</v>
+        <v>23.42</v>
       </c>
       <c r="I138" t="n">
-        <v>12.9</v>
+        <v>16.85</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D139" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E139" t="n">
-        <v>40.61</v>
+        <v>6.927</v>
       </c>
       <c r="F139" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G139" t="n">
-        <v>162.44</v>
+        <v>62.34</v>
       </c>
       <c r="H139" t="n">
-        <v>23.42</v>
+        <v>6.19</v>
       </c>
       <c r="I139" t="n">
-        <v>16.85</v>
+        <v>11.02</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>104.76</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>4.67</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>4.67</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E141" t="n">
-        <v>6.927</v>
+        <v>11.728</v>
       </c>
       <c r="F141" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G141" t="n">
-        <v>62.34</v>
+        <v>35.18</v>
       </c>
       <c r="H141" t="n">
-        <v>6.19</v>
+        <v>4.02</v>
       </c>
       <c r="I141" t="n">
-        <v>11.02</v>
+        <v>12.9</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E152" t="n">
-        <v>6.893</v>
+        <v>39.915</v>
       </c>
       <c r="F152" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G152" t="n">
-        <v>62.04</v>
+        <v>159.66</v>
       </c>
       <c r="H152" t="n">
-        <v>5.89</v>
+        <v>20.64</v>
       </c>
       <c r="I152" t="n">
-        <v>10.49</v>
+        <v>14.85</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E153" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F153" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G153" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H153" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I153" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D155" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E155" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F155" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G155" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H155" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I155" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E156" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F156" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G156" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H156" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I156" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E162" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F162" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G162" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H162" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I162" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E163" t="n">
-        <v>23.01</v>
+        <v>103.84</v>
       </c>
       <c r="F163" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G163" t="n">
-        <v>69.03</v>
+        <v>103.84</v>
       </c>
       <c r="H163" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="I163" t="n">
-        <v>5.12</v>
+        <v>3.75</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D164" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E164" t="n">
-        <v>103.84</v>
+        <v>6.927</v>
       </c>
       <c r="F164" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G164" t="n">
-        <v>103.84</v>
+        <v>62.34</v>
       </c>
       <c r="H164" t="n">
-        <v>3.75</v>
+        <v>6.19</v>
       </c>
       <c r="I164" t="n">
-        <v>3.75</v>
+        <v>11.02</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E165" t="n">
-        <v>38.845</v>
+        <v>10.748</v>
       </c>
       <c r="F165" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G165" t="n">
-        <v>155.38</v>
+        <v>32.24</v>
       </c>
       <c r="H165" t="n">
-        <v>16.36</v>
+        <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>11.77</v>
+        <v>3.47</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E166" t="n">
-        <v>6.927</v>
+        <v>23.01</v>
       </c>
       <c r="F166" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G166" t="n">
-        <v>62.34</v>
+        <v>69.03</v>
       </c>
       <c r="H166" t="n">
-        <v>6.19</v>
+        <v>3.36</v>
       </c>
       <c r="I166" t="n">
-        <v>11.02</v>
+        <v>5.12</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C167" t="n">
         <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E167" t="n">
-        <v>10.726</v>
+        <v>22.92</v>
       </c>
       <c r="F167" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G167" t="n">
-        <v>32.18</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H167" t="n">
-        <v>1.02</v>
+        <v>3.09</v>
       </c>
       <c r="I167" t="n">
-        <v>3.27</v>
+        <v>4.71</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E168" t="n">
-        <v>22.92</v>
+        <v>38.98</v>
       </c>
       <c r="F168" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G168" t="n">
-        <v>68.76000000000001</v>
+        <v>155.92</v>
       </c>
       <c r="H168" t="n">
-        <v>3.09</v>
+        <v>16.9</v>
       </c>
       <c r="I168" t="n">
-        <v>4.71</v>
+        <v>12.16</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E169" t="n">
-        <v>38.98</v>
+        <v>6.911</v>
       </c>
       <c r="F169" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G169" t="n">
-        <v>155.92</v>
+        <v>62.2</v>
       </c>
       <c r="H169" t="n">
-        <v>16.9</v>
+        <v>6.05</v>
       </c>
       <c r="I169" t="n">
-        <v>12.16</v>
+        <v>10.77</v>
       </c>
       <c r="J169" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E170" t="n">
-        <v>6.911</v>
+        <v>103.98</v>
       </c>
       <c r="F170" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G170" t="n">
-        <v>62.2</v>
+        <v>103.98</v>
       </c>
       <c r="H170" t="n">
-        <v>6.05</v>
+        <v>3.89</v>
       </c>
       <c r="I170" t="n">
-        <v>10.77</v>
+        <v>3.89</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E171" t="n">
-        <v>103.98</v>
+        <v>10.726</v>
       </c>
       <c r="F171" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G171" t="n">
-        <v>103.98</v>
+        <v>32.18</v>
       </c>
       <c r="H171" t="n">
-        <v>3.89</v>
+        <v>1.02</v>
       </c>
       <c r="I171" t="n">
-        <v>3.89</v>
+        <v>3.27</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E177" t="n">
-        <v>38.245</v>
+        <v>6.922</v>
       </c>
       <c r="F177" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G177" t="n">
-        <v>152.98</v>
+        <v>62.3</v>
       </c>
       <c r="H177" t="n">
-        <v>13.96</v>
+        <v>6.15</v>
       </c>
       <c r="I177" t="n">
-        <v>10.04</v>
+        <v>10.95</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E178" t="n">
-        <v>22.95</v>
+        <v>102.54</v>
       </c>
       <c r="F178" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G178" t="n">
-        <v>68.84999999999999</v>
+        <v>102.54</v>
       </c>
       <c r="H178" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="I178" t="n">
-        <v>4.84</v>
+        <v>2.45</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E180" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F180" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G180" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H180" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I180" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E181" t="n">
-        <v>102.54</v>
+        <v>22.95</v>
       </c>
       <c r="F181" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G181" t="n">
-        <v>102.54</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="I181" t="n">
-        <v>2.45</v>
+        <v>4.84</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E187" t="n">
-        <v>22.845</v>
+        <v>101.44</v>
       </c>
       <c r="F187" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G187" t="n">
-        <v>68.53</v>
+        <v>101.44</v>
       </c>
       <c r="H187" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>4.36</v>
+        <v>1.35</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E188" t="n">
-        <v>37.85</v>
+        <v>6.862</v>
       </c>
       <c r="F188" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G188" t="n">
-        <v>151.4</v>
+        <v>61.76</v>
       </c>
       <c r="H188" t="n">
-        <v>12.38</v>
+        <v>5.61</v>
       </c>
       <c r="I188" t="n">
-        <v>8.91</v>
+        <v>9.99</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E189" t="n">
-        <v>6.862</v>
+        <v>10.708</v>
       </c>
       <c r="F189" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G189" t="n">
-        <v>61.76</v>
+        <v>32.12</v>
       </c>
       <c r="H189" t="n">
-        <v>5.61</v>
+        <v>0.96</v>
       </c>
       <c r="I189" t="n">
-        <v>9.99</v>
+        <v>3.08</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E190" t="n">
-        <v>101.44</v>
+        <v>22.845</v>
       </c>
       <c r="F190" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G190" t="n">
-        <v>101.44</v>
+        <v>68.53</v>
       </c>
       <c r="H190" t="n">
-        <v>1.35</v>
+        <v>2.86</v>
       </c>
       <c r="I190" t="n">
-        <v>1.35</v>
+        <v>4.36</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E191" t="n">
-        <v>10.708</v>
+        <v>37.85</v>
       </c>
       <c r="F191" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G191" t="n">
-        <v>32.12</v>
+        <v>151.4</v>
       </c>
       <c r="H191" t="n">
-        <v>0.96</v>
+        <v>12.38</v>
       </c>
       <c r="I191" t="n">
-        <v>3.08</v>
+        <v>8.91</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D202" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E202" t="n">
-        <v>6.822</v>
+        <v>38.04</v>
       </c>
       <c r="F202" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G202" t="n">
-        <v>61.4</v>
+        <v>152.16</v>
       </c>
       <c r="H202" t="n">
-        <v>5.25</v>
+        <v>13.14</v>
       </c>
       <c r="I202" t="n">
-        <v>9.35</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E203" t="n">
-        <v>100.08</v>
+        <v>11.044</v>
       </c>
       <c r="F203" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G203" t="n">
-        <v>100.08</v>
+        <v>33.13</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.01</v>
+        <v>1.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.01</v>
+        <v>6.32</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E205" t="n">
-        <v>11.044</v>
+        <v>100.08</v>
       </c>
       <c r="F205" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G205" t="n">
-        <v>33.13</v>
+        <v>100.08</v>
       </c>
       <c r="H205" t="n">
-        <v>1.97</v>
+        <v>-0.01</v>
       </c>
       <c r="I205" t="n">
-        <v>6.32</v>
+        <v>-0.01</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D206" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E206" t="n">
-        <v>38.04</v>
+        <v>6.822</v>
       </c>
       <c r="F206" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G206" t="n">
-        <v>152.16</v>
+        <v>61.4</v>
       </c>
       <c r="H206" t="n">
-        <v>13.14</v>
+        <v>5.25</v>
       </c>
       <c r="I206" t="n">
-        <v>9.449999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="J206" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E212" t="n">
-        <v>6.84</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F212" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G212" t="n">
-        <v>61.56</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H212" t="n">
-        <v>5.41</v>
+        <v>-1.8</v>
       </c>
       <c r="I212" t="n">
-        <v>9.630000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E213" t="n">
-        <v>37.25</v>
+        <v>11.338</v>
       </c>
       <c r="F213" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G213" t="n">
-        <v>149</v>
+        <v>34.01</v>
       </c>
       <c r="H213" t="n">
-        <v>9.98</v>
+        <v>2.85</v>
       </c>
       <c r="I213" t="n">
-        <v>7.18</v>
+        <v>9.15</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E214" t="n">
-        <v>11.338</v>
+        <v>22.885</v>
       </c>
       <c r="F214" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G214" t="n">
-        <v>34.01</v>
+        <v>68.66</v>
       </c>
       <c r="H214" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="I214" t="n">
-        <v>9.15</v>
+        <v>4.55</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D215" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E215" t="n">
-        <v>98.29000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="F215" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G215" t="n">
-        <v>98.29000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="H215" t="n">
-        <v>-1.8</v>
+        <v>5.41</v>
       </c>
       <c r="I215" t="n">
-        <v>-1.8</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7754,29 +7754,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D216" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E216" t="n">
-        <v>22.885</v>
+        <v>37.25</v>
       </c>
       <c r="F216" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G216" t="n">
-        <v>68.66</v>
+        <v>149</v>
       </c>
       <c r="H216" t="n">
-        <v>2.99</v>
+        <v>9.98</v>
       </c>
       <c r="I216" t="n">
-        <v>4.55</v>
+        <v>7.18</v>
       </c>
       <c r="J216" t="n">
         <v>7.91</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D227" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E227" t="n">
-        <v>11.512</v>
+        <v>6.779</v>
       </c>
       <c r="F227" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G227" t="n">
-        <v>34.54</v>
+        <v>61.01</v>
       </c>
       <c r="H227" t="n">
-        <v>3.38</v>
+        <v>4.86</v>
       </c>
       <c r="I227" t="n">
-        <v>10.85</v>
+        <v>8.66</v>
       </c>
       <c r="J227" t="n">
         <v>7.91</v>
@@ -8162,29 +8162,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E228" t="n">
-        <v>36.64</v>
+        <v>23.07</v>
       </c>
       <c r="F228" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G228" t="n">
-        <v>146.56</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H228" t="n">
-        <v>7.54</v>
+        <v>3.54</v>
       </c>
       <c r="I228" t="n">
-        <v>5.42</v>
+        <v>5.39</v>
       </c>
       <c r="J228" t="n">
         <v>7.91</v>
@@ -8230,29 +8230,29 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D230" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E230" t="n">
-        <v>23.07</v>
+        <v>36.64</v>
       </c>
       <c r="F230" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G230" t="n">
-        <v>69.20999999999999</v>
+        <v>146.56</v>
       </c>
       <c r="H230" t="n">
-        <v>3.54</v>
+        <v>7.54</v>
       </c>
       <c r="I230" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="J230" t="n">
         <v>7.91</v>
@@ -8264,29 +8264,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D231" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E231" t="n">
-        <v>6.779</v>
+        <v>11.512</v>
       </c>
       <c r="F231" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G231" t="n">
-        <v>61.01</v>
+        <v>34.54</v>
       </c>
       <c r="H231" t="n">
-        <v>4.86</v>
+        <v>3.38</v>
       </c>
       <c r="I231" t="n">
-        <v>8.66</v>
+        <v>10.85</v>
       </c>
       <c r="J231" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E237" t="n">
-        <v>37.315</v>
+        <v>11.842</v>
       </c>
       <c r="F237" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G237" t="n">
-        <v>149.26</v>
+        <v>35.53</v>
       </c>
       <c r="H237" t="n">
-        <v>10.24</v>
+        <v>4.37</v>
       </c>
       <c r="I237" t="n">
-        <v>7.37</v>
+        <v>14.02</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E238" t="n">
-        <v>23.245</v>
+        <v>6.914</v>
       </c>
       <c r="F238" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G238" t="n">
-        <v>69.73</v>
+        <v>62.23</v>
       </c>
       <c r="H238" t="n">
-        <v>4.06</v>
+        <v>6.08</v>
       </c>
       <c r="I238" t="n">
-        <v>6.18</v>
+        <v>10.83</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8536,29 +8536,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E239" t="n">
-        <v>6.914</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F239" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G239" t="n">
-        <v>62.23</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H239" t="n">
-        <v>6.08</v>
+        <v>-0.24</v>
       </c>
       <c r="I239" t="n">
-        <v>10.83</v>
+        <v>-0.24</v>
       </c>
       <c r="J239" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D240" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E240" t="n">
-        <v>11.842</v>
+        <v>37.315</v>
       </c>
       <c r="F240" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G240" t="n">
-        <v>35.53</v>
+        <v>149.26</v>
       </c>
       <c r="H240" t="n">
-        <v>4.37</v>
+        <v>10.24</v>
       </c>
       <c r="I240" t="n">
-        <v>14.02</v>
+        <v>7.37</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E241" t="n">
-        <v>99.84999999999999</v>
+        <v>23.245</v>
       </c>
       <c r="F241" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G241" t="n">
-        <v>99.84999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.24</v>
+        <v>4.06</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.24</v>
+        <v>6.18</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D252" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E252" t="n">
-        <v>103.18</v>
+        <v>7.05</v>
       </c>
       <c r="F252" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G252" t="n">
-        <v>103.18</v>
+        <v>63.45</v>
       </c>
       <c r="H252" t="n">
-        <v>3.09</v>
+        <v>7.3</v>
       </c>
       <c r="I252" t="n">
-        <v>3.09</v>
+        <v>13</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D253" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E253" t="n">
-        <v>23.315</v>
+        <v>38.095</v>
       </c>
       <c r="F253" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G253" t="n">
-        <v>69.95</v>
+        <v>152.38</v>
       </c>
       <c r="H253" t="n">
-        <v>4.28</v>
+        <v>13.36</v>
       </c>
       <c r="I253" t="n">
-        <v>6.52</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E255" t="n">
-        <v>38.095</v>
+        <v>23.315</v>
       </c>
       <c r="F255" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G255" t="n">
-        <v>152.38</v>
+        <v>69.95</v>
       </c>
       <c r="H255" t="n">
-        <v>13.36</v>
+        <v>4.28</v>
       </c>
       <c r="I255" t="n">
-        <v>9.609999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E256" t="n">
-        <v>7.05</v>
+        <v>103.18</v>
       </c>
       <c r="F256" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G256" t="n">
-        <v>63.45</v>
+        <v>103.18</v>
       </c>
       <c r="H256" t="n">
-        <v>7.3</v>
+        <v>3.09</v>
       </c>
       <c r="I256" t="n">
-        <v>13</v>
+        <v>3.09</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E262" t="n">
-        <v>12.23</v>
+        <v>7.055</v>
       </c>
       <c r="F262" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G262" t="n">
-        <v>36.69</v>
+        <v>63.49</v>
       </c>
       <c r="H262" t="n">
-        <v>5.53</v>
+        <v>7.34</v>
       </c>
       <c r="I262" t="n">
-        <v>17.75</v>
+        <v>13.07</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D263" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E263" t="n">
-        <v>23.3</v>
+        <v>38.23</v>
       </c>
       <c r="F263" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G263" t="n">
-        <v>69.90000000000001</v>
+        <v>152.92</v>
       </c>
       <c r="H263" t="n">
-        <v>4.23</v>
+        <v>13.9</v>
       </c>
       <c r="I263" t="n">
-        <v>6.44</v>
+        <v>10</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9386,29 +9386,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E264" t="n">
-        <v>38.23</v>
+        <v>102.84</v>
       </c>
       <c r="F264" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G264" t="n">
-        <v>152.92</v>
+        <v>102.84</v>
       </c>
       <c r="H264" t="n">
-        <v>13.9</v>
+        <v>2.75</v>
       </c>
       <c r="I264" t="n">
-        <v>10</v>
+        <v>2.75</v>
       </c>
       <c r="J264" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D265" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E265" t="n">
-        <v>7.055</v>
+        <v>12.23</v>
       </c>
       <c r="F265" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G265" t="n">
-        <v>63.49</v>
+        <v>36.69</v>
       </c>
       <c r="H265" t="n">
-        <v>7.34</v>
+        <v>5.53</v>
       </c>
       <c r="I265" t="n">
-        <v>13.07</v>
+        <v>17.75</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D266" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E266" t="n">
-        <v>102.84</v>
+        <v>23.3</v>
       </c>
       <c r="F266" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G266" t="n">
-        <v>102.84</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H266" t="n">
-        <v>2.75</v>
+        <v>4.23</v>
       </c>
       <c r="I266" t="n">
-        <v>2.75</v>
+        <v>6.44</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D277" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E277" t="n">
-        <v>38.985</v>
+        <v>22.96</v>
       </c>
       <c r="F277" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G277" t="n">
-        <v>155.94</v>
+        <v>68.88</v>
       </c>
       <c r="H277" t="n">
-        <v>16.92</v>
+        <v>3.21</v>
       </c>
       <c r="I277" t="n">
-        <v>12.17</v>
+        <v>4.89</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D278" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E278" t="n">
-        <v>12.492</v>
+        <v>7.063</v>
       </c>
       <c r="F278" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G278" t="n">
-        <v>37.48</v>
+        <v>63.57</v>
       </c>
       <c r="H278" t="n">
-        <v>6.32</v>
+        <v>7.42</v>
       </c>
       <c r="I278" t="n">
-        <v>20.28</v>
+        <v>13.21</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D280" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E280" t="n">
-        <v>7.063</v>
+        <v>12.492</v>
       </c>
       <c r="F280" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G280" t="n">
-        <v>63.57</v>
+        <v>37.48</v>
       </c>
       <c r="H280" t="n">
-        <v>7.42</v>
+        <v>6.32</v>
       </c>
       <c r="I280" t="n">
-        <v>13.21</v>
+        <v>20.28</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D281" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E281" t="n">
-        <v>22.96</v>
+        <v>38.985</v>
       </c>
       <c r="F281" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G281" t="n">
-        <v>68.88</v>
+        <v>155.94</v>
       </c>
       <c r="H281" t="n">
-        <v>3.21</v>
+        <v>16.92</v>
       </c>
       <c r="I281" t="n">
-        <v>4.89</v>
+        <v>12.17</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -10168,29 +10168,29 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D287" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E287" t="n">
-        <v>6.983</v>
+        <v>38.18</v>
       </c>
       <c r="F287" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G287" t="n">
-        <v>62.85</v>
+        <v>152.72</v>
       </c>
       <c r="H287" t="n">
-        <v>6.7</v>
+        <v>13.7</v>
       </c>
       <c r="I287" t="n">
-        <v>11.93</v>
+        <v>9.85</v>
       </c>
       <c r="J287" t="n">
         <v>7.91</v>
@@ -10202,29 +10202,29 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E288" t="n">
-        <v>22.83</v>
+        <v>102.22</v>
       </c>
       <c r="F288" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G288" t="n">
-        <v>68.48999999999999</v>
+        <v>102.22</v>
       </c>
       <c r="H288" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="I288" t="n">
-        <v>4.29</v>
+        <v>2.13</v>
       </c>
       <c r="J288" t="n">
         <v>7.91</v>
@@ -10236,29 +10236,29 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D289" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E289" t="n">
-        <v>102.22</v>
+        <v>12.292</v>
       </c>
       <c r="F289" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G289" t="n">
-        <v>102.22</v>
+        <v>36.88</v>
       </c>
       <c r="H289" t="n">
-        <v>2.13</v>
+        <v>5.72</v>
       </c>
       <c r="I289" t="n">
-        <v>2.13</v>
+        <v>18.36</v>
       </c>
       <c r="J289" t="n">
         <v>7.91</v>
@@ -10270,29 +10270,29 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E290" t="n">
-        <v>38.18</v>
+        <v>6.983</v>
       </c>
       <c r="F290" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G290" t="n">
-        <v>152.72</v>
+        <v>62.85</v>
       </c>
       <c r="H290" t="n">
-        <v>13.7</v>
+        <v>6.7</v>
       </c>
       <c r="I290" t="n">
-        <v>9.85</v>
+        <v>11.93</v>
       </c>
       <c r="J290" t="n">
         <v>7.91</v>
@@ -10304,29 +10304,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C291" t="n">
         <v>3</v>
       </c>
       <c r="D291" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E291" t="n">
-        <v>12.292</v>
+        <v>22.83</v>
       </c>
       <c r="F291" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G291" t="n">
-        <v>36.88</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H291" t="n">
-        <v>5.72</v>
+        <v>2.82</v>
       </c>
       <c r="I291" t="n">
-        <v>18.36</v>
+        <v>4.29</v>
       </c>
       <c r="J291" t="n">
         <v>7.91</v>
@@ -10678,29 +10678,29 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D302" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E302" t="n">
-        <v>38.845</v>
+        <v>22.715</v>
       </c>
       <c r="F302" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G302" t="n">
-        <v>155.38</v>
+        <v>68.14</v>
       </c>
       <c r="H302" t="n">
-        <v>16.36</v>
+        <v>2.47</v>
       </c>
       <c r="I302" t="n">
-        <v>11.77</v>
+        <v>3.76</v>
       </c>
       <c r="J302" t="n">
         <v>7.91</v>
@@ -10712,29 +10712,29 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D303" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E303" t="n">
-        <v>6.93</v>
+        <v>100.78</v>
       </c>
       <c r="F303" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G303" t="n">
-        <v>62.37</v>
+        <v>100.78</v>
       </c>
       <c r="H303" t="n">
-        <v>6.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>11.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J303" t="n">
         <v>7.91</v>
@@ -10746,29 +10746,29 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D304" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E304" t="n">
-        <v>100.78</v>
+        <v>11.828</v>
       </c>
       <c r="F304" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G304" t="n">
-        <v>100.78</v>
+        <v>35.48</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.86</v>
       </c>
       <c r="J304" t="n">
         <v>7.91</v>
@@ -10780,29 +10780,29 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D305" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E305" t="n">
-        <v>11.828</v>
+        <v>6.93</v>
       </c>
       <c r="F305" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G305" t="n">
-        <v>35.48</v>
+        <v>62.37</v>
       </c>
       <c r="H305" t="n">
-        <v>4.32</v>
+        <v>6.22</v>
       </c>
       <c r="I305" t="n">
-        <v>13.86</v>
+        <v>11.08</v>
       </c>
       <c r="J305" t="n">
         <v>7.91</v>
@@ -10814,29 +10814,29 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D306" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E306" t="n">
-        <v>22.715</v>
+        <v>38.845</v>
       </c>
       <c r="F306" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G306" t="n">
-        <v>68.14</v>
+        <v>155.38</v>
       </c>
       <c r="H306" t="n">
-        <v>2.47</v>
+        <v>16.36</v>
       </c>
       <c r="I306" t="n">
-        <v>3.76</v>
+        <v>11.77</v>
       </c>
       <c r="J306" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D312" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E312" t="n">
-        <v>100.38</v>
+        <v>38.66</v>
       </c>
       <c r="F312" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G312" t="n">
-        <v>100.38</v>
+        <v>154.64</v>
       </c>
       <c r="H312" t="n">
-        <v>0.29</v>
+        <v>15.62</v>
       </c>
       <c r="I312" t="n">
-        <v>0.29</v>
+        <v>11.24</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D313" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E313" t="n">
-        <v>6.936</v>
+        <v>11.742</v>
       </c>
       <c r="F313" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G313" t="n">
-        <v>62.42</v>
+        <v>35.23</v>
       </c>
       <c r="H313" t="n">
-        <v>6.27</v>
+        <v>4.07</v>
       </c>
       <c r="I313" t="n">
-        <v>11.17</v>
+        <v>13.06</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11086,29 +11086,29 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C314" t="n">
         <v>3</v>
       </c>
       <c r="D314" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E314" t="n">
-        <v>11.742</v>
+        <v>22.9</v>
       </c>
       <c r="F314" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G314" t="n">
-        <v>35.23</v>
+        <v>68.7</v>
       </c>
       <c r="H314" t="n">
-        <v>4.07</v>
+        <v>3.03</v>
       </c>
       <c r="I314" t="n">
-        <v>13.06</v>
+        <v>4.61</v>
       </c>
       <c r="J314" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E315" t="n">
-        <v>38.66</v>
+        <v>100.38</v>
       </c>
       <c r="F315" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G315" t="n">
-        <v>154.64</v>
+        <v>100.38</v>
       </c>
       <c r="H315" t="n">
-        <v>15.62</v>
+        <v>0.29</v>
       </c>
       <c r="I315" t="n">
-        <v>11.24</v>
+        <v>0.29</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D316" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E316" t="n">
-        <v>22.9</v>
+        <v>6.936</v>
       </c>
       <c r="F316" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G316" t="n">
-        <v>68.7</v>
+        <v>62.42</v>
       </c>
       <c r="H316" t="n">
-        <v>3.03</v>
+        <v>6.27</v>
       </c>
       <c r="I316" t="n">
-        <v>4.61</v>
+        <v>11.17</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D327" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E327" t="n">
-        <v>39.38</v>
+        <v>102.72</v>
       </c>
       <c r="F327" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G327" t="n">
-        <v>157.52</v>
+        <v>102.72</v>
       </c>
       <c r="H327" t="n">
-        <v>18.5</v>
+        <v>2.63</v>
       </c>
       <c r="I327" t="n">
-        <v>13.31</v>
+        <v>2.63</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C328" t="n">
         <v>3</v>
       </c>
       <c r="D328" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E328" t="n">
-        <v>22.83</v>
+        <v>11.708</v>
       </c>
       <c r="F328" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G328" t="n">
-        <v>68.48999999999999</v>
+        <v>35.12</v>
       </c>
       <c r="H328" t="n">
-        <v>2.82</v>
+        <v>3.96</v>
       </c>
       <c r="I328" t="n">
-        <v>4.29</v>
+        <v>12.71</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C330" t="n">
         <v>3</v>
       </c>
       <c r="D330" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E330" t="n">
-        <v>11.708</v>
+        <v>22.83</v>
       </c>
       <c r="F330" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G330" t="n">
-        <v>35.12</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H330" t="n">
-        <v>3.96</v>
+        <v>2.82</v>
       </c>
       <c r="I330" t="n">
-        <v>12.71</v>
+        <v>4.29</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D331" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E331" t="n">
-        <v>102.72</v>
+        <v>39.38</v>
       </c>
       <c r="F331" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G331" t="n">
-        <v>102.72</v>
+        <v>157.52</v>
       </c>
       <c r="H331" t="n">
-        <v>2.63</v>
+        <v>18.5</v>
       </c>
       <c r="I331" t="n">
-        <v>2.63</v>
+        <v>13.31</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D337" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E337" t="n">
-        <v>39.15</v>
+        <v>11.284</v>
       </c>
       <c r="F337" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G337" t="n">
-        <v>156.6</v>
+        <v>33.85</v>
       </c>
       <c r="H337" t="n">
-        <v>17.58</v>
+        <v>2.69</v>
       </c>
       <c r="I337" t="n">
-        <v>12.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D338" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E338" t="n">
-        <v>101.04</v>
+        <v>22.845</v>
       </c>
       <c r="F338" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G338" t="n">
-        <v>101.04</v>
+        <v>68.53</v>
       </c>
       <c r="H338" t="n">
-        <v>0.95</v>
+        <v>2.86</v>
       </c>
       <c r="I338" t="n">
-        <v>0.95</v>
+        <v>4.36</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D339" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E339" t="n">
-        <v>22.845</v>
+        <v>6.938</v>
       </c>
       <c r="F339" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G339" t="n">
-        <v>68.53</v>
+        <v>62.44</v>
       </c>
       <c r="H339" t="n">
-        <v>2.86</v>
+        <v>6.29</v>
       </c>
       <c r="I339" t="n">
-        <v>4.36</v>
+        <v>11.2</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D340" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E340" t="n">
-        <v>11.284</v>
+        <v>39.15</v>
       </c>
       <c r="F340" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G340" t="n">
-        <v>33.85</v>
+        <v>156.6</v>
       </c>
       <c r="H340" t="n">
-        <v>2.69</v>
+        <v>17.58</v>
       </c>
       <c r="I340" t="n">
-        <v>8.630000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E341" t="n">
-        <v>6.938</v>
+        <v>101.04</v>
       </c>
       <c r="F341" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G341" t="n">
-        <v>62.44</v>
+        <v>101.04</v>
       </c>
       <c r="H341" t="n">
-        <v>6.29</v>
+        <v>0.95</v>
       </c>
       <c r="I341" t="n">
-        <v>11.2</v>
+        <v>0.95</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C352" t="n">
         <v>3</v>
       </c>
       <c r="D352" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E352" t="n">
-        <v>22.75</v>
+        <v>11.186</v>
       </c>
       <c r="F352" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G352" t="n">
-        <v>68.25</v>
+        <v>33.56</v>
       </c>
       <c r="H352" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="I352" t="n">
-        <v>3.93</v>
+        <v>7.7</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E353" t="n">
-        <v>39.745</v>
+        <v>101.76</v>
       </c>
       <c r="F353" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G353" t="n">
-        <v>158.98</v>
+        <v>101.76</v>
       </c>
       <c r="H353" t="n">
-        <v>19.96</v>
+        <v>1.67</v>
       </c>
       <c r="I353" t="n">
-        <v>14.36</v>
+        <v>1.67</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D354" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E354" t="n">
-        <v>6.983</v>
+        <v>39.745</v>
       </c>
       <c r="F354" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G354" t="n">
-        <v>62.85</v>
+        <v>158.98</v>
       </c>
       <c r="H354" t="n">
-        <v>6.7</v>
+        <v>19.96</v>
       </c>
       <c r="I354" t="n">
-        <v>11.93</v>
+        <v>14.36</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D355" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E355" t="n">
-        <v>101.76</v>
+        <v>6.983</v>
       </c>
       <c r="F355" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G355" t="n">
-        <v>101.76</v>
+        <v>62.85</v>
       </c>
       <c r="H355" t="n">
-        <v>1.67</v>
+        <v>6.7</v>
       </c>
       <c r="I355" t="n">
-        <v>1.67</v>
+        <v>11.93</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C356" t="n">
         <v>3</v>
       </c>
       <c r="D356" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E356" t="n">
-        <v>11.186</v>
+        <v>22.75</v>
       </c>
       <c r="F356" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G356" t="n">
-        <v>33.56</v>
+        <v>68.25</v>
       </c>
       <c r="H356" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="I356" t="n">
-        <v>7.7</v>
+        <v>3.93</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12718,29 +12718,29 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D362" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E362" t="n">
-        <v>102.1</v>
+        <v>22.515</v>
       </c>
       <c r="F362" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G362" t="n">
-        <v>102.1</v>
+        <v>67.55</v>
       </c>
       <c r="H362" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="I362" t="n">
-        <v>2.01</v>
+        <v>2.86</v>
       </c>
       <c r="J362" t="n">
         <v>7.91</v>
@@ -12752,29 +12752,29 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D363" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E363" t="n">
-        <v>11.208</v>
+        <v>40.15</v>
       </c>
       <c r="F363" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G363" t="n">
-        <v>33.62</v>
+        <v>160.6</v>
       </c>
       <c r="H363" t="n">
-        <v>2.46</v>
+        <v>21.58</v>
       </c>
       <c r="I363" t="n">
-        <v>7.89</v>
+        <v>15.52</v>
       </c>
       <c r="J363" t="n">
         <v>7.91</v>
@@ -12786,29 +12786,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D364" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E364" t="n">
-        <v>40.15</v>
+        <v>6.972</v>
       </c>
       <c r="F364" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G364" t="n">
-        <v>160.6</v>
+        <v>62.75</v>
       </c>
       <c r="H364" t="n">
-        <v>21.58</v>
+        <v>6.6</v>
       </c>
       <c r="I364" t="n">
-        <v>15.52</v>
+        <v>11.75</v>
       </c>
       <c r="J364" t="n">
         <v>7.91</v>
@@ -12820,29 +12820,29 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D365" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E365" t="n">
-        <v>22.515</v>
+        <v>102.1</v>
       </c>
       <c r="F365" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G365" t="n">
-        <v>67.55</v>
+        <v>102.1</v>
       </c>
       <c r="H365" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="I365" t="n">
-        <v>2.86</v>
+        <v>2.01</v>
       </c>
       <c r="J365" t="n">
         <v>7.91</v>
@@ -12854,29 +12854,29 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D366" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E366" t="n">
-        <v>6.972</v>
+        <v>11.208</v>
       </c>
       <c r="F366" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G366" t="n">
-        <v>62.75</v>
+        <v>33.62</v>
       </c>
       <c r="H366" t="n">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="I366" t="n">
-        <v>11.75</v>
+        <v>7.89</v>
       </c>
       <c r="J366" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E377" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F377" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G377" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H377" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D378" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E378" t="n">
-        <v>22.13</v>
+        <v>39.57</v>
       </c>
       <c r="F378" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G378" t="n">
-        <v>66.39</v>
+        <v>158.28</v>
       </c>
       <c r="H378" t="n">
-        <v>0.72</v>
+        <v>19.26</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1</v>
+        <v>13.85</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C379" t="n">
         <v>3</v>
       </c>
       <c r="D379" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E379" t="n">
-        <v>10.962</v>
+        <v>22.13</v>
       </c>
       <c r="F379" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G379" t="n">
-        <v>32.89</v>
+        <v>66.39</v>
       </c>
       <c r="H379" t="n">
-        <v>1.73</v>
+        <v>0.72</v>
       </c>
       <c r="I379" t="n">
-        <v>5.55</v>
+        <v>1.1</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E380" t="n">
-        <v>101.88</v>
+        <v>6.941</v>
       </c>
       <c r="F380" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G380" t="n">
-        <v>101.88</v>
+        <v>62.47</v>
       </c>
       <c r="H380" t="n">
-        <v>1.79</v>
+        <v>6.32</v>
       </c>
       <c r="I380" t="n">
-        <v>1.79</v>
+        <v>11.26</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D381" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E381" t="n">
-        <v>39.57</v>
+        <v>10.962</v>
       </c>
       <c r="F381" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G381" t="n">
-        <v>158.28</v>
+        <v>32.89</v>
       </c>
       <c r="H381" t="n">
-        <v>19.26</v>
+        <v>1.73</v>
       </c>
       <c r="I381" t="n">
-        <v>13.85</v>
+        <v>5.55</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D387" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E387" t="n">
-        <v>100.76</v>
+        <v>38.375</v>
       </c>
       <c r="F387" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G387" t="n">
-        <v>100.76</v>
+        <v>153.5</v>
       </c>
       <c r="H387" t="n">
-        <v>0.67</v>
+        <v>14.48</v>
       </c>
       <c r="I387" t="n">
-        <v>0.67</v>
+        <v>10.42</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D388" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E388" t="n">
-        <v>21.83</v>
+        <v>6.893</v>
       </c>
       <c r="F388" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G388" t="n">
-        <v>65.48999999999999</v>
+        <v>62.04</v>
       </c>
       <c r="H388" t="n">
-        <v>-0.18</v>
+        <v>5.89</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.27</v>
+        <v>10.49</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D390" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E390" t="n">
-        <v>6.893</v>
+        <v>100.76</v>
       </c>
       <c r="F390" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G390" t="n">
-        <v>62.04</v>
+        <v>100.76</v>
       </c>
       <c r="H390" t="n">
-        <v>5.89</v>
+        <v>0.67</v>
       </c>
       <c r="I390" t="n">
-        <v>10.49</v>
+        <v>0.67</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D391" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E391" t="n">
-        <v>38.375</v>
+        <v>21.83</v>
       </c>
       <c r="F391" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G391" t="n">
-        <v>153.5</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H391" t="n">
-        <v>14.48</v>
+        <v>-0.18</v>
       </c>
       <c r="I391" t="n">
-        <v>10.42</v>
+        <v>-0.27</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D397" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E397" t="n">
-        <v>11.202</v>
+        <v>102.82</v>
       </c>
       <c r="F397" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G397" t="n">
-        <v>33.61</v>
+        <v>102.82</v>
       </c>
       <c r="H397" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="I397" t="n">
-        <v>7.86</v>
+        <v>2.73</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E398" t="n">
-        <v>39.435</v>
+        <v>22.145</v>
       </c>
       <c r="F398" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G398" t="n">
-        <v>157.74</v>
+        <v>66.44</v>
       </c>
       <c r="H398" t="n">
-        <v>18.72</v>
+        <v>0.77</v>
       </c>
       <c r="I398" t="n">
-        <v>13.47</v>
+        <v>1.17</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D399" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E399" t="n">
-        <v>22.145</v>
+        <v>6.982</v>
       </c>
       <c r="F399" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G399" t="n">
-        <v>66.44</v>
+        <v>62.84</v>
       </c>
       <c r="H399" t="n">
-        <v>0.77</v>
+        <v>6.69</v>
       </c>
       <c r="I399" t="n">
-        <v>1.17</v>
+        <v>11.91</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D400" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E400" t="n">
-        <v>102.82</v>
+        <v>11.202</v>
       </c>
       <c r="F400" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G400" t="n">
-        <v>102.82</v>
+        <v>33.61</v>
       </c>
       <c r="H400" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="I400" t="n">
-        <v>2.73</v>
+        <v>7.86</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,31 +14044,201 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>4</v>
+      </c>
+      <c r="D401" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E401" t="n">
+        <v>39.435</v>
+      </c>
+      <c r="F401" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G401" t="n">
+        <v>157.74</v>
+      </c>
+      <c r="H401" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="I401" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="J401" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E402" t="n">
+        <v>103.08</v>
+      </c>
+      <c r="F402" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G402" t="n">
+        <v>103.08</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I402" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J402" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>3</v>
+      </c>
+      <c r="D403" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E403" t="n">
+        <v>11.086</v>
+      </c>
+      <c r="F403" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G403" t="n">
+        <v>33.26</v>
+      </c>
+      <c r="H403" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I403" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="J403" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>4</v>
+      </c>
+      <c r="D404" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E404" t="n">
+        <v>39.395</v>
+      </c>
+      <c r="F404" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G404" t="n">
+        <v>157.58</v>
+      </c>
+      <c r="H404" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="I404" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="J404" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3</v>
+      </c>
+      <c r="D405" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E405" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="F405" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G405" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J405" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C401" t="n">
+      <c r="C406" t="n">
         <v>9</v>
       </c>
-      <c r="D401" t="n">
+      <c r="D406" t="n">
         <v>6.239</v>
       </c>
-      <c r="E401" t="n">
-        <v>6.982</v>
-      </c>
-      <c r="F401" t="n">
+      <c r="E406" t="n">
+        <v>6.965</v>
+      </c>
+      <c r="F406" t="n">
         <v>56.15</v>
       </c>
-      <c r="G401" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="H401" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="I401" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="J401" t="n">
+      <c r="G406" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="H406" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I406" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="J406" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J406"/>
+  <dimension ref="A1:J411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E12" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F12" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G12" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E13" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F13" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G13" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H13" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I13" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E14" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F14" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G14" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H14" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I14" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E15" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F15" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G15" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H15" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E16" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F16" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G16" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H16" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E27" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F27" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G27" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E28" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F28" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G28" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E29" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F29" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G29" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H29" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E30" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F30" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G30" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H30" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E31" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F31" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G31" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H31" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I31" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E37" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F37" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G37" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H37" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I37" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E38" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F38" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G38" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H38" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I38" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E39" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F39" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G39" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H39" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E40" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F40" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G40" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E41" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F41" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G41" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H41" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I41" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E52" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F52" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G52" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H52" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I52" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E53" t="n">
-        <v>10.702</v>
+        <v>6.629</v>
       </c>
       <c r="F53" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G53" t="n">
-        <v>32.11</v>
+        <v>59.66</v>
       </c>
       <c r="H53" t="n">
-        <v>0.95</v>
+        <v>3.51</v>
       </c>
       <c r="I53" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E54" t="n">
-        <v>21.703</v>
+        <v>38.544</v>
       </c>
       <c r="F54" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G54" t="n">
-        <v>65.11</v>
+        <v>154.18</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5600000000000001</v>
+        <v>15.16</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.85</v>
+        <v>10.9</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E55" t="n">
-        <v>6.629</v>
+        <v>10.702</v>
       </c>
       <c r="F55" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G55" t="n">
-        <v>59.66</v>
+        <v>32.11</v>
       </c>
       <c r="H55" t="n">
-        <v>3.51</v>
+        <v>0.95</v>
       </c>
       <c r="I55" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E56" t="n">
-        <v>100.34</v>
+        <v>21.703</v>
       </c>
       <c r="F56" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G56" t="n">
-        <v>100.34</v>
+        <v>65.11</v>
       </c>
       <c r="H56" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E62" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F62" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G62" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H62" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E63" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F63" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G63" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H63" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I63" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E64" t="n">
-        <v>6.817</v>
+        <v>41.064</v>
       </c>
       <c r="F64" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G64" t="n">
-        <v>61.35</v>
+        <v>164.26</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>25.24</v>
       </c>
       <c r="I64" t="n">
-        <v>9.26</v>
+        <v>18.16</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E65" t="n">
-        <v>10.712</v>
+        <v>22.7</v>
       </c>
       <c r="F65" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G65" t="n">
-        <v>32.14</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>0.98</v>
+        <v>2.43</v>
       </c>
       <c r="I65" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E66" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F66" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G66" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H66" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I66" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E67" t="n">
-        <v>10.796</v>
+        <v>40.567</v>
       </c>
       <c r="F67" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G67" t="n">
-        <v>32.39</v>
+        <v>162.27</v>
       </c>
       <c r="H67" t="n">
-        <v>1.23</v>
+        <v>23.25</v>
       </c>
       <c r="I67" t="n">
-        <v>3.95</v>
+        <v>16.72</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E68" t="n">
-        <v>40.567</v>
+        <v>104.58</v>
       </c>
       <c r="F68" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G68" t="n">
-        <v>162.27</v>
+        <v>104.58</v>
       </c>
       <c r="H68" t="n">
-        <v>23.25</v>
+        <v>4.49</v>
       </c>
       <c r="I68" t="n">
-        <v>16.72</v>
+        <v>4.49</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E69" t="n">
-        <v>104.58</v>
+        <v>6.807</v>
       </c>
       <c r="F69" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G69" t="n">
-        <v>104.58</v>
+        <v>61.26</v>
       </c>
       <c r="H69" t="n">
-        <v>4.49</v>
+        <v>5.11</v>
       </c>
       <c r="I69" t="n">
-        <v>4.49</v>
+        <v>9.1</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E70" t="n">
-        <v>6.807</v>
+        <v>22.797</v>
       </c>
       <c r="F70" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G70" t="n">
-        <v>61.26</v>
+        <v>68.39</v>
       </c>
       <c r="H70" t="n">
-        <v>5.11</v>
+        <v>2.72</v>
       </c>
       <c r="I70" t="n">
-        <v>9.1</v>
+        <v>4.14</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E71" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F71" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G71" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H71" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I71" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E77" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F77" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G77" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H77" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I77" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E78" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F78" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G78" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H78" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I78" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E80" t="n">
-        <v>23.4</v>
+        <v>6.836</v>
       </c>
       <c r="F80" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G80" t="n">
-        <v>70.2</v>
+        <v>61.52</v>
       </c>
       <c r="H80" t="n">
-        <v>4.53</v>
+        <v>5.37</v>
       </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>9.56</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E81" t="n">
-        <v>42.25</v>
+        <v>105.8</v>
       </c>
       <c r="F81" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G81" t="n">
-        <v>169</v>
+        <v>105.8</v>
       </c>
       <c r="H81" t="n">
-        <v>29.98</v>
+        <v>5.71</v>
       </c>
       <c r="I81" t="n">
-        <v>21.57</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E87" t="n">
-        <v>10.852</v>
+        <v>6.856</v>
       </c>
       <c r="F87" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G87" t="n">
-        <v>32.56</v>
+        <v>61.7</v>
       </c>
       <c r="H87" t="n">
-        <v>1.4</v>
+        <v>5.55</v>
       </c>
       <c r="I87" t="n">
-        <v>4.49</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E88" t="n">
-        <v>23.32</v>
+        <v>43.005</v>
       </c>
       <c r="F88" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G88" t="n">
-        <v>69.95999999999999</v>
+        <v>172.02</v>
       </c>
       <c r="H88" t="n">
-        <v>4.29</v>
+        <v>33</v>
       </c>
       <c r="I88" t="n">
-        <v>6.53</v>
+        <v>23.74</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E89" t="n">
-        <v>43.005</v>
+        <v>106.28</v>
       </c>
       <c r="F89" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G89" t="n">
-        <v>172.02</v>
+        <v>106.28</v>
       </c>
       <c r="H89" t="n">
-        <v>33</v>
+        <v>6.19</v>
       </c>
       <c r="I89" t="n">
-        <v>23.74</v>
+        <v>6.18</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E90" t="n">
-        <v>6.856</v>
+        <v>10.852</v>
       </c>
       <c r="F90" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G90" t="n">
-        <v>61.7</v>
+        <v>32.56</v>
       </c>
       <c r="H90" t="n">
-        <v>5.55</v>
+        <v>1.4</v>
       </c>
       <c r="I90" t="n">
-        <v>9.880000000000001</v>
+        <v>4.49</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E91" t="n">
-        <v>106.28</v>
+        <v>23.32</v>
       </c>
       <c r="F91" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G91" t="n">
-        <v>106.28</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>6.19</v>
+        <v>4.29</v>
       </c>
       <c r="I91" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E102" t="n">
-        <v>40.97</v>
+        <v>6.804</v>
       </c>
       <c r="F102" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G102" t="n">
-        <v>163.88</v>
+        <v>61.24</v>
       </c>
       <c r="H102" t="n">
-        <v>24.86</v>
+        <v>5.09</v>
       </c>
       <c r="I102" t="n">
-        <v>17.88</v>
+        <v>9.07</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E103" t="n">
-        <v>23.29</v>
+        <v>103.46</v>
       </c>
       <c r="F103" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G103" t="n">
-        <v>69.87</v>
+        <v>103.46</v>
       </c>
       <c r="H103" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="I103" t="n">
-        <v>6.4</v>
+        <v>3.37</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E104" t="n">
-        <v>10.556</v>
+        <v>40.97</v>
       </c>
       <c r="F104" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G104" t="n">
-        <v>31.67</v>
+        <v>163.88</v>
       </c>
       <c r="H104" t="n">
-        <v>0.51</v>
+        <v>24.86</v>
       </c>
       <c r="I104" t="n">
-        <v>1.64</v>
+        <v>17.88</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E105" t="n">
-        <v>103.46</v>
+        <v>23.29</v>
       </c>
       <c r="F105" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G105" t="n">
-        <v>103.46</v>
+        <v>69.87</v>
       </c>
       <c r="H105" t="n">
-        <v>3.37</v>
+        <v>4.2</v>
       </c>
       <c r="I105" t="n">
-        <v>3.37</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4014,29 +4014,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E106" t="n">
-        <v>6.804</v>
+        <v>10.556</v>
       </c>
       <c r="F106" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G106" t="n">
-        <v>61.24</v>
+        <v>31.67</v>
       </c>
       <c r="H106" t="n">
-        <v>5.09</v>
+        <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>9.07</v>
+        <v>1.64</v>
       </c>
       <c r="J106" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E117" t="n">
-        <v>6.861</v>
+        <v>41</v>
       </c>
       <c r="F117" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G117" t="n">
-        <v>61.75</v>
+        <v>164</v>
       </c>
       <c r="H117" t="n">
-        <v>5.6</v>
+        <v>24.98</v>
       </c>
       <c r="I117" t="n">
-        <v>9.970000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E118" t="n">
-        <v>10.756</v>
+        <v>23.145</v>
       </c>
       <c r="F118" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G118" t="n">
-        <v>32.27</v>
+        <v>69.44</v>
       </c>
       <c r="H118" t="n">
-        <v>1.11</v>
+        <v>3.77</v>
       </c>
       <c r="I118" t="n">
-        <v>3.56</v>
+        <v>5.74</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E119" t="n">
-        <v>105.96</v>
+        <v>6.861</v>
       </c>
       <c r="F119" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G119" t="n">
-        <v>105.96</v>
+        <v>61.75</v>
       </c>
       <c r="H119" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="I119" t="n">
-        <v>5.86</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E120" t="n">
-        <v>23.145</v>
+        <v>10.756</v>
       </c>
       <c r="F120" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G120" t="n">
-        <v>69.44</v>
+        <v>32.27</v>
       </c>
       <c r="H120" t="n">
-        <v>3.77</v>
+        <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>5.74</v>
+        <v>3.56</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
+        <v>105.96</v>
       </c>
       <c r="F121" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G121" t="n">
-        <v>164</v>
+        <v>105.96</v>
       </c>
       <c r="H121" t="n">
-        <v>24.98</v>
+        <v>5.87</v>
       </c>
       <c r="I121" t="n">
-        <v>17.97</v>
+        <v>5.86</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E122" t="n">
-        <v>106</v>
+        <v>40.395</v>
       </c>
       <c r="F122" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G122" t="n">
-        <v>106</v>
+        <v>161.58</v>
       </c>
       <c r="H122" t="n">
-        <v>5.91</v>
+        <v>22.56</v>
       </c>
       <c r="I122" t="n">
-        <v>5.9</v>
+        <v>16.23</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E123" t="n">
-        <v>23.165</v>
+        <v>106</v>
       </c>
       <c r="F123" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G123" t="n">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="H123" t="n">
-        <v>3.83</v>
+        <v>5.91</v>
       </c>
       <c r="I123" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4626,29 +4626,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E124" t="n">
-        <v>6.901</v>
+        <v>23.165</v>
       </c>
       <c r="F124" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G124" t="n">
-        <v>62.11</v>
+        <v>69.5</v>
       </c>
       <c r="H124" t="n">
-        <v>5.96</v>
+        <v>3.83</v>
       </c>
       <c r="I124" t="n">
-        <v>10.61</v>
+        <v>5.83</v>
       </c>
       <c r="J124" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E125" t="n">
-        <v>11.038</v>
+        <v>6.901</v>
       </c>
       <c r="F125" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G125" t="n">
-        <v>33.11</v>
+        <v>62.11</v>
       </c>
       <c r="H125" t="n">
-        <v>1.95</v>
+        <v>5.96</v>
       </c>
       <c r="I125" t="n">
-        <v>6.26</v>
+        <v>10.61</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E126" t="n">
-        <v>40.395</v>
+        <v>11.038</v>
       </c>
       <c r="F126" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G126" t="n">
-        <v>161.58</v>
+        <v>33.11</v>
       </c>
       <c r="H126" t="n">
-        <v>22.56</v>
+        <v>1.95</v>
       </c>
       <c r="I126" t="n">
-        <v>16.23</v>
+        <v>6.26</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E127" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F127" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G127" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H127" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I127" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E128" t="n">
-        <v>6.868</v>
+        <v>11.458</v>
       </c>
       <c r="F128" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G128" t="n">
-        <v>61.81</v>
+        <v>34.37</v>
       </c>
       <c r="H128" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="I128" t="n">
-        <v>10.08</v>
+        <v>10.3</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D130" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E130" t="n">
-        <v>11.458</v>
+        <v>6.868</v>
       </c>
       <c r="F130" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G130" t="n">
-        <v>34.37</v>
+        <v>61.81</v>
       </c>
       <c r="H130" t="n">
-        <v>3.21</v>
+        <v>5.66</v>
       </c>
       <c r="I130" t="n">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E131" t="n">
-        <v>39.36</v>
+        <v>23.17</v>
       </c>
       <c r="F131" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G131" t="n">
-        <v>157.44</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>18.42</v>
+        <v>3.84</v>
       </c>
       <c r="I131" t="n">
-        <v>13.25</v>
+        <v>5.85</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E137" t="n">
-        <v>23.3</v>
+        <v>104.76</v>
       </c>
       <c r="F137" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G137" t="n">
-        <v>69.90000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="H137" t="n">
-        <v>4.23</v>
+        <v>4.67</v>
       </c>
       <c r="I137" t="n">
-        <v>6.44</v>
+        <v>4.67</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D138" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E138" t="n">
-        <v>40.61</v>
+        <v>6.927</v>
       </c>
       <c r="F138" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G138" t="n">
-        <v>162.44</v>
+        <v>62.34</v>
       </c>
       <c r="H138" t="n">
-        <v>23.42</v>
+        <v>6.19</v>
       </c>
       <c r="I138" t="n">
-        <v>16.85</v>
+        <v>11.02</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E139" t="n">
-        <v>6.927</v>
+        <v>11.728</v>
       </c>
       <c r="F139" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G139" t="n">
-        <v>62.34</v>
+        <v>35.18</v>
       </c>
       <c r="H139" t="n">
-        <v>6.19</v>
+        <v>4.02</v>
       </c>
       <c r="I139" t="n">
-        <v>11.02</v>
+        <v>12.9</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E140" t="n">
-        <v>104.76</v>
+        <v>23.3</v>
       </c>
       <c r="F140" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G140" t="n">
-        <v>104.76</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>4.67</v>
+        <v>4.23</v>
       </c>
       <c r="I140" t="n">
-        <v>4.67</v>
+        <v>6.44</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E141" t="n">
-        <v>11.728</v>
+        <v>40.61</v>
       </c>
       <c r="F141" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G141" t="n">
-        <v>35.18</v>
+        <v>162.44</v>
       </c>
       <c r="H141" t="n">
-        <v>4.02</v>
+        <v>23.42</v>
       </c>
       <c r="I141" t="n">
-        <v>12.9</v>
+        <v>16.85</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E152" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F152" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G152" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H152" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I152" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D153" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E153" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F153" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G153" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H153" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I153" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E155" t="n">
-        <v>6.893</v>
+        <v>39.915</v>
       </c>
       <c r="F155" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G155" t="n">
-        <v>62.04</v>
+        <v>159.66</v>
       </c>
       <c r="H155" t="n">
-        <v>5.89</v>
+        <v>20.64</v>
       </c>
       <c r="I155" t="n">
-        <v>10.49</v>
+        <v>14.85</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E156" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F156" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G156" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H156" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I156" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E162" t="n">
-        <v>38.845</v>
+        <v>10.748</v>
       </c>
       <c r="F162" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G162" t="n">
-        <v>155.38</v>
+        <v>32.24</v>
       </c>
       <c r="H162" t="n">
-        <v>16.36</v>
+        <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>11.77</v>
+        <v>3.47</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D163" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E163" t="n">
-        <v>103.84</v>
+        <v>6.927</v>
       </c>
       <c r="F163" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G163" t="n">
-        <v>103.84</v>
+        <v>62.34</v>
       </c>
       <c r="H163" t="n">
-        <v>3.75</v>
+        <v>6.19</v>
       </c>
       <c r="I163" t="n">
-        <v>3.75</v>
+        <v>11.02</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E164" t="n">
-        <v>6.927</v>
+        <v>23.01</v>
       </c>
       <c r="F164" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G164" t="n">
-        <v>62.34</v>
+        <v>69.03</v>
       </c>
       <c r="H164" t="n">
-        <v>6.19</v>
+        <v>3.36</v>
       </c>
       <c r="I164" t="n">
-        <v>11.02</v>
+        <v>5.12</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E165" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F165" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G165" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H165" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I165" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E166" t="n">
-        <v>23.01</v>
+        <v>103.84</v>
       </c>
       <c r="F166" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G166" t="n">
-        <v>69.03</v>
+        <v>103.84</v>
       </c>
       <c r="H166" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="I166" t="n">
-        <v>5.12</v>
+        <v>3.75</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E167" t="n">
-        <v>22.92</v>
+        <v>38.98</v>
       </c>
       <c r="F167" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G167" t="n">
-        <v>68.76000000000001</v>
+        <v>155.92</v>
       </c>
       <c r="H167" t="n">
-        <v>3.09</v>
+        <v>16.9</v>
       </c>
       <c r="I167" t="n">
-        <v>4.71</v>
+        <v>12.16</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D168" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E168" t="n">
-        <v>38.98</v>
+        <v>6.911</v>
       </c>
       <c r="F168" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G168" t="n">
-        <v>155.92</v>
+        <v>62.2</v>
       </c>
       <c r="H168" t="n">
-        <v>16.9</v>
+        <v>6.05</v>
       </c>
       <c r="I168" t="n">
-        <v>12.16</v>
+        <v>10.77</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E169" t="n">
-        <v>6.911</v>
+        <v>103.98</v>
       </c>
       <c r="F169" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G169" t="n">
-        <v>62.2</v>
+        <v>103.98</v>
       </c>
       <c r="H169" t="n">
-        <v>6.05</v>
+        <v>3.89</v>
       </c>
       <c r="I169" t="n">
-        <v>10.77</v>
+        <v>3.89</v>
       </c>
       <c r="J169" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E170" t="n">
-        <v>103.98</v>
+        <v>10.726</v>
       </c>
       <c r="F170" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G170" t="n">
-        <v>103.98</v>
+        <v>32.18</v>
       </c>
       <c r="H170" t="n">
-        <v>3.89</v>
+        <v>1.02</v>
       </c>
       <c r="I170" t="n">
-        <v>3.89</v>
+        <v>3.27</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E171" t="n">
-        <v>10.726</v>
+        <v>22.92</v>
       </c>
       <c r="F171" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G171" t="n">
-        <v>32.18</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H171" t="n">
-        <v>1.02</v>
+        <v>3.09</v>
       </c>
       <c r="I171" t="n">
-        <v>3.27</v>
+        <v>4.71</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E177" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F177" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G177" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H177" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I177" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E178" t="n">
-        <v>102.54</v>
+        <v>22.95</v>
       </c>
       <c r="F178" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G178" t="n">
-        <v>102.54</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="I178" t="n">
-        <v>2.45</v>
+        <v>4.84</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E180" t="n">
-        <v>38.245</v>
+        <v>6.922</v>
       </c>
       <c r="F180" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G180" t="n">
-        <v>152.98</v>
+        <v>62.3</v>
       </c>
       <c r="H180" t="n">
-        <v>13.96</v>
+        <v>6.15</v>
       </c>
       <c r="I180" t="n">
-        <v>10.04</v>
+        <v>10.95</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E181" t="n">
-        <v>22.95</v>
+        <v>102.54</v>
       </c>
       <c r="F181" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G181" t="n">
-        <v>68.84999999999999</v>
+        <v>102.54</v>
       </c>
       <c r="H181" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="I181" t="n">
-        <v>4.84</v>
+        <v>2.45</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E187" t="n">
-        <v>101.44</v>
+        <v>22.845</v>
       </c>
       <c r="F187" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G187" t="n">
-        <v>101.44</v>
+        <v>68.53</v>
       </c>
       <c r="H187" t="n">
-        <v>1.35</v>
+        <v>2.86</v>
       </c>
       <c r="I187" t="n">
-        <v>1.35</v>
+        <v>4.36</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E188" t="n">
-        <v>6.862</v>
+        <v>10.708</v>
       </c>
       <c r="F188" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G188" t="n">
-        <v>61.76</v>
+        <v>32.12</v>
       </c>
       <c r="H188" t="n">
-        <v>5.61</v>
+        <v>0.96</v>
       </c>
       <c r="I188" t="n">
-        <v>9.99</v>
+        <v>3.08</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E189" t="n">
-        <v>10.708</v>
+        <v>37.85</v>
       </c>
       <c r="F189" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G189" t="n">
-        <v>32.12</v>
+        <v>151.4</v>
       </c>
       <c r="H189" t="n">
-        <v>0.96</v>
+        <v>12.38</v>
       </c>
       <c r="I189" t="n">
-        <v>3.08</v>
+        <v>8.91</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E190" t="n">
-        <v>22.845</v>
+        <v>101.44</v>
       </c>
       <c r="F190" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G190" t="n">
-        <v>68.53</v>
+        <v>101.44</v>
       </c>
       <c r="H190" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>4.36</v>
+        <v>1.35</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D191" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E191" t="n">
-        <v>37.85</v>
+        <v>6.862</v>
       </c>
       <c r="F191" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G191" t="n">
-        <v>151.4</v>
+        <v>61.76</v>
       </c>
       <c r="H191" t="n">
-        <v>12.38</v>
+        <v>5.61</v>
       </c>
       <c r="I191" t="n">
-        <v>8.91</v>
+        <v>9.99</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E202" t="n">
-        <v>38.04</v>
+        <v>100.08</v>
       </c>
       <c r="F202" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G202" t="n">
-        <v>152.16</v>
+        <v>100.08</v>
       </c>
       <c r="H202" t="n">
-        <v>13.14</v>
+        <v>-0.01</v>
       </c>
       <c r="I202" t="n">
-        <v>9.449999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C203" t="n">
         <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E203" t="n">
-        <v>11.044</v>
+        <v>22.4</v>
       </c>
       <c r="F203" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G203" t="n">
-        <v>33.13</v>
+        <v>67.2</v>
       </c>
       <c r="H203" t="n">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="I203" t="n">
-        <v>6.32</v>
+        <v>2.33</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7346,29 +7346,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D204" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E204" t="n">
-        <v>22.4</v>
+        <v>6.822</v>
       </c>
       <c r="F204" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G204" t="n">
-        <v>67.2</v>
+        <v>61.4</v>
       </c>
       <c r="H204" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="I204" t="n">
-        <v>2.33</v>
+        <v>9.35</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E205" t="n">
-        <v>100.08</v>
+        <v>38.04</v>
       </c>
       <c r="F205" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G205" t="n">
-        <v>100.08</v>
+        <v>152.16</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.01</v>
+        <v>13.14</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.01</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D206" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E206" t="n">
-        <v>6.822</v>
+        <v>11.044</v>
       </c>
       <c r="F206" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G206" t="n">
-        <v>61.4</v>
+        <v>33.13</v>
       </c>
       <c r="H206" t="n">
-        <v>5.25</v>
+        <v>1.97</v>
       </c>
       <c r="I206" t="n">
-        <v>9.35</v>
+        <v>6.32</v>
       </c>
       <c r="J206" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E217" t="n">
-        <v>11.546</v>
+        <v>23.175</v>
       </c>
       <c r="F217" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G217" t="n">
-        <v>34.64</v>
+        <v>69.53</v>
       </c>
       <c r="H217" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="I217" t="n">
-        <v>11.17</v>
+        <v>5.88</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E218" t="n">
-        <v>6.864</v>
+        <v>98.02</v>
       </c>
       <c r="F218" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G218" t="n">
-        <v>61.78</v>
+        <v>98.02</v>
       </c>
       <c r="H218" t="n">
-        <v>5.63</v>
+        <v>-2.07</v>
       </c>
       <c r="I218" t="n">
-        <v>10.03</v>
+        <v>-2.07</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E219" t="n">
-        <v>36.75</v>
+        <v>11.546</v>
       </c>
       <c r="F219" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G219" t="n">
-        <v>147</v>
+        <v>34.64</v>
       </c>
       <c r="H219" t="n">
-        <v>7.98</v>
+        <v>3.48</v>
       </c>
       <c r="I219" t="n">
-        <v>5.74</v>
+        <v>11.17</v>
       </c>
       <c r="J219" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E220" t="n">
-        <v>98.02</v>
+        <v>6.864</v>
       </c>
       <c r="F220" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G220" t="n">
-        <v>98.02</v>
+        <v>61.78</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.07</v>
+        <v>5.63</v>
       </c>
       <c r="I220" t="n">
-        <v>-2.07</v>
+        <v>10.03</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E221" t="n">
-        <v>23.175</v>
+        <v>36.75</v>
       </c>
       <c r="F221" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G221" t="n">
-        <v>69.53</v>
+        <v>147</v>
       </c>
       <c r="H221" t="n">
-        <v>3.86</v>
+        <v>7.98</v>
       </c>
       <c r="I221" t="n">
-        <v>5.88</v>
+        <v>5.74</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E227" t="n">
-        <v>6.779</v>
+        <v>11.512</v>
       </c>
       <c r="F227" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G227" t="n">
-        <v>61.01</v>
+        <v>34.54</v>
       </c>
       <c r="H227" t="n">
-        <v>4.86</v>
+        <v>3.38</v>
       </c>
       <c r="I227" t="n">
-        <v>8.66</v>
+        <v>10.85</v>
       </c>
       <c r="J227" t="n">
         <v>7.91</v>
@@ -8162,29 +8162,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E228" t="n">
-        <v>23.07</v>
+        <v>97.34</v>
       </c>
       <c r="F228" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G228" t="n">
-        <v>69.20999999999999</v>
+        <v>97.34</v>
       </c>
       <c r="H228" t="n">
-        <v>3.54</v>
+        <v>-2.75</v>
       </c>
       <c r="I228" t="n">
-        <v>5.39</v>
+        <v>-2.75</v>
       </c>
       <c r="J228" t="n">
         <v>7.91</v>
@@ -8196,29 +8196,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D229" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E229" t="n">
-        <v>97.34</v>
+        <v>36.64</v>
       </c>
       <c r="F229" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G229" t="n">
-        <v>97.34</v>
+        <v>146.56</v>
       </c>
       <c r="H229" t="n">
-        <v>-2.75</v>
+        <v>7.54</v>
       </c>
       <c r="I229" t="n">
-        <v>-2.75</v>
+        <v>5.42</v>
       </c>
       <c r="J229" t="n">
         <v>7.91</v>
@@ -8230,29 +8230,29 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D230" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E230" t="n">
-        <v>36.64</v>
+        <v>6.779</v>
       </c>
       <c r="F230" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G230" t="n">
-        <v>146.56</v>
+        <v>61.01</v>
       </c>
       <c r="H230" t="n">
-        <v>7.54</v>
+        <v>4.86</v>
       </c>
       <c r="I230" t="n">
-        <v>5.42</v>
+        <v>8.66</v>
       </c>
       <c r="J230" t="n">
         <v>7.91</v>
@@ -8264,29 +8264,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>3</v>
       </c>
       <c r="D231" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E231" t="n">
-        <v>11.512</v>
+        <v>23.07</v>
       </c>
       <c r="F231" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G231" t="n">
-        <v>34.54</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H231" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="I231" t="n">
-        <v>10.85</v>
+        <v>5.39</v>
       </c>
       <c r="J231" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C237" t="n">
         <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E237" t="n">
-        <v>11.842</v>
+        <v>23.245</v>
       </c>
       <c r="F237" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G237" t="n">
-        <v>35.53</v>
+        <v>69.73</v>
       </c>
       <c r="H237" t="n">
-        <v>4.37</v>
+        <v>4.06</v>
       </c>
       <c r="I237" t="n">
-        <v>14.02</v>
+        <v>6.18</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E238" t="n">
-        <v>6.914</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F238" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G238" t="n">
-        <v>62.23</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H238" t="n">
-        <v>6.08</v>
+        <v>-0.24</v>
       </c>
       <c r="I238" t="n">
-        <v>10.83</v>
+        <v>-0.24</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8536,29 +8536,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D239" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E239" t="n">
-        <v>99.84999999999999</v>
+        <v>37.315</v>
       </c>
       <c r="F239" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G239" t="n">
-        <v>99.84999999999999</v>
+        <v>149.26</v>
       </c>
       <c r="H239" t="n">
-        <v>-0.24</v>
+        <v>10.24</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.24</v>
+        <v>7.37</v>
       </c>
       <c r="J239" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D240" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E240" t="n">
-        <v>37.315</v>
+        <v>11.842</v>
       </c>
       <c r="F240" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G240" t="n">
-        <v>149.26</v>
+        <v>35.53</v>
       </c>
       <c r="H240" t="n">
-        <v>10.24</v>
+        <v>4.37</v>
       </c>
       <c r="I240" t="n">
-        <v>7.37</v>
+        <v>14.02</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D241" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E241" t="n">
-        <v>23.245</v>
+        <v>6.914</v>
       </c>
       <c r="F241" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G241" t="n">
-        <v>69.73</v>
+        <v>62.23</v>
       </c>
       <c r="H241" t="n">
-        <v>4.06</v>
+        <v>6.08</v>
       </c>
       <c r="I241" t="n">
-        <v>6.18</v>
+        <v>10.83</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D247" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E247" t="n">
-        <v>7.032</v>
+        <v>12.18</v>
       </c>
       <c r="F247" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G247" t="n">
-        <v>63.29</v>
+        <v>36.54</v>
       </c>
       <c r="H247" t="n">
-        <v>7.14</v>
+        <v>5.38</v>
       </c>
       <c r="I247" t="n">
-        <v>12.72</v>
+        <v>17.27</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E248" t="n">
-        <v>103.2</v>
+        <v>7.032</v>
       </c>
       <c r="F248" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G248" t="n">
-        <v>103.2</v>
+        <v>63.29</v>
       </c>
       <c r="H248" t="n">
-        <v>3.11</v>
+        <v>7.14</v>
       </c>
       <c r="I248" t="n">
-        <v>3.11</v>
+        <v>12.72</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8876,29 +8876,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E249" t="n">
-        <v>38.435</v>
+        <v>103.2</v>
       </c>
       <c r="F249" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G249" t="n">
-        <v>153.74</v>
+        <v>103.2</v>
       </c>
       <c r="H249" t="n">
-        <v>14.72</v>
+        <v>3.11</v>
       </c>
       <c r="I249" t="n">
-        <v>10.59</v>
+        <v>3.11</v>
       </c>
       <c r="J249" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D250" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E250" t="n">
-        <v>12.18</v>
+        <v>38.435</v>
       </c>
       <c r="F250" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G250" t="n">
-        <v>36.54</v>
+        <v>153.74</v>
       </c>
       <c r="H250" t="n">
-        <v>5.38</v>
+        <v>14.72</v>
       </c>
       <c r="I250" t="n">
-        <v>17.27</v>
+        <v>10.59</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D252" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E252" t="n">
-        <v>7.05</v>
+        <v>23.315</v>
       </c>
       <c r="F252" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G252" t="n">
-        <v>63.45</v>
+        <v>69.95</v>
       </c>
       <c r="H252" t="n">
-        <v>7.3</v>
+        <v>4.28</v>
       </c>
       <c r="I252" t="n">
-        <v>13</v>
+        <v>6.52</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D253" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E253" t="n">
-        <v>38.095</v>
+        <v>12.128</v>
       </c>
       <c r="F253" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G253" t="n">
-        <v>152.38</v>
+        <v>36.38</v>
       </c>
       <c r="H253" t="n">
-        <v>13.36</v>
+        <v>5.22</v>
       </c>
       <c r="I253" t="n">
-        <v>9.609999999999999</v>
+        <v>16.75</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D254" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E254" t="n">
-        <v>12.128</v>
+        <v>103.18</v>
       </c>
       <c r="F254" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G254" t="n">
-        <v>36.38</v>
+        <v>103.18</v>
       </c>
       <c r="H254" t="n">
-        <v>5.22</v>
+        <v>3.09</v>
       </c>
       <c r="I254" t="n">
-        <v>16.75</v>
+        <v>3.09</v>
       </c>
       <c r="J254" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D255" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E255" t="n">
-        <v>23.315</v>
+        <v>7.05</v>
       </c>
       <c r="F255" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G255" t="n">
-        <v>69.95</v>
+        <v>63.45</v>
       </c>
       <c r="H255" t="n">
-        <v>4.28</v>
+        <v>7.3</v>
       </c>
       <c r="I255" t="n">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D256" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E256" t="n">
-        <v>103.18</v>
+        <v>38.095</v>
       </c>
       <c r="F256" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G256" t="n">
-        <v>103.18</v>
+        <v>152.38</v>
       </c>
       <c r="H256" t="n">
-        <v>3.09</v>
+        <v>13.36</v>
       </c>
       <c r="I256" t="n">
-        <v>3.09</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C257" t="n">
         <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E257" t="n">
-        <v>12.232</v>
+        <v>23.2</v>
       </c>
       <c r="F257" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G257" t="n">
-        <v>36.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>5.54</v>
+        <v>3.93</v>
       </c>
       <c r="I257" t="n">
-        <v>17.78</v>
+        <v>5.98</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E258" t="n">
-        <v>37.84</v>
+        <v>103.02</v>
       </c>
       <c r="F258" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G258" t="n">
-        <v>151.36</v>
+        <v>103.02</v>
       </c>
       <c r="H258" t="n">
-        <v>12.34</v>
+        <v>2.93</v>
       </c>
       <c r="I258" t="n">
-        <v>8.880000000000001</v>
+        <v>2.93</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D259" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E259" t="n">
-        <v>7.056</v>
+        <v>12.232</v>
       </c>
       <c r="F259" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G259" t="n">
-        <v>63.5</v>
+        <v>36.7</v>
       </c>
       <c r="H259" t="n">
-        <v>7.35</v>
+        <v>5.54</v>
       </c>
       <c r="I259" t="n">
-        <v>13.09</v>
+        <v>17.78</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D260" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E260" t="n">
-        <v>103.02</v>
+        <v>37.84</v>
       </c>
       <c r="F260" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G260" t="n">
-        <v>103.02</v>
+        <v>151.36</v>
       </c>
       <c r="H260" t="n">
-        <v>2.93</v>
+        <v>12.34</v>
       </c>
       <c r="I260" t="n">
-        <v>2.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E261" t="n">
-        <v>23.2</v>
+        <v>7.056</v>
       </c>
       <c r="F261" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G261" t="n">
-        <v>69.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="H261" t="n">
-        <v>3.93</v>
+        <v>7.35</v>
       </c>
       <c r="I261" t="n">
-        <v>5.98</v>
+        <v>13.09</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9488,29 +9488,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E267" t="n">
-        <v>38.865</v>
+        <v>103.36</v>
       </c>
       <c r="F267" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G267" t="n">
-        <v>155.46</v>
+        <v>103.36</v>
       </c>
       <c r="H267" t="n">
-        <v>16.44</v>
+        <v>3.27</v>
       </c>
       <c r="I267" t="n">
-        <v>11.83</v>
+        <v>3.27</v>
       </c>
       <c r="J267" t="n">
         <v>7.91</v>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C268" t="n">
         <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E268" t="n">
-        <v>12.388</v>
+        <v>23.12</v>
       </c>
       <c r="F268" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G268" t="n">
-        <v>37.16</v>
+        <v>69.36</v>
       </c>
       <c r="H268" t="n">
-        <v>6</v>
+        <v>3.69</v>
       </c>
       <c r="I268" t="n">
-        <v>19.26</v>
+        <v>5.62</v>
       </c>
       <c r="J268" t="n">
         <v>7.91</v>
@@ -9590,29 +9590,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C270" t="n">
         <v>3</v>
       </c>
       <c r="D270" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E270" t="n">
-        <v>23.12</v>
+        <v>12.388</v>
       </c>
       <c r="F270" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G270" t="n">
-        <v>69.36</v>
+        <v>37.16</v>
       </c>
       <c r="H270" t="n">
-        <v>3.69</v>
+        <v>6</v>
       </c>
       <c r="I270" t="n">
-        <v>5.62</v>
+        <v>19.26</v>
       </c>
       <c r="J270" t="n">
         <v>7.91</v>
@@ -9624,29 +9624,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D271" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E271" t="n">
-        <v>103.36</v>
+        <v>38.865</v>
       </c>
       <c r="F271" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G271" t="n">
-        <v>103.36</v>
+        <v>155.46</v>
       </c>
       <c r="H271" t="n">
-        <v>3.27</v>
+        <v>16.44</v>
       </c>
       <c r="I271" t="n">
-        <v>3.27</v>
+        <v>11.83</v>
       </c>
       <c r="J271" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C277" t="n">
         <v>3</v>
       </c>
       <c r="D277" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E277" t="n">
-        <v>22.96</v>
+        <v>12.492</v>
       </c>
       <c r="F277" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G277" t="n">
-        <v>68.88</v>
+        <v>37.48</v>
       </c>
       <c r="H277" t="n">
-        <v>3.21</v>
+        <v>6.32</v>
       </c>
       <c r="I277" t="n">
-        <v>4.89</v>
+        <v>20.28</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E278" t="n">
-        <v>7.063</v>
+        <v>103.76</v>
       </c>
       <c r="F278" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G278" t="n">
-        <v>63.57</v>
+        <v>103.76</v>
       </c>
       <c r="H278" t="n">
-        <v>7.42</v>
+        <v>3.67</v>
       </c>
       <c r="I278" t="n">
-        <v>13.21</v>
+        <v>3.67</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9896,29 +9896,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D279" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E279" t="n">
-        <v>103.76</v>
+        <v>38.985</v>
       </c>
       <c r="F279" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G279" t="n">
-        <v>103.76</v>
+        <v>155.94</v>
       </c>
       <c r="H279" t="n">
-        <v>3.67</v>
+        <v>16.92</v>
       </c>
       <c r="I279" t="n">
-        <v>3.67</v>
+        <v>12.17</v>
       </c>
       <c r="J279" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C280" t="n">
         <v>3</v>
       </c>
       <c r="D280" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E280" t="n">
-        <v>12.492</v>
+        <v>22.96</v>
       </c>
       <c r="F280" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G280" t="n">
-        <v>37.48</v>
+        <v>68.88</v>
       </c>
       <c r="H280" t="n">
-        <v>6.32</v>
+        <v>3.21</v>
       </c>
       <c r="I280" t="n">
-        <v>20.28</v>
+        <v>4.89</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D281" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E281" t="n">
-        <v>38.985</v>
+        <v>7.063</v>
       </c>
       <c r="F281" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G281" t="n">
-        <v>155.94</v>
+        <v>63.57</v>
       </c>
       <c r="H281" t="n">
-        <v>16.92</v>
+        <v>7.42</v>
       </c>
       <c r="I281" t="n">
-        <v>12.17</v>
+        <v>13.21</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D282" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E282" t="n">
-        <v>104.46</v>
+        <v>7.054</v>
       </c>
       <c r="F282" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G282" t="n">
-        <v>104.46</v>
+        <v>63.49</v>
       </c>
       <c r="H282" t="n">
-        <v>4.37</v>
+        <v>7.34</v>
       </c>
       <c r="I282" t="n">
-        <v>4.37</v>
+        <v>13.07</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D283" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E283" t="n">
-        <v>12.468</v>
+        <v>39.745</v>
       </c>
       <c r="F283" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G283" t="n">
-        <v>37.4</v>
+        <v>158.98</v>
       </c>
       <c r="H283" t="n">
-        <v>6.24</v>
+        <v>19.96</v>
       </c>
       <c r="I283" t="n">
-        <v>20.03</v>
+        <v>14.36</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D285" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E285" t="n">
-        <v>39.745</v>
+        <v>12.468</v>
       </c>
       <c r="F285" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G285" t="n">
-        <v>158.98</v>
+        <v>37.4</v>
       </c>
       <c r="H285" t="n">
-        <v>19.96</v>
+        <v>6.24</v>
       </c>
       <c r="I285" t="n">
-        <v>14.36</v>
+        <v>20.03</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E286" t="n">
-        <v>7.054</v>
+        <v>104.46</v>
       </c>
       <c r="F286" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G286" t="n">
-        <v>63.49</v>
+        <v>104.46</v>
       </c>
       <c r="H286" t="n">
-        <v>7.34</v>
+        <v>4.37</v>
       </c>
       <c r="I286" t="n">
-        <v>13.07</v>
+        <v>4.37</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10338,29 +10338,29 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D292" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E292" t="n">
-        <v>38.26</v>
+        <v>6.96</v>
       </c>
       <c r="F292" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G292" t="n">
-        <v>153.04</v>
+        <v>62.64</v>
       </c>
       <c r="H292" t="n">
-        <v>14.02</v>
+        <v>6.49</v>
       </c>
       <c r="I292" t="n">
-        <v>10.08</v>
+        <v>11.56</v>
       </c>
       <c r="J292" t="n">
         <v>7.91</v>
@@ -10372,29 +10372,29 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E293" t="n">
-        <v>12.096</v>
+        <v>101.5</v>
       </c>
       <c r="F293" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G293" t="n">
-        <v>36.29</v>
+        <v>101.5</v>
       </c>
       <c r="H293" t="n">
-        <v>5.13</v>
+        <v>1.41</v>
       </c>
       <c r="I293" t="n">
-        <v>16.46</v>
+        <v>1.41</v>
       </c>
       <c r="J293" t="n">
         <v>7.91</v>
@@ -10406,29 +10406,29 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D294" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E294" t="n">
-        <v>22.685</v>
+        <v>38.26</v>
       </c>
       <c r="F294" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G294" t="n">
-        <v>68.05</v>
+        <v>153.04</v>
       </c>
       <c r="H294" t="n">
-        <v>2.38</v>
+        <v>14.02</v>
       </c>
       <c r="I294" t="n">
-        <v>3.62</v>
+        <v>10.08</v>
       </c>
       <c r="J294" t="n">
         <v>7.91</v>
@@ -10440,29 +10440,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D295" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E295" t="n">
-        <v>6.96</v>
+        <v>12.096</v>
       </c>
       <c r="F295" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G295" t="n">
-        <v>62.64</v>
+        <v>36.29</v>
       </c>
       <c r="H295" t="n">
-        <v>6.49</v>
+        <v>5.13</v>
       </c>
       <c r="I295" t="n">
-        <v>11.56</v>
+        <v>16.46</v>
       </c>
       <c r="J295" t="n">
         <v>7.91</v>
@@ -10474,29 +10474,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D296" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E296" t="n">
-        <v>101.5</v>
+        <v>22.685</v>
       </c>
       <c r="F296" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G296" t="n">
-        <v>101.5</v>
+        <v>68.05</v>
       </c>
       <c r="H296" t="n">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="I296" t="n">
-        <v>1.41</v>
+        <v>3.62</v>
       </c>
       <c r="J296" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D307" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E307" t="n">
-        <v>38.055</v>
+        <v>11.686</v>
       </c>
       <c r="F307" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G307" t="n">
-        <v>152.22</v>
+        <v>35.06</v>
       </c>
       <c r="H307" t="n">
-        <v>13.2</v>
+        <v>3.9</v>
       </c>
       <c r="I307" t="n">
-        <v>9.5</v>
+        <v>12.52</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D308" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E308" t="n">
-        <v>6.916</v>
+        <v>22.555</v>
       </c>
       <c r="F308" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G308" t="n">
-        <v>62.24</v>
+        <v>67.66</v>
       </c>
       <c r="H308" t="n">
-        <v>6.09</v>
+        <v>1.99</v>
       </c>
       <c r="I308" t="n">
-        <v>10.85</v>
+        <v>3.03</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10916,29 +10916,29 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D309" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E309" t="n">
-        <v>99.95</v>
+        <v>6.916</v>
       </c>
       <c r="F309" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G309" t="n">
-        <v>99.95</v>
+        <v>62.24</v>
       </c>
       <c r="H309" t="n">
-        <v>-0.14</v>
+        <v>6.09</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.14</v>
+        <v>10.85</v>
       </c>
       <c r="J309" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D310" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E310" t="n">
-        <v>11.686</v>
+        <v>38.055</v>
       </c>
       <c r="F310" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G310" t="n">
-        <v>35.06</v>
+        <v>152.22</v>
       </c>
       <c r="H310" t="n">
-        <v>3.9</v>
+        <v>13.2</v>
       </c>
       <c r="I310" t="n">
-        <v>12.52</v>
+        <v>9.5</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E311" t="n">
-        <v>22.555</v>
+        <v>99.95</v>
       </c>
       <c r="F311" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G311" t="n">
-        <v>67.66</v>
+        <v>99.95</v>
       </c>
       <c r="H311" t="n">
-        <v>1.99</v>
+        <v>-0.14</v>
       </c>
       <c r="I311" t="n">
-        <v>3.03</v>
+        <v>-0.14</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11188,29 +11188,29 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D317" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E317" t="n">
-        <v>22.77</v>
+        <v>38.91</v>
       </c>
       <c r="F317" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G317" t="n">
-        <v>68.31</v>
+        <v>155.64</v>
       </c>
       <c r="H317" t="n">
-        <v>2.64</v>
+        <v>16.62</v>
       </c>
       <c r="I317" t="n">
-        <v>4.02</v>
+        <v>11.96</v>
       </c>
       <c r="J317" t="n">
         <v>7.91</v>
@@ -11222,29 +11222,29 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E318" t="n">
-        <v>11.822</v>
+        <v>100.48</v>
       </c>
       <c r="F318" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G318" t="n">
-        <v>35.47</v>
+        <v>100.48</v>
       </c>
       <c r="H318" t="n">
-        <v>4.31</v>
+        <v>0.39</v>
       </c>
       <c r="I318" t="n">
-        <v>13.83</v>
+        <v>0.39</v>
       </c>
       <c r="J318" t="n">
         <v>7.91</v>
@@ -11256,29 +11256,29 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D319" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E319" t="n">
-        <v>100.48</v>
+        <v>6.943</v>
       </c>
       <c r="F319" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G319" t="n">
-        <v>100.48</v>
+        <v>62.49</v>
       </c>
       <c r="H319" t="n">
-        <v>0.39</v>
+        <v>6.34</v>
       </c>
       <c r="I319" t="n">
-        <v>0.39</v>
+        <v>11.29</v>
       </c>
       <c r="J319" t="n">
         <v>7.91</v>
@@ -11290,29 +11290,29 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D320" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E320" t="n">
-        <v>38.91</v>
+        <v>22.77</v>
       </c>
       <c r="F320" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G320" t="n">
-        <v>155.64</v>
+        <v>68.31</v>
       </c>
       <c r="H320" t="n">
-        <v>16.62</v>
+        <v>2.64</v>
       </c>
       <c r="I320" t="n">
-        <v>11.96</v>
+        <v>4.02</v>
       </c>
       <c r="J320" t="n">
         <v>7.91</v>
@@ -11324,29 +11324,29 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D321" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E321" t="n">
-        <v>6.943</v>
+        <v>11.822</v>
       </c>
       <c r="F321" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G321" t="n">
-        <v>62.49</v>
+        <v>35.47</v>
       </c>
       <c r="H321" t="n">
-        <v>6.34</v>
+        <v>4.31</v>
       </c>
       <c r="I321" t="n">
-        <v>11.29</v>
+        <v>13.83</v>
       </c>
       <c r="J321" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D322" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E322" t="n">
-        <v>39.07</v>
+        <v>6.967</v>
       </c>
       <c r="F322" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G322" t="n">
-        <v>156.28</v>
+        <v>62.7</v>
       </c>
       <c r="H322" t="n">
-        <v>17.26</v>
+        <v>6.55</v>
       </c>
       <c r="I322" t="n">
-        <v>12.42</v>
+        <v>11.67</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D323" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E323" t="n">
-        <v>6.967</v>
+        <v>22.745</v>
       </c>
       <c r="F323" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G323" t="n">
-        <v>62.7</v>
+        <v>68.23</v>
       </c>
       <c r="H323" t="n">
-        <v>6.55</v>
+        <v>2.56</v>
       </c>
       <c r="I323" t="n">
-        <v>11.67</v>
+        <v>3.9</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11426,29 +11426,29 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C324" t="n">
         <v>3</v>
       </c>
       <c r="D324" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E324" t="n">
-        <v>22.745</v>
+        <v>11.81</v>
       </c>
       <c r="F324" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G324" t="n">
-        <v>68.23</v>
+        <v>35.43</v>
       </c>
       <c r="H324" t="n">
-        <v>2.56</v>
+        <v>4.27</v>
       </c>
       <c r="I324" t="n">
-        <v>3.9</v>
+        <v>13.7</v>
       </c>
       <c r="J324" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E325" t="n">
-        <v>11.81</v>
+        <v>101.7</v>
       </c>
       <c r="F325" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G325" t="n">
-        <v>35.43</v>
+        <v>101.7</v>
       </c>
       <c r="H325" t="n">
-        <v>4.27</v>
+        <v>1.61</v>
       </c>
       <c r="I325" t="n">
-        <v>13.7</v>
+        <v>1.61</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D326" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E326" t="n">
-        <v>101.7</v>
+        <v>39.07</v>
       </c>
       <c r="F326" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G326" t="n">
-        <v>101.7</v>
+        <v>156.28</v>
       </c>
       <c r="H326" t="n">
-        <v>1.61</v>
+        <v>17.26</v>
       </c>
       <c r="I326" t="n">
-        <v>1.61</v>
+        <v>12.42</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11698,29 +11698,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D332" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E332" t="n">
-        <v>38.98</v>
+        <v>6.948</v>
       </c>
       <c r="F332" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G332" t="n">
-        <v>155.92</v>
+        <v>62.53</v>
       </c>
       <c r="H332" t="n">
-        <v>16.9</v>
+        <v>6.38</v>
       </c>
       <c r="I332" t="n">
-        <v>12.16</v>
+        <v>11.36</v>
       </c>
       <c r="J332" t="n">
         <v>7.91</v>
@@ -11732,29 +11732,29 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C333" t="n">
         <v>3</v>
       </c>
       <c r="D333" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E333" t="n">
-        <v>11.5</v>
+        <v>22.745</v>
       </c>
       <c r="F333" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G333" t="n">
-        <v>34.5</v>
+        <v>68.23</v>
       </c>
       <c r="H333" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="I333" t="n">
-        <v>10.72</v>
+        <v>3.9</v>
       </c>
       <c r="J333" t="n">
         <v>7.91</v>
@@ -11800,29 +11800,29 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D335" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E335" t="n">
-        <v>6.948</v>
+        <v>38.98</v>
       </c>
       <c r="F335" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G335" t="n">
-        <v>62.53</v>
+        <v>155.92</v>
       </c>
       <c r="H335" t="n">
-        <v>6.38</v>
+        <v>16.9</v>
       </c>
       <c r="I335" t="n">
-        <v>11.36</v>
+        <v>12.16</v>
       </c>
       <c r="J335" t="n">
         <v>7.91</v>
@@ -11834,29 +11834,29 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C336" t="n">
         <v>3</v>
       </c>
       <c r="D336" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E336" t="n">
-        <v>22.745</v>
+        <v>11.5</v>
       </c>
       <c r="F336" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G336" t="n">
-        <v>68.23</v>
+        <v>34.5</v>
       </c>
       <c r="H336" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="I336" t="n">
-        <v>3.9</v>
+        <v>10.72</v>
       </c>
       <c r="J336" t="n">
         <v>7.91</v>
@@ -12038,29 +12038,29 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E342" t="n">
-        <v>22.89</v>
+        <v>100.84</v>
       </c>
       <c r="F342" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G342" t="n">
-        <v>68.67</v>
+        <v>100.84</v>
       </c>
       <c r="H342" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="I342" t="n">
-        <v>4.57</v>
+        <v>0.75</v>
       </c>
       <c r="J342" t="n">
         <v>7.91</v>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D343" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E343" t="n">
-        <v>6.95</v>
+        <v>11.264</v>
       </c>
       <c r="F343" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G343" t="n">
-        <v>62.55</v>
+        <v>33.79</v>
       </c>
       <c r="H343" t="n">
-        <v>6.4</v>
+        <v>2.63</v>
       </c>
       <c r="I343" t="n">
-        <v>11.4</v>
+        <v>8.44</v>
       </c>
       <c r="J343" t="n">
         <v>7.91</v>
@@ -12106,29 +12106,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D344" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E344" t="n">
-        <v>11.264</v>
+        <v>38.99</v>
       </c>
       <c r="F344" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G344" t="n">
-        <v>33.79</v>
+        <v>155.96</v>
       </c>
       <c r="H344" t="n">
-        <v>2.63</v>
+        <v>16.94</v>
       </c>
       <c r="I344" t="n">
-        <v>8.44</v>
+        <v>12.19</v>
       </c>
       <c r="J344" t="n">
         <v>7.91</v>
@@ -12140,29 +12140,29 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D345" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E345" t="n">
-        <v>100.84</v>
+        <v>22.89</v>
       </c>
       <c r="F345" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G345" t="n">
-        <v>100.84</v>
+        <v>68.67</v>
       </c>
       <c r="H345" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="I345" t="n">
-        <v>0.75</v>
+        <v>4.57</v>
       </c>
       <c r="J345" t="n">
         <v>7.91</v>
@@ -12174,29 +12174,29 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D346" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E346" t="n">
-        <v>38.99</v>
+        <v>6.95</v>
       </c>
       <c r="F346" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G346" t="n">
-        <v>155.96</v>
+        <v>62.55</v>
       </c>
       <c r="H346" t="n">
-        <v>16.94</v>
+        <v>6.4</v>
       </c>
       <c r="I346" t="n">
-        <v>12.19</v>
+        <v>11.4</v>
       </c>
       <c r="J346" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D357" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E357" t="n">
-        <v>11.13</v>
+        <v>40.07</v>
       </c>
       <c r="F357" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G357" t="n">
-        <v>33.39</v>
+        <v>160.28</v>
       </c>
       <c r="H357" t="n">
-        <v>2.23</v>
+        <v>21.26</v>
       </c>
       <c r="I357" t="n">
-        <v>7.16</v>
+        <v>15.29</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E358" t="n">
-        <v>6.978</v>
+        <v>101.98</v>
       </c>
       <c r="F358" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G358" t="n">
-        <v>62.8</v>
+        <v>101.98</v>
       </c>
       <c r="H358" t="n">
-        <v>6.65</v>
+        <v>1.89</v>
       </c>
       <c r="I358" t="n">
-        <v>11.84</v>
+        <v>1.89</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D359" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E359" t="n">
-        <v>101.98</v>
+        <v>22.5</v>
       </c>
       <c r="F359" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G359" t="n">
-        <v>101.98</v>
+        <v>67.5</v>
       </c>
       <c r="H359" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I359" t="n">
-        <v>1.89</v>
+        <v>2.79</v>
       </c>
       <c r="J359" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C360" t="n">
         <v>3</v>
       </c>
       <c r="D360" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E360" t="n">
-        <v>22.5</v>
+        <v>11.13</v>
       </c>
       <c r="F360" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G360" t="n">
-        <v>67.5</v>
+        <v>33.39</v>
       </c>
       <c r="H360" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="I360" t="n">
-        <v>2.79</v>
+        <v>7.16</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D361" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E361" t="n">
-        <v>40.07</v>
+        <v>6.978</v>
       </c>
       <c r="F361" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G361" t="n">
-        <v>160.28</v>
+        <v>62.8</v>
       </c>
       <c r="H361" t="n">
-        <v>21.26</v>
+        <v>6.65</v>
       </c>
       <c r="I361" t="n">
-        <v>15.29</v>
+        <v>11.84</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D367" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E367" t="n">
-        <v>101.5</v>
+        <v>39.935</v>
       </c>
       <c r="F367" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G367" t="n">
-        <v>101.5</v>
+        <v>159.74</v>
       </c>
       <c r="H367" t="n">
-        <v>1.41</v>
+        <v>20.72</v>
       </c>
       <c r="I367" t="n">
-        <v>1.41</v>
+        <v>14.9</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C368" t="n">
         <v>3</v>
       </c>
       <c r="D368" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E368" t="n">
-        <v>10.91</v>
+        <v>22.275</v>
       </c>
       <c r="F368" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G368" t="n">
-        <v>32.73</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H368" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="I368" t="n">
-        <v>5.04</v>
+        <v>1.75</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12956,29 +12956,29 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D369" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E369" t="n">
-        <v>22.275</v>
+        <v>6.91</v>
       </c>
       <c r="F369" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G369" t="n">
-        <v>66.81999999999999</v>
+        <v>62.19</v>
       </c>
       <c r="H369" t="n">
-        <v>1.15</v>
+        <v>6.04</v>
       </c>
       <c r="I369" t="n">
-        <v>1.75</v>
+        <v>10.76</v>
       </c>
       <c r="J369" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E370" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F370" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G370" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H370" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D371" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E371" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
       <c r="F371" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G371" t="n">
-        <v>62.19</v>
+        <v>32.73</v>
       </c>
       <c r="H371" t="n">
-        <v>6.04</v>
+        <v>1.57</v>
       </c>
       <c r="I371" t="n">
-        <v>10.76</v>
+        <v>5.04</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13398,29 +13398,29 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D382" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E382" t="n">
-        <v>101.3</v>
+        <v>6.931</v>
       </c>
       <c r="F382" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G382" t="n">
-        <v>101.3</v>
+        <v>62.38</v>
       </c>
       <c r="H382" t="n">
-        <v>1.21</v>
+        <v>6.23</v>
       </c>
       <c r="I382" t="n">
-        <v>1.21</v>
+        <v>11.1</v>
       </c>
       <c r="J382" t="n">
         <v>7.91</v>
@@ -13432,29 +13432,29 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D383" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E383" t="n">
-        <v>10.88</v>
+        <v>38.585</v>
       </c>
       <c r="F383" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G383" t="n">
-        <v>32.64</v>
+        <v>154.34</v>
       </c>
       <c r="H383" t="n">
-        <v>1.48</v>
+        <v>15.32</v>
       </c>
       <c r="I383" t="n">
-        <v>4.75</v>
+        <v>11.02</v>
       </c>
       <c r="J383" t="n">
         <v>7.91</v>
@@ -13466,29 +13466,29 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E384" t="n">
-        <v>38.585</v>
+        <v>22.145</v>
       </c>
       <c r="F384" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G384" t="n">
-        <v>154.34</v>
+        <v>66.44</v>
       </c>
       <c r="H384" t="n">
-        <v>15.32</v>
+        <v>0.77</v>
       </c>
       <c r="I384" t="n">
-        <v>11.02</v>
+        <v>1.17</v>
       </c>
       <c r="J384" t="n">
         <v>7.91</v>
@@ -13500,29 +13500,29 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D385" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E385" t="n">
-        <v>22.145</v>
+        <v>101.3</v>
       </c>
       <c r="F385" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G385" t="n">
-        <v>66.44</v>
+        <v>101.3</v>
       </c>
       <c r="H385" t="n">
-        <v>0.77</v>
+        <v>1.21</v>
       </c>
       <c r="I385" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="J385" t="n">
         <v>7.91</v>
@@ -13534,29 +13534,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D386" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E386" t="n">
-        <v>6.931</v>
+        <v>10.88</v>
       </c>
       <c r="F386" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G386" t="n">
-        <v>62.38</v>
+        <v>32.64</v>
       </c>
       <c r="H386" t="n">
-        <v>6.23</v>
+        <v>1.48</v>
       </c>
       <c r="I386" t="n">
-        <v>11.1</v>
+        <v>4.75</v>
       </c>
       <c r="J386" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D397" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E397" t="n">
-        <v>102.82</v>
+        <v>39.435</v>
       </c>
       <c r="F397" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G397" t="n">
-        <v>102.82</v>
+        <v>157.74</v>
       </c>
       <c r="H397" t="n">
-        <v>2.73</v>
+        <v>18.72</v>
       </c>
       <c r="I397" t="n">
-        <v>2.73</v>
+        <v>13.47</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C398" t="n">
         <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E398" t="n">
-        <v>22.145</v>
+        <v>11.202</v>
       </c>
       <c r="F398" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G398" t="n">
-        <v>66.44</v>
+        <v>33.61</v>
       </c>
       <c r="H398" t="n">
-        <v>0.77</v>
+        <v>2.45</v>
       </c>
       <c r="I398" t="n">
-        <v>1.17</v>
+        <v>7.86</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D399" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E399" t="n">
-        <v>6.982</v>
+        <v>22.145</v>
       </c>
       <c r="F399" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G399" t="n">
-        <v>62.84</v>
+        <v>66.44</v>
       </c>
       <c r="H399" t="n">
-        <v>6.69</v>
+        <v>0.77</v>
       </c>
       <c r="I399" t="n">
-        <v>11.91</v>
+        <v>1.17</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D400" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E400" t="n">
-        <v>11.202</v>
+        <v>102.82</v>
       </c>
       <c r="F400" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G400" t="n">
-        <v>33.61</v>
+        <v>102.82</v>
       </c>
       <c r="H400" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="I400" t="n">
-        <v>7.86</v>
+        <v>2.73</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D401" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E401" t="n">
-        <v>39.435</v>
+        <v>6.982</v>
       </c>
       <c r="F401" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G401" t="n">
-        <v>157.74</v>
+        <v>62.84</v>
       </c>
       <c r="H401" t="n">
-        <v>18.72</v>
+        <v>6.69</v>
       </c>
       <c r="I401" t="n">
-        <v>13.47</v>
+        <v>11.91</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14239,6 +14239,176 @@
         <v>11.65</v>
       </c>
       <c r="J406" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>3</v>
+      </c>
+      <c r="D407" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E407" t="n">
+        <v>11.232</v>
+      </c>
+      <c r="F407" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G407" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="H407" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I407" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="J407" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>4</v>
+      </c>
+      <c r="D408" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E408" t="n">
+        <v>40.695</v>
+      </c>
+      <c r="F408" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G408" t="n">
+        <v>162.78</v>
+      </c>
+      <c r="H408" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="I408" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J408" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>3</v>
+      </c>
+      <c r="D409" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E409" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F409" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G409" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="H409" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I409" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J409" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>1</v>
+      </c>
+      <c r="D410" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E410" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="F410" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G410" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="H410" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="I410" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J410" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>9</v>
+      </c>
+      <c r="D411" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E411" t="n">
+        <v>7.049</v>
+      </c>
+      <c r="F411" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G411" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="H411" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="I411" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="J411" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J411"/>
+  <dimension ref="A1:J416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E12" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F12" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G12" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H12" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E13" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F13" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G13" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H13" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I13" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E14" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F14" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G14" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H14" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E15" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F15" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G15" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E16" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F16" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G16" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I16" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E27" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F27" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G27" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H27" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I27" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E28" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F28" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G28" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H28" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E29" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F29" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G29" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E30" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F30" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G30" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E31" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F31" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G31" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H31" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E37" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F37" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G37" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E38" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F38" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G38" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H38" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E39" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F39" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G39" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H39" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I39" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E40" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F40" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G40" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H40" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I40" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E41" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F41" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G41" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H41" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I41" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E52" t="n">
-        <v>100.34</v>
+        <v>21.703</v>
       </c>
       <c r="F52" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G52" t="n">
-        <v>100.34</v>
+        <v>65.11</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E53" t="n">
-        <v>6.629</v>
+        <v>10.702</v>
       </c>
       <c r="F53" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G53" t="n">
-        <v>59.66</v>
+        <v>32.11</v>
       </c>
       <c r="H53" t="n">
-        <v>3.51</v>
+        <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E54" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F54" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G54" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H54" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I54" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E55" t="n">
-        <v>10.702</v>
+        <v>6.629</v>
       </c>
       <c r="F55" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G55" t="n">
-        <v>32.11</v>
+        <v>59.66</v>
       </c>
       <c r="H55" t="n">
-        <v>0.95</v>
+        <v>3.51</v>
       </c>
       <c r="I55" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E56" t="n">
-        <v>21.703</v>
+        <v>38.544</v>
       </c>
       <c r="F56" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G56" t="n">
-        <v>65.11</v>
+        <v>154.18</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5600000000000001</v>
+        <v>15.16</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.85</v>
+        <v>10.9</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E62" t="n">
-        <v>10.712</v>
+        <v>22.7</v>
       </c>
       <c r="F62" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G62" t="n">
-        <v>32.14</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>0.98</v>
+        <v>2.43</v>
       </c>
       <c r="I62" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E63" t="n">
-        <v>6.817</v>
+        <v>41.064</v>
       </c>
       <c r="F63" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G63" t="n">
-        <v>61.35</v>
+        <v>164.26</v>
       </c>
       <c r="H63" t="n">
-        <v>5.2</v>
+        <v>25.24</v>
       </c>
       <c r="I63" t="n">
-        <v>9.26</v>
+        <v>18.16</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E64" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F64" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G64" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H64" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I64" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E65" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F65" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G65" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H65" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E66" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F66" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G66" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H66" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E67" t="n">
-        <v>40.567</v>
+        <v>104.58</v>
       </c>
       <c r="F67" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G67" t="n">
-        <v>162.27</v>
+        <v>104.58</v>
       </c>
       <c r="H67" t="n">
-        <v>23.25</v>
+        <v>4.49</v>
       </c>
       <c r="I67" t="n">
-        <v>16.72</v>
+        <v>4.49</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E68" t="n">
-        <v>104.58</v>
+        <v>6.807</v>
       </c>
       <c r="F68" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G68" t="n">
-        <v>104.58</v>
+        <v>61.26</v>
       </c>
       <c r="H68" t="n">
-        <v>4.49</v>
+        <v>5.11</v>
       </c>
       <c r="I68" t="n">
-        <v>4.49</v>
+        <v>9.1</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E69" t="n">
-        <v>6.807</v>
+        <v>22.797</v>
       </c>
       <c r="F69" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G69" t="n">
-        <v>61.26</v>
+        <v>68.39</v>
       </c>
       <c r="H69" t="n">
-        <v>5.11</v>
+        <v>2.72</v>
       </c>
       <c r="I69" t="n">
-        <v>9.1</v>
+        <v>4.14</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E70" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F70" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G70" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H70" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I70" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E71" t="n">
-        <v>10.796</v>
+        <v>40.567</v>
       </c>
       <c r="F71" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G71" t="n">
-        <v>32.39</v>
+        <v>162.27</v>
       </c>
       <c r="H71" t="n">
-        <v>1.23</v>
+        <v>23.25</v>
       </c>
       <c r="I71" t="n">
-        <v>3.95</v>
+        <v>16.72</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E77" t="n">
-        <v>23.4</v>
+        <v>6.836</v>
       </c>
       <c r="F77" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G77" t="n">
-        <v>70.2</v>
+        <v>61.52</v>
       </c>
       <c r="H77" t="n">
-        <v>4.53</v>
+        <v>5.37</v>
       </c>
       <c r="I77" t="n">
-        <v>6.9</v>
+        <v>9.56</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E78" t="n">
-        <v>42.25</v>
+        <v>105.8</v>
       </c>
       <c r="F78" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G78" t="n">
-        <v>169</v>
+        <v>105.8</v>
       </c>
       <c r="H78" t="n">
-        <v>29.98</v>
+        <v>5.71</v>
       </c>
       <c r="I78" t="n">
-        <v>21.57</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E80" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F80" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G80" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H80" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I80" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E81" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F81" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G81" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H81" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E87" t="n">
-        <v>6.856</v>
+        <v>10.852</v>
       </c>
       <c r="F87" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G87" t="n">
-        <v>61.7</v>
+        <v>32.56</v>
       </c>
       <c r="H87" t="n">
-        <v>5.55</v>
+        <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>9.880000000000001</v>
+        <v>4.49</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E88" t="n">
-        <v>43.005</v>
+        <v>106.28</v>
       </c>
       <c r="F88" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G88" t="n">
-        <v>172.02</v>
+        <v>106.28</v>
       </c>
       <c r="H88" t="n">
-        <v>33</v>
+        <v>6.19</v>
       </c>
       <c r="I88" t="n">
-        <v>23.74</v>
+        <v>6.18</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E89" t="n">
-        <v>106.28</v>
+        <v>23.32</v>
       </c>
       <c r="F89" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G89" t="n">
-        <v>106.28</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>6.19</v>
+        <v>4.29</v>
       </c>
       <c r="I89" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E90" t="n">
-        <v>10.852</v>
+        <v>6.856</v>
       </c>
       <c r="F90" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G90" t="n">
-        <v>32.56</v>
+        <v>61.7</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4</v>
+        <v>5.55</v>
       </c>
       <c r="I90" t="n">
-        <v>4.49</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32</v>
+        <v>43.005</v>
       </c>
       <c r="F91" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G91" t="n">
-        <v>69.95999999999999</v>
+        <v>172.02</v>
       </c>
       <c r="H91" t="n">
-        <v>4.29</v>
+        <v>33</v>
       </c>
       <c r="I91" t="n">
-        <v>6.53</v>
+        <v>23.74</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E102" t="n">
-        <v>6.804</v>
+        <v>10.556</v>
       </c>
       <c r="F102" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G102" t="n">
-        <v>61.24</v>
+        <v>31.67</v>
       </c>
       <c r="H102" t="n">
-        <v>5.09</v>
+        <v>0.51</v>
       </c>
       <c r="I102" t="n">
-        <v>9.07</v>
+        <v>1.64</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E103" t="n">
-        <v>103.46</v>
+        <v>40.97</v>
       </c>
       <c r="F103" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G103" t="n">
-        <v>103.46</v>
+        <v>163.88</v>
       </c>
       <c r="H103" t="n">
-        <v>3.37</v>
+        <v>24.86</v>
       </c>
       <c r="I103" t="n">
-        <v>3.37</v>
+        <v>17.88</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E104" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F104" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G104" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H104" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I104" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E105" t="n">
-        <v>23.29</v>
+        <v>103.46</v>
       </c>
       <c r="F105" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G105" t="n">
-        <v>69.87</v>
+        <v>103.46</v>
       </c>
       <c r="H105" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>3.37</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4014,29 +4014,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E106" t="n">
-        <v>10.556</v>
+        <v>6.804</v>
       </c>
       <c r="F106" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G106" t="n">
-        <v>31.67</v>
+        <v>61.24</v>
       </c>
       <c r="H106" t="n">
-        <v>0.51</v>
+        <v>5.09</v>
       </c>
       <c r="I106" t="n">
-        <v>1.64</v>
+        <v>9.07</v>
       </c>
       <c r="J106" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E117" t="n">
-        <v>41</v>
+        <v>105.96</v>
       </c>
       <c r="F117" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G117" t="n">
-        <v>164</v>
+        <v>105.96</v>
       </c>
       <c r="H117" t="n">
-        <v>24.98</v>
+        <v>5.87</v>
       </c>
       <c r="I117" t="n">
-        <v>17.97</v>
+        <v>5.86</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E118" t="n">
-        <v>23.145</v>
+        <v>10.756</v>
       </c>
       <c r="F118" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G118" t="n">
-        <v>69.44</v>
+        <v>32.27</v>
       </c>
       <c r="H118" t="n">
-        <v>3.77</v>
+        <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>5.74</v>
+        <v>3.56</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E119" t="n">
-        <v>6.861</v>
+        <v>41</v>
       </c>
       <c r="F119" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G119" t="n">
-        <v>61.75</v>
+        <v>164</v>
       </c>
       <c r="H119" t="n">
-        <v>5.6</v>
+        <v>24.98</v>
       </c>
       <c r="I119" t="n">
-        <v>9.970000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E120" t="n">
-        <v>10.756</v>
+        <v>23.145</v>
       </c>
       <c r="F120" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G120" t="n">
-        <v>32.27</v>
+        <v>69.44</v>
       </c>
       <c r="H120" t="n">
-        <v>1.11</v>
+        <v>3.77</v>
       </c>
       <c r="I120" t="n">
-        <v>3.56</v>
+        <v>5.74</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E121" t="n">
-        <v>105.96</v>
+        <v>6.861</v>
       </c>
       <c r="F121" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G121" t="n">
-        <v>105.96</v>
+        <v>61.75</v>
       </c>
       <c r="H121" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="I121" t="n">
-        <v>5.86</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D127" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E127" t="n">
-        <v>39.36</v>
+        <v>6.868</v>
       </c>
       <c r="F127" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G127" t="n">
-        <v>157.44</v>
+        <v>61.81</v>
       </c>
       <c r="H127" t="n">
-        <v>18.42</v>
+        <v>5.66</v>
       </c>
       <c r="I127" t="n">
-        <v>13.25</v>
+        <v>10.08</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E128" t="n">
-        <v>11.458</v>
+        <v>23.17</v>
       </c>
       <c r="F128" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G128" t="n">
-        <v>34.37</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.21</v>
+        <v>3.84</v>
       </c>
       <c r="I128" t="n">
-        <v>10.3</v>
+        <v>5.85</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E130" t="n">
-        <v>6.868</v>
+        <v>11.458</v>
       </c>
       <c r="F130" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G130" t="n">
-        <v>61.81</v>
+        <v>34.37</v>
       </c>
       <c r="H130" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="I130" t="n">
-        <v>10.08</v>
+        <v>10.3</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E131" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F131" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G131" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H131" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I131" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E137" t="n">
-        <v>104.76</v>
+        <v>23.3</v>
       </c>
       <c r="F137" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G137" t="n">
-        <v>104.76</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>4.67</v>
+        <v>4.23</v>
       </c>
       <c r="I137" t="n">
-        <v>4.67</v>
+        <v>6.44</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E138" t="n">
-        <v>6.927</v>
+        <v>11.728</v>
       </c>
       <c r="F138" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G138" t="n">
-        <v>62.34</v>
+        <v>35.18</v>
       </c>
       <c r="H138" t="n">
-        <v>6.19</v>
+        <v>4.02</v>
       </c>
       <c r="I138" t="n">
-        <v>11.02</v>
+        <v>12.9</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E139" t="n">
-        <v>11.728</v>
+        <v>40.61</v>
       </c>
       <c r="F139" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G139" t="n">
-        <v>35.18</v>
+        <v>162.44</v>
       </c>
       <c r="H139" t="n">
-        <v>4.02</v>
+        <v>23.42</v>
       </c>
       <c r="I139" t="n">
-        <v>12.9</v>
+        <v>16.85</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>104.76</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>4.67</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>4.67</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E141" t="n">
-        <v>40.61</v>
+        <v>6.927</v>
       </c>
       <c r="F141" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G141" t="n">
-        <v>162.44</v>
+        <v>62.34</v>
       </c>
       <c r="H141" t="n">
-        <v>23.42</v>
+        <v>6.19</v>
       </c>
       <c r="I141" t="n">
-        <v>16.85</v>
+        <v>11.02</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5408,29 +5408,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E147" t="n">
-        <v>22.755</v>
+        <v>11.162</v>
       </c>
       <c r="F147" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G147" t="n">
-        <v>68.27</v>
+        <v>33.49</v>
       </c>
       <c r="H147" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="I147" t="n">
-        <v>3.96</v>
+        <v>7.48</v>
       </c>
       <c r="J147" t="n">
         <v>7.91</v>
@@ -5442,29 +5442,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E148" t="n">
-        <v>6.826</v>
+        <v>22.755</v>
       </c>
       <c r="F148" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G148" t="n">
-        <v>61.43</v>
+        <v>68.27</v>
       </c>
       <c r="H148" t="n">
-        <v>5.28</v>
+        <v>2.6</v>
       </c>
       <c r="I148" t="n">
-        <v>9.4</v>
+        <v>3.96</v>
       </c>
       <c r="J148" t="n">
         <v>7.91</v>
@@ -5476,29 +5476,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D149" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E149" t="n">
-        <v>101.7</v>
+        <v>6.826</v>
       </c>
       <c r="F149" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G149" t="n">
-        <v>101.7</v>
+        <v>61.43</v>
       </c>
       <c r="H149" t="n">
-        <v>1.61</v>
+        <v>5.28</v>
       </c>
       <c r="I149" t="n">
-        <v>1.61</v>
+        <v>9.4</v>
       </c>
       <c r="J149" t="n">
         <v>7.91</v>
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E150" t="n">
-        <v>11.162</v>
+        <v>101.7</v>
       </c>
       <c r="F150" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G150" t="n">
-        <v>33.49</v>
+        <v>101.7</v>
       </c>
       <c r="H150" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="I150" t="n">
-        <v>7.48</v>
+        <v>1.61</v>
       </c>
       <c r="J150" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E152" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F152" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G152" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H152" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I152" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E153" t="n">
-        <v>6.893</v>
+        <v>11.034</v>
       </c>
       <c r="F153" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G153" t="n">
-        <v>62.04</v>
+        <v>33.1</v>
       </c>
       <c r="H153" t="n">
-        <v>5.89</v>
+        <v>1.94</v>
       </c>
       <c r="I153" t="n">
-        <v>10.49</v>
+        <v>6.23</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E154" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F154" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G154" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H154" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I154" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D155" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E155" t="n">
-        <v>39.915</v>
+        <v>6.893</v>
       </c>
       <c r="F155" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G155" t="n">
-        <v>159.66</v>
+        <v>62.04</v>
       </c>
       <c r="H155" t="n">
-        <v>20.64</v>
+        <v>5.89</v>
       </c>
       <c r="I155" t="n">
-        <v>14.85</v>
+        <v>10.49</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E156" t="n">
-        <v>23.045</v>
+        <v>104.12</v>
       </c>
       <c r="F156" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G156" t="n">
-        <v>69.14</v>
+        <v>104.12</v>
       </c>
       <c r="H156" t="n">
-        <v>3.47</v>
+        <v>4.03</v>
       </c>
       <c r="I156" t="n">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E162" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F162" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G162" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H162" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I162" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E163" t="n">
-        <v>6.927</v>
+        <v>23.01</v>
       </c>
       <c r="F163" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G163" t="n">
-        <v>62.34</v>
+        <v>69.03</v>
       </c>
       <c r="H163" t="n">
-        <v>6.19</v>
+        <v>3.36</v>
       </c>
       <c r="I163" t="n">
-        <v>11.02</v>
+        <v>5.12</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E164" t="n">
-        <v>23.01</v>
+        <v>103.84</v>
       </c>
       <c r="F164" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G164" t="n">
-        <v>69.03</v>
+        <v>103.84</v>
       </c>
       <c r="H164" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="I164" t="n">
-        <v>5.12</v>
+        <v>3.75</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E165" t="n">
-        <v>38.845</v>
+        <v>10.748</v>
       </c>
       <c r="F165" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G165" t="n">
-        <v>155.38</v>
+        <v>32.24</v>
       </c>
       <c r="H165" t="n">
-        <v>16.36</v>
+        <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>11.77</v>
+        <v>3.47</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D166" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E166" t="n">
-        <v>103.84</v>
+        <v>6.927</v>
       </c>
       <c r="F166" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G166" t="n">
-        <v>103.84</v>
+        <v>62.34</v>
       </c>
       <c r="H166" t="n">
-        <v>3.75</v>
+        <v>6.19</v>
       </c>
       <c r="I166" t="n">
-        <v>3.75</v>
+        <v>11.02</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E177" t="n">
-        <v>38.245</v>
+        <v>102.54</v>
       </c>
       <c r="F177" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G177" t="n">
-        <v>152.98</v>
+        <v>102.54</v>
       </c>
       <c r="H177" t="n">
-        <v>13.96</v>
+        <v>2.45</v>
       </c>
       <c r="I177" t="n">
-        <v>10.04</v>
+        <v>2.45</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D178" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E178" t="n">
-        <v>22.95</v>
+        <v>6.922</v>
       </c>
       <c r="F178" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G178" t="n">
-        <v>68.84999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H178" t="n">
-        <v>3.18</v>
+        <v>6.15</v>
       </c>
       <c r="I178" t="n">
-        <v>4.84</v>
+        <v>10.95</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E179" t="n">
-        <v>10.642</v>
+        <v>22.95</v>
       </c>
       <c r="F179" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G179" t="n">
-        <v>31.93</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>0.77</v>
+        <v>3.18</v>
       </c>
       <c r="I179" t="n">
-        <v>2.47</v>
+        <v>4.84</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E180" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F180" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G180" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H180" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I180" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E181" t="n">
-        <v>102.54</v>
+        <v>10.642</v>
       </c>
       <c r="F181" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G181" t="n">
-        <v>102.54</v>
+        <v>31.93</v>
       </c>
       <c r="H181" t="n">
-        <v>2.45</v>
+        <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D187" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E187" t="n">
-        <v>22.845</v>
+        <v>6.862</v>
       </c>
       <c r="F187" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G187" t="n">
-        <v>68.53</v>
+        <v>61.76</v>
       </c>
       <c r="H187" t="n">
-        <v>2.86</v>
+        <v>5.61</v>
       </c>
       <c r="I187" t="n">
-        <v>4.36</v>
+        <v>9.99</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E188" t="n">
-        <v>10.708</v>
+        <v>101.44</v>
       </c>
       <c r="F188" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G188" t="n">
-        <v>32.12</v>
+        <v>101.44</v>
       </c>
       <c r="H188" t="n">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I188" t="n">
-        <v>3.08</v>
+        <v>1.35</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E190" t="n">
-        <v>101.44</v>
+        <v>10.708</v>
       </c>
       <c r="F190" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G190" t="n">
-        <v>101.44</v>
+        <v>32.12</v>
       </c>
       <c r="H190" t="n">
-        <v>1.35</v>
+        <v>0.96</v>
       </c>
       <c r="I190" t="n">
-        <v>1.35</v>
+        <v>3.08</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E191" t="n">
-        <v>6.862</v>
+        <v>22.845</v>
       </c>
       <c r="F191" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G191" t="n">
-        <v>61.76</v>
+        <v>68.53</v>
       </c>
       <c r="H191" t="n">
-        <v>5.61</v>
+        <v>2.86</v>
       </c>
       <c r="I191" t="n">
-        <v>9.99</v>
+        <v>4.36</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E197" t="n">
-        <v>102.48</v>
+        <v>11.022</v>
       </c>
       <c r="F197" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G197" t="n">
-        <v>102.48</v>
+        <v>33.07</v>
       </c>
       <c r="H197" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="I197" t="n">
-        <v>2.39</v>
+        <v>6.13</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E198" t="n">
-        <v>6.909</v>
+        <v>38.565</v>
       </c>
       <c r="F198" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G198" t="n">
-        <v>62.18</v>
+        <v>154.26</v>
       </c>
       <c r="H198" t="n">
-        <v>6.03</v>
+        <v>15.24</v>
       </c>
       <c r="I198" t="n">
-        <v>10.74</v>
+        <v>10.96</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7176,29 +7176,29 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E199" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F199" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G199" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H199" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I199" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J199" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E200" t="n">
-        <v>11.022</v>
+        <v>102.48</v>
       </c>
       <c r="F200" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G200" t="n">
-        <v>33.07</v>
+        <v>102.48</v>
       </c>
       <c r="H200" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="I200" t="n">
-        <v>6.13</v>
+        <v>2.39</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D201" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E201" t="n">
-        <v>22.6</v>
+        <v>6.909</v>
       </c>
       <c r="F201" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G201" t="n">
-        <v>67.8</v>
+        <v>62.18</v>
       </c>
       <c r="H201" t="n">
-        <v>2.13</v>
+        <v>6.03</v>
       </c>
       <c r="I201" t="n">
-        <v>3.24</v>
+        <v>10.74</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D202" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E202" t="n">
-        <v>100.08</v>
+        <v>6.822</v>
       </c>
       <c r="F202" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G202" t="n">
-        <v>100.08</v>
+        <v>61.4</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.01</v>
+        <v>5.25</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.01</v>
+        <v>9.35</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E203" t="n">
-        <v>22.4</v>
+        <v>38.04</v>
       </c>
       <c r="F203" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G203" t="n">
-        <v>67.2</v>
+        <v>152.16</v>
       </c>
       <c r="H203" t="n">
-        <v>1.53</v>
+        <v>13.14</v>
       </c>
       <c r="I203" t="n">
-        <v>2.33</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7346,29 +7346,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E204" t="n">
-        <v>6.822</v>
+        <v>100.08</v>
       </c>
       <c r="F204" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G204" t="n">
-        <v>61.4</v>
+        <v>100.08</v>
       </c>
       <c r="H204" t="n">
-        <v>5.25</v>
+        <v>-0.01</v>
       </c>
       <c r="I204" t="n">
-        <v>9.35</v>
+        <v>-0.01</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D205" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E205" t="n">
-        <v>38.04</v>
+        <v>22.4</v>
       </c>
       <c r="F205" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G205" t="n">
-        <v>152.16</v>
+        <v>67.2</v>
       </c>
       <c r="H205" t="n">
-        <v>13.14</v>
+        <v>1.53</v>
       </c>
       <c r="I205" t="n">
-        <v>9.449999999999999</v>
+        <v>2.33</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D207" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E207" t="n">
-        <v>6.865</v>
+        <v>37.82</v>
       </c>
       <c r="F207" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G207" t="n">
-        <v>61.79</v>
+        <v>151.28</v>
       </c>
       <c r="H207" t="n">
-        <v>5.64</v>
+        <v>12.26</v>
       </c>
       <c r="I207" t="n">
-        <v>10.04</v>
+        <v>8.82</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C208" t="n">
         <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E208" t="n">
-        <v>11.172</v>
+        <v>22.725</v>
       </c>
       <c r="F208" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G208" t="n">
-        <v>33.52</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H208" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="I208" t="n">
-        <v>7.57</v>
+        <v>3.82</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E210" t="n">
-        <v>22.725</v>
+        <v>11.172</v>
       </c>
       <c r="F210" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G210" t="n">
-        <v>68.18000000000001</v>
+        <v>33.52</v>
       </c>
       <c r="H210" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="I210" t="n">
-        <v>3.82</v>
+        <v>7.57</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D211" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E211" t="n">
-        <v>37.82</v>
+        <v>6.865</v>
       </c>
       <c r="F211" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G211" t="n">
-        <v>151.28</v>
+        <v>61.79</v>
       </c>
       <c r="H211" t="n">
-        <v>12.26</v>
+        <v>5.64</v>
       </c>
       <c r="I211" t="n">
-        <v>8.82</v>
+        <v>10.04</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E217" t="n">
-        <v>23.175</v>
+        <v>6.864</v>
       </c>
       <c r="F217" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G217" t="n">
-        <v>69.53</v>
+        <v>61.78</v>
       </c>
       <c r="H217" t="n">
-        <v>3.86</v>
+        <v>5.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.88</v>
+        <v>10.03</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D218" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E218" t="n">
-        <v>98.02</v>
+        <v>11.546</v>
       </c>
       <c r="F218" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G218" t="n">
-        <v>98.02</v>
+        <v>34.64</v>
       </c>
       <c r="H218" t="n">
-        <v>-2.07</v>
+        <v>3.48</v>
       </c>
       <c r="I218" t="n">
-        <v>-2.07</v>
+        <v>11.17</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E219" t="n">
-        <v>11.546</v>
+        <v>36.75</v>
       </c>
       <c r="F219" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G219" t="n">
-        <v>34.64</v>
+        <v>147</v>
       </c>
       <c r="H219" t="n">
-        <v>3.48</v>
+        <v>7.98</v>
       </c>
       <c r="I219" t="n">
-        <v>11.17</v>
+        <v>5.74</v>
       </c>
       <c r="J219" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E220" t="n">
-        <v>6.864</v>
+        <v>23.175</v>
       </c>
       <c r="F220" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G220" t="n">
-        <v>61.78</v>
+        <v>69.53</v>
       </c>
       <c r="H220" t="n">
-        <v>5.63</v>
+        <v>3.86</v>
       </c>
       <c r="I220" t="n">
-        <v>10.03</v>
+        <v>5.88</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E221" t="n">
-        <v>36.75</v>
+        <v>98.02</v>
       </c>
       <c r="F221" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G221" t="n">
-        <v>147</v>
+        <v>98.02</v>
       </c>
       <c r="H221" t="n">
-        <v>7.98</v>
+        <v>-2.07</v>
       </c>
       <c r="I221" t="n">
-        <v>5.74</v>
+        <v>-2.07</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D232" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E232" t="n">
-        <v>37.44</v>
+        <v>6.812</v>
       </c>
       <c r="F232" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G232" t="n">
-        <v>149.76</v>
+        <v>61.31</v>
       </c>
       <c r="H232" t="n">
-        <v>10.74</v>
+        <v>5.16</v>
       </c>
       <c r="I232" t="n">
-        <v>7.73</v>
+        <v>9.19</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E233" t="n">
-        <v>23.17</v>
+        <v>97.86</v>
       </c>
       <c r="F233" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G233" t="n">
-        <v>69.51000000000001</v>
+        <v>97.86</v>
       </c>
       <c r="H233" t="n">
-        <v>3.84</v>
+        <v>-2.23</v>
       </c>
       <c r="I233" t="n">
-        <v>5.85</v>
+        <v>-2.23</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E235" t="n">
-        <v>97.86</v>
+        <v>23.17</v>
       </c>
       <c r="F235" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G235" t="n">
-        <v>97.86</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.23</v>
+        <v>3.84</v>
       </c>
       <c r="I235" t="n">
-        <v>-2.23</v>
+        <v>5.85</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D236" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E236" t="n">
-        <v>6.812</v>
+        <v>37.44</v>
       </c>
       <c r="F236" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G236" t="n">
-        <v>61.31</v>
+        <v>149.76</v>
       </c>
       <c r="H236" t="n">
-        <v>5.16</v>
+        <v>10.74</v>
       </c>
       <c r="I236" t="n">
-        <v>9.19</v>
+        <v>7.73</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E242" t="n">
-        <v>38.52</v>
+        <v>12.08</v>
       </c>
       <c r="F242" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G242" t="n">
-        <v>154.08</v>
+        <v>36.24</v>
       </c>
       <c r="H242" t="n">
-        <v>15.06</v>
+        <v>5.08</v>
       </c>
       <c r="I242" t="n">
-        <v>10.83</v>
+        <v>16.3</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D243" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E243" t="n">
-        <v>102.86</v>
+        <v>7.005</v>
       </c>
       <c r="F243" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G243" t="n">
-        <v>102.86</v>
+        <v>63.05</v>
       </c>
       <c r="H243" t="n">
-        <v>2.77</v>
+        <v>6.9</v>
       </c>
       <c r="I243" t="n">
-        <v>2.77</v>
+        <v>12.29</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8706,29 +8706,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E244" t="n">
-        <v>7.005</v>
+        <v>23.465</v>
       </c>
       <c r="F244" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G244" t="n">
-        <v>63.05</v>
+        <v>70.39</v>
       </c>
       <c r="H244" t="n">
-        <v>6.9</v>
+        <v>4.72</v>
       </c>
       <c r="I244" t="n">
-        <v>12.29</v>
+        <v>7.19</v>
       </c>
       <c r="J244" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E245" t="n">
-        <v>12.08</v>
+        <v>38.52</v>
       </c>
       <c r="F245" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G245" t="n">
-        <v>36.24</v>
+        <v>154.08</v>
       </c>
       <c r="H245" t="n">
-        <v>5.08</v>
+        <v>15.06</v>
       </c>
       <c r="I245" t="n">
-        <v>16.3</v>
+        <v>10.83</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E246" t="n">
-        <v>23.465</v>
+        <v>102.86</v>
       </c>
       <c r="F246" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G246" t="n">
-        <v>70.39</v>
+        <v>102.86</v>
       </c>
       <c r="H246" t="n">
-        <v>4.72</v>
+        <v>2.77</v>
       </c>
       <c r="I246" t="n">
-        <v>7.19</v>
+        <v>2.77</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D257" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E257" t="n">
-        <v>23.2</v>
+        <v>37.84</v>
       </c>
       <c r="F257" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G257" t="n">
-        <v>69.59999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="H257" t="n">
-        <v>3.93</v>
+        <v>12.34</v>
       </c>
       <c r="I257" t="n">
-        <v>5.98</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D258" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E258" t="n">
-        <v>103.02</v>
+        <v>12.232</v>
       </c>
       <c r="F258" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G258" t="n">
-        <v>103.02</v>
+        <v>36.7</v>
       </c>
       <c r="H258" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="I258" t="n">
-        <v>2.93</v>
+        <v>17.78</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D259" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E259" t="n">
-        <v>12.232</v>
+        <v>7.056</v>
       </c>
       <c r="F259" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G259" t="n">
-        <v>36.7</v>
+        <v>63.5</v>
       </c>
       <c r="H259" t="n">
-        <v>5.54</v>
+        <v>7.35</v>
       </c>
       <c r="I259" t="n">
-        <v>17.78</v>
+        <v>13.09</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E260" t="n">
-        <v>37.84</v>
+        <v>23.2</v>
       </c>
       <c r="F260" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G260" t="n">
-        <v>151.36</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H260" t="n">
-        <v>12.34</v>
+        <v>3.93</v>
       </c>
       <c r="I260" t="n">
-        <v>8.880000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E261" t="n">
-        <v>7.056</v>
+        <v>103.02</v>
       </c>
       <c r="F261" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G261" t="n">
-        <v>63.5</v>
+        <v>103.02</v>
       </c>
       <c r="H261" t="n">
-        <v>7.35</v>
+        <v>2.93</v>
       </c>
       <c r="I261" t="n">
-        <v>13.09</v>
+        <v>2.93</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9488,29 +9488,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D267" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E267" t="n">
-        <v>103.36</v>
+        <v>12.388</v>
       </c>
       <c r="F267" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G267" t="n">
-        <v>103.36</v>
+        <v>37.16</v>
       </c>
       <c r="H267" t="n">
-        <v>3.27</v>
+        <v>6</v>
       </c>
       <c r="I267" t="n">
-        <v>3.27</v>
+        <v>19.26</v>
       </c>
       <c r="J267" t="n">
         <v>7.91</v>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D268" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E268" t="n">
-        <v>23.12</v>
+        <v>7.06</v>
       </c>
       <c r="F268" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G268" t="n">
-        <v>69.36</v>
+        <v>63.54</v>
       </c>
       <c r="H268" t="n">
-        <v>3.69</v>
+        <v>7.39</v>
       </c>
       <c r="I268" t="n">
-        <v>5.62</v>
+        <v>13.16</v>
       </c>
       <c r="J268" t="n">
         <v>7.91</v>
@@ -9556,29 +9556,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E269" t="n">
-        <v>7.06</v>
+        <v>38.865</v>
       </c>
       <c r="F269" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G269" t="n">
-        <v>63.54</v>
+        <v>155.46</v>
       </c>
       <c r="H269" t="n">
-        <v>7.39</v>
+        <v>16.44</v>
       </c>
       <c r="I269" t="n">
-        <v>13.16</v>
+        <v>11.83</v>
       </c>
       <c r="J269" t="n">
         <v>7.91</v>
@@ -9590,29 +9590,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E270" t="n">
-        <v>12.388</v>
+        <v>103.36</v>
       </c>
       <c r="F270" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G270" t="n">
-        <v>37.16</v>
+        <v>103.36</v>
       </c>
       <c r="H270" t="n">
-        <v>6</v>
+        <v>3.27</v>
       </c>
       <c r="I270" t="n">
-        <v>19.26</v>
+        <v>3.27</v>
       </c>
       <c r="J270" t="n">
         <v>7.91</v>
@@ -9624,29 +9624,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D271" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E271" t="n">
-        <v>38.865</v>
+        <v>23.12</v>
       </c>
       <c r="F271" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G271" t="n">
-        <v>155.46</v>
+        <v>69.36</v>
       </c>
       <c r="H271" t="n">
-        <v>16.44</v>
+        <v>3.69</v>
       </c>
       <c r="I271" t="n">
-        <v>11.83</v>
+        <v>5.62</v>
       </c>
       <c r="J271" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D282" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E282" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F282" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G282" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H282" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I282" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D283" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E283" t="n">
-        <v>39.745</v>
+        <v>22.97</v>
       </c>
       <c r="F283" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G283" t="n">
-        <v>158.98</v>
+        <v>68.91</v>
       </c>
       <c r="H283" t="n">
-        <v>19.96</v>
+        <v>3.24</v>
       </c>
       <c r="I283" t="n">
-        <v>14.36</v>
+        <v>4.93</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E284" t="n">
-        <v>22.97</v>
+        <v>104.46</v>
       </c>
       <c r="F284" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G284" t="n">
-        <v>68.91</v>
+        <v>104.46</v>
       </c>
       <c r="H284" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="I284" t="n">
-        <v>4.93</v>
+        <v>4.37</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D285" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E285" t="n">
-        <v>12.468</v>
+        <v>7.054</v>
       </c>
       <c r="F285" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G285" t="n">
-        <v>37.4</v>
+        <v>63.49</v>
       </c>
       <c r="H285" t="n">
-        <v>6.24</v>
+        <v>7.34</v>
       </c>
       <c r="I285" t="n">
-        <v>20.03</v>
+        <v>13.07</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D286" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E286" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F286" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G286" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H286" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I286" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D297" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E297" t="n">
-        <v>38.49</v>
+        <v>6.915</v>
       </c>
       <c r="F297" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G297" t="n">
-        <v>153.96</v>
+        <v>62.23</v>
       </c>
       <c r="H297" t="n">
-        <v>14.94</v>
+        <v>6.08</v>
       </c>
       <c r="I297" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E298" t="n">
-        <v>22.78</v>
+        <v>100.42</v>
       </c>
       <c r="F298" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G298" t="n">
-        <v>68.34</v>
+        <v>100.42</v>
       </c>
       <c r="H298" t="n">
-        <v>2.67</v>
+        <v>0.33</v>
       </c>
       <c r="I298" t="n">
-        <v>4.07</v>
+        <v>0.33</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D300" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E300" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F300" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G300" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H300" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I300" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D301" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E301" t="n">
-        <v>6.915</v>
+        <v>22.78</v>
       </c>
       <c r="F301" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G301" t="n">
-        <v>62.23</v>
+        <v>68.34</v>
       </c>
       <c r="H301" t="n">
-        <v>6.08</v>
+        <v>2.67</v>
       </c>
       <c r="I301" t="n">
-        <v>10.83</v>
+        <v>4.07</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D312" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E312" t="n">
-        <v>38.66</v>
+        <v>6.936</v>
       </c>
       <c r="F312" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G312" t="n">
-        <v>154.64</v>
+        <v>62.42</v>
       </c>
       <c r="H312" t="n">
-        <v>15.62</v>
+        <v>6.27</v>
       </c>
       <c r="I312" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E313" t="n">
-        <v>11.742</v>
+        <v>100.38</v>
       </c>
       <c r="F313" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G313" t="n">
-        <v>35.23</v>
+        <v>100.38</v>
       </c>
       <c r="H313" t="n">
-        <v>4.07</v>
+        <v>0.29</v>
       </c>
       <c r="I313" t="n">
-        <v>13.06</v>
+        <v>0.29</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11086,29 +11086,29 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C314" t="n">
         <v>3</v>
       </c>
       <c r="D314" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E314" t="n">
-        <v>22.9</v>
+        <v>11.742</v>
       </c>
       <c r="F314" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G314" t="n">
-        <v>68.7</v>
+        <v>35.23</v>
       </c>
       <c r="H314" t="n">
-        <v>3.03</v>
+        <v>4.07</v>
       </c>
       <c r="I314" t="n">
-        <v>4.61</v>
+        <v>13.06</v>
       </c>
       <c r="J314" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D315" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E315" t="n">
-        <v>100.38</v>
+        <v>22.9</v>
       </c>
       <c r="F315" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G315" t="n">
-        <v>100.38</v>
+        <v>68.7</v>
       </c>
       <c r="H315" t="n">
-        <v>0.29</v>
+        <v>3.03</v>
       </c>
       <c r="I315" t="n">
-        <v>0.29</v>
+        <v>4.61</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D316" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E316" t="n">
-        <v>6.936</v>
+        <v>38.66</v>
       </c>
       <c r="F316" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G316" t="n">
-        <v>62.42</v>
+        <v>154.64</v>
       </c>
       <c r="H316" t="n">
-        <v>6.27</v>
+        <v>15.62</v>
       </c>
       <c r="I316" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D322" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E322" t="n">
-        <v>6.967</v>
+        <v>101.7</v>
       </c>
       <c r="F322" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G322" t="n">
-        <v>62.7</v>
+        <v>101.7</v>
       </c>
       <c r="H322" t="n">
-        <v>6.55</v>
+        <v>1.61</v>
       </c>
       <c r="I322" t="n">
-        <v>11.67</v>
+        <v>1.61</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C323" t="n">
         <v>3</v>
       </c>
       <c r="D323" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E323" t="n">
-        <v>22.745</v>
+        <v>11.81</v>
       </c>
       <c r="F323" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G323" t="n">
-        <v>68.23</v>
+        <v>35.43</v>
       </c>
       <c r="H323" t="n">
-        <v>2.56</v>
+        <v>4.27</v>
       </c>
       <c r="I323" t="n">
-        <v>3.9</v>
+        <v>13.7</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11426,29 +11426,29 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D324" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E324" t="n">
-        <v>11.81</v>
+        <v>39.07</v>
       </c>
       <c r="F324" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G324" t="n">
-        <v>35.43</v>
+        <v>156.28</v>
       </c>
       <c r="H324" t="n">
-        <v>4.27</v>
+        <v>17.26</v>
       </c>
       <c r="I324" t="n">
-        <v>13.7</v>
+        <v>12.42</v>
       </c>
       <c r="J324" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D325" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E325" t="n">
-        <v>101.7</v>
+        <v>6.967</v>
       </c>
       <c r="F325" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G325" t="n">
-        <v>101.7</v>
+        <v>62.7</v>
       </c>
       <c r="H325" t="n">
-        <v>1.61</v>
+        <v>6.55</v>
       </c>
       <c r="I325" t="n">
-        <v>1.61</v>
+        <v>11.67</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D326" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E326" t="n">
-        <v>39.07</v>
+        <v>22.745</v>
       </c>
       <c r="F326" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G326" t="n">
-        <v>156.28</v>
+        <v>68.23</v>
       </c>
       <c r="H326" t="n">
-        <v>17.26</v>
+        <v>2.56</v>
       </c>
       <c r="I326" t="n">
-        <v>12.42</v>
+        <v>3.9</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D337" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E337" t="n">
-        <v>11.284</v>
+        <v>101.04</v>
       </c>
       <c r="F337" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G337" t="n">
-        <v>33.85</v>
+        <v>101.04</v>
       </c>
       <c r="H337" t="n">
-        <v>2.69</v>
+        <v>0.95</v>
       </c>
       <c r="I337" t="n">
-        <v>8.630000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D338" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E338" t="n">
-        <v>22.845</v>
+        <v>39.15</v>
       </c>
       <c r="F338" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G338" t="n">
-        <v>68.53</v>
+        <v>156.6</v>
       </c>
       <c r="H338" t="n">
-        <v>2.86</v>
+        <v>17.58</v>
       </c>
       <c r="I338" t="n">
-        <v>4.36</v>
+        <v>12.65</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D340" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E340" t="n">
-        <v>39.15</v>
+        <v>22.845</v>
       </c>
       <c r="F340" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G340" t="n">
-        <v>156.6</v>
+        <v>68.53</v>
       </c>
       <c r="H340" t="n">
-        <v>17.58</v>
+        <v>2.86</v>
       </c>
       <c r="I340" t="n">
-        <v>12.65</v>
+        <v>4.36</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D341" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E341" t="n">
-        <v>101.04</v>
+        <v>11.284</v>
       </c>
       <c r="F341" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G341" t="n">
-        <v>101.04</v>
+        <v>33.85</v>
       </c>
       <c r="H341" t="n">
-        <v>0.95</v>
+        <v>2.69</v>
       </c>
       <c r="I341" t="n">
-        <v>0.95</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D347" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E347" t="n">
-        <v>101.78</v>
+        <v>7.005</v>
       </c>
       <c r="F347" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G347" t="n">
-        <v>101.78</v>
+        <v>63.05</v>
       </c>
       <c r="H347" t="n">
-        <v>1.69</v>
+        <v>6.9</v>
       </c>
       <c r="I347" t="n">
-        <v>1.69</v>
+        <v>12.29</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D348" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E348" t="n">
-        <v>39</v>
+        <v>22.82</v>
       </c>
       <c r="F348" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G348" t="n">
-        <v>156</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H348" t="n">
-        <v>16.98</v>
+        <v>2.79</v>
       </c>
       <c r="I348" t="n">
-        <v>12.21</v>
+        <v>4.25</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12276,29 +12276,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C349" t="n">
         <v>3</v>
       </c>
       <c r="D349" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E349" t="n">
-        <v>22.82</v>
+        <v>11.206</v>
       </c>
       <c r="F349" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G349" t="n">
-        <v>68.45999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="H349" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="I349" t="n">
-        <v>4.25</v>
+        <v>7.89</v>
       </c>
       <c r="J349" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D350" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E350" t="n">
-        <v>7.005</v>
+        <v>101.78</v>
       </c>
       <c r="F350" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G350" t="n">
-        <v>63.05</v>
+        <v>101.78</v>
       </c>
       <c r="H350" t="n">
-        <v>6.9</v>
+        <v>1.69</v>
       </c>
       <c r="I350" t="n">
-        <v>12.29</v>
+        <v>1.69</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D351" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E351" t="n">
-        <v>11.206</v>
+        <v>39</v>
       </c>
       <c r="F351" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G351" t="n">
-        <v>33.62</v>
+        <v>156</v>
       </c>
       <c r="H351" t="n">
-        <v>2.46</v>
+        <v>16.98</v>
       </c>
       <c r="I351" t="n">
-        <v>7.89</v>
+        <v>12.21</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12718,29 +12718,29 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C362" t="n">
         <v>3</v>
       </c>
       <c r="D362" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E362" t="n">
-        <v>22.515</v>
+        <v>11.208</v>
       </c>
       <c r="F362" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G362" t="n">
-        <v>67.55</v>
+        <v>33.62</v>
       </c>
       <c r="H362" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="I362" t="n">
-        <v>2.86</v>
+        <v>7.89</v>
       </c>
       <c r="J362" t="n">
         <v>7.91</v>
@@ -12752,29 +12752,29 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D363" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E363" t="n">
-        <v>40.15</v>
+        <v>102.1</v>
       </c>
       <c r="F363" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G363" t="n">
-        <v>160.6</v>
+        <v>102.1</v>
       </c>
       <c r="H363" t="n">
-        <v>21.58</v>
+        <v>2.01</v>
       </c>
       <c r="I363" t="n">
-        <v>15.52</v>
+        <v>2.01</v>
       </c>
       <c r="J363" t="n">
         <v>7.91</v>
@@ -12786,29 +12786,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D364" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E364" t="n">
-        <v>6.972</v>
+        <v>40.15</v>
       </c>
       <c r="F364" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G364" t="n">
-        <v>62.75</v>
+        <v>160.6</v>
       </c>
       <c r="H364" t="n">
-        <v>6.6</v>
+        <v>21.58</v>
       </c>
       <c r="I364" t="n">
-        <v>11.75</v>
+        <v>15.52</v>
       </c>
       <c r="J364" t="n">
         <v>7.91</v>
@@ -12820,29 +12820,29 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D365" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E365" t="n">
-        <v>102.1</v>
+        <v>6.972</v>
       </c>
       <c r="F365" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G365" t="n">
-        <v>102.1</v>
+        <v>62.75</v>
       </c>
       <c r="H365" t="n">
-        <v>2.01</v>
+        <v>6.6</v>
       </c>
       <c r="I365" t="n">
-        <v>2.01</v>
+        <v>11.75</v>
       </c>
       <c r="J365" t="n">
         <v>7.91</v>
@@ -12854,29 +12854,29 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C366" t="n">
         <v>3</v>
       </c>
       <c r="D366" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E366" t="n">
-        <v>11.208</v>
+        <v>22.515</v>
       </c>
       <c r="F366" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G366" t="n">
-        <v>33.62</v>
+        <v>67.55</v>
       </c>
       <c r="H366" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="I366" t="n">
-        <v>7.89</v>
+        <v>2.86</v>
       </c>
       <c r="J366" t="n">
         <v>7.91</v>
@@ -13058,29 +13058,29 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D372" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E372" t="n">
-        <v>6.878</v>
+        <v>100.88</v>
       </c>
       <c r="F372" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G372" t="n">
-        <v>61.9</v>
+        <v>100.88</v>
       </c>
       <c r="H372" t="n">
-        <v>5.75</v>
+        <v>0.79</v>
       </c>
       <c r="I372" t="n">
-        <v>10.24</v>
+        <v>0.79</v>
       </c>
       <c r="J372" t="n">
         <v>7.91</v>
@@ -13092,29 +13092,29 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D373" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E373" t="n">
-        <v>39.05</v>
+        <v>21.94</v>
       </c>
       <c r="F373" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G373" t="n">
-        <v>156.2</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H373" t="n">
-        <v>17.18</v>
+        <v>0.15</v>
       </c>
       <c r="I373" t="n">
-        <v>12.36</v>
+        <v>0.23</v>
       </c>
       <c r="J373" t="n">
         <v>7.91</v>
@@ -13126,29 +13126,29 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C374" t="n">
         <v>3</v>
       </c>
       <c r="D374" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E374" t="n">
-        <v>21.94</v>
+        <v>10.912</v>
       </c>
       <c r="F374" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G374" t="n">
-        <v>65.81999999999999</v>
+        <v>32.74</v>
       </c>
       <c r="H374" t="n">
-        <v>0.15</v>
+        <v>1.58</v>
       </c>
       <c r="I374" t="n">
-        <v>0.23</v>
+        <v>5.07</v>
       </c>
       <c r="J374" t="n">
         <v>7.91</v>
@@ -13160,29 +13160,29 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D375" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E375" t="n">
-        <v>100.88</v>
+        <v>6.878</v>
       </c>
       <c r="F375" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G375" t="n">
-        <v>100.88</v>
+        <v>61.9</v>
       </c>
       <c r="H375" t="n">
-        <v>0.79</v>
+        <v>5.75</v>
       </c>
       <c r="I375" t="n">
-        <v>0.79</v>
+        <v>10.24</v>
       </c>
       <c r="J375" t="n">
         <v>7.91</v>
@@ -13194,29 +13194,29 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D376" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E376" t="n">
-        <v>10.912</v>
+        <v>39.05</v>
       </c>
       <c r="F376" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G376" t="n">
-        <v>32.74</v>
+        <v>156.2</v>
       </c>
       <c r="H376" t="n">
-        <v>1.58</v>
+        <v>17.18</v>
       </c>
       <c r="I376" t="n">
-        <v>5.07</v>
+        <v>12.36</v>
       </c>
       <c r="J376" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D387" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E387" t="n">
-        <v>38.375</v>
+        <v>100.76</v>
       </c>
       <c r="F387" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G387" t="n">
-        <v>153.5</v>
+        <v>100.76</v>
       </c>
       <c r="H387" t="n">
-        <v>14.48</v>
+        <v>0.67</v>
       </c>
       <c r="I387" t="n">
-        <v>10.42</v>
+        <v>0.67</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D388" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E388" t="n">
-        <v>6.893</v>
+        <v>21.83</v>
       </c>
       <c r="F388" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G388" t="n">
-        <v>62.04</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H388" t="n">
-        <v>5.89</v>
+        <v>-0.18</v>
       </c>
       <c r="I388" t="n">
-        <v>10.49</v>
+        <v>-0.27</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D389" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E389" t="n">
-        <v>11.006</v>
+        <v>6.893</v>
       </c>
       <c r="F389" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G389" t="n">
-        <v>33.02</v>
+        <v>62.04</v>
       </c>
       <c r="H389" t="n">
-        <v>1.86</v>
+        <v>5.89</v>
       </c>
       <c r="I389" t="n">
-        <v>5.97</v>
+        <v>10.49</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D390" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E390" t="n">
-        <v>100.76</v>
+        <v>38.375</v>
       </c>
       <c r="F390" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G390" t="n">
-        <v>100.76</v>
+        <v>153.5</v>
       </c>
       <c r="H390" t="n">
-        <v>0.67</v>
+        <v>14.48</v>
       </c>
       <c r="I390" t="n">
-        <v>0.67</v>
+        <v>10.42</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C391" t="n">
         <v>3</v>
       </c>
       <c r="D391" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E391" t="n">
-        <v>21.83</v>
+        <v>11.006</v>
       </c>
       <c r="F391" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G391" t="n">
-        <v>65.48999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="H391" t="n">
-        <v>-0.18</v>
+        <v>1.86</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.27</v>
+        <v>5.97</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D397" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E397" t="n">
-        <v>39.435</v>
+        <v>6.982</v>
       </c>
       <c r="F397" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G397" t="n">
-        <v>157.74</v>
+        <v>62.84</v>
       </c>
       <c r="H397" t="n">
-        <v>18.72</v>
+        <v>6.69</v>
       </c>
       <c r="I397" t="n">
-        <v>13.47</v>
+        <v>11.91</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E398" t="n">
-        <v>11.202</v>
+        <v>102.82</v>
       </c>
       <c r="F398" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G398" t="n">
-        <v>33.61</v>
+        <v>102.82</v>
       </c>
       <c r="H398" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="I398" t="n">
-        <v>7.86</v>
+        <v>2.73</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D400" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E400" t="n">
-        <v>102.82</v>
+        <v>39.435</v>
       </c>
       <c r="F400" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G400" t="n">
-        <v>102.82</v>
+        <v>157.74</v>
       </c>
       <c r="H400" t="n">
-        <v>2.73</v>
+        <v>18.72</v>
       </c>
       <c r="I400" t="n">
-        <v>2.73</v>
+        <v>13.47</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D401" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E401" t="n">
-        <v>6.982</v>
+        <v>11.202</v>
       </c>
       <c r="F401" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G401" t="n">
-        <v>62.84</v>
+        <v>33.61</v>
       </c>
       <c r="H401" t="n">
-        <v>6.69</v>
+        <v>2.45</v>
       </c>
       <c r="I401" t="n">
-        <v>11.91</v>
+        <v>7.86</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D407" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E407" t="n">
-        <v>11.232</v>
+        <v>105.98</v>
       </c>
       <c r="F407" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G407" t="n">
-        <v>33.7</v>
+        <v>105.98</v>
       </c>
       <c r="H407" t="n">
-        <v>2.54</v>
+        <v>5.89</v>
       </c>
       <c r="I407" t="n">
-        <v>8.15</v>
+        <v>5.88</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E408" t="n">
-        <v>40.695</v>
+        <v>22.35</v>
       </c>
       <c r="F408" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G408" t="n">
-        <v>162.78</v>
+        <v>67.05</v>
       </c>
       <c r="H408" t="n">
-        <v>23.76</v>
+        <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>17.09</v>
+        <v>2.1</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D409" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E409" t="n">
-        <v>22.35</v>
+        <v>7.049</v>
       </c>
       <c r="F409" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G409" t="n">
-        <v>67.05</v>
+        <v>63.44</v>
       </c>
       <c r="H409" t="n">
-        <v>1.38</v>
+        <v>7.29</v>
       </c>
       <c r="I409" t="n">
-        <v>2.1</v>
+        <v>12.98</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D410" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E410" t="n">
-        <v>105.98</v>
+        <v>11.232</v>
       </c>
       <c r="F410" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G410" t="n">
-        <v>105.98</v>
+        <v>33.7</v>
       </c>
       <c r="H410" t="n">
-        <v>5.89</v>
+        <v>2.54</v>
       </c>
       <c r="I410" t="n">
-        <v>5.88</v>
+        <v>8.15</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14384,31 +14384,201 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>4</v>
+      </c>
+      <c r="D411" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E411" t="n">
+        <v>40.695</v>
+      </c>
+      <c r="F411" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G411" t="n">
+        <v>162.78</v>
+      </c>
+      <c r="H411" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="I411" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J411" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E412" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="F412" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G412" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="H412" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="I412" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="J412" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>3</v>
+      </c>
+      <c r="D413" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E413" t="n">
+        <v>11.154</v>
+      </c>
+      <c r="F413" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G413" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="H413" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>4</v>
+      </c>
+      <c r="D414" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E414" t="n">
+        <v>40.955</v>
+      </c>
+      <c r="F414" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G414" t="n">
+        <v>163.82</v>
+      </c>
+      <c r="H414" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I414" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>3</v>
+      </c>
+      <c r="D415" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E415" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="F415" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G415" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="H415" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C411" t="n">
+      <c r="C416" t="n">
         <v>9</v>
       </c>
-      <c r="D411" t="n">
+      <c r="D416" t="n">
         <v>6.239</v>
       </c>
-      <c r="E411" t="n">
-        <v>7.049</v>
-      </c>
-      <c r="F411" t="n">
+      <c r="E416" t="n">
+        <v>7.093</v>
+      </c>
+      <c r="F416" t="n">
         <v>56.15</v>
       </c>
-      <c r="G411" t="n">
-        <v>63.44</v>
-      </c>
-      <c r="H411" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="I411" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="J411" t="n">
+      <c r="G416" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="H416" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="I416" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J416" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E12" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F12" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G12" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H12" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I12" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E13" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F13" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G13" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H13" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I13" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E14" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F14" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G14" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E15" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F15" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G15" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H15" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E16" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F16" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G16" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H16" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I16" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E27" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F27" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G27" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H27" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E28" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F28" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G28" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E29" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F29" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G29" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H29" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I29" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E30" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F30" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G30" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H30" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E31" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F31" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G31" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I31" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E37" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F37" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G37" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H37" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I37" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E38" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F38" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G38" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H38" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E39" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F39" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G39" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H39" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I39" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E40" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F40" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G40" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E41" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F41" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G41" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H41" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I41" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E52" t="n">
-        <v>21.703</v>
+        <v>38.544</v>
       </c>
       <c r="F52" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G52" t="n">
-        <v>65.11</v>
+        <v>154.18</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5600000000000001</v>
+        <v>15.16</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.85</v>
+        <v>10.9</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E53" t="n">
-        <v>10.702</v>
+        <v>6.629</v>
       </c>
       <c r="F53" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G53" t="n">
-        <v>32.11</v>
+        <v>59.66</v>
       </c>
       <c r="H53" t="n">
-        <v>0.95</v>
+        <v>3.51</v>
       </c>
       <c r="I53" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E54" t="n">
-        <v>100.34</v>
+        <v>21.703</v>
       </c>
       <c r="F54" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G54" t="n">
-        <v>100.34</v>
+        <v>65.11</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E55" t="n">
-        <v>6.629</v>
+        <v>10.702</v>
       </c>
       <c r="F55" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G55" t="n">
-        <v>59.66</v>
+        <v>32.11</v>
       </c>
       <c r="H55" t="n">
-        <v>3.51</v>
+        <v>0.95</v>
       </c>
       <c r="I55" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E56" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F56" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G56" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H56" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E62" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F62" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G62" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H62" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E63" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F63" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G63" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H63" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I63" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E64" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F64" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G64" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H64" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I64" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E65" t="n">
-        <v>10.712</v>
+        <v>22.7</v>
       </c>
       <c r="F65" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G65" t="n">
-        <v>32.14</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>0.98</v>
+        <v>2.43</v>
       </c>
       <c r="I65" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E66" t="n">
-        <v>6.817</v>
+        <v>41.064</v>
       </c>
       <c r="F66" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G66" t="n">
-        <v>61.35</v>
+        <v>164.26</v>
       </c>
       <c r="H66" t="n">
-        <v>5.2</v>
+        <v>25.24</v>
       </c>
       <c r="I66" t="n">
-        <v>9.26</v>
+        <v>18.16</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E67" t="n">
-        <v>104.58</v>
+        <v>6.807</v>
       </c>
       <c r="F67" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G67" t="n">
-        <v>104.58</v>
+        <v>61.26</v>
       </c>
       <c r="H67" t="n">
-        <v>4.49</v>
+        <v>5.11</v>
       </c>
       <c r="I67" t="n">
-        <v>4.49</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E68" t="n">
-        <v>6.807</v>
+        <v>22.797</v>
       </c>
       <c r="F68" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G68" t="n">
-        <v>61.26</v>
+        <v>68.39</v>
       </c>
       <c r="H68" t="n">
-        <v>5.11</v>
+        <v>2.72</v>
       </c>
       <c r="I68" t="n">
-        <v>9.1</v>
+        <v>4.14</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E69" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F69" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G69" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H69" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I69" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E70" t="n">
-        <v>10.796</v>
+        <v>40.567</v>
       </c>
       <c r="F70" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G70" t="n">
-        <v>32.39</v>
+        <v>162.27</v>
       </c>
       <c r="H70" t="n">
-        <v>1.23</v>
+        <v>23.25</v>
       </c>
       <c r="I70" t="n">
-        <v>3.95</v>
+        <v>16.72</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E71" t="n">
-        <v>40.567</v>
+        <v>104.58</v>
       </c>
       <c r="F71" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G71" t="n">
-        <v>162.27</v>
+        <v>104.58</v>
       </c>
       <c r="H71" t="n">
-        <v>23.25</v>
+        <v>4.49</v>
       </c>
       <c r="I71" t="n">
-        <v>16.72</v>
+        <v>4.49</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E77" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F77" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G77" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H77" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I77" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E78" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F78" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G78" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H78" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I78" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E80" t="n">
-        <v>23.4</v>
+        <v>6.836</v>
       </c>
       <c r="F80" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G80" t="n">
-        <v>70.2</v>
+        <v>61.52</v>
       </c>
       <c r="H80" t="n">
-        <v>4.53</v>
+        <v>5.37</v>
       </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>9.56</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E81" t="n">
-        <v>42.25</v>
+        <v>105.8</v>
       </c>
       <c r="F81" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G81" t="n">
-        <v>169</v>
+        <v>105.8</v>
       </c>
       <c r="H81" t="n">
-        <v>29.98</v>
+        <v>5.71</v>
       </c>
       <c r="I81" t="n">
-        <v>21.57</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E87" t="n">
-        <v>10.852</v>
+        <v>6.856</v>
       </c>
       <c r="F87" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G87" t="n">
-        <v>32.56</v>
+        <v>61.7</v>
       </c>
       <c r="H87" t="n">
-        <v>1.4</v>
+        <v>5.55</v>
       </c>
       <c r="I87" t="n">
-        <v>4.49</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E88" t="n">
-        <v>106.28</v>
+        <v>23.32</v>
       </c>
       <c r="F88" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G88" t="n">
-        <v>106.28</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>6.19</v>
+        <v>4.29</v>
       </c>
       <c r="I88" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E89" t="n">
-        <v>23.32</v>
+        <v>43.005</v>
       </c>
       <c r="F89" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G89" t="n">
-        <v>69.95999999999999</v>
+        <v>172.02</v>
       </c>
       <c r="H89" t="n">
-        <v>4.29</v>
+        <v>33</v>
       </c>
       <c r="I89" t="n">
-        <v>6.53</v>
+        <v>23.74</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E90" t="n">
-        <v>6.856</v>
+        <v>10.852</v>
       </c>
       <c r="F90" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G90" t="n">
-        <v>61.7</v>
+        <v>32.56</v>
       </c>
       <c r="H90" t="n">
-        <v>5.55</v>
+        <v>1.4</v>
       </c>
       <c r="I90" t="n">
-        <v>9.880000000000001</v>
+        <v>4.49</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E91" t="n">
-        <v>43.005</v>
+        <v>106.28</v>
       </c>
       <c r="F91" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G91" t="n">
-        <v>172.02</v>
+        <v>106.28</v>
       </c>
       <c r="H91" t="n">
-        <v>33</v>
+        <v>6.19</v>
       </c>
       <c r="I91" t="n">
-        <v>23.74</v>
+        <v>6.18</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E102" t="n">
-        <v>10.556</v>
+        <v>6.804</v>
       </c>
       <c r="F102" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G102" t="n">
-        <v>31.67</v>
+        <v>61.24</v>
       </c>
       <c r="H102" t="n">
-        <v>0.51</v>
+        <v>5.09</v>
       </c>
       <c r="I102" t="n">
-        <v>1.64</v>
+        <v>9.07</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E103" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F103" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G103" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H103" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I103" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E104" t="n">
-        <v>23.29</v>
+        <v>103.46</v>
       </c>
       <c r="F104" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G104" t="n">
-        <v>69.87</v>
+        <v>103.46</v>
       </c>
       <c r="H104" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="I104" t="n">
-        <v>6.4</v>
+        <v>3.37</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E105" t="n">
-        <v>103.46</v>
+        <v>40.97</v>
       </c>
       <c r="F105" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G105" t="n">
-        <v>103.46</v>
+        <v>163.88</v>
       </c>
       <c r="H105" t="n">
-        <v>3.37</v>
+        <v>24.86</v>
       </c>
       <c r="I105" t="n">
-        <v>3.37</v>
+        <v>17.88</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4014,29 +4014,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E106" t="n">
-        <v>6.804</v>
+        <v>10.556</v>
       </c>
       <c r="F106" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G106" t="n">
-        <v>61.24</v>
+        <v>31.67</v>
       </c>
       <c r="H106" t="n">
-        <v>5.09</v>
+        <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>9.07</v>
+        <v>1.64</v>
       </c>
       <c r="J106" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E117" t="n">
-        <v>105.96</v>
+        <v>6.861</v>
       </c>
       <c r="F117" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G117" t="n">
-        <v>105.96</v>
+        <v>61.75</v>
       </c>
       <c r="H117" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="I117" t="n">
-        <v>5.86</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E118" t="n">
-        <v>10.756</v>
+        <v>23.145</v>
       </c>
       <c r="F118" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G118" t="n">
-        <v>32.27</v>
+        <v>69.44</v>
       </c>
       <c r="H118" t="n">
-        <v>1.11</v>
+        <v>3.77</v>
       </c>
       <c r="I118" t="n">
-        <v>3.56</v>
+        <v>5.74</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E119" t="n">
-        <v>41</v>
+        <v>105.96</v>
       </c>
       <c r="F119" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G119" t="n">
-        <v>164</v>
+        <v>105.96</v>
       </c>
       <c r="H119" t="n">
-        <v>24.98</v>
+        <v>5.87</v>
       </c>
       <c r="I119" t="n">
-        <v>17.97</v>
+        <v>5.86</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E120" t="n">
-        <v>23.145</v>
+        <v>10.756</v>
       </c>
       <c r="F120" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G120" t="n">
-        <v>69.44</v>
+        <v>32.27</v>
       </c>
       <c r="H120" t="n">
-        <v>3.77</v>
+        <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>5.74</v>
+        <v>3.56</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E121" t="n">
-        <v>6.861</v>
+        <v>41</v>
       </c>
       <c r="F121" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G121" t="n">
-        <v>61.75</v>
+        <v>164</v>
       </c>
       <c r="H121" t="n">
-        <v>5.6</v>
+        <v>24.98</v>
       </c>
       <c r="I121" t="n">
-        <v>9.970000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E127" t="n">
-        <v>6.868</v>
+        <v>11.458</v>
       </c>
       <c r="F127" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G127" t="n">
-        <v>61.81</v>
+        <v>34.37</v>
       </c>
       <c r="H127" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="I127" t="n">
-        <v>10.08</v>
+        <v>10.3</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E128" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F128" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G128" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H128" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I128" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E130" t="n">
-        <v>11.458</v>
+        <v>23.17</v>
       </c>
       <c r="F130" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G130" t="n">
-        <v>34.37</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>3.21</v>
+        <v>3.84</v>
       </c>
       <c r="I130" t="n">
-        <v>10.3</v>
+        <v>5.85</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D131" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E131" t="n">
-        <v>39.36</v>
+        <v>6.868</v>
       </c>
       <c r="F131" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G131" t="n">
-        <v>157.44</v>
+        <v>61.81</v>
       </c>
       <c r="H131" t="n">
-        <v>18.42</v>
+        <v>5.66</v>
       </c>
       <c r="I131" t="n">
-        <v>13.25</v>
+        <v>10.08</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E137" t="n">
-        <v>23.3</v>
+        <v>104.76</v>
       </c>
       <c r="F137" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G137" t="n">
-        <v>69.90000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="H137" t="n">
-        <v>4.23</v>
+        <v>4.67</v>
       </c>
       <c r="I137" t="n">
-        <v>6.44</v>
+        <v>4.67</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E138" t="n">
-        <v>11.728</v>
+        <v>40.61</v>
       </c>
       <c r="F138" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G138" t="n">
-        <v>35.18</v>
+        <v>162.44</v>
       </c>
       <c r="H138" t="n">
-        <v>4.02</v>
+        <v>23.42</v>
       </c>
       <c r="I138" t="n">
-        <v>12.9</v>
+        <v>16.85</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D139" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E139" t="n">
-        <v>40.61</v>
+        <v>6.927</v>
       </c>
       <c r="F139" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G139" t="n">
-        <v>162.44</v>
+        <v>62.34</v>
       </c>
       <c r="H139" t="n">
-        <v>23.42</v>
+        <v>6.19</v>
       </c>
       <c r="I139" t="n">
-        <v>16.85</v>
+        <v>11.02</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E140" t="n">
-        <v>104.76</v>
+        <v>23.3</v>
       </c>
       <c r="F140" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G140" t="n">
-        <v>104.76</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>4.67</v>
+        <v>4.23</v>
       </c>
       <c r="I140" t="n">
-        <v>4.67</v>
+        <v>6.44</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E141" t="n">
-        <v>6.927</v>
+        <v>11.728</v>
       </c>
       <c r="F141" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G141" t="n">
-        <v>62.34</v>
+        <v>35.18</v>
       </c>
       <c r="H141" t="n">
-        <v>6.19</v>
+        <v>4.02</v>
       </c>
       <c r="I141" t="n">
-        <v>11.02</v>
+        <v>12.9</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5408,29 +5408,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E147" t="n">
-        <v>11.162</v>
+        <v>101.7</v>
       </c>
       <c r="F147" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G147" t="n">
-        <v>33.49</v>
+        <v>101.7</v>
       </c>
       <c r="H147" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="I147" t="n">
-        <v>7.48</v>
+        <v>1.61</v>
       </c>
       <c r="J147" t="n">
         <v>7.91</v>
@@ -5442,29 +5442,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E148" t="n">
-        <v>22.755</v>
+        <v>11.162</v>
       </c>
       <c r="F148" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G148" t="n">
-        <v>68.27</v>
+        <v>33.49</v>
       </c>
       <c r="H148" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="I148" t="n">
-        <v>3.96</v>
+        <v>7.48</v>
       </c>
       <c r="J148" t="n">
         <v>7.91</v>
@@ -5476,29 +5476,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E149" t="n">
-        <v>6.826</v>
+        <v>22.755</v>
       </c>
       <c r="F149" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G149" t="n">
-        <v>61.43</v>
+        <v>68.27</v>
       </c>
       <c r="H149" t="n">
-        <v>5.28</v>
+        <v>2.6</v>
       </c>
       <c r="I149" t="n">
-        <v>9.4</v>
+        <v>3.96</v>
       </c>
       <c r="J149" t="n">
         <v>7.91</v>
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E150" t="n">
-        <v>101.7</v>
+        <v>6.826</v>
       </c>
       <c r="F150" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G150" t="n">
-        <v>101.7</v>
+        <v>61.43</v>
       </c>
       <c r="H150" t="n">
-        <v>1.61</v>
+        <v>5.28</v>
       </c>
       <c r="I150" t="n">
-        <v>1.61</v>
+        <v>9.4</v>
       </c>
       <c r="J150" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E152" t="n">
-        <v>23.045</v>
+        <v>104.12</v>
       </c>
       <c r="F152" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G152" t="n">
-        <v>69.14</v>
+        <v>104.12</v>
       </c>
       <c r="H152" t="n">
-        <v>3.47</v>
+        <v>4.03</v>
       </c>
       <c r="I152" t="n">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E153" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F153" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G153" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H153" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I153" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E154" t="n">
-        <v>39.915</v>
+        <v>6.893</v>
       </c>
       <c r="F154" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G154" t="n">
-        <v>159.66</v>
+        <v>62.04</v>
       </c>
       <c r="H154" t="n">
-        <v>20.64</v>
+        <v>5.89</v>
       </c>
       <c r="I154" t="n">
-        <v>14.85</v>
+        <v>10.49</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E155" t="n">
-        <v>6.893</v>
+        <v>11.034</v>
       </c>
       <c r="F155" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G155" t="n">
-        <v>62.04</v>
+        <v>33.1</v>
       </c>
       <c r="H155" t="n">
-        <v>5.89</v>
+        <v>1.94</v>
       </c>
       <c r="I155" t="n">
-        <v>10.49</v>
+        <v>6.23</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E156" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F156" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G156" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H156" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I156" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E162" t="n">
-        <v>38.845</v>
+        <v>10.748</v>
       </c>
       <c r="F162" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G162" t="n">
-        <v>155.38</v>
+        <v>32.24</v>
       </c>
       <c r="H162" t="n">
-        <v>16.36</v>
+        <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>11.77</v>
+        <v>3.47</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E163" t="n">
-        <v>23.01</v>
+        <v>103.84</v>
       </c>
       <c r="F163" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G163" t="n">
-        <v>69.03</v>
+        <v>103.84</v>
       </c>
       <c r="H163" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="I163" t="n">
-        <v>5.12</v>
+        <v>3.75</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D164" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E164" t="n">
-        <v>103.84</v>
+        <v>6.927</v>
       </c>
       <c r="F164" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G164" t="n">
-        <v>103.84</v>
+        <v>62.34</v>
       </c>
       <c r="H164" t="n">
-        <v>3.75</v>
+        <v>6.19</v>
       </c>
       <c r="I164" t="n">
-        <v>3.75</v>
+        <v>11.02</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E165" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F165" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G165" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H165" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I165" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E166" t="n">
-        <v>6.927</v>
+        <v>23.01</v>
       </c>
       <c r="F166" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G166" t="n">
-        <v>62.34</v>
+        <v>69.03</v>
       </c>
       <c r="H166" t="n">
-        <v>6.19</v>
+        <v>3.36</v>
       </c>
       <c r="I166" t="n">
-        <v>11.02</v>
+        <v>5.12</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E177" t="n">
-        <v>102.54</v>
+        <v>10.642</v>
       </c>
       <c r="F177" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G177" t="n">
-        <v>102.54</v>
+        <v>31.93</v>
       </c>
       <c r="H177" t="n">
-        <v>2.45</v>
+        <v>0.77</v>
       </c>
       <c r="I177" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D178" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E178" t="n">
-        <v>6.922</v>
+        <v>38.245</v>
       </c>
       <c r="F178" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G178" t="n">
-        <v>62.3</v>
+        <v>152.98</v>
       </c>
       <c r="H178" t="n">
-        <v>6.15</v>
+        <v>13.96</v>
       </c>
       <c r="I178" t="n">
-        <v>10.95</v>
+        <v>10.04</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E179" t="n">
-        <v>22.95</v>
+        <v>6.922</v>
       </c>
       <c r="F179" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G179" t="n">
-        <v>68.84999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H179" t="n">
-        <v>3.18</v>
+        <v>6.15</v>
       </c>
       <c r="I179" t="n">
-        <v>4.84</v>
+        <v>10.95</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E180" t="n">
-        <v>38.245</v>
+        <v>102.54</v>
       </c>
       <c r="F180" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G180" t="n">
-        <v>152.98</v>
+        <v>102.54</v>
       </c>
       <c r="H180" t="n">
-        <v>13.96</v>
+        <v>2.45</v>
       </c>
       <c r="I180" t="n">
-        <v>10.04</v>
+        <v>2.45</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E181" t="n">
-        <v>10.642</v>
+        <v>22.95</v>
       </c>
       <c r="F181" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G181" t="n">
-        <v>31.93</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>0.77</v>
+        <v>3.18</v>
       </c>
       <c r="I181" t="n">
-        <v>2.47</v>
+        <v>4.84</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E187" t="n">
-        <v>6.862</v>
+        <v>22.845</v>
       </c>
       <c r="F187" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G187" t="n">
-        <v>61.76</v>
+        <v>68.53</v>
       </c>
       <c r="H187" t="n">
-        <v>5.61</v>
+        <v>2.86</v>
       </c>
       <c r="I187" t="n">
-        <v>9.99</v>
+        <v>4.36</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E188" t="n">
-        <v>101.44</v>
+        <v>10.708</v>
       </c>
       <c r="F188" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G188" t="n">
-        <v>101.44</v>
+        <v>32.12</v>
       </c>
       <c r="H188" t="n">
-        <v>1.35</v>
+        <v>0.96</v>
       </c>
       <c r="I188" t="n">
-        <v>1.35</v>
+        <v>3.08</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E190" t="n">
-        <v>10.708</v>
+        <v>101.44</v>
       </c>
       <c r="F190" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G190" t="n">
-        <v>32.12</v>
+        <v>101.44</v>
       </c>
       <c r="H190" t="n">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>3.08</v>
+        <v>1.35</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D191" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E191" t="n">
-        <v>22.845</v>
+        <v>6.862</v>
       </c>
       <c r="F191" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G191" t="n">
-        <v>68.53</v>
+        <v>61.76</v>
       </c>
       <c r="H191" t="n">
-        <v>2.86</v>
+        <v>5.61</v>
       </c>
       <c r="I191" t="n">
-        <v>4.36</v>
+        <v>9.99</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E197" t="n">
-        <v>11.022</v>
+        <v>102.48</v>
       </c>
       <c r="F197" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G197" t="n">
-        <v>33.07</v>
+        <v>102.48</v>
       </c>
       <c r="H197" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="I197" t="n">
-        <v>6.13</v>
+        <v>2.39</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E198" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F198" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G198" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H198" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I198" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7176,29 +7176,29 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D199" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E199" t="n">
-        <v>22.6</v>
+        <v>6.909</v>
       </c>
       <c r="F199" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G199" t="n">
-        <v>67.8</v>
+        <v>62.18</v>
       </c>
       <c r="H199" t="n">
-        <v>2.13</v>
+        <v>6.03</v>
       </c>
       <c r="I199" t="n">
-        <v>3.24</v>
+        <v>10.74</v>
       </c>
       <c r="J199" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E200" t="n">
-        <v>102.48</v>
+        <v>11.022</v>
       </c>
       <c r="F200" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G200" t="n">
-        <v>102.48</v>
+        <v>33.07</v>
       </c>
       <c r="H200" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="I200" t="n">
-        <v>2.39</v>
+        <v>6.13</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D201" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E201" t="n">
-        <v>6.909</v>
+        <v>38.565</v>
       </c>
       <c r="F201" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G201" t="n">
-        <v>62.18</v>
+        <v>154.26</v>
       </c>
       <c r="H201" t="n">
-        <v>6.03</v>
+        <v>15.24</v>
       </c>
       <c r="I201" t="n">
-        <v>10.74</v>
+        <v>10.96</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E202" t="n">
-        <v>6.822</v>
+        <v>100.08</v>
       </c>
       <c r="F202" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G202" t="n">
-        <v>61.4</v>
+        <v>100.08</v>
       </c>
       <c r="H202" t="n">
-        <v>5.25</v>
+        <v>-0.01</v>
       </c>
       <c r="I202" t="n">
-        <v>9.35</v>
+        <v>-0.01</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E203" t="n">
-        <v>38.04</v>
+        <v>22.4</v>
       </c>
       <c r="F203" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G203" t="n">
-        <v>152.16</v>
+        <v>67.2</v>
       </c>
       <c r="H203" t="n">
-        <v>13.14</v>
+        <v>1.53</v>
       </c>
       <c r="I203" t="n">
-        <v>9.449999999999999</v>
+        <v>2.33</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7346,29 +7346,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D204" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E204" t="n">
-        <v>100.08</v>
+        <v>6.822</v>
       </c>
       <c r="F204" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G204" t="n">
-        <v>100.08</v>
+        <v>61.4</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.01</v>
+        <v>5.25</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.01</v>
+        <v>9.35</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E205" t="n">
-        <v>22.4</v>
+        <v>38.04</v>
       </c>
       <c r="F205" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G205" t="n">
-        <v>67.2</v>
+        <v>152.16</v>
       </c>
       <c r="H205" t="n">
-        <v>1.53</v>
+        <v>13.14</v>
       </c>
       <c r="I205" t="n">
-        <v>2.33</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E207" t="n">
-        <v>37.82</v>
+        <v>11.172</v>
       </c>
       <c r="F207" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G207" t="n">
-        <v>151.28</v>
+        <v>33.52</v>
       </c>
       <c r="H207" t="n">
-        <v>12.26</v>
+        <v>2.36</v>
       </c>
       <c r="I207" t="n">
-        <v>8.82</v>
+        <v>7.57</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E208" t="n">
-        <v>22.725</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G208" t="n">
-        <v>68.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H208" t="n">
-        <v>2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="I208" t="n">
-        <v>3.82</v>
+        <v>-0.19</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7516,29 +7516,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D209" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E209" t="n">
-        <v>99.90000000000001</v>
+        <v>6.865</v>
       </c>
       <c r="F209" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G209" t="n">
-        <v>99.90000000000001</v>
+        <v>61.79</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.19</v>
+        <v>5.64</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.19</v>
+        <v>10.04</v>
       </c>
       <c r="J209" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D210" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E210" t="n">
-        <v>11.172</v>
+        <v>37.82</v>
       </c>
       <c r="F210" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G210" t="n">
-        <v>33.52</v>
+        <v>151.28</v>
       </c>
       <c r="H210" t="n">
-        <v>2.36</v>
+        <v>12.26</v>
       </c>
       <c r="I210" t="n">
-        <v>7.57</v>
+        <v>8.82</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E211" t="n">
-        <v>6.865</v>
+        <v>22.725</v>
       </c>
       <c r="F211" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G211" t="n">
-        <v>61.79</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H211" t="n">
-        <v>5.64</v>
+        <v>2.51</v>
       </c>
       <c r="I211" t="n">
-        <v>10.04</v>
+        <v>3.82</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E217" t="n">
-        <v>6.864</v>
+        <v>23.175</v>
       </c>
       <c r="F217" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G217" t="n">
-        <v>61.78</v>
+        <v>69.53</v>
       </c>
       <c r="H217" t="n">
-        <v>5.63</v>
+        <v>3.86</v>
       </c>
       <c r="I217" t="n">
-        <v>10.03</v>
+        <v>5.88</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E218" t="n">
-        <v>11.546</v>
+        <v>36.75</v>
       </c>
       <c r="F218" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G218" t="n">
-        <v>34.64</v>
+        <v>147</v>
       </c>
       <c r="H218" t="n">
-        <v>3.48</v>
+        <v>7.98</v>
       </c>
       <c r="I218" t="n">
-        <v>11.17</v>
+        <v>5.74</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E219" t="n">
-        <v>36.75</v>
+        <v>98.02</v>
       </c>
       <c r="F219" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G219" t="n">
-        <v>147</v>
+        <v>98.02</v>
       </c>
       <c r="H219" t="n">
-        <v>7.98</v>
+        <v>-2.07</v>
       </c>
       <c r="I219" t="n">
-        <v>5.74</v>
+        <v>-2.07</v>
       </c>
       <c r="J219" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E220" t="n">
-        <v>23.175</v>
+        <v>6.864</v>
       </c>
       <c r="F220" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G220" t="n">
-        <v>69.53</v>
+        <v>61.78</v>
       </c>
       <c r="H220" t="n">
-        <v>3.86</v>
+        <v>5.63</v>
       </c>
       <c r="I220" t="n">
-        <v>5.88</v>
+        <v>10.03</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E221" t="n">
-        <v>98.02</v>
+        <v>11.546</v>
       </c>
       <c r="F221" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G221" t="n">
-        <v>98.02</v>
+        <v>34.64</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.07</v>
+        <v>3.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-2.07</v>
+        <v>11.17</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D232" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E232" t="n">
-        <v>6.812</v>
+        <v>37.44</v>
       </c>
       <c r="F232" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G232" t="n">
-        <v>61.31</v>
+        <v>149.76</v>
       </c>
       <c r="H232" t="n">
-        <v>5.16</v>
+        <v>10.74</v>
       </c>
       <c r="I232" t="n">
-        <v>9.19</v>
+        <v>7.73</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E233" t="n">
-        <v>97.86</v>
+        <v>23.17</v>
       </c>
       <c r="F233" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G233" t="n">
-        <v>97.86</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H233" t="n">
-        <v>-2.23</v>
+        <v>3.84</v>
       </c>
       <c r="I233" t="n">
-        <v>-2.23</v>
+        <v>5.85</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E235" t="n">
-        <v>23.17</v>
+        <v>97.86</v>
       </c>
       <c r="F235" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G235" t="n">
-        <v>69.51000000000001</v>
+        <v>97.86</v>
       </c>
       <c r="H235" t="n">
-        <v>3.84</v>
+        <v>-2.23</v>
       </c>
       <c r="I235" t="n">
-        <v>5.85</v>
+        <v>-2.23</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D236" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E236" t="n">
-        <v>37.44</v>
+        <v>6.812</v>
       </c>
       <c r="F236" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G236" t="n">
-        <v>149.76</v>
+        <v>61.31</v>
       </c>
       <c r="H236" t="n">
-        <v>10.74</v>
+        <v>5.16</v>
       </c>
       <c r="I236" t="n">
-        <v>7.73</v>
+        <v>9.19</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D242" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E242" t="n">
-        <v>12.08</v>
+        <v>38.52</v>
       </c>
       <c r="F242" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G242" t="n">
-        <v>36.24</v>
+        <v>154.08</v>
       </c>
       <c r="H242" t="n">
-        <v>5.08</v>
+        <v>15.06</v>
       </c>
       <c r="I242" t="n">
-        <v>16.3</v>
+        <v>10.83</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D243" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E243" t="n">
-        <v>7.005</v>
+        <v>23.465</v>
       </c>
       <c r="F243" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G243" t="n">
-        <v>63.05</v>
+        <v>70.39</v>
       </c>
       <c r="H243" t="n">
-        <v>6.9</v>
+        <v>4.72</v>
       </c>
       <c r="I243" t="n">
-        <v>12.29</v>
+        <v>7.19</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8706,29 +8706,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E244" t="n">
-        <v>23.465</v>
+        <v>102.86</v>
       </c>
       <c r="F244" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G244" t="n">
-        <v>70.39</v>
+        <v>102.86</v>
       </c>
       <c r="H244" t="n">
-        <v>4.72</v>
+        <v>2.77</v>
       </c>
       <c r="I244" t="n">
-        <v>7.19</v>
+        <v>2.77</v>
       </c>
       <c r="J244" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E245" t="n">
-        <v>38.52</v>
+        <v>12.08</v>
       </c>
       <c r="F245" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G245" t="n">
-        <v>154.08</v>
+        <v>36.24</v>
       </c>
       <c r="H245" t="n">
-        <v>15.06</v>
+        <v>5.08</v>
       </c>
       <c r="I245" t="n">
-        <v>10.83</v>
+        <v>16.3</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D246" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E246" t="n">
-        <v>102.86</v>
+        <v>7.005</v>
       </c>
       <c r="F246" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G246" t="n">
-        <v>102.86</v>
+        <v>63.05</v>
       </c>
       <c r="H246" t="n">
-        <v>2.77</v>
+        <v>6.9</v>
       </c>
       <c r="I246" t="n">
-        <v>2.77</v>
+        <v>12.29</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E257" t="n">
-        <v>37.84</v>
+        <v>23.2</v>
       </c>
       <c r="F257" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G257" t="n">
-        <v>151.36</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>12.34</v>
+        <v>3.93</v>
       </c>
       <c r="I257" t="n">
-        <v>8.880000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D258" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E258" t="n">
-        <v>12.232</v>
+        <v>7.056</v>
       </c>
       <c r="F258" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G258" t="n">
-        <v>36.7</v>
+        <v>63.5</v>
       </c>
       <c r="H258" t="n">
-        <v>5.54</v>
+        <v>7.35</v>
       </c>
       <c r="I258" t="n">
-        <v>17.78</v>
+        <v>13.09</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E259" t="n">
-        <v>7.056</v>
+        <v>103.02</v>
       </c>
       <c r="F259" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G259" t="n">
-        <v>63.5</v>
+        <v>103.02</v>
       </c>
       <c r="H259" t="n">
-        <v>7.35</v>
+        <v>2.93</v>
       </c>
       <c r="I259" t="n">
-        <v>13.09</v>
+        <v>2.93</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D260" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E260" t="n">
-        <v>23.2</v>
+        <v>37.84</v>
       </c>
       <c r="F260" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G260" t="n">
-        <v>69.59999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="H260" t="n">
-        <v>3.93</v>
+        <v>12.34</v>
       </c>
       <c r="I260" t="n">
-        <v>5.98</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D261" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E261" t="n">
-        <v>103.02</v>
+        <v>12.232</v>
       </c>
       <c r="F261" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G261" t="n">
-        <v>103.02</v>
+        <v>36.7</v>
       </c>
       <c r="H261" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="I261" t="n">
-        <v>2.93</v>
+        <v>17.78</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9488,29 +9488,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E267" t="n">
-        <v>12.388</v>
+        <v>103.36</v>
       </c>
       <c r="F267" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G267" t="n">
-        <v>37.16</v>
+        <v>103.36</v>
       </c>
       <c r="H267" t="n">
-        <v>6</v>
+        <v>3.27</v>
       </c>
       <c r="I267" t="n">
-        <v>19.26</v>
+        <v>3.27</v>
       </c>
       <c r="J267" t="n">
         <v>7.91</v>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D268" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E268" t="n">
-        <v>7.06</v>
+        <v>38.865</v>
       </c>
       <c r="F268" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G268" t="n">
-        <v>63.54</v>
+        <v>155.46</v>
       </c>
       <c r="H268" t="n">
-        <v>7.39</v>
+        <v>16.44</v>
       </c>
       <c r="I268" t="n">
-        <v>13.16</v>
+        <v>11.83</v>
       </c>
       <c r="J268" t="n">
         <v>7.91</v>
@@ -9556,29 +9556,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D269" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E269" t="n">
-        <v>38.865</v>
+        <v>23.12</v>
       </c>
       <c r="F269" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G269" t="n">
-        <v>155.46</v>
+        <v>69.36</v>
       </c>
       <c r="H269" t="n">
-        <v>16.44</v>
+        <v>3.69</v>
       </c>
       <c r="I269" t="n">
-        <v>11.83</v>
+        <v>5.62</v>
       </c>
       <c r="J269" t="n">
         <v>7.91</v>
@@ -9590,29 +9590,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D270" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E270" t="n">
-        <v>103.36</v>
+        <v>12.388</v>
       </c>
       <c r="F270" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G270" t="n">
-        <v>103.36</v>
+        <v>37.16</v>
       </c>
       <c r="H270" t="n">
-        <v>3.27</v>
+        <v>6</v>
       </c>
       <c r="I270" t="n">
-        <v>3.27</v>
+        <v>19.26</v>
       </c>
       <c r="J270" t="n">
         <v>7.91</v>
@@ -9624,29 +9624,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D271" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E271" t="n">
-        <v>23.12</v>
+        <v>7.06</v>
       </c>
       <c r="F271" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G271" t="n">
-        <v>69.36</v>
+        <v>63.54</v>
       </c>
       <c r="H271" t="n">
-        <v>3.69</v>
+        <v>7.39</v>
       </c>
       <c r="I271" t="n">
-        <v>5.62</v>
+        <v>13.16</v>
       </c>
       <c r="J271" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D282" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E282" t="n">
-        <v>12.468</v>
+        <v>7.054</v>
       </c>
       <c r="F282" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G282" t="n">
-        <v>37.4</v>
+        <v>63.49</v>
       </c>
       <c r="H282" t="n">
-        <v>6.24</v>
+        <v>7.34</v>
       </c>
       <c r="I282" t="n">
-        <v>20.03</v>
+        <v>13.07</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E283" t="n">
-        <v>22.97</v>
+        <v>104.46</v>
       </c>
       <c r="F283" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G283" t="n">
-        <v>68.91</v>
+        <v>104.46</v>
       </c>
       <c r="H283" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="I283" t="n">
-        <v>4.93</v>
+        <v>4.37</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D284" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E284" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F284" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G284" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H284" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I284" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D285" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E285" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F285" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G285" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H285" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I285" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D286" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E286" t="n">
-        <v>39.745</v>
+        <v>22.97</v>
       </c>
       <c r="F286" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G286" t="n">
-        <v>158.98</v>
+        <v>68.91</v>
       </c>
       <c r="H286" t="n">
-        <v>19.96</v>
+        <v>3.24</v>
       </c>
       <c r="I286" t="n">
-        <v>14.36</v>
+        <v>4.93</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D297" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E297" t="n">
-        <v>6.915</v>
+        <v>22.78</v>
       </c>
       <c r="F297" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G297" t="n">
-        <v>62.23</v>
+        <v>68.34</v>
       </c>
       <c r="H297" t="n">
-        <v>6.08</v>
+        <v>2.67</v>
       </c>
       <c r="I297" t="n">
-        <v>10.83</v>
+        <v>4.07</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D298" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E298" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F298" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G298" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H298" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I298" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D300" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E300" t="n">
-        <v>38.49</v>
+        <v>6.915</v>
       </c>
       <c r="F300" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G300" t="n">
-        <v>153.96</v>
+        <v>62.23</v>
       </c>
       <c r="H300" t="n">
-        <v>14.94</v>
+        <v>6.08</v>
       </c>
       <c r="I300" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E301" t="n">
-        <v>22.78</v>
+        <v>100.42</v>
       </c>
       <c r="F301" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G301" t="n">
-        <v>68.34</v>
+        <v>100.42</v>
       </c>
       <c r="H301" t="n">
-        <v>2.67</v>
+        <v>0.33</v>
       </c>
       <c r="I301" t="n">
-        <v>4.07</v>
+        <v>0.33</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D312" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E312" t="n">
-        <v>6.936</v>
+        <v>38.66</v>
       </c>
       <c r="F312" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G312" t="n">
-        <v>62.42</v>
+        <v>154.64</v>
       </c>
       <c r="H312" t="n">
-        <v>6.27</v>
+        <v>15.62</v>
       </c>
       <c r="I312" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D313" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E313" t="n">
-        <v>100.38</v>
+        <v>11.742</v>
       </c>
       <c r="F313" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G313" t="n">
-        <v>100.38</v>
+        <v>35.23</v>
       </c>
       <c r="H313" t="n">
-        <v>0.29</v>
+        <v>4.07</v>
       </c>
       <c r="I313" t="n">
-        <v>0.29</v>
+        <v>13.06</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11086,29 +11086,29 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C314" t="n">
         <v>3</v>
       </c>
       <c r="D314" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E314" t="n">
-        <v>11.742</v>
+        <v>22.9</v>
       </c>
       <c r="F314" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G314" t="n">
-        <v>35.23</v>
+        <v>68.7</v>
       </c>
       <c r="H314" t="n">
-        <v>4.07</v>
+        <v>3.03</v>
       </c>
       <c r="I314" t="n">
-        <v>13.06</v>
+        <v>4.61</v>
       </c>
       <c r="J314" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D315" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E315" t="n">
-        <v>22.9</v>
+        <v>6.936</v>
       </c>
       <c r="F315" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G315" t="n">
-        <v>68.7</v>
+        <v>62.42</v>
       </c>
       <c r="H315" t="n">
-        <v>3.03</v>
+        <v>6.27</v>
       </c>
       <c r="I315" t="n">
-        <v>4.61</v>
+        <v>11.17</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E316" t="n">
-        <v>38.66</v>
+        <v>100.38</v>
       </c>
       <c r="F316" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G316" t="n">
-        <v>154.64</v>
+        <v>100.38</v>
       </c>
       <c r="H316" t="n">
-        <v>15.62</v>
+        <v>0.29</v>
       </c>
       <c r="I316" t="n">
-        <v>11.24</v>
+        <v>0.29</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D327" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E327" t="n">
-        <v>102.72</v>
+        <v>39.38</v>
       </c>
       <c r="F327" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G327" t="n">
-        <v>102.72</v>
+        <v>157.52</v>
       </c>
       <c r="H327" t="n">
-        <v>2.63</v>
+        <v>18.5</v>
       </c>
       <c r="I327" t="n">
-        <v>2.63</v>
+        <v>13.31</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C328" t="n">
         <v>3</v>
       </c>
       <c r="D328" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E328" t="n">
-        <v>11.708</v>
+        <v>22.83</v>
       </c>
       <c r="F328" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G328" t="n">
-        <v>35.12</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H328" t="n">
-        <v>3.96</v>
+        <v>2.82</v>
       </c>
       <c r="I328" t="n">
-        <v>12.71</v>
+        <v>4.29</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11596,29 +11596,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E329" t="n">
-        <v>7.027</v>
+        <v>102.72</v>
       </c>
       <c r="F329" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G329" t="n">
-        <v>63.24</v>
+        <v>102.72</v>
       </c>
       <c r="H329" t="n">
-        <v>7.09</v>
+        <v>2.63</v>
       </c>
       <c r="I329" t="n">
-        <v>12.63</v>
+        <v>2.63</v>
       </c>
       <c r="J329" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C330" t="n">
         <v>3</v>
       </c>
       <c r="D330" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E330" t="n">
-        <v>22.83</v>
+        <v>11.708</v>
       </c>
       <c r="F330" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G330" t="n">
-        <v>68.48999999999999</v>
+        <v>35.12</v>
       </c>
       <c r="H330" t="n">
-        <v>2.82</v>
+        <v>3.96</v>
       </c>
       <c r="I330" t="n">
-        <v>4.29</v>
+        <v>12.71</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D331" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E331" t="n">
-        <v>39.38</v>
+        <v>7.027</v>
       </c>
       <c r="F331" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G331" t="n">
-        <v>157.52</v>
+        <v>63.24</v>
       </c>
       <c r="H331" t="n">
-        <v>18.5</v>
+        <v>7.09</v>
       </c>
       <c r="I331" t="n">
-        <v>13.31</v>
+        <v>12.63</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D337" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E337" t="n">
-        <v>101.04</v>
+        <v>22.845</v>
       </c>
       <c r="F337" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G337" t="n">
-        <v>101.04</v>
+        <v>68.53</v>
       </c>
       <c r="H337" t="n">
-        <v>0.95</v>
+        <v>2.86</v>
       </c>
       <c r="I337" t="n">
-        <v>0.95</v>
+        <v>4.36</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D338" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E338" t="n">
-        <v>39.15</v>
+        <v>6.938</v>
       </c>
       <c r="F338" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G338" t="n">
-        <v>156.6</v>
+        <v>62.44</v>
       </c>
       <c r="H338" t="n">
-        <v>17.58</v>
+        <v>6.29</v>
       </c>
       <c r="I338" t="n">
-        <v>12.65</v>
+        <v>11.2</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E339" t="n">
-        <v>6.938</v>
+        <v>11.284</v>
       </c>
       <c r="F339" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G339" t="n">
-        <v>62.44</v>
+        <v>33.85</v>
       </c>
       <c r="H339" t="n">
-        <v>6.29</v>
+        <v>2.69</v>
       </c>
       <c r="I339" t="n">
-        <v>11.2</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E340" t="n">
-        <v>22.845</v>
+        <v>101.04</v>
       </c>
       <c r="F340" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G340" t="n">
-        <v>68.53</v>
+        <v>101.04</v>
       </c>
       <c r="H340" t="n">
-        <v>2.86</v>
+        <v>0.95</v>
       </c>
       <c r="I340" t="n">
-        <v>4.36</v>
+        <v>0.95</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D341" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E341" t="n">
-        <v>11.284</v>
+        <v>39.15</v>
       </c>
       <c r="F341" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G341" t="n">
-        <v>33.85</v>
+        <v>156.6</v>
       </c>
       <c r="H341" t="n">
-        <v>2.69</v>
+        <v>17.58</v>
       </c>
       <c r="I341" t="n">
-        <v>8.630000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12038,29 +12038,29 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D342" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E342" t="n">
-        <v>100.84</v>
+        <v>6.95</v>
       </c>
       <c r="F342" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G342" t="n">
-        <v>100.84</v>
+        <v>62.55</v>
       </c>
       <c r="H342" t="n">
-        <v>0.75</v>
+        <v>6.4</v>
       </c>
       <c r="I342" t="n">
-        <v>0.75</v>
+        <v>11.4</v>
       </c>
       <c r="J342" t="n">
         <v>7.91</v>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C343" t="n">
         <v>3</v>
       </c>
       <c r="D343" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E343" t="n">
-        <v>11.264</v>
+        <v>22.89</v>
       </c>
       <c r="F343" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G343" t="n">
-        <v>33.79</v>
+        <v>68.67</v>
       </c>
       <c r="H343" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="I343" t="n">
-        <v>8.44</v>
+        <v>4.57</v>
       </c>
       <c r="J343" t="n">
         <v>7.91</v>
@@ -12106,29 +12106,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D344" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E344" t="n">
-        <v>38.99</v>
+        <v>100.84</v>
       </c>
       <c r="F344" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G344" t="n">
-        <v>155.96</v>
+        <v>100.84</v>
       </c>
       <c r="H344" t="n">
-        <v>16.94</v>
+        <v>0.75</v>
       </c>
       <c r="I344" t="n">
-        <v>12.19</v>
+        <v>0.75</v>
       </c>
       <c r="J344" t="n">
         <v>7.91</v>
@@ -12140,29 +12140,29 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C345" t="n">
         <v>3</v>
       </c>
       <c r="D345" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E345" t="n">
-        <v>22.89</v>
+        <v>11.264</v>
       </c>
       <c r="F345" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G345" t="n">
-        <v>68.67</v>
+        <v>33.79</v>
       </c>
       <c r="H345" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="I345" t="n">
-        <v>4.57</v>
+        <v>8.44</v>
       </c>
       <c r="J345" t="n">
         <v>7.91</v>
@@ -12174,29 +12174,29 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D346" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E346" t="n">
-        <v>6.95</v>
+        <v>38.99</v>
       </c>
       <c r="F346" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G346" t="n">
-        <v>62.55</v>
+        <v>155.96</v>
       </c>
       <c r="H346" t="n">
-        <v>6.4</v>
+        <v>16.94</v>
       </c>
       <c r="I346" t="n">
-        <v>11.4</v>
+        <v>12.19</v>
       </c>
       <c r="J346" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D352" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E352" t="n">
-        <v>11.186</v>
+        <v>6.983</v>
       </c>
       <c r="F352" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G352" t="n">
-        <v>33.56</v>
+        <v>62.85</v>
       </c>
       <c r="H352" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="I352" t="n">
-        <v>7.7</v>
+        <v>11.93</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D353" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E353" t="n">
-        <v>101.76</v>
+        <v>22.75</v>
       </c>
       <c r="F353" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G353" t="n">
-        <v>101.76</v>
+        <v>68.25</v>
       </c>
       <c r="H353" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="I353" t="n">
-        <v>1.67</v>
+        <v>3.93</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D354" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E354" t="n">
-        <v>39.745</v>
+        <v>11.186</v>
       </c>
       <c r="F354" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G354" t="n">
-        <v>158.98</v>
+        <v>33.56</v>
       </c>
       <c r="H354" t="n">
-        <v>19.96</v>
+        <v>2.4</v>
       </c>
       <c r="I354" t="n">
-        <v>14.36</v>
+        <v>7.7</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E355" t="n">
-        <v>6.983</v>
+        <v>101.76</v>
       </c>
       <c r="F355" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G355" t="n">
-        <v>62.85</v>
+        <v>101.76</v>
       </c>
       <c r="H355" t="n">
-        <v>6.7</v>
+        <v>1.67</v>
       </c>
       <c r="I355" t="n">
-        <v>11.93</v>
+        <v>1.67</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D356" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E356" t="n">
-        <v>22.75</v>
+        <v>39.745</v>
       </c>
       <c r="F356" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G356" t="n">
-        <v>68.25</v>
+        <v>158.98</v>
       </c>
       <c r="H356" t="n">
-        <v>2.58</v>
+        <v>19.96</v>
       </c>
       <c r="I356" t="n">
-        <v>3.93</v>
+        <v>14.36</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D367" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E367" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F367" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G367" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H367" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I367" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C368" t="n">
         <v>3</v>
       </c>
       <c r="D368" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E368" t="n">
-        <v>22.275</v>
+        <v>10.91</v>
       </c>
       <c r="F368" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G368" t="n">
-        <v>66.81999999999999</v>
+        <v>32.73</v>
       </c>
       <c r="H368" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="I368" t="n">
-        <v>1.75</v>
+        <v>5.04</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12956,29 +12956,29 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D369" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E369" t="n">
-        <v>6.91</v>
+        <v>22.275</v>
       </c>
       <c r="F369" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G369" t="n">
-        <v>62.19</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H369" t="n">
-        <v>6.04</v>
+        <v>1.15</v>
       </c>
       <c r="I369" t="n">
-        <v>10.76</v>
+        <v>1.75</v>
       </c>
       <c r="J369" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D370" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E370" t="n">
-        <v>101.5</v>
+        <v>39.935</v>
       </c>
       <c r="F370" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G370" t="n">
-        <v>101.5</v>
+        <v>159.74</v>
       </c>
       <c r="H370" t="n">
-        <v>1.41</v>
+        <v>20.72</v>
       </c>
       <c r="I370" t="n">
-        <v>1.41</v>
+        <v>14.9</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E371" t="n">
-        <v>10.91</v>
+        <v>6.91</v>
       </c>
       <c r="F371" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G371" t="n">
-        <v>32.73</v>
+        <v>62.19</v>
       </c>
       <c r="H371" t="n">
-        <v>1.57</v>
+        <v>6.04</v>
       </c>
       <c r="I371" t="n">
-        <v>5.04</v>
+        <v>10.76</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D377" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E377" t="n">
-        <v>101.88</v>
+        <v>6.941</v>
       </c>
       <c r="F377" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G377" t="n">
-        <v>101.88</v>
+        <v>62.47</v>
       </c>
       <c r="H377" t="n">
-        <v>1.79</v>
+        <v>6.32</v>
       </c>
       <c r="I377" t="n">
-        <v>1.79</v>
+        <v>11.26</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D378" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E378" t="n">
-        <v>39.57</v>
+        <v>22.13</v>
       </c>
       <c r="F378" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G378" t="n">
-        <v>158.28</v>
+        <v>66.39</v>
       </c>
       <c r="H378" t="n">
-        <v>19.26</v>
+        <v>0.72</v>
       </c>
       <c r="I378" t="n">
-        <v>13.85</v>
+        <v>1.1</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C379" t="n">
         <v>3</v>
       </c>
       <c r="D379" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E379" t="n">
-        <v>22.13</v>
+        <v>10.962</v>
       </c>
       <c r="F379" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G379" t="n">
-        <v>66.39</v>
+        <v>32.89</v>
       </c>
       <c r="H379" t="n">
-        <v>0.72</v>
+        <v>1.73</v>
       </c>
       <c r="I379" t="n">
-        <v>1.1</v>
+        <v>5.55</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D380" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E380" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F380" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G380" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H380" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I380" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D381" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E381" t="n">
-        <v>10.962</v>
+        <v>39.57</v>
       </c>
       <c r="F381" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G381" t="n">
-        <v>32.89</v>
+        <v>158.28</v>
       </c>
       <c r="H381" t="n">
-        <v>1.73</v>
+        <v>19.26</v>
       </c>
       <c r="I381" t="n">
-        <v>5.55</v>
+        <v>13.85</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13738,29 +13738,29 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D392" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E392" t="n">
-        <v>101.52</v>
+        <v>6.931</v>
       </c>
       <c r="F392" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G392" t="n">
-        <v>101.52</v>
+        <v>62.38</v>
       </c>
       <c r="H392" t="n">
-        <v>1.43</v>
+        <v>6.23</v>
       </c>
       <c r="I392" t="n">
-        <v>1.43</v>
+        <v>11.1</v>
       </c>
       <c r="J392" t="n">
         <v>7.91</v>
@@ -13772,29 +13772,29 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D393" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E393" t="n">
-        <v>11.1</v>
+        <v>38.92</v>
       </c>
       <c r="F393" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G393" t="n">
-        <v>33.3</v>
+        <v>155.68</v>
       </c>
       <c r="H393" t="n">
-        <v>2.14</v>
+        <v>16.66</v>
       </c>
       <c r="I393" t="n">
-        <v>6.87</v>
+        <v>11.98</v>
       </c>
       <c r="J393" t="n">
         <v>7.91</v>
@@ -13806,29 +13806,29 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D394" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E394" t="n">
-        <v>38.92</v>
+        <v>21.845</v>
       </c>
       <c r="F394" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G394" t="n">
-        <v>155.68</v>
+        <v>65.53</v>
       </c>
       <c r="H394" t="n">
-        <v>16.66</v>
+        <v>-0.14</v>
       </c>
       <c r="I394" t="n">
-        <v>11.98</v>
+        <v>-0.21</v>
       </c>
       <c r="J394" t="n">
         <v>7.91</v>
@@ -13840,29 +13840,29 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D395" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E395" t="n">
-        <v>21.845</v>
+        <v>101.52</v>
       </c>
       <c r="F395" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G395" t="n">
-        <v>65.53</v>
+        <v>101.52</v>
       </c>
       <c r="H395" t="n">
-        <v>-0.14</v>
+        <v>1.43</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.21</v>
+        <v>1.43</v>
       </c>
       <c r="J395" t="n">
         <v>7.91</v>
@@ -13874,29 +13874,29 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D396" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E396" t="n">
-        <v>6.931</v>
+        <v>11.1</v>
       </c>
       <c r="F396" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G396" t="n">
-        <v>62.38</v>
+        <v>33.3</v>
       </c>
       <c r="H396" t="n">
-        <v>6.23</v>
+        <v>2.14</v>
       </c>
       <c r="I396" t="n">
-        <v>11.1</v>
+        <v>6.87</v>
       </c>
       <c r="J396" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D407" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E407" t="n">
-        <v>105.98</v>
+        <v>40.695</v>
       </c>
       <c r="F407" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G407" t="n">
-        <v>105.98</v>
+        <v>162.78</v>
       </c>
       <c r="H407" t="n">
-        <v>5.89</v>
+        <v>23.76</v>
       </c>
       <c r="I407" t="n">
-        <v>5.88</v>
+        <v>17.09</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C408" t="n">
         <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E408" t="n">
-        <v>22.35</v>
+        <v>11.232</v>
       </c>
       <c r="F408" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G408" t="n">
-        <v>67.05</v>
+        <v>33.7</v>
       </c>
       <c r="H408" t="n">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="I408" t="n">
-        <v>2.1</v>
+        <v>8.15</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D409" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E409" t="n">
-        <v>7.049</v>
+        <v>22.35</v>
       </c>
       <c r="F409" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G409" t="n">
-        <v>63.44</v>
+        <v>67.05</v>
       </c>
       <c r="H409" t="n">
-        <v>7.29</v>
+        <v>1.38</v>
       </c>
       <c r="I409" t="n">
-        <v>12.98</v>
+        <v>2.1</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D410" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E410" t="n">
-        <v>11.232</v>
+        <v>105.98</v>
       </c>
       <c r="F410" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G410" t="n">
-        <v>33.7</v>
+        <v>105.98</v>
       </c>
       <c r="H410" t="n">
-        <v>2.54</v>
+        <v>5.89</v>
       </c>
       <c r="I410" t="n">
-        <v>8.15</v>
+        <v>5.88</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14384,29 +14384,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D411" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E411" t="n">
-        <v>40.695</v>
+        <v>7.049</v>
       </c>
       <c r="F411" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G411" t="n">
-        <v>162.78</v>
+        <v>63.44</v>
       </c>
       <c r="H411" t="n">
-        <v>23.76</v>
+        <v>7.29</v>
       </c>
       <c r="I411" t="n">
-        <v>17.09</v>
+        <v>12.98</v>
       </c>
       <c r="J411" t="n">
         <v>7.91</v>
@@ -14579,6 +14579,176 @@
         <v>13.7</v>
       </c>
       <c r="J416" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>3</v>
+      </c>
+      <c r="D417" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E417" t="n">
+        <v>11.338</v>
+      </c>
+      <c r="F417" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G417" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="H417" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I417" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J417" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>4</v>
+      </c>
+      <c r="D418" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E418" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="F418" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G418" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="H418" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I418" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J418" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>3</v>
+      </c>
+      <c r="D419" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E419" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="F419" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G419" t="n">
+        <v>67.41</v>
+      </c>
+      <c r="H419" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I419" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J419" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D420" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E420" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="F420" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G420" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="H420" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="I420" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J420" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>9</v>
+      </c>
+      <c r="D421" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E421" t="n">
+        <v>7.079</v>
+      </c>
+      <c r="F421" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G421" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="H421" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="I421" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="J421" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J421"/>
+  <dimension ref="A1:J426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E12" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F12" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G12" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H12" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I12" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E13" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F13" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G13" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E14" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F14" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G14" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H14" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E15" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F15" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G15" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I15" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E16" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F16" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G16" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H16" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E27" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F27" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G27" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E28" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F28" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G28" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H28" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E29" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F29" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G29" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H29" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E30" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F30" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G30" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E31" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F31" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G31" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H31" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I31" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E37" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F37" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G37" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E38" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F38" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G38" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H38" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I38" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E39" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F39" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G39" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H39" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E40" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F40" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G40" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H40" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I40" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E41" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F41" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G41" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H41" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I41" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E52" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F52" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G52" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H52" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I52" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E53" t="n">
-        <v>6.629</v>
+        <v>21.703</v>
       </c>
       <c r="F53" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G53" t="n">
-        <v>59.66</v>
+        <v>65.11</v>
       </c>
       <c r="H53" t="n">
-        <v>3.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>6.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E54" t="n">
-        <v>21.703</v>
+        <v>10.702</v>
       </c>
       <c r="F54" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G54" t="n">
-        <v>65.11</v>
+        <v>32.11</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.85</v>
+        <v>3.05</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E55" t="n">
-        <v>10.702</v>
+        <v>38.544</v>
       </c>
       <c r="F55" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G55" t="n">
-        <v>32.11</v>
+        <v>154.18</v>
       </c>
       <c r="H55" t="n">
-        <v>0.95</v>
+        <v>15.16</v>
       </c>
       <c r="I55" t="n">
-        <v>3.05</v>
+        <v>10.9</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E56" t="n">
-        <v>100.34</v>
+        <v>6.629</v>
       </c>
       <c r="F56" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G56" t="n">
-        <v>100.34</v>
+        <v>59.66</v>
       </c>
       <c r="H56" t="n">
-        <v>0.25</v>
+        <v>3.51</v>
       </c>
       <c r="I56" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E62" t="n">
-        <v>10.712</v>
+        <v>41.064</v>
       </c>
       <c r="F62" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G62" t="n">
-        <v>32.14</v>
+        <v>164.26</v>
       </c>
       <c r="H62" t="n">
-        <v>0.98</v>
+        <v>25.24</v>
       </c>
       <c r="I62" t="n">
-        <v>3.15</v>
+        <v>18.16</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E63" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F63" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G63" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H63" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I63" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E64" t="n">
-        <v>6.817</v>
+        <v>22.7</v>
       </c>
       <c r="F64" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G64" t="n">
-        <v>61.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="I64" t="n">
-        <v>9.26</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E65" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F65" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G65" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H65" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E66" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F66" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G66" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H66" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I66" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E72" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F72" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G72" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H72" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I72" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E73" t="n">
-        <v>104.22</v>
+        <v>6.811</v>
       </c>
       <c r="F73" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G73" t="n">
-        <v>104.22</v>
+        <v>61.3</v>
       </c>
       <c r="H73" t="n">
-        <v>4.13</v>
+        <v>5.15</v>
       </c>
       <c r="I73" t="n">
-        <v>4.13</v>
+        <v>9.17</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2926,29 +2926,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E74" t="n">
-        <v>23</v>
+        <v>104.22</v>
       </c>
       <c r="F74" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G74" t="n">
-        <v>69</v>
+        <v>104.22</v>
       </c>
       <c r="H74" t="n">
-        <v>3.33</v>
+        <v>4.13</v>
       </c>
       <c r="I74" t="n">
-        <v>5.07</v>
+        <v>4.13</v>
       </c>
       <c r="J74" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E75" t="n">
-        <v>41.15</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G75" t="n">
-        <v>164.6</v>
+        <v>69</v>
       </c>
       <c r="H75" t="n">
-        <v>25.58</v>
+        <v>3.33</v>
       </c>
       <c r="I75" t="n">
-        <v>18.4</v>
+        <v>5.07</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E77" t="n">
-        <v>23.4</v>
+        <v>105.8</v>
       </c>
       <c r="F77" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G77" t="n">
-        <v>70.2</v>
+        <v>105.8</v>
       </c>
       <c r="H77" t="n">
-        <v>4.53</v>
+        <v>5.71</v>
       </c>
       <c r="I77" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E78" t="n">
-        <v>42.25</v>
+        <v>10.958</v>
       </c>
       <c r="F78" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G78" t="n">
-        <v>169</v>
+        <v>32.87</v>
       </c>
       <c r="H78" t="n">
-        <v>29.98</v>
+        <v>1.71</v>
       </c>
       <c r="I78" t="n">
-        <v>21.57</v>
+        <v>5.49</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3096,29 +3096,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D79" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E79" t="n">
-        <v>10.958</v>
+        <v>6.836</v>
       </c>
       <c r="F79" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G79" t="n">
-        <v>32.87</v>
+        <v>61.52</v>
       </c>
       <c r="H79" t="n">
-        <v>1.71</v>
+        <v>5.37</v>
       </c>
       <c r="I79" t="n">
-        <v>5.49</v>
+        <v>9.56</v>
       </c>
       <c r="J79" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E80" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F80" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G80" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H80" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I80" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E81" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F81" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G81" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H81" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E87" t="n">
-        <v>6.856</v>
+        <v>106.28</v>
       </c>
       <c r="F87" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G87" t="n">
-        <v>61.7</v>
+        <v>106.28</v>
       </c>
       <c r="H87" t="n">
-        <v>5.55</v>
+        <v>6.19</v>
       </c>
       <c r="I87" t="n">
-        <v>9.880000000000001</v>
+        <v>6.18</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D88" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E88" t="n">
-        <v>23.32</v>
+        <v>6.856</v>
       </c>
       <c r="F88" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G88" t="n">
-        <v>69.95999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="H88" t="n">
-        <v>4.29</v>
+        <v>5.55</v>
       </c>
       <c r="I88" t="n">
-        <v>6.53</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E89" t="n">
-        <v>43.005</v>
+        <v>23.32</v>
       </c>
       <c r="F89" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G89" t="n">
-        <v>172.02</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>33</v>
+        <v>4.29</v>
       </c>
       <c r="I89" t="n">
-        <v>23.74</v>
+        <v>6.53</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E90" t="n">
-        <v>10.852</v>
+        <v>43.005</v>
       </c>
       <c r="F90" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G90" t="n">
-        <v>32.56</v>
+        <v>172.02</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4</v>
+        <v>33</v>
       </c>
       <c r="I90" t="n">
-        <v>4.49</v>
+        <v>23.74</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E91" t="n">
-        <v>106.28</v>
+        <v>10.852</v>
       </c>
       <c r="F91" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G91" t="n">
-        <v>106.28</v>
+        <v>32.56</v>
       </c>
       <c r="H91" t="n">
-        <v>6.19</v>
+        <v>1.4</v>
       </c>
       <c r="I91" t="n">
-        <v>6.18</v>
+        <v>4.49</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E92" t="n">
-        <v>6.797</v>
+        <v>23.025</v>
       </c>
       <c r="F92" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G92" t="n">
-        <v>61.17</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>5.02</v>
+        <v>3.4</v>
       </c>
       <c r="I92" t="n">
-        <v>8.94</v>
+        <v>5.18</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E93" t="n">
-        <v>10.876</v>
+        <v>103.88</v>
       </c>
       <c r="F93" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G93" t="n">
-        <v>32.63</v>
+        <v>103.88</v>
       </c>
       <c r="H93" t="n">
-        <v>1.47</v>
+        <v>3.79</v>
       </c>
       <c r="I93" t="n">
-        <v>4.72</v>
+        <v>3.79</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E94" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F94" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G94" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H94" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I94" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E95" t="n">
-        <v>103.88</v>
+        <v>6.797</v>
       </c>
       <c r="F95" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G95" t="n">
-        <v>103.88</v>
+        <v>61.17</v>
       </c>
       <c r="H95" t="n">
-        <v>3.79</v>
+        <v>5.02</v>
       </c>
       <c r="I95" t="n">
-        <v>3.79</v>
+        <v>8.94</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3674,29 +3674,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E96" t="n">
-        <v>23.025</v>
+        <v>40.575</v>
       </c>
       <c r="F96" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G96" t="n">
-        <v>69.06999999999999</v>
+        <v>162.3</v>
       </c>
       <c r="H96" t="n">
-        <v>3.4</v>
+        <v>23.28</v>
       </c>
       <c r="I96" t="n">
-        <v>5.18</v>
+        <v>16.75</v>
       </c>
       <c r="J96" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E97" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F97" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G97" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H97" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E98" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F98" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G98" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H98" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I98" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E99" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F99" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G99" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H99" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I99" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E100" t="n">
-        <v>23.35</v>
+        <v>40.65</v>
       </c>
       <c r="F100" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G100" t="n">
-        <v>70.05</v>
+        <v>162.6</v>
       </c>
       <c r="H100" t="n">
-        <v>4.38</v>
+        <v>23.58</v>
       </c>
       <c r="I100" t="n">
-        <v>6.67</v>
+        <v>16.96</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E101" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F101" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G101" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H101" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I101" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E102" t="n">
-        <v>6.804</v>
+        <v>103.46</v>
       </c>
       <c r="F102" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G102" t="n">
-        <v>61.24</v>
+        <v>103.46</v>
       </c>
       <c r="H102" t="n">
-        <v>5.09</v>
+        <v>3.37</v>
       </c>
       <c r="I102" t="n">
-        <v>9.07</v>
+        <v>3.37</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E103" t="n">
-        <v>23.29</v>
+        <v>40.97</v>
       </c>
       <c r="F103" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G103" t="n">
-        <v>69.87</v>
+        <v>163.88</v>
       </c>
       <c r="H103" t="n">
-        <v>4.2</v>
+        <v>24.86</v>
       </c>
       <c r="I103" t="n">
-        <v>6.4</v>
+        <v>17.88</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E104" t="n">
-        <v>103.46</v>
+        <v>6.804</v>
       </c>
       <c r="F104" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G104" t="n">
-        <v>103.46</v>
+        <v>61.24</v>
       </c>
       <c r="H104" t="n">
-        <v>3.37</v>
+        <v>5.09</v>
       </c>
       <c r="I104" t="n">
-        <v>3.37</v>
+        <v>9.07</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E105" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F105" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G105" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H105" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I105" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E107" t="n">
-        <v>40.5</v>
+        <v>10.456</v>
       </c>
       <c r="F107" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G107" t="n">
-        <v>162</v>
+        <v>31.37</v>
       </c>
       <c r="H107" t="n">
-        <v>22.98</v>
+        <v>0.21</v>
       </c>
       <c r="I107" t="n">
-        <v>16.53</v>
+        <v>0.67</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E108" t="n">
-        <v>6.785</v>
+        <v>103.14</v>
       </c>
       <c r="F108" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G108" t="n">
-        <v>61.06</v>
+        <v>103.14</v>
       </c>
       <c r="H108" t="n">
-        <v>4.91</v>
+        <v>3.05</v>
       </c>
       <c r="I108" t="n">
-        <v>8.74</v>
+        <v>3.05</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E109" t="n">
-        <v>23.33</v>
+        <v>40.5</v>
       </c>
       <c r="F109" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G109" t="n">
-        <v>69.98999999999999</v>
+        <v>162</v>
       </c>
       <c r="H109" t="n">
-        <v>4.32</v>
+        <v>22.98</v>
       </c>
       <c r="I109" t="n">
-        <v>6.58</v>
+        <v>16.53</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E110" t="n">
-        <v>103.14</v>
+        <v>6.785</v>
       </c>
       <c r="F110" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G110" t="n">
-        <v>103.14</v>
+        <v>61.06</v>
       </c>
       <c r="H110" t="n">
-        <v>3.05</v>
+        <v>4.91</v>
       </c>
       <c r="I110" t="n">
-        <v>3.05</v>
+        <v>8.74</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E111" t="n">
-        <v>10.456</v>
+        <v>23.33</v>
       </c>
       <c r="F111" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G111" t="n">
-        <v>31.37</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>0.21</v>
+        <v>4.32</v>
       </c>
       <c r="I111" t="n">
-        <v>0.67</v>
+        <v>6.58</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E117" t="n">
-        <v>6.861</v>
+        <v>10.756</v>
       </c>
       <c r="F117" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G117" t="n">
-        <v>61.75</v>
+        <v>32.27</v>
       </c>
       <c r="H117" t="n">
-        <v>5.6</v>
+        <v>1.11</v>
       </c>
       <c r="I117" t="n">
-        <v>9.970000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E118" t="n">
-        <v>23.145</v>
+        <v>105.96</v>
       </c>
       <c r="F118" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G118" t="n">
-        <v>69.44</v>
+        <v>105.96</v>
       </c>
       <c r="H118" t="n">
-        <v>3.77</v>
+        <v>5.87</v>
       </c>
       <c r="I118" t="n">
-        <v>5.74</v>
+        <v>5.86</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E119" t="n">
-        <v>105.96</v>
+        <v>41</v>
       </c>
       <c r="F119" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G119" t="n">
-        <v>105.96</v>
+        <v>164</v>
       </c>
       <c r="H119" t="n">
-        <v>5.87</v>
+        <v>24.98</v>
       </c>
       <c r="I119" t="n">
-        <v>5.86</v>
+        <v>17.97</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E120" t="n">
-        <v>10.756</v>
+        <v>6.861</v>
       </c>
       <c r="F120" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G120" t="n">
-        <v>32.27</v>
+        <v>61.75</v>
       </c>
       <c r="H120" t="n">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="I120" t="n">
-        <v>3.56</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
+        <v>23.145</v>
       </c>
       <c r="F121" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G121" t="n">
-        <v>164</v>
+        <v>69.44</v>
       </c>
       <c r="H121" t="n">
-        <v>24.98</v>
+        <v>3.77</v>
       </c>
       <c r="I121" t="n">
-        <v>17.97</v>
+        <v>5.74</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4898,29 +4898,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E132" t="n">
-        <v>23.18</v>
+        <v>40.54</v>
       </c>
       <c r="F132" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G132" t="n">
-        <v>69.54000000000001</v>
+        <v>162.16</v>
       </c>
       <c r="H132" t="n">
-        <v>3.87</v>
+        <v>23.14</v>
       </c>
       <c r="I132" t="n">
-        <v>5.89</v>
+        <v>16.65</v>
       </c>
       <c r="J132" t="n">
         <v>7.91</v>
@@ -4932,29 +4932,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E133" t="n">
-        <v>6.895</v>
+        <v>104.02</v>
       </c>
       <c r="F133" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G133" t="n">
-        <v>62.05</v>
+        <v>104.02</v>
       </c>
       <c r="H133" t="n">
-        <v>5.9</v>
+        <v>3.93</v>
       </c>
       <c r="I133" t="n">
-        <v>10.51</v>
+        <v>3.93</v>
       </c>
       <c r="J133" t="n">
         <v>7.91</v>
@@ -5000,29 +5000,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E135" t="n">
-        <v>104.02</v>
+        <v>6.895</v>
       </c>
       <c r="F135" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G135" t="n">
-        <v>104.02</v>
+        <v>62.05</v>
       </c>
       <c r="H135" t="n">
-        <v>3.93</v>
+        <v>5.9</v>
       </c>
       <c r="I135" t="n">
-        <v>3.93</v>
+        <v>10.51</v>
       </c>
       <c r="J135" t="n">
         <v>7.91</v>
@@ -5034,29 +5034,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E136" t="n">
-        <v>40.54</v>
+        <v>23.18</v>
       </c>
       <c r="F136" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G136" t="n">
-        <v>162.16</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="H136" t="n">
-        <v>23.14</v>
+        <v>3.87</v>
       </c>
       <c r="I136" t="n">
-        <v>16.65</v>
+        <v>5.89</v>
       </c>
       <c r="J136" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E142" t="n">
-        <v>38.89</v>
+        <v>11.498</v>
       </c>
       <c r="F142" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G142" t="n">
-        <v>155.56</v>
+        <v>34.49</v>
       </c>
       <c r="H142" t="n">
-        <v>16.54</v>
+        <v>3.33</v>
       </c>
       <c r="I142" t="n">
-        <v>11.9</v>
+        <v>10.69</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E143" t="n">
-        <v>6.878</v>
+        <v>102.06</v>
       </c>
       <c r="F143" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G143" t="n">
-        <v>61.9</v>
+        <v>102.06</v>
       </c>
       <c r="H143" t="n">
-        <v>5.75</v>
+        <v>1.97</v>
       </c>
       <c r="I143" t="n">
-        <v>10.24</v>
+        <v>1.97</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E144" t="n">
-        <v>102.06</v>
+        <v>23.135</v>
       </c>
       <c r="F144" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G144" t="n">
-        <v>102.06</v>
+        <v>69.41</v>
       </c>
       <c r="H144" t="n">
-        <v>1.97</v>
+        <v>3.74</v>
       </c>
       <c r="I144" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E145" t="n">
-        <v>11.498</v>
+        <v>38.89</v>
       </c>
       <c r="F145" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G145" t="n">
-        <v>34.49</v>
+        <v>155.56</v>
       </c>
       <c r="H145" t="n">
-        <v>3.33</v>
+        <v>16.54</v>
       </c>
       <c r="I145" t="n">
-        <v>10.69</v>
+        <v>11.9</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D146" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E146" t="n">
-        <v>23.135</v>
+        <v>6.878</v>
       </c>
       <c r="F146" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G146" t="n">
-        <v>69.41</v>
+        <v>61.9</v>
       </c>
       <c r="H146" t="n">
-        <v>3.74</v>
+        <v>5.75</v>
       </c>
       <c r="I146" t="n">
-        <v>5.7</v>
+        <v>10.24</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5748,29 +5748,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E157" t="n">
-        <v>40.015</v>
+        <v>104.5</v>
       </c>
       <c r="F157" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G157" t="n">
-        <v>160.06</v>
+        <v>104.5</v>
       </c>
       <c r="H157" t="n">
-        <v>21.04</v>
+        <v>4.41</v>
       </c>
       <c r="I157" t="n">
-        <v>15.13</v>
+        <v>4.41</v>
       </c>
       <c r="J157" t="n">
         <v>7.91</v>
@@ -5782,29 +5782,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D158" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E158" t="n">
-        <v>23.08</v>
+        <v>6.913</v>
       </c>
       <c r="F158" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G158" t="n">
-        <v>69.23999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="H158" t="n">
-        <v>3.57</v>
+        <v>6.07</v>
       </c>
       <c r="I158" t="n">
-        <v>5.44</v>
+        <v>10.81</v>
       </c>
       <c r="J158" t="n">
         <v>7.91</v>
@@ -5816,29 +5816,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E159" t="n">
-        <v>6.913</v>
+        <v>10.92</v>
       </c>
       <c r="F159" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G159" t="n">
-        <v>62.22</v>
+        <v>32.76</v>
       </c>
       <c r="H159" t="n">
-        <v>6.07</v>
+        <v>1.6</v>
       </c>
       <c r="I159" t="n">
-        <v>10.81</v>
+        <v>5.13</v>
       </c>
       <c r="J159" t="n">
         <v>7.91</v>
@@ -5850,29 +5850,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E160" t="n">
-        <v>104.5</v>
+        <v>40.015</v>
       </c>
       <c r="F160" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G160" t="n">
-        <v>104.5</v>
+        <v>160.06</v>
       </c>
       <c r="H160" t="n">
-        <v>4.41</v>
+        <v>21.04</v>
       </c>
       <c r="I160" t="n">
-        <v>4.41</v>
+        <v>15.13</v>
       </c>
       <c r="J160" t="n">
         <v>7.91</v>
@@ -5884,29 +5884,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E161" t="n">
-        <v>10.92</v>
+        <v>23.08</v>
       </c>
       <c r="F161" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G161" t="n">
-        <v>32.76</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H161" t="n">
-        <v>1.6</v>
+        <v>3.57</v>
       </c>
       <c r="I161" t="n">
-        <v>5.13</v>
+        <v>5.44</v>
       </c>
       <c r="J161" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E167" t="n">
-        <v>38.98</v>
+        <v>10.726</v>
       </c>
       <c r="F167" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G167" t="n">
-        <v>155.92</v>
+        <v>32.18</v>
       </c>
       <c r="H167" t="n">
-        <v>16.9</v>
+        <v>1.02</v>
       </c>
       <c r="I167" t="n">
-        <v>12.16</v>
+        <v>3.27</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E168" t="n">
-        <v>6.911</v>
+        <v>103.98</v>
       </c>
       <c r="F168" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G168" t="n">
-        <v>62.2</v>
+        <v>103.98</v>
       </c>
       <c r="H168" t="n">
-        <v>6.05</v>
+        <v>3.89</v>
       </c>
       <c r="I168" t="n">
-        <v>10.77</v>
+        <v>3.89</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E169" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F169" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G169" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H169" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I169" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J169" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E170" t="n">
-        <v>10.726</v>
+        <v>38.98</v>
       </c>
       <c r="F170" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G170" t="n">
-        <v>32.18</v>
+        <v>155.92</v>
       </c>
       <c r="H170" t="n">
-        <v>1.02</v>
+        <v>16.9</v>
       </c>
       <c r="I170" t="n">
-        <v>3.27</v>
+        <v>12.16</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D171" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E171" t="n">
-        <v>22.92</v>
+        <v>6.911</v>
       </c>
       <c r="F171" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G171" t="n">
-        <v>68.76000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="H171" t="n">
-        <v>3.09</v>
+        <v>6.05</v>
       </c>
       <c r="I171" t="n">
-        <v>4.71</v>
+        <v>10.77</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6598,29 +6598,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E182" t="n">
-        <v>100.14</v>
+        <v>22.835</v>
       </c>
       <c r="F182" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G182" t="n">
-        <v>100.14</v>
+        <v>68.5</v>
       </c>
       <c r="H182" t="n">
-        <v>0.05</v>
+        <v>2.83</v>
       </c>
       <c r="I182" t="n">
-        <v>0.05</v>
+        <v>4.31</v>
       </c>
       <c r="J182" t="n">
         <v>7.91</v>
@@ -6632,29 +6632,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D183" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E183" t="n">
-        <v>37.235</v>
+        <v>6.848</v>
       </c>
       <c r="F183" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G183" t="n">
-        <v>148.94</v>
+        <v>61.63</v>
       </c>
       <c r="H183" t="n">
-        <v>9.92</v>
+        <v>5.48</v>
       </c>
       <c r="I183" t="n">
-        <v>7.14</v>
+        <v>9.76</v>
       </c>
       <c r="J183" t="n">
         <v>7.91</v>
@@ -6666,29 +6666,29 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E184" t="n">
-        <v>6.848</v>
+        <v>10.776</v>
       </c>
       <c r="F184" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G184" t="n">
-        <v>61.63</v>
+        <v>32.33</v>
       </c>
       <c r="H184" t="n">
-        <v>5.48</v>
+        <v>1.17</v>
       </c>
       <c r="I184" t="n">
-        <v>9.76</v>
+        <v>3.75</v>
       </c>
       <c r="J184" t="n">
         <v>7.91</v>
@@ -6700,29 +6700,29 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E185" t="n">
-        <v>22.835</v>
+        <v>100.14</v>
       </c>
       <c r="F185" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G185" t="n">
-        <v>68.5</v>
+        <v>100.14</v>
       </c>
       <c r="H185" t="n">
-        <v>2.83</v>
+        <v>0.05</v>
       </c>
       <c r="I185" t="n">
-        <v>4.31</v>
+        <v>0.05</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -6734,29 +6734,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E186" t="n">
-        <v>10.776</v>
+        <v>37.235</v>
       </c>
       <c r="F186" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G186" t="n">
-        <v>32.33</v>
+        <v>148.94</v>
       </c>
       <c r="H186" t="n">
-        <v>1.17</v>
+        <v>9.92</v>
       </c>
       <c r="I186" t="n">
-        <v>3.75</v>
+        <v>7.14</v>
       </c>
       <c r="J186" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D197" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E197" t="n">
-        <v>102.48</v>
+        <v>38.565</v>
       </c>
       <c r="F197" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G197" t="n">
-        <v>102.48</v>
+        <v>154.26</v>
       </c>
       <c r="H197" t="n">
-        <v>2.39</v>
+        <v>15.24</v>
       </c>
       <c r="I197" t="n">
-        <v>2.39</v>
+        <v>10.96</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E198" t="n">
-        <v>22.6</v>
+        <v>11.022</v>
       </c>
       <c r="F198" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G198" t="n">
-        <v>67.8</v>
+        <v>33.07</v>
       </c>
       <c r="H198" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="I198" t="n">
-        <v>3.24</v>
+        <v>6.13</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E200" t="n">
-        <v>11.022</v>
+        <v>102.48</v>
       </c>
       <c r="F200" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G200" t="n">
-        <v>33.07</v>
+        <v>102.48</v>
       </c>
       <c r="H200" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="I200" t="n">
-        <v>6.13</v>
+        <v>2.39</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E201" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F201" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G201" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H201" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I201" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D212" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E212" t="n">
-        <v>98.29000000000001</v>
+        <v>37.25</v>
       </c>
       <c r="F212" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G212" t="n">
-        <v>98.29000000000001</v>
+        <v>149</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.8</v>
+        <v>9.98</v>
       </c>
       <c r="I212" t="n">
-        <v>-1.8</v>
+        <v>7.18</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D213" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E213" t="n">
-        <v>11.338</v>
+        <v>6.84</v>
       </c>
       <c r="F213" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G213" t="n">
-        <v>34.01</v>
+        <v>61.56</v>
       </c>
       <c r="H213" t="n">
-        <v>2.85</v>
+        <v>5.41</v>
       </c>
       <c r="I213" t="n">
-        <v>9.15</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E215" t="n">
-        <v>6.84</v>
+        <v>11.338</v>
       </c>
       <c r="F215" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G215" t="n">
-        <v>61.56</v>
+        <v>34.01</v>
       </c>
       <c r="H215" t="n">
-        <v>5.41</v>
+        <v>2.85</v>
       </c>
       <c r="I215" t="n">
-        <v>9.630000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7754,29 +7754,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E216" t="n">
-        <v>37.25</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G216" t="n">
-        <v>149</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>9.98</v>
+        <v>-1.8</v>
       </c>
       <c r="I216" t="n">
-        <v>7.18</v>
+        <v>-1.8</v>
       </c>
       <c r="J216" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D222" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E222" t="n">
-        <v>35.89</v>
+        <v>6.818</v>
       </c>
       <c r="F222" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G222" t="n">
-        <v>143.56</v>
+        <v>61.36</v>
       </c>
       <c r="H222" t="n">
-        <v>4.54</v>
+        <v>5.21</v>
       </c>
       <c r="I222" t="n">
-        <v>3.27</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E223" t="n">
-        <v>11.5</v>
+        <v>96.67</v>
       </c>
       <c r="F223" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G223" t="n">
-        <v>34.5</v>
+        <v>96.67</v>
       </c>
       <c r="H223" t="n">
-        <v>3.34</v>
+        <v>-3.42</v>
       </c>
       <c r="I223" t="n">
-        <v>10.72</v>
+        <v>-3.42</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8026,29 +8026,29 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E224" t="n">
-        <v>96.67</v>
+        <v>23.12</v>
       </c>
       <c r="F224" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G224" t="n">
-        <v>96.67</v>
+        <v>69.36</v>
       </c>
       <c r="H224" t="n">
-        <v>-3.42</v>
+        <v>3.69</v>
       </c>
       <c r="I224" t="n">
-        <v>-3.42</v>
+        <v>5.62</v>
       </c>
       <c r="J224" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D225" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E225" t="n">
-        <v>6.818</v>
+        <v>35.89</v>
       </c>
       <c r="F225" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G225" t="n">
-        <v>61.36</v>
+        <v>143.56</v>
       </c>
       <c r="H225" t="n">
-        <v>5.21</v>
+        <v>4.54</v>
       </c>
       <c r="I225" t="n">
-        <v>9.279999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C226" t="n">
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E226" t="n">
-        <v>23.12</v>
+        <v>11.5</v>
       </c>
       <c r="F226" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G226" t="n">
-        <v>69.36</v>
+        <v>34.5</v>
       </c>
       <c r="H226" t="n">
-        <v>3.69</v>
+        <v>3.34</v>
       </c>
       <c r="I226" t="n">
-        <v>5.62</v>
+        <v>10.72</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D237" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E237" t="n">
-        <v>23.245</v>
+        <v>6.914</v>
       </c>
       <c r="F237" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G237" t="n">
-        <v>69.73</v>
+        <v>62.23</v>
       </c>
       <c r="H237" t="n">
-        <v>4.06</v>
+        <v>6.08</v>
       </c>
       <c r="I237" t="n">
-        <v>6.18</v>
+        <v>10.83</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E238" t="n">
-        <v>99.84999999999999</v>
+        <v>11.842</v>
       </c>
       <c r="F238" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G238" t="n">
-        <v>99.84999999999999</v>
+        <v>35.53</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.24</v>
+        <v>4.37</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.24</v>
+        <v>14.02</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E240" t="n">
-        <v>11.842</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F240" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G240" t="n">
-        <v>35.53</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>4.37</v>
+        <v>-0.24</v>
       </c>
       <c r="I240" t="n">
-        <v>14.02</v>
+        <v>-0.24</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E241" t="n">
-        <v>6.914</v>
+        <v>23.245</v>
       </c>
       <c r="F241" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G241" t="n">
-        <v>62.23</v>
+        <v>69.73</v>
       </c>
       <c r="H241" t="n">
-        <v>6.08</v>
+        <v>4.06</v>
       </c>
       <c r="I241" t="n">
-        <v>10.83</v>
+        <v>6.18</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D247" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E247" t="n">
-        <v>12.18</v>
+        <v>38.435</v>
       </c>
       <c r="F247" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G247" t="n">
-        <v>36.54</v>
+        <v>153.74</v>
       </c>
       <c r="H247" t="n">
-        <v>5.38</v>
+        <v>14.72</v>
       </c>
       <c r="I247" t="n">
-        <v>17.27</v>
+        <v>10.59</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E248" t="n">
-        <v>7.032</v>
+        <v>103.2</v>
       </c>
       <c r="F248" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G248" t="n">
-        <v>63.29</v>
+        <v>103.2</v>
       </c>
       <c r="H248" t="n">
-        <v>7.14</v>
+        <v>3.11</v>
       </c>
       <c r="I248" t="n">
-        <v>12.72</v>
+        <v>3.11</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8876,29 +8876,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D249" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E249" t="n">
-        <v>103.2</v>
+        <v>23.28</v>
       </c>
       <c r="F249" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G249" t="n">
-        <v>103.2</v>
+        <v>69.84</v>
       </c>
       <c r="H249" t="n">
-        <v>3.11</v>
+        <v>4.17</v>
       </c>
       <c r="I249" t="n">
-        <v>3.11</v>
+        <v>6.35</v>
       </c>
       <c r="J249" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D250" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E250" t="n">
-        <v>38.435</v>
+        <v>12.18</v>
       </c>
       <c r="F250" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G250" t="n">
-        <v>153.74</v>
+        <v>36.54</v>
       </c>
       <c r="H250" t="n">
-        <v>14.72</v>
+        <v>5.38</v>
       </c>
       <c r="I250" t="n">
-        <v>10.59</v>
+        <v>17.27</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D251" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E251" t="n">
-        <v>23.28</v>
+        <v>7.032</v>
       </c>
       <c r="F251" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G251" t="n">
-        <v>69.84</v>
+        <v>63.29</v>
       </c>
       <c r="H251" t="n">
-        <v>4.17</v>
+        <v>7.14</v>
       </c>
       <c r="I251" t="n">
-        <v>6.35</v>
+        <v>12.72</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D262" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E262" t="n">
-        <v>7.055</v>
+        <v>12.23</v>
       </c>
       <c r="F262" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G262" t="n">
-        <v>63.49</v>
+        <v>36.69</v>
       </c>
       <c r="H262" t="n">
-        <v>7.34</v>
+        <v>5.53</v>
       </c>
       <c r="I262" t="n">
-        <v>13.07</v>
+        <v>17.75</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E263" t="n">
-        <v>38.23</v>
+        <v>102.84</v>
       </c>
       <c r="F263" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G263" t="n">
-        <v>152.92</v>
+        <v>102.84</v>
       </c>
       <c r="H263" t="n">
-        <v>13.9</v>
+        <v>2.75</v>
       </c>
       <c r="I263" t="n">
-        <v>10</v>
+        <v>2.75</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9386,29 +9386,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D264" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E264" t="n">
-        <v>102.84</v>
+        <v>23.3</v>
       </c>
       <c r="F264" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G264" t="n">
-        <v>102.84</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H264" t="n">
-        <v>2.75</v>
+        <v>4.23</v>
       </c>
       <c r="I264" t="n">
-        <v>2.75</v>
+        <v>6.44</v>
       </c>
       <c r="J264" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E265" t="n">
-        <v>12.23</v>
+        <v>7.055</v>
       </c>
       <c r="F265" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G265" t="n">
-        <v>36.69</v>
+        <v>63.49</v>
       </c>
       <c r="H265" t="n">
-        <v>5.53</v>
+        <v>7.34</v>
       </c>
       <c r="I265" t="n">
-        <v>17.75</v>
+        <v>13.07</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D266" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E266" t="n">
-        <v>23.3</v>
+        <v>38.23</v>
       </c>
       <c r="F266" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G266" t="n">
-        <v>69.90000000000001</v>
+        <v>152.92</v>
       </c>
       <c r="H266" t="n">
-        <v>4.23</v>
+        <v>13.9</v>
       </c>
       <c r="I266" t="n">
-        <v>6.44</v>
+        <v>10</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D272" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E272" t="n">
-        <v>104.54</v>
+        <v>23.135</v>
       </c>
       <c r="F272" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G272" t="n">
-        <v>104.54</v>
+        <v>69.41</v>
       </c>
       <c r="H272" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="I272" t="n">
-        <v>4.45</v>
+        <v>5.7</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D273" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E273" t="n">
-        <v>12.308</v>
+        <v>7.091</v>
       </c>
       <c r="F273" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G273" t="n">
-        <v>36.92</v>
+        <v>63.82</v>
       </c>
       <c r="H273" t="n">
-        <v>5.76</v>
+        <v>7.67</v>
       </c>
       <c r="I273" t="n">
-        <v>18.49</v>
+        <v>13.66</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9726,29 +9726,29 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E274" t="n">
-        <v>7.091</v>
+        <v>39.325</v>
       </c>
       <c r="F274" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G274" t="n">
-        <v>63.82</v>
+        <v>157.3</v>
       </c>
       <c r="H274" t="n">
-        <v>7.67</v>
+        <v>18.28</v>
       </c>
       <c r="I274" t="n">
-        <v>13.66</v>
+        <v>13.15</v>
       </c>
       <c r="J274" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E275" t="n">
-        <v>23.135</v>
+        <v>104.54</v>
       </c>
       <c r="F275" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G275" t="n">
-        <v>69.41</v>
+        <v>104.54</v>
       </c>
       <c r="H275" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="I275" t="n">
-        <v>5.7</v>
+        <v>4.45</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D276" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E276" t="n">
-        <v>39.325</v>
+        <v>12.308</v>
       </c>
       <c r="F276" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G276" t="n">
-        <v>157.3</v>
+        <v>36.92</v>
       </c>
       <c r="H276" t="n">
-        <v>18.28</v>
+        <v>5.76</v>
       </c>
       <c r="I276" t="n">
-        <v>13.15</v>
+        <v>18.49</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -10168,29 +10168,29 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D287" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E287" t="n">
-        <v>38.18</v>
+        <v>6.983</v>
       </c>
       <c r="F287" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G287" t="n">
-        <v>152.72</v>
+        <v>62.85</v>
       </c>
       <c r="H287" t="n">
-        <v>13.7</v>
+        <v>6.7</v>
       </c>
       <c r="I287" t="n">
-        <v>9.85</v>
+        <v>11.93</v>
       </c>
       <c r="J287" t="n">
         <v>7.91</v>
@@ -10202,29 +10202,29 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D288" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E288" t="n">
-        <v>102.22</v>
+        <v>12.292</v>
       </c>
       <c r="F288" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G288" t="n">
-        <v>102.22</v>
+        <v>36.88</v>
       </c>
       <c r="H288" t="n">
-        <v>2.13</v>
+        <v>5.72</v>
       </c>
       <c r="I288" t="n">
-        <v>2.13</v>
+        <v>18.36</v>
       </c>
       <c r="J288" t="n">
         <v>7.91</v>
@@ -10236,29 +10236,29 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C289" t="n">
         <v>3</v>
       </c>
       <c r="D289" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E289" t="n">
-        <v>12.292</v>
+        <v>22.83</v>
       </c>
       <c r="F289" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G289" t="n">
-        <v>36.88</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H289" t="n">
-        <v>5.72</v>
+        <v>2.82</v>
       </c>
       <c r="I289" t="n">
-        <v>18.36</v>
+        <v>4.29</v>
       </c>
       <c r="J289" t="n">
         <v>7.91</v>
@@ -10270,29 +10270,29 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D290" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E290" t="n">
-        <v>6.983</v>
+        <v>38.18</v>
       </c>
       <c r="F290" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G290" t="n">
-        <v>62.85</v>
+        <v>152.72</v>
       </c>
       <c r="H290" t="n">
-        <v>6.7</v>
+        <v>13.7</v>
       </c>
       <c r="I290" t="n">
-        <v>11.93</v>
+        <v>9.85</v>
       </c>
       <c r="J290" t="n">
         <v>7.91</v>
@@ -10304,29 +10304,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E291" t="n">
-        <v>22.83</v>
+        <v>102.22</v>
       </c>
       <c r="F291" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G291" t="n">
-        <v>68.48999999999999</v>
+        <v>102.22</v>
       </c>
       <c r="H291" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="I291" t="n">
-        <v>4.29</v>
+        <v>2.13</v>
       </c>
       <c r="J291" t="n">
         <v>7.91</v>
@@ -10678,29 +10678,29 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D302" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E302" t="n">
-        <v>22.715</v>
+        <v>38.845</v>
       </c>
       <c r="F302" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G302" t="n">
-        <v>68.14</v>
+        <v>155.38</v>
       </c>
       <c r="H302" t="n">
-        <v>2.47</v>
+        <v>16.36</v>
       </c>
       <c r="I302" t="n">
-        <v>3.76</v>
+        <v>11.77</v>
       </c>
       <c r="J302" t="n">
         <v>7.91</v>
@@ -10712,29 +10712,29 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D303" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E303" t="n">
-        <v>100.78</v>
+        <v>6.93</v>
       </c>
       <c r="F303" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G303" t="n">
-        <v>100.78</v>
+        <v>62.37</v>
       </c>
       <c r="H303" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6899999999999999</v>
+        <v>11.08</v>
       </c>
       <c r="J303" t="n">
         <v>7.91</v>
@@ -10780,29 +10780,29 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D305" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E305" t="n">
-        <v>6.93</v>
+        <v>22.715</v>
       </c>
       <c r="F305" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G305" t="n">
-        <v>62.37</v>
+        <v>68.14</v>
       </c>
       <c r="H305" t="n">
-        <v>6.22</v>
+        <v>2.47</v>
       </c>
       <c r="I305" t="n">
-        <v>11.08</v>
+        <v>3.76</v>
       </c>
       <c r="J305" t="n">
         <v>7.91</v>
@@ -10814,29 +10814,29 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D306" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E306" t="n">
-        <v>38.845</v>
+        <v>100.78</v>
       </c>
       <c r="F306" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G306" t="n">
-        <v>155.38</v>
+        <v>100.78</v>
       </c>
       <c r="H306" t="n">
-        <v>16.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>11.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J306" t="n">
         <v>7.91</v>
@@ -11188,29 +11188,29 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D317" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E317" t="n">
-        <v>38.91</v>
+        <v>11.822</v>
       </c>
       <c r="F317" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G317" t="n">
-        <v>155.64</v>
+        <v>35.47</v>
       </c>
       <c r="H317" t="n">
-        <v>16.62</v>
+        <v>4.31</v>
       </c>
       <c r="I317" t="n">
-        <v>11.96</v>
+        <v>13.83</v>
       </c>
       <c r="J317" t="n">
         <v>7.91</v>
@@ -11222,29 +11222,29 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D318" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E318" t="n">
-        <v>100.48</v>
+        <v>6.943</v>
       </c>
       <c r="F318" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G318" t="n">
-        <v>100.48</v>
+        <v>62.49</v>
       </c>
       <c r="H318" t="n">
-        <v>0.39</v>
+        <v>6.34</v>
       </c>
       <c r="I318" t="n">
-        <v>0.39</v>
+        <v>11.29</v>
       </c>
       <c r="J318" t="n">
         <v>7.91</v>
@@ -11256,29 +11256,29 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D319" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E319" t="n">
-        <v>6.943</v>
+        <v>22.77</v>
       </c>
       <c r="F319" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G319" t="n">
-        <v>62.49</v>
+        <v>68.31</v>
       </c>
       <c r="H319" t="n">
-        <v>6.34</v>
+        <v>2.64</v>
       </c>
       <c r="I319" t="n">
-        <v>11.29</v>
+        <v>4.02</v>
       </c>
       <c r="J319" t="n">
         <v>7.91</v>
@@ -11290,29 +11290,29 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E320" t="n">
-        <v>22.77</v>
+        <v>100.48</v>
       </c>
       <c r="F320" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G320" t="n">
-        <v>68.31</v>
+        <v>100.48</v>
       </c>
       <c r="H320" t="n">
-        <v>2.64</v>
+        <v>0.39</v>
       </c>
       <c r="I320" t="n">
-        <v>4.02</v>
+        <v>0.39</v>
       </c>
       <c r="J320" t="n">
         <v>7.91</v>
@@ -11324,29 +11324,29 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D321" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E321" t="n">
-        <v>11.822</v>
+        <v>38.91</v>
       </c>
       <c r="F321" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G321" t="n">
-        <v>35.47</v>
+        <v>155.64</v>
       </c>
       <c r="H321" t="n">
-        <v>4.31</v>
+        <v>16.62</v>
       </c>
       <c r="I321" t="n">
-        <v>13.83</v>
+        <v>11.96</v>
       </c>
       <c r="J321" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D327" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E327" t="n">
-        <v>39.38</v>
+        <v>11.708</v>
       </c>
       <c r="F327" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G327" t="n">
-        <v>157.52</v>
+        <v>35.12</v>
       </c>
       <c r="H327" t="n">
-        <v>18.5</v>
+        <v>3.96</v>
       </c>
       <c r="I327" t="n">
-        <v>13.31</v>
+        <v>12.71</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D328" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E328" t="n">
-        <v>22.83</v>
+        <v>102.72</v>
       </c>
       <c r="F328" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G328" t="n">
-        <v>68.48999999999999</v>
+        <v>102.72</v>
       </c>
       <c r="H328" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="I328" t="n">
-        <v>4.29</v>
+        <v>2.63</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11596,29 +11596,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D329" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E329" t="n">
-        <v>102.72</v>
+        <v>7.027</v>
       </c>
       <c r="F329" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G329" t="n">
-        <v>102.72</v>
+        <v>63.24</v>
       </c>
       <c r="H329" t="n">
-        <v>2.63</v>
+        <v>7.09</v>
       </c>
       <c r="I329" t="n">
-        <v>2.63</v>
+        <v>12.63</v>
       </c>
       <c r="J329" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D330" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E330" t="n">
-        <v>11.708</v>
+        <v>39.38</v>
       </c>
       <c r="F330" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G330" t="n">
-        <v>35.12</v>
+        <v>157.52</v>
       </c>
       <c r="H330" t="n">
-        <v>3.96</v>
+        <v>18.5</v>
       </c>
       <c r="I330" t="n">
-        <v>12.71</v>
+        <v>13.31</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D331" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E331" t="n">
-        <v>7.027</v>
+        <v>22.83</v>
       </c>
       <c r="F331" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G331" t="n">
-        <v>63.24</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H331" t="n">
-        <v>7.09</v>
+        <v>2.82</v>
       </c>
       <c r="I331" t="n">
-        <v>12.63</v>
+        <v>4.29</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -12038,29 +12038,29 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D342" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E342" t="n">
-        <v>6.95</v>
+        <v>11.264</v>
       </c>
       <c r="F342" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G342" t="n">
-        <v>62.55</v>
+        <v>33.79</v>
       </c>
       <c r="H342" t="n">
-        <v>6.4</v>
+        <v>2.63</v>
       </c>
       <c r="I342" t="n">
-        <v>11.4</v>
+        <v>8.44</v>
       </c>
       <c r="J342" t="n">
         <v>7.91</v>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E343" t="n">
-        <v>22.89</v>
+        <v>100.84</v>
       </c>
       <c r="F343" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G343" t="n">
-        <v>68.67</v>
+        <v>100.84</v>
       </c>
       <c r="H343" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="I343" t="n">
-        <v>4.57</v>
+        <v>0.75</v>
       </c>
       <c r="J343" t="n">
         <v>7.91</v>
@@ -12106,29 +12106,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D344" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E344" t="n">
-        <v>100.84</v>
+        <v>38.99</v>
       </c>
       <c r="F344" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G344" t="n">
-        <v>100.84</v>
+        <v>155.96</v>
       </c>
       <c r="H344" t="n">
-        <v>0.75</v>
+        <v>16.94</v>
       </c>
       <c r="I344" t="n">
-        <v>0.75</v>
+        <v>12.19</v>
       </c>
       <c r="J344" t="n">
         <v>7.91</v>
@@ -12140,29 +12140,29 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D345" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E345" t="n">
-        <v>11.264</v>
+        <v>6.95</v>
       </c>
       <c r="F345" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G345" t="n">
-        <v>33.79</v>
+        <v>62.55</v>
       </c>
       <c r="H345" t="n">
-        <v>2.63</v>
+        <v>6.4</v>
       </c>
       <c r="I345" t="n">
-        <v>8.44</v>
+        <v>11.4</v>
       </c>
       <c r="J345" t="n">
         <v>7.91</v>
@@ -12174,29 +12174,29 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D346" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E346" t="n">
-        <v>38.99</v>
+        <v>22.89</v>
       </c>
       <c r="F346" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G346" t="n">
-        <v>155.96</v>
+        <v>68.67</v>
       </c>
       <c r="H346" t="n">
-        <v>16.94</v>
+        <v>3</v>
       </c>
       <c r="I346" t="n">
-        <v>12.19</v>
+        <v>4.57</v>
       </c>
       <c r="J346" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D357" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E357" t="n">
-        <v>40.07</v>
+        <v>6.978</v>
       </c>
       <c r="F357" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G357" t="n">
-        <v>160.28</v>
+        <v>62.8</v>
       </c>
       <c r="H357" t="n">
-        <v>21.26</v>
+        <v>6.65</v>
       </c>
       <c r="I357" t="n">
-        <v>15.29</v>
+        <v>11.84</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E358" t="n">
-        <v>101.98</v>
+        <v>11.13</v>
       </c>
       <c r="F358" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G358" t="n">
-        <v>101.98</v>
+        <v>33.39</v>
       </c>
       <c r="H358" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="I358" t="n">
-        <v>1.89</v>
+        <v>7.16</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D360" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E360" t="n">
-        <v>11.13</v>
+        <v>40.07</v>
       </c>
       <c r="F360" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G360" t="n">
-        <v>33.39</v>
+        <v>160.28</v>
       </c>
       <c r="H360" t="n">
-        <v>2.23</v>
+        <v>21.26</v>
       </c>
       <c r="I360" t="n">
-        <v>7.16</v>
+        <v>15.29</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E361" t="n">
-        <v>6.978</v>
+        <v>101.98</v>
       </c>
       <c r="F361" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G361" t="n">
-        <v>62.8</v>
+        <v>101.98</v>
       </c>
       <c r="H361" t="n">
-        <v>6.65</v>
+        <v>1.89</v>
       </c>
       <c r="I361" t="n">
-        <v>11.84</v>
+        <v>1.89</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -13058,29 +13058,29 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D372" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E372" t="n">
-        <v>100.88</v>
+        <v>6.878</v>
       </c>
       <c r="F372" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G372" t="n">
-        <v>100.88</v>
+        <v>61.9</v>
       </c>
       <c r="H372" t="n">
-        <v>0.79</v>
+        <v>5.75</v>
       </c>
       <c r="I372" t="n">
-        <v>0.79</v>
+        <v>10.24</v>
       </c>
       <c r="J372" t="n">
         <v>7.91</v>
@@ -13092,29 +13092,29 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D373" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E373" t="n">
-        <v>21.94</v>
+        <v>39.05</v>
       </c>
       <c r="F373" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G373" t="n">
-        <v>65.81999999999999</v>
+        <v>156.2</v>
       </c>
       <c r="H373" t="n">
-        <v>0.15</v>
+        <v>17.18</v>
       </c>
       <c r="I373" t="n">
-        <v>0.23</v>
+        <v>12.36</v>
       </c>
       <c r="J373" t="n">
         <v>7.91</v>
@@ -13126,29 +13126,29 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C374" t="n">
         <v>3</v>
       </c>
       <c r="D374" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E374" t="n">
-        <v>10.912</v>
+        <v>21.94</v>
       </c>
       <c r="F374" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G374" t="n">
-        <v>32.74</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H374" t="n">
-        <v>1.58</v>
+        <v>0.15</v>
       </c>
       <c r="I374" t="n">
-        <v>5.07</v>
+        <v>0.23</v>
       </c>
       <c r="J374" t="n">
         <v>7.91</v>
@@ -13160,29 +13160,29 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E375" t="n">
-        <v>6.878</v>
+        <v>100.88</v>
       </c>
       <c r="F375" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G375" t="n">
-        <v>61.9</v>
+        <v>100.88</v>
       </c>
       <c r="H375" t="n">
-        <v>5.75</v>
+        <v>0.79</v>
       </c>
       <c r="I375" t="n">
-        <v>10.24</v>
+        <v>0.79</v>
       </c>
       <c r="J375" t="n">
         <v>7.91</v>
@@ -13194,29 +13194,29 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D376" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E376" t="n">
-        <v>39.05</v>
+        <v>10.912</v>
       </c>
       <c r="F376" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G376" t="n">
-        <v>156.2</v>
+        <v>32.74</v>
       </c>
       <c r="H376" t="n">
-        <v>17.18</v>
+        <v>1.58</v>
       </c>
       <c r="I376" t="n">
-        <v>12.36</v>
+        <v>5.07</v>
       </c>
       <c r="J376" t="n">
         <v>7.91</v>
@@ -13398,29 +13398,29 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E382" t="n">
-        <v>6.931</v>
+        <v>101.3</v>
       </c>
       <c r="F382" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G382" t="n">
-        <v>62.38</v>
+        <v>101.3</v>
       </c>
       <c r="H382" t="n">
-        <v>6.23</v>
+        <v>1.21</v>
       </c>
       <c r="I382" t="n">
-        <v>11.1</v>
+        <v>1.21</v>
       </c>
       <c r="J382" t="n">
         <v>7.91</v>
@@ -13432,29 +13432,29 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D383" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E383" t="n">
-        <v>38.585</v>
+        <v>22.145</v>
       </c>
       <c r="F383" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G383" t="n">
-        <v>154.34</v>
+        <v>66.44</v>
       </c>
       <c r="H383" t="n">
-        <v>15.32</v>
+        <v>0.77</v>
       </c>
       <c r="I383" t="n">
-        <v>11.02</v>
+        <v>1.17</v>
       </c>
       <c r="J383" t="n">
         <v>7.91</v>
@@ -13466,29 +13466,29 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E384" t="n">
-        <v>22.145</v>
+        <v>10.88</v>
       </c>
       <c r="F384" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G384" t="n">
-        <v>66.44</v>
+        <v>32.64</v>
       </c>
       <c r="H384" t="n">
-        <v>0.77</v>
+        <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.17</v>
+        <v>4.75</v>
       </c>
       <c r="J384" t="n">
         <v>7.91</v>
@@ -13500,29 +13500,29 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D385" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E385" t="n">
-        <v>101.3</v>
+        <v>6.931</v>
       </c>
       <c r="F385" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G385" t="n">
-        <v>101.3</v>
+        <v>62.38</v>
       </c>
       <c r="H385" t="n">
-        <v>1.21</v>
+        <v>6.23</v>
       </c>
       <c r="I385" t="n">
-        <v>1.21</v>
+        <v>11.1</v>
       </c>
       <c r="J385" t="n">
         <v>7.91</v>
@@ -13534,29 +13534,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D386" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E386" t="n">
-        <v>10.88</v>
+        <v>38.585</v>
       </c>
       <c r="F386" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G386" t="n">
-        <v>32.64</v>
+        <v>154.34</v>
       </c>
       <c r="H386" t="n">
-        <v>1.48</v>
+        <v>15.32</v>
       </c>
       <c r="I386" t="n">
-        <v>4.75</v>
+        <v>11.02</v>
       </c>
       <c r="J386" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D387" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E387" t="n">
-        <v>100.76</v>
+        <v>21.83</v>
       </c>
       <c r="F387" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G387" t="n">
-        <v>100.76</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H387" t="n">
-        <v>0.67</v>
+        <v>-0.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.67</v>
+        <v>-0.27</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D388" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E388" t="n">
-        <v>21.83</v>
+        <v>6.893</v>
       </c>
       <c r="F388" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G388" t="n">
-        <v>65.48999999999999</v>
+        <v>62.04</v>
       </c>
       <c r="H388" t="n">
-        <v>-0.18</v>
+        <v>5.89</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.27</v>
+        <v>10.49</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D389" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E389" t="n">
-        <v>6.893</v>
+        <v>38.375</v>
       </c>
       <c r="F389" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G389" t="n">
-        <v>62.04</v>
+        <v>153.5</v>
       </c>
       <c r="H389" t="n">
-        <v>5.89</v>
+        <v>14.48</v>
       </c>
       <c r="I389" t="n">
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D390" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E390" t="n">
-        <v>38.375</v>
+        <v>11.006</v>
       </c>
       <c r="F390" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G390" t="n">
-        <v>153.5</v>
+        <v>33.02</v>
       </c>
       <c r="H390" t="n">
-        <v>14.48</v>
+        <v>1.86</v>
       </c>
       <c r="I390" t="n">
-        <v>10.42</v>
+        <v>5.97</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D391" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E391" t="n">
-        <v>11.006</v>
+        <v>100.76</v>
       </c>
       <c r="F391" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G391" t="n">
-        <v>33.02</v>
+        <v>100.76</v>
       </c>
       <c r="H391" t="n">
-        <v>1.86</v>
+        <v>0.67</v>
       </c>
       <c r="I391" t="n">
-        <v>5.97</v>
+        <v>0.67</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D397" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E397" t="n">
-        <v>6.982</v>
+        <v>39.435</v>
       </c>
       <c r="F397" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G397" t="n">
-        <v>62.84</v>
+        <v>157.74</v>
       </c>
       <c r="H397" t="n">
-        <v>6.69</v>
+        <v>18.72</v>
       </c>
       <c r="I397" t="n">
-        <v>11.91</v>
+        <v>13.47</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E398" t="n">
-        <v>102.82</v>
+        <v>11.202</v>
       </c>
       <c r="F398" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G398" t="n">
-        <v>102.82</v>
+        <v>33.61</v>
       </c>
       <c r="H398" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="I398" t="n">
-        <v>2.73</v>
+        <v>7.86</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E399" t="n">
-        <v>22.145</v>
+        <v>102.82</v>
       </c>
       <c r="F399" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G399" t="n">
-        <v>66.44</v>
+        <v>102.82</v>
       </c>
       <c r="H399" t="n">
-        <v>0.77</v>
+        <v>2.73</v>
       </c>
       <c r="I399" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D400" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E400" t="n">
-        <v>39.435</v>
+        <v>6.982</v>
       </c>
       <c r="F400" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G400" t="n">
-        <v>157.74</v>
+        <v>62.84</v>
       </c>
       <c r="H400" t="n">
-        <v>18.72</v>
+        <v>6.69</v>
       </c>
       <c r="I400" t="n">
-        <v>13.47</v>
+        <v>11.91</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C401" t="n">
         <v>3</v>
       </c>
       <c r="D401" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E401" t="n">
-        <v>11.202</v>
+        <v>22.145</v>
       </c>
       <c r="F401" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G401" t="n">
-        <v>33.61</v>
+        <v>66.44</v>
       </c>
       <c r="H401" t="n">
-        <v>2.45</v>
+        <v>0.77</v>
       </c>
       <c r="I401" t="n">
-        <v>7.86</v>
+        <v>1.17</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D407" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E407" t="n">
-        <v>40.695</v>
+        <v>105.98</v>
       </c>
       <c r="F407" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G407" t="n">
-        <v>162.78</v>
+        <v>105.98</v>
       </c>
       <c r="H407" t="n">
-        <v>23.76</v>
+        <v>5.89</v>
       </c>
       <c r="I407" t="n">
-        <v>17.09</v>
+        <v>5.88</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C408" t="n">
         <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E408" t="n">
-        <v>11.232</v>
+        <v>22.35</v>
       </c>
       <c r="F408" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G408" t="n">
-        <v>33.7</v>
+        <v>67.05</v>
       </c>
       <c r="H408" t="n">
-        <v>2.54</v>
+        <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>8.15</v>
+        <v>2.1</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D409" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E409" t="n">
-        <v>22.35</v>
+        <v>7.049</v>
       </c>
       <c r="F409" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G409" t="n">
-        <v>67.05</v>
+        <v>63.44</v>
       </c>
       <c r="H409" t="n">
-        <v>1.38</v>
+        <v>7.29</v>
       </c>
       <c r="I409" t="n">
-        <v>2.1</v>
+        <v>12.98</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D410" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E410" t="n">
-        <v>105.98</v>
+        <v>40.695</v>
       </c>
       <c r="F410" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G410" t="n">
-        <v>105.98</v>
+        <v>162.78</v>
       </c>
       <c r="H410" t="n">
-        <v>5.89</v>
+        <v>23.76</v>
       </c>
       <c r="I410" t="n">
-        <v>5.88</v>
+        <v>17.09</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14384,29 +14384,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D411" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E411" t="n">
-        <v>7.049</v>
+        <v>11.232</v>
       </c>
       <c r="F411" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G411" t="n">
-        <v>63.44</v>
+        <v>33.7</v>
       </c>
       <c r="H411" t="n">
-        <v>7.29</v>
+        <v>2.54</v>
       </c>
       <c r="I411" t="n">
-        <v>12.98</v>
+        <v>8.15</v>
       </c>
       <c r="J411" t="n">
         <v>7.91</v>
@@ -14588,29 +14588,29 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D417" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E417" t="n">
-        <v>11.338</v>
+        <v>7.079</v>
       </c>
       <c r="F417" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G417" t="n">
-        <v>34.01</v>
+        <v>63.71</v>
       </c>
       <c r="H417" t="n">
-        <v>2.85</v>
+        <v>7.56</v>
       </c>
       <c r="I417" t="n">
-        <v>9.15</v>
+        <v>13.46</v>
       </c>
       <c r="J417" t="n">
         <v>7.91</v>
@@ -14622,29 +14622,29 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D418" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E418" t="n">
-        <v>40.63</v>
+        <v>11.338</v>
       </c>
       <c r="F418" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G418" t="n">
-        <v>162.52</v>
+        <v>34.01</v>
       </c>
       <c r="H418" t="n">
-        <v>23.5</v>
+        <v>2.85</v>
       </c>
       <c r="I418" t="n">
-        <v>16.9</v>
+        <v>9.15</v>
       </c>
       <c r="J418" t="n">
         <v>7.91</v>
@@ -14656,29 +14656,29 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D419" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E419" t="n">
-        <v>22.47</v>
+        <v>40.63</v>
       </c>
       <c r="F419" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G419" t="n">
-        <v>67.41</v>
+        <v>162.52</v>
       </c>
       <c r="H419" t="n">
-        <v>1.74</v>
+        <v>23.5</v>
       </c>
       <c r="I419" t="n">
-        <v>2.65</v>
+        <v>16.9</v>
       </c>
       <c r="J419" t="n">
         <v>7.91</v>
@@ -14690,29 +14690,29 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D420" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E420" t="n">
-        <v>107.38</v>
+        <v>22.47</v>
       </c>
       <c r="F420" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G420" t="n">
-        <v>107.38</v>
+        <v>67.41</v>
       </c>
       <c r="H420" t="n">
-        <v>7.29</v>
+        <v>1.74</v>
       </c>
       <c r="I420" t="n">
-        <v>7.28</v>
+        <v>2.65</v>
       </c>
       <c r="J420" t="n">
         <v>7.91</v>
@@ -14724,31 +14724,201 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D421" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E421" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="F421" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G421" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="H421" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="I421" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J421" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E422" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="F422" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G422" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="H422" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I422" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J422" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>3</v>
+      </c>
+      <c r="D423" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E423" t="n">
+        <v>11.144</v>
+      </c>
+      <c r="F423" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G423" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="H423" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I423" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J423" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>4</v>
+      </c>
+      <c r="D424" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E424" t="n">
+        <v>40.225</v>
+      </c>
+      <c r="F424" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G424" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H424" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="I424" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="J424" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>3</v>
+      </c>
+      <c r="D425" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E425" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="F425" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G425" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I425" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J425" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C421" t="n">
+      <c r="C426" t="n">
         <v>9</v>
       </c>
-      <c r="D421" t="n">
+      <c r="D426" t="n">
         <v>6.239</v>
       </c>
-      <c r="E421" t="n">
-        <v>7.079</v>
-      </c>
-      <c r="F421" t="n">
+      <c r="E426" t="n">
+        <v>7.037</v>
+      </c>
+      <c r="F426" t="n">
         <v>56.15</v>
       </c>
-      <c r="G421" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="H421" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="I421" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="J421" t="n">
+      <c r="G426" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="H426" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="I426" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="J426" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J426"/>
+  <dimension ref="A1:J431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E12" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F12" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G12" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E13" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F13" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G13" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H13" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E14" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F14" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G14" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H14" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I14" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E15" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F15" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G15" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H15" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I15" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E16" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F16" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G16" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E27" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F27" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G27" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H27" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I27" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E28" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F28" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G28" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E29" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F29" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G29" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E30" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F30" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G30" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H30" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E31" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F31" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G31" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H31" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E37" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F37" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G37" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H37" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I37" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E38" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F38" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G38" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H38" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E39" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F39" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G39" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H39" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I39" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E40" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F40" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G40" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E41" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F41" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G41" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H41" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I41" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E52" t="n">
-        <v>100.34</v>
+        <v>6.629</v>
       </c>
       <c r="F52" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G52" t="n">
-        <v>100.34</v>
+        <v>59.66</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>3.51</v>
       </c>
       <c r="I52" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E53" t="n">
-        <v>21.703</v>
+        <v>10.702</v>
       </c>
       <c r="F53" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G53" t="n">
-        <v>65.11</v>
+        <v>32.11</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.85</v>
+        <v>3.05</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E54" t="n">
-        <v>10.702</v>
+        <v>38.544</v>
       </c>
       <c r="F54" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G54" t="n">
-        <v>32.11</v>
+        <v>154.18</v>
       </c>
       <c r="H54" t="n">
-        <v>0.95</v>
+        <v>15.16</v>
       </c>
       <c r="I54" t="n">
-        <v>3.05</v>
+        <v>10.9</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E55" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F55" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G55" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H55" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I55" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E56" t="n">
-        <v>6.629</v>
+        <v>21.703</v>
       </c>
       <c r="F56" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G56" t="n">
-        <v>59.66</v>
+        <v>65.11</v>
       </c>
       <c r="H56" t="n">
-        <v>3.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>6.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E62" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F62" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G62" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H62" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I62" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E63" t="n">
-        <v>6.817</v>
+        <v>22.7</v>
       </c>
       <c r="F63" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G63" t="n">
-        <v>61.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="I63" t="n">
-        <v>9.26</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E64" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F64" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G64" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H64" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E65" t="n">
-        <v>10.712</v>
+        <v>41.064</v>
       </c>
       <c r="F65" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G65" t="n">
-        <v>32.14</v>
+        <v>164.26</v>
       </c>
       <c r="H65" t="n">
-        <v>0.98</v>
+        <v>25.24</v>
       </c>
       <c r="I65" t="n">
-        <v>3.15</v>
+        <v>18.16</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E66" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F66" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G66" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H66" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E72" t="n">
-        <v>41.15</v>
+        <v>23</v>
       </c>
       <c r="F72" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G72" t="n">
-        <v>164.6</v>
+        <v>69</v>
       </c>
       <c r="H72" t="n">
-        <v>25.58</v>
+        <v>3.33</v>
       </c>
       <c r="I72" t="n">
-        <v>18.4</v>
+        <v>5.07</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E73" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F73" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H73" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I73" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2926,29 +2926,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E74" t="n">
-        <v>104.22</v>
+        <v>6.811</v>
       </c>
       <c r="F74" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G74" t="n">
-        <v>104.22</v>
+        <v>61.3</v>
       </c>
       <c r="H74" t="n">
-        <v>4.13</v>
+        <v>5.15</v>
       </c>
       <c r="I74" t="n">
-        <v>4.13</v>
+        <v>9.17</v>
       </c>
       <c r="J74" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E75" t="n">
-        <v>23</v>
+        <v>104.22</v>
       </c>
       <c r="F75" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G75" t="n">
-        <v>69</v>
+        <v>104.22</v>
       </c>
       <c r="H75" t="n">
-        <v>3.33</v>
+        <v>4.13</v>
       </c>
       <c r="I75" t="n">
-        <v>5.07</v>
+        <v>4.13</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E77" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F77" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G77" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H77" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I77" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E78" t="n">
-        <v>10.958</v>
+        <v>6.836</v>
       </c>
       <c r="F78" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G78" t="n">
-        <v>32.87</v>
+        <v>61.52</v>
       </c>
       <c r="H78" t="n">
-        <v>1.71</v>
+        <v>5.37</v>
       </c>
       <c r="I78" t="n">
-        <v>5.49</v>
+        <v>9.56</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3096,29 +3096,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E79" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F79" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G79" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H79" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I79" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J79" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E80" t="n">
-        <v>23.4</v>
+        <v>105.8</v>
       </c>
       <c r="F80" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G80" t="n">
-        <v>70.2</v>
+        <v>105.8</v>
       </c>
       <c r="H80" t="n">
-        <v>4.53</v>
+        <v>5.71</v>
       </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E81" t="n">
-        <v>42.25</v>
+        <v>10.958</v>
       </c>
       <c r="F81" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G81" t="n">
-        <v>169</v>
+        <v>32.87</v>
       </c>
       <c r="H81" t="n">
-        <v>29.98</v>
+        <v>1.71</v>
       </c>
       <c r="I81" t="n">
-        <v>21.57</v>
+        <v>5.49</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E87" t="n">
-        <v>106.28</v>
+        <v>10.852</v>
       </c>
       <c r="F87" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G87" t="n">
-        <v>106.28</v>
+        <v>32.56</v>
       </c>
       <c r="H87" t="n">
-        <v>6.19</v>
+        <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>6.18</v>
+        <v>4.49</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E88" t="n">
-        <v>6.856</v>
+        <v>106.28</v>
       </c>
       <c r="F88" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G88" t="n">
-        <v>61.7</v>
+        <v>106.28</v>
       </c>
       <c r="H88" t="n">
-        <v>5.55</v>
+        <v>6.19</v>
       </c>
       <c r="I88" t="n">
-        <v>9.880000000000001</v>
+        <v>6.18</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D89" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E89" t="n">
-        <v>23.32</v>
+        <v>6.856</v>
       </c>
       <c r="F89" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G89" t="n">
-        <v>69.95999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="H89" t="n">
-        <v>4.29</v>
+        <v>5.55</v>
       </c>
       <c r="I89" t="n">
-        <v>6.53</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E90" t="n">
-        <v>43.005</v>
+        <v>23.32</v>
       </c>
       <c r="F90" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G90" t="n">
-        <v>172.02</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>33</v>
+        <v>4.29</v>
       </c>
       <c r="I90" t="n">
-        <v>23.74</v>
+        <v>6.53</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E91" t="n">
-        <v>10.852</v>
+        <v>43.005</v>
       </c>
       <c r="F91" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G91" t="n">
-        <v>32.56</v>
+        <v>172.02</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4</v>
+        <v>33</v>
       </c>
       <c r="I91" t="n">
-        <v>4.49</v>
+        <v>23.74</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E92" t="n">
-        <v>23.025</v>
+        <v>40.575</v>
       </c>
       <c r="F92" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G92" t="n">
-        <v>69.06999999999999</v>
+        <v>162.3</v>
       </c>
       <c r="H92" t="n">
-        <v>3.4</v>
+        <v>23.28</v>
       </c>
       <c r="I92" t="n">
-        <v>5.18</v>
+        <v>16.75</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E93" t="n">
-        <v>103.88</v>
+        <v>6.797</v>
       </c>
       <c r="F93" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G93" t="n">
-        <v>103.88</v>
+        <v>61.17</v>
       </c>
       <c r="H93" t="n">
-        <v>3.79</v>
+        <v>5.02</v>
       </c>
       <c r="I93" t="n">
-        <v>3.79</v>
+        <v>8.94</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E94" t="n">
-        <v>10.876</v>
+        <v>103.88</v>
       </c>
       <c r="F94" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G94" t="n">
-        <v>32.63</v>
+        <v>103.88</v>
       </c>
       <c r="H94" t="n">
-        <v>1.47</v>
+        <v>3.79</v>
       </c>
       <c r="I94" t="n">
-        <v>4.72</v>
+        <v>3.79</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E95" t="n">
-        <v>6.797</v>
+        <v>23.025</v>
       </c>
       <c r="F95" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G95" t="n">
-        <v>61.17</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>5.02</v>
+        <v>3.4</v>
       </c>
       <c r="I95" t="n">
-        <v>8.94</v>
+        <v>5.18</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3674,29 +3674,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E96" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F96" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G96" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H96" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I96" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J96" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E97" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F97" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G97" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H97" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I97" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E98" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F98" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G98" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H98" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I98" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E99" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F99" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G99" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H99" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I99" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E100" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F100" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G100" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H100" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I100" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E101" t="n">
-        <v>23.35</v>
+        <v>40.65</v>
       </c>
       <c r="F101" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G101" t="n">
-        <v>70.05</v>
+        <v>162.6</v>
       </c>
       <c r="H101" t="n">
-        <v>4.38</v>
+        <v>23.58</v>
       </c>
       <c r="I101" t="n">
-        <v>6.67</v>
+        <v>16.96</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E102" t="n">
-        <v>103.46</v>
+        <v>6.804</v>
       </c>
       <c r="F102" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G102" t="n">
-        <v>103.46</v>
+        <v>61.24</v>
       </c>
       <c r="H102" t="n">
-        <v>3.37</v>
+        <v>5.09</v>
       </c>
       <c r="I102" t="n">
-        <v>3.37</v>
+        <v>9.07</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E103" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F103" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G103" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H103" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I103" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E104" t="n">
-        <v>6.804</v>
+        <v>103.46</v>
       </c>
       <c r="F104" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G104" t="n">
-        <v>61.24</v>
+        <v>103.46</v>
       </c>
       <c r="H104" t="n">
-        <v>5.09</v>
+        <v>3.37</v>
       </c>
       <c r="I104" t="n">
-        <v>9.07</v>
+        <v>3.37</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E105" t="n">
-        <v>23.29</v>
+        <v>40.97</v>
       </c>
       <c r="F105" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G105" t="n">
-        <v>69.87</v>
+        <v>163.88</v>
       </c>
       <c r="H105" t="n">
-        <v>4.2</v>
+        <v>24.86</v>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>17.88</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E107" t="n">
-        <v>10.456</v>
+        <v>23.33</v>
       </c>
       <c r="F107" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G107" t="n">
-        <v>31.37</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>0.21</v>
+        <v>4.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.67</v>
+        <v>6.58</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E108" t="n">
-        <v>103.14</v>
+        <v>6.785</v>
       </c>
       <c r="F108" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G108" t="n">
-        <v>103.14</v>
+        <v>61.06</v>
       </c>
       <c r="H108" t="n">
-        <v>3.05</v>
+        <v>4.91</v>
       </c>
       <c r="I108" t="n">
-        <v>3.05</v>
+        <v>8.74</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E109" t="n">
-        <v>40.5</v>
+        <v>10.456</v>
       </c>
       <c r="F109" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G109" t="n">
-        <v>162</v>
+        <v>31.37</v>
       </c>
       <c r="H109" t="n">
-        <v>22.98</v>
+        <v>0.21</v>
       </c>
       <c r="I109" t="n">
-        <v>16.53</v>
+        <v>0.67</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E110" t="n">
-        <v>6.785</v>
+        <v>103.14</v>
       </c>
       <c r="F110" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G110" t="n">
-        <v>61.06</v>
+        <v>103.14</v>
       </c>
       <c r="H110" t="n">
-        <v>4.91</v>
+        <v>3.05</v>
       </c>
       <c r="I110" t="n">
-        <v>8.74</v>
+        <v>3.05</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E111" t="n">
-        <v>23.33</v>
+        <v>40.5</v>
       </c>
       <c r="F111" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G111" t="n">
-        <v>69.98999999999999</v>
+        <v>162</v>
       </c>
       <c r="H111" t="n">
-        <v>4.32</v>
+        <v>22.98</v>
       </c>
       <c r="I111" t="n">
-        <v>6.58</v>
+        <v>16.53</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4388,29 +4388,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E117" t="n">
-        <v>10.756</v>
+        <v>6.861</v>
       </c>
       <c r="F117" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G117" t="n">
-        <v>32.27</v>
+        <v>61.75</v>
       </c>
       <c r="H117" t="n">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="I117" t="n">
-        <v>3.56</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>7.91</v>
@@ -4422,29 +4422,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E118" t="n">
-        <v>105.96</v>
+        <v>41</v>
       </c>
       <c r="F118" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G118" t="n">
-        <v>105.96</v>
+        <v>164</v>
       </c>
       <c r="H118" t="n">
-        <v>5.87</v>
+        <v>24.98</v>
       </c>
       <c r="I118" t="n">
-        <v>5.86</v>
+        <v>17.97</v>
       </c>
       <c r="J118" t="n">
         <v>7.91</v>
@@ -4456,29 +4456,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E119" t="n">
-        <v>41</v>
+        <v>23.145</v>
       </c>
       <c r="F119" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G119" t="n">
-        <v>164</v>
+        <v>69.44</v>
       </c>
       <c r="H119" t="n">
-        <v>24.98</v>
+        <v>3.77</v>
       </c>
       <c r="I119" t="n">
-        <v>17.97</v>
+        <v>5.74</v>
       </c>
       <c r="J119" t="n">
         <v>7.91</v>
@@ -4490,29 +4490,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E120" t="n">
-        <v>6.861</v>
+        <v>10.756</v>
       </c>
       <c r="F120" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G120" t="n">
-        <v>61.75</v>
+        <v>32.27</v>
       </c>
       <c r="H120" t="n">
-        <v>5.6</v>
+        <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>9.970000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J120" t="n">
         <v>7.91</v>
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E121" t="n">
-        <v>23.145</v>
+        <v>105.96</v>
       </c>
       <c r="F121" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G121" t="n">
-        <v>69.44</v>
+        <v>105.96</v>
       </c>
       <c r="H121" t="n">
-        <v>3.77</v>
+        <v>5.87</v>
       </c>
       <c r="I121" t="n">
-        <v>5.74</v>
+        <v>5.86</v>
       </c>
       <c r="J121" t="n">
         <v>7.91</v>
@@ -4898,29 +4898,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E132" t="n">
-        <v>40.54</v>
+        <v>23.18</v>
       </c>
       <c r="F132" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G132" t="n">
-        <v>162.16</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>23.14</v>
+        <v>3.87</v>
       </c>
       <c r="I132" t="n">
-        <v>16.65</v>
+        <v>5.89</v>
       </c>
       <c r="J132" t="n">
         <v>7.91</v>
@@ -4932,29 +4932,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D133" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E133" t="n">
-        <v>104.02</v>
+        <v>6.895</v>
       </c>
       <c r="F133" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G133" t="n">
-        <v>104.02</v>
+        <v>62.05</v>
       </c>
       <c r="H133" t="n">
-        <v>3.93</v>
+        <v>5.9</v>
       </c>
       <c r="I133" t="n">
-        <v>3.93</v>
+        <v>10.51</v>
       </c>
       <c r="J133" t="n">
         <v>7.91</v>
@@ -5000,29 +5000,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E135" t="n">
-        <v>6.895</v>
+        <v>104.02</v>
       </c>
       <c r="F135" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G135" t="n">
-        <v>62.05</v>
+        <v>104.02</v>
       </c>
       <c r="H135" t="n">
-        <v>5.9</v>
+        <v>3.93</v>
       </c>
       <c r="I135" t="n">
-        <v>10.51</v>
+        <v>3.93</v>
       </c>
       <c r="J135" t="n">
         <v>7.91</v>
@@ -5034,29 +5034,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E136" t="n">
-        <v>23.18</v>
+        <v>40.54</v>
       </c>
       <c r="F136" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G136" t="n">
-        <v>69.54000000000001</v>
+        <v>162.16</v>
       </c>
       <c r="H136" t="n">
-        <v>3.87</v>
+        <v>23.14</v>
       </c>
       <c r="I136" t="n">
-        <v>5.89</v>
+        <v>16.65</v>
       </c>
       <c r="J136" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E142" t="n">
-        <v>11.498</v>
+        <v>38.89</v>
       </c>
       <c r="F142" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G142" t="n">
-        <v>34.49</v>
+        <v>155.56</v>
       </c>
       <c r="H142" t="n">
-        <v>3.33</v>
+        <v>16.54</v>
       </c>
       <c r="I142" t="n">
-        <v>10.69</v>
+        <v>11.9</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E143" t="n">
-        <v>102.06</v>
+        <v>23.135</v>
       </c>
       <c r="F143" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G143" t="n">
-        <v>102.06</v>
+        <v>69.41</v>
       </c>
       <c r="H143" t="n">
-        <v>1.97</v>
+        <v>3.74</v>
       </c>
       <c r="I143" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E144" t="n">
-        <v>23.135</v>
+        <v>6.878</v>
       </c>
       <c r="F144" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G144" t="n">
-        <v>69.41</v>
+        <v>61.9</v>
       </c>
       <c r="H144" t="n">
-        <v>3.74</v>
+        <v>5.75</v>
       </c>
       <c r="I144" t="n">
-        <v>5.7</v>
+        <v>10.24</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E145" t="n">
-        <v>38.89</v>
+        <v>11.498</v>
       </c>
       <c r="F145" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G145" t="n">
-        <v>155.56</v>
+        <v>34.49</v>
       </c>
       <c r="H145" t="n">
-        <v>16.54</v>
+        <v>3.33</v>
       </c>
       <c r="I145" t="n">
-        <v>11.9</v>
+        <v>10.69</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E146" t="n">
-        <v>6.878</v>
+        <v>102.06</v>
       </c>
       <c r="F146" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G146" t="n">
-        <v>61.9</v>
+        <v>102.06</v>
       </c>
       <c r="H146" t="n">
-        <v>5.75</v>
+        <v>1.97</v>
       </c>
       <c r="I146" t="n">
-        <v>10.24</v>
+        <v>1.97</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5748,29 +5748,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E157" t="n">
-        <v>104.5</v>
+        <v>40.015</v>
       </c>
       <c r="F157" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G157" t="n">
-        <v>104.5</v>
+        <v>160.06</v>
       </c>
       <c r="H157" t="n">
-        <v>4.41</v>
+        <v>21.04</v>
       </c>
       <c r="I157" t="n">
-        <v>4.41</v>
+        <v>15.13</v>
       </c>
       <c r="J157" t="n">
         <v>7.91</v>
@@ -5782,29 +5782,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E158" t="n">
-        <v>6.913</v>
+        <v>10.92</v>
       </c>
       <c r="F158" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G158" t="n">
-        <v>62.22</v>
+        <v>32.76</v>
       </c>
       <c r="H158" t="n">
-        <v>6.07</v>
+        <v>1.6</v>
       </c>
       <c r="I158" t="n">
-        <v>10.81</v>
+        <v>5.13</v>
       </c>
       <c r="J158" t="n">
         <v>7.91</v>
@@ -5816,29 +5816,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E159" t="n">
-        <v>10.92</v>
+        <v>23.08</v>
       </c>
       <c r="F159" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G159" t="n">
-        <v>32.76</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H159" t="n">
-        <v>1.6</v>
+        <v>3.57</v>
       </c>
       <c r="I159" t="n">
-        <v>5.13</v>
+        <v>5.44</v>
       </c>
       <c r="J159" t="n">
         <v>7.91</v>
@@ -5850,29 +5850,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E160" t="n">
-        <v>40.015</v>
+        <v>104.5</v>
       </c>
       <c r="F160" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G160" t="n">
-        <v>160.06</v>
+        <v>104.5</v>
       </c>
       <c r="H160" t="n">
-        <v>21.04</v>
+        <v>4.41</v>
       </c>
       <c r="I160" t="n">
-        <v>15.13</v>
+        <v>4.41</v>
       </c>
       <c r="J160" t="n">
         <v>7.91</v>
@@ -5884,29 +5884,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D161" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E161" t="n">
-        <v>23.08</v>
+        <v>6.913</v>
       </c>
       <c r="F161" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G161" t="n">
-        <v>69.23999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="H161" t="n">
-        <v>3.57</v>
+        <v>6.07</v>
       </c>
       <c r="I161" t="n">
-        <v>5.44</v>
+        <v>10.81</v>
       </c>
       <c r="J161" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E167" t="n">
-        <v>10.726</v>
+        <v>38.98</v>
       </c>
       <c r="F167" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G167" t="n">
-        <v>32.18</v>
+        <v>155.92</v>
       </c>
       <c r="H167" t="n">
-        <v>1.02</v>
+        <v>16.9</v>
       </c>
       <c r="I167" t="n">
-        <v>3.27</v>
+        <v>12.16</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E168" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F168" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G168" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I168" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E169" t="n">
-        <v>22.92</v>
+        <v>6.911</v>
       </c>
       <c r="F169" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G169" t="n">
-        <v>68.76000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="H169" t="n">
-        <v>3.09</v>
+        <v>6.05</v>
       </c>
       <c r="I169" t="n">
-        <v>4.71</v>
+        <v>10.77</v>
       </c>
       <c r="J169" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E170" t="n">
-        <v>38.98</v>
+        <v>10.726</v>
       </c>
       <c r="F170" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G170" t="n">
-        <v>155.92</v>
+        <v>32.18</v>
       </c>
       <c r="H170" t="n">
-        <v>16.9</v>
+        <v>1.02</v>
       </c>
       <c r="I170" t="n">
-        <v>12.16</v>
+        <v>3.27</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E171" t="n">
-        <v>6.911</v>
+        <v>103.98</v>
       </c>
       <c r="F171" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G171" t="n">
-        <v>62.2</v>
+        <v>103.98</v>
       </c>
       <c r="H171" t="n">
-        <v>6.05</v>
+        <v>3.89</v>
       </c>
       <c r="I171" t="n">
-        <v>10.77</v>
+        <v>3.89</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6598,29 +6598,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E182" t="n">
-        <v>22.835</v>
+        <v>100.14</v>
       </c>
       <c r="F182" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G182" t="n">
-        <v>68.5</v>
+        <v>100.14</v>
       </c>
       <c r="H182" t="n">
-        <v>2.83</v>
+        <v>0.05</v>
       </c>
       <c r="I182" t="n">
-        <v>4.31</v>
+        <v>0.05</v>
       </c>
       <c r="J182" t="n">
         <v>7.91</v>
@@ -6632,29 +6632,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E183" t="n">
-        <v>6.848</v>
+        <v>10.776</v>
       </c>
       <c r="F183" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G183" t="n">
-        <v>61.63</v>
+        <v>32.33</v>
       </c>
       <c r="H183" t="n">
-        <v>5.48</v>
+        <v>1.17</v>
       </c>
       <c r="I183" t="n">
-        <v>9.76</v>
+        <v>3.75</v>
       </c>
       <c r="J183" t="n">
         <v>7.91</v>
@@ -6666,29 +6666,29 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D184" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E184" t="n">
-        <v>10.776</v>
+        <v>37.235</v>
       </c>
       <c r="F184" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G184" t="n">
-        <v>32.33</v>
+        <v>148.94</v>
       </c>
       <c r="H184" t="n">
-        <v>1.17</v>
+        <v>9.92</v>
       </c>
       <c r="I184" t="n">
-        <v>3.75</v>
+        <v>7.14</v>
       </c>
       <c r="J184" t="n">
         <v>7.91</v>
@@ -6700,29 +6700,29 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E185" t="n">
-        <v>100.14</v>
+        <v>22.835</v>
       </c>
       <c r="F185" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G185" t="n">
-        <v>100.14</v>
+        <v>68.5</v>
       </c>
       <c r="H185" t="n">
-        <v>0.05</v>
+        <v>2.83</v>
       </c>
       <c r="I185" t="n">
-        <v>0.05</v>
+        <v>4.31</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -6734,29 +6734,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D186" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E186" t="n">
-        <v>37.235</v>
+        <v>6.848</v>
       </c>
       <c r="F186" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G186" t="n">
-        <v>148.94</v>
+        <v>61.63</v>
       </c>
       <c r="H186" t="n">
-        <v>9.92</v>
+        <v>5.48</v>
       </c>
       <c r="I186" t="n">
-        <v>7.14</v>
+        <v>9.76</v>
       </c>
       <c r="J186" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E197" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F197" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G197" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H197" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I197" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E198" t="n">
-        <v>11.022</v>
+        <v>102.48</v>
       </c>
       <c r="F198" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G198" t="n">
-        <v>33.07</v>
+        <v>102.48</v>
       </c>
       <c r="H198" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="I198" t="n">
-        <v>6.13</v>
+        <v>2.39</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E200" t="n">
-        <v>102.48</v>
+        <v>38.565</v>
       </c>
       <c r="F200" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G200" t="n">
-        <v>102.48</v>
+        <v>154.26</v>
       </c>
       <c r="H200" t="n">
-        <v>2.39</v>
+        <v>15.24</v>
       </c>
       <c r="I200" t="n">
-        <v>2.39</v>
+        <v>10.96</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E201" t="n">
-        <v>22.6</v>
+        <v>11.022</v>
       </c>
       <c r="F201" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G201" t="n">
-        <v>67.8</v>
+        <v>33.07</v>
       </c>
       <c r="H201" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="I201" t="n">
-        <v>3.24</v>
+        <v>6.13</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D212" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E212" t="n">
-        <v>37.25</v>
+        <v>11.338</v>
       </c>
       <c r="F212" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G212" t="n">
-        <v>149</v>
+        <v>34.01</v>
       </c>
       <c r="H212" t="n">
-        <v>9.98</v>
+        <v>2.85</v>
       </c>
       <c r="I212" t="n">
-        <v>7.18</v>
+        <v>9.15</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E213" t="n">
-        <v>6.84</v>
+        <v>22.885</v>
       </c>
       <c r="F213" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G213" t="n">
-        <v>61.56</v>
+        <v>68.66</v>
       </c>
       <c r="H213" t="n">
-        <v>5.41</v>
+        <v>2.99</v>
       </c>
       <c r="I213" t="n">
-        <v>9.630000000000001</v>
+        <v>4.55</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E214" t="n">
-        <v>22.885</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F214" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G214" t="n">
-        <v>68.66</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>2.99</v>
+        <v>-1.8</v>
       </c>
       <c r="I214" t="n">
-        <v>4.55</v>
+        <v>-1.8</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D215" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E215" t="n">
-        <v>11.338</v>
+        <v>37.25</v>
       </c>
       <c r="F215" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G215" t="n">
-        <v>34.01</v>
+        <v>149</v>
       </c>
       <c r="H215" t="n">
-        <v>2.85</v>
+        <v>9.98</v>
       </c>
       <c r="I215" t="n">
-        <v>9.15</v>
+        <v>7.18</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7754,29 +7754,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E216" t="n">
-        <v>98.29000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="F216" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G216" t="n">
-        <v>98.29000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="H216" t="n">
-        <v>-1.8</v>
+        <v>5.41</v>
       </c>
       <c r="I216" t="n">
-        <v>-1.8</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J216" t="n">
         <v>7.91</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C227" t="n">
         <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E227" t="n">
-        <v>11.512</v>
+        <v>23.07</v>
       </c>
       <c r="F227" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G227" t="n">
-        <v>34.54</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H227" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="I227" t="n">
-        <v>10.85</v>
+        <v>5.39</v>
       </c>
       <c r="J227" t="n">
         <v>7.91</v>
@@ -8162,29 +8162,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D228" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E228" t="n">
-        <v>97.34</v>
+        <v>36.64</v>
       </c>
       <c r="F228" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G228" t="n">
-        <v>97.34</v>
+        <v>146.56</v>
       </c>
       <c r="H228" t="n">
-        <v>-2.75</v>
+        <v>7.54</v>
       </c>
       <c r="I228" t="n">
-        <v>-2.75</v>
+        <v>5.42</v>
       </c>
       <c r="J228" t="n">
         <v>7.91</v>
@@ -8196,29 +8196,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D229" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E229" t="n">
-        <v>36.64</v>
+        <v>6.779</v>
       </c>
       <c r="F229" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G229" t="n">
-        <v>146.56</v>
+        <v>61.01</v>
       </c>
       <c r="H229" t="n">
-        <v>7.54</v>
+        <v>4.86</v>
       </c>
       <c r="I229" t="n">
-        <v>5.42</v>
+        <v>8.66</v>
       </c>
       <c r="J229" t="n">
         <v>7.91</v>
@@ -8230,29 +8230,29 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E230" t="n">
-        <v>6.779</v>
+        <v>11.512</v>
       </c>
       <c r="F230" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G230" t="n">
-        <v>61.01</v>
+        <v>34.54</v>
       </c>
       <c r="H230" t="n">
-        <v>4.86</v>
+        <v>3.38</v>
       </c>
       <c r="I230" t="n">
-        <v>8.66</v>
+        <v>10.85</v>
       </c>
       <c r="J230" t="n">
         <v>7.91</v>
@@ -8264,29 +8264,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E231" t="n">
-        <v>23.07</v>
+        <v>97.34</v>
       </c>
       <c r="F231" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G231" t="n">
-        <v>69.20999999999999</v>
+        <v>97.34</v>
       </c>
       <c r="H231" t="n">
-        <v>3.54</v>
+        <v>-2.75</v>
       </c>
       <c r="I231" t="n">
-        <v>5.39</v>
+        <v>-2.75</v>
       </c>
       <c r="J231" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D242" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E242" t="n">
-        <v>38.52</v>
+        <v>7.005</v>
       </c>
       <c r="F242" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G242" t="n">
-        <v>154.08</v>
+        <v>63.05</v>
       </c>
       <c r="H242" t="n">
-        <v>15.06</v>
+        <v>6.9</v>
       </c>
       <c r="I242" t="n">
-        <v>10.83</v>
+        <v>12.29</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C243" t="n">
         <v>3</v>
       </c>
       <c r="D243" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E243" t="n">
-        <v>23.465</v>
+        <v>12.08</v>
       </c>
       <c r="F243" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G243" t="n">
-        <v>70.39</v>
+        <v>36.24</v>
       </c>
       <c r="H243" t="n">
-        <v>4.72</v>
+        <v>5.08</v>
       </c>
       <c r="I243" t="n">
-        <v>7.19</v>
+        <v>16.3</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8706,29 +8706,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D244" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E244" t="n">
-        <v>102.86</v>
+        <v>38.52</v>
       </c>
       <c r="F244" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G244" t="n">
-        <v>102.86</v>
+        <v>154.08</v>
       </c>
       <c r="H244" t="n">
-        <v>2.77</v>
+        <v>15.06</v>
       </c>
       <c r="I244" t="n">
-        <v>2.77</v>
+        <v>10.83</v>
       </c>
       <c r="J244" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C245" t="n">
         <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E245" t="n">
-        <v>12.08</v>
+        <v>23.465</v>
       </c>
       <c r="F245" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G245" t="n">
-        <v>36.24</v>
+        <v>70.39</v>
       </c>
       <c r="H245" t="n">
-        <v>5.08</v>
+        <v>4.72</v>
       </c>
       <c r="I245" t="n">
-        <v>16.3</v>
+        <v>7.19</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E246" t="n">
-        <v>7.005</v>
+        <v>102.86</v>
       </c>
       <c r="F246" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G246" t="n">
-        <v>63.05</v>
+        <v>102.86</v>
       </c>
       <c r="H246" t="n">
-        <v>6.9</v>
+        <v>2.77</v>
       </c>
       <c r="I246" t="n">
-        <v>12.29</v>
+        <v>2.77</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D252" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E252" t="n">
-        <v>23.315</v>
+        <v>7.05</v>
       </c>
       <c r="F252" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G252" t="n">
-        <v>69.95</v>
+        <v>63.45</v>
       </c>
       <c r="H252" t="n">
-        <v>4.28</v>
+        <v>7.3</v>
       </c>
       <c r="I252" t="n">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E253" t="n">
-        <v>12.128</v>
+        <v>103.18</v>
       </c>
       <c r="F253" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G253" t="n">
-        <v>36.38</v>
+        <v>103.18</v>
       </c>
       <c r="H253" t="n">
-        <v>5.22</v>
+        <v>3.09</v>
       </c>
       <c r="I253" t="n">
-        <v>16.75</v>
+        <v>3.09</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D254" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E254" t="n">
-        <v>103.18</v>
+        <v>38.095</v>
       </c>
       <c r="F254" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G254" t="n">
-        <v>103.18</v>
+        <v>152.38</v>
       </c>
       <c r="H254" t="n">
-        <v>3.09</v>
+        <v>13.36</v>
       </c>
       <c r="I254" t="n">
-        <v>3.09</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J254" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E255" t="n">
-        <v>7.05</v>
+        <v>23.315</v>
       </c>
       <c r="F255" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G255" t="n">
-        <v>63.45</v>
+        <v>69.95</v>
       </c>
       <c r="H255" t="n">
-        <v>7.3</v>
+        <v>4.28</v>
       </c>
       <c r="I255" t="n">
-        <v>13</v>
+        <v>6.52</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D256" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E256" t="n">
-        <v>38.095</v>
+        <v>12.128</v>
       </c>
       <c r="F256" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G256" t="n">
-        <v>152.38</v>
+        <v>36.38</v>
       </c>
       <c r="H256" t="n">
-        <v>13.36</v>
+        <v>5.22</v>
       </c>
       <c r="I256" t="n">
-        <v>9.609999999999999</v>
+        <v>16.75</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D262" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E262" t="n">
-        <v>12.23</v>
+        <v>38.23</v>
       </c>
       <c r="F262" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G262" t="n">
-        <v>36.69</v>
+        <v>152.92</v>
       </c>
       <c r="H262" t="n">
-        <v>5.53</v>
+        <v>13.9</v>
       </c>
       <c r="I262" t="n">
-        <v>17.75</v>
+        <v>10</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E263" t="n">
-        <v>102.84</v>
+        <v>12.23</v>
       </c>
       <c r="F263" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G263" t="n">
-        <v>102.84</v>
+        <v>36.69</v>
       </c>
       <c r="H263" t="n">
-        <v>2.75</v>
+        <v>5.53</v>
       </c>
       <c r="I263" t="n">
-        <v>2.75</v>
+        <v>17.75</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9386,29 +9386,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E264" t="n">
-        <v>23.3</v>
+        <v>102.84</v>
       </c>
       <c r="F264" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G264" t="n">
-        <v>69.90000000000001</v>
+        <v>102.84</v>
       </c>
       <c r="H264" t="n">
-        <v>4.23</v>
+        <v>2.75</v>
       </c>
       <c r="I264" t="n">
-        <v>6.44</v>
+        <v>2.75</v>
       </c>
       <c r="J264" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D265" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E265" t="n">
-        <v>7.055</v>
+        <v>23.3</v>
       </c>
       <c r="F265" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G265" t="n">
-        <v>63.49</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H265" t="n">
-        <v>7.34</v>
+        <v>4.23</v>
       </c>
       <c r="I265" t="n">
-        <v>13.07</v>
+        <v>6.44</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D266" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E266" t="n">
-        <v>38.23</v>
+        <v>7.055</v>
       </c>
       <c r="F266" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G266" t="n">
-        <v>152.92</v>
+        <v>63.49</v>
       </c>
       <c r="H266" t="n">
-        <v>13.9</v>
+        <v>7.34</v>
       </c>
       <c r="I266" t="n">
-        <v>10</v>
+        <v>13.07</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9488,29 +9488,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D267" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E267" t="n">
-        <v>103.36</v>
+        <v>7.06</v>
       </c>
       <c r="F267" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G267" t="n">
-        <v>103.36</v>
+        <v>63.54</v>
       </c>
       <c r="H267" t="n">
-        <v>3.27</v>
+        <v>7.39</v>
       </c>
       <c r="I267" t="n">
-        <v>3.27</v>
+        <v>13.16</v>
       </c>
       <c r="J267" t="n">
         <v>7.91</v>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E268" t="n">
-        <v>38.865</v>
+        <v>12.388</v>
       </c>
       <c r="F268" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G268" t="n">
-        <v>155.46</v>
+        <v>37.16</v>
       </c>
       <c r="H268" t="n">
-        <v>16.44</v>
+        <v>6</v>
       </c>
       <c r="I268" t="n">
-        <v>11.83</v>
+        <v>19.26</v>
       </c>
       <c r="J268" t="n">
         <v>7.91</v>
@@ -9590,29 +9590,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D270" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E270" t="n">
-        <v>12.388</v>
+        <v>38.865</v>
       </c>
       <c r="F270" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G270" t="n">
-        <v>37.16</v>
+        <v>155.46</v>
       </c>
       <c r="H270" t="n">
-        <v>6</v>
+        <v>16.44</v>
       </c>
       <c r="I270" t="n">
-        <v>19.26</v>
+        <v>11.83</v>
       </c>
       <c r="J270" t="n">
         <v>7.91</v>
@@ -9624,29 +9624,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E271" t="n">
-        <v>7.06</v>
+        <v>103.36</v>
       </c>
       <c r="F271" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G271" t="n">
-        <v>63.54</v>
+        <v>103.36</v>
       </c>
       <c r="H271" t="n">
-        <v>7.39</v>
+        <v>3.27</v>
       </c>
       <c r="I271" t="n">
-        <v>13.16</v>
+        <v>3.27</v>
       </c>
       <c r="J271" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C277" t="n">
         <v>3</v>
       </c>
       <c r="D277" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E277" t="n">
-        <v>12.492</v>
+        <v>22.96</v>
       </c>
       <c r="F277" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G277" t="n">
-        <v>37.48</v>
+        <v>68.88</v>
       </c>
       <c r="H277" t="n">
-        <v>6.32</v>
+        <v>3.21</v>
       </c>
       <c r="I277" t="n">
-        <v>20.28</v>
+        <v>4.89</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D278" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E278" t="n">
-        <v>103.76</v>
+        <v>38.985</v>
       </c>
       <c r="F278" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G278" t="n">
-        <v>103.76</v>
+        <v>155.94</v>
       </c>
       <c r="H278" t="n">
-        <v>3.67</v>
+        <v>16.92</v>
       </c>
       <c r="I278" t="n">
-        <v>3.67</v>
+        <v>12.17</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9896,29 +9896,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D279" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E279" t="n">
-        <v>38.985</v>
+        <v>7.063</v>
       </c>
       <c r="F279" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G279" t="n">
-        <v>155.94</v>
+        <v>63.57</v>
       </c>
       <c r="H279" t="n">
-        <v>16.92</v>
+        <v>7.42</v>
       </c>
       <c r="I279" t="n">
-        <v>12.17</v>
+        <v>13.21</v>
       </c>
       <c r="J279" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C280" t="n">
         <v>3</v>
       </c>
       <c r="D280" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E280" t="n">
-        <v>22.96</v>
+        <v>12.492</v>
       </c>
       <c r="F280" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G280" t="n">
-        <v>68.88</v>
+        <v>37.48</v>
       </c>
       <c r="H280" t="n">
-        <v>3.21</v>
+        <v>6.32</v>
       </c>
       <c r="I280" t="n">
-        <v>4.89</v>
+        <v>20.28</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E281" t="n">
-        <v>7.063</v>
+        <v>103.76</v>
       </c>
       <c r="F281" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G281" t="n">
-        <v>63.57</v>
+        <v>103.76</v>
       </c>
       <c r="H281" t="n">
-        <v>7.42</v>
+        <v>3.67</v>
       </c>
       <c r="I281" t="n">
-        <v>13.21</v>
+        <v>3.67</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -10338,29 +10338,29 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D292" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E292" t="n">
-        <v>6.96</v>
+        <v>12.096</v>
       </c>
       <c r="F292" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G292" t="n">
-        <v>62.64</v>
+        <v>36.29</v>
       </c>
       <c r="H292" t="n">
-        <v>6.49</v>
+        <v>5.13</v>
       </c>
       <c r="I292" t="n">
-        <v>11.56</v>
+        <v>16.46</v>
       </c>
       <c r="J292" t="n">
         <v>7.91</v>
@@ -10372,29 +10372,29 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D293" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E293" t="n">
-        <v>101.5</v>
+        <v>38.26</v>
       </c>
       <c r="F293" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G293" t="n">
-        <v>101.5</v>
+        <v>153.04</v>
       </c>
       <c r="H293" t="n">
-        <v>1.41</v>
+        <v>14.02</v>
       </c>
       <c r="I293" t="n">
-        <v>1.41</v>
+        <v>10.08</v>
       </c>
       <c r="J293" t="n">
         <v>7.91</v>
@@ -10406,29 +10406,29 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D294" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E294" t="n">
-        <v>38.26</v>
+        <v>22.685</v>
       </c>
       <c r="F294" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G294" t="n">
-        <v>153.04</v>
+        <v>68.05</v>
       </c>
       <c r="H294" t="n">
-        <v>14.02</v>
+        <v>2.38</v>
       </c>
       <c r="I294" t="n">
-        <v>10.08</v>
+        <v>3.62</v>
       </c>
       <c r="J294" t="n">
         <v>7.91</v>
@@ -10440,29 +10440,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D295" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E295" t="n">
-        <v>12.096</v>
+        <v>6.96</v>
       </c>
       <c r="F295" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G295" t="n">
-        <v>36.29</v>
+        <v>62.64</v>
       </c>
       <c r="H295" t="n">
-        <v>5.13</v>
+        <v>6.49</v>
       </c>
       <c r="I295" t="n">
-        <v>16.46</v>
+        <v>11.56</v>
       </c>
       <c r="J295" t="n">
         <v>7.91</v>
@@ -10474,29 +10474,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E296" t="n">
-        <v>22.685</v>
+        <v>101.5</v>
       </c>
       <c r="F296" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G296" t="n">
-        <v>68.05</v>
+        <v>101.5</v>
       </c>
       <c r="H296" t="n">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="I296" t="n">
-        <v>3.62</v>
+        <v>1.41</v>
       </c>
       <c r="J296" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E307" t="n">
-        <v>11.686</v>
+        <v>99.95</v>
       </c>
       <c r="F307" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G307" t="n">
-        <v>35.06</v>
+        <v>99.95</v>
       </c>
       <c r="H307" t="n">
-        <v>3.9</v>
+        <v>-0.14</v>
       </c>
       <c r="I307" t="n">
-        <v>12.52</v>
+        <v>-0.14</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D308" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E308" t="n">
-        <v>22.555</v>
+        <v>38.055</v>
       </c>
       <c r="F308" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G308" t="n">
-        <v>67.66</v>
+        <v>152.22</v>
       </c>
       <c r="H308" t="n">
-        <v>1.99</v>
+        <v>13.2</v>
       </c>
       <c r="I308" t="n">
-        <v>3.03</v>
+        <v>9.5</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D310" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E310" t="n">
-        <v>38.055</v>
+        <v>11.686</v>
       </c>
       <c r="F310" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G310" t="n">
-        <v>152.22</v>
+        <v>35.06</v>
       </c>
       <c r="H310" t="n">
-        <v>13.2</v>
+        <v>3.9</v>
       </c>
       <c r="I310" t="n">
-        <v>9.5</v>
+        <v>12.52</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D311" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E311" t="n">
-        <v>99.95</v>
+        <v>22.555</v>
       </c>
       <c r="F311" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G311" t="n">
-        <v>99.95</v>
+        <v>67.66</v>
       </c>
       <c r="H311" t="n">
-        <v>-0.14</v>
+        <v>1.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.14</v>
+        <v>3.03</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D322" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E322" t="n">
-        <v>101.7</v>
+        <v>22.745</v>
       </c>
       <c r="F322" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G322" t="n">
-        <v>101.7</v>
+        <v>68.23</v>
       </c>
       <c r="H322" t="n">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="I322" t="n">
-        <v>1.61</v>
+        <v>3.9</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D323" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E323" t="n">
-        <v>11.81</v>
+        <v>6.967</v>
       </c>
       <c r="F323" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G323" t="n">
-        <v>35.43</v>
+        <v>62.7</v>
       </c>
       <c r="H323" t="n">
-        <v>4.27</v>
+        <v>6.55</v>
       </c>
       <c r="I323" t="n">
-        <v>13.7</v>
+        <v>11.67</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11426,29 +11426,29 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D324" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E324" t="n">
-        <v>39.07</v>
+        <v>11.81</v>
       </c>
       <c r="F324" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G324" t="n">
-        <v>156.28</v>
+        <v>35.43</v>
       </c>
       <c r="H324" t="n">
-        <v>17.26</v>
+        <v>4.27</v>
       </c>
       <c r="I324" t="n">
-        <v>12.42</v>
+        <v>13.7</v>
       </c>
       <c r="J324" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E325" t="n">
-        <v>6.967</v>
+        <v>101.7</v>
       </c>
       <c r="F325" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G325" t="n">
-        <v>62.7</v>
+        <v>101.7</v>
       </c>
       <c r="H325" t="n">
-        <v>6.55</v>
+        <v>1.61</v>
       </c>
       <c r="I325" t="n">
-        <v>11.67</v>
+        <v>1.61</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D326" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E326" t="n">
-        <v>22.745</v>
+        <v>39.07</v>
       </c>
       <c r="F326" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G326" t="n">
-        <v>68.23</v>
+        <v>156.28</v>
       </c>
       <c r="H326" t="n">
-        <v>2.56</v>
+        <v>17.26</v>
       </c>
       <c r="I326" t="n">
-        <v>3.9</v>
+        <v>12.42</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D337" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E337" t="n">
-        <v>22.845</v>
+        <v>39.15</v>
       </c>
       <c r="F337" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G337" t="n">
-        <v>68.53</v>
+        <v>156.6</v>
       </c>
       <c r="H337" t="n">
-        <v>2.86</v>
+        <v>17.58</v>
       </c>
       <c r="I337" t="n">
-        <v>4.36</v>
+        <v>12.65</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E338" t="n">
-        <v>6.938</v>
+        <v>101.04</v>
       </c>
       <c r="F338" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G338" t="n">
-        <v>62.44</v>
+        <v>101.04</v>
       </c>
       <c r="H338" t="n">
-        <v>6.29</v>
+        <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>11.2</v>
+        <v>0.95</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C339" t="n">
         <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E339" t="n">
-        <v>11.284</v>
+        <v>22.845</v>
       </c>
       <c r="F339" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G339" t="n">
-        <v>33.85</v>
+        <v>68.53</v>
       </c>
       <c r="H339" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="I339" t="n">
-        <v>8.630000000000001</v>
+        <v>4.36</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D340" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E340" t="n">
-        <v>101.04</v>
+        <v>6.938</v>
       </c>
       <c r="F340" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G340" t="n">
-        <v>101.04</v>
+        <v>62.44</v>
       </c>
       <c r="H340" t="n">
-        <v>0.95</v>
+        <v>6.29</v>
       </c>
       <c r="I340" t="n">
-        <v>0.95</v>
+        <v>11.2</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D341" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E341" t="n">
-        <v>39.15</v>
+        <v>11.284</v>
       </c>
       <c r="F341" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G341" t="n">
-        <v>156.6</v>
+        <v>33.85</v>
       </c>
       <c r="H341" t="n">
-        <v>17.58</v>
+        <v>2.69</v>
       </c>
       <c r="I341" t="n">
-        <v>12.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E347" t="n">
-        <v>7.005</v>
+        <v>101.78</v>
       </c>
       <c r="F347" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G347" t="n">
-        <v>63.05</v>
+        <v>101.78</v>
       </c>
       <c r="H347" t="n">
-        <v>6.9</v>
+        <v>1.69</v>
       </c>
       <c r="I347" t="n">
-        <v>12.29</v>
+        <v>1.69</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C348" t="n">
         <v>3</v>
       </c>
       <c r="D348" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E348" t="n">
-        <v>22.82</v>
+        <v>11.206</v>
       </c>
       <c r="F348" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G348" t="n">
-        <v>68.45999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="H348" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="I348" t="n">
-        <v>4.25</v>
+        <v>7.89</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12276,29 +12276,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D349" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E349" t="n">
-        <v>11.206</v>
+        <v>39</v>
       </c>
       <c r="F349" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G349" t="n">
-        <v>33.62</v>
+        <v>156</v>
       </c>
       <c r="H349" t="n">
-        <v>2.46</v>
+        <v>16.98</v>
       </c>
       <c r="I349" t="n">
-        <v>7.89</v>
+        <v>12.21</v>
       </c>
       <c r="J349" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D350" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E350" t="n">
-        <v>101.78</v>
+        <v>7.005</v>
       </c>
       <c r="F350" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G350" t="n">
-        <v>101.78</v>
+        <v>63.05</v>
       </c>
       <c r="H350" t="n">
-        <v>1.69</v>
+        <v>6.9</v>
       </c>
       <c r="I350" t="n">
-        <v>1.69</v>
+        <v>12.29</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D351" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E351" t="n">
-        <v>39</v>
+        <v>22.82</v>
       </c>
       <c r="F351" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G351" t="n">
-        <v>156</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H351" t="n">
-        <v>16.98</v>
+        <v>2.79</v>
       </c>
       <c r="I351" t="n">
-        <v>12.21</v>
+        <v>4.25</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D352" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E352" t="n">
-        <v>6.983</v>
+        <v>39.745</v>
       </c>
       <c r="F352" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G352" t="n">
-        <v>62.85</v>
+        <v>158.98</v>
       </c>
       <c r="H352" t="n">
-        <v>6.7</v>
+        <v>19.96</v>
       </c>
       <c r="I352" t="n">
-        <v>11.93</v>
+        <v>14.36</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E353" t="n">
-        <v>22.75</v>
+        <v>101.76</v>
       </c>
       <c r="F353" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G353" t="n">
-        <v>68.25</v>
+        <v>101.76</v>
       </c>
       <c r="H353" t="n">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="I353" t="n">
-        <v>3.93</v>
+        <v>1.67</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D354" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E354" t="n">
-        <v>11.186</v>
+        <v>6.983</v>
       </c>
       <c r="F354" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G354" t="n">
-        <v>33.56</v>
+        <v>62.85</v>
       </c>
       <c r="H354" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="I354" t="n">
-        <v>7.7</v>
+        <v>11.93</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D355" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E355" t="n">
-        <v>101.76</v>
+        <v>22.75</v>
       </c>
       <c r="F355" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G355" t="n">
-        <v>101.76</v>
+        <v>68.25</v>
       </c>
       <c r="H355" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="I355" t="n">
-        <v>1.67</v>
+        <v>3.93</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D356" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E356" t="n">
-        <v>39.745</v>
+        <v>11.186</v>
       </c>
       <c r="F356" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G356" t="n">
-        <v>158.98</v>
+        <v>33.56</v>
       </c>
       <c r="H356" t="n">
-        <v>19.96</v>
+        <v>2.4</v>
       </c>
       <c r="I356" t="n">
-        <v>14.36</v>
+        <v>7.7</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12718,29 +12718,29 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D362" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E362" t="n">
-        <v>11.208</v>
+        <v>6.972</v>
       </c>
       <c r="F362" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G362" t="n">
-        <v>33.62</v>
+        <v>62.75</v>
       </c>
       <c r="H362" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="I362" t="n">
-        <v>7.89</v>
+        <v>11.75</v>
       </c>
       <c r="J362" t="n">
         <v>7.91</v>
@@ -12752,29 +12752,29 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D363" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E363" t="n">
-        <v>102.1</v>
+        <v>22.515</v>
       </c>
       <c r="F363" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G363" t="n">
-        <v>102.1</v>
+        <v>67.55</v>
       </c>
       <c r="H363" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="I363" t="n">
-        <v>2.01</v>
+        <v>2.86</v>
       </c>
       <c r="J363" t="n">
         <v>7.91</v>
@@ -12786,29 +12786,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D364" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E364" t="n">
-        <v>40.15</v>
+        <v>11.208</v>
       </c>
       <c r="F364" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G364" t="n">
-        <v>160.6</v>
+        <v>33.62</v>
       </c>
       <c r="H364" t="n">
-        <v>21.58</v>
+        <v>2.46</v>
       </c>
       <c r="I364" t="n">
-        <v>15.52</v>
+        <v>7.89</v>
       </c>
       <c r="J364" t="n">
         <v>7.91</v>
@@ -12820,29 +12820,29 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D365" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E365" t="n">
-        <v>6.972</v>
+        <v>102.1</v>
       </c>
       <c r="F365" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G365" t="n">
-        <v>62.75</v>
+        <v>102.1</v>
       </c>
       <c r="H365" t="n">
-        <v>6.6</v>
+        <v>2.01</v>
       </c>
       <c r="I365" t="n">
-        <v>11.75</v>
+        <v>2.01</v>
       </c>
       <c r="J365" t="n">
         <v>7.91</v>
@@ -12854,29 +12854,29 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D366" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E366" t="n">
-        <v>22.515</v>
+        <v>40.15</v>
       </c>
       <c r="F366" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G366" t="n">
-        <v>67.55</v>
+        <v>160.6</v>
       </c>
       <c r="H366" t="n">
-        <v>1.88</v>
+        <v>21.58</v>
       </c>
       <c r="I366" t="n">
-        <v>2.86</v>
+        <v>15.52</v>
       </c>
       <c r="J366" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E377" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F377" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G377" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H377" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I377" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D378" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E378" t="n">
-        <v>22.13</v>
+        <v>39.57</v>
       </c>
       <c r="F378" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G378" t="n">
-        <v>66.39</v>
+        <v>158.28</v>
       </c>
       <c r="H378" t="n">
-        <v>0.72</v>
+        <v>19.26</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1</v>
+        <v>13.85</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13296,29 +13296,29 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C379" t="n">
         <v>3</v>
       </c>
       <c r="D379" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E379" t="n">
-        <v>10.962</v>
+        <v>22.13</v>
       </c>
       <c r="F379" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G379" t="n">
-        <v>32.89</v>
+        <v>66.39</v>
       </c>
       <c r="H379" t="n">
-        <v>1.73</v>
+        <v>0.72</v>
       </c>
       <c r="I379" t="n">
-        <v>5.55</v>
+        <v>1.1</v>
       </c>
       <c r="J379" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E380" t="n">
-        <v>101.88</v>
+        <v>6.941</v>
       </c>
       <c r="F380" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G380" t="n">
-        <v>101.88</v>
+        <v>62.47</v>
       </c>
       <c r="H380" t="n">
-        <v>1.79</v>
+        <v>6.32</v>
       </c>
       <c r="I380" t="n">
-        <v>1.79</v>
+        <v>11.26</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D381" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E381" t="n">
-        <v>39.57</v>
+        <v>10.962</v>
       </c>
       <c r="F381" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G381" t="n">
-        <v>158.28</v>
+        <v>32.89</v>
       </c>
       <c r="H381" t="n">
-        <v>19.26</v>
+        <v>1.73</v>
       </c>
       <c r="I381" t="n">
-        <v>13.85</v>
+        <v>5.55</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C387" t="n">
         <v>3</v>
       </c>
       <c r="D387" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E387" t="n">
-        <v>21.83</v>
+        <v>11.006</v>
       </c>
       <c r="F387" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G387" t="n">
-        <v>65.48999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="H387" t="n">
-        <v>-0.18</v>
+        <v>1.86</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.27</v>
+        <v>5.97</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D388" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E388" t="n">
-        <v>6.893</v>
+        <v>38.375</v>
       </c>
       <c r="F388" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G388" t="n">
-        <v>62.04</v>
+        <v>153.5</v>
       </c>
       <c r="H388" t="n">
-        <v>5.89</v>
+        <v>14.48</v>
       </c>
       <c r="I388" t="n">
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D389" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E389" t="n">
-        <v>38.375</v>
+        <v>100.76</v>
       </c>
       <c r="F389" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G389" t="n">
-        <v>153.5</v>
+        <v>100.76</v>
       </c>
       <c r="H389" t="n">
-        <v>14.48</v>
+        <v>0.67</v>
       </c>
       <c r="I389" t="n">
-        <v>10.42</v>
+        <v>0.67</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C390" t="n">
         <v>3</v>
       </c>
       <c r="D390" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E390" t="n">
-        <v>11.006</v>
+        <v>21.83</v>
       </c>
       <c r="F390" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G390" t="n">
-        <v>33.02</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H390" t="n">
-        <v>1.86</v>
+        <v>-0.18</v>
       </c>
       <c r="I390" t="n">
-        <v>5.97</v>
+        <v>-0.27</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D391" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E391" t="n">
-        <v>100.76</v>
+        <v>6.893</v>
       </c>
       <c r="F391" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G391" t="n">
-        <v>100.76</v>
+        <v>62.04</v>
       </c>
       <c r="H391" t="n">
-        <v>0.67</v>
+        <v>5.89</v>
       </c>
       <c r="I391" t="n">
-        <v>0.67</v>
+        <v>10.49</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -14078,29 +14078,29 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D402" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E402" t="n">
-        <v>103.08</v>
+        <v>6.965</v>
       </c>
       <c r="F402" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G402" t="n">
-        <v>103.08</v>
+        <v>62.69</v>
       </c>
       <c r="H402" t="n">
-        <v>2.99</v>
+        <v>6.54</v>
       </c>
       <c r="I402" t="n">
-        <v>2.99</v>
+        <v>11.65</v>
       </c>
       <c r="J402" t="n">
         <v>7.91</v>
@@ -14112,29 +14112,29 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D403" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E403" t="n">
-        <v>11.086</v>
+        <v>39.395</v>
       </c>
       <c r="F403" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G403" t="n">
-        <v>33.26</v>
+        <v>157.58</v>
       </c>
       <c r="H403" t="n">
-        <v>2.1</v>
+        <v>18.56</v>
       </c>
       <c r="I403" t="n">
-        <v>6.74</v>
+        <v>13.35</v>
       </c>
       <c r="J403" t="n">
         <v>7.91</v>
@@ -14146,29 +14146,29 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D404" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E404" t="n">
-        <v>39.395</v>
+        <v>22.15</v>
       </c>
       <c r="F404" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G404" t="n">
-        <v>157.58</v>
+        <v>66.45</v>
       </c>
       <c r="H404" t="n">
-        <v>18.56</v>
+        <v>0.78</v>
       </c>
       <c r="I404" t="n">
-        <v>13.35</v>
+        <v>1.19</v>
       </c>
       <c r="J404" t="n">
         <v>7.91</v>
@@ -14180,29 +14180,29 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D405" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E405" t="n">
-        <v>22.15</v>
+        <v>103.08</v>
       </c>
       <c r="F405" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G405" t="n">
-        <v>66.45</v>
+        <v>103.08</v>
       </c>
       <c r="H405" t="n">
-        <v>0.78</v>
+        <v>2.99</v>
       </c>
       <c r="I405" t="n">
-        <v>1.19</v>
+        <v>2.99</v>
       </c>
       <c r="J405" t="n">
         <v>7.91</v>
@@ -14214,29 +14214,29 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D406" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E406" t="n">
-        <v>6.965</v>
+        <v>11.086</v>
       </c>
       <c r="F406" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G406" t="n">
-        <v>62.69</v>
+        <v>33.26</v>
       </c>
       <c r="H406" t="n">
-        <v>6.54</v>
+        <v>2.1</v>
       </c>
       <c r="I406" t="n">
-        <v>11.65</v>
+        <v>6.74</v>
       </c>
       <c r="J406" t="n">
         <v>7.91</v>
@@ -14588,29 +14588,29 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D417" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E417" t="n">
-        <v>7.079</v>
+        <v>107.38</v>
       </c>
       <c r="F417" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G417" t="n">
-        <v>63.71</v>
+        <v>107.38</v>
       </c>
       <c r="H417" t="n">
-        <v>7.56</v>
+        <v>7.29</v>
       </c>
       <c r="I417" t="n">
-        <v>13.46</v>
+        <v>7.28</v>
       </c>
       <c r="J417" t="n">
         <v>7.91</v>
@@ -14622,29 +14622,29 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C418" t="n">
         <v>3</v>
       </c>
       <c r="D418" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E418" t="n">
-        <v>11.338</v>
+        <v>22.47</v>
       </c>
       <c r="F418" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G418" t="n">
-        <v>34.01</v>
+        <v>67.41</v>
       </c>
       <c r="H418" t="n">
-        <v>2.85</v>
+        <v>1.74</v>
       </c>
       <c r="I418" t="n">
-        <v>9.15</v>
+        <v>2.65</v>
       </c>
       <c r="J418" t="n">
         <v>7.91</v>
@@ -14656,29 +14656,29 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D419" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E419" t="n">
-        <v>40.63</v>
+        <v>11.338</v>
       </c>
       <c r="F419" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G419" t="n">
-        <v>162.52</v>
+        <v>34.01</v>
       </c>
       <c r="H419" t="n">
-        <v>23.5</v>
+        <v>2.85</v>
       </c>
       <c r="I419" t="n">
-        <v>16.9</v>
+        <v>9.15</v>
       </c>
       <c r="J419" t="n">
         <v>7.91</v>
@@ -14690,29 +14690,29 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D420" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E420" t="n">
-        <v>22.47</v>
+        <v>7.079</v>
       </c>
       <c r="F420" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G420" t="n">
-        <v>67.41</v>
+        <v>63.71</v>
       </c>
       <c r="H420" t="n">
-        <v>1.74</v>
+        <v>7.56</v>
       </c>
       <c r="I420" t="n">
-        <v>2.65</v>
+        <v>13.46</v>
       </c>
       <c r="J420" t="n">
         <v>7.91</v>
@@ -14724,29 +14724,29 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D421" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E421" t="n">
-        <v>107.38</v>
+        <v>40.63</v>
       </c>
       <c r="F421" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G421" t="n">
-        <v>107.38</v>
+        <v>162.52</v>
       </c>
       <c r="H421" t="n">
-        <v>7.29</v>
+        <v>23.5</v>
       </c>
       <c r="I421" t="n">
-        <v>7.28</v>
+        <v>16.9</v>
       </c>
       <c r="J421" t="n">
         <v>7.91</v>
@@ -14919,6 +14919,176 @@
         <v>12.79</v>
       </c>
       <c r="J426" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>3</v>
+      </c>
+      <c r="D427" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E427" t="n">
+        <v>11.132</v>
+      </c>
+      <c r="F427" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G427" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="H427" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I427" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="J427" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>4</v>
+      </c>
+      <c r="D428" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E428" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="F428" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G428" t="n">
+        <v>162.28</v>
+      </c>
+      <c r="H428" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="I428" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="J428" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>3</v>
+      </c>
+      <c r="D429" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E429" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F429" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G429" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H429" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I429" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J429" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E430" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="F430" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G430" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="H430" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I430" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="J430" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>9</v>
+      </c>
+      <c r="D431" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E431" t="n">
+        <v>7.068</v>
+      </c>
+      <c r="F431" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G431" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="H431" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="I431" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="J431" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J431"/>
+  <dimension ref="A1:J436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E12" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F12" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G12" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E13" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F13" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G13" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H13" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I13" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E14" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F14" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G14" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H14" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I14" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E15" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F15" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G15" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H15" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E16" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F16" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G16" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H16" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E27" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F27" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G27" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H27" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E28" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F28" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G28" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H28" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E29" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F29" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G29" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H29" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I29" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E30" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F30" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G30" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E31" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F31" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G31" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I31" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E37" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F37" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G37" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E38" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F38" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G38" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H38" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E39" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F39" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G39" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H39" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I39" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E40" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F40" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G40" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H40" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I40" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E41" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F41" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G41" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H41" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I41" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E52" t="n">
-        <v>6.629</v>
+        <v>21.703</v>
       </c>
       <c r="F52" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G52" t="n">
-        <v>59.66</v>
+        <v>65.11</v>
       </c>
       <c r="H52" t="n">
-        <v>3.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>6.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E53" t="n">
-        <v>10.702</v>
+        <v>38.544</v>
       </c>
       <c r="F53" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G53" t="n">
-        <v>32.11</v>
+        <v>154.18</v>
       </c>
       <c r="H53" t="n">
-        <v>0.95</v>
+        <v>15.16</v>
       </c>
       <c r="I53" t="n">
-        <v>3.05</v>
+        <v>10.9</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E54" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F54" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G54" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H54" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I54" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E55" t="n">
-        <v>100.34</v>
+        <v>6.629</v>
       </c>
       <c r="F55" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G55" t="n">
-        <v>100.34</v>
+        <v>59.66</v>
       </c>
       <c r="H55" t="n">
-        <v>0.25</v>
+        <v>3.51</v>
       </c>
       <c r="I55" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E56" t="n">
-        <v>21.703</v>
+        <v>10.702</v>
       </c>
       <c r="F56" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G56" t="n">
-        <v>65.11</v>
+        <v>32.11</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.85</v>
+        <v>3.05</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E62" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F62" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G62" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H62" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I62" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E63" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F63" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G63" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H63" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E64" t="n">
-        <v>10.712</v>
+        <v>41.064</v>
       </c>
       <c r="F64" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G64" t="n">
-        <v>32.14</v>
+        <v>164.26</v>
       </c>
       <c r="H64" t="n">
-        <v>0.98</v>
+        <v>25.24</v>
       </c>
       <c r="I64" t="n">
-        <v>3.15</v>
+        <v>18.16</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E65" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F65" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G65" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H65" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I65" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E66" t="n">
-        <v>6.817</v>
+        <v>22.7</v>
       </c>
       <c r="F66" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G66" t="n">
-        <v>61.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="I66" t="n">
-        <v>9.26</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>104.22</v>
       </c>
       <c r="F72" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G72" t="n">
-        <v>69</v>
+        <v>104.22</v>
       </c>
       <c r="H72" t="n">
-        <v>3.33</v>
+        <v>4.13</v>
       </c>
       <c r="I72" t="n">
-        <v>5.07</v>
+        <v>4.13</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E73" t="n">
-        <v>41.15</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G73" t="n">
-        <v>164.6</v>
+        <v>69</v>
       </c>
       <c r="H73" t="n">
-        <v>25.58</v>
+        <v>3.33</v>
       </c>
       <c r="I73" t="n">
-        <v>18.4</v>
+        <v>5.07</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2926,29 +2926,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E74" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F74" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G74" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H74" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I74" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J74" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E75" t="n">
-        <v>104.22</v>
+        <v>6.811</v>
       </c>
       <c r="F75" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G75" t="n">
-        <v>104.22</v>
+        <v>61.3</v>
       </c>
       <c r="H75" t="n">
-        <v>4.13</v>
+        <v>5.15</v>
       </c>
       <c r="I75" t="n">
-        <v>4.13</v>
+        <v>9.17</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E77" t="n">
-        <v>42.25</v>
+        <v>10.958</v>
       </c>
       <c r="F77" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G77" t="n">
-        <v>169</v>
+        <v>32.87</v>
       </c>
       <c r="H77" t="n">
-        <v>29.98</v>
+        <v>1.71</v>
       </c>
       <c r="I77" t="n">
-        <v>21.57</v>
+        <v>5.49</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E78" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F78" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G78" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H78" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I78" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3096,29 +3096,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E79" t="n">
-        <v>23.4</v>
+        <v>105.8</v>
       </c>
       <c r="F79" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G79" t="n">
-        <v>70.2</v>
+        <v>105.8</v>
       </c>
       <c r="H79" t="n">
-        <v>4.53</v>
+        <v>5.71</v>
       </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="J79" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E80" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F80" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G80" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H80" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I80" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E81" t="n">
-        <v>10.958</v>
+        <v>6.836</v>
       </c>
       <c r="F81" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G81" t="n">
-        <v>32.87</v>
+        <v>61.52</v>
       </c>
       <c r="H81" t="n">
-        <v>1.71</v>
+        <v>5.37</v>
       </c>
       <c r="I81" t="n">
-        <v>5.49</v>
+        <v>9.56</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E87" t="n">
-        <v>10.852</v>
+        <v>43.005</v>
       </c>
       <c r="F87" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G87" t="n">
-        <v>32.56</v>
+        <v>172.02</v>
       </c>
       <c r="H87" t="n">
-        <v>1.4</v>
+        <v>33</v>
       </c>
       <c r="I87" t="n">
-        <v>4.49</v>
+        <v>23.74</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E88" t="n">
-        <v>106.28</v>
+        <v>10.852</v>
       </c>
       <c r="F88" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G88" t="n">
-        <v>106.28</v>
+        <v>32.56</v>
       </c>
       <c r="H88" t="n">
-        <v>6.19</v>
+        <v>1.4</v>
       </c>
       <c r="I88" t="n">
-        <v>6.18</v>
+        <v>4.49</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E89" t="n">
-        <v>6.856</v>
+        <v>106.28</v>
       </c>
       <c r="F89" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G89" t="n">
-        <v>61.7</v>
+        <v>106.28</v>
       </c>
       <c r="H89" t="n">
-        <v>5.55</v>
+        <v>6.19</v>
       </c>
       <c r="I89" t="n">
-        <v>9.880000000000001</v>
+        <v>6.18</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E90" t="n">
-        <v>23.32</v>
+        <v>6.856</v>
       </c>
       <c r="F90" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G90" t="n">
-        <v>69.95999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="H90" t="n">
-        <v>4.29</v>
+        <v>5.55</v>
       </c>
       <c r="I90" t="n">
-        <v>6.53</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E91" t="n">
-        <v>43.005</v>
+        <v>23.32</v>
       </c>
       <c r="F91" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G91" t="n">
-        <v>172.02</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>33</v>
+        <v>4.29</v>
       </c>
       <c r="I91" t="n">
-        <v>23.74</v>
+        <v>6.53</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E92" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F92" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G92" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H92" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I92" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E93" t="n">
-        <v>6.797</v>
+        <v>23.025</v>
       </c>
       <c r="F93" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G93" t="n">
-        <v>61.17</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>5.02</v>
+        <v>3.4</v>
       </c>
       <c r="I93" t="n">
-        <v>8.94</v>
+        <v>5.18</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D94" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E94" t="n">
-        <v>103.88</v>
+        <v>6.797</v>
       </c>
       <c r="F94" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G94" t="n">
-        <v>103.88</v>
+        <v>61.17</v>
       </c>
       <c r="H94" t="n">
-        <v>3.79</v>
+        <v>5.02</v>
       </c>
       <c r="I94" t="n">
-        <v>3.79</v>
+        <v>8.94</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E95" t="n">
-        <v>23.025</v>
+        <v>40.575</v>
       </c>
       <c r="F95" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G95" t="n">
-        <v>69.06999999999999</v>
+        <v>162.3</v>
       </c>
       <c r="H95" t="n">
-        <v>3.4</v>
+        <v>23.28</v>
       </c>
       <c r="I95" t="n">
-        <v>5.18</v>
+        <v>16.75</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3674,29 +3674,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E96" t="n">
-        <v>10.876</v>
+        <v>103.88</v>
       </c>
       <c r="F96" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G96" t="n">
-        <v>32.63</v>
+        <v>103.88</v>
       </c>
       <c r="H96" t="n">
-        <v>1.47</v>
+        <v>3.79</v>
       </c>
       <c r="I96" t="n">
-        <v>4.72</v>
+        <v>3.79</v>
       </c>
       <c r="J96" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E97" t="n">
-        <v>23.35</v>
+        <v>40.65</v>
       </c>
       <c r="F97" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G97" t="n">
-        <v>70.05</v>
+        <v>162.6</v>
       </c>
       <c r="H97" t="n">
-        <v>4.38</v>
+        <v>23.58</v>
       </c>
       <c r="I97" t="n">
-        <v>6.67</v>
+        <v>16.96</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E98" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F98" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G98" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H98" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I98" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E99" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F99" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G99" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H99" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E100" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F100" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G100" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H100" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I100" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E101" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F101" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G101" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H101" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I101" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E102" t="n">
-        <v>6.804</v>
+        <v>103.46</v>
       </c>
       <c r="F102" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G102" t="n">
-        <v>61.24</v>
+        <v>103.46</v>
       </c>
       <c r="H102" t="n">
-        <v>5.09</v>
+        <v>3.37</v>
       </c>
       <c r="I102" t="n">
-        <v>9.07</v>
+        <v>3.37</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E103" t="n">
-        <v>23.29</v>
+        <v>40.97</v>
       </c>
       <c r="F103" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G103" t="n">
-        <v>69.87</v>
+        <v>163.88</v>
       </c>
       <c r="H103" t="n">
-        <v>4.2</v>
+        <v>24.86</v>
       </c>
       <c r="I103" t="n">
-        <v>6.4</v>
+        <v>17.88</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E104" t="n">
-        <v>103.46</v>
+        <v>6.804</v>
       </c>
       <c r="F104" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G104" t="n">
-        <v>103.46</v>
+        <v>61.24</v>
       </c>
       <c r="H104" t="n">
-        <v>3.37</v>
+        <v>5.09</v>
       </c>
       <c r="I104" t="n">
-        <v>3.37</v>
+        <v>9.07</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E105" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F105" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G105" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H105" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I105" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E107" t="n">
-        <v>23.33</v>
+        <v>40.5</v>
       </c>
       <c r="F107" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G107" t="n">
-        <v>69.98999999999999</v>
+        <v>162</v>
       </c>
       <c r="H107" t="n">
-        <v>4.32</v>
+        <v>22.98</v>
       </c>
       <c r="I107" t="n">
-        <v>6.58</v>
+        <v>16.53</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E108" t="n">
-        <v>6.785</v>
+        <v>10.456</v>
       </c>
       <c r="F108" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G108" t="n">
-        <v>61.06</v>
+        <v>31.37</v>
       </c>
       <c r="H108" t="n">
-        <v>4.91</v>
+        <v>0.21</v>
       </c>
       <c r="I108" t="n">
-        <v>8.74</v>
+        <v>0.67</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E109" t="n">
-        <v>10.456</v>
+        <v>103.14</v>
       </c>
       <c r="F109" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G109" t="n">
-        <v>31.37</v>
+        <v>103.14</v>
       </c>
       <c r="H109" t="n">
-        <v>0.21</v>
+        <v>3.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.67</v>
+        <v>3.05</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E110" t="n">
-        <v>103.14</v>
+        <v>6.785</v>
       </c>
       <c r="F110" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G110" t="n">
-        <v>103.14</v>
+        <v>61.06</v>
       </c>
       <c r="H110" t="n">
-        <v>3.05</v>
+        <v>4.91</v>
       </c>
       <c r="I110" t="n">
-        <v>3.05</v>
+        <v>8.74</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E111" t="n">
-        <v>40.5</v>
+        <v>23.33</v>
       </c>
       <c r="F111" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G111" t="n">
-        <v>162</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>22.98</v>
+        <v>4.32</v>
       </c>
       <c r="I111" t="n">
-        <v>16.53</v>
+        <v>6.58</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E122" t="n">
-        <v>40.395</v>
+        <v>11.038</v>
       </c>
       <c r="F122" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G122" t="n">
-        <v>161.58</v>
+        <v>33.11</v>
       </c>
       <c r="H122" t="n">
-        <v>22.56</v>
+        <v>1.95</v>
       </c>
       <c r="I122" t="n">
-        <v>16.23</v>
+        <v>6.26</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E123" t="n">
-        <v>106</v>
+        <v>6.901</v>
       </c>
       <c r="F123" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G123" t="n">
-        <v>106</v>
+        <v>62.11</v>
       </c>
       <c r="H123" t="n">
-        <v>5.91</v>
+        <v>5.96</v>
       </c>
       <c r="I123" t="n">
-        <v>5.9</v>
+        <v>10.61</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E125" t="n">
-        <v>6.901</v>
+        <v>106</v>
       </c>
       <c r="F125" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G125" t="n">
-        <v>62.11</v>
+        <v>106</v>
       </c>
       <c r="H125" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="I125" t="n">
-        <v>10.61</v>
+        <v>5.9</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E126" t="n">
-        <v>11.038</v>
+        <v>40.395</v>
       </c>
       <c r="F126" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G126" t="n">
-        <v>33.11</v>
+        <v>161.58</v>
       </c>
       <c r="H126" t="n">
-        <v>1.95</v>
+        <v>22.56</v>
       </c>
       <c r="I126" t="n">
-        <v>6.26</v>
+        <v>16.23</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E137" t="n">
-        <v>104.76</v>
+        <v>11.728</v>
       </c>
       <c r="F137" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G137" t="n">
-        <v>104.76</v>
+        <v>35.18</v>
       </c>
       <c r="H137" t="n">
-        <v>4.67</v>
+        <v>4.02</v>
       </c>
       <c r="I137" t="n">
-        <v>4.67</v>
+        <v>12.9</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E138" t="n">
-        <v>40.61</v>
+        <v>23.3</v>
       </c>
       <c r="F138" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G138" t="n">
-        <v>162.44</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>23.42</v>
+        <v>4.23</v>
       </c>
       <c r="I138" t="n">
-        <v>16.85</v>
+        <v>6.44</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E139" t="n">
-        <v>6.927</v>
+        <v>104.76</v>
       </c>
       <c r="F139" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G139" t="n">
-        <v>62.34</v>
+        <v>104.76</v>
       </c>
       <c r="H139" t="n">
-        <v>6.19</v>
+        <v>4.67</v>
       </c>
       <c r="I139" t="n">
-        <v>11.02</v>
+        <v>4.67</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>40.61</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>162.44</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>23.42</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>16.85</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E141" t="n">
-        <v>11.728</v>
+        <v>6.927</v>
       </c>
       <c r="F141" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G141" t="n">
-        <v>35.18</v>
+        <v>62.34</v>
       </c>
       <c r="H141" t="n">
-        <v>4.02</v>
+        <v>6.19</v>
       </c>
       <c r="I141" t="n">
-        <v>12.9</v>
+        <v>11.02</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E152" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F152" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G152" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H152" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I152" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E153" t="n">
-        <v>39.915</v>
+        <v>11.034</v>
       </c>
       <c r="F153" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G153" t="n">
-        <v>159.66</v>
+        <v>33.1</v>
       </c>
       <c r="H153" t="n">
-        <v>20.64</v>
+        <v>1.94</v>
       </c>
       <c r="I153" t="n">
-        <v>14.85</v>
+        <v>6.23</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E154" t="n">
-        <v>6.893</v>
+        <v>104.12</v>
       </c>
       <c r="F154" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G154" t="n">
-        <v>62.04</v>
+        <v>104.12</v>
       </c>
       <c r="H154" t="n">
-        <v>5.89</v>
+        <v>4.03</v>
       </c>
       <c r="I154" t="n">
-        <v>10.49</v>
+        <v>4.03</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E155" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F155" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G155" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H155" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I155" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D156" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E156" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F156" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G156" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H156" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I156" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E162" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F162" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G162" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H162" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I162" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E163" t="n">
-        <v>103.84</v>
+        <v>23.01</v>
       </c>
       <c r="F163" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G163" t="n">
-        <v>103.84</v>
+        <v>69.03</v>
       </c>
       <c r="H163" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="I163" t="n">
-        <v>3.75</v>
+        <v>5.12</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E165" t="n">
-        <v>38.845</v>
+        <v>103.84</v>
       </c>
       <c r="F165" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G165" t="n">
-        <v>155.38</v>
+        <v>103.84</v>
       </c>
       <c r="H165" t="n">
-        <v>16.36</v>
+        <v>3.75</v>
       </c>
       <c r="I165" t="n">
-        <v>11.77</v>
+        <v>3.75</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E166" t="n">
-        <v>23.01</v>
+        <v>10.748</v>
       </c>
       <c r="F166" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G166" t="n">
-        <v>69.03</v>
+        <v>32.24</v>
       </c>
       <c r="H166" t="n">
-        <v>3.36</v>
+        <v>1.08</v>
       </c>
       <c r="I166" t="n">
-        <v>5.12</v>
+        <v>3.47</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E177" t="n">
-        <v>10.642</v>
+        <v>22.95</v>
       </c>
       <c r="F177" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G177" t="n">
-        <v>31.93</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>0.77</v>
+        <v>3.18</v>
       </c>
       <c r="I177" t="n">
-        <v>2.47</v>
+        <v>4.84</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E178" t="n">
-        <v>38.245</v>
+        <v>102.54</v>
       </c>
       <c r="F178" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G178" t="n">
-        <v>152.98</v>
+        <v>102.54</v>
       </c>
       <c r="H178" t="n">
-        <v>13.96</v>
+        <v>2.45</v>
       </c>
       <c r="I178" t="n">
-        <v>10.04</v>
+        <v>2.45</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E179" t="n">
-        <v>6.922</v>
+        <v>10.642</v>
       </c>
       <c r="F179" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G179" t="n">
-        <v>62.3</v>
+        <v>31.93</v>
       </c>
       <c r="H179" t="n">
-        <v>6.15</v>
+        <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>10.95</v>
+        <v>2.47</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E180" t="n">
-        <v>102.54</v>
+        <v>38.245</v>
       </c>
       <c r="F180" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G180" t="n">
-        <v>102.54</v>
+        <v>152.98</v>
       </c>
       <c r="H180" t="n">
-        <v>2.45</v>
+        <v>13.96</v>
       </c>
       <c r="I180" t="n">
-        <v>2.45</v>
+        <v>10.04</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D181" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E181" t="n">
-        <v>22.95</v>
+        <v>6.922</v>
       </c>
       <c r="F181" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G181" t="n">
-        <v>68.84999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H181" t="n">
-        <v>3.18</v>
+        <v>6.15</v>
       </c>
       <c r="I181" t="n">
-        <v>4.84</v>
+        <v>10.95</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E187" t="n">
-        <v>22.845</v>
+        <v>101.44</v>
       </c>
       <c r="F187" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G187" t="n">
-        <v>68.53</v>
+        <v>101.44</v>
       </c>
       <c r="H187" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>4.36</v>
+        <v>1.35</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D188" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E188" t="n">
-        <v>10.708</v>
+        <v>37.85</v>
       </c>
       <c r="F188" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G188" t="n">
-        <v>32.12</v>
+        <v>151.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.96</v>
+        <v>12.38</v>
       </c>
       <c r="I188" t="n">
-        <v>3.08</v>
+        <v>8.91</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D189" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E189" t="n">
-        <v>37.85</v>
+        <v>6.862</v>
       </c>
       <c r="F189" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G189" t="n">
-        <v>151.4</v>
+        <v>61.76</v>
       </c>
       <c r="H189" t="n">
-        <v>12.38</v>
+        <v>5.61</v>
       </c>
       <c r="I189" t="n">
-        <v>8.91</v>
+        <v>9.99</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E190" t="n">
-        <v>101.44</v>
+        <v>22.845</v>
       </c>
       <c r="F190" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G190" t="n">
-        <v>101.44</v>
+        <v>68.53</v>
       </c>
       <c r="H190" t="n">
-        <v>1.35</v>
+        <v>2.86</v>
       </c>
       <c r="I190" t="n">
-        <v>1.35</v>
+        <v>4.36</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E191" t="n">
-        <v>6.862</v>
+        <v>10.708</v>
       </c>
       <c r="F191" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G191" t="n">
-        <v>61.76</v>
+        <v>32.12</v>
       </c>
       <c r="H191" t="n">
-        <v>5.61</v>
+        <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>9.99</v>
+        <v>3.08</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D202" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E202" t="n">
-        <v>100.08</v>
+        <v>11.044</v>
       </c>
       <c r="F202" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G202" t="n">
-        <v>100.08</v>
+        <v>33.13</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.01</v>
+        <v>1.97</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.01</v>
+        <v>6.32</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E203" t="n">
-        <v>22.4</v>
+        <v>38.04</v>
       </c>
       <c r="F203" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G203" t="n">
-        <v>67.2</v>
+        <v>152.16</v>
       </c>
       <c r="H203" t="n">
-        <v>1.53</v>
+        <v>13.14</v>
       </c>
       <c r="I203" t="n">
-        <v>2.33</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7346,29 +7346,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D204" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E204" t="n">
-        <v>6.822</v>
+        <v>22.4</v>
       </c>
       <c r="F204" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G204" t="n">
-        <v>61.4</v>
+        <v>67.2</v>
       </c>
       <c r="H204" t="n">
-        <v>5.25</v>
+        <v>1.53</v>
       </c>
       <c r="I204" t="n">
-        <v>9.35</v>
+        <v>2.33</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E205" t="n">
-        <v>38.04</v>
+        <v>100.08</v>
       </c>
       <c r="F205" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G205" t="n">
-        <v>152.16</v>
+        <v>100.08</v>
       </c>
       <c r="H205" t="n">
-        <v>13.14</v>
+        <v>-0.01</v>
       </c>
       <c r="I205" t="n">
-        <v>9.449999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D206" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E206" t="n">
-        <v>11.044</v>
+        <v>6.822</v>
       </c>
       <c r="F206" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G206" t="n">
-        <v>33.13</v>
+        <v>61.4</v>
       </c>
       <c r="H206" t="n">
-        <v>1.97</v>
+        <v>5.25</v>
       </c>
       <c r="I206" t="n">
-        <v>6.32</v>
+        <v>9.35</v>
       </c>
       <c r="J206" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D212" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E212" t="n">
-        <v>11.338</v>
+        <v>37.25</v>
       </c>
       <c r="F212" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G212" t="n">
-        <v>34.01</v>
+        <v>149</v>
       </c>
       <c r="H212" t="n">
-        <v>2.85</v>
+        <v>9.98</v>
       </c>
       <c r="I212" t="n">
-        <v>9.15</v>
+        <v>7.18</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C213" t="n">
         <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E213" t="n">
-        <v>22.885</v>
+        <v>11.338</v>
       </c>
       <c r="F213" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G213" t="n">
-        <v>68.66</v>
+        <v>34.01</v>
       </c>
       <c r="H213" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="I213" t="n">
-        <v>4.55</v>
+        <v>9.15</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E214" t="n">
-        <v>98.29000000000001</v>
+        <v>22.885</v>
       </c>
       <c r="F214" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G214" t="n">
-        <v>98.29000000000001</v>
+        <v>68.66</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.8</v>
+        <v>2.99</v>
       </c>
       <c r="I214" t="n">
-        <v>-1.8</v>
+        <v>4.55</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E215" t="n">
-        <v>37.25</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F215" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G215" t="n">
-        <v>149</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H215" t="n">
-        <v>9.98</v>
+        <v>-1.8</v>
       </c>
       <c r="I215" t="n">
-        <v>7.18</v>
+        <v>-1.8</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E217" t="n">
-        <v>23.175</v>
+        <v>11.546</v>
       </c>
       <c r="F217" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G217" t="n">
-        <v>69.53</v>
+        <v>34.64</v>
       </c>
       <c r="H217" t="n">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="I217" t="n">
-        <v>5.88</v>
+        <v>11.17</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E218" t="n">
-        <v>36.75</v>
+        <v>6.864</v>
       </c>
       <c r="F218" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G218" t="n">
-        <v>147</v>
+        <v>61.78</v>
       </c>
       <c r="H218" t="n">
-        <v>7.98</v>
+        <v>5.63</v>
       </c>
       <c r="I218" t="n">
-        <v>5.74</v>
+        <v>10.03</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D220" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E220" t="n">
-        <v>6.864</v>
+        <v>36.75</v>
       </c>
       <c r="F220" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G220" t="n">
-        <v>61.78</v>
+        <v>147</v>
       </c>
       <c r="H220" t="n">
-        <v>5.63</v>
+        <v>7.98</v>
       </c>
       <c r="I220" t="n">
-        <v>10.03</v>
+        <v>5.74</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C221" t="n">
         <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E221" t="n">
-        <v>11.546</v>
+        <v>23.175</v>
       </c>
       <c r="F221" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G221" t="n">
-        <v>34.64</v>
+        <v>69.53</v>
       </c>
       <c r="H221" t="n">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="I221" t="n">
-        <v>11.17</v>
+        <v>5.88</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C227" t="n">
         <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E227" t="n">
-        <v>23.07</v>
+        <v>11.512</v>
       </c>
       <c r="F227" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G227" t="n">
-        <v>69.20999999999999</v>
+        <v>34.54</v>
       </c>
       <c r="H227" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="I227" t="n">
-        <v>5.39</v>
+        <v>10.85</v>
       </c>
       <c r="J227" t="n">
         <v>7.91</v>
@@ -8162,29 +8162,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D228" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E228" t="n">
-        <v>36.64</v>
+        <v>6.779</v>
       </c>
       <c r="F228" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G228" t="n">
-        <v>146.56</v>
+        <v>61.01</v>
       </c>
       <c r="H228" t="n">
-        <v>7.54</v>
+        <v>4.86</v>
       </c>
       <c r="I228" t="n">
-        <v>5.42</v>
+        <v>8.66</v>
       </c>
       <c r="J228" t="n">
         <v>7.91</v>
@@ -8196,29 +8196,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E229" t="n">
-        <v>6.779</v>
+        <v>97.34</v>
       </c>
       <c r="F229" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G229" t="n">
-        <v>61.01</v>
+        <v>97.34</v>
       </c>
       <c r="H229" t="n">
-        <v>4.86</v>
+        <v>-2.75</v>
       </c>
       <c r="I229" t="n">
-        <v>8.66</v>
+        <v>-2.75</v>
       </c>
       <c r="J229" t="n">
         <v>7.91</v>
@@ -8230,29 +8230,29 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E230" t="n">
-        <v>11.512</v>
+        <v>23.07</v>
       </c>
       <c r="F230" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G230" t="n">
-        <v>34.54</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H230" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="I230" t="n">
-        <v>10.85</v>
+        <v>5.39</v>
       </c>
       <c r="J230" t="n">
         <v>7.91</v>
@@ -8264,29 +8264,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D231" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E231" t="n">
-        <v>97.34</v>
+        <v>36.64</v>
       </c>
       <c r="F231" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G231" t="n">
-        <v>97.34</v>
+        <v>146.56</v>
       </c>
       <c r="H231" t="n">
-        <v>-2.75</v>
+        <v>7.54</v>
       </c>
       <c r="I231" t="n">
-        <v>-2.75</v>
+        <v>5.42</v>
       </c>
       <c r="J231" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E242" t="n">
-        <v>7.005</v>
+        <v>23.465</v>
       </c>
       <c r="F242" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G242" t="n">
-        <v>63.05</v>
+        <v>70.39</v>
       </c>
       <c r="H242" t="n">
-        <v>6.9</v>
+        <v>4.72</v>
       </c>
       <c r="I242" t="n">
-        <v>12.29</v>
+        <v>7.19</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E243" t="n">
-        <v>12.08</v>
+        <v>38.52</v>
       </c>
       <c r="F243" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G243" t="n">
-        <v>36.24</v>
+        <v>154.08</v>
       </c>
       <c r="H243" t="n">
-        <v>5.08</v>
+        <v>15.06</v>
       </c>
       <c r="I243" t="n">
-        <v>16.3</v>
+        <v>10.83</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8706,29 +8706,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E244" t="n">
-        <v>38.52</v>
+        <v>102.86</v>
       </c>
       <c r="F244" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G244" t="n">
-        <v>154.08</v>
+        <v>102.86</v>
       </c>
       <c r="H244" t="n">
-        <v>15.06</v>
+        <v>2.77</v>
       </c>
       <c r="I244" t="n">
-        <v>10.83</v>
+        <v>2.77</v>
       </c>
       <c r="J244" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D245" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E245" t="n">
-        <v>23.465</v>
+        <v>7.005</v>
       </c>
       <c r="F245" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G245" t="n">
-        <v>70.39</v>
+        <v>63.05</v>
       </c>
       <c r="H245" t="n">
-        <v>4.72</v>
+        <v>6.9</v>
       </c>
       <c r="I245" t="n">
-        <v>7.19</v>
+        <v>12.29</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E246" t="n">
-        <v>102.86</v>
+        <v>12.08</v>
       </c>
       <c r="F246" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G246" t="n">
-        <v>102.86</v>
+        <v>36.24</v>
       </c>
       <c r="H246" t="n">
-        <v>2.77</v>
+        <v>5.08</v>
       </c>
       <c r="I246" t="n">
-        <v>2.77</v>
+        <v>16.3</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C257" t="n">
         <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E257" t="n">
-        <v>23.2</v>
+        <v>12.232</v>
       </c>
       <c r="F257" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G257" t="n">
-        <v>69.59999999999999</v>
+        <v>36.7</v>
       </c>
       <c r="H257" t="n">
-        <v>3.93</v>
+        <v>5.54</v>
       </c>
       <c r="I257" t="n">
-        <v>5.98</v>
+        <v>17.78</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D258" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E258" t="n">
-        <v>7.056</v>
+        <v>37.84</v>
       </c>
       <c r="F258" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G258" t="n">
-        <v>63.5</v>
+        <v>151.36</v>
       </c>
       <c r="H258" t="n">
-        <v>7.35</v>
+        <v>12.34</v>
       </c>
       <c r="I258" t="n">
-        <v>13.09</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E260" t="n">
-        <v>37.84</v>
+        <v>23.2</v>
       </c>
       <c r="F260" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G260" t="n">
-        <v>151.36</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H260" t="n">
-        <v>12.34</v>
+        <v>3.93</v>
       </c>
       <c r="I260" t="n">
-        <v>8.880000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E261" t="n">
-        <v>12.232</v>
+        <v>7.056</v>
       </c>
       <c r="F261" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G261" t="n">
-        <v>36.7</v>
+        <v>63.5</v>
       </c>
       <c r="H261" t="n">
-        <v>5.54</v>
+        <v>7.35</v>
       </c>
       <c r="I261" t="n">
-        <v>17.78</v>
+        <v>13.09</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C272" t="n">
         <v>3</v>
       </c>
       <c r="D272" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E272" t="n">
-        <v>23.135</v>
+        <v>12.308</v>
       </c>
       <c r="F272" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G272" t="n">
-        <v>69.41</v>
+        <v>36.92</v>
       </c>
       <c r="H272" t="n">
-        <v>3.74</v>
+        <v>5.76</v>
       </c>
       <c r="I272" t="n">
-        <v>5.7</v>
+        <v>18.49</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E273" t="n">
-        <v>7.091</v>
+        <v>104.54</v>
       </c>
       <c r="F273" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G273" t="n">
-        <v>63.82</v>
+        <v>104.54</v>
       </c>
       <c r="H273" t="n">
-        <v>7.67</v>
+        <v>4.45</v>
       </c>
       <c r="I273" t="n">
-        <v>13.66</v>
+        <v>4.45</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D275" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E275" t="n">
-        <v>104.54</v>
+        <v>7.091</v>
       </c>
       <c r="F275" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G275" t="n">
-        <v>104.54</v>
+        <v>63.82</v>
       </c>
       <c r="H275" t="n">
-        <v>4.45</v>
+        <v>7.67</v>
       </c>
       <c r="I275" t="n">
-        <v>4.45</v>
+        <v>13.66</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C276" t="n">
         <v>3</v>
       </c>
       <c r="D276" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E276" t="n">
-        <v>12.308</v>
+        <v>23.135</v>
       </c>
       <c r="F276" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G276" t="n">
-        <v>36.92</v>
+        <v>69.41</v>
       </c>
       <c r="H276" t="n">
-        <v>5.76</v>
+        <v>3.74</v>
       </c>
       <c r="I276" t="n">
-        <v>18.49</v>
+        <v>5.7</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D282" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E282" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F282" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G282" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H282" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I282" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D283" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E283" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F283" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G283" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H283" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I283" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D284" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E284" t="n">
-        <v>39.745</v>
+        <v>22.97</v>
       </c>
       <c r="F284" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G284" t="n">
-        <v>158.98</v>
+        <v>68.91</v>
       </c>
       <c r="H284" t="n">
-        <v>19.96</v>
+        <v>3.24</v>
       </c>
       <c r="I284" t="n">
-        <v>14.36</v>
+        <v>4.93</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D285" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E285" t="n">
-        <v>12.468</v>
+        <v>7.054</v>
       </c>
       <c r="F285" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G285" t="n">
-        <v>37.4</v>
+        <v>63.49</v>
       </c>
       <c r="H285" t="n">
-        <v>6.24</v>
+        <v>7.34</v>
       </c>
       <c r="I285" t="n">
-        <v>20.03</v>
+        <v>13.07</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E286" t="n">
-        <v>22.97</v>
+        <v>104.46</v>
       </c>
       <c r="F286" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G286" t="n">
-        <v>68.91</v>
+        <v>104.46</v>
       </c>
       <c r="H286" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="I286" t="n">
-        <v>4.93</v>
+        <v>4.37</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D297" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E297" t="n">
-        <v>22.78</v>
+        <v>6.915</v>
       </c>
       <c r="F297" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G297" t="n">
-        <v>68.34</v>
+        <v>62.23</v>
       </c>
       <c r="H297" t="n">
-        <v>2.67</v>
+        <v>6.08</v>
       </c>
       <c r="I297" t="n">
-        <v>4.07</v>
+        <v>10.83</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D298" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E298" t="n">
-        <v>38.49</v>
+        <v>11.92</v>
       </c>
       <c r="F298" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G298" t="n">
-        <v>153.96</v>
+        <v>35.76</v>
       </c>
       <c r="H298" t="n">
-        <v>14.94</v>
+        <v>4.6</v>
       </c>
       <c r="I298" t="n">
-        <v>10.75</v>
+        <v>14.76</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10576,29 +10576,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D299" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E299" t="n">
-        <v>11.92</v>
+        <v>100.42</v>
       </c>
       <c r="F299" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G299" t="n">
-        <v>35.76</v>
+        <v>100.42</v>
       </c>
       <c r="H299" t="n">
-        <v>4.6</v>
+        <v>0.33</v>
       </c>
       <c r="I299" t="n">
-        <v>14.76</v>
+        <v>0.33</v>
       </c>
       <c r="J299" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D300" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E300" t="n">
-        <v>6.915</v>
+        <v>22.78</v>
       </c>
       <c r="F300" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G300" t="n">
-        <v>62.23</v>
+        <v>68.34</v>
       </c>
       <c r="H300" t="n">
-        <v>6.08</v>
+        <v>2.67</v>
       </c>
       <c r="I300" t="n">
-        <v>10.83</v>
+        <v>4.07</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D301" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E301" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F301" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G301" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H301" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I301" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E312" t="n">
-        <v>38.66</v>
+        <v>100.38</v>
       </c>
       <c r="F312" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G312" t="n">
-        <v>154.64</v>
+        <v>100.38</v>
       </c>
       <c r="H312" t="n">
-        <v>15.62</v>
+        <v>0.29</v>
       </c>
       <c r="I312" t="n">
-        <v>11.24</v>
+        <v>0.29</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D313" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E313" t="n">
-        <v>11.742</v>
+        <v>6.936</v>
       </c>
       <c r="F313" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G313" t="n">
-        <v>35.23</v>
+        <v>62.42</v>
       </c>
       <c r="H313" t="n">
-        <v>4.07</v>
+        <v>6.27</v>
       </c>
       <c r="I313" t="n">
-        <v>13.06</v>
+        <v>11.17</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D315" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E315" t="n">
-        <v>6.936</v>
+        <v>38.66</v>
       </c>
       <c r="F315" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G315" t="n">
-        <v>62.42</v>
+        <v>154.64</v>
       </c>
       <c r="H315" t="n">
-        <v>6.27</v>
+        <v>15.62</v>
       </c>
       <c r="I315" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D316" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E316" t="n">
-        <v>100.38</v>
+        <v>11.742</v>
       </c>
       <c r="F316" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G316" t="n">
-        <v>100.38</v>
+        <v>35.23</v>
       </c>
       <c r="H316" t="n">
-        <v>0.29</v>
+        <v>4.07</v>
       </c>
       <c r="I316" t="n">
-        <v>0.29</v>
+        <v>13.06</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C327" t="n">
         <v>3</v>
       </c>
       <c r="D327" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E327" t="n">
-        <v>11.708</v>
+        <v>22.83</v>
       </c>
       <c r="F327" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G327" t="n">
-        <v>35.12</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H327" t="n">
-        <v>3.96</v>
+        <v>2.82</v>
       </c>
       <c r="I327" t="n">
-        <v>12.71</v>
+        <v>4.29</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D328" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E328" t="n">
-        <v>102.72</v>
+        <v>39.38</v>
       </c>
       <c r="F328" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G328" t="n">
-        <v>102.72</v>
+        <v>157.52</v>
       </c>
       <c r="H328" t="n">
-        <v>2.63</v>
+        <v>18.5</v>
       </c>
       <c r="I328" t="n">
-        <v>2.63</v>
+        <v>13.31</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11596,29 +11596,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E329" t="n">
-        <v>7.027</v>
+        <v>102.72</v>
       </c>
       <c r="F329" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G329" t="n">
-        <v>63.24</v>
+        <v>102.72</v>
       </c>
       <c r="H329" t="n">
-        <v>7.09</v>
+        <v>2.63</v>
       </c>
       <c r="I329" t="n">
-        <v>12.63</v>
+        <v>2.63</v>
       </c>
       <c r="J329" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D330" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E330" t="n">
-        <v>39.38</v>
+        <v>7.027</v>
       </c>
       <c r="F330" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G330" t="n">
-        <v>157.52</v>
+        <v>63.24</v>
       </c>
       <c r="H330" t="n">
-        <v>18.5</v>
+        <v>7.09</v>
       </c>
       <c r="I330" t="n">
-        <v>13.31</v>
+        <v>12.63</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C331" t="n">
         <v>3</v>
       </c>
       <c r="D331" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E331" t="n">
-        <v>22.83</v>
+        <v>11.708</v>
       </c>
       <c r="F331" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G331" t="n">
-        <v>68.48999999999999</v>
+        <v>35.12</v>
       </c>
       <c r="H331" t="n">
-        <v>2.82</v>
+        <v>3.96</v>
       </c>
       <c r="I331" t="n">
-        <v>4.29</v>
+        <v>12.71</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D337" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E337" t="n">
-        <v>39.15</v>
+        <v>6.938</v>
       </c>
       <c r="F337" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G337" t="n">
-        <v>156.6</v>
+        <v>62.44</v>
       </c>
       <c r="H337" t="n">
-        <v>17.58</v>
+        <v>6.29</v>
       </c>
       <c r="I337" t="n">
-        <v>12.65</v>
+        <v>11.2</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D338" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E338" t="n">
-        <v>101.04</v>
+        <v>22.845</v>
       </c>
       <c r="F338" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G338" t="n">
-        <v>101.04</v>
+        <v>68.53</v>
       </c>
       <c r="H338" t="n">
-        <v>0.95</v>
+        <v>2.86</v>
       </c>
       <c r="I338" t="n">
-        <v>0.95</v>
+        <v>4.36</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C339" t="n">
         <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E339" t="n">
-        <v>22.845</v>
+        <v>11.284</v>
       </c>
       <c r="F339" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G339" t="n">
-        <v>68.53</v>
+        <v>33.85</v>
       </c>
       <c r="H339" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="I339" t="n">
-        <v>4.36</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D340" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E340" t="n">
-        <v>6.938</v>
+        <v>39.15</v>
       </c>
       <c r="F340" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G340" t="n">
-        <v>62.44</v>
+        <v>156.6</v>
       </c>
       <c r="H340" t="n">
-        <v>6.29</v>
+        <v>17.58</v>
       </c>
       <c r="I340" t="n">
-        <v>11.2</v>
+        <v>12.65</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E341" t="n">
-        <v>11.284</v>
+        <v>101.04</v>
       </c>
       <c r="F341" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G341" t="n">
-        <v>33.85</v>
+        <v>101.04</v>
       </c>
       <c r="H341" t="n">
-        <v>2.69</v>
+        <v>0.95</v>
       </c>
       <c r="I341" t="n">
-        <v>8.630000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D352" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E352" t="n">
-        <v>39.745</v>
+        <v>22.75</v>
       </c>
       <c r="F352" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G352" t="n">
-        <v>158.98</v>
+        <v>68.25</v>
       </c>
       <c r="H352" t="n">
-        <v>19.96</v>
+        <v>2.58</v>
       </c>
       <c r="I352" t="n">
-        <v>14.36</v>
+        <v>3.93</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D353" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E353" t="n">
-        <v>101.76</v>
+        <v>6.983</v>
       </c>
       <c r="F353" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G353" t="n">
-        <v>101.76</v>
+        <v>62.85</v>
       </c>
       <c r="H353" t="n">
-        <v>1.67</v>
+        <v>6.7</v>
       </c>
       <c r="I353" t="n">
-        <v>1.67</v>
+        <v>11.93</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D354" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E354" t="n">
-        <v>6.983</v>
+        <v>11.186</v>
       </c>
       <c r="F354" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G354" t="n">
-        <v>62.85</v>
+        <v>33.56</v>
       </c>
       <c r="H354" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="I354" t="n">
-        <v>11.93</v>
+        <v>7.7</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D355" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E355" t="n">
-        <v>22.75</v>
+        <v>39.745</v>
       </c>
       <c r="F355" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G355" t="n">
-        <v>68.25</v>
+        <v>158.98</v>
       </c>
       <c r="H355" t="n">
-        <v>2.58</v>
+        <v>19.96</v>
       </c>
       <c r="I355" t="n">
-        <v>3.93</v>
+        <v>14.36</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D356" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E356" t="n">
-        <v>11.186</v>
+        <v>101.76</v>
       </c>
       <c r="F356" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G356" t="n">
-        <v>33.56</v>
+        <v>101.76</v>
       </c>
       <c r="H356" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="I356" t="n">
-        <v>7.7</v>
+        <v>1.67</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D367" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E367" t="n">
-        <v>101.5</v>
+        <v>6.91</v>
       </c>
       <c r="F367" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G367" t="n">
-        <v>101.5</v>
+        <v>62.19</v>
       </c>
       <c r="H367" t="n">
-        <v>1.41</v>
+        <v>6.04</v>
       </c>
       <c r="I367" t="n">
-        <v>1.41</v>
+        <v>10.76</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D368" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E368" t="n">
-        <v>10.91</v>
+        <v>39.935</v>
       </c>
       <c r="F368" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G368" t="n">
-        <v>32.73</v>
+        <v>159.74</v>
       </c>
       <c r="H368" t="n">
-        <v>1.57</v>
+        <v>20.72</v>
       </c>
       <c r="I368" t="n">
-        <v>5.04</v>
+        <v>14.9</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E370" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F370" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G370" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H370" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D371" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E371" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
       <c r="F371" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G371" t="n">
-        <v>62.19</v>
+        <v>32.73</v>
       </c>
       <c r="H371" t="n">
-        <v>6.04</v>
+        <v>1.57</v>
       </c>
       <c r="I371" t="n">
-        <v>10.76</v>
+        <v>5.04</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13398,29 +13398,29 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D382" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E382" t="n">
-        <v>101.3</v>
+        <v>6.931</v>
       </c>
       <c r="F382" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G382" t="n">
-        <v>101.3</v>
+        <v>62.38</v>
       </c>
       <c r="H382" t="n">
-        <v>1.21</v>
+        <v>6.23</v>
       </c>
       <c r="I382" t="n">
-        <v>1.21</v>
+        <v>11.1</v>
       </c>
       <c r="J382" t="n">
         <v>7.91</v>
@@ -13432,29 +13432,29 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D383" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E383" t="n">
-        <v>22.145</v>
+        <v>38.585</v>
       </c>
       <c r="F383" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G383" t="n">
-        <v>66.44</v>
+        <v>154.34</v>
       </c>
       <c r="H383" t="n">
-        <v>0.77</v>
+        <v>15.32</v>
       </c>
       <c r="I383" t="n">
-        <v>1.17</v>
+        <v>11.02</v>
       </c>
       <c r="J383" t="n">
         <v>7.91</v>
@@ -13466,29 +13466,29 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E384" t="n">
-        <v>10.88</v>
+        <v>22.145</v>
       </c>
       <c r="F384" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G384" t="n">
-        <v>32.64</v>
+        <v>66.44</v>
       </c>
       <c r="H384" t="n">
-        <v>1.48</v>
+        <v>0.77</v>
       </c>
       <c r="I384" t="n">
-        <v>4.75</v>
+        <v>1.17</v>
       </c>
       <c r="J384" t="n">
         <v>7.91</v>
@@ -13500,29 +13500,29 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D385" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E385" t="n">
-        <v>6.931</v>
+        <v>101.3</v>
       </c>
       <c r="F385" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G385" t="n">
-        <v>62.38</v>
+        <v>101.3</v>
       </c>
       <c r="H385" t="n">
-        <v>6.23</v>
+        <v>1.21</v>
       </c>
       <c r="I385" t="n">
-        <v>11.1</v>
+        <v>1.21</v>
       </c>
       <c r="J385" t="n">
         <v>7.91</v>
@@ -13534,29 +13534,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E386" t="n">
-        <v>38.585</v>
+        <v>10.88</v>
       </c>
       <c r="F386" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G386" t="n">
-        <v>154.34</v>
+        <v>32.64</v>
       </c>
       <c r="H386" t="n">
-        <v>15.32</v>
+        <v>1.48</v>
       </c>
       <c r="I386" t="n">
-        <v>11.02</v>
+        <v>4.75</v>
       </c>
       <c r="J386" t="n">
         <v>7.91</v>
@@ -13738,29 +13738,29 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D392" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E392" t="n">
-        <v>6.931</v>
+        <v>101.52</v>
       </c>
       <c r="F392" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G392" t="n">
-        <v>62.38</v>
+        <v>101.52</v>
       </c>
       <c r="H392" t="n">
-        <v>6.23</v>
+        <v>1.43</v>
       </c>
       <c r="I392" t="n">
-        <v>11.1</v>
+        <v>1.43</v>
       </c>
       <c r="J392" t="n">
         <v>7.91</v>
@@ -13772,29 +13772,29 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D393" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E393" t="n">
-        <v>38.92</v>
+        <v>21.845</v>
       </c>
       <c r="F393" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G393" t="n">
-        <v>155.68</v>
+        <v>65.53</v>
       </c>
       <c r="H393" t="n">
-        <v>16.66</v>
+        <v>-0.14</v>
       </c>
       <c r="I393" t="n">
-        <v>11.98</v>
+        <v>-0.21</v>
       </c>
       <c r="J393" t="n">
         <v>7.91</v>
@@ -13806,29 +13806,29 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C394" t="n">
         <v>3</v>
       </c>
       <c r="D394" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E394" t="n">
-        <v>21.845</v>
+        <v>11.1</v>
       </c>
       <c r="F394" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G394" t="n">
-        <v>65.53</v>
+        <v>33.3</v>
       </c>
       <c r="H394" t="n">
-        <v>-0.14</v>
+        <v>2.14</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.21</v>
+        <v>6.87</v>
       </c>
       <c r="J394" t="n">
         <v>7.91</v>
@@ -13840,29 +13840,29 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D395" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E395" t="n">
-        <v>101.52</v>
+        <v>6.931</v>
       </c>
       <c r="F395" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G395" t="n">
-        <v>101.52</v>
+        <v>62.38</v>
       </c>
       <c r="H395" t="n">
-        <v>1.43</v>
+        <v>6.23</v>
       </c>
       <c r="I395" t="n">
-        <v>1.43</v>
+        <v>11.1</v>
       </c>
       <c r="J395" t="n">
         <v>7.91</v>
@@ -13874,29 +13874,29 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D396" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E396" t="n">
-        <v>11.1</v>
+        <v>38.92</v>
       </c>
       <c r="F396" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G396" t="n">
-        <v>33.3</v>
+        <v>155.68</v>
       </c>
       <c r="H396" t="n">
-        <v>2.14</v>
+        <v>16.66</v>
       </c>
       <c r="I396" t="n">
-        <v>6.87</v>
+        <v>11.98</v>
       </c>
       <c r="J396" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D397" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E397" t="n">
-        <v>39.435</v>
+        <v>11.202</v>
       </c>
       <c r="F397" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G397" t="n">
-        <v>157.74</v>
+        <v>33.61</v>
       </c>
       <c r="H397" t="n">
-        <v>18.72</v>
+        <v>2.45</v>
       </c>
       <c r="I397" t="n">
-        <v>13.47</v>
+        <v>7.86</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E398" t="n">
-        <v>11.202</v>
+        <v>102.82</v>
       </c>
       <c r="F398" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G398" t="n">
-        <v>33.61</v>
+        <v>102.82</v>
       </c>
       <c r="H398" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="I398" t="n">
-        <v>7.86</v>
+        <v>2.73</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D399" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E399" t="n">
-        <v>102.82</v>
+        <v>6.982</v>
       </c>
       <c r="F399" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G399" t="n">
-        <v>102.82</v>
+        <v>62.84</v>
       </c>
       <c r="H399" t="n">
-        <v>2.73</v>
+        <v>6.69</v>
       </c>
       <c r="I399" t="n">
-        <v>2.73</v>
+        <v>11.91</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D400" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E400" t="n">
-        <v>6.982</v>
+        <v>22.145</v>
       </c>
       <c r="F400" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G400" t="n">
-        <v>62.84</v>
+        <v>66.44</v>
       </c>
       <c r="H400" t="n">
-        <v>6.69</v>
+        <v>0.77</v>
       </c>
       <c r="I400" t="n">
-        <v>11.91</v>
+        <v>1.17</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D401" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E401" t="n">
-        <v>22.145</v>
+        <v>39.435</v>
       </c>
       <c r="F401" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G401" t="n">
-        <v>66.44</v>
+        <v>157.74</v>
       </c>
       <c r="H401" t="n">
-        <v>0.77</v>
+        <v>18.72</v>
       </c>
       <c r="I401" t="n">
-        <v>1.17</v>
+        <v>13.47</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D407" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E407" t="n">
-        <v>105.98</v>
+        <v>40.695</v>
       </c>
       <c r="F407" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G407" t="n">
-        <v>105.98</v>
+        <v>162.78</v>
       </c>
       <c r="H407" t="n">
-        <v>5.89</v>
+        <v>23.76</v>
       </c>
       <c r="I407" t="n">
-        <v>5.88</v>
+        <v>17.09</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C408" t="n">
         <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E408" t="n">
-        <v>22.35</v>
+        <v>11.232</v>
       </c>
       <c r="F408" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G408" t="n">
-        <v>67.05</v>
+        <v>33.7</v>
       </c>
       <c r="H408" t="n">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="I408" t="n">
-        <v>2.1</v>
+        <v>8.15</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D409" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E409" t="n">
-        <v>7.049</v>
+        <v>22.35</v>
       </c>
       <c r="F409" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G409" t="n">
-        <v>63.44</v>
+        <v>67.05</v>
       </c>
       <c r="H409" t="n">
-        <v>7.29</v>
+        <v>1.38</v>
       </c>
       <c r="I409" t="n">
-        <v>12.98</v>
+        <v>2.1</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D410" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E410" t="n">
-        <v>40.695</v>
+        <v>105.98</v>
       </c>
       <c r="F410" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G410" t="n">
-        <v>162.78</v>
+        <v>105.98</v>
       </c>
       <c r="H410" t="n">
-        <v>23.76</v>
+        <v>5.89</v>
       </c>
       <c r="I410" t="n">
-        <v>17.09</v>
+        <v>5.88</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14384,29 +14384,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D411" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E411" t="n">
-        <v>11.232</v>
+        <v>7.049</v>
       </c>
       <c r="F411" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G411" t="n">
-        <v>33.7</v>
+        <v>63.44</v>
       </c>
       <c r="H411" t="n">
-        <v>2.54</v>
+        <v>7.29</v>
       </c>
       <c r="I411" t="n">
-        <v>8.15</v>
+        <v>12.98</v>
       </c>
       <c r="J411" t="n">
         <v>7.91</v>
@@ -14588,29 +14588,29 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D417" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E417" t="n">
-        <v>107.38</v>
+        <v>7.079</v>
       </c>
       <c r="F417" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G417" t="n">
-        <v>107.38</v>
+        <v>63.71</v>
       </c>
       <c r="H417" t="n">
-        <v>7.29</v>
+        <v>7.56</v>
       </c>
       <c r="I417" t="n">
-        <v>7.28</v>
+        <v>13.46</v>
       </c>
       <c r="J417" t="n">
         <v>7.91</v>
@@ -14622,29 +14622,29 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C418" t="n">
         <v>3</v>
       </c>
       <c r="D418" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E418" t="n">
-        <v>22.47</v>
+        <v>11.338</v>
       </c>
       <c r="F418" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G418" t="n">
-        <v>67.41</v>
+        <v>34.01</v>
       </c>
       <c r="H418" t="n">
-        <v>1.74</v>
+        <v>2.85</v>
       </c>
       <c r="I418" t="n">
-        <v>2.65</v>
+        <v>9.15</v>
       </c>
       <c r="J418" t="n">
         <v>7.91</v>
@@ -14656,29 +14656,29 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D419" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E419" t="n">
-        <v>11.338</v>
+        <v>40.63</v>
       </c>
       <c r="F419" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G419" t="n">
-        <v>34.01</v>
+        <v>162.52</v>
       </c>
       <c r="H419" t="n">
-        <v>2.85</v>
+        <v>23.5</v>
       </c>
       <c r="I419" t="n">
-        <v>9.15</v>
+        <v>16.9</v>
       </c>
       <c r="J419" t="n">
         <v>7.91</v>
@@ -14690,29 +14690,29 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D420" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E420" t="n">
-        <v>7.079</v>
+        <v>107.38</v>
       </c>
       <c r="F420" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G420" t="n">
-        <v>63.71</v>
+        <v>107.38</v>
       </c>
       <c r="H420" t="n">
-        <v>7.56</v>
+        <v>7.29</v>
       </c>
       <c r="I420" t="n">
-        <v>13.46</v>
+        <v>7.28</v>
       </c>
       <c r="J420" t="n">
         <v>7.91</v>
@@ -14724,29 +14724,29 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D421" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E421" t="n">
-        <v>40.63</v>
+        <v>22.47</v>
       </c>
       <c r="F421" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G421" t="n">
-        <v>162.52</v>
+        <v>67.41</v>
       </c>
       <c r="H421" t="n">
-        <v>23.5</v>
+        <v>1.74</v>
       </c>
       <c r="I421" t="n">
-        <v>16.9</v>
+        <v>2.65</v>
       </c>
       <c r="J421" t="n">
         <v>7.91</v>
@@ -14928,29 +14928,29 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D427" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E427" t="n">
-        <v>11.132</v>
+        <v>7.068</v>
       </c>
       <c r="F427" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G427" t="n">
-        <v>33.4</v>
+        <v>63.61</v>
       </c>
       <c r="H427" t="n">
-        <v>2.24</v>
+        <v>7.46</v>
       </c>
       <c r="I427" t="n">
-        <v>7.19</v>
+        <v>13.29</v>
       </c>
       <c r="J427" t="n">
         <v>7.91</v>
@@ -14962,29 +14962,29 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D428" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E428" t="n">
-        <v>40.57</v>
+        <v>11.132</v>
       </c>
       <c r="F428" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G428" t="n">
-        <v>162.28</v>
+        <v>33.4</v>
       </c>
       <c r="H428" t="n">
-        <v>23.26</v>
+        <v>2.24</v>
       </c>
       <c r="I428" t="n">
-        <v>16.73</v>
+        <v>7.19</v>
       </c>
       <c r="J428" t="n">
         <v>7.91</v>
@@ -14996,29 +14996,29 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D429" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E429" t="n">
-        <v>22.4</v>
+        <v>40.57</v>
       </c>
       <c r="F429" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G429" t="n">
-        <v>67.2</v>
+        <v>162.28</v>
       </c>
       <c r="H429" t="n">
-        <v>1.53</v>
+        <v>23.26</v>
       </c>
       <c r="I429" t="n">
-        <v>2.33</v>
+        <v>16.73</v>
       </c>
       <c r="J429" t="n">
         <v>7.91</v>
@@ -15030,29 +15030,29 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D430" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E430" t="n">
-        <v>107.54</v>
+        <v>22.4</v>
       </c>
       <c r="F430" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G430" t="n">
-        <v>107.54</v>
+        <v>67.2</v>
       </c>
       <c r="H430" t="n">
-        <v>7.45</v>
+        <v>1.53</v>
       </c>
       <c r="I430" t="n">
-        <v>7.44</v>
+        <v>2.33</v>
       </c>
       <c r="J430" t="n">
         <v>7.91</v>
@@ -15064,31 +15064,201 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E431" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="F431" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G431" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="H431" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I431" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="J431" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1</v>
+      </c>
+      <c r="D432" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E432" t="n">
+        <v>106.68</v>
+      </c>
+      <c r="F432" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G432" t="n">
+        <v>106.68</v>
+      </c>
+      <c r="H432" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="I432" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="J432" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>3</v>
+      </c>
+      <c r="D433" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E433" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="F433" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G433" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="H433" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I433" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="J433" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>4</v>
+      </c>
+      <c r="D434" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E434" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F434" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G434" t="n">
+        <v>160.24</v>
+      </c>
+      <c r="H434" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="I434" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="J434" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>3</v>
+      </c>
+      <c r="D435" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E435" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="F435" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G435" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J435" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C431" t="n">
+      <c r="C436" t="n">
         <v>9</v>
       </c>
-      <c r="D431" t="n">
+      <c r="D436" t="n">
         <v>6.239</v>
       </c>
-      <c r="E431" t="n">
-        <v>7.068</v>
-      </c>
-      <c r="F431" t="n">
+      <c r="E436" t="n">
+        <v>7.048</v>
+      </c>
+      <c r="F436" t="n">
         <v>56.15</v>
       </c>
-      <c r="G431" t="n">
-        <v>63.61</v>
-      </c>
-      <c r="H431" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="I431" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="J431" t="n">
+      <c r="G436" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="H436" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="I436" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="J436" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J436"/>
+  <dimension ref="A1:J441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E12" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F12" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G12" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H12" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E13" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F13" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G13" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H13" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I13" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E14" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F14" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G14" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H14" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E15" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F15" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G15" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E16" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F16" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G16" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I16" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E27" t="n">
-        <v>21.98</v>
+        <v>6.795</v>
       </c>
       <c r="F27" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G27" t="n">
-        <v>65.94</v>
+        <v>61.16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>5.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.41</v>
+        <v>8.92</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E28" t="n">
-        <v>10.66</v>
+        <v>104.9</v>
       </c>
       <c r="F28" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G28" t="n">
-        <v>31.98</v>
+        <v>104.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>4.81</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>4.81</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E29" t="n">
-        <v>40.532</v>
+        <v>21.98</v>
       </c>
       <c r="F29" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G29" t="n">
-        <v>162.13</v>
+        <v>65.94</v>
       </c>
       <c r="H29" t="n">
-        <v>23.11</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>16.62</v>
+        <v>0.41</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E30" t="n">
-        <v>104.9</v>
+        <v>10.66</v>
       </c>
       <c r="F30" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G30" t="n">
-        <v>104.9</v>
+        <v>31.98</v>
       </c>
       <c r="H30" t="n">
-        <v>4.81</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>4.81</v>
+        <v>2.63</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E31" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F31" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G31" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H31" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I31" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E37" t="n">
-        <v>10.67</v>
+        <v>21.839</v>
       </c>
       <c r="F37" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G37" t="n">
-        <v>32.01</v>
+        <v>65.52</v>
       </c>
       <c r="H37" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="I37" t="n">
-        <v>2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="J37" t="n">
         <v>7.91</v>
@@ -1702,29 +1702,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E38" t="n">
-        <v>6.728</v>
+        <v>102.8</v>
       </c>
       <c r="F38" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G38" t="n">
-        <v>60.55</v>
+        <v>102.8</v>
       </c>
       <c r="H38" t="n">
-        <v>4.4</v>
+        <v>2.71</v>
       </c>
       <c r="I38" t="n">
-        <v>7.84</v>
+        <v>2.71</v>
       </c>
       <c r="J38" t="n">
         <v>7.91</v>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E39" t="n">
-        <v>102.8</v>
+        <v>38.879</v>
       </c>
       <c r="F39" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G39" t="n">
-        <v>102.8</v>
+        <v>155.52</v>
       </c>
       <c r="H39" t="n">
-        <v>2.71</v>
+        <v>16.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2.71</v>
+        <v>11.87</v>
       </c>
       <c r="J39" t="n">
         <v>7.91</v>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E40" t="n">
-        <v>21.839</v>
+        <v>10.67</v>
       </c>
       <c r="F40" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G40" t="n">
-        <v>65.52</v>
+        <v>32.01</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.15</v>
+        <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.23</v>
+        <v>2.73</v>
       </c>
       <c r="J40" t="n">
         <v>7.91</v>
@@ -1804,29 +1804,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E41" t="n">
-        <v>38.879</v>
+        <v>6.728</v>
       </c>
       <c r="F41" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G41" t="n">
-        <v>155.52</v>
+        <v>60.55</v>
       </c>
       <c r="H41" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="I41" t="n">
-        <v>11.87</v>
+        <v>7.84</v>
       </c>
       <c r="J41" t="n">
         <v>7.91</v>
@@ -2178,29 +2178,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E52" t="n">
-        <v>21.703</v>
+        <v>10.702</v>
       </c>
       <c r="F52" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G52" t="n">
-        <v>65.11</v>
+        <v>32.11</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.85</v>
+        <v>3.05</v>
       </c>
       <c r="J52" t="n">
         <v>7.91</v>
@@ -2212,29 +2212,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E53" t="n">
-        <v>38.544</v>
+        <v>100.34</v>
       </c>
       <c r="F53" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G53" t="n">
-        <v>154.18</v>
+        <v>100.34</v>
       </c>
       <c r="H53" t="n">
-        <v>15.16</v>
+        <v>0.25</v>
       </c>
       <c r="I53" t="n">
-        <v>10.9</v>
+        <v>0.25</v>
       </c>
       <c r="J53" t="n">
         <v>7.91</v>
@@ -2246,29 +2246,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E54" t="n">
-        <v>100.34</v>
+        <v>6.629</v>
       </c>
       <c r="F54" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G54" t="n">
-        <v>100.34</v>
+        <v>59.66</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>3.51</v>
       </c>
       <c r="I54" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="J54" t="n">
         <v>7.91</v>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E55" t="n">
-        <v>6.629</v>
+        <v>21.703</v>
       </c>
       <c r="F55" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G55" t="n">
-        <v>59.66</v>
+        <v>65.11</v>
       </c>
       <c r="H55" t="n">
-        <v>3.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>6.25</v>
+        <v>-0.85</v>
       </c>
       <c r="J55" t="n">
         <v>7.91</v>
@@ -2314,29 +2314,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E56" t="n">
-        <v>10.702</v>
+        <v>38.544</v>
       </c>
       <c r="F56" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G56" t="n">
-        <v>32.11</v>
+        <v>154.18</v>
       </c>
       <c r="H56" t="n">
-        <v>0.95</v>
+        <v>15.16</v>
       </c>
       <c r="I56" t="n">
-        <v>3.05</v>
+        <v>10.9</v>
       </c>
       <c r="J56" t="n">
         <v>7.91</v>
@@ -2518,29 +2518,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E62" t="n">
-        <v>6.817</v>
+        <v>22.7</v>
       </c>
       <c r="F62" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G62" t="n">
-        <v>61.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="I62" t="n">
-        <v>9.26</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>7.91</v>
@@ -2552,29 +2552,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E63" t="n">
-        <v>10.712</v>
+        <v>41.064</v>
       </c>
       <c r="F63" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G63" t="n">
-        <v>32.14</v>
+        <v>164.26</v>
       </c>
       <c r="H63" t="n">
-        <v>0.98</v>
+        <v>25.24</v>
       </c>
       <c r="I63" t="n">
-        <v>3.15</v>
+        <v>18.16</v>
       </c>
       <c r="J63" t="n">
         <v>7.91</v>
@@ -2586,29 +2586,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E64" t="n">
-        <v>41.064</v>
+        <v>105.5</v>
       </c>
       <c r="F64" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G64" t="n">
-        <v>164.26</v>
+        <v>105.5</v>
       </c>
       <c r="H64" t="n">
-        <v>25.24</v>
+        <v>5.41</v>
       </c>
       <c r="I64" t="n">
-        <v>18.16</v>
+        <v>5.41</v>
       </c>
       <c r="J64" t="n">
         <v>7.91</v>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D65" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E65" t="n">
-        <v>105.5</v>
+        <v>6.817</v>
       </c>
       <c r="F65" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G65" t="n">
-        <v>105.5</v>
+        <v>61.35</v>
       </c>
       <c r="H65" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="I65" t="n">
-        <v>5.41</v>
+        <v>9.26</v>
       </c>
       <c r="J65" t="n">
         <v>7.91</v>
@@ -2654,29 +2654,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E66" t="n">
-        <v>22.7</v>
+        <v>10.712</v>
       </c>
       <c r="F66" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G66" t="n">
-        <v>68.09999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="H66" t="n">
-        <v>2.43</v>
+        <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="J66" t="n">
         <v>7.91</v>
@@ -2858,29 +2858,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E72" t="n">
-        <v>104.22</v>
+        <v>6.811</v>
       </c>
       <c r="F72" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G72" t="n">
-        <v>104.22</v>
+        <v>61.3</v>
       </c>
       <c r="H72" t="n">
-        <v>4.13</v>
+        <v>5.15</v>
       </c>
       <c r="I72" t="n">
-        <v>4.13</v>
+        <v>9.17</v>
       </c>
       <c r="J72" t="n">
         <v>7.91</v>
@@ -2892,29 +2892,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>104.22</v>
       </c>
       <c r="F73" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G73" t="n">
-        <v>69</v>
+        <v>104.22</v>
       </c>
       <c r="H73" t="n">
-        <v>3.33</v>
+        <v>4.13</v>
       </c>
       <c r="I73" t="n">
-        <v>5.07</v>
+        <v>4.13</v>
       </c>
       <c r="J73" t="n">
         <v>7.91</v>
@@ -2926,29 +2926,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E74" t="n">
-        <v>41.15</v>
+        <v>23</v>
       </c>
       <c r="F74" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G74" t="n">
-        <v>164.6</v>
+        <v>69</v>
       </c>
       <c r="H74" t="n">
-        <v>25.58</v>
+        <v>3.33</v>
       </c>
       <c r="I74" t="n">
-        <v>18.4</v>
+        <v>5.07</v>
       </c>
       <c r="J74" t="n">
         <v>7.91</v>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E75" t="n">
-        <v>6.811</v>
+        <v>41.15</v>
       </c>
       <c r="F75" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G75" t="n">
-        <v>61.3</v>
+        <v>164.6</v>
       </c>
       <c r="H75" t="n">
-        <v>5.15</v>
+        <v>25.58</v>
       </c>
       <c r="I75" t="n">
-        <v>9.17</v>
+        <v>18.4</v>
       </c>
       <c r="J75" t="n">
         <v>7.91</v>
@@ -3028,29 +3028,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E77" t="n">
-        <v>10.958</v>
+        <v>6.836</v>
       </c>
       <c r="F77" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G77" t="n">
-        <v>32.87</v>
+        <v>61.52</v>
       </c>
       <c r="H77" t="n">
-        <v>1.71</v>
+        <v>5.37</v>
       </c>
       <c r="I77" t="n">
-        <v>5.49</v>
+        <v>9.56</v>
       </c>
       <c r="J77" t="n">
         <v>7.91</v>
@@ -3062,29 +3062,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E78" t="n">
-        <v>23.4</v>
+        <v>105.8</v>
       </c>
       <c r="F78" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G78" t="n">
-        <v>70.2</v>
+        <v>105.8</v>
       </c>
       <c r="H78" t="n">
-        <v>4.53</v>
+        <v>5.71</v>
       </c>
       <c r="I78" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>7.91</v>
@@ -3096,29 +3096,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E79" t="n">
-        <v>105.8</v>
+        <v>42.25</v>
       </c>
       <c r="F79" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G79" t="n">
-        <v>105.8</v>
+        <v>169</v>
       </c>
       <c r="H79" t="n">
-        <v>5.71</v>
+        <v>29.98</v>
       </c>
       <c r="I79" t="n">
-        <v>5.7</v>
+        <v>21.57</v>
       </c>
       <c r="J79" t="n">
         <v>7.91</v>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E80" t="n">
-        <v>42.25</v>
+        <v>10.958</v>
       </c>
       <c r="F80" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G80" t="n">
-        <v>169</v>
+        <v>32.87</v>
       </c>
       <c r="H80" t="n">
-        <v>29.98</v>
+        <v>1.71</v>
       </c>
       <c r="I80" t="n">
-        <v>21.57</v>
+        <v>5.49</v>
       </c>
       <c r="J80" t="n">
         <v>7.91</v>
@@ -3164,29 +3164,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E81" t="n">
-        <v>6.836</v>
+        <v>23.4</v>
       </c>
       <c r="F81" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G81" t="n">
-        <v>61.52</v>
+        <v>70.2</v>
       </c>
       <c r="H81" t="n">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="I81" t="n">
-        <v>9.56</v>
+        <v>6.9</v>
       </c>
       <c r="J81" t="n">
         <v>7.91</v>
@@ -3368,29 +3368,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E87" t="n">
-        <v>43.005</v>
+        <v>23.32</v>
       </c>
       <c r="F87" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G87" t="n">
-        <v>172.02</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>33</v>
+        <v>4.29</v>
       </c>
       <c r="I87" t="n">
-        <v>23.74</v>
+        <v>6.53</v>
       </c>
       <c r="J87" t="n">
         <v>7.91</v>
@@ -3402,29 +3402,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E88" t="n">
-        <v>10.852</v>
+        <v>43.005</v>
       </c>
       <c r="F88" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G88" t="n">
-        <v>32.56</v>
+        <v>172.02</v>
       </c>
       <c r="H88" t="n">
-        <v>1.4</v>
+        <v>33</v>
       </c>
       <c r="I88" t="n">
-        <v>4.49</v>
+        <v>23.74</v>
       </c>
       <c r="J88" t="n">
         <v>7.91</v>
@@ -3436,29 +3436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E89" t="n">
-        <v>106.28</v>
+        <v>10.852</v>
       </c>
       <c r="F89" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G89" t="n">
-        <v>106.28</v>
+        <v>32.56</v>
       </c>
       <c r="H89" t="n">
-        <v>6.19</v>
+        <v>1.4</v>
       </c>
       <c r="I89" t="n">
-        <v>6.18</v>
+        <v>4.49</v>
       </c>
       <c r="J89" t="n">
         <v>7.91</v>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E90" t="n">
-        <v>6.856</v>
+        <v>106.28</v>
       </c>
       <c r="F90" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G90" t="n">
-        <v>61.7</v>
+        <v>106.28</v>
       </c>
       <c r="H90" t="n">
-        <v>5.55</v>
+        <v>6.19</v>
       </c>
       <c r="I90" t="n">
-        <v>9.880000000000001</v>
+        <v>6.18</v>
       </c>
       <c r="J90" t="n">
         <v>7.91</v>
@@ -3504,29 +3504,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D91" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32</v>
+        <v>6.856</v>
       </c>
       <c r="F91" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G91" t="n">
-        <v>69.95999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="H91" t="n">
-        <v>4.29</v>
+        <v>5.55</v>
       </c>
       <c r="I91" t="n">
-        <v>6.53</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J91" t="n">
         <v>7.91</v>
@@ -3538,29 +3538,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E92" t="n">
-        <v>10.876</v>
+        <v>103.88</v>
       </c>
       <c r="F92" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G92" t="n">
-        <v>32.63</v>
+        <v>103.88</v>
       </c>
       <c r="H92" t="n">
-        <v>1.47</v>
+        <v>3.79</v>
       </c>
       <c r="I92" t="n">
-        <v>4.72</v>
+        <v>3.79</v>
       </c>
       <c r="J92" t="n">
         <v>7.91</v>
@@ -3572,29 +3572,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E93" t="n">
-        <v>23.025</v>
+        <v>40.575</v>
       </c>
       <c r="F93" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G93" t="n">
-        <v>69.06999999999999</v>
+        <v>162.3</v>
       </c>
       <c r="H93" t="n">
-        <v>3.4</v>
+        <v>23.28</v>
       </c>
       <c r="I93" t="n">
-        <v>5.18</v>
+        <v>16.75</v>
       </c>
       <c r="J93" t="n">
         <v>7.91</v>
@@ -3606,29 +3606,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E94" t="n">
-        <v>6.797</v>
+        <v>23.025</v>
       </c>
       <c r="F94" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G94" t="n">
-        <v>61.17</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>5.02</v>
+        <v>3.4</v>
       </c>
       <c r="I94" t="n">
-        <v>8.94</v>
+        <v>5.18</v>
       </c>
       <c r="J94" t="n">
         <v>7.91</v>
@@ -3640,29 +3640,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E95" t="n">
-        <v>40.575</v>
+        <v>10.876</v>
       </c>
       <c r="F95" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G95" t="n">
-        <v>162.3</v>
+        <v>32.63</v>
       </c>
       <c r="H95" t="n">
-        <v>23.28</v>
+        <v>1.47</v>
       </c>
       <c r="I95" t="n">
-        <v>16.75</v>
+        <v>4.72</v>
       </c>
       <c r="J95" t="n">
         <v>7.91</v>
@@ -3674,29 +3674,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E96" t="n">
-        <v>103.88</v>
+        <v>6.797</v>
       </c>
       <c r="F96" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G96" t="n">
-        <v>103.88</v>
+        <v>61.17</v>
       </c>
       <c r="H96" t="n">
-        <v>3.79</v>
+        <v>5.02</v>
       </c>
       <c r="I96" t="n">
-        <v>3.79</v>
+        <v>8.94</v>
       </c>
       <c r="J96" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E97" t="n">
-        <v>40.65</v>
+        <v>6.839</v>
       </c>
       <c r="F97" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G97" t="n">
-        <v>162.6</v>
+        <v>61.55</v>
       </c>
       <c r="H97" t="n">
-        <v>23.58</v>
+        <v>5.4</v>
       </c>
       <c r="I97" t="n">
-        <v>16.96</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E98" t="n">
-        <v>23.35</v>
+        <v>40.65</v>
       </c>
       <c r="F98" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G98" t="n">
-        <v>70.05</v>
+        <v>162.6</v>
       </c>
       <c r="H98" t="n">
-        <v>4.38</v>
+        <v>23.58</v>
       </c>
       <c r="I98" t="n">
-        <v>6.67</v>
+        <v>16.96</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3776,29 +3776,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E99" t="n">
-        <v>10.642</v>
+        <v>23.35</v>
       </c>
       <c r="F99" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G99" t="n">
-        <v>31.93</v>
+        <v>70.05</v>
       </c>
       <c r="H99" t="n">
-        <v>0.77</v>
+        <v>4.38</v>
       </c>
       <c r="I99" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="J99" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E100" t="n">
-        <v>104.22</v>
+        <v>10.642</v>
       </c>
       <c r="F100" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G100" t="n">
-        <v>104.22</v>
+        <v>31.93</v>
       </c>
       <c r="H100" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>4.13</v>
+        <v>2.47</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E101" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F101" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G101" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H101" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I101" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E102" t="n">
-        <v>103.46</v>
+        <v>6.804</v>
       </c>
       <c r="F102" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G102" t="n">
-        <v>103.46</v>
+        <v>61.24</v>
       </c>
       <c r="H102" t="n">
-        <v>3.37</v>
+        <v>5.09</v>
       </c>
       <c r="I102" t="n">
-        <v>3.37</v>
+        <v>9.07</v>
       </c>
       <c r="J102" t="n">
         <v>7.91</v>
@@ -3912,29 +3912,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E103" t="n">
-        <v>40.97</v>
+        <v>23.29</v>
       </c>
       <c r="F103" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G103" t="n">
-        <v>163.88</v>
+        <v>69.87</v>
       </c>
       <c r="H103" t="n">
-        <v>24.86</v>
+        <v>4.2</v>
       </c>
       <c r="I103" t="n">
-        <v>17.88</v>
+        <v>6.4</v>
       </c>
       <c r="J103" t="n">
         <v>7.91</v>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E104" t="n">
-        <v>6.804</v>
+        <v>103.46</v>
       </c>
       <c r="F104" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G104" t="n">
-        <v>61.24</v>
+        <v>103.46</v>
       </c>
       <c r="H104" t="n">
-        <v>5.09</v>
+        <v>3.37</v>
       </c>
       <c r="I104" t="n">
-        <v>9.07</v>
+        <v>3.37</v>
       </c>
       <c r="J104" t="n">
         <v>7.91</v>
@@ -3980,29 +3980,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E105" t="n">
-        <v>23.29</v>
+        <v>40.97</v>
       </c>
       <c r="F105" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G105" t="n">
-        <v>69.87</v>
+        <v>163.88</v>
       </c>
       <c r="H105" t="n">
-        <v>4.2</v>
+        <v>24.86</v>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>17.88</v>
       </c>
       <c r="J105" t="n">
         <v>7.91</v>
@@ -4048,29 +4048,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E107" t="n">
-        <v>40.5</v>
+        <v>23.33</v>
       </c>
       <c r="F107" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G107" t="n">
-        <v>162</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>22.98</v>
+        <v>4.32</v>
       </c>
       <c r="I107" t="n">
-        <v>16.53</v>
+        <v>6.58</v>
       </c>
       <c r="J107" t="n">
         <v>7.91</v>
@@ -4082,29 +4082,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E108" t="n">
-        <v>10.456</v>
+        <v>103.14</v>
       </c>
       <c r="F108" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G108" t="n">
-        <v>31.37</v>
+        <v>103.14</v>
       </c>
       <c r="H108" t="n">
-        <v>0.21</v>
+        <v>3.05</v>
       </c>
       <c r="I108" t="n">
-        <v>0.67</v>
+        <v>3.05</v>
       </c>
       <c r="J108" t="n">
         <v>7.91</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E109" t="n">
-        <v>103.14</v>
+        <v>6.785</v>
       </c>
       <c r="F109" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G109" t="n">
-        <v>103.14</v>
+        <v>61.06</v>
       </c>
       <c r="H109" t="n">
-        <v>3.05</v>
+        <v>4.91</v>
       </c>
       <c r="I109" t="n">
-        <v>3.05</v>
+        <v>8.74</v>
       </c>
       <c r="J109" t="n">
         <v>7.91</v>
@@ -4150,29 +4150,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E110" t="n">
-        <v>6.785</v>
+        <v>10.456</v>
       </c>
       <c r="F110" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G110" t="n">
-        <v>61.06</v>
+        <v>31.37</v>
       </c>
       <c r="H110" t="n">
-        <v>4.91</v>
+        <v>0.21</v>
       </c>
       <c r="I110" t="n">
-        <v>8.74</v>
+        <v>0.67</v>
       </c>
       <c r="J110" t="n">
         <v>7.91</v>
@@ -4184,29 +4184,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E111" t="n">
-        <v>23.33</v>
+        <v>40.5</v>
       </c>
       <c r="F111" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G111" t="n">
-        <v>69.98999999999999</v>
+        <v>162</v>
       </c>
       <c r="H111" t="n">
-        <v>4.32</v>
+        <v>22.98</v>
       </c>
       <c r="I111" t="n">
-        <v>6.58</v>
+        <v>16.53</v>
       </c>
       <c r="J111" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E122" t="n">
-        <v>11.038</v>
+        <v>40.395</v>
       </c>
       <c r="F122" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G122" t="n">
-        <v>33.11</v>
+        <v>161.58</v>
       </c>
       <c r="H122" t="n">
-        <v>1.95</v>
+        <v>22.56</v>
       </c>
       <c r="I122" t="n">
-        <v>6.26</v>
+        <v>16.23</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E123" t="n">
-        <v>6.901</v>
+        <v>106</v>
       </c>
       <c r="F123" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G123" t="n">
-        <v>62.11</v>
+        <v>106</v>
       </c>
       <c r="H123" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="I123" t="n">
-        <v>10.61</v>
+        <v>5.9</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E125" t="n">
-        <v>106</v>
+        <v>6.901</v>
       </c>
       <c r="F125" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G125" t="n">
-        <v>106</v>
+        <v>62.11</v>
       </c>
       <c r="H125" t="n">
-        <v>5.91</v>
+        <v>5.96</v>
       </c>
       <c r="I125" t="n">
-        <v>5.9</v>
+        <v>10.61</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E126" t="n">
-        <v>40.395</v>
+        <v>11.038</v>
       </c>
       <c r="F126" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G126" t="n">
-        <v>161.58</v>
+        <v>33.11</v>
       </c>
       <c r="H126" t="n">
-        <v>22.56</v>
+        <v>1.95</v>
       </c>
       <c r="I126" t="n">
-        <v>16.23</v>
+        <v>6.26</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D137" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E137" t="n">
-        <v>11.728</v>
+        <v>6.927</v>
       </c>
       <c r="F137" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G137" t="n">
-        <v>35.18</v>
+        <v>62.34</v>
       </c>
       <c r="H137" t="n">
-        <v>4.02</v>
+        <v>6.19</v>
       </c>
       <c r="I137" t="n">
-        <v>12.9</v>
+        <v>11.02</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E138" t="n">
-        <v>23.3</v>
+        <v>40.61</v>
       </c>
       <c r="F138" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G138" t="n">
-        <v>69.90000000000001</v>
+        <v>162.44</v>
       </c>
       <c r="H138" t="n">
-        <v>4.23</v>
+        <v>23.42</v>
       </c>
       <c r="I138" t="n">
-        <v>6.44</v>
+        <v>16.85</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E139" t="n">
-        <v>104.76</v>
+        <v>11.728</v>
       </c>
       <c r="F139" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G139" t="n">
-        <v>104.76</v>
+        <v>35.18</v>
       </c>
       <c r="H139" t="n">
-        <v>4.67</v>
+        <v>4.02</v>
       </c>
       <c r="I139" t="n">
-        <v>4.67</v>
+        <v>12.9</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E140" t="n">
-        <v>40.61</v>
+        <v>23.3</v>
       </c>
       <c r="F140" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G140" t="n">
-        <v>162.44</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>23.42</v>
+        <v>4.23</v>
       </c>
       <c r="I140" t="n">
-        <v>16.85</v>
+        <v>6.44</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E141" t="n">
-        <v>6.927</v>
+        <v>104.76</v>
       </c>
       <c r="F141" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G141" t="n">
-        <v>62.34</v>
+        <v>104.76</v>
       </c>
       <c r="H141" t="n">
-        <v>6.19</v>
+        <v>4.67</v>
       </c>
       <c r="I141" t="n">
-        <v>11.02</v>
+        <v>4.67</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D152" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E152" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F152" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G152" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H152" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I152" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E153" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F153" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G153" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H153" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I153" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E154" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F154" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G154" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H154" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I154" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E155" t="n">
-        <v>39.915</v>
+        <v>11.034</v>
       </c>
       <c r="F155" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G155" t="n">
-        <v>159.66</v>
+        <v>33.1</v>
       </c>
       <c r="H155" t="n">
-        <v>20.64</v>
+        <v>1.94</v>
       </c>
       <c r="I155" t="n">
-        <v>14.85</v>
+        <v>6.23</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E156" t="n">
-        <v>6.893</v>
+        <v>104.12</v>
       </c>
       <c r="F156" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G156" t="n">
-        <v>62.04</v>
+        <v>104.12</v>
       </c>
       <c r="H156" t="n">
-        <v>5.89</v>
+        <v>4.03</v>
       </c>
       <c r="I156" t="n">
-        <v>10.49</v>
+        <v>4.03</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E162" t="n">
-        <v>38.845</v>
+        <v>103.84</v>
       </c>
       <c r="F162" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G162" t="n">
-        <v>155.38</v>
+        <v>103.84</v>
       </c>
       <c r="H162" t="n">
-        <v>16.36</v>
+        <v>3.75</v>
       </c>
       <c r="I162" t="n">
-        <v>11.77</v>
+        <v>3.75</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E163" t="n">
-        <v>23.01</v>
+        <v>10.748</v>
       </c>
       <c r="F163" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G163" t="n">
-        <v>69.03</v>
+        <v>32.24</v>
       </c>
       <c r="H163" t="n">
-        <v>3.36</v>
+        <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>5.12</v>
+        <v>3.47</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E165" t="n">
-        <v>103.84</v>
+        <v>23.01</v>
       </c>
       <c r="F165" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G165" t="n">
-        <v>103.84</v>
+        <v>69.03</v>
       </c>
       <c r="H165" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="I165" t="n">
-        <v>3.75</v>
+        <v>5.12</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6054,29 +6054,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E166" t="n">
-        <v>10.748</v>
+        <v>38.845</v>
       </c>
       <c r="F166" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G166" t="n">
-        <v>32.24</v>
+        <v>155.38</v>
       </c>
       <c r="H166" t="n">
-        <v>1.08</v>
+        <v>16.36</v>
       </c>
       <c r="I166" t="n">
-        <v>3.47</v>
+        <v>11.77</v>
       </c>
       <c r="J166" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E177" t="n">
-        <v>22.95</v>
+        <v>6.922</v>
       </c>
       <c r="F177" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G177" t="n">
-        <v>68.84999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H177" t="n">
-        <v>3.18</v>
+        <v>6.15</v>
       </c>
       <c r="I177" t="n">
-        <v>4.84</v>
+        <v>10.95</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D178" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E178" t="n">
-        <v>102.54</v>
+        <v>38.245</v>
       </c>
       <c r="F178" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G178" t="n">
-        <v>102.54</v>
+        <v>152.98</v>
       </c>
       <c r="H178" t="n">
-        <v>2.45</v>
+        <v>13.96</v>
       </c>
       <c r="I178" t="n">
-        <v>2.45</v>
+        <v>10.04</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E179" t="n">
-        <v>10.642</v>
+        <v>22.95</v>
       </c>
       <c r="F179" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G179" t="n">
-        <v>31.93</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>0.77</v>
+        <v>3.18</v>
       </c>
       <c r="I179" t="n">
-        <v>2.47</v>
+        <v>4.84</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E180" t="n">
-        <v>38.245</v>
+        <v>102.54</v>
       </c>
       <c r="F180" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G180" t="n">
-        <v>152.98</v>
+        <v>102.54</v>
       </c>
       <c r="H180" t="n">
-        <v>13.96</v>
+        <v>2.45</v>
       </c>
       <c r="I180" t="n">
-        <v>10.04</v>
+        <v>2.45</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E181" t="n">
-        <v>6.922</v>
+        <v>10.642</v>
       </c>
       <c r="F181" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G181" t="n">
-        <v>62.3</v>
+        <v>31.93</v>
       </c>
       <c r="H181" t="n">
-        <v>6.15</v>
+        <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>10.95</v>
+        <v>2.47</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6768,29 +6768,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E187" t="n">
-        <v>101.44</v>
+        <v>22.845</v>
       </c>
       <c r="F187" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G187" t="n">
-        <v>101.44</v>
+        <v>68.53</v>
       </c>
       <c r="H187" t="n">
-        <v>1.35</v>
+        <v>2.86</v>
       </c>
       <c r="I187" t="n">
-        <v>1.35</v>
+        <v>4.36</v>
       </c>
       <c r="J187" t="n">
         <v>7.91</v>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E188" t="n">
-        <v>37.85</v>
+        <v>6.862</v>
       </c>
       <c r="F188" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G188" t="n">
-        <v>151.4</v>
+        <v>61.76</v>
       </c>
       <c r="H188" t="n">
-        <v>12.38</v>
+        <v>5.61</v>
       </c>
       <c r="I188" t="n">
-        <v>8.91</v>
+        <v>9.99</v>
       </c>
       <c r="J188" t="n">
         <v>7.91</v>
@@ -6836,29 +6836,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E189" t="n">
-        <v>6.862</v>
+        <v>10.708</v>
       </c>
       <c r="F189" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G189" t="n">
-        <v>61.76</v>
+        <v>32.12</v>
       </c>
       <c r="H189" t="n">
-        <v>5.61</v>
+        <v>0.96</v>
       </c>
       <c r="I189" t="n">
-        <v>9.99</v>
+        <v>3.08</v>
       </c>
       <c r="J189" t="n">
         <v>7.91</v>
@@ -6870,29 +6870,29 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E190" t="n">
-        <v>22.845</v>
+        <v>101.44</v>
       </c>
       <c r="F190" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G190" t="n">
-        <v>68.53</v>
+        <v>101.44</v>
       </c>
       <c r="H190" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>4.36</v>
+        <v>1.35</v>
       </c>
       <c r="J190" t="n">
         <v>7.91</v>
@@ -6904,29 +6904,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E191" t="n">
-        <v>10.708</v>
+        <v>37.85</v>
       </c>
       <c r="F191" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G191" t="n">
-        <v>32.12</v>
+        <v>151.4</v>
       </c>
       <c r="H191" t="n">
-        <v>0.96</v>
+        <v>12.38</v>
       </c>
       <c r="I191" t="n">
-        <v>3.08</v>
+        <v>8.91</v>
       </c>
       <c r="J191" t="n">
         <v>7.91</v>
@@ -7278,29 +7278,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D202" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E202" t="n">
-        <v>11.044</v>
+        <v>6.822</v>
       </c>
       <c r="F202" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G202" t="n">
-        <v>33.13</v>
+        <v>61.4</v>
       </c>
       <c r="H202" t="n">
-        <v>1.97</v>
+        <v>5.25</v>
       </c>
       <c r="I202" t="n">
-        <v>6.32</v>
+        <v>9.35</v>
       </c>
       <c r="J202" t="n">
         <v>7.91</v>
@@ -7312,29 +7312,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E203" t="n">
-        <v>38.04</v>
+        <v>100.08</v>
       </c>
       <c r="F203" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G203" t="n">
-        <v>152.16</v>
+        <v>100.08</v>
       </c>
       <c r="H203" t="n">
-        <v>13.14</v>
+        <v>-0.01</v>
       </c>
       <c r="I203" t="n">
-        <v>9.449999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -7346,29 +7346,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D204" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E204" t="n">
-        <v>22.4</v>
+        <v>38.04</v>
       </c>
       <c r="F204" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G204" t="n">
-        <v>67.2</v>
+        <v>152.16</v>
       </c>
       <c r="H204" t="n">
-        <v>1.53</v>
+        <v>13.14</v>
       </c>
       <c r="I204" t="n">
-        <v>2.33</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D205" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E205" t="n">
-        <v>100.08</v>
+        <v>11.044</v>
       </c>
       <c r="F205" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G205" t="n">
-        <v>100.08</v>
+        <v>33.13</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.01</v>
+        <v>1.97</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.01</v>
+        <v>6.32</v>
       </c>
       <c r="J205" t="n">
         <v>7.91</v>
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D206" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E206" t="n">
-        <v>6.822</v>
+        <v>22.4</v>
       </c>
       <c r="F206" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G206" t="n">
-        <v>61.4</v>
+        <v>67.2</v>
       </c>
       <c r="H206" t="n">
-        <v>5.25</v>
+        <v>1.53</v>
       </c>
       <c r="I206" t="n">
-        <v>9.35</v>
+        <v>2.33</v>
       </c>
       <c r="J206" t="n">
         <v>7.91</v>
@@ -7618,29 +7618,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E212" t="n">
-        <v>37.25</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F212" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G212" t="n">
-        <v>149</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="H212" t="n">
-        <v>9.98</v>
+        <v>-1.8</v>
       </c>
       <c r="I212" t="n">
-        <v>7.18</v>
+        <v>-1.8</v>
       </c>
       <c r="J212" t="n">
         <v>7.91</v>
@@ -7652,29 +7652,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E213" t="n">
-        <v>11.338</v>
+        <v>37.25</v>
       </c>
       <c r="F213" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G213" t="n">
-        <v>34.01</v>
+        <v>149</v>
       </c>
       <c r="H213" t="n">
-        <v>2.85</v>
+        <v>9.98</v>
       </c>
       <c r="I213" t="n">
-        <v>9.15</v>
+        <v>7.18</v>
       </c>
       <c r="J213" t="n">
         <v>7.91</v>
@@ -7686,29 +7686,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E214" t="n">
-        <v>22.885</v>
+        <v>11.338</v>
       </c>
       <c r="F214" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G214" t="n">
-        <v>68.66</v>
+        <v>34.01</v>
       </c>
       <c r="H214" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="I214" t="n">
-        <v>4.55</v>
+        <v>9.15</v>
       </c>
       <c r="J214" t="n">
         <v>7.91</v>
@@ -7720,29 +7720,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E215" t="n">
-        <v>98.29000000000001</v>
+        <v>22.885</v>
       </c>
       <c r="F215" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G215" t="n">
-        <v>98.29000000000001</v>
+        <v>68.66</v>
       </c>
       <c r="H215" t="n">
-        <v>-1.8</v>
+        <v>2.99</v>
       </c>
       <c r="I215" t="n">
-        <v>-1.8</v>
+        <v>4.55</v>
       </c>
       <c r="J215" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E217" t="n">
-        <v>11.546</v>
+        <v>36.75</v>
       </c>
       <c r="F217" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G217" t="n">
-        <v>34.64</v>
+        <v>147</v>
       </c>
       <c r="H217" t="n">
-        <v>3.48</v>
+        <v>7.98</v>
       </c>
       <c r="I217" t="n">
-        <v>11.17</v>
+        <v>5.74</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E218" t="n">
-        <v>6.864</v>
+        <v>98.02</v>
       </c>
       <c r="F218" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G218" t="n">
-        <v>61.78</v>
+        <v>98.02</v>
       </c>
       <c r="H218" t="n">
-        <v>5.63</v>
+        <v>-2.07</v>
       </c>
       <c r="I218" t="n">
-        <v>10.03</v>
+        <v>-2.07</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E219" t="n">
-        <v>98.02</v>
+        <v>23.175</v>
       </c>
       <c r="F219" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G219" t="n">
-        <v>98.02</v>
+        <v>69.53</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.07</v>
+        <v>3.86</v>
       </c>
       <c r="I219" t="n">
-        <v>-2.07</v>
+        <v>5.88</v>
       </c>
       <c r="J219" t="n">
         <v>7.91</v>
@@ -7890,29 +7890,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E220" t="n">
-        <v>36.75</v>
+        <v>11.546</v>
       </c>
       <c r="F220" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G220" t="n">
-        <v>147</v>
+        <v>34.64</v>
       </c>
       <c r="H220" t="n">
-        <v>7.98</v>
+        <v>3.48</v>
       </c>
       <c r="I220" t="n">
-        <v>5.74</v>
+        <v>11.17</v>
       </c>
       <c r="J220" t="n">
         <v>7.91</v>
@@ -7924,29 +7924,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D221" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E221" t="n">
-        <v>23.175</v>
+        <v>6.864</v>
       </c>
       <c r="F221" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G221" t="n">
-        <v>69.53</v>
+        <v>61.78</v>
       </c>
       <c r="H221" t="n">
-        <v>3.86</v>
+        <v>5.63</v>
       </c>
       <c r="I221" t="n">
-        <v>5.88</v>
+        <v>10.03</v>
       </c>
       <c r="J221" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D232" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E232" t="n">
-        <v>37.44</v>
+        <v>6.812</v>
       </c>
       <c r="F232" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G232" t="n">
-        <v>149.76</v>
+        <v>61.31</v>
       </c>
       <c r="H232" t="n">
-        <v>10.74</v>
+        <v>5.16</v>
       </c>
       <c r="I232" t="n">
-        <v>7.73</v>
+        <v>9.19</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E233" t="n">
-        <v>23.17</v>
+        <v>97.86</v>
       </c>
       <c r="F233" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G233" t="n">
-        <v>69.51000000000001</v>
+        <v>97.86</v>
       </c>
       <c r="H233" t="n">
-        <v>3.84</v>
+        <v>-2.23</v>
       </c>
       <c r="I233" t="n">
-        <v>5.85</v>
+        <v>-2.23</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8366,29 +8366,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D234" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E234" t="n">
-        <v>11.544</v>
+        <v>37.44</v>
       </c>
       <c r="F234" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G234" t="n">
-        <v>34.63</v>
+        <v>149.76</v>
       </c>
       <c r="H234" t="n">
-        <v>3.47</v>
+        <v>10.74</v>
       </c>
       <c r="I234" t="n">
-        <v>11.14</v>
+        <v>7.73</v>
       </c>
       <c r="J234" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E235" t="n">
-        <v>97.86</v>
+        <v>23.17</v>
       </c>
       <c r="F235" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G235" t="n">
-        <v>97.86</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.23</v>
+        <v>3.84</v>
       </c>
       <c r="I235" t="n">
-        <v>-2.23</v>
+        <v>5.85</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E236" t="n">
-        <v>6.812</v>
+        <v>11.544</v>
       </c>
       <c r="F236" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G236" t="n">
-        <v>61.31</v>
+        <v>34.63</v>
       </c>
       <c r="H236" t="n">
-        <v>5.16</v>
+        <v>3.47</v>
       </c>
       <c r="I236" t="n">
-        <v>9.19</v>
+        <v>11.14</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8638,29 +8638,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D242" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E242" t="n">
-        <v>23.465</v>
+        <v>7.005</v>
       </c>
       <c r="F242" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G242" t="n">
-        <v>70.39</v>
+        <v>63.05</v>
       </c>
       <c r="H242" t="n">
-        <v>4.72</v>
+        <v>6.9</v>
       </c>
       <c r="I242" t="n">
-        <v>7.19</v>
+        <v>12.29</v>
       </c>
       <c r="J242" t="n">
         <v>7.91</v>
@@ -8672,29 +8672,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E243" t="n">
-        <v>38.52</v>
+        <v>102.86</v>
       </c>
       <c r="F243" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G243" t="n">
-        <v>154.08</v>
+        <v>102.86</v>
       </c>
       <c r="H243" t="n">
-        <v>15.06</v>
+        <v>2.77</v>
       </c>
       <c r="I243" t="n">
-        <v>10.83</v>
+        <v>2.77</v>
       </c>
       <c r="J243" t="n">
         <v>7.91</v>
@@ -8706,29 +8706,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E244" t="n">
-        <v>102.86</v>
+        <v>12.08</v>
       </c>
       <c r="F244" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G244" t="n">
-        <v>102.86</v>
+        <v>36.24</v>
       </c>
       <c r="H244" t="n">
-        <v>2.77</v>
+        <v>5.08</v>
       </c>
       <c r="I244" t="n">
-        <v>2.77</v>
+        <v>16.3</v>
       </c>
       <c r="J244" t="n">
         <v>7.91</v>
@@ -8740,29 +8740,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E245" t="n">
-        <v>7.005</v>
+        <v>23.465</v>
       </c>
       <c r="F245" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G245" t="n">
-        <v>63.05</v>
+        <v>70.39</v>
       </c>
       <c r="H245" t="n">
-        <v>6.9</v>
+        <v>4.72</v>
       </c>
       <c r="I245" t="n">
-        <v>12.29</v>
+        <v>7.19</v>
       </c>
       <c r="J245" t="n">
         <v>7.91</v>
@@ -8774,29 +8774,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D246" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E246" t="n">
-        <v>12.08</v>
+        <v>38.52</v>
       </c>
       <c r="F246" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G246" t="n">
-        <v>36.24</v>
+        <v>154.08</v>
       </c>
       <c r="H246" t="n">
-        <v>5.08</v>
+        <v>15.06</v>
       </c>
       <c r="I246" t="n">
-        <v>16.3</v>
+        <v>10.83</v>
       </c>
       <c r="J246" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D247" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E247" t="n">
-        <v>38.435</v>
+        <v>7.032</v>
       </c>
       <c r="F247" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G247" t="n">
-        <v>153.74</v>
+        <v>63.29</v>
       </c>
       <c r="H247" t="n">
-        <v>14.72</v>
+        <v>7.14</v>
       </c>
       <c r="I247" t="n">
-        <v>10.59</v>
+        <v>12.72</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E248" t="n">
-        <v>103.2</v>
+        <v>12.18</v>
       </c>
       <c r="F248" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G248" t="n">
-        <v>103.2</v>
+        <v>36.54</v>
       </c>
       <c r="H248" t="n">
-        <v>3.11</v>
+        <v>5.38</v>
       </c>
       <c r="I248" t="n">
-        <v>3.11</v>
+        <v>17.27</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8876,29 +8876,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D249" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E249" t="n">
-        <v>23.28</v>
+        <v>38.435</v>
       </c>
       <c r="F249" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G249" t="n">
-        <v>69.84</v>
+        <v>153.74</v>
       </c>
       <c r="H249" t="n">
-        <v>4.17</v>
+        <v>14.72</v>
       </c>
       <c r="I249" t="n">
-        <v>6.35</v>
+        <v>10.59</v>
       </c>
       <c r="J249" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E250" t="n">
-        <v>12.18</v>
+        <v>103.2</v>
       </c>
       <c r="F250" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G250" t="n">
-        <v>36.54</v>
+        <v>103.2</v>
       </c>
       <c r="H250" t="n">
-        <v>5.38</v>
+        <v>3.11</v>
       </c>
       <c r="I250" t="n">
-        <v>17.27</v>
+        <v>3.11</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E251" t="n">
-        <v>7.032</v>
+        <v>23.28</v>
       </c>
       <c r="F251" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G251" t="n">
-        <v>63.29</v>
+        <v>69.84</v>
       </c>
       <c r="H251" t="n">
-        <v>7.14</v>
+        <v>4.17</v>
       </c>
       <c r="I251" t="n">
-        <v>12.72</v>
+        <v>6.35</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -9148,29 +9148,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C257" t="n">
         <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E257" t="n">
-        <v>12.232</v>
+        <v>23.2</v>
       </c>
       <c r="F257" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G257" t="n">
-        <v>36.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>5.54</v>
+        <v>3.93</v>
       </c>
       <c r="I257" t="n">
-        <v>17.78</v>
+        <v>5.98</v>
       </c>
       <c r="J257" t="n">
         <v>7.91</v>
@@ -9182,29 +9182,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D258" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E258" t="n">
-        <v>37.84</v>
+        <v>7.056</v>
       </c>
       <c r="F258" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G258" t="n">
-        <v>151.36</v>
+        <v>63.5</v>
       </c>
       <c r="H258" t="n">
-        <v>12.34</v>
+        <v>7.35</v>
       </c>
       <c r="I258" t="n">
-        <v>8.880000000000001</v>
+        <v>13.09</v>
       </c>
       <c r="J258" t="n">
         <v>7.91</v>
@@ -9216,29 +9216,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D259" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E259" t="n">
-        <v>103.02</v>
+        <v>12.232</v>
       </c>
       <c r="F259" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G259" t="n">
-        <v>103.02</v>
+        <v>36.7</v>
       </c>
       <c r="H259" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="I259" t="n">
-        <v>2.93</v>
+        <v>17.78</v>
       </c>
       <c r="J259" t="n">
         <v>7.91</v>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D260" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E260" t="n">
-        <v>23.2</v>
+        <v>37.84</v>
       </c>
       <c r="F260" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G260" t="n">
-        <v>69.59999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="H260" t="n">
-        <v>3.93</v>
+        <v>12.34</v>
       </c>
       <c r="I260" t="n">
-        <v>5.98</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J260" t="n">
         <v>7.91</v>
@@ -9284,29 +9284,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E261" t="n">
-        <v>7.056</v>
+        <v>103.02</v>
       </c>
       <c r="F261" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G261" t="n">
-        <v>63.5</v>
+        <v>103.02</v>
       </c>
       <c r="H261" t="n">
-        <v>7.35</v>
+        <v>2.93</v>
       </c>
       <c r="I261" t="n">
-        <v>13.09</v>
+        <v>2.93</v>
       </c>
       <c r="J261" t="n">
         <v>7.91</v>
@@ -9658,29 +9658,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D272" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E272" t="n">
-        <v>12.308</v>
+        <v>7.091</v>
       </c>
       <c r="F272" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G272" t="n">
-        <v>36.92</v>
+        <v>63.82</v>
       </c>
       <c r="H272" t="n">
-        <v>5.76</v>
+        <v>7.67</v>
       </c>
       <c r="I272" t="n">
-        <v>18.49</v>
+        <v>13.66</v>
       </c>
       <c r="J272" t="n">
         <v>7.91</v>
@@ -9692,29 +9692,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E273" t="n">
-        <v>104.54</v>
+        <v>23.135</v>
       </c>
       <c r="F273" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G273" t="n">
-        <v>104.54</v>
+        <v>69.41</v>
       </c>
       <c r="H273" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="I273" t="n">
-        <v>4.45</v>
+        <v>5.7</v>
       </c>
       <c r="J273" t="n">
         <v>7.91</v>
@@ -9760,29 +9760,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D275" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E275" t="n">
-        <v>7.091</v>
+        <v>12.308</v>
       </c>
       <c r="F275" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G275" t="n">
-        <v>63.82</v>
+        <v>36.92</v>
       </c>
       <c r="H275" t="n">
-        <v>7.67</v>
+        <v>5.76</v>
       </c>
       <c r="I275" t="n">
-        <v>13.66</v>
+        <v>18.49</v>
       </c>
       <c r="J275" t="n">
         <v>7.91</v>
@@ -9794,29 +9794,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E276" t="n">
-        <v>23.135</v>
+        <v>104.54</v>
       </c>
       <c r="F276" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G276" t="n">
-        <v>69.41</v>
+        <v>104.54</v>
       </c>
       <c r="H276" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="I276" t="n">
-        <v>5.7</v>
+        <v>4.45</v>
       </c>
       <c r="J276" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D282" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E282" t="n">
-        <v>12.468</v>
+        <v>7.054</v>
       </c>
       <c r="F282" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G282" t="n">
-        <v>37.4</v>
+        <v>63.49</v>
       </c>
       <c r="H282" t="n">
-        <v>6.24</v>
+        <v>7.34</v>
       </c>
       <c r="I282" t="n">
-        <v>20.03</v>
+        <v>13.07</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D283" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E283" t="n">
-        <v>39.745</v>
+        <v>22.97</v>
       </c>
       <c r="F283" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G283" t="n">
-        <v>158.98</v>
+        <v>68.91</v>
       </c>
       <c r="H283" t="n">
-        <v>19.96</v>
+        <v>3.24</v>
       </c>
       <c r="I283" t="n">
-        <v>14.36</v>
+        <v>4.93</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E284" t="n">
-        <v>22.97</v>
+        <v>104.46</v>
       </c>
       <c r="F284" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G284" t="n">
-        <v>68.91</v>
+        <v>104.46</v>
       </c>
       <c r="H284" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="I284" t="n">
-        <v>4.93</v>
+        <v>4.37</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D285" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E285" t="n">
-        <v>7.054</v>
+        <v>12.468</v>
       </c>
       <c r="F285" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G285" t="n">
-        <v>63.49</v>
+        <v>37.4</v>
       </c>
       <c r="H285" t="n">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="I285" t="n">
-        <v>13.07</v>
+        <v>20.03</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D286" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E286" t="n">
-        <v>104.46</v>
+        <v>39.745</v>
       </c>
       <c r="F286" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G286" t="n">
-        <v>104.46</v>
+        <v>158.98</v>
       </c>
       <c r="H286" t="n">
-        <v>4.37</v>
+        <v>19.96</v>
       </c>
       <c r="I286" t="n">
-        <v>4.37</v>
+        <v>14.36</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10508,29 +10508,29 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D297" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E297" t="n">
-        <v>6.915</v>
+        <v>22.78</v>
       </c>
       <c r="F297" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G297" t="n">
-        <v>62.23</v>
+        <v>68.34</v>
       </c>
       <c r="H297" t="n">
-        <v>6.08</v>
+        <v>2.67</v>
       </c>
       <c r="I297" t="n">
-        <v>10.83</v>
+        <v>4.07</v>
       </c>
       <c r="J297" t="n">
         <v>7.91</v>
@@ -10542,29 +10542,29 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E298" t="n">
-        <v>11.92</v>
+        <v>100.42</v>
       </c>
       <c r="F298" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G298" t="n">
-        <v>35.76</v>
+        <v>100.42</v>
       </c>
       <c r="H298" t="n">
-        <v>4.6</v>
+        <v>0.33</v>
       </c>
       <c r="I298" t="n">
-        <v>14.76</v>
+        <v>0.33</v>
       </c>
       <c r="J298" t="n">
         <v>7.91</v>
@@ -10576,29 +10576,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D299" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E299" t="n">
-        <v>100.42</v>
+        <v>38.49</v>
       </c>
       <c r="F299" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G299" t="n">
-        <v>100.42</v>
+        <v>153.96</v>
       </c>
       <c r="H299" t="n">
-        <v>0.33</v>
+        <v>14.94</v>
       </c>
       <c r="I299" t="n">
-        <v>0.33</v>
+        <v>10.75</v>
       </c>
       <c r="J299" t="n">
         <v>7.91</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D300" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E300" t="n">
-        <v>22.78</v>
+        <v>6.915</v>
       </c>
       <c r="F300" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G300" t="n">
-        <v>68.34</v>
+        <v>62.23</v>
       </c>
       <c r="H300" t="n">
-        <v>2.67</v>
+        <v>6.08</v>
       </c>
       <c r="I300" t="n">
-        <v>4.07</v>
+        <v>10.83</v>
       </c>
       <c r="J300" t="n">
         <v>7.91</v>
@@ -10644,29 +10644,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D301" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E301" t="n">
-        <v>38.49</v>
+        <v>11.92</v>
       </c>
       <c r="F301" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G301" t="n">
-        <v>153.96</v>
+        <v>35.76</v>
       </c>
       <c r="H301" t="n">
-        <v>14.94</v>
+        <v>4.6</v>
       </c>
       <c r="I301" t="n">
-        <v>10.75</v>
+        <v>14.76</v>
       </c>
       <c r="J301" t="n">
         <v>7.91</v>
@@ -11018,29 +11018,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D312" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E312" t="n">
-        <v>100.38</v>
+        <v>11.742</v>
       </c>
       <c r="F312" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G312" t="n">
-        <v>100.38</v>
+        <v>35.23</v>
       </c>
       <c r="H312" t="n">
-        <v>0.29</v>
+        <v>4.07</v>
       </c>
       <c r="I312" t="n">
-        <v>0.29</v>
+        <v>13.06</v>
       </c>
       <c r="J312" t="n">
         <v>7.91</v>
@@ -11052,29 +11052,29 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D313" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E313" t="n">
-        <v>6.936</v>
+        <v>38.66</v>
       </c>
       <c r="F313" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G313" t="n">
-        <v>62.42</v>
+        <v>154.64</v>
       </c>
       <c r="H313" t="n">
-        <v>6.27</v>
+        <v>15.62</v>
       </c>
       <c r="I313" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="J313" t="n">
         <v>7.91</v>
@@ -11120,29 +11120,29 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E315" t="n">
-        <v>38.66</v>
+        <v>100.38</v>
       </c>
       <c r="F315" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G315" t="n">
-        <v>154.64</v>
+        <v>100.38</v>
       </c>
       <c r="H315" t="n">
-        <v>15.62</v>
+        <v>0.29</v>
       </c>
       <c r="I315" t="n">
-        <v>11.24</v>
+        <v>0.29</v>
       </c>
       <c r="J315" t="n">
         <v>7.91</v>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D316" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E316" t="n">
-        <v>11.742</v>
+        <v>6.936</v>
       </c>
       <c r="F316" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G316" t="n">
-        <v>35.23</v>
+        <v>62.42</v>
       </c>
       <c r="H316" t="n">
-        <v>4.07</v>
+        <v>6.27</v>
       </c>
       <c r="I316" t="n">
-        <v>13.06</v>
+        <v>11.17</v>
       </c>
       <c r="J316" t="n">
         <v>7.91</v>
@@ -11528,29 +11528,29 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C327" t="n">
         <v>3</v>
       </c>
       <c r="D327" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E327" t="n">
-        <v>22.83</v>
+        <v>11.708</v>
       </c>
       <c r="F327" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G327" t="n">
-        <v>68.48999999999999</v>
+        <v>35.12</v>
       </c>
       <c r="H327" t="n">
-        <v>2.82</v>
+        <v>3.96</v>
       </c>
       <c r="I327" t="n">
-        <v>4.29</v>
+        <v>12.71</v>
       </c>
       <c r="J327" t="n">
         <v>7.91</v>
@@ -11562,29 +11562,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D328" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E328" t="n">
-        <v>39.38</v>
+        <v>102.72</v>
       </c>
       <c r="F328" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G328" t="n">
-        <v>157.52</v>
+        <v>102.72</v>
       </c>
       <c r="H328" t="n">
-        <v>18.5</v>
+        <v>2.63</v>
       </c>
       <c r="I328" t="n">
-        <v>13.31</v>
+        <v>2.63</v>
       </c>
       <c r="J328" t="n">
         <v>7.91</v>
@@ -11596,29 +11596,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D329" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E329" t="n">
-        <v>102.72</v>
+        <v>7.027</v>
       </c>
       <c r="F329" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G329" t="n">
-        <v>102.72</v>
+        <v>63.24</v>
       </c>
       <c r="H329" t="n">
-        <v>2.63</v>
+        <v>7.09</v>
       </c>
       <c r="I329" t="n">
-        <v>2.63</v>
+        <v>12.63</v>
       </c>
       <c r="J329" t="n">
         <v>7.91</v>
@@ -11630,29 +11630,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D330" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E330" t="n">
-        <v>7.027</v>
+        <v>22.83</v>
       </c>
       <c r="F330" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G330" t="n">
-        <v>63.24</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H330" t="n">
-        <v>7.09</v>
+        <v>2.82</v>
       </c>
       <c r="I330" t="n">
-        <v>12.63</v>
+        <v>4.29</v>
       </c>
       <c r="J330" t="n">
         <v>7.91</v>
@@ -11664,29 +11664,29 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D331" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E331" t="n">
-        <v>11.708</v>
+        <v>39.38</v>
       </c>
       <c r="F331" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G331" t="n">
-        <v>35.12</v>
+        <v>157.52</v>
       </c>
       <c r="H331" t="n">
-        <v>3.96</v>
+        <v>18.5</v>
       </c>
       <c r="I331" t="n">
-        <v>12.71</v>
+        <v>13.31</v>
       </c>
       <c r="J331" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D337" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E337" t="n">
-        <v>6.938</v>
+        <v>39.15</v>
       </c>
       <c r="F337" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G337" t="n">
-        <v>62.44</v>
+        <v>156.6</v>
       </c>
       <c r="H337" t="n">
-        <v>6.29</v>
+        <v>17.58</v>
       </c>
       <c r="I337" t="n">
-        <v>11.2</v>
+        <v>12.65</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C338" t="n">
         <v>3</v>
       </c>
       <c r="D338" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E338" t="n">
-        <v>22.845</v>
+        <v>11.284</v>
       </c>
       <c r="F338" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G338" t="n">
-        <v>68.53</v>
+        <v>33.85</v>
       </c>
       <c r="H338" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="I338" t="n">
-        <v>4.36</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E339" t="n">
-        <v>11.284</v>
+        <v>101.04</v>
       </c>
       <c r="F339" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G339" t="n">
-        <v>33.85</v>
+        <v>101.04</v>
       </c>
       <c r="H339" t="n">
-        <v>2.69</v>
+        <v>0.95</v>
       </c>
       <c r="I339" t="n">
-        <v>8.630000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D340" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E340" t="n">
-        <v>39.15</v>
+        <v>6.938</v>
       </c>
       <c r="F340" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G340" t="n">
-        <v>156.6</v>
+        <v>62.44</v>
       </c>
       <c r="H340" t="n">
-        <v>17.58</v>
+        <v>6.29</v>
       </c>
       <c r="I340" t="n">
-        <v>12.65</v>
+        <v>11.2</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D341" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E341" t="n">
-        <v>101.04</v>
+        <v>22.845</v>
       </c>
       <c r="F341" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G341" t="n">
-        <v>101.04</v>
+        <v>68.53</v>
       </c>
       <c r="H341" t="n">
-        <v>0.95</v>
+        <v>2.86</v>
       </c>
       <c r="I341" t="n">
-        <v>0.95</v>
+        <v>4.36</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12378,29 +12378,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D352" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E352" t="n">
-        <v>22.75</v>
+        <v>39.745</v>
       </c>
       <c r="F352" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G352" t="n">
-        <v>68.25</v>
+        <v>158.98</v>
       </c>
       <c r="H352" t="n">
-        <v>2.58</v>
+        <v>19.96</v>
       </c>
       <c r="I352" t="n">
-        <v>3.93</v>
+        <v>14.36</v>
       </c>
       <c r="J352" t="n">
         <v>7.91</v>
@@ -12412,29 +12412,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D353" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E353" t="n">
-        <v>6.983</v>
+        <v>11.186</v>
       </c>
       <c r="F353" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G353" t="n">
-        <v>62.85</v>
+        <v>33.56</v>
       </c>
       <c r="H353" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="I353" t="n">
-        <v>11.93</v>
+        <v>7.7</v>
       </c>
       <c r="J353" t="n">
         <v>7.91</v>
@@ -12446,29 +12446,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E354" t="n">
-        <v>11.186</v>
+        <v>101.76</v>
       </c>
       <c r="F354" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G354" t="n">
-        <v>33.56</v>
+        <v>101.76</v>
       </c>
       <c r="H354" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="I354" t="n">
-        <v>7.7</v>
+        <v>1.67</v>
       </c>
       <c r="J354" t="n">
         <v>7.91</v>
@@ -12480,29 +12480,29 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D355" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E355" t="n">
-        <v>39.745</v>
+        <v>22.75</v>
       </c>
       <c r="F355" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G355" t="n">
-        <v>158.98</v>
+        <v>68.25</v>
       </c>
       <c r="H355" t="n">
-        <v>19.96</v>
+        <v>2.58</v>
       </c>
       <c r="I355" t="n">
-        <v>14.36</v>
+        <v>3.93</v>
       </c>
       <c r="J355" t="n">
         <v>7.91</v>
@@ -12514,29 +12514,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D356" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E356" t="n">
-        <v>101.76</v>
+        <v>6.983</v>
       </c>
       <c r="F356" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G356" t="n">
-        <v>101.76</v>
+        <v>62.85</v>
       </c>
       <c r="H356" t="n">
-        <v>1.67</v>
+        <v>6.7</v>
       </c>
       <c r="I356" t="n">
-        <v>1.67</v>
+        <v>11.93</v>
       </c>
       <c r="J356" t="n">
         <v>7.91</v>
@@ -12888,29 +12888,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D367" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E367" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
       <c r="F367" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G367" t="n">
-        <v>62.19</v>
+        <v>32.73</v>
       </c>
       <c r="H367" t="n">
-        <v>6.04</v>
+        <v>1.57</v>
       </c>
       <c r="I367" t="n">
-        <v>10.76</v>
+        <v>5.04</v>
       </c>
       <c r="J367" t="n">
         <v>7.91</v>
@@ -12922,29 +12922,29 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D368" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E368" t="n">
-        <v>39.935</v>
+        <v>101.5</v>
       </c>
       <c r="F368" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G368" t="n">
-        <v>159.74</v>
+        <v>101.5</v>
       </c>
       <c r="H368" t="n">
-        <v>20.72</v>
+        <v>1.41</v>
       </c>
       <c r="I368" t="n">
-        <v>14.9</v>
+        <v>1.41</v>
       </c>
       <c r="J368" t="n">
         <v>7.91</v>
@@ -12990,29 +12990,29 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D370" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E370" t="n">
-        <v>101.5</v>
+        <v>6.91</v>
       </c>
       <c r="F370" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G370" t="n">
-        <v>101.5</v>
+        <v>62.19</v>
       </c>
       <c r="H370" t="n">
-        <v>1.41</v>
+        <v>6.04</v>
       </c>
       <c r="I370" t="n">
-        <v>1.41</v>
+        <v>10.76</v>
       </c>
       <c r="J370" t="n">
         <v>7.91</v>
@@ -13024,29 +13024,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D371" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E371" t="n">
-        <v>10.91</v>
+        <v>39.935</v>
       </c>
       <c r="F371" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G371" t="n">
-        <v>32.73</v>
+        <v>159.74</v>
       </c>
       <c r="H371" t="n">
-        <v>1.57</v>
+        <v>20.72</v>
       </c>
       <c r="I371" t="n">
-        <v>5.04</v>
+        <v>14.9</v>
       </c>
       <c r="J371" t="n">
         <v>7.91</v>
@@ -13398,29 +13398,29 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D382" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E382" t="n">
-        <v>6.931</v>
+        <v>10.88</v>
       </c>
       <c r="F382" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G382" t="n">
-        <v>62.38</v>
+        <v>32.64</v>
       </c>
       <c r="H382" t="n">
-        <v>6.23</v>
+        <v>1.48</v>
       </c>
       <c r="I382" t="n">
-        <v>11.1</v>
+        <v>4.75</v>
       </c>
       <c r="J382" t="n">
         <v>7.91</v>
@@ -13432,29 +13432,29 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D383" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E383" t="n">
-        <v>38.585</v>
+        <v>22.145</v>
       </c>
       <c r="F383" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G383" t="n">
-        <v>154.34</v>
+        <v>66.44</v>
       </c>
       <c r="H383" t="n">
-        <v>15.32</v>
+        <v>0.77</v>
       </c>
       <c r="I383" t="n">
-        <v>11.02</v>
+        <v>1.17</v>
       </c>
       <c r="J383" t="n">
         <v>7.91</v>
@@ -13466,29 +13466,29 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D384" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E384" t="n">
-        <v>22.145</v>
+        <v>101.3</v>
       </c>
       <c r="F384" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G384" t="n">
-        <v>66.44</v>
+        <v>101.3</v>
       </c>
       <c r="H384" t="n">
-        <v>0.77</v>
+        <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="J384" t="n">
         <v>7.91</v>
@@ -13500,29 +13500,29 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D385" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E385" t="n">
-        <v>101.3</v>
+        <v>6.931</v>
       </c>
       <c r="F385" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G385" t="n">
-        <v>101.3</v>
+        <v>62.38</v>
       </c>
       <c r="H385" t="n">
-        <v>1.21</v>
+        <v>6.23</v>
       </c>
       <c r="I385" t="n">
-        <v>1.21</v>
+        <v>11.1</v>
       </c>
       <c r="J385" t="n">
         <v>7.91</v>
@@ -13534,29 +13534,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D386" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E386" t="n">
-        <v>10.88</v>
+        <v>38.585</v>
       </c>
       <c r="F386" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G386" t="n">
-        <v>32.64</v>
+        <v>154.34</v>
       </c>
       <c r="H386" t="n">
-        <v>1.48</v>
+        <v>15.32</v>
       </c>
       <c r="I386" t="n">
-        <v>4.75</v>
+        <v>11.02</v>
       </c>
       <c r="J386" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D397" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E397" t="n">
-        <v>11.202</v>
+        <v>39.435</v>
       </c>
       <c r="F397" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G397" t="n">
-        <v>33.61</v>
+        <v>157.74</v>
       </c>
       <c r="H397" t="n">
-        <v>2.45</v>
+        <v>18.72</v>
       </c>
       <c r="I397" t="n">
-        <v>7.86</v>
+        <v>13.47</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E398" t="n">
-        <v>102.82</v>
+        <v>22.145</v>
       </c>
       <c r="F398" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G398" t="n">
-        <v>102.82</v>
+        <v>66.44</v>
       </c>
       <c r="H398" t="n">
-        <v>2.73</v>
+        <v>0.77</v>
       </c>
       <c r="I398" t="n">
-        <v>2.73</v>
+        <v>1.17</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D399" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E399" t="n">
-        <v>6.982</v>
+        <v>11.202</v>
       </c>
       <c r="F399" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G399" t="n">
-        <v>62.84</v>
+        <v>33.61</v>
       </c>
       <c r="H399" t="n">
-        <v>6.69</v>
+        <v>2.45</v>
       </c>
       <c r="I399" t="n">
-        <v>11.91</v>
+        <v>7.86</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D400" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E400" t="n">
-        <v>22.145</v>
+        <v>102.82</v>
       </c>
       <c r="F400" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G400" t="n">
-        <v>66.44</v>
+        <v>102.82</v>
       </c>
       <c r="H400" t="n">
-        <v>0.77</v>
+        <v>2.73</v>
       </c>
       <c r="I400" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D401" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E401" t="n">
-        <v>39.435</v>
+        <v>6.982</v>
       </c>
       <c r="F401" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G401" t="n">
-        <v>157.74</v>
+        <v>62.84</v>
       </c>
       <c r="H401" t="n">
-        <v>18.72</v>
+        <v>6.69</v>
       </c>
       <c r="I401" t="n">
-        <v>13.47</v>
+        <v>11.91</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14418,29 +14418,29 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D412" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E412" t="n">
-        <v>107.44</v>
+        <v>22.37</v>
       </c>
       <c r="F412" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G412" t="n">
-        <v>107.44</v>
+        <v>67.11</v>
       </c>
       <c r="H412" t="n">
-        <v>7.35</v>
+        <v>1.44</v>
       </c>
       <c r="I412" t="n">
-        <v>7.34</v>
+        <v>2.19</v>
       </c>
       <c r="J412" t="n">
         <v>7.91</v>
@@ -14452,29 +14452,29 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D413" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E413" t="n">
-        <v>11.154</v>
+        <v>7.093</v>
       </c>
       <c r="F413" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G413" t="n">
-        <v>33.46</v>
+        <v>63.84</v>
       </c>
       <c r="H413" t="n">
-        <v>2.3</v>
+        <v>7.69</v>
       </c>
       <c r="I413" t="n">
-        <v>7.38</v>
+        <v>13.7</v>
       </c>
       <c r="J413" t="n">
         <v>7.91</v>
@@ -14486,29 +14486,29 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D414" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E414" t="n">
-        <v>40.955</v>
+        <v>11.154</v>
       </c>
       <c r="F414" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G414" t="n">
-        <v>163.82</v>
+        <v>33.46</v>
       </c>
       <c r="H414" t="n">
-        <v>24.8</v>
+        <v>2.3</v>
       </c>
       <c r="I414" t="n">
-        <v>17.84</v>
+        <v>7.38</v>
       </c>
       <c r="J414" t="n">
         <v>7.91</v>
@@ -14520,29 +14520,29 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D415" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E415" t="n">
-        <v>22.37</v>
+        <v>107.44</v>
       </c>
       <c r="F415" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G415" t="n">
-        <v>67.11</v>
+        <v>107.44</v>
       </c>
       <c r="H415" t="n">
-        <v>1.44</v>
+        <v>7.35</v>
       </c>
       <c r="I415" t="n">
-        <v>2.19</v>
+        <v>7.34</v>
       </c>
       <c r="J415" t="n">
         <v>7.91</v>
@@ -14554,29 +14554,29 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D416" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E416" t="n">
-        <v>7.093</v>
+        <v>40.955</v>
       </c>
       <c r="F416" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G416" t="n">
-        <v>63.84</v>
+        <v>163.82</v>
       </c>
       <c r="H416" t="n">
-        <v>7.69</v>
+        <v>24.8</v>
       </c>
       <c r="I416" t="n">
-        <v>13.7</v>
+        <v>17.84</v>
       </c>
       <c r="J416" t="n">
         <v>7.91</v>
@@ -14928,29 +14928,29 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D427" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E427" t="n">
-        <v>7.068</v>
+        <v>107.54</v>
       </c>
       <c r="F427" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G427" t="n">
-        <v>63.61</v>
+        <v>107.54</v>
       </c>
       <c r="H427" t="n">
-        <v>7.46</v>
+        <v>7.45</v>
       </c>
       <c r="I427" t="n">
-        <v>13.29</v>
+        <v>7.44</v>
       </c>
       <c r="J427" t="n">
         <v>7.91</v>
@@ -14962,29 +14962,29 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C428" t="n">
         <v>3</v>
       </c>
       <c r="D428" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E428" t="n">
-        <v>11.132</v>
+        <v>22.4</v>
       </c>
       <c r="F428" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G428" t="n">
-        <v>33.4</v>
+        <v>67.2</v>
       </c>
       <c r="H428" t="n">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="I428" t="n">
-        <v>7.19</v>
+        <v>2.33</v>
       </c>
       <c r="J428" t="n">
         <v>7.91</v>
@@ -14996,29 +14996,29 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D429" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E429" t="n">
-        <v>40.57</v>
+        <v>11.132</v>
       </c>
       <c r="F429" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G429" t="n">
-        <v>162.28</v>
+        <v>33.4</v>
       </c>
       <c r="H429" t="n">
-        <v>23.26</v>
+        <v>2.24</v>
       </c>
       <c r="I429" t="n">
-        <v>16.73</v>
+        <v>7.19</v>
       </c>
       <c r="J429" t="n">
         <v>7.91</v>
@@ -15030,29 +15030,29 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D430" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E430" t="n">
-        <v>22.4</v>
+        <v>7.068</v>
       </c>
       <c r="F430" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G430" t="n">
-        <v>67.2</v>
+        <v>63.61</v>
       </c>
       <c r="H430" t="n">
-        <v>1.53</v>
+        <v>7.46</v>
       </c>
       <c r="I430" t="n">
-        <v>2.33</v>
+        <v>13.29</v>
       </c>
       <c r="J430" t="n">
         <v>7.91</v>
@@ -15064,29 +15064,29 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D431" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E431" t="n">
-        <v>107.54</v>
+        <v>40.57</v>
       </c>
       <c r="F431" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G431" t="n">
-        <v>107.54</v>
+        <v>162.28</v>
       </c>
       <c r="H431" t="n">
-        <v>7.45</v>
+        <v>23.26</v>
       </c>
       <c r="I431" t="n">
-        <v>7.44</v>
+        <v>16.73</v>
       </c>
       <c r="J431" t="n">
         <v>7.91</v>
@@ -15259,6 +15259,176 @@
         <v>12.97</v>
       </c>
       <c r="J436" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>3</v>
+      </c>
+      <c r="D437" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E437" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F437" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G437" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I437" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>4</v>
+      </c>
+      <c r="D438" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E438" t="n">
+        <v>40.495</v>
+      </c>
+      <c r="F438" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G438" t="n">
+        <v>161.98</v>
+      </c>
+      <c r="H438" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="I438" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="J438" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>3</v>
+      </c>
+      <c r="D439" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E439" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F439" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G439" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I439" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="J439" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+      <c r="D440" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E440" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="F440" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G440" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="H440" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="I440" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J440" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>9</v>
+      </c>
+      <c r="D441" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E441" t="n">
+        <v>7.055</v>
+      </c>
+      <c r="F441" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G441" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="H441" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I441" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="J441" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J441"/>
+  <dimension ref="A1:J446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E12" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F12" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G12" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H12" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I12" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E13" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F13" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G13" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H13" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I13" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E14" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F14" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G14" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E15" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F15" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G15" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H15" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E16" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F16" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G16" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H16" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I16" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E27" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F27" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G27" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H27" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I27" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E28" t="n">
-        <v>104.9</v>
+        <v>21.98</v>
       </c>
       <c r="F28" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G28" t="n">
-        <v>104.9</v>
+        <v>65.94</v>
       </c>
       <c r="H28" t="n">
-        <v>4.81</v>
+        <v>0.27</v>
       </c>
       <c r="I28" t="n">
-        <v>4.81</v>
+        <v>0.41</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E29" t="n">
-        <v>21.98</v>
+        <v>10.66</v>
       </c>
       <c r="F29" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G29" t="n">
-        <v>65.94</v>
+        <v>31.98</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>0.82</v>
       </c>
       <c r="I29" t="n">
-        <v>0.41</v>
+        <v>2.63</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E30" t="n">
-        <v>10.66</v>
+        <v>6.795</v>
       </c>
       <c r="F30" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G30" t="n">
-        <v>31.98</v>
+        <v>61.16</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>8.92</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E31" t="n">
-        <v>40.532</v>
+        <v>104.9</v>
       </c>
       <c r="F31" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G31" t="n">
-        <v>162.13</v>
+        <v>104.9</v>
       </c>
       <c r="H31" t="n">
-        <v>23.11</v>
+        <v>4.81</v>
       </c>
       <c r="I31" t="n">
-        <v>16.62</v>
+        <v>4.81</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E42" t="n">
-        <v>10.61</v>
+        <v>22</v>
       </c>
       <c r="F42" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G42" t="n">
-        <v>31.83</v>
+        <v>66</v>
       </c>
       <c r="H42" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I42" t="n">
-        <v>2.15</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E43" t="n">
-        <v>100.06</v>
+        <v>38.497</v>
       </c>
       <c r="F43" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G43" t="n">
-        <v>100.06</v>
+        <v>153.99</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.03</v>
+        <v>14.97</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.03</v>
+        <v>10.77</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E44" t="n">
-        <v>22</v>
+        <v>6.629</v>
       </c>
       <c r="F44" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G44" t="n">
-        <v>66</v>
+        <v>59.66</v>
       </c>
       <c r="H44" t="n">
-        <v>0.33</v>
+        <v>3.51</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E45" t="n">
-        <v>6.629</v>
+        <v>100.06</v>
       </c>
       <c r="F45" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G45" t="n">
-        <v>59.66</v>
+        <v>100.06</v>
       </c>
       <c r="H45" t="n">
-        <v>3.51</v>
+        <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>6.25</v>
+        <v>-0.03</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -1974,29 +1974,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E46" t="n">
-        <v>38.497</v>
+        <v>10.61</v>
       </c>
       <c r="F46" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G46" t="n">
-        <v>153.99</v>
+        <v>31.83</v>
       </c>
       <c r="H46" t="n">
-        <v>14.97</v>
+        <v>0.67</v>
       </c>
       <c r="I46" t="n">
-        <v>10.77</v>
+        <v>2.15</v>
       </c>
       <c r="J46" t="n">
         <v>7.91</v>
@@ -2348,29 +2348,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E57" t="n">
-        <v>10.75</v>
+        <v>22.289</v>
       </c>
       <c r="F57" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G57" t="n">
-        <v>32.25</v>
+        <v>66.87</v>
       </c>
       <c r="H57" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="J57" t="n">
         <v>7.91</v>
@@ -2382,29 +2382,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E58" t="n">
-        <v>6.736</v>
+        <v>102.86</v>
       </c>
       <c r="F58" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G58" t="n">
-        <v>60.62</v>
+        <v>102.86</v>
       </c>
       <c r="H58" t="n">
-        <v>4.47</v>
+        <v>2.77</v>
       </c>
       <c r="I58" t="n">
-        <v>7.96</v>
+        <v>2.77</v>
       </c>
       <c r="J58" t="n">
         <v>7.91</v>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E59" t="n">
-        <v>39.845</v>
+        <v>10.75</v>
       </c>
       <c r="F59" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G59" t="n">
-        <v>159.38</v>
+        <v>32.25</v>
       </c>
       <c r="H59" t="n">
-        <v>20.36</v>
+        <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>14.65</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>7.91</v>
@@ -2450,29 +2450,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E60" t="n">
-        <v>102.86</v>
+        <v>6.736</v>
       </c>
       <c r="F60" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G60" t="n">
-        <v>102.86</v>
+        <v>60.62</v>
       </c>
       <c r="H60" t="n">
-        <v>2.77</v>
+        <v>4.47</v>
       </c>
       <c r="I60" t="n">
-        <v>2.77</v>
+        <v>7.96</v>
       </c>
       <c r="J60" t="n">
         <v>7.91</v>
@@ -2484,29 +2484,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E61" t="n">
-        <v>22.289</v>
+        <v>39.845</v>
       </c>
       <c r="F61" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G61" t="n">
-        <v>66.87</v>
+        <v>159.38</v>
       </c>
       <c r="H61" t="n">
-        <v>1.2</v>
+        <v>20.36</v>
       </c>
       <c r="I61" t="n">
-        <v>1.83</v>
+        <v>14.65</v>
       </c>
       <c r="J61" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E67" t="n">
-        <v>6.807</v>
+        <v>40.567</v>
       </c>
       <c r="F67" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G67" t="n">
-        <v>61.26</v>
+        <v>162.27</v>
       </c>
       <c r="H67" t="n">
-        <v>5.11</v>
+        <v>23.25</v>
       </c>
       <c r="I67" t="n">
-        <v>9.1</v>
+        <v>16.72</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E68" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F68" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G68" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H68" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E69" t="n">
-        <v>10.796</v>
+        <v>104.58</v>
       </c>
       <c r="F69" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G69" t="n">
-        <v>32.39</v>
+        <v>104.58</v>
       </c>
       <c r="H69" t="n">
-        <v>1.23</v>
+        <v>4.49</v>
       </c>
       <c r="I69" t="n">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E70" t="n">
-        <v>40.567</v>
+        <v>6.807</v>
       </c>
       <c r="F70" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G70" t="n">
-        <v>162.27</v>
+        <v>61.26</v>
       </c>
       <c r="H70" t="n">
-        <v>23.25</v>
+        <v>5.11</v>
       </c>
       <c r="I70" t="n">
-        <v>16.72</v>
+        <v>9.1</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E71" t="n">
-        <v>104.58</v>
+        <v>22.797</v>
       </c>
       <c r="F71" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G71" t="n">
-        <v>104.58</v>
+        <v>68.39</v>
       </c>
       <c r="H71" t="n">
-        <v>4.49</v>
+        <v>2.72</v>
       </c>
       <c r="I71" t="n">
-        <v>4.49</v>
+        <v>4.14</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E82" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F82" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G82" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I82" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E83" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F83" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G83" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H83" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I83" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E84" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F84" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G84" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H84" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I84" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E85" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F85" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G85" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I85" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E86" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F86" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G86" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H86" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I86" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E97" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F97" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G97" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H97" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I97" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E98" t="n">
-        <v>40.65</v>
+        <v>10.642</v>
       </c>
       <c r="F98" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G98" t="n">
-        <v>162.6</v>
+        <v>31.93</v>
       </c>
       <c r="H98" t="n">
-        <v>23.58</v>
+        <v>0.77</v>
       </c>
       <c r="I98" t="n">
-        <v>16.96</v>
+        <v>2.47</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E100" t="n">
-        <v>10.642</v>
+        <v>6.839</v>
       </c>
       <c r="F100" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G100" t="n">
-        <v>31.93</v>
+        <v>61.55</v>
       </c>
       <c r="H100" t="n">
-        <v>0.77</v>
+        <v>5.4</v>
       </c>
       <c r="I100" t="n">
-        <v>2.47</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E101" t="n">
-        <v>104.22</v>
+        <v>40.65</v>
       </c>
       <c r="F101" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G101" t="n">
-        <v>104.22</v>
+        <v>162.6</v>
       </c>
       <c r="H101" t="n">
-        <v>4.13</v>
+        <v>23.58</v>
       </c>
       <c r="I101" t="n">
-        <v>4.13</v>
+        <v>16.96</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4218,29 +4218,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E112" t="n">
-        <v>40</v>
+        <v>10.568</v>
       </c>
       <c r="F112" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G112" t="n">
-        <v>160</v>
+        <v>31.7</v>
       </c>
       <c r="H112" t="n">
-        <v>20.98</v>
+        <v>0.54</v>
       </c>
       <c r="I112" t="n">
-        <v>15.09</v>
+        <v>1.73</v>
       </c>
       <c r="J112" t="n">
         <v>7.91</v>
@@ -4252,29 +4252,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E113" t="n">
-        <v>103.56</v>
+        <v>23.025</v>
       </c>
       <c r="F113" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G113" t="n">
-        <v>103.56</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="I113" t="n">
-        <v>3.47</v>
+        <v>5.18</v>
       </c>
       <c r="J113" t="n">
         <v>7.91</v>
@@ -4286,29 +4286,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E114" t="n">
-        <v>6.797</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G114" t="n">
-        <v>61.17</v>
+        <v>160</v>
       </c>
       <c r="H114" t="n">
-        <v>5.02</v>
+        <v>20.98</v>
       </c>
       <c r="I114" t="n">
-        <v>8.94</v>
+        <v>15.09</v>
       </c>
       <c r="J114" t="n">
         <v>7.91</v>
@@ -4320,29 +4320,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E115" t="n">
-        <v>23.025</v>
+        <v>103.56</v>
       </c>
       <c r="F115" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G115" t="n">
-        <v>69.06999999999999</v>
+        <v>103.56</v>
       </c>
       <c r="H115" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="I115" t="n">
-        <v>5.18</v>
+        <v>3.47</v>
       </c>
       <c r="J115" t="n">
         <v>7.91</v>
@@ -4354,29 +4354,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E116" t="n">
-        <v>10.568</v>
+        <v>6.797</v>
       </c>
       <c r="F116" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G116" t="n">
-        <v>31.7</v>
+        <v>61.17</v>
       </c>
       <c r="H116" t="n">
-        <v>0.54</v>
+        <v>5.02</v>
       </c>
       <c r="I116" t="n">
-        <v>1.73</v>
+        <v>8.94</v>
       </c>
       <c r="J116" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D127" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E127" t="n">
-        <v>11.458</v>
+        <v>6.868</v>
       </c>
       <c r="F127" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G127" t="n">
-        <v>34.37</v>
+        <v>61.81</v>
       </c>
       <c r="H127" t="n">
-        <v>3.21</v>
+        <v>5.66</v>
       </c>
       <c r="I127" t="n">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E128" t="n">
-        <v>39.36</v>
+        <v>23.17</v>
       </c>
       <c r="F128" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G128" t="n">
-        <v>157.44</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>18.42</v>
+        <v>3.84</v>
       </c>
       <c r="I128" t="n">
-        <v>13.25</v>
+        <v>5.85</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4796,29 +4796,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E129" t="n">
-        <v>103.46</v>
+        <v>11.458</v>
       </c>
       <c r="F129" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G129" t="n">
-        <v>103.46</v>
+        <v>34.37</v>
       </c>
       <c r="H129" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="I129" t="n">
-        <v>3.37</v>
+        <v>10.3</v>
       </c>
       <c r="J129" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E130" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F130" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G130" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H130" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I130" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E131" t="n">
-        <v>6.868</v>
+        <v>103.46</v>
       </c>
       <c r="F131" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G131" t="n">
-        <v>61.81</v>
+        <v>103.46</v>
       </c>
       <c r="H131" t="n">
-        <v>5.66</v>
+        <v>3.37</v>
       </c>
       <c r="I131" t="n">
-        <v>10.08</v>
+        <v>3.37</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E137" t="n">
-        <v>6.927</v>
+        <v>23.3</v>
       </c>
       <c r="F137" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G137" t="n">
-        <v>62.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>6.19</v>
+        <v>4.23</v>
       </c>
       <c r="I137" t="n">
-        <v>11.02</v>
+        <v>6.44</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E138" t="n">
-        <v>40.61</v>
+        <v>11.728</v>
       </c>
       <c r="F138" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G138" t="n">
-        <v>162.44</v>
+        <v>35.18</v>
       </c>
       <c r="H138" t="n">
-        <v>23.42</v>
+        <v>4.02</v>
       </c>
       <c r="I138" t="n">
-        <v>16.85</v>
+        <v>12.9</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E139" t="n">
-        <v>11.728</v>
+        <v>104.76</v>
       </c>
       <c r="F139" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G139" t="n">
-        <v>35.18</v>
+        <v>104.76</v>
       </c>
       <c r="H139" t="n">
-        <v>4.02</v>
+        <v>4.67</v>
       </c>
       <c r="I139" t="n">
-        <v>12.9</v>
+        <v>4.67</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>6.927</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>62.34</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>6.19</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>11.02</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E141" t="n">
-        <v>104.76</v>
+        <v>40.61</v>
       </c>
       <c r="F141" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G141" t="n">
-        <v>104.76</v>
+        <v>162.44</v>
       </c>
       <c r="H141" t="n">
-        <v>4.67</v>
+        <v>23.42</v>
       </c>
       <c r="I141" t="n">
-        <v>4.67</v>
+        <v>16.85</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E142" t="n">
-        <v>38.89</v>
+        <v>102.06</v>
       </c>
       <c r="F142" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G142" t="n">
-        <v>155.56</v>
+        <v>102.06</v>
       </c>
       <c r="H142" t="n">
-        <v>16.54</v>
+        <v>1.97</v>
       </c>
       <c r="I142" t="n">
-        <v>11.9</v>
+        <v>1.97</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E143" t="n">
-        <v>23.135</v>
+        <v>11.498</v>
       </c>
       <c r="F143" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G143" t="n">
-        <v>69.41</v>
+        <v>34.49</v>
       </c>
       <c r="H143" t="n">
-        <v>3.74</v>
+        <v>3.33</v>
       </c>
       <c r="I143" t="n">
-        <v>5.7</v>
+        <v>10.69</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E144" t="n">
-        <v>6.878</v>
+        <v>38.89</v>
       </c>
       <c r="F144" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G144" t="n">
-        <v>61.9</v>
+        <v>155.56</v>
       </c>
       <c r="H144" t="n">
-        <v>5.75</v>
+        <v>16.54</v>
       </c>
       <c r="I144" t="n">
-        <v>10.24</v>
+        <v>11.9</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E145" t="n">
-        <v>11.498</v>
+        <v>23.135</v>
       </c>
       <c r="F145" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G145" t="n">
-        <v>34.49</v>
+        <v>69.41</v>
       </c>
       <c r="H145" t="n">
-        <v>3.33</v>
+        <v>3.74</v>
       </c>
       <c r="I145" t="n">
-        <v>10.69</v>
+        <v>5.7</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D146" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E146" t="n">
-        <v>102.06</v>
+        <v>6.878</v>
       </c>
       <c r="F146" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G146" t="n">
-        <v>102.06</v>
+        <v>61.9</v>
       </c>
       <c r="H146" t="n">
-        <v>1.97</v>
+        <v>5.75</v>
       </c>
       <c r="I146" t="n">
-        <v>1.97</v>
+        <v>10.24</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E152" t="n">
-        <v>6.893</v>
+        <v>11.034</v>
       </c>
       <c r="F152" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G152" t="n">
-        <v>62.04</v>
+        <v>33.1</v>
       </c>
       <c r="H152" t="n">
-        <v>5.89</v>
+        <v>1.94</v>
       </c>
       <c r="I152" t="n">
-        <v>10.49</v>
+        <v>6.23</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E153" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F153" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G153" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H153" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I153" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E154" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F154" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G154" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H154" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I154" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E155" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F155" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G155" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H155" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I155" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E156" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F156" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G156" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H156" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I156" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E167" t="n">
-        <v>38.98</v>
+        <v>10.726</v>
       </c>
       <c r="F167" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G167" t="n">
-        <v>155.92</v>
+        <v>32.18</v>
       </c>
       <c r="H167" t="n">
-        <v>16.9</v>
+        <v>1.02</v>
       </c>
       <c r="I167" t="n">
-        <v>12.16</v>
+        <v>3.27</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E168" t="n">
-        <v>22.92</v>
+        <v>103.98</v>
       </c>
       <c r="F168" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G168" t="n">
-        <v>68.76000000000001</v>
+        <v>103.98</v>
       </c>
       <c r="H168" t="n">
-        <v>3.09</v>
+        <v>3.89</v>
       </c>
       <c r="I168" t="n">
-        <v>4.71</v>
+        <v>3.89</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E170" t="n">
-        <v>10.726</v>
+        <v>38.98</v>
       </c>
       <c r="F170" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G170" t="n">
-        <v>32.18</v>
+        <v>155.92</v>
       </c>
       <c r="H170" t="n">
-        <v>1.02</v>
+        <v>16.9</v>
       </c>
       <c r="I170" t="n">
-        <v>3.27</v>
+        <v>12.16</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E171" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F171" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G171" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H171" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I171" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E177" t="n">
-        <v>6.922</v>
+        <v>102.54</v>
       </c>
       <c r="F177" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G177" t="n">
-        <v>62.3</v>
+        <v>102.54</v>
       </c>
       <c r="H177" t="n">
-        <v>6.15</v>
+        <v>2.45</v>
       </c>
       <c r="I177" t="n">
-        <v>10.95</v>
+        <v>2.45</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E178" t="n">
-        <v>38.245</v>
+        <v>22.95</v>
       </c>
       <c r="F178" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G178" t="n">
-        <v>152.98</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>13.96</v>
+        <v>3.18</v>
       </c>
       <c r="I178" t="n">
-        <v>10.04</v>
+        <v>4.84</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E179" t="n">
-        <v>22.95</v>
+        <v>10.642</v>
       </c>
       <c r="F179" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G179" t="n">
-        <v>68.84999999999999</v>
+        <v>31.93</v>
       </c>
       <c r="H179" t="n">
-        <v>3.18</v>
+        <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>4.84</v>
+        <v>2.47</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E180" t="n">
-        <v>102.54</v>
+        <v>6.922</v>
       </c>
       <c r="F180" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G180" t="n">
-        <v>102.54</v>
+        <v>62.3</v>
       </c>
       <c r="H180" t="n">
-        <v>2.45</v>
+        <v>6.15</v>
       </c>
       <c r="I180" t="n">
-        <v>2.45</v>
+        <v>10.95</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E181" t="n">
-        <v>10.642</v>
+        <v>38.245</v>
       </c>
       <c r="F181" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G181" t="n">
-        <v>31.93</v>
+        <v>152.98</v>
       </c>
       <c r="H181" t="n">
-        <v>0.77</v>
+        <v>13.96</v>
       </c>
       <c r="I181" t="n">
-        <v>2.47</v>
+        <v>10.04</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C192" t="n">
         <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E192" t="n">
-        <v>22.82</v>
+        <v>10.792</v>
       </c>
       <c r="F192" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G192" t="n">
-        <v>68.45999999999999</v>
+        <v>32.38</v>
       </c>
       <c r="H192" t="n">
-        <v>2.79</v>
+        <v>1.22</v>
       </c>
       <c r="I192" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E193" t="n">
-        <v>38.755</v>
+        <v>102.46</v>
       </c>
       <c r="F193" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G193" t="n">
-        <v>155.02</v>
+        <v>102.46</v>
       </c>
       <c r="H193" t="n">
-        <v>16</v>
+        <v>2.37</v>
       </c>
       <c r="I193" t="n">
-        <v>11.51</v>
+        <v>2.37</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D194" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E194" t="n">
-        <v>102.46</v>
+        <v>6.894</v>
       </c>
       <c r="F194" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G194" t="n">
-        <v>102.46</v>
+        <v>62.05</v>
       </c>
       <c r="H194" t="n">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="I194" t="n">
-        <v>2.37</v>
+        <v>10.51</v>
       </c>
       <c r="J194" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E195" t="n">
-        <v>10.792</v>
+        <v>22.82</v>
       </c>
       <c r="F195" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G195" t="n">
-        <v>32.38</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>1.22</v>
+        <v>2.79</v>
       </c>
       <c r="I195" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7074,29 +7074,29 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E196" t="n">
-        <v>6.894</v>
+        <v>38.755</v>
       </c>
       <c r="F196" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G196" t="n">
-        <v>62.05</v>
+        <v>155.02</v>
       </c>
       <c r="H196" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="I196" t="n">
-        <v>10.51</v>
+        <v>11.51</v>
       </c>
       <c r="J196" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C207" t="n">
         <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E207" t="n">
-        <v>11.172</v>
+        <v>22.725</v>
       </c>
       <c r="F207" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G207" t="n">
-        <v>33.52</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H207" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="I207" t="n">
-        <v>7.57</v>
+        <v>3.82</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D208" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E208" t="n">
-        <v>99.90000000000001</v>
+        <v>37.82</v>
       </c>
       <c r="F208" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G208" t="n">
-        <v>99.90000000000001</v>
+        <v>151.28</v>
       </c>
       <c r="H208" t="n">
-        <v>-0.19</v>
+        <v>12.26</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.19</v>
+        <v>8.82</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E210" t="n">
-        <v>37.82</v>
+        <v>11.172</v>
       </c>
       <c r="F210" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G210" t="n">
-        <v>151.28</v>
+        <v>33.52</v>
       </c>
       <c r="H210" t="n">
-        <v>12.26</v>
+        <v>2.36</v>
       </c>
       <c r="I210" t="n">
-        <v>8.82</v>
+        <v>7.57</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E211" t="n">
-        <v>22.725</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F211" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G211" t="n">
-        <v>68.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H211" t="n">
-        <v>2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="I211" t="n">
-        <v>3.82</v>
+        <v>-0.19</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E222" t="n">
-        <v>6.818</v>
+        <v>11.5</v>
       </c>
       <c r="F222" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G222" t="n">
-        <v>61.36</v>
+        <v>34.5</v>
       </c>
       <c r="H222" t="n">
-        <v>5.21</v>
+        <v>3.34</v>
       </c>
       <c r="I222" t="n">
-        <v>9.279999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D223" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E223" t="n">
-        <v>96.67</v>
+        <v>35.89</v>
       </c>
       <c r="F223" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G223" t="n">
-        <v>96.67</v>
+        <v>143.56</v>
       </c>
       <c r="H223" t="n">
-        <v>-3.42</v>
+        <v>4.54</v>
       </c>
       <c r="I223" t="n">
-        <v>-3.42</v>
+        <v>3.27</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E225" t="n">
-        <v>35.89</v>
+        <v>96.67</v>
       </c>
       <c r="F225" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G225" t="n">
-        <v>143.56</v>
+        <v>96.67</v>
       </c>
       <c r="H225" t="n">
-        <v>4.54</v>
+        <v>-3.42</v>
       </c>
       <c r="I225" t="n">
-        <v>3.27</v>
+        <v>-3.42</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D226" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E226" t="n">
-        <v>11.5</v>
+        <v>6.818</v>
       </c>
       <c r="F226" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G226" t="n">
-        <v>34.5</v>
+        <v>61.36</v>
       </c>
       <c r="H226" t="n">
-        <v>3.34</v>
+        <v>5.21</v>
       </c>
       <c r="I226" t="n">
-        <v>10.72</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8298,29 +8298,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D232" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E232" t="n">
-        <v>6.812</v>
+        <v>23.17</v>
       </c>
       <c r="F232" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G232" t="n">
-        <v>61.31</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H232" t="n">
-        <v>5.16</v>
+        <v>3.84</v>
       </c>
       <c r="I232" t="n">
-        <v>9.19</v>
+        <v>5.85</v>
       </c>
       <c r="J232" t="n">
         <v>7.91</v>
@@ -8332,29 +8332,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D233" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E233" t="n">
-        <v>97.86</v>
+        <v>37.44</v>
       </c>
       <c r="F233" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G233" t="n">
-        <v>97.86</v>
+        <v>149.76</v>
       </c>
       <c r="H233" t="n">
-        <v>-2.23</v>
+        <v>10.74</v>
       </c>
       <c r="I233" t="n">
-        <v>-2.23</v>
+        <v>7.73</v>
       </c>
       <c r="J233" t="n">
         <v>7.91</v>
@@ -8366,29 +8366,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E234" t="n">
-        <v>37.44</v>
+        <v>11.544</v>
       </c>
       <c r="F234" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G234" t="n">
-        <v>149.76</v>
+        <v>34.63</v>
       </c>
       <c r="H234" t="n">
-        <v>10.74</v>
+        <v>3.47</v>
       </c>
       <c r="I234" t="n">
-        <v>7.73</v>
+        <v>11.14</v>
       </c>
       <c r="J234" t="n">
         <v>7.91</v>
@@ -8400,29 +8400,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D235" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E235" t="n">
-        <v>23.17</v>
+        <v>6.812</v>
       </c>
       <c r="F235" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G235" t="n">
-        <v>69.51000000000001</v>
+        <v>61.31</v>
       </c>
       <c r="H235" t="n">
-        <v>3.84</v>
+        <v>5.16</v>
       </c>
       <c r="I235" t="n">
-        <v>5.85</v>
+        <v>9.19</v>
       </c>
       <c r="J235" t="n">
         <v>7.91</v>
@@ -8434,29 +8434,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E236" t="n">
-        <v>11.544</v>
+        <v>97.86</v>
       </c>
       <c r="F236" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G236" t="n">
-        <v>34.63</v>
+        <v>97.86</v>
       </c>
       <c r="H236" t="n">
-        <v>3.47</v>
+        <v>-2.23</v>
       </c>
       <c r="I236" t="n">
-        <v>11.14</v>
+        <v>-2.23</v>
       </c>
       <c r="J236" t="n">
         <v>7.91</v>
@@ -8808,29 +8808,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E247" t="n">
-        <v>7.032</v>
+        <v>103.2</v>
       </c>
       <c r="F247" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G247" t="n">
-        <v>63.29</v>
+        <v>103.2</v>
       </c>
       <c r="H247" t="n">
-        <v>7.14</v>
+        <v>3.11</v>
       </c>
       <c r="I247" t="n">
-        <v>12.72</v>
+        <v>3.11</v>
       </c>
       <c r="J247" t="n">
         <v>7.91</v>
@@ -8842,29 +8842,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D248" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E248" t="n">
-        <v>12.18</v>
+        <v>38.435</v>
       </c>
       <c r="F248" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G248" t="n">
-        <v>36.54</v>
+        <v>153.74</v>
       </c>
       <c r="H248" t="n">
-        <v>5.38</v>
+        <v>14.72</v>
       </c>
       <c r="I248" t="n">
-        <v>17.27</v>
+        <v>10.59</v>
       </c>
       <c r="J248" t="n">
         <v>7.91</v>
@@ -8876,29 +8876,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D249" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E249" t="n">
-        <v>38.435</v>
+        <v>23.28</v>
       </c>
       <c r="F249" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G249" t="n">
-        <v>153.74</v>
+        <v>69.84</v>
       </c>
       <c r="H249" t="n">
-        <v>14.72</v>
+        <v>4.17</v>
       </c>
       <c r="I249" t="n">
-        <v>10.59</v>
+        <v>6.35</v>
       </c>
       <c r="J249" t="n">
         <v>7.91</v>
@@ -8910,29 +8910,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D250" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E250" t="n">
-        <v>103.2</v>
+        <v>7.032</v>
       </c>
       <c r="F250" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G250" t="n">
-        <v>103.2</v>
+        <v>63.29</v>
       </c>
       <c r="H250" t="n">
-        <v>3.11</v>
+        <v>7.14</v>
       </c>
       <c r="I250" t="n">
-        <v>3.11</v>
+        <v>12.72</v>
       </c>
       <c r="J250" t="n">
         <v>7.91</v>
@@ -8944,29 +8944,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C251" t="n">
         <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E251" t="n">
-        <v>23.28</v>
+        <v>12.18</v>
       </c>
       <c r="F251" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G251" t="n">
-        <v>69.84</v>
+        <v>36.54</v>
       </c>
       <c r="H251" t="n">
-        <v>4.17</v>
+        <v>5.38</v>
       </c>
       <c r="I251" t="n">
-        <v>6.35</v>
+        <v>17.27</v>
       </c>
       <c r="J251" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E262" t="n">
-        <v>38.23</v>
+        <v>7.055</v>
       </c>
       <c r="F262" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G262" t="n">
-        <v>152.92</v>
+        <v>63.49</v>
       </c>
       <c r="H262" t="n">
-        <v>13.9</v>
+        <v>7.34</v>
       </c>
       <c r="I262" t="n">
-        <v>10</v>
+        <v>13.07</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C263" t="n">
         <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E263" t="n">
-        <v>12.23</v>
+        <v>23.3</v>
       </c>
       <c r="F263" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G263" t="n">
-        <v>36.69</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H263" t="n">
-        <v>5.53</v>
+        <v>4.23</v>
       </c>
       <c r="I263" t="n">
-        <v>17.75</v>
+        <v>6.44</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D265" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E265" t="n">
-        <v>23.3</v>
+        <v>38.23</v>
       </c>
       <c r="F265" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G265" t="n">
-        <v>69.90000000000001</v>
+        <v>152.92</v>
       </c>
       <c r="H265" t="n">
-        <v>4.23</v>
+        <v>13.9</v>
       </c>
       <c r="I265" t="n">
-        <v>6.44</v>
+        <v>10</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D266" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E266" t="n">
-        <v>7.055</v>
+        <v>12.23</v>
       </c>
       <c r="F266" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G266" t="n">
-        <v>63.49</v>
+        <v>36.69</v>
       </c>
       <c r="H266" t="n">
-        <v>7.34</v>
+        <v>5.53</v>
       </c>
       <c r="I266" t="n">
-        <v>13.07</v>
+        <v>17.75</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D277" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E277" t="n">
-        <v>22.96</v>
+        <v>103.76</v>
       </c>
       <c r="F277" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G277" t="n">
-        <v>68.88</v>
+        <v>103.76</v>
       </c>
       <c r="H277" t="n">
-        <v>3.21</v>
+        <v>3.67</v>
       </c>
       <c r="I277" t="n">
-        <v>4.89</v>
+        <v>3.67</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D278" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E278" t="n">
-        <v>38.985</v>
+        <v>12.492</v>
       </c>
       <c r="F278" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G278" t="n">
-        <v>155.94</v>
+        <v>37.48</v>
       </c>
       <c r="H278" t="n">
-        <v>16.92</v>
+        <v>6.32</v>
       </c>
       <c r="I278" t="n">
-        <v>12.17</v>
+        <v>20.28</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D280" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E280" t="n">
-        <v>12.492</v>
+        <v>38.985</v>
       </c>
       <c r="F280" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G280" t="n">
-        <v>37.48</v>
+        <v>155.94</v>
       </c>
       <c r="H280" t="n">
-        <v>6.32</v>
+        <v>16.92</v>
       </c>
       <c r="I280" t="n">
-        <v>20.28</v>
+        <v>12.17</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E281" t="n">
-        <v>103.76</v>
+        <v>22.96</v>
       </c>
       <c r="F281" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G281" t="n">
-        <v>103.76</v>
+        <v>68.88</v>
       </c>
       <c r="H281" t="n">
-        <v>3.67</v>
+        <v>3.21</v>
       </c>
       <c r="I281" t="n">
-        <v>3.67</v>
+        <v>4.89</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -10168,29 +10168,29 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D287" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E287" t="n">
-        <v>6.983</v>
+        <v>38.18</v>
       </c>
       <c r="F287" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G287" t="n">
-        <v>62.85</v>
+        <v>152.72</v>
       </c>
       <c r="H287" t="n">
-        <v>6.7</v>
+        <v>13.7</v>
       </c>
       <c r="I287" t="n">
-        <v>11.93</v>
+        <v>9.85</v>
       </c>
       <c r="J287" t="n">
         <v>7.91</v>
@@ -10202,29 +10202,29 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C288" t="n">
         <v>3</v>
       </c>
       <c r="D288" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E288" t="n">
-        <v>12.292</v>
+        <v>22.83</v>
       </c>
       <c r="F288" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G288" t="n">
-        <v>36.88</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H288" t="n">
-        <v>5.72</v>
+        <v>2.82</v>
       </c>
       <c r="I288" t="n">
-        <v>18.36</v>
+        <v>4.29</v>
       </c>
       <c r="J288" t="n">
         <v>7.91</v>
@@ -10236,29 +10236,29 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E289" t="n">
-        <v>22.83</v>
+        <v>102.22</v>
       </c>
       <c r="F289" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G289" t="n">
-        <v>68.48999999999999</v>
+        <v>102.22</v>
       </c>
       <c r="H289" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="I289" t="n">
-        <v>4.29</v>
+        <v>2.13</v>
       </c>
       <c r="J289" t="n">
         <v>7.91</v>
@@ -10270,29 +10270,29 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E290" t="n">
-        <v>38.18</v>
+        <v>6.983</v>
       </c>
       <c r="F290" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G290" t="n">
-        <v>152.72</v>
+        <v>62.85</v>
       </c>
       <c r="H290" t="n">
-        <v>13.7</v>
+        <v>6.7</v>
       </c>
       <c r="I290" t="n">
-        <v>9.85</v>
+        <v>11.93</v>
       </c>
       <c r="J290" t="n">
         <v>7.91</v>
@@ -10304,29 +10304,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D291" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E291" t="n">
-        <v>102.22</v>
+        <v>12.292</v>
       </c>
       <c r="F291" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G291" t="n">
-        <v>102.22</v>
+        <v>36.88</v>
       </c>
       <c r="H291" t="n">
-        <v>2.13</v>
+        <v>5.72</v>
       </c>
       <c r="I291" t="n">
-        <v>2.13</v>
+        <v>18.36</v>
       </c>
       <c r="J291" t="n">
         <v>7.91</v>
@@ -10678,29 +10678,29 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D302" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E302" t="n">
-        <v>38.845</v>
+        <v>22.715</v>
       </c>
       <c r="F302" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G302" t="n">
-        <v>155.38</v>
+        <v>68.14</v>
       </c>
       <c r="H302" t="n">
-        <v>16.36</v>
+        <v>2.47</v>
       </c>
       <c r="I302" t="n">
-        <v>11.77</v>
+        <v>3.76</v>
       </c>
       <c r="J302" t="n">
         <v>7.91</v>
@@ -10712,29 +10712,29 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E303" t="n">
-        <v>6.93</v>
+        <v>11.828</v>
       </c>
       <c r="F303" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G303" t="n">
-        <v>62.37</v>
+        <v>35.48</v>
       </c>
       <c r="H303" t="n">
-        <v>6.22</v>
+        <v>4.32</v>
       </c>
       <c r="I303" t="n">
-        <v>11.08</v>
+        <v>13.86</v>
       </c>
       <c r="J303" t="n">
         <v>7.91</v>
@@ -10746,29 +10746,29 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D304" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E304" t="n">
-        <v>11.828</v>
+        <v>100.78</v>
       </c>
       <c r="F304" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G304" t="n">
-        <v>35.48</v>
+        <v>100.78</v>
       </c>
       <c r="H304" t="n">
-        <v>4.32</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>13.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J304" t="n">
         <v>7.91</v>
@@ -10780,29 +10780,29 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D305" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E305" t="n">
-        <v>22.715</v>
+        <v>38.845</v>
       </c>
       <c r="F305" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G305" t="n">
-        <v>68.14</v>
+        <v>155.38</v>
       </c>
       <c r="H305" t="n">
-        <v>2.47</v>
+        <v>16.36</v>
       </c>
       <c r="I305" t="n">
-        <v>3.76</v>
+        <v>11.77</v>
       </c>
       <c r="J305" t="n">
         <v>7.91</v>
@@ -10814,29 +10814,29 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D306" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E306" t="n">
-        <v>100.78</v>
+        <v>6.93</v>
       </c>
       <c r="F306" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G306" t="n">
-        <v>100.78</v>
+        <v>62.37</v>
       </c>
       <c r="H306" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I306" t="n">
-        <v>0.6899999999999999</v>
+        <v>11.08</v>
       </c>
       <c r="J306" t="n">
         <v>7.91</v>
@@ -11188,29 +11188,29 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D317" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E317" t="n">
-        <v>11.822</v>
+        <v>38.91</v>
       </c>
       <c r="F317" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G317" t="n">
-        <v>35.47</v>
+        <v>155.64</v>
       </c>
       <c r="H317" t="n">
-        <v>4.31</v>
+        <v>16.62</v>
       </c>
       <c r="I317" t="n">
-        <v>13.83</v>
+        <v>11.96</v>
       </c>
       <c r="J317" t="n">
         <v>7.91</v>
@@ -11222,29 +11222,29 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E318" t="n">
-        <v>6.943</v>
+        <v>100.48</v>
       </c>
       <c r="F318" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G318" t="n">
-        <v>62.49</v>
+        <v>100.48</v>
       </c>
       <c r="H318" t="n">
-        <v>6.34</v>
+        <v>0.39</v>
       </c>
       <c r="I318" t="n">
-        <v>11.29</v>
+        <v>0.39</v>
       </c>
       <c r="J318" t="n">
         <v>7.91</v>
@@ -11290,29 +11290,29 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D320" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E320" t="n">
-        <v>100.48</v>
+        <v>11.822</v>
       </c>
       <c r="F320" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G320" t="n">
-        <v>100.48</v>
+        <v>35.47</v>
       </c>
       <c r="H320" t="n">
-        <v>0.39</v>
+        <v>4.31</v>
       </c>
       <c r="I320" t="n">
-        <v>0.39</v>
+        <v>13.83</v>
       </c>
       <c r="J320" t="n">
         <v>7.91</v>
@@ -11324,29 +11324,29 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D321" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E321" t="n">
-        <v>38.91</v>
+        <v>6.943</v>
       </c>
       <c r="F321" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G321" t="n">
-        <v>155.64</v>
+        <v>62.49</v>
       </c>
       <c r="H321" t="n">
-        <v>16.62</v>
+        <v>6.34</v>
       </c>
       <c r="I321" t="n">
-        <v>11.96</v>
+        <v>11.29</v>
       </c>
       <c r="J321" t="n">
         <v>7.91</v>
@@ -11698,29 +11698,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D332" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E332" t="n">
-        <v>6.948</v>
+        <v>11.5</v>
       </c>
       <c r="F332" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G332" t="n">
-        <v>62.53</v>
+        <v>34.5</v>
       </c>
       <c r="H332" t="n">
-        <v>6.38</v>
+        <v>3.34</v>
       </c>
       <c r="I332" t="n">
-        <v>11.36</v>
+        <v>10.72</v>
       </c>
       <c r="J332" t="n">
         <v>7.91</v>
@@ -11732,29 +11732,29 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D333" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E333" t="n">
-        <v>22.745</v>
+        <v>101.38</v>
       </c>
       <c r="F333" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G333" t="n">
-        <v>68.23</v>
+        <v>101.38</v>
       </c>
       <c r="H333" t="n">
-        <v>2.56</v>
+        <v>1.29</v>
       </c>
       <c r="I333" t="n">
-        <v>3.9</v>
+        <v>1.29</v>
       </c>
       <c r="J333" t="n">
         <v>7.91</v>
@@ -11766,29 +11766,29 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D334" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E334" t="n">
-        <v>101.38</v>
+        <v>38.98</v>
       </c>
       <c r="F334" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G334" t="n">
-        <v>101.38</v>
+        <v>155.92</v>
       </c>
       <c r="H334" t="n">
-        <v>1.29</v>
+        <v>16.9</v>
       </c>
       <c r="I334" t="n">
-        <v>1.29</v>
+        <v>12.16</v>
       </c>
       <c r="J334" t="n">
         <v>7.91</v>
@@ -11800,29 +11800,29 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D335" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E335" t="n">
-        <v>38.98</v>
+        <v>22.745</v>
       </c>
       <c r="F335" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G335" t="n">
-        <v>155.92</v>
+        <v>68.23</v>
       </c>
       <c r="H335" t="n">
-        <v>16.9</v>
+        <v>2.56</v>
       </c>
       <c r="I335" t="n">
-        <v>12.16</v>
+        <v>3.9</v>
       </c>
       <c r="J335" t="n">
         <v>7.91</v>
@@ -11834,29 +11834,29 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D336" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E336" t="n">
-        <v>11.5</v>
+        <v>6.948</v>
       </c>
       <c r="F336" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G336" t="n">
-        <v>34.5</v>
+        <v>62.53</v>
       </c>
       <c r="H336" t="n">
-        <v>3.34</v>
+        <v>6.38</v>
       </c>
       <c r="I336" t="n">
-        <v>10.72</v>
+        <v>11.36</v>
       </c>
       <c r="J336" t="n">
         <v>7.91</v>
@@ -12038,29 +12038,29 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D342" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E342" t="n">
-        <v>11.264</v>
+        <v>6.95</v>
       </c>
       <c r="F342" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G342" t="n">
-        <v>33.79</v>
+        <v>62.55</v>
       </c>
       <c r="H342" t="n">
-        <v>2.63</v>
+        <v>6.4</v>
       </c>
       <c r="I342" t="n">
-        <v>8.44</v>
+        <v>11.4</v>
       </c>
       <c r="J342" t="n">
         <v>7.91</v>
@@ -12072,29 +12072,29 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D343" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E343" t="n">
-        <v>100.84</v>
+        <v>38.99</v>
       </c>
       <c r="F343" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G343" t="n">
-        <v>100.84</v>
+        <v>155.96</v>
       </c>
       <c r="H343" t="n">
-        <v>0.75</v>
+        <v>16.94</v>
       </c>
       <c r="I343" t="n">
-        <v>0.75</v>
+        <v>12.19</v>
       </c>
       <c r="J343" t="n">
         <v>7.91</v>
@@ -12106,29 +12106,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D344" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E344" t="n">
-        <v>38.99</v>
+        <v>22.89</v>
       </c>
       <c r="F344" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G344" t="n">
-        <v>155.96</v>
+        <v>68.67</v>
       </c>
       <c r="H344" t="n">
-        <v>16.94</v>
+        <v>3</v>
       </c>
       <c r="I344" t="n">
-        <v>12.19</v>
+        <v>4.57</v>
       </c>
       <c r="J344" t="n">
         <v>7.91</v>
@@ -12140,29 +12140,29 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D345" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E345" t="n">
-        <v>6.95</v>
+        <v>11.264</v>
       </c>
       <c r="F345" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G345" t="n">
-        <v>62.55</v>
+        <v>33.79</v>
       </c>
       <c r="H345" t="n">
-        <v>6.4</v>
+        <v>2.63</v>
       </c>
       <c r="I345" t="n">
-        <v>11.4</v>
+        <v>8.44</v>
       </c>
       <c r="J345" t="n">
         <v>7.91</v>
@@ -12174,29 +12174,29 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E346" t="n">
-        <v>22.89</v>
+        <v>100.84</v>
       </c>
       <c r="F346" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G346" t="n">
-        <v>68.67</v>
+        <v>100.84</v>
       </c>
       <c r="H346" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="I346" t="n">
-        <v>4.57</v>
+        <v>0.75</v>
       </c>
       <c r="J346" t="n">
         <v>7.91</v>
@@ -12548,29 +12548,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D357" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E357" t="n">
-        <v>6.978</v>
+        <v>40.07</v>
       </c>
       <c r="F357" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G357" t="n">
-        <v>62.8</v>
+        <v>160.28</v>
       </c>
       <c r="H357" t="n">
-        <v>6.65</v>
+        <v>21.26</v>
       </c>
       <c r="I357" t="n">
-        <v>11.84</v>
+        <v>15.29</v>
       </c>
       <c r="J357" t="n">
         <v>7.91</v>
@@ -12582,29 +12582,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C358" t="n">
         <v>3</v>
       </c>
       <c r="D358" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E358" t="n">
-        <v>11.13</v>
+        <v>22.5</v>
       </c>
       <c r="F358" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G358" t="n">
-        <v>33.39</v>
+        <v>67.5</v>
       </c>
       <c r="H358" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="I358" t="n">
-        <v>7.16</v>
+        <v>2.79</v>
       </c>
       <c r="J358" t="n">
         <v>7.91</v>
@@ -12616,29 +12616,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E359" t="n">
-        <v>22.5</v>
+        <v>101.98</v>
       </c>
       <c r="F359" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G359" t="n">
-        <v>67.5</v>
+        <v>101.98</v>
       </c>
       <c r="H359" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="I359" t="n">
-        <v>2.79</v>
+        <v>1.89</v>
       </c>
       <c r="J359" t="n">
         <v>7.91</v>
@@ -12650,29 +12650,29 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D360" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E360" t="n">
-        <v>40.07</v>
+        <v>6.978</v>
       </c>
       <c r="F360" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G360" t="n">
-        <v>160.28</v>
+        <v>62.8</v>
       </c>
       <c r="H360" t="n">
-        <v>21.26</v>
+        <v>6.65</v>
       </c>
       <c r="I360" t="n">
-        <v>15.29</v>
+        <v>11.84</v>
       </c>
       <c r="J360" t="n">
         <v>7.91</v>
@@ -12684,29 +12684,29 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D361" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E361" t="n">
-        <v>101.98</v>
+        <v>11.13</v>
       </c>
       <c r="F361" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G361" t="n">
-        <v>101.98</v>
+        <v>33.39</v>
       </c>
       <c r="H361" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="I361" t="n">
-        <v>1.89</v>
+        <v>7.16</v>
       </c>
       <c r="J361" t="n">
         <v>7.91</v>
@@ -13058,29 +13058,29 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D372" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E372" t="n">
-        <v>6.878</v>
+        <v>10.912</v>
       </c>
       <c r="F372" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G372" t="n">
-        <v>61.9</v>
+        <v>32.74</v>
       </c>
       <c r="H372" t="n">
-        <v>5.75</v>
+        <v>1.58</v>
       </c>
       <c r="I372" t="n">
-        <v>10.24</v>
+        <v>5.07</v>
       </c>
       <c r="J372" t="n">
         <v>7.91</v>
@@ -13092,29 +13092,29 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D373" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E373" t="n">
-        <v>39.05</v>
+        <v>100.88</v>
       </c>
       <c r="F373" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G373" t="n">
-        <v>156.2</v>
+        <v>100.88</v>
       </c>
       <c r="H373" t="n">
-        <v>17.18</v>
+        <v>0.79</v>
       </c>
       <c r="I373" t="n">
-        <v>12.36</v>
+        <v>0.79</v>
       </c>
       <c r="J373" t="n">
         <v>7.91</v>
@@ -13160,29 +13160,29 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D375" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E375" t="n">
-        <v>100.88</v>
+        <v>6.878</v>
       </c>
       <c r="F375" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G375" t="n">
-        <v>100.88</v>
+        <v>61.9</v>
       </c>
       <c r="H375" t="n">
-        <v>0.79</v>
+        <v>5.75</v>
       </c>
       <c r="I375" t="n">
-        <v>0.79</v>
+        <v>10.24</v>
       </c>
       <c r="J375" t="n">
         <v>7.91</v>
@@ -13194,29 +13194,29 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D376" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E376" t="n">
-        <v>10.912</v>
+        <v>39.05</v>
       </c>
       <c r="F376" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G376" t="n">
-        <v>32.74</v>
+        <v>156.2</v>
       </c>
       <c r="H376" t="n">
-        <v>1.58</v>
+        <v>17.18</v>
       </c>
       <c r="I376" t="n">
-        <v>5.07</v>
+        <v>12.36</v>
       </c>
       <c r="J376" t="n">
         <v>7.91</v>
@@ -13568,29 +13568,29 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D387" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E387" t="n">
-        <v>11.006</v>
+        <v>6.893</v>
       </c>
       <c r="F387" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G387" t="n">
-        <v>33.02</v>
+        <v>62.04</v>
       </c>
       <c r="H387" t="n">
-        <v>1.86</v>
+        <v>5.89</v>
       </c>
       <c r="I387" t="n">
-        <v>5.97</v>
+        <v>10.49</v>
       </c>
       <c r="J387" t="n">
         <v>7.91</v>
@@ -13602,29 +13602,29 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D388" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E388" t="n">
-        <v>38.375</v>
+        <v>21.83</v>
       </c>
       <c r="F388" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G388" t="n">
-        <v>153.5</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H388" t="n">
-        <v>14.48</v>
+        <v>-0.18</v>
       </c>
       <c r="I388" t="n">
-        <v>10.42</v>
+        <v>-0.27</v>
       </c>
       <c r="J388" t="n">
         <v>7.91</v>
@@ -13636,29 +13636,29 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D389" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E389" t="n">
-        <v>100.76</v>
+        <v>38.375</v>
       </c>
       <c r="F389" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G389" t="n">
-        <v>100.76</v>
+        <v>153.5</v>
       </c>
       <c r="H389" t="n">
-        <v>0.67</v>
+        <v>14.48</v>
       </c>
       <c r="I389" t="n">
-        <v>0.67</v>
+        <v>10.42</v>
       </c>
       <c r="J389" t="n">
         <v>7.91</v>
@@ -13670,29 +13670,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C390" t="n">
         <v>3</v>
       </c>
       <c r="D390" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E390" t="n">
-        <v>21.83</v>
+        <v>11.006</v>
       </c>
       <c r="F390" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G390" t="n">
-        <v>65.48999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="H390" t="n">
-        <v>-0.18</v>
+        <v>1.86</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.27</v>
+        <v>5.97</v>
       </c>
       <c r="J390" t="n">
         <v>7.91</v>
@@ -13704,29 +13704,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D391" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E391" t="n">
-        <v>6.893</v>
+        <v>100.76</v>
       </c>
       <c r="F391" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G391" t="n">
-        <v>62.04</v>
+        <v>100.76</v>
       </c>
       <c r="H391" t="n">
-        <v>5.89</v>
+        <v>0.67</v>
       </c>
       <c r="I391" t="n">
-        <v>10.49</v>
+        <v>0.67</v>
       </c>
       <c r="J391" t="n">
         <v>7.91</v>
@@ -13908,29 +13908,29 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D397" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E397" t="n">
-        <v>39.435</v>
+        <v>6.982</v>
       </c>
       <c r="F397" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G397" t="n">
-        <v>157.74</v>
+        <v>62.84</v>
       </c>
       <c r="H397" t="n">
-        <v>18.72</v>
+        <v>6.69</v>
       </c>
       <c r="I397" t="n">
-        <v>13.47</v>
+        <v>11.91</v>
       </c>
       <c r="J397" t="n">
         <v>7.91</v>
@@ -13942,29 +13942,29 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C398" t="n">
         <v>3</v>
       </c>
       <c r="D398" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E398" t="n">
-        <v>22.145</v>
+        <v>11.202</v>
       </c>
       <c r="F398" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G398" t="n">
-        <v>66.44</v>
+        <v>33.61</v>
       </c>
       <c r="H398" t="n">
-        <v>0.77</v>
+        <v>2.45</v>
       </c>
       <c r="I398" t="n">
-        <v>1.17</v>
+        <v>7.86</v>
       </c>
       <c r="J398" t="n">
         <v>7.91</v>
@@ -13976,29 +13976,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E399" t="n">
-        <v>11.202</v>
+        <v>102.82</v>
       </c>
       <c r="F399" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G399" t="n">
-        <v>33.61</v>
+        <v>102.82</v>
       </c>
       <c r="H399" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="I399" t="n">
-        <v>7.86</v>
+        <v>2.73</v>
       </c>
       <c r="J399" t="n">
         <v>7.91</v>
@@ -14010,29 +14010,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D400" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E400" t="n">
-        <v>102.82</v>
+        <v>39.435</v>
       </c>
       <c r="F400" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G400" t="n">
-        <v>102.82</v>
+        <v>157.74</v>
       </c>
       <c r="H400" t="n">
-        <v>2.73</v>
+        <v>18.72</v>
       </c>
       <c r="I400" t="n">
-        <v>2.73</v>
+        <v>13.47</v>
       </c>
       <c r="J400" t="n">
         <v>7.91</v>
@@ -14044,29 +14044,29 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D401" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E401" t="n">
-        <v>6.982</v>
+        <v>22.145</v>
       </c>
       <c r="F401" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G401" t="n">
-        <v>62.84</v>
+        <v>66.44</v>
       </c>
       <c r="H401" t="n">
-        <v>6.69</v>
+        <v>0.77</v>
       </c>
       <c r="I401" t="n">
-        <v>11.91</v>
+        <v>1.17</v>
       </c>
       <c r="J401" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D407" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E407" t="n">
-        <v>40.695</v>
+        <v>105.98</v>
       </c>
       <c r="F407" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G407" t="n">
-        <v>162.78</v>
+        <v>105.98</v>
       </c>
       <c r="H407" t="n">
-        <v>23.76</v>
+        <v>5.89</v>
       </c>
       <c r="I407" t="n">
-        <v>17.09</v>
+        <v>5.88</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D408" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E408" t="n">
-        <v>11.232</v>
+        <v>40.695</v>
       </c>
       <c r="F408" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G408" t="n">
-        <v>33.7</v>
+        <v>162.78</v>
       </c>
       <c r="H408" t="n">
-        <v>2.54</v>
+        <v>23.76</v>
       </c>
       <c r="I408" t="n">
-        <v>8.15</v>
+        <v>17.09</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C409" t="n">
         <v>3</v>
       </c>
       <c r="D409" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E409" t="n">
-        <v>22.35</v>
+        <v>11.232</v>
       </c>
       <c r="F409" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G409" t="n">
-        <v>67.05</v>
+        <v>33.7</v>
       </c>
       <c r="H409" t="n">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="I409" t="n">
-        <v>2.1</v>
+        <v>8.15</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D410" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E410" t="n">
-        <v>105.98</v>
+        <v>22.35</v>
       </c>
       <c r="F410" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G410" t="n">
-        <v>105.98</v>
+        <v>67.05</v>
       </c>
       <c r="H410" t="n">
-        <v>5.89</v>
+        <v>1.38</v>
       </c>
       <c r="I410" t="n">
-        <v>5.88</v>
+        <v>2.1</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14418,29 +14418,29 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D412" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E412" t="n">
-        <v>22.37</v>
+        <v>40.955</v>
       </c>
       <c r="F412" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G412" t="n">
-        <v>67.11</v>
+        <v>163.82</v>
       </c>
       <c r="H412" t="n">
-        <v>1.44</v>
+        <v>24.8</v>
       </c>
       <c r="I412" t="n">
-        <v>2.19</v>
+        <v>17.84</v>
       </c>
       <c r="J412" t="n">
         <v>7.91</v>
@@ -14452,29 +14452,29 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D413" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E413" t="n">
-        <v>7.093</v>
+        <v>107.44</v>
       </c>
       <c r="F413" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G413" t="n">
-        <v>63.84</v>
+        <v>107.44</v>
       </c>
       <c r="H413" t="n">
-        <v>7.69</v>
+        <v>7.35</v>
       </c>
       <c r="I413" t="n">
-        <v>13.7</v>
+        <v>7.34</v>
       </c>
       <c r="J413" t="n">
         <v>7.91</v>
@@ -14520,29 +14520,29 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D415" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E415" t="n">
-        <v>107.44</v>
+        <v>7.093</v>
       </c>
       <c r="F415" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G415" t="n">
-        <v>107.44</v>
+        <v>63.84</v>
       </c>
       <c r="H415" t="n">
-        <v>7.35</v>
+        <v>7.69</v>
       </c>
       <c r="I415" t="n">
-        <v>7.34</v>
+        <v>13.7</v>
       </c>
       <c r="J415" t="n">
         <v>7.91</v>
@@ -14554,29 +14554,29 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D416" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E416" t="n">
-        <v>40.955</v>
+        <v>22.37</v>
       </c>
       <c r="F416" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G416" t="n">
-        <v>163.82</v>
+        <v>67.11</v>
       </c>
       <c r="H416" t="n">
-        <v>24.8</v>
+        <v>1.44</v>
       </c>
       <c r="I416" t="n">
-        <v>17.84</v>
+        <v>2.19</v>
       </c>
       <c r="J416" t="n">
         <v>7.91</v>
@@ -14758,29 +14758,29 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D422" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E422" t="n">
-        <v>106.78</v>
+        <v>22.11</v>
       </c>
       <c r="F422" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G422" t="n">
-        <v>106.78</v>
+        <v>66.33</v>
       </c>
       <c r="H422" t="n">
-        <v>6.69</v>
+        <v>0.66</v>
       </c>
       <c r="I422" t="n">
-        <v>6.68</v>
+        <v>1.01</v>
       </c>
       <c r="J422" t="n">
         <v>7.91</v>
@@ -14792,29 +14792,29 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D423" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E423" t="n">
-        <v>11.144</v>
+        <v>40.225</v>
       </c>
       <c r="F423" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G423" t="n">
-        <v>33.43</v>
+        <v>160.9</v>
       </c>
       <c r="H423" t="n">
-        <v>2.27</v>
+        <v>21.88</v>
       </c>
       <c r="I423" t="n">
-        <v>7.28</v>
+        <v>15.74</v>
       </c>
       <c r="J423" t="n">
         <v>7.91</v>
@@ -14826,29 +14826,29 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D424" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E424" t="n">
-        <v>40.225</v>
+        <v>7.037</v>
       </c>
       <c r="F424" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G424" t="n">
-        <v>160.9</v>
+        <v>63.33</v>
       </c>
       <c r="H424" t="n">
-        <v>21.88</v>
+        <v>7.18</v>
       </c>
       <c r="I424" t="n">
-        <v>15.74</v>
+        <v>12.79</v>
       </c>
       <c r="J424" t="n">
         <v>7.91</v>
@@ -14860,29 +14860,29 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D425" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E425" t="n">
-        <v>22.11</v>
+        <v>106.78</v>
       </c>
       <c r="F425" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G425" t="n">
-        <v>66.33</v>
+        <v>106.78</v>
       </c>
       <c r="H425" t="n">
-        <v>0.66</v>
+        <v>6.69</v>
       </c>
       <c r="I425" t="n">
-        <v>1.01</v>
+        <v>6.68</v>
       </c>
       <c r="J425" t="n">
         <v>7.91</v>
@@ -14894,29 +14894,29 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D426" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E426" t="n">
-        <v>7.037</v>
+        <v>11.144</v>
       </c>
       <c r="F426" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G426" t="n">
-        <v>63.33</v>
+        <v>33.43</v>
       </c>
       <c r="H426" t="n">
-        <v>7.18</v>
+        <v>2.27</v>
       </c>
       <c r="I426" t="n">
-        <v>12.79</v>
+        <v>7.28</v>
       </c>
       <c r="J426" t="n">
         <v>7.91</v>
@@ -15268,29 +15268,29 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D437" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E437" t="n">
-        <v>11.02</v>
+        <v>107.38</v>
       </c>
       <c r="F437" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G437" t="n">
-        <v>33.06</v>
+        <v>107.38</v>
       </c>
       <c r="H437" t="n">
-        <v>1.9</v>
+        <v>7.29</v>
       </c>
       <c r="I437" t="n">
-        <v>6.1</v>
+        <v>7.28</v>
       </c>
       <c r="J437" t="n">
         <v>7.91</v>
@@ -15302,29 +15302,29 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D438" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E438" t="n">
-        <v>40.495</v>
+        <v>21.7</v>
       </c>
       <c r="F438" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G438" t="n">
-        <v>161.98</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H438" t="n">
-        <v>22.96</v>
+        <v>-0.57</v>
       </c>
       <c r="I438" t="n">
-        <v>16.52</v>
+        <v>-0.87</v>
       </c>
       <c r="J438" t="n">
         <v>7.91</v>
@@ -15336,29 +15336,29 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D439" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E439" t="n">
-        <v>21.7</v>
+        <v>7.055</v>
       </c>
       <c r="F439" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G439" t="n">
-        <v>65.09999999999999</v>
+        <v>63.49</v>
       </c>
       <c r="H439" t="n">
-        <v>-0.57</v>
+        <v>7.34</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.87</v>
+        <v>13.07</v>
       </c>
       <c r="J439" t="n">
         <v>7.91</v>
@@ -15370,29 +15370,29 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D440" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E440" t="n">
-        <v>107.38</v>
+        <v>11.02</v>
       </c>
       <c r="F440" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G440" t="n">
-        <v>107.38</v>
+        <v>33.06</v>
       </c>
       <c r="H440" t="n">
-        <v>7.29</v>
+        <v>1.9</v>
       </c>
       <c r="I440" t="n">
-        <v>7.28</v>
+        <v>6.1</v>
       </c>
       <c r="J440" t="n">
         <v>7.91</v>
@@ -15404,31 +15404,201 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>4</v>
+      </c>
+      <c r="D441" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E441" t="n">
+        <v>40.495</v>
+      </c>
+      <c r="F441" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G441" t="n">
+        <v>161.98</v>
+      </c>
+      <c r="H441" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="I441" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="J441" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E442" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="F442" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G442" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="H442" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I442" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="J442" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>3</v>
+      </c>
+      <c r="D443" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E443" t="n">
+        <v>11.026</v>
+      </c>
+      <c r="F443" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G443" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="H443" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I443" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J443" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>4</v>
+      </c>
+      <c r="D444" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E444" t="n">
+        <v>40.195</v>
+      </c>
+      <c r="F444" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G444" t="n">
+        <v>160.78</v>
+      </c>
+      <c r="H444" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="I444" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="J444" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>3</v>
+      </c>
+      <c r="D445" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E445" t="n">
+        <v>21.635</v>
+      </c>
+      <c r="F445" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G445" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I445" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="J445" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
           <t>IWSC</t>
         </is>
       </c>
-      <c r="C441" t="n">
+      <c r="C446" t="n">
         <v>9</v>
       </c>
-      <c r="D441" t="n">
+      <c r="D446" t="n">
         <v>6.239</v>
       </c>
-      <c r="E441" t="n">
-        <v>7.055</v>
-      </c>
-      <c r="F441" t="n">
+      <c r="E446" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="F446" t="n">
         <v>56.15</v>
       </c>
-      <c r="G441" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="H441" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="I441" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="J441" t="n">
+      <c r="G446" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="H446" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="I446" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="J446" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J446"/>
+  <dimension ref="A1:J451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E12" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F12" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G12" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H12" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I12" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E13" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F13" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G13" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E14" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F14" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G14" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H14" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E15" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F15" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G15" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I15" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E16" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F16" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G16" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H16" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E27" t="n">
-        <v>40.532</v>
+        <v>104.9</v>
       </c>
       <c r="F27" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G27" t="n">
-        <v>162.13</v>
+        <v>104.9</v>
       </c>
       <c r="H27" t="n">
-        <v>23.11</v>
+        <v>4.81</v>
       </c>
       <c r="I27" t="n">
-        <v>16.62</v>
+        <v>4.81</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E28" t="n">
-        <v>21.98</v>
+        <v>10.66</v>
       </c>
       <c r="F28" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G28" t="n">
-        <v>65.94</v>
+        <v>31.98</v>
       </c>
       <c r="H28" t="n">
-        <v>0.27</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>0.41</v>
+        <v>2.63</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E29" t="n">
-        <v>10.66</v>
+        <v>6.795</v>
       </c>
       <c r="F29" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G29" t="n">
-        <v>31.98</v>
+        <v>61.16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I29" t="n">
-        <v>2.63</v>
+        <v>8.92</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E30" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F30" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G30" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H30" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I30" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E31" t="n">
-        <v>104.9</v>
+        <v>21.98</v>
       </c>
       <c r="F31" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G31" t="n">
-        <v>104.9</v>
+        <v>65.94</v>
       </c>
       <c r="H31" t="n">
-        <v>4.81</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>4.81</v>
+        <v>0.41</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E42" t="n">
-        <v>22</v>
+        <v>6.629</v>
       </c>
       <c r="F42" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G42" t="n">
-        <v>66</v>
+        <v>59.66</v>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>3.51</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E43" t="n">
-        <v>38.497</v>
+        <v>10.61</v>
       </c>
       <c r="F43" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G43" t="n">
-        <v>153.99</v>
+        <v>31.83</v>
       </c>
       <c r="H43" t="n">
-        <v>14.97</v>
+        <v>0.67</v>
       </c>
       <c r="I43" t="n">
-        <v>10.77</v>
+        <v>2.15</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E44" t="n">
-        <v>6.629</v>
+        <v>100.06</v>
       </c>
       <c r="F44" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G44" t="n">
-        <v>59.66</v>
+        <v>100.06</v>
       </c>
       <c r="H44" t="n">
-        <v>3.51</v>
+        <v>-0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>6.25</v>
+        <v>-0.03</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E45" t="n">
-        <v>100.06</v>
+        <v>38.497</v>
       </c>
       <c r="F45" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G45" t="n">
-        <v>100.06</v>
+        <v>153.99</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03</v>
+        <v>14.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.03</v>
+        <v>10.77</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -1974,29 +1974,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E46" t="n">
-        <v>10.61</v>
+        <v>22</v>
       </c>
       <c r="F46" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G46" t="n">
-        <v>31.83</v>
+        <v>66</v>
       </c>
       <c r="H46" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I46" t="n">
-        <v>2.15</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>7.91</v>
@@ -2348,29 +2348,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E57" t="n">
-        <v>22.289</v>
+        <v>39.845</v>
       </c>
       <c r="F57" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G57" t="n">
-        <v>66.87</v>
+        <v>159.38</v>
       </c>
       <c r="H57" t="n">
-        <v>1.2</v>
+        <v>20.36</v>
       </c>
       <c r="I57" t="n">
-        <v>1.83</v>
+        <v>14.65</v>
       </c>
       <c r="J57" t="n">
         <v>7.91</v>
@@ -2382,29 +2382,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E58" t="n">
-        <v>102.86</v>
+        <v>6.736</v>
       </c>
       <c r="F58" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G58" t="n">
-        <v>102.86</v>
+        <v>60.62</v>
       </c>
       <c r="H58" t="n">
-        <v>2.77</v>
+        <v>4.47</v>
       </c>
       <c r="I58" t="n">
-        <v>2.77</v>
+        <v>7.96</v>
       </c>
       <c r="J58" t="n">
         <v>7.91</v>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E59" t="n">
-        <v>10.75</v>
+        <v>22.289</v>
       </c>
       <c r="F59" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G59" t="n">
-        <v>32.25</v>
+        <v>66.87</v>
       </c>
       <c r="H59" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="J59" t="n">
         <v>7.91</v>
@@ -2450,29 +2450,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E60" t="n">
-        <v>6.736</v>
+        <v>102.86</v>
       </c>
       <c r="F60" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G60" t="n">
-        <v>60.62</v>
+        <v>102.86</v>
       </c>
       <c r="H60" t="n">
-        <v>4.47</v>
+        <v>2.77</v>
       </c>
       <c r="I60" t="n">
-        <v>7.96</v>
+        <v>2.77</v>
       </c>
       <c r="J60" t="n">
         <v>7.91</v>
@@ -2484,29 +2484,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E61" t="n">
-        <v>39.845</v>
+        <v>10.75</v>
       </c>
       <c r="F61" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G61" t="n">
-        <v>159.38</v>
+        <v>32.25</v>
       </c>
       <c r="H61" t="n">
-        <v>20.36</v>
+        <v>1.09</v>
       </c>
       <c r="I61" t="n">
-        <v>14.65</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E67" t="n">
-        <v>40.567</v>
+        <v>6.807</v>
       </c>
       <c r="F67" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G67" t="n">
-        <v>162.27</v>
+        <v>61.26</v>
       </c>
       <c r="H67" t="n">
-        <v>23.25</v>
+        <v>5.11</v>
       </c>
       <c r="I67" t="n">
-        <v>16.72</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E68" t="n">
-        <v>10.796</v>
+        <v>104.58</v>
       </c>
       <c r="F68" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G68" t="n">
-        <v>32.39</v>
+        <v>104.58</v>
       </c>
       <c r="H68" t="n">
-        <v>1.23</v>
+        <v>4.49</v>
       </c>
       <c r="I68" t="n">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E69" t="n">
-        <v>104.58</v>
+        <v>22.797</v>
       </c>
       <c r="F69" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G69" t="n">
-        <v>104.58</v>
+        <v>68.39</v>
       </c>
       <c r="H69" t="n">
-        <v>4.49</v>
+        <v>2.72</v>
       </c>
       <c r="I69" t="n">
-        <v>4.49</v>
+        <v>4.14</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E70" t="n">
-        <v>6.807</v>
+        <v>40.567</v>
       </c>
       <c r="F70" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G70" t="n">
-        <v>61.26</v>
+        <v>162.27</v>
       </c>
       <c r="H70" t="n">
-        <v>5.11</v>
+        <v>23.25</v>
       </c>
       <c r="I70" t="n">
-        <v>9.1</v>
+        <v>16.72</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E71" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F71" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G71" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H71" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I71" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E82" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F82" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G82" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H82" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I82" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E83" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F83" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G83" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H83" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I83" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E84" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F84" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G84" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H84" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I84" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E85" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F85" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G85" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I85" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E86" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F86" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G86" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H86" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I86" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E97" t="n">
-        <v>104.22</v>
+        <v>40.65</v>
       </c>
       <c r="F97" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G97" t="n">
-        <v>104.22</v>
+        <v>162.6</v>
       </c>
       <c r="H97" t="n">
-        <v>4.13</v>
+        <v>23.58</v>
       </c>
       <c r="I97" t="n">
-        <v>4.13</v>
+        <v>16.96</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E98" t="n">
-        <v>10.642</v>
+        <v>6.839</v>
       </c>
       <c r="F98" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G98" t="n">
-        <v>31.93</v>
+        <v>61.55</v>
       </c>
       <c r="H98" t="n">
-        <v>0.77</v>
+        <v>5.4</v>
       </c>
       <c r="I98" t="n">
-        <v>2.47</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E100" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F100" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G100" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H100" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I100" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E101" t="n">
-        <v>40.65</v>
+        <v>10.642</v>
       </c>
       <c r="F101" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G101" t="n">
-        <v>162.6</v>
+        <v>31.93</v>
       </c>
       <c r="H101" t="n">
-        <v>23.58</v>
+        <v>0.77</v>
       </c>
       <c r="I101" t="n">
-        <v>16.96</v>
+        <v>2.47</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4218,29 +4218,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E112" t="n">
-        <v>10.568</v>
+        <v>6.797</v>
       </c>
       <c r="F112" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G112" t="n">
-        <v>31.7</v>
+        <v>61.17</v>
       </c>
       <c r="H112" t="n">
-        <v>0.54</v>
+        <v>5.02</v>
       </c>
       <c r="I112" t="n">
-        <v>1.73</v>
+        <v>8.94</v>
       </c>
       <c r="J112" t="n">
         <v>7.91</v>
@@ -4252,29 +4252,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E113" t="n">
-        <v>23.025</v>
+        <v>103.56</v>
       </c>
       <c r="F113" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G113" t="n">
-        <v>69.06999999999999</v>
+        <v>103.56</v>
       </c>
       <c r="H113" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="I113" t="n">
-        <v>5.18</v>
+        <v>3.47</v>
       </c>
       <c r="J113" t="n">
         <v>7.91</v>
@@ -4286,29 +4286,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E114" t="n">
-        <v>40</v>
+        <v>10.568</v>
       </c>
       <c r="F114" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G114" t="n">
-        <v>160</v>
+        <v>31.7</v>
       </c>
       <c r="H114" t="n">
-        <v>20.98</v>
+        <v>0.54</v>
       </c>
       <c r="I114" t="n">
-        <v>15.09</v>
+        <v>1.73</v>
       </c>
       <c r="J114" t="n">
         <v>7.91</v>
@@ -4320,29 +4320,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E115" t="n">
-        <v>103.56</v>
+        <v>23.025</v>
       </c>
       <c r="F115" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G115" t="n">
-        <v>103.56</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="I115" t="n">
-        <v>3.47</v>
+        <v>5.18</v>
       </c>
       <c r="J115" t="n">
         <v>7.91</v>
@@ -4354,29 +4354,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E116" t="n">
-        <v>6.797</v>
+        <v>40</v>
       </c>
       <c r="F116" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G116" t="n">
-        <v>61.17</v>
+        <v>160</v>
       </c>
       <c r="H116" t="n">
-        <v>5.02</v>
+        <v>20.98</v>
       </c>
       <c r="I116" t="n">
-        <v>8.94</v>
+        <v>15.09</v>
       </c>
       <c r="J116" t="n">
         <v>7.91</v>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E127" t="n">
-        <v>6.868</v>
+        <v>103.46</v>
       </c>
       <c r="F127" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G127" t="n">
-        <v>61.81</v>
+        <v>103.46</v>
       </c>
       <c r="H127" t="n">
-        <v>5.66</v>
+        <v>3.37</v>
       </c>
       <c r="I127" t="n">
-        <v>10.08</v>
+        <v>3.37</v>
       </c>
       <c r="J127" t="n">
         <v>7.91</v>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E128" t="n">
-        <v>23.17</v>
+        <v>39.36</v>
       </c>
       <c r="F128" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G128" t="n">
-        <v>69.51000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="H128" t="n">
-        <v>3.84</v>
+        <v>18.42</v>
       </c>
       <c r="I128" t="n">
-        <v>5.85</v>
+        <v>13.25</v>
       </c>
       <c r="J128" t="n">
         <v>7.91</v>
@@ -4796,29 +4796,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D129" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E129" t="n">
-        <v>11.458</v>
+        <v>6.868</v>
       </c>
       <c r="F129" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G129" t="n">
-        <v>34.37</v>
+        <v>61.81</v>
       </c>
       <c r="H129" t="n">
-        <v>3.21</v>
+        <v>5.66</v>
       </c>
       <c r="I129" t="n">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="J129" t="n">
         <v>7.91</v>
@@ -4830,29 +4830,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E130" t="n">
-        <v>39.36</v>
+        <v>23.17</v>
       </c>
       <c r="F130" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G130" t="n">
-        <v>157.44</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>18.42</v>
+        <v>3.84</v>
       </c>
       <c r="I130" t="n">
-        <v>13.25</v>
+        <v>5.85</v>
       </c>
       <c r="J130" t="n">
         <v>7.91</v>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E131" t="n">
-        <v>103.46</v>
+        <v>11.458</v>
       </c>
       <c r="F131" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G131" t="n">
-        <v>103.46</v>
+        <v>34.37</v>
       </c>
       <c r="H131" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="I131" t="n">
-        <v>3.37</v>
+        <v>10.3</v>
       </c>
       <c r="J131" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D137" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E137" t="n">
-        <v>23.3</v>
+        <v>6.927</v>
       </c>
       <c r="F137" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G137" t="n">
-        <v>69.90000000000001</v>
+        <v>62.34</v>
       </c>
       <c r="H137" t="n">
-        <v>4.23</v>
+        <v>6.19</v>
       </c>
       <c r="I137" t="n">
-        <v>6.44</v>
+        <v>11.02</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E138" t="n">
-        <v>11.728</v>
+        <v>104.76</v>
       </c>
       <c r="F138" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G138" t="n">
-        <v>35.18</v>
+        <v>104.76</v>
       </c>
       <c r="H138" t="n">
-        <v>4.02</v>
+        <v>4.67</v>
       </c>
       <c r="I138" t="n">
-        <v>12.9</v>
+        <v>4.67</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E139" t="n">
-        <v>104.76</v>
+        <v>40.61</v>
       </c>
       <c r="F139" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G139" t="n">
-        <v>104.76</v>
+        <v>162.44</v>
       </c>
       <c r="H139" t="n">
-        <v>4.67</v>
+        <v>23.42</v>
       </c>
       <c r="I139" t="n">
-        <v>4.67</v>
+        <v>16.85</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E140" t="n">
-        <v>6.927</v>
+        <v>23.3</v>
       </c>
       <c r="F140" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G140" t="n">
-        <v>62.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>6.19</v>
+        <v>4.23</v>
       </c>
       <c r="I140" t="n">
-        <v>11.02</v>
+        <v>6.44</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E141" t="n">
-        <v>40.61</v>
+        <v>11.728</v>
       </c>
       <c r="F141" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G141" t="n">
-        <v>162.44</v>
+        <v>35.18</v>
       </c>
       <c r="H141" t="n">
-        <v>23.42</v>
+        <v>4.02</v>
       </c>
       <c r="I141" t="n">
-        <v>16.85</v>
+        <v>12.9</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5238,29 +5238,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D142" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E142" t="n">
-        <v>102.06</v>
+        <v>6.878</v>
       </c>
       <c r="F142" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G142" t="n">
-        <v>102.06</v>
+        <v>61.9</v>
       </c>
       <c r="H142" t="n">
-        <v>1.97</v>
+        <v>5.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.97</v>
+        <v>10.24</v>
       </c>
       <c r="J142" t="n">
         <v>7.91</v>
@@ -5272,29 +5272,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E143" t="n">
-        <v>11.498</v>
+        <v>23.135</v>
       </c>
       <c r="F143" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G143" t="n">
-        <v>34.49</v>
+        <v>69.41</v>
       </c>
       <c r="H143" t="n">
-        <v>3.33</v>
+        <v>3.74</v>
       </c>
       <c r="I143" t="n">
-        <v>10.69</v>
+        <v>5.7</v>
       </c>
       <c r="J143" t="n">
         <v>7.91</v>
@@ -5306,29 +5306,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E144" t="n">
-        <v>38.89</v>
+        <v>102.06</v>
       </c>
       <c r="F144" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G144" t="n">
-        <v>155.56</v>
+        <v>102.06</v>
       </c>
       <c r="H144" t="n">
-        <v>16.54</v>
+        <v>1.97</v>
       </c>
       <c r="I144" t="n">
-        <v>11.9</v>
+        <v>1.97</v>
       </c>
       <c r="J144" t="n">
         <v>7.91</v>
@@ -5340,29 +5340,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E145" t="n">
-        <v>23.135</v>
+        <v>11.498</v>
       </c>
       <c r="F145" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G145" t="n">
-        <v>69.41</v>
+        <v>34.49</v>
       </c>
       <c r="H145" t="n">
-        <v>3.74</v>
+        <v>3.33</v>
       </c>
       <c r="I145" t="n">
-        <v>5.7</v>
+        <v>10.69</v>
       </c>
       <c r="J145" t="n">
         <v>7.91</v>
@@ -5374,29 +5374,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D146" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E146" t="n">
-        <v>6.878</v>
+        <v>38.89</v>
       </c>
       <c r="F146" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G146" t="n">
-        <v>61.9</v>
+        <v>155.56</v>
       </c>
       <c r="H146" t="n">
-        <v>5.75</v>
+        <v>16.54</v>
       </c>
       <c r="I146" t="n">
-        <v>10.24</v>
+        <v>11.9</v>
       </c>
       <c r="J146" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E152" t="n">
-        <v>11.034</v>
+        <v>39.915</v>
       </c>
       <c r="F152" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G152" t="n">
-        <v>33.1</v>
+        <v>159.66</v>
       </c>
       <c r="H152" t="n">
-        <v>1.94</v>
+        <v>20.64</v>
       </c>
       <c r="I152" t="n">
-        <v>6.23</v>
+        <v>14.85</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E153" t="n">
-        <v>104.12</v>
+        <v>23.045</v>
       </c>
       <c r="F153" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G153" t="n">
-        <v>104.12</v>
+        <v>69.14</v>
       </c>
       <c r="H153" t="n">
-        <v>4.03</v>
+        <v>3.47</v>
       </c>
       <c r="I153" t="n">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E154" t="n">
-        <v>6.893</v>
+        <v>11.034</v>
       </c>
       <c r="F154" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G154" t="n">
-        <v>62.04</v>
+        <v>33.1</v>
       </c>
       <c r="H154" t="n">
-        <v>5.89</v>
+        <v>1.94</v>
       </c>
       <c r="I154" t="n">
-        <v>10.49</v>
+        <v>6.23</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E155" t="n">
-        <v>39.915</v>
+        <v>104.12</v>
       </c>
       <c r="F155" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G155" t="n">
-        <v>159.66</v>
+        <v>104.12</v>
       </c>
       <c r="H155" t="n">
-        <v>20.64</v>
+        <v>4.03</v>
       </c>
       <c r="I155" t="n">
-        <v>14.85</v>
+        <v>4.03</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D156" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E156" t="n">
-        <v>23.045</v>
+        <v>6.893</v>
       </c>
       <c r="F156" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G156" t="n">
-        <v>69.14</v>
+        <v>62.04</v>
       </c>
       <c r="H156" t="n">
-        <v>3.47</v>
+        <v>5.89</v>
       </c>
       <c r="I156" t="n">
-        <v>5.28</v>
+        <v>10.49</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E167" t="n">
-        <v>10.726</v>
+        <v>38.98</v>
       </c>
       <c r="F167" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G167" t="n">
-        <v>32.18</v>
+        <v>155.92</v>
       </c>
       <c r="H167" t="n">
-        <v>1.02</v>
+        <v>16.9</v>
       </c>
       <c r="I167" t="n">
-        <v>3.27</v>
+        <v>12.16</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E168" t="n">
-        <v>103.98</v>
+        <v>22.92</v>
       </c>
       <c r="F168" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G168" t="n">
-        <v>103.98</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="I168" t="n">
-        <v>3.89</v>
+        <v>4.71</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E170" t="n">
-        <v>38.98</v>
+        <v>10.726</v>
       </c>
       <c r="F170" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G170" t="n">
-        <v>155.92</v>
+        <v>32.18</v>
       </c>
       <c r="H170" t="n">
-        <v>16.9</v>
+        <v>1.02</v>
       </c>
       <c r="I170" t="n">
-        <v>12.16</v>
+        <v>3.27</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E171" t="n">
-        <v>22.92</v>
+        <v>103.98</v>
       </c>
       <c r="F171" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G171" t="n">
-        <v>68.76000000000001</v>
+        <v>103.98</v>
       </c>
       <c r="H171" t="n">
-        <v>3.09</v>
+        <v>3.89</v>
       </c>
       <c r="I171" t="n">
-        <v>4.71</v>
+        <v>3.89</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6428,29 +6428,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E177" t="n">
-        <v>102.54</v>
+        <v>6.922</v>
       </c>
       <c r="F177" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G177" t="n">
-        <v>102.54</v>
+        <v>62.3</v>
       </c>
       <c r="H177" t="n">
-        <v>2.45</v>
+        <v>6.15</v>
       </c>
       <c r="I177" t="n">
-        <v>2.45</v>
+        <v>10.95</v>
       </c>
       <c r="J177" t="n">
         <v>7.91</v>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E178" t="n">
-        <v>22.95</v>
+        <v>10.642</v>
       </c>
       <c r="F178" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G178" t="n">
-        <v>68.84999999999999</v>
+        <v>31.93</v>
       </c>
       <c r="H178" t="n">
-        <v>3.18</v>
+        <v>0.77</v>
       </c>
       <c r="I178" t="n">
-        <v>4.84</v>
+        <v>2.47</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -6496,29 +6496,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E179" t="n">
-        <v>10.642</v>
+        <v>38.245</v>
       </c>
       <c r="F179" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G179" t="n">
-        <v>31.93</v>
+        <v>152.98</v>
       </c>
       <c r="H179" t="n">
-        <v>0.77</v>
+        <v>13.96</v>
       </c>
       <c r="I179" t="n">
-        <v>2.47</v>
+        <v>10.04</v>
       </c>
       <c r="J179" t="n">
         <v>7.91</v>
@@ -6530,29 +6530,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E180" t="n">
-        <v>6.922</v>
+        <v>102.54</v>
       </c>
       <c r="F180" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G180" t="n">
-        <v>62.3</v>
+        <v>102.54</v>
       </c>
       <c r="H180" t="n">
-        <v>6.15</v>
+        <v>2.45</v>
       </c>
       <c r="I180" t="n">
-        <v>10.95</v>
+        <v>2.45</v>
       </c>
       <c r="J180" t="n">
         <v>7.91</v>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E181" t="n">
-        <v>38.245</v>
+        <v>22.95</v>
       </c>
       <c r="F181" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G181" t="n">
-        <v>152.98</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>13.96</v>
+        <v>3.18</v>
       </c>
       <c r="I181" t="n">
-        <v>10.04</v>
+        <v>4.84</v>
       </c>
       <c r="J181" t="n">
         <v>7.91</v>
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C192" t="n">
         <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E192" t="n">
-        <v>10.792</v>
+        <v>22.82</v>
       </c>
       <c r="F192" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G192" t="n">
-        <v>32.38</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H192" t="n">
-        <v>1.22</v>
+        <v>2.79</v>
       </c>
       <c r="I192" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="J192" t="n">
         <v>7.91</v>
@@ -6972,29 +6972,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D193" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E193" t="n">
-        <v>102.46</v>
+        <v>6.894</v>
       </c>
       <c r="F193" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G193" t="n">
-        <v>102.46</v>
+        <v>62.05</v>
       </c>
       <c r="H193" t="n">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="I193" t="n">
-        <v>2.37</v>
+        <v>10.51</v>
       </c>
       <c r="J193" t="n">
         <v>7.91</v>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D194" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E194" t="n">
-        <v>6.894</v>
+        <v>38.755</v>
       </c>
       <c r="F194" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G194" t="n">
-        <v>62.05</v>
+        <v>155.02</v>
       </c>
       <c r="H194" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="I194" t="n">
-        <v>10.51</v>
+        <v>11.51</v>
       </c>
       <c r="J194" t="n">
         <v>7.91</v>
@@ -7040,29 +7040,29 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E195" t="n">
-        <v>22.82</v>
+        <v>10.792</v>
       </c>
       <c r="F195" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G195" t="n">
-        <v>68.45999999999999</v>
+        <v>32.38</v>
       </c>
       <c r="H195" t="n">
-        <v>2.79</v>
+        <v>1.22</v>
       </c>
       <c r="I195" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="J195" t="n">
         <v>7.91</v>
@@ -7074,29 +7074,29 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E196" t="n">
-        <v>38.755</v>
+        <v>102.46</v>
       </c>
       <c r="F196" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G196" t="n">
-        <v>155.02</v>
+        <v>102.46</v>
       </c>
       <c r="H196" t="n">
-        <v>16</v>
+        <v>2.37</v>
       </c>
       <c r="I196" t="n">
-        <v>11.51</v>
+        <v>2.37</v>
       </c>
       <c r="J196" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E207" t="n">
-        <v>22.725</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F207" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G207" t="n">
-        <v>68.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H207" t="n">
-        <v>2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="I207" t="n">
-        <v>3.82</v>
+        <v>-0.19</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E208" t="n">
-        <v>37.82</v>
+        <v>11.172</v>
       </c>
       <c r="F208" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G208" t="n">
-        <v>151.28</v>
+        <v>33.52</v>
       </c>
       <c r="H208" t="n">
-        <v>12.26</v>
+        <v>2.36</v>
       </c>
       <c r="I208" t="n">
-        <v>8.82</v>
+        <v>7.57</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E210" t="n">
-        <v>11.172</v>
+        <v>22.725</v>
       </c>
       <c r="F210" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G210" t="n">
-        <v>33.52</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H210" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="I210" t="n">
-        <v>7.57</v>
+        <v>3.82</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D211" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E211" t="n">
-        <v>99.90000000000001</v>
+        <v>37.82</v>
       </c>
       <c r="F211" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G211" t="n">
-        <v>99.90000000000001</v>
+        <v>151.28</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.19</v>
+        <v>12.26</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.19</v>
+        <v>8.82</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E222" t="n">
-        <v>11.5</v>
+        <v>96.67</v>
       </c>
       <c r="F222" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G222" t="n">
-        <v>34.5</v>
+        <v>96.67</v>
       </c>
       <c r="H222" t="n">
-        <v>3.34</v>
+        <v>-3.42</v>
       </c>
       <c r="I222" t="n">
-        <v>10.72</v>
+        <v>-3.42</v>
       </c>
       <c r="J222" t="n">
         <v>7.91</v>
@@ -7992,29 +7992,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E223" t="n">
-        <v>35.89</v>
+        <v>23.12</v>
       </c>
       <c r="F223" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G223" t="n">
-        <v>143.56</v>
+        <v>69.36</v>
       </c>
       <c r="H223" t="n">
-        <v>4.54</v>
+        <v>3.69</v>
       </c>
       <c r="I223" t="n">
-        <v>3.27</v>
+        <v>5.62</v>
       </c>
       <c r="J223" t="n">
         <v>7.91</v>
@@ -8026,29 +8026,29 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D224" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E224" t="n">
-        <v>23.12</v>
+        <v>6.818</v>
       </c>
       <c r="F224" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G224" t="n">
-        <v>69.36</v>
+        <v>61.36</v>
       </c>
       <c r="H224" t="n">
-        <v>3.69</v>
+        <v>5.21</v>
       </c>
       <c r="I224" t="n">
-        <v>5.62</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J224" t="n">
         <v>7.91</v>
@@ -8060,29 +8060,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E225" t="n">
-        <v>96.67</v>
+        <v>11.5</v>
       </c>
       <c r="F225" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G225" t="n">
-        <v>96.67</v>
+        <v>34.5</v>
       </c>
       <c r="H225" t="n">
-        <v>-3.42</v>
+        <v>3.34</v>
       </c>
       <c r="I225" t="n">
-        <v>-3.42</v>
+        <v>10.72</v>
       </c>
       <c r="J225" t="n">
         <v>7.91</v>
@@ -8094,29 +8094,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D226" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E226" t="n">
-        <v>6.818</v>
+        <v>35.89</v>
       </c>
       <c r="F226" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G226" t="n">
-        <v>61.36</v>
+        <v>143.56</v>
       </c>
       <c r="H226" t="n">
-        <v>5.21</v>
+        <v>4.54</v>
       </c>
       <c r="I226" t="n">
-        <v>9.279999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="J226" t="n">
         <v>7.91</v>
@@ -8468,29 +8468,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E237" t="n">
-        <v>6.914</v>
+        <v>23.245</v>
       </c>
       <c r="F237" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G237" t="n">
-        <v>62.23</v>
+        <v>69.73</v>
       </c>
       <c r="H237" t="n">
-        <v>6.08</v>
+        <v>4.06</v>
       </c>
       <c r="I237" t="n">
-        <v>10.83</v>
+        <v>6.18</v>
       </c>
       <c r="J237" t="n">
         <v>7.91</v>
@@ -8502,29 +8502,29 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D238" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E238" t="n">
-        <v>11.842</v>
+        <v>37.315</v>
       </c>
       <c r="F238" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G238" t="n">
-        <v>35.53</v>
+        <v>149.26</v>
       </c>
       <c r="H238" t="n">
-        <v>4.37</v>
+        <v>10.24</v>
       </c>
       <c r="I238" t="n">
-        <v>14.02</v>
+        <v>7.37</v>
       </c>
       <c r="J238" t="n">
         <v>7.91</v>
@@ -8536,29 +8536,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E239" t="n">
-        <v>37.315</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F239" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G239" t="n">
-        <v>149.26</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H239" t="n">
-        <v>10.24</v>
+        <v>-0.24</v>
       </c>
       <c r="I239" t="n">
-        <v>7.37</v>
+        <v>-0.24</v>
       </c>
       <c r="J239" t="n">
         <v>7.91</v>
@@ -8570,29 +8570,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D240" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E240" t="n">
-        <v>99.84999999999999</v>
+        <v>6.914</v>
       </c>
       <c r="F240" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G240" t="n">
-        <v>99.84999999999999</v>
+        <v>62.23</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.24</v>
+        <v>6.08</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.24</v>
+        <v>10.83</v>
       </c>
       <c r="J240" t="n">
         <v>7.91</v>
@@ -8604,29 +8604,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C241" t="n">
         <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E241" t="n">
-        <v>23.245</v>
+        <v>11.842</v>
       </c>
       <c r="F241" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G241" t="n">
-        <v>69.73</v>
+        <v>35.53</v>
       </c>
       <c r="H241" t="n">
-        <v>4.06</v>
+        <v>4.37</v>
       </c>
       <c r="I241" t="n">
-        <v>6.18</v>
+        <v>14.02</v>
       </c>
       <c r="J241" t="n">
         <v>7.91</v>
@@ -8978,29 +8978,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D252" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E252" t="n">
-        <v>7.05</v>
+        <v>12.128</v>
       </c>
       <c r="F252" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G252" t="n">
-        <v>63.45</v>
+        <v>36.38</v>
       </c>
       <c r="H252" t="n">
-        <v>7.3</v>
+        <v>5.22</v>
       </c>
       <c r="I252" t="n">
-        <v>13</v>
+        <v>16.75</v>
       </c>
       <c r="J252" t="n">
         <v>7.91</v>
@@ -9012,29 +9012,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D253" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E253" t="n">
-        <v>103.18</v>
+        <v>23.315</v>
       </c>
       <c r="F253" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G253" t="n">
-        <v>103.18</v>
+        <v>69.95</v>
       </c>
       <c r="H253" t="n">
-        <v>3.09</v>
+        <v>4.28</v>
       </c>
       <c r="I253" t="n">
-        <v>3.09</v>
+        <v>6.52</v>
       </c>
       <c r="J253" t="n">
         <v>7.91</v>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D254" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E254" t="n">
-        <v>38.095</v>
+        <v>7.05</v>
       </c>
       <c r="F254" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G254" t="n">
-        <v>152.38</v>
+        <v>63.45</v>
       </c>
       <c r="H254" t="n">
-        <v>13.36</v>
+        <v>7.3</v>
       </c>
       <c r="I254" t="n">
-        <v>9.609999999999999</v>
+        <v>13</v>
       </c>
       <c r="J254" t="n">
         <v>7.91</v>
@@ -9080,29 +9080,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E255" t="n">
-        <v>23.315</v>
+        <v>103.18</v>
       </c>
       <c r="F255" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G255" t="n">
-        <v>69.95</v>
+        <v>103.18</v>
       </c>
       <c r="H255" t="n">
-        <v>4.28</v>
+        <v>3.09</v>
       </c>
       <c r="I255" t="n">
-        <v>6.52</v>
+        <v>3.09</v>
       </c>
       <c r="J255" t="n">
         <v>7.91</v>
@@ -9114,29 +9114,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D256" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E256" t="n">
-        <v>12.128</v>
+        <v>38.095</v>
       </c>
       <c r="F256" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G256" t="n">
-        <v>36.38</v>
+        <v>152.38</v>
       </c>
       <c r="H256" t="n">
-        <v>5.22</v>
+        <v>13.36</v>
       </c>
       <c r="I256" t="n">
-        <v>16.75</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J256" t="n">
         <v>7.91</v>
@@ -9318,29 +9318,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D262" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E262" t="n">
-        <v>7.055</v>
+        <v>38.23</v>
       </c>
       <c r="F262" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G262" t="n">
-        <v>63.49</v>
+        <v>152.92</v>
       </c>
       <c r="H262" t="n">
-        <v>7.34</v>
+        <v>13.9</v>
       </c>
       <c r="I262" t="n">
-        <v>13.07</v>
+        <v>10</v>
       </c>
       <c r="J262" t="n">
         <v>7.91</v>
@@ -9352,29 +9352,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E263" t="n">
-        <v>23.3</v>
+        <v>102.84</v>
       </c>
       <c r="F263" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G263" t="n">
-        <v>69.90000000000001</v>
+        <v>102.84</v>
       </c>
       <c r="H263" t="n">
-        <v>4.23</v>
+        <v>2.75</v>
       </c>
       <c r="I263" t="n">
-        <v>6.44</v>
+        <v>2.75</v>
       </c>
       <c r="J263" t="n">
         <v>7.91</v>
@@ -9386,29 +9386,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D264" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E264" t="n">
-        <v>102.84</v>
+        <v>12.23</v>
       </c>
       <c r="F264" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G264" t="n">
-        <v>102.84</v>
+        <v>36.69</v>
       </c>
       <c r="H264" t="n">
-        <v>2.75</v>
+        <v>5.53</v>
       </c>
       <c r="I264" t="n">
-        <v>2.75</v>
+        <v>17.75</v>
       </c>
       <c r="J264" t="n">
         <v>7.91</v>
@@ -9420,29 +9420,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E265" t="n">
-        <v>38.23</v>
+        <v>7.055</v>
       </c>
       <c r="F265" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G265" t="n">
-        <v>152.92</v>
+        <v>63.49</v>
       </c>
       <c r="H265" t="n">
-        <v>13.9</v>
+        <v>7.34</v>
       </c>
       <c r="I265" t="n">
-        <v>10</v>
+        <v>13.07</v>
       </c>
       <c r="J265" t="n">
         <v>7.91</v>
@@ -9454,29 +9454,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C266" t="n">
         <v>3</v>
       </c>
       <c r="D266" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E266" t="n">
-        <v>12.23</v>
+        <v>23.3</v>
       </c>
       <c r="F266" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G266" t="n">
-        <v>36.69</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H266" t="n">
-        <v>5.53</v>
+        <v>4.23</v>
       </c>
       <c r="I266" t="n">
-        <v>17.75</v>
+        <v>6.44</v>
       </c>
       <c r="J266" t="n">
         <v>7.91</v>
@@ -9828,29 +9828,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D277" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E277" t="n">
-        <v>103.76</v>
+        <v>38.985</v>
       </c>
       <c r="F277" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G277" t="n">
-        <v>103.76</v>
+        <v>155.94</v>
       </c>
       <c r="H277" t="n">
-        <v>3.67</v>
+        <v>16.92</v>
       </c>
       <c r="I277" t="n">
-        <v>3.67</v>
+        <v>12.17</v>
       </c>
       <c r="J277" t="n">
         <v>7.91</v>
@@ -9862,29 +9862,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D278" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E278" t="n">
-        <v>12.492</v>
+        <v>7.063</v>
       </c>
       <c r="F278" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G278" t="n">
-        <v>37.48</v>
+        <v>63.57</v>
       </c>
       <c r="H278" t="n">
-        <v>6.32</v>
+        <v>7.42</v>
       </c>
       <c r="I278" t="n">
-        <v>20.28</v>
+        <v>13.21</v>
       </c>
       <c r="J278" t="n">
         <v>7.91</v>
@@ -9896,29 +9896,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D279" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E279" t="n">
-        <v>7.063</v>
+        <v>22.96</v>
       </c>
       <c r="F279" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G279" t="n">
-        <v>63.57</v>
+        <v>68.88</v>
       </c>
       <c r="H279" t="n">
-        <v>7.42</v>
+        <v>3.21</v>
       </c>
       <c r="I279" t="n">
-        <v>13.21</v>
+        <v>4.89</v>
       </c>
       <c r="J279" t="n">
         <v>7.91</v>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D280" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E280" t="n">
-        <v>38.985</v>
+        <v>103.76</v>
       </c>
       <c r="F280" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G280" t="n">
-        <v>155.94</v>
+        <v>103.76</v>
       </c>
       <c r="H280" t="n">
-        <v>16.92</v>
+        <v>3.67</v>
       </c>
       <c r="I280" t="n">
-        <v>12.17</v>
+        <v>3.67</v>
       </c>
       <c r="J280" t="n">
         <v>7.91</v>
@@ -9964,29 +9964,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C281" t="n">
         <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E281" t="n">
-        <v>22.96</v>
+        <v>12.492</v>
       </c>
       <c r="F281" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G281" t="n">
-        <v>68.88</v>
+        <v>37.48</v>
       </c>
       <c r="H281" t="n">
-        <v>3.21</v>
+        <v>6.32</v>
       </c>
       <c r="I281" t="n">
-        <v>4.89</v>
+        <v>20.28</v>
       </c>
       <c r="J281" t="n">
         <v>7.91</v>
@@ -9998,29 +9998,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D282" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E282" t="n">
-        <v>7.054</v>
+        <v>39.745</v>
       </c>
       <c r="F282" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G282" t="n">
-        <v>63.49</v>
+        <v>158.98</v>
       </c>
       <c r="H282" t="n">
-        <v>7.34</v>
+        <v>19.96</v>
       </c>
       <c r="I282" t="n">
-        <v>13.07</v>
+        <v>14.36</v>
       </c>
       <c r="J282" t="n">
         <v>7.91</v>
@@ -10032,29 +10032,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C283" t="n">
         <v>3</v>
       </c>
       <c r="D283" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E283" t="n">
-        <v>22.97</v>
+        <v>12.468</v>
       </c>
       <c r="F283" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G283" t="n">
-        <v>68.91</v>
+        <v>37.4</v>
       </c>
       <c r="H283" t="n">
-        <v>3.24</v>
+        <v>6.24</v>
       </c>
       <c r="I283" t="n">
-        <v>4.93</v>
+        <v>20.03</v>
       </c>
       <c r="J283" t="n">
         <v>7.91</v>
@@ -10066,29 +10066,29 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D284" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E284" t="n">
-        <v>104.46</v>
+        <v>7.054</v>
       </c>
       <c r="F284" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G284" t="n">
-        <v>104.46</v>
+        <v>63.49</v>
       </c>
       <c r="H284" t="n">
-        <v>4.37</v>
+        <v>7.34</v>
       </c>
       <c r="I284" t="n">
-        <v>4.37</v>
+        <v>13.07</v>
       </c>
       <c r="J284" t="n">
         <v>7.91</v>
@@ -10100,29 +10100,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C285" t="n">
         <v>3</v>
       </c>
       <c r="D285" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E285" t="n">
-        <v>12.468</v>
+        <v>22.97</v>
       </c>
       <c r="F285" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G285" t="n">
-        <v>37.4</v>
+        <v>68.91</v>
       </c>
       <c r="H285" t="n">
-        <v>6.24</v>
+        <v>3.24</v>
       </c>
       <c r="I285" t="n">
-        <v>20.03</v>
+        <v>4.93</v>
       </c>
       <c r="J285" t="n">
         <v>7.91</v>
@@ -10134,29 +10134,29 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E286" t="n">
-        <v>39.745</v>
+        <v>104.46</v>
       </c>
       <c r="F286" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G286" t="n">
-        <v>158.98</v>
+        <v>104.46</v>
       </c>
       <c r="H286" t="n">
-        <v>19.96</v>
+        <v>4.37</v>
       </c>
       <c r="I286" t="n">
-        <v>14.36</v>
+        <v>4.37</v>
       </c>
       <c r="J286" t="n">
         <v>7.91</v>
@@ -10338,29 +10338,29 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D292" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E292" t="n">
-        <v>12.096</v>
+        <v>6.96</v>
       </c>
       <c r="F292" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G292" t="n">
-        <v>36.29</v>
+        <v>62.64</v>
       </c>
       <c r="H292" t="n">
-        <v>5.13</v>
+        <v>6.49</v>
       </c>
       <c r="I292" t="n">
-        <v>16.46</v>
+        <v>11.56</v>
       </c>
       <c r="J292" t="n">
         <v>7.91</v>
@@ -10372,29 +10372,29 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D293" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E293" t="n">
-        <v>38.26</v>
+        <v>22.685</v>
       </c>
       <c r="F293" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G293" t="n">
-        <v>153.04</v>
+        <v>68.05</v>
       </c>
       <c r="H293" t="n">
-        <v>14.02</v>
+        <v>2.38</v>
       </c>
       <c r="I293" t="n">
-        <v>10.08</v>
+        <v>3.62</v>
       </c>
       <c r="J293" t="n">
         <v>7.91</v>
@@ -10406,29 +10406,29 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E294" t="n">
-        <v>22.685</v>
+        <v>101.5</v>
       </c>
       <c r="F294" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G294" t="n">
-        <v>68.05</v>
+        <v>101.5</v>
       </c>
       <c r="H294" t="n">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="I294" t="n">
-        <v>3.62</v>
+        <v>1.41</v>
       </c>
       <c r="J294" t="n">
         <v>7.91</v>
@@ -10440,29 +10440,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D295" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E295" t="n">
-        <v>6.96</v>
+        <v>12.096</v>
       </c>
       <c r="F295" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G295" t="n">
-        <v>62.64</v>
+        <v>36.29</v>
       </c>
       <c r="H295" t="n">
-        <v>6.49</v>
+        <v>5.13</v>
       </c>
       <c r="I295" t="n">
-        <v>11.56</v>
+        <v>16.46</v>
       </c>
       <c r="J295" t="n">
         <v>7.91</v>
@@ -10474,29 +10474,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D296" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E296" t="n">
-        <v>101.5</v>
+        <v>38.26</v>
       </c>
       <c r="F296" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G296" t="n">
-        <v>101.5</v>
+        <v>153.04</v>
       </c>
       <c r="H296" t="n">
-        <v>1.41</v>
+        <v>14.02</v>
       </c>
       <c r="I296" t="n">
-        <v>1.41</v>
+        <v>10.08</v>
       </c>
       <c r="J296" t="n">
         <v>7.91</v>
@@ -10678,29 +10678,29 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D302" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E302" t="n">
-        <v>22.715</v>
+        <v>6.93</v>
       </c>
       <c r="F302" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G302" t="n">
-        <v>68.14</v>
+        <v>62.37</v>
       </c>
       <c r="H302" t="n">
-        <v>2.47</v>
+        <v>6.22</v>
       </c>
       <c r="I302" t="n">
-        <v>3.76</v>
+        <v>11.08</v>
       </c>
       <c r="J302" t="n">
         <v>7.91</v>
@@ -10712,29 +10712,29 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C303" t="n">
         <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E303" t="n">
-        <v>11.828</v>
+        <v>22.715</v>
       </c>
       <c r="F303" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G303" t="n">
-        <v>35.48</v>
+        <v>68.14</v>
       </c>
       <c r="H303" t="n">
-        <v>4.32</v>
+        <v>2.47</v>
       </c>
       <c r="I303" t="n">
-        <v>13.86</v>
+        <v>3.76</v>
       </c>
       <c r="J303" t="n">
         <v>7.91</v>
@@ -10746,29 +10746,29 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D304" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E304" t="n">
-        <v>100.78</v>
+        <v>11.828</v>
       </c>
       <c r="F304" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G304" t="n">
-        <v>100.78</v>
+        <v>35.48</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.86</v>
       </c>
       <c r="J304" t="n">
         <v>7.91</v>
@@ -10780,29 +10780,29 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D305" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E305" t="n">
-        <v>38.845</v>
+        <v>100.78</v>
       </c>
       <c r="F305" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G305" t="n">
-        <v>155.38</v>
+        <v>100.78</v>
       </c>
       <c r="H305" t="n">
-        <v>16.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I305" t="n">
-        <v>11.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J305" t="n">
         <v>7.91</v>
@@ -10814,29 +10814,29 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D306" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E306" t="n">
-        <v>6.93</v>
+        <v>38.845</v>
       </c>
       <c r="F306" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G306" t="n">
-        <v>62.37</v>
+        <v>155.38</v>
       </c>
       <c r="H306" t="n">
-        <v>6.22</v>
+        <v>16.36</v>
       </c>
       <c r="I306" t="n">
-        <v>11.08</v>
+        <v>11.77</v>
       </c>
       <c r="J306" t="n">
         <v>7.91</v>
@@ -10848,29 +10848,29 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D307" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E307" t="n">
-        <v>99.95</v>
+        <v>11.686</v>
       </c>
       <c r="F307" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G307" t="n">
-        <v>99.95</v>
+        <v>35.06</v>
       </c>
       <c r="H307" t="n">
-        <v>-0.14</v>
+        <v>3.9</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.14</v>
+        <v>12.52</v>
       </c>
       <c r="J307" t="n">
         <v>7.91</v>
@@ -10882,29 +10882,29 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D308" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E308" t="n">
-        <v>38.055</v>
+        <v>22.555</v>
       </c>
       <c r="F308" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G308" t="n">
-        <v>152.22</v>
+        <v>67.66</v>
       </c>
       <c r="H308" t="n">
-        <v>13.2</v>
+        <v>1.99</v>
       </c>
       <c r="I308" t="n">
-        <v>9.5</v>
+        <v>3.03</v>
       </c>
       <c r="J308" t="n">
         <v>7.91</v>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E310" t="n">
-        <v>11.686</v>
+        <v>99.95</v>
       </c>
       <c r="F310" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G310" t="n">
-        <v>35.06</v>
+        <v>99.95</v>
       </c>
       <c r="H310" t="n">
-        <v>3.9</v>
+        <v>-0.14</v>
       </c>
       <c r="I310" t="n">
-        <v>12.52</v>
+        <v>-0.14</v>
       </c>
       <c r="J310" t="n">
         <v>7.91</v>
@@ -10984,29 +10984,29 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D311" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E311" t="n">
-        <v>22.555</v>
+        <v>38.055</v>
       </c>
       <c r="F311" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G311" t="n">
-        <v>67.66</v>
+        <v>152.22</v>
       </c>
       <c r="H311" t="n">
-        <v>1.99</v>
+        <v>13.2</v>
       </c>
       <c r="I311" t="n">
-        <v>3.03</v>
+        <v>9.5</v>
       </c>
       <c r="J311" t="n">
         <v>7.91</v>
@@ -11358,29 +11358,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D322" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E322" t="n">
-        <v>22.745</v>
+        <v>39.07</v>
       </c>
       <c r="F322" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G322" t="n">
-        <v>68.23</v>
+        <v>156.28</v>
       </c>
       <c r="H322" t="n">
-        <v>2.56</v>
+        <v>17.26</v>
       </c>
       <c r="I322" t="n">
-        <v>3.9</v>
+        <v>12.42</v>
       </c>
       <c r="J322" t="n">
         <v>7.91</v>
@@ -11392,29 +11392,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D323" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E323" t="n">
-        <v>6.967</v>
+        <v>101.7</v>
       </c>
       <c r="F323" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G323" t="n">
-        <v>62.7</v>
+        <v>101.7</v>
       </c>
       <c r="H323" t="n">
-        <v>6.55</v>
+        <v>1.61</v>
       </c>
       <c r="I323" t="n">
-        <v>11.67</v>
+        <v>1.61</v>
       </c>
       <c r="J323" t="n">
         <v>7.91</v>
@@ -11426,29 +11426,29 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D324" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E324" t="n">
-        <v>11.81</v>
+        <v>6.967</v>
       </c>
       <c r="F324" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G324" t="n">
-        <v>35.43</v>
+        <v>62.7</v>
       </c>
       <c r="H324" t="n">
-        <v>4.27</v>
+        <v>6.55</v>
       </c>
       <c r="I324" t="n">
-        <v>13.7</v>
+        <v>11.67</v>
       </c>
       <c r="J324" t="n">
         <v>7.91</v>
@@ -11460,29 +11460,29 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D325" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E325" t="n">
-        <v>101.7</v>
+        <v>22.745</v>
       </c>
       <c r="F325" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G325" t="n">
-        <v>101.7</v>
+        <v>68.23</v>
       </c>
       <c r="H325" t="n">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="I325" t="n">
-        <v>1.61</v>
+        <v>3.9</v>
       </c>
       <c r="J325" t="n">
         <v>7.91</v>
@@ -11494,29 +11494,29 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D326" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E326" t="n">
-        <v>39.07</v>
+        <v>11.81</v>
       </c>
       <c r="F326" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G326" t="n">
-        <v>156.28</v>
+        <v>35.43</v>
       </c>
       <c r="H326" t="n">
-        <v>17.26</v>
+        <v>4.27</v>
       </c>
       <c r="I326" t="n">
-        <v>12.42</v>
+        <v>13.7</v>
       </c>
       <c r="J326" t="n">
         <v>7.91</v>
@@ -11868,29 +11868,29 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D337" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E337" t="n">
-        <v>39.15</v>
+        <v>22.845</v>
       </c>
       <c r="F337" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G337" t="n">
-        <v>156.6</v>
+        <v>68.53</v>
       </c>
       <c r="H337" t="n">
-        <v>17.58</v>
+        <v>2.86</v>
       </c>
       <c r="I337" t="n">
-        <v>12.65</v>
+        <v>4.36</v>
       </c>
       <c r="J337" t="n">
         <v>7.91</v>
@@ -11902,29 +11902,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D338" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E338" t="n">
-        <v>11.284</v>
+        <v>6.938</v>
       </c>
       <c r="F338" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G338" t="n">
-        <v>33.85</v>
+        <v>62.44</v>
       </c>
       <c r="H338" t="n">
-        <v>2.69</v>
+        <v>6.29</v>
       </c>
       <c r="I338" t="n">
-        <v>8.630000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="J338" t="n">
         <v>7.91</v>
@@ -11936,29 +11936,29 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D339" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E339" t="n">
-        <v>101.04</v>
+        <v>11.284</v>
       </c>
       <c r="F339" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G339" t="n">
-        <v>101.04</v>
+        <v>33.85</v>
       </c>
       <c r="H339" t="n">
-        <v>0.95</v>
+        <v>2.69</v>
       </c>
       <c r="I339" t="n">
-        <v>0.95</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J339" t="n">
         <v>7.91</v>
@@ -11970,29 +11970,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D340" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E340" t="n">
-        <v>6.938</v>
+        <v>39.15</v>
       </c>
       <c r="F340" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G340" t="n">
-        <v>62.44</v>
+        <v>156.6</v>
       </c>
       <c r="H340" t="n">
-        <v>6.29</v>
+        <v>17.58</v>
       </c>
       <c r="I340" t="n">
-        <v>11.2</v>
+        <v>12.65</v>
       </c>
       <c r="J340" t="n">
         <v>7.91</v>
@@ -12004,29 +12004,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E341" t="n">
-        <v>22.845</v>
+        <v>101.04</v>
       </c>
       <c r="F341" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G341" t="n">
-        <v>68.53</v>
+        <v>101.04</v>
       </c>
       <c r="H341" t="n">
-        <v>2.86</v>
+        <v>0.95</v>
       </c>
       <c r="I341" t="n">
-        <v>4.36</v>
+        <v>0.95</v>
       </c>
       <c r="J341" t="n">
         <v>7.91</v>
@@ -12208,29 +12208,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D347" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E347" t="n">
-        <v>101.78</v>
+        <v>7.005</v>
       </c>
       <c r="F347" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G347" t="n">
-        <v>101.78</v>
+        <v>63.05</v>
       </c>
       <c r="H347" t="n">
-        <v>1.69</v>
+        <v>6.9</v>
       </c>
       <c r="I347" t="n">
-        <v>1.69</v>
+        <v>12.29</v>
       </c>
       <c r="J347" t="n">
         <v>7.91</v>
@@ -12242,29 +12242,29 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D348" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E348" t="n">
-        <v>11.206</v>
+        <v>39</v>
       </c>
       <c r="F348" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G348" t="n">
-        <v>33.62</v>
+        <v>156</v>
       </c>
       <c r="H348" t="n">
-        <v>2.46</v>
+        <v>16.98</v>
       </c>
       <c r="I348" t="n">
-        <v>7.89</v>
+        <v>12.21</v>
       </c>
       <c r="J348" t="n">
         <v>7.91</v>
@@ -12276,29 +12276,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D349" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E349" t="n">
-        <v>39</v>
+        <v>22.82</v>
       </c>
       <c r="F349" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G349" t="n">
-        <v>156</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="H349" t="n">
-        <v>16.98</v>
+        <v>2.79</v>
       </c>
       <c r="I349" t="n">
-        <v>12.21</v>
+        <v>4.25</v>
       </c>
       <c r="J349" t="n">
         <v>7.91</v>
@@ -12310,29 +12310,29 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D350" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E350" t="n">
-        <v>7.005</v>
+        <v>101.78</v>
       </c>
       <c r="F350" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G350" t="n">
-        <v>63.05</v>
+        <v>101.78</v>
       </c>
       <c r="H350" t="n">
-        <v>6.9</v>
+        <v>1.69</v>
       </c>
       <c r="I350" t="n">
-        <v>12.29</v>
+        <v>1.69</v>
       </c>
       <c r="J350" t="n">
         <v>7.91</v>
@@ -12344,29 +12344,29 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C351" t="n">
         <v>3</v>
       </c>
       <c r="D351" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E351" t="n">
-        <v>22.82</v>
+        <v>11.206</v>
       </c>
       <c r="F351" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G351" t="n">
-        <v>68.45999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="H351" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="I351" t="n">
-        <v>4.25</v>
+        <v>7.89</v>
       </c>
       <c r="J351" t="n">
         <v>7.91</v>
@@ -12718,29 +12718,29 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D362" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E362" t="n">
-        <v>6.972</v>
+        <v>102.1</v>
       </c>
       <c r="F362" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G362" t="n">
-        <v>62.75</v>
+        <v>102.1</v>
       </c>
       <c r="H362" t="n">
-        <v>6.6</v>
+        <v>2.01</v>
       </c>
       <c r="I362" t="n">
-        <v>11.75</v>
+        <v>2.01</v>
       </c>
       <c r="J362" t="n">
         <v>7.91</v>
@@ -12752,29 +12752,29 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C363" t="n">
         <v>3</v>
       </c>
       <c r="D363" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E363" t="n">
-        <v>22.515</v>
+        <v>11.208</v>
       </c>
       <c r="F363" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G363" t="n">
-        <v>67.55</v>
+        <v>33.62</v>
       </c>
       <c r="H363" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="I363" t="n">
-        <v>2.86</v>
+        <v>7.89</v>
       </c>
       <c r="J363" t="n">
         <v>7.91</v>
@@ -12786,29 +12786,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D364" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E364" t="n">
-        <v>11.208</v>
+        <v>40.15</v>
       </c>
       <c r="F364" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G364" t="n">
-        <v>33.62</v>
+        <v>160.6</v>
       </c>
       <c r="H364" t="n">
-        <v>2.46</v>
+        <v>21.58</v>
       </c>
       <c r="I364" t="n">
-        <v>7.89</v>
+        <v>15.52</v>
       </c>
       <c r="J364" t="n">
         <v>7.91</v>
@@ -12820,29 +12820,29 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D365" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E365" t="n">
-        <v>102.1</v>
+        <v>6.972</v>
       </c>
       <c r="F365" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G365" t="n">
-        <v>102.1</v>
+        <v>62.75</v>
       </c>
       <c r="H365" t="n">
-        <v>2.01</v>
+        <v>6.6</v>
       </c>
       <c r="I365" t="n">
-        <v>2.01</v>
+        <v>11.75</v>
       </c>
       <c r="J365" t="n">
         <v>7.91</v>
@@ -12854,29 +12854,29 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D366" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E366" t="n">
-        <v>40.15</v>
+        <v>22.515</v>
       </c>
       <c r="F366" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G366" t="n">
-        <v>160.6</v>
+        <v>67.55</v>
       </c>
       <c r="H366" t="n">
-        <v>21.58</v>
+        <v>1.88</v>
       </c>
       <c r="I366" t="n">
-        <v>15.52</v>
+        <v>2.86</v>
       </c>
       <c r="J366" t="n">
         <v>7.91</v>
@@ -13228,29 +13228,29 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D377" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E377" t="n">
-        <v>101.88</v>
+        <v>10.962</v>
       </c>
       <c r="F377" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G377" t="n">
-        <v>101.88</v>
+        <v>32.89</v>
       </c>
       <c r="H377" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="I377" t="n">
-        <v>1.79</v>
+        <v>5.55</v>
       </c>
       <c r="J377" t="n">
         <v>7.91</v>
@@ -13262,29 +13262,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D378" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E378" t="n">
-        <v>39.57</v>
+        <v>6.941</v>
       </c>
       <c r="F378" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G378" t="n">
-        <v>158.28</v>
+        <v>62.47</v>
       </c>
       <c r="H378" t="n">
-        <v>19.26</v>
+        <v>6.32</v>
       </c>
       <c r="I378" t="n">
-        <v>13.85</v>
+        <v>11.26</v>
       </c>
       <c r="J378" t="n">
         <v>7.91</v>
@@ -13330,29 +13330,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D380" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E380" t="n">
-        <v>6.941</v>
+        <v>101.88</v>
       </c>
       <c r="F380" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G380" t="n">
-        <v>62.47</v>
+        <v>101.88</v>
       </c>
       <c r="H380" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="I380" t="n">
-        <v>11.26</v>
+        <v>1.79</v>
       </c>
       <c r="J380" t="n">
         <v>7.91</v>
@@ -13364,29 +13364,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D381" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E381" t="n">
-        <v>10.962</v>
+        <v>39.57</v>
       </c>
       <c r="F381" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G381" t="n">
-        <v>32.89</v>
+        <v>158.28</v>
       </c>
       <c r="H381" t="n">
-        <v>1.73</v>
+        <v>19.26</v>
       </c>
       <c r="I381" t="n">
-        <v>5.55</v>
+        <v>13.85</v>
       </c>
       <c r="J381" t="n">
         <v>7.91</v>
@@ -13738,29 +13738,29 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D392" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E392" t="n">
-        <v>101.52</v>
+        <v>38.92</v>
       </c>
       <c r="F392" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G392" t="n">
-        <v>101.52</v>
+        <v>155.68</v>
       </c>
       <c r="H392" t="n">
-        <v>1.43</v>
+        <v>16.66</v>
       </c>
       <c r="I392" t="n">
-        <v>1.43</v>
+        <v>11.98</v>
       </c>
       <c r="J392" t="n">
         <v>7.91</v>
@@ -13772,29 +13772,29 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C393" t="n">
         <v>3</v>
       </c>
       <c r="D393" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E393" t="n">
-        <v>21.845</v>
+        <v>11.1</v>
       </c>
       <c r="F393" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G393" t="n">
-        <v>65.53</v>
+        <v>33.3</v>
       </c>
       <c r="H393" t="n">
-        <v>-0.14</v>
+        <v>2.14</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.21</v>
+        <v>6.87</v>
       </c>
       <c r="J393" t="n">
         <v>7.91</v>
@@ -13806,29 +13806,29 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D394" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E394" t="n">
+        <v>6.931</v>
+      </c>
+      <c r="F394" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G394" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="H394" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="I394" t="n">
         <v>11.1</v>
-      </c>
-      <c r="F394" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="G394" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H394" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I394" t="n">
-        <v>6.87</v>
       </c>
       <c r="J394" t="n">
         <v>7.91</v>
@@ -13840,29 +13840,29 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D395" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E395" t="n">
-        <v>6.931</v>
+        <v>101.52</v>
       </c>
       <c r="F395" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G395" t="n">
-        <v>62.38</v>
+        <v>101.52</v>
       </c>
       <c r="H395" t="n">
-        <v>6.23</v>
+        <v>1.43</v>
       </c>
       <c r="I395" t="n">
-        <v>11.1</v>
+        <v>1.43</v>
       </c>
       <c r="J395" t="n">
         <v>7.91</v>
@@ -13874,29 +13874,29 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D396" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E396" t="n">
-        <v>38.92</v>
+        <v>21.845</v>
       </c>
       <c r="F396" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G396" t="n">
-        <v>155.68</v>
+        <v>65.53</v>
       </c>
       <c r="H396" t="n">
-        <v>16.66</v>
+        <v>-0.14</v>
       </c>
       <c r="I396" t="n">
-        <v>11.98</v>
+        <v>-0.21</v>
       </c>
       <c r="J396" t="n">
         <v>7.91</v>
@@ -14248,29 +14248,29 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D407" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E407" t="n">
-        <v>105.98</v>
+        <v>7.049</v>
       </c>
       <c r="F407" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G407" t="n">
-        <v>105.98</v>
+        <v>63.44</v>
       </c>
       <c r="H407" t="n">
-        <v>5.89</v>
+        <v>7.29</v>
       </c>
       <c r="I407" t="n">
-        <v>5.88</v>
+        <v>12.98</v>
       </c>
       <c r="J407" t="n">
         <v>7.91</v>
@@ -14282,29 +14282,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D408" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E408" t="n">
-        <v>40.695</v>
+        <v>22.35</v>
       </c>
       <c r="F408" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G408" t="n">
-        <v>162.78</v>
+        <v>67.05</v>
       </c>
       <c r="H408" t="n">
-        <v>23.76</v>
+        <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>17.09</v>
+        <v>2.1</v>
       </c>
       <c r="J408" t="n">
         <v>7.91</v>
@@ -14316,29 +14316,29 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D409" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E409" t="n">
-        <v>11.232</v>
+        <v>105.98</v>
       </c>
       <c r="F409" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G409" t="n">
-        <v>33.7</v>
+        <v>105.98</v>
       </c>
       <c r="H409" t="n">
-        <v>2.54</v>
+        <v>5.89</v>
       </c>
       <c r="I409" t="n">
-        <v>8.15</v>
+        <v>5.88</v>
       </c>
       <c r="J409" t="n">
         <v>7.91</v>
@@ -14350,29 +14350,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D410" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E410" t="n">
-        <v>22.35</v>
+        <v>40.695</v>
       </c>
       <c r="F410" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G410" t="n">
-        <v>67.05</v>
+        <v>162.78</v>
       </c>
       <c r="H410" t="n">
-        <v>1.38</v>
+        <v>23.76</v>
       </c>
       <c r="I410" t="n">
-        <v>2.1</v>
+        <v>17.09</v>
       </c>
       <c r="J410" t="n">
         <v>7.91</v>
@@ -14384,29 +14384,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D411" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E411" t="n">
-        <v>7.049</v>
+        <v>11.232</v>
       </c>
       <c r="F411" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G411" t="n">
-        <v>63.44</v>
+        <v>33.7</v>
       </c>
       <c r="H411" t="n">
-        <v>7.29</v>
+        <v>2.54</v>
       </c>
       <c r="I411" t="n">
-        <v>12.98</v>
+        <v>8.15</v>
       </c>
       <c r="J411" t="n">
         <v>7.91</v>
@@ -14758,29 +14758,29 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D422" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E422" t="n">
-        <v>22.11</v>
+        <v>106.78</v>
       </c>
       <c r="F422" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G422" t="n">
-        <v>66.33</v>
+        <v>106.78</v>
       </c>
       <c r="H422" t="n">
-        <v>0.66</v>
+        <v>6.69</v>
       </c>
       <c r="I422" t="n">
-        <v>1.01</v>
+        <v>6.68</v>
       </c>
       <c r="J422" t="n">
         <v>7.91</v>
@@ -14792,29 +14792,29 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D423" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E423" t="n">
-        <v>40.225</v>
+        <v>11.144</v>
       </c>
       <c r="F423" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G423" t="n">
-        <v>160.9</v>
+        <v>33.43</v>
       </c>
       <c r="H423" t="n">
-        <v>21.88</v>
+        <v>2.27</v>
       </c>
       <c r="I423" t="n">
-        <v>15.74</v>
+        <v>7.28</v>
       </c>
       <c r="J423" t="n">
         <v>7.91</v>
@@ -14826,29 +14826,29 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D424" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E424" t="n">
-        <v>7.037</v>
+        <v>40.225</v>
       </c>
       <c r="F424" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G424" t="n">
-        <v>63.33</v>
+        <v>160.9</v>
       </c>
       <c r="H424" t="n">
-        <v>7.18</v>
+        <v>21.88</v>
       </c>
       <c r="I424" t="n">
-        <v>12.79</v>
+        <v>15.74</v>
       </c>
       <c r="J424" t="n">
         <v>7.91</v>
@@ -14860,29 +14860,29 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D425" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E425" t="n">
-        <v>106.78</v>
+        <v>22.11</v>
       </c>
       <c r="F425" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G425" t="n">
-        <v>106.78</v>
+        <v>66.33</v>
       </c>
       <c r="H425" t="n">
-        <v>6.69</v>
+        <v>0.66</v>
       </c>
       <c r="I425" t="n">
-        <v>6.68</v>
+        <v>1.01</v>
       </c>
       <c r="J425" t="n">
         <v>7.91</v>
@@ -14894,29 +14894,29 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D426" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E426" t="n">
-        <v>11.144</v>
+        <v>7.037</v>
       </c>
       <c r="F426" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G426" t="n">
-        <v>33.43</v>
+        <v>63.33</v>
       </c>
       <c r="H426" t="n">
-        <v>2.27</v>
+        <v>7.18</v>
       </c>
       <c r="I426" t="n">
-        <v>7.28</v>
+        <v>12.79</v>
       </c>
       <c r="J426" t="n">
         <v>7.91</v>
@@ -15268,29 +15268,29 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D437" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E437" t="n">
-        <v>107.38</v>
+        <v>40.495</v>
       </c>
       <c r="F437" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G437" t="n">
-        <v>107.38</v>
+        <v>161.98</v>
       </c>
       <c r="H437" t="n">
-        <v>7.29</v>
+        <v>22.96</v>
       </c>
       <c r="I437" t="n">
-        <v>7.28</v>
+        <v>16.52</v>
       </c>
       <c r="J437" t="n">
         <v>7.91</v>
@@ -15302,29 +15302,29 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C438" t="n">
         <v>3</v>
       </c>
       <c r="D438" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E438" t="n">
-        <v>21.7</v>
+        <v>11.02</v>
       </c>
       <c r="F438" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G438" t="n">
-        <v>65.09999999999999</v>
+        <v>33.06</v>
       </c>
       <c r="H438" t="n">
-        <v>-0.57</v>
+        <v>1.9</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.87</v>
+        <v>6.1</v>
       </c>
       <c r="J438" t="n">
         <v>7.91</v>
@@ -15336,29 +15336,29 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D439" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E439" t="n">
-        <v>7.055</v>
+        <v>21.7</v>
       </c>
       <c r="F439" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G439" t="n">
-        <v>63.49</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H439" t="n">
-        <v>7.34</v>
+        <v>-0.57</v>
       </c>
       <c r="I439" t="n">
-        <v>13.07</v>
+        <v>-0.87</v>
       </c>
       <c r="J439" t="n">
         <v>7.91</v>
@@ -15370,29 +15370,29 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D440" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E440" t="n">
-        <v>11.02</v>
+        <v>107.38</v>
       </c>
       <c r="F440" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G440" t="n">
-        <v>33.06</v>
+        <v>107.38</v>
       </c>
       <c r="H440" t="n">
-        <v>1.9</v>
+        <v>7.29</v>
       </c>
       <c r="I440" t="n">
-        <v>6.1</v>
+        <v>7.28</v>
       </c>
       <c r="J440" t="n">
         <v>7.91</v>
@@ -15404,29 +15404,29 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D441" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E441" t="n">
-        <v>40.495</v>
+        <v>7.055</v>
       </c>
       <c r="F441" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G441" t="n">
-        <v>161.98</v>
+        <v>63.49</v>
       </c>
       <c r="H441" t="n">
-        <v>22.96</v>
+        <v>7.34</v>
       </c>
       <c r="I441" t="n">
-        <v>16.52</v>
+        <v>13.07</v>
       </c>
       <c r="J441" t="n">
         <v>7.91</v>
@@ -15599,6 +15599,176 @@
         <v>13.48</v>
       </c>
       <c r="J446" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>EFENSE</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>3</v>
+      </c>
+      <c r="D447" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E447" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F447" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="G447" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="H447" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I447" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J447" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>PAASI</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>4</v>
+      </c>
+      <c r="D448" t="n">
+        <v>34.755</v>
+      </c>
+      <c r="E448" t="n">
+        <v>40.265</v>
+      </c>
+      <c r="F448" t="n">
+        <v>139.02</v>
+      </c>
+      <c r="G448" t="n">
+        <v>161.06</v>
+      </c>
+      <c r="H448" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="I448" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="J448" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>PINDIA</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>3</v>
+      </c>
+      <c r="D449" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E449" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="F449" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G449" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="H449" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I449" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="J449" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>PUST</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E450" t="n">
+        <v>108.28</v>
+      </c>
+      <c r="F450" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="G450" t="n">
+        <v>108.28</v>
+      </c>
+      <c r="H450" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="I450" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="J450" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>IWSC</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>9</v>
+      </c>
+      <c r="D451" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E451" t="n">
+        <v>7.062</v>
+      </c>
+      <c r="F451" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G451" t="n">
+        <v>63.56</v>
+      </c>
+      <c r="H451" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="I451" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J451" t="n">
         <v>7.91</v>
       </c>
     </row>

--- a/suivi_pea_detail.xlsx
+++ b/suivi_pea_detail.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J451"/>
+  <dimension ref="A1:J456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,29 +818,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E12" t="n">
-        <v>105.22</v>
+        <v>21.907</v>
       </c>
       <c r="F12" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G12" t="n">
-        <v>105.22</v>
+        <v>65.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.13</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.13</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>7.91</v>
@@ -852,29 +852,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E13" t="n">
-        <v>6.788</v>
+        <v>10.756</v>
       </c>
       <c r="F13" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G13" t="n">
-        <v>61.09</v>
+        <v>32.27</v>
       </c>
       <c r="H13" t="n">
-        <v>4.94</v>
+        <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="J13" t="n">
         <v>7.91</v>
@@ -886,29 +886,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E14" t="n">
-        <v>10.756</v>
+        <v>41.121</v>
       </c>
       <c r="F14" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G14" t="n">
-        <v>32.27</v>
+        <v>164.48</v>
       </c>
       <c r="H14" t="n">
-        <v>1.11</v>
+        <v>25.46</v>
       </c>
       <c r="I14" t="n">
-        <v>3.56</v>
+        <v>18.31</v>
       </c>
       <c r="J14" t="n">
         <v>7.91</v>
@@ -920,29 +920,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E15" t="n">
-        <v>41.121</v>
+        <v>105.22</v>
       </c>
       <c r="F15" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G15" t="n">
-        <v>164.48</v>
+        <v>105.22</v>
       </c>
       <c r="H15" t="n">
-        <v>25.46</v>
+        <v>5.13</v>
       </c>
       <c r="I15" t="n">
-        <v>18.31</v>
+        <v>5.13</v>
       </c>
       <c r="J15" t="n">
         <v>7.91</v>
@@ -954,29 +954,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E16" t="n">
-        <v>21.907</v>
+        <v>6.788</v>
       </c>
       <c r="F16" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G16" t="n">
-        <v>65.72</v>
+        <v>61.09</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>4.94</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>7.91</v>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E27" t="n">
-        <v>104.9</v>
+        <v>21.98</v>
       </c>
       <c r="F27" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G27" t="n">
-        <v>104.9</v>
+        <v>65.94</v>
       </c>
       <c r="H27" t="n">
-        <v>4.81</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>4.81</v>
+        <v>0.41</v>
       </c>
       <c r="J27" t="n">
         <v>7.91</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E28" t="n">
-        <v>10.66</v>
+        <v>6.795</v>
       </c>
       <c r="F28" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G28" t="n">
-        <v>31.98</v>
+        <v>61.16</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>8.92</v>
       </c>
       <c r="J28" t="n">
         <v>7.91</v>
@@ -1396,29 +1396,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E29" t="n">
-        <v>6.795</v>
+        <v>40.532</v>
       </c>
       <c r="F29" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G29" t="n">
-        <v>61.16</v>
+        <v>162.13</v>
       </c>
       <c r="H29" t="n">
-        <v>5.01</v>
+        <v>23.11</v>
       </c>
       <c r="I29" t="n">
-        <v>8.92</v>
+        <v>16.62</v>
       </c>
       <c r="J29" t="n">
         <v>7.91</v>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E30" t="n">
-        <v>40.532</v>
+        <v>104.9</v>
       </c>
       <c r="F30" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G30" t="n">
-        <v>162.13</v>
+        <v>104.9</v>
       </c>
       <c r="H30" t="n">
-        <v>23.11</v>
+        <v>4.81</v>
       </c>
       <c r="I30" t="n">
-        <v>16.62</v>
+        <v>4.81</v>
       </c>
       <c r="J30" t="n">
         <v>7.91</v>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E31" t="n">
-        <v>21.98</v>
+        <v>10.66</v>
       </c>
       <c r="F31" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G31" t="n">
-        <v>65.94</v>
+        <v>31.98</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>0.41</v>
+        <v>2.63</v>
       </c>
       <c r="J31" t="n">
         <v>7.91</v>
@@ -1838,29 +1838,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E42" t="n">
-        <v>6.629</v>
+        <v>100.06</v>
       </c>
       <c r="F42" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G42" t="n">
-        <v>59.66</v>
+        <v>100.06</v>
       </c>
       <c r="H42" t="n">
-        <v>3.51</v>
+        <v>-0.03</v>
       </c>
       <c r="I42" t="n">
-        <v>6.25</v>
+        <v>-0.03</v>
       </c>
       <c r="J42" t="n">
         <v>7.91</v>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E43" t="n">
-        <v>10.61</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G43" t="n">
-        <v>31.83</v>
+        <v>66</v>
       </c>
       <c r="H43" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I43" t="n">
-        <v>2.15</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>7.91</v>
@@ -1906,29 +1906,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E44" t="n">
-        <v>100.06</v>
+        <v>38.497</v>
       </c>
       <c r="F44" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G44" t="n">
-        <v>100.06</v>
+        <v>153.99</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.03</v>
+        <v>14.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.03</v>
+        <v>10.77</v>
       </c>
       <c r="J44" t="n">
         <v>7.91</v>
@@ -1940,29 +1940,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E45" t="n">
-        <v>38.497</v>
+        <v>10.61</v>
       </c>
       <c r="F45" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G45" t="n">
-        <v>153.99</v>
+        <v>31.83</v>
       </c>
       <c r="H45" t="n">
-        <v>14.97</v>
+        <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>10.77</v>
+        <v>2.15</v>
       </c>
       <c r="J45" t="n">
         <v>7.91</v>
@@ -1974,29 +1974,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E46" t="n">
-        <v>22</v>
+        <v>6.629</v>
       </c>
       <c r="F46" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G46" t="n">
-        <v>66</v>
+        <v>59.66</v>
       </c>
       <c r="H46" t="n">
-        <v>0.33</v>
+        <v>3.51</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="J46" t="n">
         <v>7.91</v>
@@ -2348,29 +2348,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E57" t="n">
-        <v>39.845</v>
+        <v>10.75</v>
       </c>
       <c r="F57" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G57" t="n">
-        <v>159.38</v>
+        <v>32.25</v>
       </c>
       <c r="H57" t="n">
-        <v>20.36</v>
+        <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>14.65</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>7.91</v>
@@ -2382,29 +2382,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E58" t="n">
-        <v>6.736</v>
+        <v>102.86</v>
       </c>
       <c r="F58" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G58" t="n">
-        <v>60.62</v>
+        <v>102.86</v>
       </c>
       <c r="H58" t="n">
-        <v>4.47</v>
+        <v>2.77</v>
       </c>
       <c r="I58" t="n">
-        <v>7.96</v>
+        <v>2.77</v>
       </c>
       <c r="J58" t="n">
         <v>7.91</v>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E59" t="n">
-        <v>22.289</v>
+        <v>39.845</v>
       </c>
       <c r="F59" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G59" t="n">
-        <v>66.87</v>
+        <v>159.38</v>
       </c>
       <c r="H59" t="n">
-        <v>1.2</v>
+        <v>20.36</v>
       </c>
       <c r="I59" t="n">
-        <v>1.83</v>
+        <v>14.65</v>
       </c>
       <c r="J59" t="n">
         <v>7.91</v>
@@ -2450,29 +2450,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E60" t="n">
-        <v>102.86</v>
+        <v>6.736</v>
       </c>
       <c r="F60" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G60" t="n">
-        <v>102.86</v>
+        <v>60.62</v>
       </c>
       <c r="H60" t="n">
-        <v>2.77</v>
+        <v>4.47</v>
       </c>
       <c r="I60" t="n">
-        <v>2.77</v>
+        <v>7.96</v>
       </c>
       <c r="J60" t="n">
         <v>7.91</v>
@@ -2484,29 +2484,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E61" t="n">
-        <v>10.75</v>
+        <v>22.289</v>
       </c>
       <c r="F61" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G61" t="n">
-        <v>32.25</v>
+        <v>66.87</v>
       </c>
       <c r="H61" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="J61" t="n">
         <v>7.91</v>
@@ -2688,29 +2688,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E67" t="n">
-        <v>6.807</v>
+        <v>40.567</v>
       </c>
       <c r="F67" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G67" t="n">
-        <v>61.26</v>
+        <v>162.27</v>
       </c>
       <c r="H67" t="n">
-        <v>5.11</v>
+        <v>23.25</v>
       </c>
       <c r="I67" t="n">
-        <v>9.1</v>
+        <v>16.72</v>
       </c>
       <c r="J67" t="n">
         <v>7.91</v>
@@ -2722,29 +2722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E68" t="n">
-        <v>104.58</v>
+        <v>22.797</v>
       </c>
       <c r="F68" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G68" t="n">
-        <v>104.58</v>
+        <v>68.39</v>
       </c>
       <c r="H68" t="n">
-        <v>4.49</v>
+        <v>2.72</v>
       </c>
       <c r="I68" t="n">
-        <v>4.49</v>
+        <v>4.14</v>
       </c>
       <c r="J68" t="n">
         <v>7.91</v>
@@ -2756,29 +2756,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E69" t="n">
-        <v>22.797</v>
+        <v>10.796</v>
       </c>
       <c r="F69" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G69" t="n">
-        <v>68.39</v>
+        <v>32.39</v>
       </c>
       <c r="H69" t="n">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="I69" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="J69" t="n">
         <v>7.91</v>
@@ -2790,29 +2790,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E70" t="n">
-        <v>40.567</v>
+        <v>6.807</v>
       </c>
       <c r="F70" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G70" t="n">
-        <v>162.27</v>
+        <v>61.26</v>
       </c>
       <c r="H70" t="n">
-        <v>23.25</v>
+        <v>5.11</v>
       </c>
       <c r="I70" t="n">
-        <v>16.72</v>
+        <v>9.1</v>
       </c>
       <c r="J70" t="n">
         <v>7.91</v>
@@ -2824,29 +2824,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E71" t="n">
-        <v>10.796</v>
+        <v>104.58</v>
       </c>
       <c r="F71" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G71" t="n">
-        <v>32.39</v>
+        <v>104.58</v>
       </c>
       <c r="H71" t="n">
-        <v>1.23</v>
+        <v>4.49</v>
       </c>
       <c r="I71" t="n">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="J71" t="n">
         <v>7.91</v>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E82" t="n">
-        <v>42.1</v>
+        <v>23.3</v>
       </c>
       <c r="F82" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G82" t="n">
-        <v>168.4</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>29.38</v>
+        <v>4.23</v>
       </c>
       <c r="I82" t="n">
-        <v>21.13</v>
+        <v>6.44</v>
       </c>
       <c r="J82" t="n">
         <v>7.91</v>
@@ -3232,29 +3232,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E83" t="n">
-        <v>106.26</v>
+        <v>10.988</v>
       </c>
       <c r="F83" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G83" t="n">
-        <v>106.26</v>
+        <v>32.96</v>
       </c>
       <c r="H83" t="n">
-        <v>6.17</v>
+        <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="J83" t="n">
         <v>7.91</v>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E84" t="n">
-        <v>10.988</v>
+        <v>6.846</v>
       </c>
       <c r="F84" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G84" t="n">
-        <v>32.96</v>
+        <v>61.61</v>
       </c>
       <c r="H84" t="n">
-        <v>1.8</v>
+        <v>5.46</v>
       </c>
       <c r="I84" t="n">
-        <v>5.78</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>7.91</v>
@@ -3300,29 +3300,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>21.89</v>
+        <v>34.755</v>
       </c>
       <c r="E85" t="n">
-        <v>23.3</v>
+        <v>42.1</v>
       </c>
       <c r="F85" t="n">
-        <v>65.67</v>
+        <v>139.02</v>
       </c>
       <c r="G85" t="n">
-        <v>69.90000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.23</v>
+        <v>29.38</v>
       </c>
       <c r="I85" t="n">
-        <v>6.44</v>
+        <v>21.13</v>
       </c>
       <c r="J85" t="n">
         <v>7.91</v>
@@ -3334,29 +3334,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E86" t="n">
-        <v>6.846</v>
+        <v>106.26</v>
       </c>
       <c r="F86" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G86" t="n">
-        <v>61.61</v>
+        <v>106.26</v>
       </c>
       <c r="H86" t="n">
-        <v>5.46</v>
+        <v>6.17</v>
       </c>
       <c r="I86" t="n">
-        <v>9.720000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J86" t="n">
         <v>7.91</v>
@@ -3708,29 +3708,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E97" t="n">
-        <v>40.65</v>
+        <v>10.642</v>
       </c>
       <c r="F97" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G97" t="n">
-        <v>162.6</v>
+        <v>31.93</v>
       </c>
       <c r="H97" t="n">
-        <v>23.58</v>
+        <v>0.77</v>
       </c>
       <c r="I97" t="n">
-        <v>16.96</v>
+        <v>2.47</v>
       </c>
       <c r="J97" t="n">
         <v>7.91</v>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E98" t="n">
-        <v>6.839</v>
+        <v>104.22</v>
       </c>
       <c r="F98" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G98" t="n">
-        <v>61.55</v>
+        <v>104.22</v>
       </c>
       <c r="H98" t="n">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="I98" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="J98" t="n">
         <v>7.91</v>
@@ -3810,29 +3810,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E100" t="n">
-        <v>104.22</v>
+        <v>40.65</v>
       </c>
       <c r="F100" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G100" t="n">
-        <v>104.22</v>
+        <v>162.6</v>
       </c>
       <c r="H100" t="n">
-        <v>4.13</v>
+        <v>23.58</v>
       </c>
       <c r="I100" t="n">
-        <v>4.13</v>
+        <v>16.96</v>
       </c>
       <c r="J100" t="n">
         <v>7.91</v>
@@ -3844,29 +3844,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E101" t="n">
-        <v>10.642</v>
+        <v>6.839</v>
       </c>
       <c r="F101" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G101" t="n">
-        <v>31.93</v>
+        <v>61.55</v>
       </c>
       <c r="H101" t="n">
-        <v>0.77</v>
+        <v>5.4</v>
       </c>
       <c r="I101" t="n">
-        <v>2.47</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>7.91</v>
@@ -4218,29 +4218,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E112" t="n">
-        <v>6.797</v>
+        <v>40</v>
       </c>
       <c r="F112" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G112" t="n">
-        <v>61.17</v>
+        <v>160</v>
       </c>
       <c r="H112" t="n">
-        <v>5.02</v>
+        <v>20.98</v>
       </c>
       <c r="I112" t="n">
-        <v>8.94</v>
+        <v>15.09</v>
       </c>
       <c r="J112" t="n">
         <v>7.91</v>
@@ -4252,29 +4252,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E113" t="n">
-        <v>103.56</v>
+        <v>10.568</v>
       </c>
       <c r="F113" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G113" t="n">
-        <v>103.56</v>
+        <v>31.7</v>
       </c>
       <c r="H113" t="n">
-        <v>3.47</v>
+        <v>0.54</v>
       </c>
       <c r="I113" t="n">
-        <v>3.47</v>
+        <v>1.73</v>
       </c>
       <c r="J113" t="n">
         <v>7.91</v>
@@ -4286,29 +4286,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E114" t="n">
-        <v>10.568</v>
+        <v>23.025</v>
       </c>
       <c r="F114" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G114" t="n">
-        <v>31.7</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>0.54</v>
+        <v>3.4</v>
       </c>
       <c r="I114" t="n">
-        <v>1.73</v>
+        <v>5.18</v>
       </c>
       <c r="J114" t="n">
         <v>7.91</v>
@@ -4320,29 +4320,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E115" t="n">
-        <v>23.025</v>
+        <v>6.797</v>
       </c>
       <c r="F115" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G115" t="n">
-        <v>69.06999999999999</v>
+        <v>61.17</v>
       </c>
       <c r="H115" t="n">
-        <v>3.4</v>
+        <v>5.02</v>
       </c>
       <c r="I115" t="n">
-        <v>5.18</v>
+        <v>8.94</v>
       </c>
       <c r="J115" t="n">
         <v>7.91</v>
@@ -4354,29 +4354,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E116" t="n">
-        <v>40</v>
+        <v>103.56</v>
       </c>
       <c r="F116" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G116" t="n">
-        <v>160</v>
+        <v>103.56</v>
       </c>
       <c r="H116" t="n">
-        <v>20.98</v>
+        <v>3.47</v>
       </c>
       <c r="I116" t="n">
-        <v>15.09</v>
+        <v>3.47</v>
       </c>
       <c r="J116" t="n">
         <v>7.91</v>
@@ -4558,29 +4558,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E122" t="n">
-        <v>40.395</v>
+        <v>11.038</v>
       </c>
       <c r="F122" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G122" t="n">
-        <v>161.58</v>
+        <v>33.11</v>
       </c>
       <c r="H122" t="n">
-        <v>22.56</v>
+        <v>1.95</v>
       </c>
       <c r="I122" t="n">
-        <v>16.23</v>
+        <v>6.26</v>
       </c>
       <c r="J122" t="n">
         <v>7.91</v>
@@ -4592,29 +4592,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E123" t="n">
-        <v>106</v>
+        <v>23.165</v>
       </c>
       <c r="F123" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G123" t="n">
-        <v>106</v>
+        <v>69.5</v>
       </c>
       <c r="H123" t="n">
-        <v>5.91</v>
+        <v>3.83</v>
       </c>
       <c r="I123" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="J123" t="n">
         <v>7.91</v>
@@ -4626,29 +4626,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E124" t="n">
-        <v>23.165</v>
+        <v>6.901</v>
       </c>
       <c r="F124" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G124" t="n">
-        <v>69.5</v>
+        <v>62.11</v>
       </c>
       <c r="H124" t="n">
-        <v>3.83</v>
+        <v>5.96</v>
       </c>
       <c r="I124" t="n">
-        <v>5.83</v>
+        <v>10.61</v>
       </c>
       <c r="J124" t="n">
         <v>7.91</v>
@@ -4660,29 +4660,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E125" t="n">
-        <v>6.901</v>
+        <v>40.395</v>
       </c>
       <c r="F125" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G125" t="n">
-        <v>62.11</v>
+        <v>161.58</v>
       </c>
       <c r="H125" t="n">
-        <v>5.96</v>
+        <v>22.56</v>
       </c>
       <c r="I125" t="n">
-        <v>10.61</v>
+        <v>16.23</v>
       </c>
       <c r="J125" t="n">
         <v>7.91</v>
@@ -4694,29 +4694,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E126" t="n">
-        <v>11.038</v>
+        <v>106</v>
       </c>
       <c r="F126" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G126" t="n">
-        <v>33.11</v>
+        <v>106</v>
       </c>
       <c r="H126" t="n">
-        <v>1.95</v>
+        <v>5.91</v>
       </c>
       <c r="I126" t="n">
-        <v>6.26</v>
+        <v>5.9</v>
       </c>
       <c r="J126" t="n">
         <v>7.91</v>
@@ -4898,29 +4898,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E132" t="n">
-        <v>23.18</v>
+        <v>104.02</v>
       </c>
       <c r="F132" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G132" t="n">
-        <v>69.54000000000001</v>
+        <v>104.02</v>
       </c>
       <c r="H132" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="I132" t="n">
-        <v>5.89</v>
+        <v>3.93</v>
       </c>
       <c r="J132" t="n">
         <v>7.91</v>
@@ -4932,29 +4932,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E133" t="n">
-        <v>6.895</v>
+        <v>23.18</v>
       </c>
       <c r="F133" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G133" t="n">
-        <v>62.05</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>5.9</v>
+        <v>3.87</v>
       </c>
       <c r="I133" t="n">
-        <v>10.51</v>
+        <v>5.89</v>
       </c>
       <c r="J133" t="n">
         <v>7.91</v>
@@ -4966,29 +4966,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D134" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E134" t="n">
-        <v>11.516</v>
+        <v>6.895</v>
       </c>
       <c r="F134" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G134" t="n">
-        <v>34.55</v>
+        <v>62.05</v>
       </c>
       <c r="H134" t="n">
-        <v>3.39</v>
+        <v>5.9</v>
       </c>
       <c r="I134" t="n">
-        <v>10.88</v>
+        <v>10.51</v>
       </c>
       <c r="J134" t="n">
         <v>7.91</v>
@@ -5000,29 +5000,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>100.09</v>
+        <v>10.387</v>
       </c>
       <c r="E135" t="n">
-        <v>104.02</v>
+        <v>11.516</v>
       </c>
       <c r="F135" t="n">
-        <v>100.09</v>
+        <v>31.16</v>
       </c>
       <c r="G135" t="n">
-        <v>104.02</v>
+        <v>34.55</v>
       </c>
       <c r="H135" t="n">
-        <v>3.93</v>
+        <v>3.39</v>
       </c>
       <c r="I135" t="n">
-        <v>3.93</v>
+        <v>10.88</v>
       </c>
       <c r="J135" t="n">
         <v>7.91</v>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E137" t="n">
-        <v>6.927</v>
+        <v>11.728</v>
       </c>
       <c r="F137" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G137" t="n">
-        <v>62.34</v>
+        <v>35.18</v>
       </c>
       <c r="H137" t="n">
-        <v>6.19</v>
+        <v>4.02</v>
       </c>
       <c r="I137" t="n">
-        <v>11.02</v>
+        <v>12.9</v>
       </c>
       <c r="J137" t="n">
         <v>7.91</v>
@@ -5102,29 +5102,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E138" t="n">
-        <v>104.76</v>
+        <v>40.61</v>
       </c>
       <c r="F138" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G138" t="n">
-        <v>104.76</v>
+        <v>162.44</v>
       </c>
       <c r="H138" t="n">
-        <v>4.67</v>
+        <v>23.42</v>
       </c>
       <c r="I138" t="n">
-        <v>4.67</v>
+        <v>16.85</v>
       </c>
       <c r="J138" t="n">
         <v>7.91</v>
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E139" t="n">
-        <v>40.61</v>
+        <v>23.3</v>
       </c>
       <c r="F139" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G139" t="n">
-        <v>162.44</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>23.42</v>
+        <v>4.23</v>
       </c>
       <c r="I139" t="n">
-        <v>16.85</v>
+        <v>6.44</v>
       </c>
       <c r="J139" t="n">
         <v>7.91</v>
@@ -5170,29 +5170,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E140" t="n">
-        <v>23.3</v>
+        <v>6.927</v>
       </c>
       <c r="F140" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G140" t="n">
-        <v>69.90000000000001</v>
+        <v>62.34</v>
       </c>
       <c r="H140" t="n">
-        <v>4.23</v>
+        <v>6.19</v>
       </c>
       <c r="I140" t="n">
-        <v>6.44</v>
+        <v>11.02</v>
       </c>
       <c r="J140" t="n">
         <v>7.91</v>
@@ -5204,29 +5204,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E141" t="n">
-        <v>11.728</v>
+        <v>104.76</v>
       </c>
       <c r="F141" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G141" t="n">
-        <v>35.18</v>
+        <v>104.76</v>
       </c>
       <c r="H141" t="n">
-        <v>4.02</v>
+        <v>4.67</v>
       </c>
       <c r="I141" t="n">
-        <v>12.9</v>
+        <v>4.67</v>
       </c>
       <c r="J141" t="n">
         <v>7.91</v>
@@ -5408,29 +5408,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E147" t="n">
-        <v>101.7</v>
+        <v>38.955</v>
       </c>
       <c r="F147" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G147" t="n">
-        <v>101.7</v>
+        <v>155.82</v>
       </c>
       <c r="H147" t="n">
-        <v>1.61</v>
+        <v>16.8</v>
       </c>
       <c r="I147" t="n">
-        <v>1.61</v>
+        <v>12.08</v>
       </c>
       <c r="J147" t="n">
         <v>7.91</v>
@@ -5442,29 +5442,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>10.387</v>
+        <v>100.09</v>
       </c>
       <c r="E148" t="n">
-        <v>11.162</v>
+        <v>101.7</v>
       </c>
       <c r="F148" t="n">
-        <v>31.16</v>
+        <v>100.09</v>
       </c>
       <c r="G148" t="n">
-        <v>33.49</v>
+        <v>101.7</v>
       </c>
       <c r="H148" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="I148" t="n">
-        <v>7.48</v>
+        <v>1.61</v>
       </c>
       <c r="J148" t="n">
         <v>7.91</v>
@@ -5476,29 +5476,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E149" t="n">
-        <v>22.755</v>
+        <v>11.162</v>
       </c>
       <c r="F149" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G149" t="n">
-        <v>68.27</v>
+        <v>33.49</v>
       </c>
       <c r="H149" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="I149" t="n">
-        <v>3.96</v>
+        <v>7.48</v>
       </c>
       <c r="J149" t="n">
         <v>7.91</v>
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>6.239</v>
+        <v>21.89</v>
       </c>
       <c r="E150" t="n">
-        <v>6.826</v>
+        <v>22.755</v>
       </c>
       <c r="F150" t="n">
-        <v>56.15</v>
+        <v>65.67</v>
       </c>
       <c r="G150" t="n">
-        <v>61.43</v>
+        <v>68.27</v>
       </c>
       <c r="H150" t="n">
-        <v>5.28</v>
+        <v>2.6</v>
       </c>
       <c r="I150" t="n">
-        <v>9.4</v>
+        <v>3.96</v>
       </c>
       <c r="J150" t="n">
         <v>7.91</v>
@@ -5544,29 +5544,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E151" t="n">
-        <v>38.955</v>
+        <v>6.826</v>
       </c>
       <c r="F151" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G151" t="n">
-        <v>155.82</v>
+        <v>61.43</v>
       </c>
       <c r="H151" t="n">
-        <v>16.8</v>
+        <v>5.28</v>
       </c>
       <c r="I151" t="n">
-        <v>12.08</v>
+        <v>9.4</v>
       </c>
       <c r="J151" t="n">
         <v>7.91</v>
@@ -5578,29 +5578,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D152" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E152" t="n">
-        <v>39.915</v>
+        <v>6.893</v>
       </c>
       <c r="F152" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G152" t="n">
-        <v>159.66</v>
+        <v>62.04</v>
       </c>
       <c r="H152" t="n">
-        <v>20.64</v>
+        <v>5.89</v>
       </c>
       <c r="I152" t="n">
-        <v>14.85</v>
+        <v>10.49</v>
       </c>
       <c r="J152" t="n">
         <v>7.91</v>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E153" t="n">
-        <v>23.045</v>
+        <v>104.12</v>
       </c>
       <c r="F153" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G153" t="n">
-        <v>69.14</v>
+        <v>104.12</v>
       </c>
       <c r="H153" t="n">
-        <v>3.47</v>
+        <v>4.03</v>
       </c>
       <c r="I153" t="n">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="J153" t="n">
         <v>7.91</v>
@@ -5646,29 +5646,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E154" t="n">
-        <v>11.034</v>
+        <v>23.045</v>
       </c>
       <c r="F154" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G154" t="n">
-        <v>33.1</v>
+        <v>69.14</v>
       </c>
       <c r="H154" t="n">
-        <v>1.94</v>
+        <v>3.47</v>
       </c>
       <c r="I154" t="n">
-        <v>6.23</v>
+        <v>5.28</v>
       </c>
       <c r="J154" t="n">
         <v>7.91</v>
@@ -5680,29 +5680,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E155" t="n">
-        <v>104.12</v>
+        <v>39.915</v>
       </c>
       <c r="F155" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G155" t="n">
-        <v>104.12</v>
+        <v>159.66</v>
       </c>
       <c r="H155" t="n">
-        <v>4.03</v>
+        <v>20.64</v>
       </c>
       <c r="I155" t="n">
-        <v>4.03</v>
+        <v>14.85</v>
       </c>
       <c r="J155" t="n">
         <v>7.91</v>
@@ -5714,29 +5714,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E156" t="n">
-        <v>6.893</v>
+        <v>11.034</v>
       </c>
       <c r="F156" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G156" t="n">
-        <v>62.04</v>
+        <v>33.1</v>
       </c>
       <c r="H156" t="n">
-        <v>5.89</v>
+        <v>1.94</v>
       </c>
       <c r="I156" t="n">
-        <v>10.49</v>
+        <v>6.23</v>
       </c>
       <c r="J156" t="n">
         <v>7.91</v>
@@ -5748,29 +5748,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D157" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E157" t="n">
-        <v>40.015</v>
+        <v>6.913</v>
       </c>
       <c r="F157" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G157" t="n">
-        <v>160.06</v>
+        <v>62.22</v>
       </c>
       <c r="H157" t="n">
-        <v>21.04</v>
+        <v>6.07</v>
       </c>
       <c r="I157" t="n">
-        <v>15.13</v>
+        <v>10.81</v>
       </c>
       <c r="J157" t="n">
         <v>7.91</v>
@@ -5782,29 +5782,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>10.387</v>
+        <v>34.755</v>
       </c>
       <c r="E158" t="n">
-        <v>10.92</v>
+        <v>40.015</v>
       </c>
       <c r="F158" t="n">
-        <v>31.16</v>
+        <v>139.02</v>
       </c>
       <c r="G158" t="n">
-        <v>32.76</v>
+        <v>160.06</v>
       </c>
       <c r="H158" t="n">
-        <v>1.6</v>
+        <v>21.04</v>
       </c>
       <c r="I158" t="n">
-        <v>5.13</v>
+        <v>15.13</v>
       </c>
       <c r="J158" t="n">
         <v>7.91</v>
@@ -5816,29 +5816,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E159" t="n">
-        <v>23.08</v>
+        <v>10.92</v>
       </c>
       <c r="F159" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G159" t="n">
-        <v>69.23999999999999</v>
+        <v>32.76</v>
       </c>
       <c r="H159" t="n">
-        <v>3.57</v>
+        <v>1.6</v>
       </c>
       <c r="I159" t="n">
-        <v>5.44</v>
+        <v>5.13</v>
       </c>
       <c r="J159" t="n">
         <v>7.91</v>
@@ -5850,29 +5850,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E160" t="n">
-        <v>104.5</v>
+        <v>23.08</v>
       </c>
       <c r="F160" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G160" t="n">
-        <v>104.5</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H160" t="n">
-        <v>4.41</v>
+        <v>3.57</v>
       </c>
       <c r="I160" t="n">
-        <v>4.41</v>
+        <v>5.44</v>
       </c>
       <c r="J160" t="n">
         <v>7.91</v>
@@ -5884,29 +5884,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E161" t="n">
-        <v>6.913</v>
+        <v>104.5</v>
       </c>
       <c r="F161" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G161" t="n">
-        <v>62.22</v>
+        <v>104.5</v>
       </c>
       <c r="H161" t="n">
-        <v>6.07</v>
+        <v>4.41</v>
       </c>
       <c r="I161" t="n">
-        <v>10.81</v>
+        <v>4.41</v>
       </c>
       <c r="J161" t="n">
         <v>7.91</v>
@@ -5918,29 +5918,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D162" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E162" t="n">
-        <v>103.84</v>
+        <v>6.927</v>
       </c>
       <c r="F162" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G162" t="n">
-        <v>103.84</v>
+        <v>62.34</v>
       </c>
       <c r="H162" t="n">
-        <v>3.75</v>
+        <v>6.19</v>
       </c>
       <c r="I162" t="n">
-        <v>3.75</v>
+        <v>11.02</v>
       </c>
       <c r="J162" t="n">
         <v>7.91</v>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E163" t="n">
-        <v>10.748</v>
+        <v>23.01</v>
       </c>
       <c r="F163" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G163" t="n">
-        <v>32.24</v>
+        <v>69.03</v>
       </c>
       <c r="H163" t="n">
-        <v>1.08</v>
+        <v>3.36</v>
       </c>
       <c r="I163" t="n">
-        <v>3.47</v>
+        <v>5.12</v>
       </c>
       <c r="J163" t="n">
         <v>7.91</v>
@@ -5986,29 +5986,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E164" t="n">
-        <v>6.927</v>
+        <v>103.84</v>
       </c>
       <c r="F164" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G164" t="n">
-        <v>62.34</v>
+        <v>103.84</v>
       </c>
       <c r="H164" t="n">
-        <v>6.19</v>
+        <v>3.75</v>
       </c>
       <c r="I164" t="n">
-        <v>11.02</v>
+        <v>3.75</v>
       </c>
       <c r="J164" t="n">
         <v>7.91</v>
@@ -6020,29 +6020,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E165" t="n">
-        <v>23.01</v>
+        <v>10.748</v>
       </c>
       <c r="F165" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G165" t="n">
-        <v>69.03</v>
+        <v>32.24</v>
       </c>
       <c r="H165" t="n">
-        <v>3.36</v>
+        <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>5.12</v>
+        <v>3.47</v>
       </c>
       <c r="J165" t="n">
         <v>7.91</v>
@@ -6088,29 +6088,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>34.755</v>
+        <v>100.09</v>
       </c>
       <c r="E167" t="n">
-        <v>38.98</v>
+        <v>103.98</v>
       </c>
       <c r="F167" t="n">
-        <v>139.02</v>
+        <v>100.09</v>
       </c>
       <c r="G167" t="n">
-        <v>155.92</v>
+        <v>103.98</v>
       </c>
       <c r="H167" t="n">
-        <v>16.9</v>
+        <v>3.89</v>
       </c>
       <c r="I167" t="n">
-        <v>12.16</v>
+        <v>3.89</v>
       </c>
       <c r="J167" t="n">
         <v>7.91</v>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D168" t="n">
-        <v>21.89</v>
+        <v>6.239</v>
       </c>
       <c r="E168" t="n">
-        <v>22.92</v>
+        <v>6.911</v>
       </c>
       <c r="F168" t="n">
-        <v>65.67</v>
+        <v>56.15</v>
       </c>
       <c r="G168" t="n">
-        <v>68.76000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="H168" t="n">
-        <v>3.09</v>
+        <v>6.05</v>
       </c>
       <c r="I168" t="n">
-        <v>4.71</v>
+        <v>10.77</v>
       </c>
       <c r="J168" t="n">
         <v>7.91</v>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>6.239</v>
+        <v>10.387</v>
       </c>
       <c r="E169" t="n">
-        <v>6.911</v>
+        <v>10.726</v>
       </c>
       <c r="F169" t="n">
-        <v>56.15</v>
+        <v>31.16</v>
       </c>
       <c r="G169" t="n">
-        <v>62.2</v>
+        <v>32.18</v>
       </c>
       <c r="H169" t="n">
-        <v>6.05</v>
+        <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>10.77</v>
+        <v>3.27</v>
       </c>
       <c r="J169" t="n">
         <v>7.91</v>
@@ -6190,29 +6190,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C170" t="n">
         <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E170" t="n">
-        <v>10.726</v>
+        <v>22.92</v>
       </c>
       <c r="F170" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G170" t="n">
-        <v>32.18</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H170" t="n">
-        <v>1.02</v>
+        <v>3.09</v>
       </c>
       <c r="I170" t="n">
-        <v>3.27</v>
+        <v>4.71</v>
       </c>
       <c r="J170" t="n">
         <v>7.91</v>
@@ -6224,29 +6224,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E171" t="n">
-        <v>103.98</v>
+        <v>38.98</v>
       </c>
       <c r="F171" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G171" t="n">
-        <v>103.98</v>
+        <v>155.92</v>
       </c>
       <c r="H171" t="n">
-        <v>3.89</v>
+        <v>16.9</v>
       </c>
       <c r="I171" t="n">
-        <v>3.89</v>
+        <v>12.16</v>
       </c>
       <c r="J171" t="n">
         <v>7.91</v>
@@ -6598,29 +6598,29 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D182" t="n">
-        <v>100.09</v>
+        <v>6.239</v>
       </c>
       <c r="E182" t="n">
-        <v>100.14</v>
+        <v>6.848</v>
       </c>
       <c r="F182" t="n">
-        <v>100.09</v>
+        <v>56.15</v>
       </c>
       <c r="G182" t="n">
-        <v>100.14</v>
+        <v>61.63</v>
       </c>
       <c r="H182" t="n">
-        <v>0.05</v>
+        <v>5.48</v>
       </c>
       <c r="I182" t="n">
-        <v>0.05</v>
+        <v>9.76</v>
       </c>
       <c r="J182" t="n">
         <v>7.91</v>
@@ -6632,29 +6632,29 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C183" t="n">
         <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>10.387</v>
+        <v>21.89</v>
       </c>
       <c r="E183" t="n">
-        <v>10.776</v>
+        <v>22.835</v>
       </c>
       <c r="F183" t="n">
-        <v>31.16</v>
+        <v>65.67</v>
       </c>
       <c r="G183" t="n">
-        <v>32.33</v>
+        <v>68.5</v>
       </c>
       <c r="H183" t="n">
-        <v>1.17</v>
+        <v>2.83</v>
       </c>
       <c r="I183" t="n">
-        <v>3.75</v>
+        <v>4.31</v>
       </c>
       <c r="J183" t="n">
         <v>7.91</v>
@@ -6700,29 +6700,29 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E185" t="n">
-        <v>22.835</v>
+        <v>10.776</v>
       </c>
       <c r="F185" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G185" t="n">
-        <v>68.5</v>
+        <v>32.33</v>
       </c>
       <c r="H185" t="n">
-        <v>2.83</v>
+        <v>1.17</v>
       </c>
       <c r="I185" t="n">
-        <v>4.31</v>
+        <v>3.75</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -6734,29 +6734,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E186" t="n">
-        <v>6.848</v>
+        <v>100.14</v>
       </c>
       <c r="F186" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G186" t="n">
-        <v>61.63</v>
+        <v>100.14</v>
       </c>
       <c r="H186" t="n">
-        <v>5.48</v>
+        <v>0.05</v>
       </c>
       <c r="I186" t="n">
-        <v>9.76</v>
+        <v>0.05</v>
       </c>
       <c r="J186" t="n">
         <v>7.91</v>
@@ -7108,29 +7108,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>21.89</v>
+        <v>10.387</v>
       </c>
       <c r="E197" t="n">
-        <v>22.6</v>
+        <v>11.022</v>
       </c>
       <c r="F197" t="n">
-        <v>65.67</v>
+        <v>31.16</v>
       </c>
       <c r="G197" t="n">
-        <v>67.8</v>
+        <v>33.07</v>
       </c>
       <c r="H197" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="I197" t="n">
-        <v>3.24</v>
+        <v>6.13</v>
       </c>
       <c r="J197" t="n">
         <v>7.91</v>
@@ -7142,29 +7142,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E198" t="n">
-        <v>102.48</v>
+        <v>38.565</v>
       </c>
       <c r="F198" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G198" t="n">
-        <v>102.48</v>
+        <v>154.26</v>
       </c>
       <c r="H198" t="n">
-        <v>2.39</v>
+        <v>15.24</v>
       </c>
       <c r="I198" t="n">
-        <v>2.39</v>
+        <v>10.96</v>
       </c>
       <c r="J198" t="n">
         <v>7.91</v>
@@ -7176,29 +7176,29 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>6.239</v>
+        <v>100.09</v>
       </c>
       <c r="E199" t="n">
-        <v>6.909</v>
+        <v>102.48</v>
       </c>
       <c r="F199" t="n">
-        <v>56.15</v>
+        <v>100.09</v>
       </c>
       <c r="G199" t="n">
-        <v>62.18</v>
+        <v>102.48</v>
       </c>
       <c r="H199" t="n">
-        <v>6.03</v>
+        <v>2.39</v>
       </c>
       <c r="I199" t="n">
-        <v>10.74</v>
+        <v>2.39</v>
       </c>
       <c r="J199" t="n">
         <v>7.91</v>
@@ -7210,29 +7210,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>34.755</v>
+        <v>21.89</v>
       </c>
       <c r="E200" t="n">
-        <v>38.565</v>
+        <v>22.6</v>
       </c>
       <c r="F200" t="n">
-        <v>139.02</v>
+        <v>65.67</v>
       </c>
       <c r="G200" t="n">
-        <v>154.26</v>
+        <v>67.8</v>
       </c>
       <c r="H200" t="n">
-        <v>15.24</v>
+        <v>2.13</v>
       </c>
       <c r="I200" t="n">
-        <v>10.96</v>
+        <v>3.24</v>
       </c>
       <c r="J200" t="n">
         <v>7.91</v>
@@ -7244,29 +7244,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D201" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E201" t="n">
-        <v>11.022</v>
+        <v>6.909</v>
       </c>
       <c r="F201" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G201" t="n">
-        <v>33.07</v>
+        <v>62.18</v>
       </c>
       <c r="H201" t="n">
-        <v>1.91</v>
+        <v>6.03</v>
       </c>
       <c r="I201" t="n">
-        <v>6.13</v>
+        <v>10.74</v>
       </c>
       <c r="J201" t="n">
         <v>7.91</v>
@@ -7448,29 +7448,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PINDIA</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>100.09</v>
+        <v>21.89</v>
       </c>
       <c r="E207" t="n">
-        <v>99.90000000000001</v>
+        <v>22.725</v>
       </c>
       <c r="F207" t="n">
-        <v>100.09</v>
+        <v>65.67</v>
       </c>
       <c r="G207" t="n">
-        <v>99.90000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.19</v>
+        <v>2.51</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.19</v>
+        <v>3.82</v>
       </c>
       <c r="J207" t="n">
         <v>7.91</v>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EFENSE</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D208" t="n">
-        <v>10.387</v>
+        <v>6.239</v>
       </c>
       <c r="E208" t="n">
-        <v>11.172</v>
+        <v>6.865</v>
       </c>
       <c r="F208" t="n">
-        <v>31.16</v>
+        <v>56.15</v>
       </c>
       <c r="G208" t="n">
-        <v>33.52</v>
+        <v>61.79</v>
       </c>
       <c r="H208" t="n">
-        <v>2.36</v>
+        <v>5.64</v>
       </c>
       <c r="I208" t="n">
-        <v>7.57</v>
+        <v>10.04</v>
       </c>
       <c r="J208" t="n">
         <v>7.91</v>
@@ -7516,29 +7516,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IWSC</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
-        <v>6.239</v>
+        <v>34.755</v>
       </c>
       <c r="E209" t="n">
-        <v>6.865</v>
+        <v>37.82</v>
       </c>
       <c r="F209" t="n">
-        <v>56.15</v>
+        <v>139.02</v>
       </c>
       <c r="G209" t="n">
-        <v>61.79</v>
+        <v>151.28</v>
       </c>
       <c r="H209" t="n">
-        <v>5.64</v>
+        <v>12.26</v>
       </c>
       <c r="I209" t="n">
-        <v>10.04</v>
+        <v>8.82</v>
       </c>
       <c r="J209" t="n">
         <v>7.91</v>
@@ -7550,29 +7550,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E210" t="n">
-        <v>22.725</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F210" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G210" t="n">
-        <v>68.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H210" t="n">
-        <v>2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="I210" t="n">
-        <v>3.82</v>
+        <v>-0.19</v>
       </c>
       <c r="J210" t="n">
         <v>7.91</v>
@@ -7584,29 +7584,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>EFENSE</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>34.755</v>
+        <v>10.387</v>
       </c>
       <c r="E211" t="n">
-        <v>37.82</v>
+        <v>11.172</v>
       </c>
       <c r="F211" t="n">
-        <v>139.02</v>
+        <v>31.16</v>
       </c>
       <c r="G211" t="n">
-        <v>151.28</v>
+        <v>33.52</v>
       </c>
       <c r="H211" t="n">
-        <v>12.26</v>
+        <v>2.36</v>
       </c>
       <c r="I211" t="n">
-        <v>8.82</v>
+        <v>7.57</v>
       </c>
       <c r="J211" t="n">
         <v>7.91</v>
@@ -7788,29 +7788,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PAASI</t>
+          <t>IWSC</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>34.755</v>
+        <v>6.239</v>
       </c>
       <c r="E217" t="n">
-        <v>36.75</v>
+        <v>6.864</v>
       </c>
       <c r="F217" t="n">
-        <v>139.02</v>
+        <v>56.15</v>
       </c>
       <c r="G217" t="n">
-        <v>147</v>
+        <v>61.78</v>
       </c>
       <c r="H217" t="n">
-        <v>7.98</v>
+        <v>5.63</v>
       </c>
       <c r="I217" t="n">
-        <v>5.74</v>
+        <v>10.03</v>
       </c>
       <c r="J217" t="n">
         <v>7.91</v>
@@ -7822,29 +7822,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PUST</t>
+          <t>PAASI</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>100.09</v>
+        <v>34.755</v>
       </c>
       <c r="E218" t="n">
-        <v>98.02</v>
+        <v>36.75</v>
       </c>
       <c r="F218" t="n">
-        <v>100.09</v>
+        <v>139.02</v>
       </c>
       <c r="G218" t="n">
-        <v>98.02</v>
+        <v>147</v>
       </c>
       <c r="H218" t="n">
-        <v>-2.07</v>
+        <v>7.98</v>
       </c>
       <c r="I218" t="n">
-        <v>-2.07</v>
+        <v>5.74</v>
       </c>
       <c r="J218" t="n">
         <v>7.91</v>
@@ -7856,29 +7856,29 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PINDIA</t>
+          <t>PUST</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>21.89</v>
+        <v>100.09</v>
       </c>
       <c r="E219" t="n">
-        <v>23.175</v>
+        <v>98.02</v>
       </c>
       <c r="F219" t="n">
-        <v>65.67</v>
+        <v>100.09</v>
       </c>
       <c r="G219" t="n">
-        <v>69.53</v>
+        <v>98.02</v>
       </c>
       <c r="H219" t="n">
-        <v>3.86</v>
+        <v>-2.07</v>
       </c>
       <c r="I219" t="n"